--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,52 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>54.4 → 43.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>54.4</t>
+  </si>
+  <si>
+    <t>43.6</t>
+  </si>
+  <si>
+    <t>58.6 → 50.0</t>
+  </si>
+  <si>
+    <t>58.6</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>51.0 → 42.9</t>
+  </si>
+  <si>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>42.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,14 +425,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -902,58 +948,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1246.5</v>
+        <v>1225.2</v>
       </c>
       <c r="D2">
-        <v>-0.62</v>
+        <v>-1.71</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1246.5</v>
+        <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-34.49</v>
+        <v>-35.61</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-2.91</v>
+        <v>-3.43</v>
       </c>
       <c r="J2">
-        <v>-5.9</v>
+        <v>-7.28</v>
       </c>
       <c r="K2">
-        <v>-8.1</v>
+        <v>-9.18</v>
       </c>
       <c r="L2">
-        <v>-32.24</v>
+        <v>-33.35</v>
       </c>
       <c r="M2">
-        <v>-12.02</v>
+        <v>-12.28</v>
       </c>
       <c r="N2">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2">
-        <v>1258</v>
+        <v>1249.3</v>
       </c>
       <c r="Q2">
-        <v>1286.72</v>
+        <v>1282.15</v>
       </c>
       <c r="R2">
-        <v>1333.09</v>
+        <v>1329.65</v>
       </c>
       <c r="S2">
-        <v>1477.22</v>
+        <v>1473.98</v>
       </c>
       <c r="T2">
-        <v>-15.62</v>
+        <v>-16.88</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +1014,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.95</v>
+        <v>27.67</v>
       </c>
       <c r="Z2">
-        <v>-22.76</v>
+        <v>-24.82</v>
       </c>
       <c r="AA2">
-        <v>-20.24</v>
+        <v>-21.16</v>
       </c>
       <c r="AB2">
-        <v>-2.52</v>
+        <v>-3.66</v>
       </c>
       <c r="AC2">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>6.32</v>
+        <v>2.07</v>
       </c>
       <c r="AE2">
-        <v>21.03</v>
+        <v>23.87</v>
       </c>
       <c r="AF2">
-        <v>-3.12</v>
+        <v>77.73</v>
       </c>
       <c r="AG2">
-        <v>1334.23</v>
+        <v>1334.85</v>
       </c>
       <c r="AH2">
-        <v>1239.2</v>
+        <v>1229.44</v>
       </c>
       <c r="AI2">
         <v>1304.25</v>
@@ -1004,7 +1050,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>34.69</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1061,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3060</v>
+        <v>2928.6</v>
       </c>
       <c r="D3">
-        <v>-0.5600000000000001</v>
+        <v>-4.29</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1073,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-4.74</v>
+        <v>-8.83</v>
       </c>
       <c r="H3">
-        <v>74.06</v>
+        <v>66.59</v>
       </c>
       <c r="I3">
-        <v>4.15</v>
+        <v>-0.73</v>
       </c>
       <c r="J3">
-        <v>3.21</v>
+        <v>-3.51</v>
       </c>
       <c r="K3">
-        <v>3.99</v>
+        <v>-0.51</v>
       </c>
       <c r="L3">
-        <v>32.43</v>
+        <v>25.2</v>
       </c>
       <c r="M3">
-        <v>14.9</v>
+        <v>14.12</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>3029</v>
+        <v>3024.72</v>
       </c>
       <c r="Q3">
-        <v>3007.45</v>
+        <v>3003.51</v>
       </c>
       <c r="R3">
-        <v>3049.14</v>
+        <v>3043.58</v>
       </c>
       <c r="S3">
-        <v>2527.39</v>
+        <v>2530.47</v>
       </c>
       <c r="T3">
-        <v>21.07</v>
+        <v>15.73</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,34 +1127,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>54.4</v>
+        <v>43.64</v>
       </c>
       <c r="Z3">
-        <v>-1.71</v>
+        <v>-8.17</v>
       </c>
       <c r="AA3">
-        <v>-13.31</v>
+        <v>-12.28</v>
       </c>
       <c r="AB3">
-        <v>11.6</v>
+        <v>4.12</v>
       </c>
       <c r="AC3">
-        <v>67.51000000000001</v>
+        <v>51.4</v>
       </c>
       <c r="AD3">
-        <v>57.13</v>
+        <v>58.92</v>
       </c>
       <c r="AE3">
-        <v>82.89</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="AF3">
-        <v>-12.13</v>
+        <v>-14.69</v>
       </c>
       <c r="AG3">
-        <v>3196.42</v>
+        <v>3195.75</v>
       </c>
       <c r="AH3">
-        <v>2818.47</v>
+        <v>2811.27</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1117,7 +1163,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>31.09</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1174,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1281.3</v>
+        <v>1255</v>
       </c>
       <c r="D4">
-        <v>-1.37</v>
+        <v>-2.05</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,25 +1186,25 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-20.14</v>
+        <v>-21.78</v>
       </c>
       <c r="H4">
-        <v>65.8</v>
+        <v>62.4</v>
       </c>
       <c r="I4">
-        <v>-1.54</v>
+        <v>-2.56</v>
       </c>
       <c r="J4">
-        <v>-2.86</v>
+        <v>-6.9</v>
       </c>
       <c r="K4">
-        <v>-13.58</v>
+        <v>-15.35</v>
       </c>
       <c r="L4">
-        <v>35.77</v>
+        <v>30.27</v>
       </c>
       <c r="M4">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="N4">
         <v>66</v>
@@ -1167,19 +1213,19 @@
         <v>68</v>
       </c>
       <c r="P4">
-        <v>1295.08</v>
+        <v>1288.48</v>
       </c>
       <c r="Q4">
-        <v>1298.36</v>
+        <v>1294.73</v>
       </c>
       <c r="R4">
-        <v>1383.52</v>
+        <v>1377.63</v>
       </c>
       <c r="S4">
-        <v>1183.22</v>
+        <v>1184.32</v>
       </c>
       <c r="T4">
-        <v>8.289999999999999</v>
+        <v>5.97</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,34 +1240,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>43.14</v>
+        <v>39.52</v>
       </c>
       <c r="Z4">
-        <v>-22.64</v>
+        <v>-24.25</v>
       </c>
       <c r="AA4">
-        <v>-28.29</v>
+        <v>-27.48</v>
       </c>
       <c r="AB4">
-        <v>5.64</v>
+        <v>3.23</v>
       </c>
       <c r="AC4">
-        <v>86.77</v>
+        <v>71.48</v>
       </c>
       <c r="AD4">
-        <v>91.45999999999999</v>
+        <v>83.91</v>
       </c>
       <c r="AE4">
-        <v>38.18</v>
+        <v>38.66</v>
       </c>
       <c r="AF4">
-        <v>-33.36</v>
+        <v>-33.12</v>
       </c>
       <c r="AG4">
-        <v>1350.01</v>
+        <v>1347.91</v>
       </c>
       <c r="AH4">
-        <v>1246.7</v>
+        <v>1241.54</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1230,7 +1276,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>19.05</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1287,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1764.6</v>
+        <v>1713.8</v>
       </c>
       <c r="D5">
-        <v>-0.19</v>
+        <v>-2.88</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,46 +1299,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-6.3</v>
+        <v>-9</v>
       </c>
       <c r="H5">
-        <v>35.93</v>
+        <v>32.02</v>
       </c>
       <c r="I5">
-        <v>3.36</v>
+        <v>1.15</v>
       </c>
       <c r="J5">
-        <v>6.43</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K5">
-        <v>-2.23</v>
+        <v>-5.94</v>
       </c>
       <c r="L5">
-        <v>28.33</v>
+        <v>23.89</v>
       </c>
       <c r="M5">
-        <v>19.49</v>
+        <v>18.11</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P5">
-        <v>1742.38</v>
+        <v>1746.28</v>
       </c>
       <c r="Q5">
-        <v>1699.35</v>
+        <v>1700.05</v>
       </c>
       <c r="R5">
-        <v>1735.62</v>
+        <v>1732.61</v>
       </c>
       <c r="S5">
-        <v>1608.53</v>
+        <v>1609.6</v>
       </c>
       <c r="T5">
-        <v>9.699999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1307,34 +1353,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>58.61</v>
+        <v>49.99</v>
       </c>
       <c r="Z5">
-        <v>7.32</v>
+        <v>6.21</v>
       </c>
       <c r="AA5">
-        <v>-6.58</v>
+        <v>-4.02</v>
       </c>
       <c r="AB5">
-        <v>13.9</v>
+        <v>10.23</v>
       </c>
       <c r="AC5">
-        <v>96.45999999999999</v>
+        <v>84.62</v>
       </c>
       <c r="AD5">
-        <v>97.20999999999999</v>
+        <v>93.22</v>
       </c>
       <c r="AE5">
-        <v>38.03</v>
+        <v>40.86</v>
       </c>
       <c r="AF5">
-        <v>-31.15</v>
+        <v>-33.47</v>
       </c>
       <c r="AG5">
-        <v>1780.58</v>
+        <v>1781.52</v>
       </c>
       <c r="AH5">
-        <v>1618.13</v>
+        <v>1618.57</v>
       </c>
       <c r="AI5">
         <v>1647.25</v>
@@ -1343,7 +1389,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>27.05</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1400,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>209.97</v>
+        <v>202</v>
       </c>
       <c r="D6">
-        <v>-1.65</v>
+        <v>-3.8</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,25 +1412,25 @@
         <v>124.93</v>
       </c>
       <c r="G6">
-        <v>-15.64</v>
+        <v>-18.85</v>
       </c>
       <c r="H6">
-        <v>68.06999999999999</v>
+        <v>61.69</v>
       </c>
       <c r="I6">
-        <v>1.34</v>
+        <v>-1.22</v>
       </c>
       <c r="J6">
-        <v>1.88</v>
+        <v>-1.58</v>
       </c>
       <c r="K6">
-        <v>-4.78</v>
+        <v>-9.25</v>
       </c>
       <c r="L6">
-        <v>63.11</v>
+        <v>59.19</v>
       </c>
       <c r="M6">
-        <v>59.96</v>
+        <v>58.97</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1393,19 +1439,19 @@
         <v>84</v>
       </c>
       <c r="P6">
-        <v>210.25</v>
+        <v>209.75</v>
       </c>
       <c r="Q6">
-        <v>207.22</v>
+        <v>207.14</v>
       </c>
       <c r="R6">
-        <v>210.96</v>
+        <v>210.6</v>
       </c>
       <c r="S6">
-        <v>184.34</v>
+        <v>184.61</v>
       </c>
       <c r="T6">
-        <v>13.9</v>
+        <v>9.42</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1466,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>51.05</v>
+        <v>42.89</v>
       </c>
       <c r="Z6">
-        <v>0.05</v>
+        <v>-0.52</v>
       </c>
       <c r="AA6">
-        <v>-0.96</v>
+        <v>-0.87</v>
       </c>
       <c r="AB6">
-        <v>1.02</v>
+        <v>0.36</v>
       </c>
       <c r="AC6">
-        <v>79.91</v>
+        <v>58.54</v>
       </c>
       <c r="AD6">
-        <v>74.09</v>
+        <v>72.39</v>
       </c>
       <c r="AE6">
-        <v>5.66</v>
+        <v>6.01</v>
       </c>
       <c r="AF6">
-        <v>-51.31</v>
+        <v>-31.16</v>
       </c>
       <c r="AG6">
-        <v>215.83</v>
+        <v>215.91</v>
       </c>
       <c r="AH6">
-        <v>198.61</v>
+        <v>198.36</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1456,7 +1502,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>18.39</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,58 +1513,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>391.85</v>
+        <v>381.75</v>
       </c>
       <c r="D7">
-        <v>-0.95</v>
+        <v>-2.58</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
       </c>
       <c r="F7">
-        <v>391.85</v>
+        <v>381.75</v>
       </c>
       <c r="G7">
-        <v>-33.44</v>
+        <v>-35.15</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-3.25</v>
+        <v>-4.23</v>
       </c>
       <c r="J7">
-        <v>-6.57</v>
+        <v>-8.56</v>
       </c>
       <c r="K7">
-        <v>-8.630000000000001</v>
+        <v>-10.4</v>
       </c>
       <c r="L7">
-        <v>-30.62</v>
+        <v>-32.32</v>
       </c>
       <c r="M7">
-        <v>-1.37</v>
+        <v>-1.92</v>
       </c>
       <c r="N7">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P7">
-        <v>396.27</v>
+        <v>392.9</v>
       </c>
       <c r="Q7">
-        <v>406.11</v>
+        <v>404.44</v>
       </c>
       <c r="R7">
-        <v>421.59</v>
+        <v>420.4</v>
       </c>
       <c r="S7">
-        <v>464.72</v>
+        <v>463.89</v>
       </c>
       <c r="T7">
-        <v>-15.68</v>
+        <v>-17.71</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,43 +1579,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>31.26</v>
+        <v>25.72</v>
       </c>
       <c r="Z7">
-        <v>-7.64</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="AA7">
-        <v>-6.76</v>
+        <v>-7.14</v>
       </c>
       <c r="AB7">
-        <v>-0.88</v>
+        <v>-1.5</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>7.44</v>
+        <v>7.89</v>
       </c>
       <c r="AF7">
-        <v>-33.88</v>
+        <v>-29.68</v>
       </c>
       <c r="AG7">
-        <v>421.15</v>
+        <v>422.37</v>
       </c>
       <c r="AH7">
-        <v>391.07</v>
+        <v>386.5</v>
       </c>
       <c r="AI7">
-        <v>412.92</v>
+        <v>410.64</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>34.52</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1626,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>594.8</v>
+        <v>580.15</v>
       </c>
       <c r="D8">
-        <v>-1.31</v>
+        <v>-2.46</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,25 +1638,25 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-26.41</v>
+        <v>-28.22</v>
       </c>
       <c r="H8">
-        <v>27.16</v>
+        <v>24.03</v>
       </c>
       <c r="I8">
-        <v>-2.87</v>
+        <v>-3.9</v>
       </c>
       <c r="J8">
-        <v>-9.199999999999999</v>
+        <v>-11.3</v>
       </c>
       <c r="K8">
-        <v>-17.39</v>
+        <v>-18.71</v>
       </c>
       <c r="L8">
-        <v>0.07000000000000001</v>
+        <v>-2.93</v>
       </c>
       <c r="M8">
-        <v>-15.43</v>
+        <v>-16.22</v>
       </c>
       <c r="N8">
         <v>55</v>
@@ -1619,19 +1665,19 @@
         <v>39</v>
       </c>
       <c r="P8">
-        <v>604.58</v>
+        <v>599.87</v>
       </c>
       <c r="Q8">
-        <v>628.34</v>
+        <v>625</v>
       </c>
       <c r="R8">
-        <v>659.6</v>
+        <v>656.72</v>
       </c>
       <c r="S8">
-        <v>613.83</v>
+        <v>613.7</v>
       </c>
       <c r="T8">
-        <v>-3.1</v>
+        <v>-5.47</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,43 +1692,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>26.91</v>
+        <v>22.82</v>
       </c>
       <c r="Z8">
-        <v>-16.89</v>
+        <v>-18.39</v>
       </c>
       <c r="AA8">
-        <v>-15.32</v>
+        <v>-15.93</v>
       </c>
       <c r="AB8">
-        <v>-1.57</v>
+        <v>-2.46</v>
       </c>
       <c r="AC8">
-        <v>27.07</v>
+        <v>10.48</v>
       </c>
       <c r="AD8">
-        <v>28.81</v>
+        <v>23.79</v>
       </c>
       <c r="AE8">
-        <v>14.93</v>
+        <v>15.75</v>
       </c>
       <c r="AF8">
-        <v>-53.64</v>
+        <v>-44.85</v>
       </c>
       <c r="AG8">
-        <v>669.22</v>
+        <v>670.17</v>
       </c>
       <c r="AH8">
-        <v>587.45</v>
+        <v>579.8200000000001</v>
       </c>
       <c r="AI8">
-        <v>641.75</v>
+        <v>636.91</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>35.06</v>
+        <v>38.01</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1739,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>185.02</v>
+        <v>183.14</v>
       </c>
       <c r="D9">
-        <v>-0.37</v>
+        <v>-1.02</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1751,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.35</v>
+        <v>-34.03</v>
       </c>
       <c r="H9">
-        <v>7.38</v>
+        <v>6.29</v>
       </c>
       <c r="I9">
-        <v>-1.21</v>
+        <v>-2.72</v>
       </c>
       <c r="J9">
-        <v>-3.69</v>
+        <v>-4.69</v>
       </c>
       <c r="K9">
-        <v>-3.21</v>
+        <v>-7.16</v>
       </c>
       <c r="L9">
-        <v>-27.98</v>
+        <v>-28.53</v>
       </c>
       <c r="M9">
-        <v>-7.78</v>
+        <v>-7.96</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P9">
-        <v>186.81</v>
+        <v>185.78</v>
       </c>
       <c r="Q9">
-        <v>191.52</v>
+        <v>191.07</v>
       </c>
       <c r="R9">
-        <v>190.72</v>
+        <v>190.57</v>
       </c>
       <c r="S9">
-        <v>201.17</v>
+        <v>200.76</v>
       </c>
       <c r="T9">
-        <v>-8.029999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1759,34 +1805,34 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>38.31</v>
+        <v>35.55</v>
       </c>
       <c r="Z9">
-        <v>-1.45</v>
+        <v>-1.83</v>
       </c>
       <c r="AA9">
-        <v>-0.33</v>
+        <v>-0.63</v>
       </c>
       <c r="AB9">
-        <v>-1.13</v>
+        <v>-1.2</v>
       </c>
       <c r="AC9">
+        <v>0</v>
+      </c>
+      <c r="AD9">
         <v>0.97</v>
       </c>
-      <c r="AD9">
-        <v>2.41</v>
-      </c>
       <c r="AE9">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="AF9">
-        <v>-47.28</v>
+        <v>-65.01000000000001</v>
       </c>
       <c r="AG9">
-        <v>201.4</v>
+        <v>201.62</v>
       </c>
       <c r="AH9">
-        <v>181.64</v>
+        <v>180.52</v>
       </c>
       <c r="AI9">
         <v>197.27</v>
@@ -1795,7 +1841,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>37.75</v>
+        <v>41.11</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1852,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>72.02</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="D10">
-        <v>-0.37</v>
+        <v>-2.21</v>
       </c>
       <c r="E10">
         <v>131.73</v>
@@ -1818,46 +1864,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-45.33</v>
+        <v>-46.53</v>
       </c>
       <c r="H10">
-        <v>21.49</v>
+        <v>18.81</v>
       </c>
       <c r="I10">
-        <v>-3.03</v>
+        <v>-3.35</v>
       </c>
       <c r="J10">
-        <v>-5.7</v>
+        <v>-7.97</v>
       </c>
       <c r="K10">
-        <v>-11.99</v>
+        <v>-14.52</v>
       </c>
       <c r="L10">
-        <v>-37.3</v>
+        <v>-41.61</v>
       </c>
       <c r="M10">
-        <v>-0.26</v>
+        <v>-0.85</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P10">
-        <v>72.79000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="Q10">
-        <v>73.61</v>
+        <v>73.3</v>
       </c>
       <c r="R10">
-        <v>76.44</v>
+        <v>76.23</v>
       </c>
       <c r="S10">
-        <v>80.62</v>
+        <v>80.55</v>
       </c>
       <c r="T10">
-        <v>-10.67</v>
+        <v>-12.57</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1918,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>40.19</v>
+        <v>35.19</v>
       </c>
       <c r="Z10">
-        <v>-1.16</v>
+        <v>-1.28</v>
       </c>
       <c r="AA10">
-        <v>-1.25</v>
+        <v>-1.26</v>
       </c>
       <c r="AB10">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="AC10">
-        <v>77.09999999999999</v>
+        <v>59.53</v>
       </c>
       <c r="AD10">
-        <v>80.77</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="AE10">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="AF10">
-        <v>8.199999999999999</v>
+        <v>-31.09</v>
       </c>
       <c r="AG10">
-        <v>76.95999999999999</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="AH10">
-        <v>70.25</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1908,7 +1954,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>31.57</v>
+        <v>31.43</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1263 +2115,1372 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>57</v>
       </c>
+      <c r="C5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-5.89</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-5.9</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.01</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5.9</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-7.28</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>3.06</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="6">
         <v>3.21</v>
       </c>
-      <c r="E8" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-6.72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-2.49</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="6">
         <v>-2.86</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-6.9</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>6.19</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="6">
         <v>6.43</v>
       </c>
-      <c r="E10" s="7">
+      <c r="D12" s="6">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-5.62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1.88</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-1.58</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-6.57</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-8.56</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-11.3</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.69</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-5.7</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-7.97</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.91</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.43</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4.15</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.73</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-4.88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-1.54</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.56</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>3.36</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.15</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1.34</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-1.22</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-3.25</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-4.23</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-2.87</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.9</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-1.21</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-2.72</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-3.03</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-3.35</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-32.24</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-33.35</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>32.43</v>
+      </c>
+      <c r="D28" s="6">
+        <v>25.2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-7.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>35.77</v>
+      </c>
+      <c r="D29" s="6">
+        <v>30.27</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>28.33</v>
+      </c>
+      <c r="D30" s="6">
+        <v>23.89</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>63.11</v>
+      </c>
+      <c r="D31" s="6">
+        <v>59.19</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-3.92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-30.62</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-32.32</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-2.93</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-27.98</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-28.53</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-37.3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-41.61</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-4.31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-8.1</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-9.18</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>3.99</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.51</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-4.5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-13.58</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-15.35</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-2.23</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-5.94</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-3.71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-4.78</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-9.25</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-4.47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-10.4</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-17.39</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-18.71</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-3.21</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-7.16</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-11.99</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-14.52</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-34.49</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-35.61</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-4.74</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-8.83</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-4.09</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-20.14</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-21.78</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-6.3</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-9</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-15.64</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-18.85</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-33.44</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-35.15</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-26.41</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-28.22</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-33.35</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-34.03</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-45.33</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-46.53</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1246.5</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1225.2</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-21.3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>3060</v>
+      </c>
+      <c r="D55" s="6">
+        <v>2928.6</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-131.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1281.3</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1255</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-26.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>1764.6</v>
+      </c>
+      <c r="D57" s="6">
+        <v>1713.8</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-50.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>209.97</v>
+      </c>
+      <c r="D58" s="6">
+        <v>202</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-7.97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>391.85</v>
+      </c>
+      <c r="D59" s="6">
+        <v>381.75</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-10.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>594.8</v>
+      </c>
+      <c r="D60" s="6">
+        <v>580.15</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-14.65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>185.02</v>
+      </c>
+      <c r="D61" s="6">
+        <v>183.14</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-1.88</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="6">
+        <v>72.02</v>
+      </c>
+      <c r="D62" s="6">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>23</v>
+      </c>
+      <c r="D63" s="6">
+        <v>34</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>34</v>
+      </c>
+      <c r="D64" s="6">
+        <v>23</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>31.95</v>
+      </c>
+      <c r="D65" s="6">
+        <v>27.67</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-4.28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>54.4</v>
+      </c>
+      <c r="D66" s="6">
+        <v>43.64</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-10.76</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>43.14</v>
+      </c>
+      <c r="D67" s="6">
+        <v>39.52</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>58.61</v>
+      </c>
+      <c r="D68" s="6">
+        <v>49.99</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-8.619999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>51.05</v>
+      </c>
+      <c r="D69" s="6">
+        <v>42.89</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-8.16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>31.26</v>
+      </c>
+      <c r="D70" s="6">
+        <v>25.72</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-5.54</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>26.91</v>
+      </c>
+      <c r="D71" s="6">
+        <v>22.82</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-4.09</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>38.31</v>
+      </c>
+      <c r="D72" s="6">
+        <v>35.55</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>40.19</v>
+      </c>
+      <c r="D73" s="6">
+        <v>35.19</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-3.12</v>
+      </c>
+      <c r="D74" s="6">
+        <v>77.73</v>
+      </c>
+      <c r="E74" s="8">
+        <v>80.84999999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-12.13</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-14.69</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-2.56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-33.36</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-33.12</v>
+      </c>
+      <c r="E76" s="8">
         <v>0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-31.15</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-33.47</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3.15</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1.88</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-51.31</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-31.16</v>
+      </c>
+      <c r="E78" s="8">
+        <v>20.15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-6.03</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-6.57</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-33.88</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-29.68</v>
+      </c>
+      <c r="E79" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-8.73</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-53.64</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-44.85</v>
+      </c>
+      <c r="E80" s="8">
+        <v>8.789999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-4.4</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-3.69</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-47.28</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-65.01000000000001</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-17.73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-5.02</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-5.7</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-1.39</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.91</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>6.07</v>
-      </c>
-      <c r="D17" s="5">
-        <v>4.15</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1.22</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.54</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="D19" s="5">
-        <v>3.36</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1.34</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-2.32</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-3.25</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-1.85</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-2.87</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-2.67</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-1.21</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>2.31</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-3.03</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-5.34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-31.37</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-32.24</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>33.22</v>
-      </c>
-      <c r="D26" s="5">
-        <v>32.43</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>38.62</v>
-      </c>
-      <c r="D27" s="5">
-        <v>35.77</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>31.68</v>
-      </c>
-      <c r="D28" s="5">
-        <v>28.33</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>68.42</v>
-      </c>
-      <c r="D29" s="5">
-        <v>63.11</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-5.31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-30.29</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-30.62</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1.79</v>
-      </c>
-      <c r="D31" s="5">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-28.88</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-27.98</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-35.81</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-37.3</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-6.16</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-8.1</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>5.33</v>
-      </c>
-      <c r="D35" s="5">
-        <v>3.99</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-12.56</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-13.58</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-2.48</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-2.23</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-4.29</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-4.78</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-6.5</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-8.630000000000001</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-17.27</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-17.39</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-2.68</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-3.21</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-11.03</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-11.99</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-34.08</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-34.49</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-4.2</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-4.74</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-19.03</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-20.14</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-6.12</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-6.3</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-14.23</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-15.64</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-32.8</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-33.44</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-25.43</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-26.41</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-33.11</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-33.35</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-45.12</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-45.33</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1254.3</v>
-      </c>
-      <c r="D52" s="5">
-        <v>1246.5</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-7.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3077.2</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3060</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-17.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1299.1</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1281.3</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-17.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>1768</v>
-      </c>
-      <c r="D55" s="5">
-        <v>1764.6</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>213.5</v>
-      </c>
-      <c r="D56" s="5">
-        <v>209.97</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-3.53</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>395.6</v>
-      </c>
-      <c r="D57" s="5">
-        <v>391.85</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>602.7</v>
-      </c>
-      <c r="D58" s="5">
-        <v>594.8</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-7.9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>185.7</v>
-      </c>
-      <c r="D59" s="5">
-        <v>185.02</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>72.29000000000001</v>
-      </c>
-      <c r="D60" s="5">
-        <v>72.02</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>33.72</v>
-      </c>
-      <c r="D61" s="5">
-        <v>31.95</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>56.08</v>
-      </c>
-      <c r="D62" s="5">
-        <v>54.4</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>45.78</v>
-      </c>
-      <c r="D63" s="5">
-        <v>43.14</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>59.25</v>
-      </c>
-      <c r="D64" s="5">
-        <v>58.61</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>55.39</v>
-      </c>
-      <c r="D65" s="5">
-        <v>51.05</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-4.34</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>33.77</v>
-      </c>
-      <c r="D66" s="5">
-        <v>31.26</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>29.56</v>
-      </c>
-      <c r="D67" s="5">
-        <v>26.91</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>39.34</v>
-      </c>
-      <c r="D68" s="5">
-        <v>38.31</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>41.11</v>
-      </c>
-      <c r="D69" s="5">
-        <v>40.19</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="5">
-        <v>-5.64</v>
-      </c>
-      <c r="D70" s="5">
-        <v>-3.12</v>
-      </c>
-      <c r="E70" s="7">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-15.87</v>
-      </c>
-      <c r="D71" s="5">
-        <v>-12.13</v>
-      </c>
-      <c r="E71" s="7">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>-24.63</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-33.36</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-8.73</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>17.1</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-31.15</v>
-      </c>
-      <c r="E73" s="6">
-        <v>-48.25</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>-10.28</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-51.31</v>
-      </c>
-      <c r="E74" s="6">
-        <v>-41.03</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-34.27</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-33.88</v>
-      </c>
-      <c r="E75" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-52.04</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-53.64</v>
-      </c>
-      <c r="E76" s="6">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-76.33</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-47.28</v>
-      </c>
-      <c r="E77" s="7">
-        <v>29.05</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-43.47</v>
-      </c>
-      <c r="D78" s="5">
+      <c r="C82" s="6">
         <v>8.199999999999999</v>
       </c>
-      <c r="E78" s="7">
-        <v>51.67</v>
+      <c r="D82" s="6">
+        <v>-31.09</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-39.29</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3345,60 +3500,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.16</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>41.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-2.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.3</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-5.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-10.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3500,61 +3655,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.5996</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1949</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.149</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0157</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.0026</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0137</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.07780000000000001</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.1202</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.1543</v>
+      <c r="A2" s="14">
+        <v>0.5897</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1811</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1412</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0218</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0192</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.0796</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.1228</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1622</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,34 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>54.4 → 43.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.4</t>
-  </si>
-  <si>
-    <t>43.6</t>
-  </si>
-  <si>
-    <t>58.6 → 50.0</t>
-  </si>
-  <si>
-    <t>58.6</t>
+    <t>50.0 → 51.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>50.0</t>
   </si>
   <si>
-    <t>51.0 → 42.9</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>42.9</t>
+    <t>51.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -309,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -349,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -948,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1225.2</v>
+        <v>1226.6</v>
       </c>
       <c r="D2">
-        <v>-1.71</v>
+        <v>0.11</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -960,46 +942,46 @@
         <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-35.61</v>
+        <v>-35.53</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="I2">
-        <v>-3.43</v>
+        <v>-2.87</v>
       </c>
       <c r="J2">
-        <v>-7.28</v>
+        <v>-6.84</v>
       </c>
       <c r="K2">
-        <v>-9.18</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L2">
-        <v>-33.35</v>
+        <v>-33.11</v>
       </c>
       <c r="M2">
-        <v>-12.28</v>
+        <v>-11.99</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P2">
-        <v>1249.3</v>
+        <v>1242.06</v>
       </c>
       <c r="Q2">
-        <v>1282.15</v>
+        <v>1278.28</v>
       </c>
       <c r="R2">
-        <v>1329.65</v>
+        <v>1326.49</v>
       </c>
       <c r="S2">
-        <v>1473.98</v>
+        <v>1470.81</v>
       </c>
       <c r="T2">
-        <v>-16.88</v>
+        <v>-16.6</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1014,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>27.67</v>
+        <v>28.35</v>
       </c>
       <c r="Z2">
-        <v>-24.82</v>
+        <v>-26.04</v>
       </c>
       <c r="AA2">
-        <v>-21.16</v>
+        <v>-22.13</v>
       </c>
       <c r="AB2">
-        <v>-3.66</v>
+        <v>-3.9</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD2">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="AE2">
-        <v>23.87</v>
+        <v>23.3</v>
       </c>
       <c r="AF2">
-        <v>77.73</v>
+        <v>-28.98</v>
       </c>
       <c r="AG2">
-        <v>1334.85</v>
+        <v>1335.44</v>
       </c>
       <c r="AH2">
-        <v>1229.44</v>
+        <v>1221.13</v>
       </c>
       <c r="AI2">
-        <v>1304.25</v>
+        <v>1296.94</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>30.83</v>
+        <v>27.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1061,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2928.6</v>
+        <v>2920</v>
       </c>
       <c r="D3">
-        <v>-4.29</v>
+        <v>-0.29</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1073,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-8.83</v>
+        <v>-9.09</v>
       </c>
       <c r="H3">
-        <v>66.59</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I3">
-        <v>-0.73</v>
+        <v>-1.12</v>
       </c>
       <c r="J3">
-        <v>-3.51</v>
+        <v>-2.9</v>
       </c>
       <c r="K3">
-        <v>-0.51</v>
+        <v>-1.08</v>
       </c>
       <c r="L3">
-        <v>25.2</v>
+        <v>21.78</v>
       </c>
       <c r="M3">
-        <v>14.12</v>
+        <v>14.25</v>
       </c>
       <c r="N3">
         <v>88</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P3">
-        <v>3024.72</v>
+        <v>3018.1</v>
       </c>
       <c r="Q3">
-        <v>3003.51</v>
+        <v>2999.39</v>
       </c>
       <c r="R3">
-        <v>3043.58</v>
+        <v>3039.83</v>
       </c>
       <c r="S3">
-        <v>2530.47</v>
+        <v>2533.8</v>
       </c>
       <c r="T3">
-        <v>15.73</v>
+        <v>15.24</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1127,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.64</v>
+        <v>43.04</v>
       </c>
       <c r="Z3">
-        <v>-8.17</v>
+        <v>-13.82</v>
       </c>
       <c r="AA3">
-        <v>-12.28</v>
+        <v>-12.59</v>
       </c>
       <c r="AB3">
-        <v>4.12</v>
+        <v>-1.23</v>
       </c>
       <c r="AC3">
-        <v>51.4</v>
+        <v>37.51</v>
       </c>
       <c r="AD3">
-        <v>58.92</v>
+        <v>52.14</v>
       </c>
       <c r="AE3">
-        <v>88.56999999999999</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="AF3">
-        <v>-14.69</v>
+        <v>-63.51</v>
       </c>
       <c r="AG3">
-        <v>3195.75</v>
+        <v>3195.22</v>
       </c>
       <c r="AH3">
-        <v>2811.27</v>
+        <v>2803.55</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1163,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>28.01</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1174,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1255</v>
+        <v>1270.2</v>
       </c>
       <c r="D4">
-        <v>-2.05</v>
+        <v>1.21</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1186,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-21.78</v>
+        <v>-20.84</v>
       </c>
       <c r="H4">
-        <v>62.4</v>
+        <v>64.36</v>
       </c>
       <c r="I4">
-        <v>-2.56</v>
+        <v>-1.69</v>
       </c>
       <c r="J4">
-        <v>-6.9</v>
+        <v>-4.32</v>
       </c>
       <c r="K4">
-        <v>-15.35</v>
+        <v>-13.34</v>
       </c>
       <c r="L4">
-        <v>30.27</v>
+        <v>30.1</v>
       </c>
       <c r="M4">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1288.48</v>
+        <v>1284.12</v>
       </c>
       <c r="Q4">
-        <v>1294.73</v>
+        <v>1292.84</v>
       </c>
       <c r="R4">
-        <v>1377.63</v>
+        <v>1372.66</v>
       </c>
       <c r="S4">
-        <v>1184.32</v>
+        <v>1185.52</v>
       </c>
       <c r="T4">
-        <v>5.97</v>
+        <v>7.14</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1240,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>39.52</v>
+        <v>42.52</v>
       </c>
       <c r="Z4">
-        <v>-24.25</v>
+        <v>-24.02</v>
       </c>
       <c r="AA4">
-        <v>-27.48</v>
+        <v>-26.79</v>
       </c>
       <c r="AB4">
-        <v>3.23</v>
+        <v>2.77</v>
       </c>
       <c r="AC4">
-        <v>71.48</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="AD4">
-        <v>83.91</v>
+        <v>74.67</v>
       </c>
       <c r="AE4">
-        <v>38.66</v>
+        <v>38.14</v>
       </c>
       <c r="AF4">
-        <v>-33.12</v>
+        <v>-57.17</v>
       </c>
       <c r="AG4">
-        <v>1347.91</v>
+        <v>1346.72</v>
       </c>
       <c r="AH4">
-        <v>1241.54</v>
+        <v>1238.95</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1276,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>19.44</v>
+        <v>20.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1287,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1713.8</v>
+        <v>1723.8</v>
       </c>
       <c r="D5">
-        <v>-2.88</v>
+        <v>0.58</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1299,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="H5">
-        <v>32.02</v>
+        <v>32.79</v>
       </c>
       <c r="I5">
-        <v>1.15</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J5">
-        <v>0.8100000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="K5">
-        <v>-5.94</v>
+        <v>-5.73</v>
       </c>
       <c r="L5">
-        <v>23.89</v>
+        <v>24.26</v>
       </c>
       <c r="M5">
-        <v>18.11</v>
+        <v>18.14</v>
       </c>
       <c r="N5">
         <v>77</v>
       </c>
       <c r="O5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>1746.28</v>
+        <v>1749.04</v>
       </c>
       <c r="Q5">
-        <v>1700.05</v>
+        <v>1702.12</v>
       </c>
       <c r="R5">
-        <v>1732.61</v>
+        <v>1730.4</v>
       </c>
       <c r="S5">
-        <v>1609.6</v>
+        <v>1610.71</v>
       </c>
       <c r="T5">
-        <v>6.47</v>
+        <v>7.02</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1353,34 +1335,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>49.99</v>
+        <v>51.5</v>
       </c>
       <c r="Z5">
-        <v>6.21</v>
+        <v>6.07</v>
       </c>
       <c r="AA5">
-        <v>-4.02</v>
+        <v>-2</v>
       </c>
       <c r="AB5">
-        <v>10.23</v>
+        <v>8.08</v>
       </c>
       <c r="AC5">
-        <v>84.62</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AD5">
-        <v>93.22</v>
+        <v>85.66</v>
       </c>
       <c r="AE5">
-        <v>40.86</v>
+        <v>40.15</v>
       </c>
       <c r="AF5">
-        <v>-33.47</v>
+        <v>-55.82</v>
       </c>
       <c r="AG5">
-        <v>1781.52</v>
+        <v>1783.81</v>
       </c>
       <c r="AH5">
-        <v>1618.57</v>
+        <v>1620.42</v>
       </c>
       <c r="AI5">
         <v>1647.25</v>
@@ -1389,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>24.06</v>
+        <v>20.94</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1400,58 +1382,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>202</v>
+        <v>202.34</v>
       </c>
       <c r="D6">
-        <v>-3.8</v>
+        <v>0.17</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>124.93</v>
+        <v>126.1</v>
       </c>
       <c r="G6">
-        <v>-18.85</v>
+        <v>-18.71</v>
       </c>
       <c r="H6">
-        <v>61.69</v>
+        <v>60.46</v>
       </c>
       <c r="I6">
-        <v>-1.22</v>
+        <v>-2.91</v>
       </c>
       <c r="J6">
-        <v>-1.58</v>
+        <v>-0.6</v>
       </c>
       <c r="K6">
-        <v>-9.25</v>
+        <v>-8.19</v>
       </c>
       <c r="L6">
-        <v>59.19</v>
+        <v>61.96</v>
       </c>
       <c r="M6">
-        <v>58.97</v>
+        <v>59.33</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P6">
-        <v>209.75</v>
+        <v>208.54</v>
       </c>
       <c r="Q6">
-        <v>207.14</v>
+        <v>206.98</v>
       </c>
       <c r="R6">
-        <v>210.6</v>
+        <v>210.29</v>
       </c>
       <c r="S6">
-        <v>184.61</v>
+        <v>184.88</v>
       </c>
       <c r="T6">
-        <v>9.42</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1466,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>42.89</v>
+        <v>43.3</v>
       </c>
       <c r="Z6">
-        <v>-0.52</v>
+        <v>-0.93</v>
       </c>
       <c r="AA6">
-        <v>-0.87</v>
+        <v>-0.88</v>
       </c>
       <c r="AB6">
-        <v>0.36</v>
+        <v>-0.04</v>
       </c>
       <c r="AC6">
-        <v>58.54</v>
+        <v>40.46</v>
       </c>
       <c r="AD6">
-        <v>72.39</v>
+        <v>59.64</v>
       </c>
       <c r="AE6">
-        <v>6.01</v>
+        <v>5.91</v>
       </c>
       <c r="AF6">
-        <v>-31.16</v>
+        <v>-42.27</v>
       </c>
       <c r="AG6">
-        <v>215.91</v>
+        <v>215.99</v>
       </c>
       <c r="AH6">
-        <v>198.36</v>
+        <v>197.96</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1502,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>19.48</v>
+        <v>20.86</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1513,37 +1495,37 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>381.75</v>
+        <v>381.05</v>
       </c>
       <c r="D7">
-        <v>-2.58</v>
+        <v>-0.18</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
       </c>
       <c r="F7">
-        <v>381.75</v>
+        <v>381.05</v>
       </c>
       <c r="G7">
-        <v>-35.15</v>
+        <v>-35.27</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-4.23</v>
+        <v>-4.33</v>
       </c>
       <c r="J7">
-        <v>-8.56</v>
+        <v>-8.24</v>
       </c>
       <c r="K7">
-        <v>-10.4</v>
+        <v>-10.65</v>
       </c>
       <c r="L7">
-        <v>-32.32</v>
+        <v>-31.67</v>
       </c>
       <c r="M7">
-        <v>-1.92</v>
+        <v>-1.64</v>
       </c>
       <c r="N7">
         <v>23</v>
@@ -1552,16 +1534,16 @@
         <v>21</v>
       </c>
       <c r="P7">
-        <v>392.9</v>
+        <v>389.45</v>
       </c>
       <c r="Q7">
-        <v>404.44</v>
+        <v>402.87</v>
       </c>
       <c r="R7">
-        <v>420.4</v>
+        <v>419.3</v>
       </c>
       <c r="S7">
-        <v>463.89</v>
+        <v>463.07</v>
       </c>
       <c r="T7">
         <v>-17.71</v>
@@ -1579,16 +1561,16 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>25.72</v>
+        <v>25.39</v>
       </c>
       <c r="Z7">
-        <v>-8.640000000000001</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="AA7">
-        <v>-7.14</v>
+        <v>-7.58</v>
       </c>
       <c r="AB7">
-        <v>-1.5</v>
+        <v>-1.79</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1597,25 +1579,25 @@
         <v>0</v>
       </c>
       <c r="AE7">
-        <v>7.89</v>
+        <v>7.75</v>
       </c>
       <c r="AF7">
-        <v>-29.68</v>
+        <v>-46.55</v>
       </c>
       <c r="AG7">
-        <v>422.37</v>
+        <v>423.19</v>
       </c>
       <c r="AH7">
-        <v>386.5</v>
+        <v>382.54</v>
       </c>
       <c r="AI7">
-        <v>410.64</v>
+        <v>405.74</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>38.92</v>
+        <v>42.83</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1626,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>580.15</v>
+        <v>586.5</v>
       </c>
       <c r="D8">
-        <v>-2.46</v>
+        <v>1.09</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1638,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-28.22</v>
+        <v>-27.44</v>
       </c>
       <c r="H8">
-        <v>24.03</v>
+        <v>25.39</v>
       </c>
       <c r="I8">
-        <v>-3.9</v>
+        <v>-3.76</v>
       </c>
       <c r="J8">
-        <v>-11.3</v>
+        <v>-9.34</v>
       </c>
       <c r="K8">
-        <v>-18.71</v>
+        <v>-16.53</v>
       </c>
       <c r="L8">
-        <v>-2.93</v>
+        <v>-3.22</v>
       </c>
       <c r="M8">
-        <v>-16.22</v>
+        <v>-16.35</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P8">
-        <v>599.87</v>
+        <v>595.29</v>
       </c>
       <c r="Q8">
-        <v>625</v>
+        <v>621.96</v>
       </c>
       <c r="R8">
-        <v>656.72</v>
+        <v>654.22</v>
       </c>
       <c r="S8">
-        <v>613.7</v>
+        <v>613.62</v>
       </c>
       <c r="T8">
-        <v>-5.47</v>
+        <v>-4.42</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1692,43 +1674,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>22.82</v>
+        <v>27.93</v>
       </c>
       <c r="Z8">
-        <v>-18.39</v>
+        <v>-18.85</v>
       </c>
       <c r="AA8">
-        <v>-15.93</v>
+        <v>-16.52</v>
       </c>
       <c r="AB8">
-        <v>-2.46</v>
+        <v>-2.34</v>
       </c>
       <c r="AC8">
-        <v>10.48</v>
+        <v>11.79</v>
       </c>
       <c r="AD8">
-        <v>23.79</v>
+        <v>16.45</v>
       </c>
       <c r="AE8">
-        <v>15.75</v>
+        <v>15.85</v>
       </c>
       <c r="AF8">
-        <v>-44.85</v>
+        <v>-10.79</v>
       </c>
       <c r="AG8">
-        <v>670.17</v>
+        <v>668.96</v>
       </c>
       <c r="AH8">
-        <v>579.8200000000001</v>
+        <v>574.95</v>
       </c>
       <c r="AI8">
-        <v>636.91</v>
+        <v>636.3</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>38.01</v>
+        <v>40.56</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1739,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>183.14</v>
+        <v>181.94</v>
       </c>
       <c r="D9">
-        <v>-1.02</v>
+        <v>-0.66</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1751,25 +1733,25 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-34.03</v>
+        <v>-34.46</v>
       </c>
       <c r="H9">
-        <v>6.29</v>
+        <v>5.59</v>
       </c>
       <c r="I9">
-        <v>-2.72</v>
+        <v>-2.98</v>
       </c>
       <c r="J9">
-        <v>-4.69</v>
+        <v>-5.32</v>
       </c>
       <c r="K9">
-        <v>-7.16</v>
+        <v>-6.02</v>
       </c>
       <c r="L9">
-        <v>-28.53</v>
+        <v>-29.7</v>
       </c>
       <c r="M9">
-        <v>-7.96</v>
+        <v>-8.09</v>
       </c>
       <c r="N9">
         <v>45</v>
@@ -1778,19 +1760,19 @@
         <v>28</v>
       </c>
       <c r="P9">
-        <v>185.78</v>
+        <v>184.66</v>
       </c>
       <c r="Q9">
-        <v>191.07</v>
+        <v>190.66</v>
       </c>
       <c r="R9">
-        <v>190.57</v>
+        <v>190.5</v>
       </c>
       <c r="S9">
-        <v>200.76</v>
+        <v>200.36</v>
       </c>
       <c r="T9">
-        <v>-8.779999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>48</v>
@@ -1805,43 +1787,43 @@
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>35.55</v>
+        <v>33.87</v>
       </c>
       <c r="Z9">
-        <v>-1.83</v>
+        <v>-2.2</v>
       </c>
       <c r="AA9">
-        <v>-0.63</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AB9">
-        <v>-1.2</v>
+        <v>-1.26</v>
       </c>
       <c r="AC9">
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>0.97</v>
+        <v>0.32</v>
       </c>
       <c r="AE9">
-        <v>4.62</v>
+        <v>4.53</v>
       </c>
       <c r="AF9">
-        <v>-65.01000000000001</v>
+        <v>-73.7</v>
       </c>
       <c r="AG9">
-        <v>201.62</v>
+        <v>201.98</v>
       </c>
       <c r="AH9">
-        <v>180.52</v>
+        <v>179.35</v>
       </c>
       <c r="AI9">
-        <v>197.27</v>
+        <v>195.69</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>41.11</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1852,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>70.43000000000001</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="D10">
-        <v>-2.21</v>
+        <v>-0.98</v>
       </c>
       <c r="E10">
         <v>131.73</v>
@@ -1864,46 +1846,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-46.53</v>
+        <v>-47.06</v>
       </c>
       <c r="H10">
-        <v>18.81</v>
+        <v>17.65</v>
       </c>
       <c r="I10">
-        <v>-3.35</v>
+        <v>-4.5</v>
       </c>
       <c r="J10">
-        <v>-7.97</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="K10">
-        <v>-14.52</v>
+        <v>-14.59</v>
       </c>
       <c r="L10">
-        <v>-41.61</v>
+        <v>-44.41</v>
       </c>
       <c r="M10">
-        <v>-0.85</v>
+        <v>-1.06</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>72.3</v>
+        <v>71.64</v>
       </c>
       <c r="Q10">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="R10">
-        <v>76.23</v>
+        <v>76.04000000000001</v>
       </c>
       <c r="S10">
-        <v>80.55</v>
+        <v>80.47</v>
       </c>
       <c r="T10">
-        <v>-12.57</v>
+        <v>-13.34</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1918,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>35.19</v>
+        <v>33.25</v>
       </c>
       <c r="Z10">
-        <v>-1.28</v>
+        <v>-1.41</v>
       </c>
       <c r="AA10">
-        <v>-1.26</v>
+        <v>-1.29</v>
       </c>
       <c r="AB10">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="AC10">
-        <v>59.53</v>
+        <v>47.19</v>
       </c>
       <c r="AD10">
-        <v>72.76000000000001</v>
+        <v>61.28</v>
       </c>
       <c r="AE10">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="AF10">
-        <v>-31.09</v>
+        <v>-51.73</v>
       </c>
       <c r="AG10">
-        <v>76.65000000000001</v>
+        <v>76.51000000000001</v>
       </c>
       <c r="AH10">
-        <v>69.95999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1954,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>31.43</v>
+        <v>33.32</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2135,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2153,1334 +2135,1260 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-7.28</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-6.84</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-3.51</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-2.9</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.61</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.9</v>
+        <v>-6.9</v>
       </c>
       <c r="D9" s="6">
-        <v>-7.28</v>
+        <v>-4.32</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.38</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>3.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D10" s="6">
-        <v>-3.51</v>
+        <v>1.4</v>
       </c>
       <c r="E10" s="7">
-        <v>-6.72</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-2.86</v>
+        <v>-1.58</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.9</v>
+        <v>-0.6</v>
       </c>
       <c r="E11" s="7">
-        <v>-4.04</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>6.43</v>
+        <v>-8.56</v>
       </c>
       <c r="D12" s="6">
-        <v>0.8100000000000001</v>
+        <v>-8.24</v>
       </c>
       <c r="E12" s="7">
-        <v>-5.62</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>1.88</v>
+        <v>-11.3</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.58</v>
+        <v>-9.34</v>
       </c>
       <c r="E13" s="7">
-        <v>-3.46</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.57</v>
+        <v>-4.69</v>
       </c>
       <c r="D14" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.99</v>
+        <v>-5.32</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-9.199999999999999</v>
+        <v>-7.97</v>
       </c>
       <c r="D15" s="6">
-        <v>-11.3</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.1</v>
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.69</v>
+        <v>-3.43</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.69</v>
+        <v>-2.87</v>
       </c>
       <c r="E16" s="7">
-        <v>-1</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.7</v>
+        <v>-0.73</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.97</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.27</v>
+        <v>-1.12</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.91</v>
+        <v>-2.56</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.43</v>
+        <v>-1.69</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.52</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>4.15</v>
+        <v>1.15</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.73</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-4.88</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.54</v>
+        <v>-1.22</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.56</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.02</v>
+        <v>-2.91</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>3.36</v>
+        <v>-4.23</v>
       </c>
       <c r="D21" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.21</v>
+        <v>-4.33</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>1.34</v>
+        <v>-3.9</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.22</v>
+        <v>-3.76</v>
       </c>
       <c r="E22" s="7">
-        <v>-2.56</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.25</v>
+        <v>-2.72</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.23</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.98</v>
+        <v>-2.98</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.87</v>
+        <v>-3.35</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.03</v>
+        <v>-4.5</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-1.21</v>
+        <v>-33.35</v>
       </c>
       <c r="D25" s="6">
-        <v>-2.72</v>
+        <v>-33.11</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.51</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-3.03</v>
+        <v>25.2</v>
       </c>
       <c r="D26" s="6">
-        <v>-3.35</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.32</v>
+        <v>21.78</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-32.24</v>
+        <v>30.27</v>
       </c>
       <c r="D27" s="6">
-        <v>-33.35</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.11</v>
+        <v>30.1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>32.43</v>
+        <v>23.89</v>
       </c>
       <c r="D28" s="6">
-        <v>25.2</v>
+        <v>24.26</v>
       </c>
       <c r="E28" s="7">
-        <v>-7.23</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>35.77</v>
+        <v>59.19</v>
       </c>
       <c r="D29" s="6">
-        <v>30.27</v>
+        <v>61.96</v>
       </c>
       <c r="E29" s="7">
-        <v>-5.5</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>28.33</v>
+        <v>-32.32</v>
       </c>
       <c r="D30" s="6">
-        <v>23.89</v>
+        <v>-31.67</v>
       </c>
       <c r="E30" s="7">
-        <v>-4.44</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>63.11</v>
+        <v>-2.93</v>
       </c>
       <c r="D31" s="6">
-        <v>59.19</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-3.92</v>
+        <v>-3.22</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-30.62</v>
+        <v>-28.53</v>
       </c>
       <c r="D32" s="6">
-        <v>-32.32</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.7</v>
+        <v>-29.7</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>0.07000000000000001</v>
+        <v>-41.61</v>
       </c>
       <c r="D33" s="6">
-        <v>-2.93</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-3</v>
+        <v>-44.41</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-27.98</v>
+        <v>-9.18</v>
       </c>
       <c r="D34" s="6">
-        <v>-28.53</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.55</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-37.3</v>
+        <v>-0.51</v>
       </c>
       <c r="D35" s="6">
-        <v>-41.61</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-4.31</v>
+        <v>-1.08</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-8.1</v>
+        <v>-15.35</v>
       </c>
       <c r="D36" s="6">
-        <v>-9.18</v>
+        <v>-13.34</v>
       </c>
       <c r="E36" s="7">
-        <v>-1.08</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>3.99</v>
+        <v>-5.94</v>
       </c>
       <c r="D37" s="6">
-        <v>-0.51</v>
+        <v>-5.73</v>
       </c>
       <c r="E37" s="7">
-        <v>-4.5</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-13.58</v>
+        <v>-9.25</v>
       </c>
       <c r="D38" s="6">
-        <v>-15.35</v>
+        <v>-8.19</v>
       </c>
       <c r="E38" s="7">
-        <v>-1.77</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-2.23</v>
+        <v>-10.4</v>
       </c>
       <c r="D39" s="6">
-        <v>-5.94</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-3.71</v>
+        <v>-10.65</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-4.78</v>
+        <v>-18.71</v>
       </c>
       <c r="D40" s="6">
-        <v>-9.25</v>
+        <v>-16.53</v>
       </c>
       <c r="E40" s="7">
-        <v>-4.47</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-8.630000000000001</v>
+        <v>-7.16</v>
       </c>
       <c r="D41" s="6">
-        <v>-10.4</v>
+        <v>-6.02</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.77</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-17.39</v>
+        <v>-14.52</v>
       </c>
       <c r="D42" s="6">
-        <v>-18.71</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.32</v>
+        <v>-14.59</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-3.21</v>
+        <v>-35.61</v>
       </c>
       <c r="D43" s="6">
-        <v>-7.16</v>
+        <v>-35.53</v>
       </c>
       <c r="E43" s="7">
-        <v>-3.95</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-11.99</v>
+        <v>-8.83</v>
       </c>
       <c r="D44" s="6">
-        <v>-14.52</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.53</v>
+        <v>-9.09</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-34.49</v>
+        <v>-21.78</v>
       </c>
       <c r="D45" s="6">
-        <v>-35.61</v>
+        <v>-20.84</v>
       </c>
       <c r="E45" s="7">
-        <v>-1.12</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-4.74</v>
+        <v>-9</v>
       </c>
       <c r="D46" s="6">
-        <v>-8.83</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="E46" s="7">
-        <v>-4.09</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-20.14</v>
+        <v>-18.85</v>
       </c>
       <c r="D47" s="6">
-        <v>-21.78</v>
+        <v>-18.71</v>
       </c>
       <c r="E47" s="7">
-        <v>-1.64</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-6.3</v>
+        <v>-35.15</v>
       </c>
       <c r="D48" s="6">
-        <v>-9</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-2.7</v>
+        <v>-35.27</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.12</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-15.64</v>
+        <v>-28.22</v>
       </c>
       <c r="D49" s="6">
-        <v>-18.85</v>
+        <v>-27.44</v>
       </c>
       <c r="E49" s="7">
-        <v>-3.21</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-33.44</v>
+        <v>-34.03</v>
       </c>
       <c r="D50" s="6">
-        <v>-35.15</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.71</v>
+        <v>-34.46</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-26.41</v>
+        <v>-46.53</v>
       </c>
       <c r="D51" s="6">
-        <v>-28.22</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.81</v>
+        <v>-47.06</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>-33.35</v>
+        <v>1225.2</v>
       </c>
       <c r="D52" s="6">
-        <v>-34.03</v>
+        <v>1226.6</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.68</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>-45.33</v>
+        <v>2928.6</v>
       </c>
       <c r="D53" s="6">
-        <v>-46.53</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.2</v>
+        <v>2920</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-8.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1246.5</v>
+        <v>1255</v>
       </c>
       <c r="D54" s="6">
-        <v>1225.2</v>
+        <v>1270.2</v>
       </c>
       <c r="E54" s="7">
-        <v>-21.3</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>3060</v>
+        <v>1713.8</v>
       </c>
       <c r="D55" s="6">
-        <v>2928.6</v>
+        <v>1723.8</v>
       </c>
       <c r="E55" s="7">
-        <v>-131.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1281.3</v>
+        <v>202</v>
       </c>
       <c r="D56" s="6">
-        <v>1255</v>
+        <v>202.34</v>
       </c>
       <c r="E56" s="7">
-        <v>-26.3</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>1764.6</v>
+        <v>381.75</v>
       </c>
       <c r="D57" s="6">
-        <v>1713.8</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-50.8</v>
+        <v>381.05</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>209.97</v>
+        <v>580.15</v>
       </c>
       <c r="D58" s="6">
-        <v>202</v>
+        <v>586.5</v>
       </c>
       <c r="E58" s="7">
-        <v>-7.97</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>391.85</v>
+        <v>183.14</v>
       </c>
       <c r="D59" s="6">
-        <v>381.75</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-10.1</v>
+        <v>181.94</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>594.8</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="D60" s="6">
-        <v>580.15</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-14.65</v>
+        <v>69.73999999999999</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>185.02</v>
+        <v>27.67</v>
       </c>
       <c r="D61" s="6">
-        <v>183.14</v>
+        <v>28.35</v>
       </c>
       <c r="E61" s="7">
-        <v>-1.88</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>72.02</v>
+        <v>43.64</v>
       </c>
       <c r="D62" s="6">
-        <v>70.43000000000001</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1.59</v>
+        <v>43.04</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>23</v>
+        <v>39.52</v>
       </c>
       <c r="D63" s="6">
-        <v>34</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
+        <v>42.52</v>
+      </c>
+      <c r="E63" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>34</v>
+        <v>49.99</v>
       </c>
       <c r="D64" s="6">
-        <v>23</v>
+        <v>51.5</v>
       </c>
       <c r="E64" s="7">
-        <v>-11</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>31.95</v>
+        <v>42.89</v>
       </c>
       <c r="D65" s="6">
-        <v>27.67</v>
+        <v>43.3</v>
       </c>
       <c r="E65" s="7">
-        <v>-4.28</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>54.4</v>
+        <v>25.72</v>
       </c>
       <c r="D66" s="6">
-        <v>43.64</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-10.76</v>
+        <v>25.39</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>43.14</v>
+        <v>22.82</v>
       </c>
       <c r="D67" s="6">
-        <v>39.52</v>
+        <v>27.93</v>
       </c>
       <c r="E67" s="7">
-        <v>-3.62</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>58.61</v>
+        <v>35.55</v>
       </c>
       <c r="D68" s="6">
-        <v>49.99</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-8.619999999999999</v>
+        <v>33.87</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>51.05</v>
+        <v>35.19</v>
       </c>
       <c r="D69" s="6">
-        <v>42.89</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-8.16</v>
+        <v>33.25</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>31.26</v>
+        <v>77.73</v>
       </c>
       <c r="D70" s="6">
-        <v>25.72</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-5.54</v>
+        <v>-28.98</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-106.71</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>26.91</v>
+        <v>-14.69</v>
       </c>
       <c r="D71" s="6">
-        <v>22.82</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-4.09</v>
+        <v>-63.51</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-48.82</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>38.31</v>
+        <v>-33.12</v>
       </c>
       <c r="D72" s="6">
-        <v>35.55</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-2.76</v>
+        <v>-57.17</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-24.05</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>40.19</v>
+        <v>-33.47</v>
       </c>
       <c r="D73" s="6">
-        <v>35.19</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-5</v>
+        <v>-55.82</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-22.35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-3.12</v>
+        <v>-31.16</v>
       </c>
       <c r="D74" s="6">
-        <v>77.73</v>
+        <v>-42.27</v>
       </c>
       <c r="E74" s="8">
-        <v>80.84999999999999</v>
+        <v>-11.11</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-12.13</v>
+        <v>-29.68</v>
       </c>
       <c r="D75" s="6">
-        <v>-14.69</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-2.56</v>
+        <v>-46.55</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-16.87</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-33.36</v>
+        <v>-44.85</v>
       </c>
       <c r="D76" s="6">
-        <v>-33.12</v>
-      </c>
-      <c r="E76" s="8">
-        <v>0.24</v>
+        <v>-10.79</v>
+      </c>
+      <c r="E76" s="7">
+        <v>34.06</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-31.15</v>
+        <v>-65.01000000000001</v>
       </c>
       <c r="D77" s="6">
-        <v>-33.47</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-2.32</v>
+        <v>-73.7</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-8.69</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-51.31</v>
+        <v>-31.09</v>
       </c>
       <c r="D78" s="6">
-        <v>-31.16</v>
+        <v>-51.73</v>
       </c>
       <c r="E78" s="8">
-        <v>20.15</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-33.88</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-29.68</v>
-      </c>
-      <c r="E79" s="8">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-53.64</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-44.85</v>
-      </c>
-      <c r="E80" s="8">
-        <v>8.789999999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-47.28</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-65.01000000000001</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-17.73</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-31.09</v>
-      </c>
-      <c r="E82" s="7">
-        <v>-39.29</v>
+        <v>-20.64</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3504,28 +3412,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3539,16 +3447,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>35.9</v>
+        <v>36.6</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.7</v>
+        <v>-5</v>
       </c>
       <c r="G2" s="11">
-        <v>-10.1</v>
+        <v>-9.5</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3685,31 +3593,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5897</v>
+        <v>0.5932999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1811</v>
+        <v>0.1814</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1412</v>
+        <v>0.1425</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0218</v>
+        <v>0.0166</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.008500000000000001</v>
+        <v>-0.0106</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0192</v>
+        <v>-0.0164</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.0796</v>
+        <v>-0.0809</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1228</v>
+        <v>-0.1199</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1622</v>
+        <v>-0.1635</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.0 → 51.5</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.4 → 31.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>51.5</t>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>31.3</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,6 +424,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -930,10 +940,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1226.6</v>
+        <v>1232.5</v>
       </c>
       <c r="D2">
-        <v>0.11</v>
+        <v>0.48</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,25 +952,25 @@
         <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-35.53</v>
+        <v>-35.22</v>
       </c>
       <c r="H2">
-        <v>0.11</v>
+        <v>0.6</v>
       </c>
       <c r="I2">
-        <v>-2.87</v>
+        <v>-2</v>
       </c>
       <c r="J2">
-        <v>-6.84</v>
+        <v>-5.47</v>
       </c>
       <c r="K2">
-        <v>-9.140000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L2">
-        <v>-33.11</v>
+        <v>-33.01</v>
       </c>
       <c r="M2">
-        <v>-11.99</v>
+        <v>-11.65</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -969,19 +979,19 @@
         <v>22</v>
       </c>
       <c r="P2">
-        <v>1242.06</v>
+        <v>1237.02</v>
       </c>
       <c r="Q2">
-        <v>1278.28</v>
+        <v>1275.47</v>
       </c>
       <c r="R2">
-        <v>1326.49</v>
+        <v>1324.44</v>
       </c>
       <c r="S2">
-        <v>1470.81</v>
+        <v>1467.78</v>
       </c>
       <c r="T2">
-        <v>-16.6</v>
+        <v>-16.03</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1006,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.35</v>
+        <v>31.28</v>
       </c>
       <c r="Z2">
-        <v>-26.04</v>
+        <v>-26.23</v>
       </c>
       <c r="AA2">
-        <v>-22.13</v>
+        <v>-22.95</v>
       </c>
       <c r="AB2">
-        <v>-3.9</v>
+        <v>-3.27</v>
       </c>
       <c r="AC2">
-        <v>1.43</v>
+        <v>9.59</v>
       </c>
       <c r="AD2">
-        <v>0.89</v>
+        <v>3.67</v>
       </c>
       <c r="AE2">
-        <v>23.3</v>
+        <v>22.73</v>
       </c>
       <c r="AF2">
-        <v>-28.98</v>
+        <v>-43.14</v>
       </c>
       <c r="AG2">
-        <v>1335.44</v>
+        <v>1335.9</v>
       </c>
       <c r="AH2">
-        <v>1221.13</v>
+        <v>1215.05</v>
       </c>
       <c r="AI2">
         <v>1296.94</v>
@@ -1032,7 +1042,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>27.57</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1053,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2920</v>
+        <v>2923.2</v>
       </c>
       <c r="D3">
-        <v>-0.29</v>
+        <v>0.11</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1065,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-9.09</v>
+        <v>-8.99</v>
       </c>
       <c r="H3">
-        <v>66.09999999999999</v>
+        <v>66.28</v>
       </c>
       <c r="I3">
-        <v>-1.12</v>
+        <v>-5.85</v>
       </c>
       <c r="J3">
-        <v>-2.9</v>
+        <v>-2.64</v>
       </c>
       <c r="K3">
-        <v>-1.08</v>
+        <v>-2.99</v>
       </c>
       <c r="L3">
-        <v>21.78</v>
+        <v>22.26</v>
       </c>
       <c r="M3">
-        <v>14.25</v>
+        <v>14.63</v>
       </c>
       <c r="N3">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O3">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>3018.1</v>
+        <v>2981.8</v>
       </c>
       <c r="Q3">
-        <v>2999.39</v>
+        <v>2996.03</v>
       </c>
       <c r="R3">
-        <v>3039.83</v>
+        <v>3037.36</v>
       </c>
       <c r="S3">
-        <v>2533.8</v>
+        <v>2537.02</v>
       </c>
       <c r="T3">
-        <v>15.24</v>
+        <v>15.22</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1119,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.04</v>
+        <v>43.35</v>
       </c>
       <c r="Z3">
-        <v>-13.82</v>
+        <v>-17.84</v>
       </c>
       <c r="AA3">
-        <v>-12.59</v>
+        <v>-13.64</v>
       </c>
       <c r="AB3">
-        <v>-1.23</v>
+        <v>-4.2</v>
       </c>
       <c r="AC3">
-        <v>37.51</v>
+        <v>25.78</v>
       </c>
       <c r="AD3">
-        <v>52.14</v>
+        <v>38.23</v>
       </c>
       <c r="AE3">
-        <v>86.43000000000001</v>
+        <v>82.97</v>
       </c>
       <c r="AF3">
-        <v>-63.51</v>
+        <v>-71.84</v>
       </c>
       <c r="AG3">
-        <v>3195.22</v>
+        <v>3194.8</v>
       </c>
       <c r="AH3">
-        <v>2803.55</v>
+        <v>2797.26</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1145,7 +1155,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>25.6</v>
+        <v>23.81</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1166,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1270.2</v>
+        <v>1274.2</v>
       </c>
       <c r="D4">
-        <v>1.21</v>
+        <v>0.31</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1178,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-20.84</v>
+        <v>-20.59</v>
       </c>
       <c r="H4">
-        <v>64.36</v>
+        <v>64.88</v>
       </c>
       <c r="I4">
-        <v>-1.69</v>
+        <v>-3.1</v>
       </c>
       <c r="J4">
-        <v>-4.32</v>
+        <v>-2.58</v>
       </c>
       <c r="K4">
-        <v>-13.34</v>
+        <v>-15.44</v>
       </c>
       <c r="L4">
-        <v>30.1</v>
+        <v>29.8</v>
       </c>
       <c r="M4">
-        <v>1.66</v>
+        <v>2.01</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1284.12</v>
+        <v>1275.96</v>
       </c>
       <c r="Q4">
-        <v>1292.84</v>
+        <v>1291.9</v>
       </c>
       <c r="R4">
-        <v>1372.66</v>
+        <v>1368.05</v>
       </c>
       <c r="S4">
-        <v>1185.52</v>
+        <v>1186.65</v>
       </c>
       <c r="T4">
-        <v>7.14</v>
+        <v>7.38</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1232,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>42.52</v>
+        <v>43.32</v>
       </c>
       <c r="Z4">
-        <v>-24.02</v>
+        <v>-23.25</v>
       </c>
       <c r="AA4">
-        <v>-26.79</v>
+        <v>-26.08</v>
       </c>
       <c r="AB4">
-        <v>2.77</v>
+        <v>2.83</v>
       </c>
       <c r="AC4">
-        <v>65.76000000000001</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="AD4">
-        <v>74.67</v>
+        <v>67.77</v>
       </c>
       <c r="AE4">
-        <v>38.14</v>
+        <v>37.52</v>
       </c>
       <c r="AF4">
-        <v>-57.17</v>
+        <v>-50.68</v>
       </c>
       <c r="AG4">
-        <v>1346.72</v>
+        <v>1346.42</v>
       </c>
       <c r="AH4">
-        <v>1238.95</v>
+        <v>1237.37</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1258,7 +1268,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>20.09</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1279,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1723.8</v>
+        <v>1738.3</v>
       </c>
       <c r="D5">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1291,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-8.460000000000001</v>
+        <v>-7.69</v>
       </c>
       <c r="H5">
-        <v>32.79</v>
+        <v>33.91</v>
       </c>
       <c r="I5">
-        <v>0.8100000000000001</v>
+        <v>-2.07</v>
       </c>
       <c r="J5">
-        <v>1.4</v>
+        <v>3.32</v>
       </c>
       <c r="K5">
-        <v>-5.73</v>
+        <v>-5.63</v>
       </c>
       <c r="L5">
-        <v>24.26</v>
+        <v>25.31</v>
       </c>
       <c r="M5">
-        <v>18.14</v>
+        <v>18.41</v>
       </c>
       <c r="N5">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O5">
         <v>73</v>
       </c>
       <c r="P5">
-        <v>1749.04</v>
+        <v>1741.7</v>
       </c>
       <c r="Q5">
-        <v>1702.12</v>
+        <v>1704.94</v>
       </c>
       <c r="R5">
-        <v>1730.4</v>
+        <v>1729.34</v>
       </c>
       <c r="S5">
-        <v>1610.71</v>
+        <v>1611.85</v>
       </c>
       <c r="T5">
-        <v>7.02</v>
+        <v>7.85</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1335,34 +1345,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>51.5</v>
+        <v>53.69</v>
       </c>
       <c r="Z5">
-        <v>6.07</v>
+        <v>7.05</v>
       </c>
       <c r="AA5">
-        <v>-2</v>
+        <v>-0.19</v>
       </c>
       <c r="AB5">
-        <v>8.08</v>
+        <v>7.24</v>
       </c>
       <c r="AC5">
-        <v>75.90000000000001</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="AD5">
-        <v>85.66</v>
+        <v>76.95999999999999</v>
       </c>
       <c r="AE5">
-        <v>40.15</v>
+        <v>38.35</v>
       </c>
       <c r="AF5">
-        <v>-55.82</v>
+        <v>-66.67</v>
       </c>
       <c r="AG5">
-        <v>1783.81</v>
+        <v>1787.58</v>
       </c>
       <c r="AH5">
-        <v>1620.42</v>
+        <v>1622.29</v>
       </c>
       <c r="AI5">
         <v>1647.25</v>
@@ -1371,7 +1381,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>20.94</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1392,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>202.34</v>
+        <v>205.92</v>
       </c>
       <c r="D6">
-        <v>0.17</v>
+        <v>1.77</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1404,46 @@
         <v>126.1</v>
       </c>
       <c r="G6">
-        <v>-18.71</v>
+        <v>-17.27</v>
       </c>
       <c r="H6">
-        <v>60.46</v>
+        <v>63.3</v>
       </c>
       <c r="I6">
-        <v>-2.91</v>
+        <v>-4.18</v>
       </c>
       <c r="J6">
-        <v>-0.6</v>
+        <v>0.17</v>
       </c>
       <c r="K6">
-        <v>-8.19</v>
+        <v>-10.69</v>
       </c>
       <c r="L6">
-        <v>61.96</v>
+        <v>58.75</v>
       </c>
       <c r="M6">
-        <v>59.33</v>
+        <v>59.28</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P6">
-        <v>208.54</v>
+        <v>206.75</v>
       </c>
       <c r="Q6">
-        <v>206.98</v>
+        <v>207.07</v>
       </c>
       <c r="R6">
-        <v>210.29</v>
+        <v>210.08</v>
       </c>
       <c r="S6">
-        <v>184.88</v>
+        <v>185.17</v>
       </c>
       <c r="T6">
-        <v>9.449999999999999</v>
+        <v>11.21</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1458,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>43.3</v>
+        <v>47.64</v>
       </c>
       <c r="Z6">
-        <v>-0.93</v>
+        <v>-0.95</v>
       </c>
       <c r="AA6">
-        <v>-0.88</v>
+        <v>-0.9</v>
       </c>
       <c r="AB6">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="AC6">
-        <v>40.46</v>
+        <v>36.82</v>
       </c>
       <c r="AD6">
-        <v>59.64</v>
+        <v>45.27</v>
       </c>
       <c r="AE6">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="AF6">
-        <v>-42.27</v>
+        <v>-57.58</v>
       </c>
       <c r="AG6">
         <v>215.99</v>
       </c>
       <c r="AH6">
-        <v>197.96</v>
+        <v>198.15</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1484,7 +1494,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>20.86</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1505,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>381.05</v>
+        <v>383.25</v>
       </c>
       <c r="D7">
-        <v>-0.18</v>
+        <v>0.58</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1507,46 +1517,46 @@
         <v>381.05</v>
       </c>
       <c r="G7">
-        <v>-35.27</v>
+        <v>-34.9</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="I7">
-        <v>-4.33</v>
+        <v>-3.46</v>
       </c>
       <c r="J7">
-        <v>-8.24</v>
+        <v>-7.07</v>
       </c>
       <c r="K7">
-        <v>-10.65</v>
+        <v>-10.87</v>
       </c>
       <c r="L7">
-        <v>-31.67</v>
+        <v>-31.29</v>
       </c>
       <c r="M7">
-        <v>-1.64</v>
+        <v>-1.05</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P7">
-        <v>389.45</v>
+        <v>386.7</v>
       </c>
       <c r="Q7">
-        <v>402.87</v>
+        <v>401.66</v>
       </c>
       <c r="R7">
-        <v>419.3</v>
+        <v>418.54</v>
       </c>
       <c r="S7">
-        <v>463.07</v>
+        <v>462.25</v>
       </c>
       <c r="T7">
-        <v>-17.71</v>
+        <v>-17.09</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1571,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>25.39</v>
+        <v>28.54</v>
       </c>
       <c r="Z7">
-        <v>-9.380000000000001</v>
+        <v>-9.68</v>
       </c>
       <c r="AA7">
-        <v>-7.58</v>
+        <v>-8</v>
       </c>
       <c r="AB7">
-        <v>-1.79</v>
+        <v>-1.67</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>6.04</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AE7">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="AF7">
-        <v>-46.55</v>
+        <v>-32.02</v>
       </c>
       <c r="AG7">
-        <v>423.19</v>
+        <v>423.64</v>
       </c>
       <c r="AH7">
-        <v>382.54</v>
+        <v>379.67</v>
       </c>
       <c r="AI7">
         <v>405.74</v>
@@ -1597,7 +1607,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>42.83</v>
+        <v>45.41</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1618,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>586.5</v>
+        <v>587</v>
       </c>
       <c r="D8">
-        <v>1.09</v>
+        <v>0.09</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1630,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-27.44</v>
+        <v>-27.38</v>
       </c>
       <c r="H8">
-        <v>25.39</v>
+        <v>25.5</v>
       </c>
       <c r="I8">
-        <v>-3.76</v>
+        <v>-4.13</v>
       </c>
       <c r="J8">
-        <v>-9.34</v>
+        <v>-9.32</v>
       </c>
       <c r="K8">
-        <v>-16.53</v>
+        <v>-18.96</v>
       </c>
       <c r="L8">
-        <v>-3.22</v>
+        <v>-3.04</v>
       </c>
       <c r="M8">
-        <v>-16.35</v>
+        <v>-16.03</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="P8">
-        <v>595.29</v>
+        <v>590.23</v>
       </c>
       <c r="Q8">
-        <v>621.96</v>
+        <v>618.1</v>
       </c>
       <c r="R8">
-        <v>654.22</v>
+        <v>651.99</v>
       </c>
       <c r="S8">
-        <v>613.62</v>
+        <v>613.52</v>
       </c>
       <c r="T8">
-        <v>-4.42</v>
+        <v>-4.32</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1684,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>27.93</v>
+        <v>28.33</v>
       </c>
       <c r="Z8">
-        <v>-18.85</v>
+        <v>-18.96</v>
       </c>
       <c r="AA8">
-        <v>-16.52</v>
+        <v>-17.01</v>
       </c>
       <c r="AB8">
-        <v>-2.34</v>
+        <v>-1.95</v>
       </c>
       <c r="AC8">
-        <v>11.79</v>
+        <v>22.78</v>
       </c>
       <c r="AD8">
-        <v>16.45</v>
+        <v>15.02</v>
       </c>
       <c r="AE8">
-        <v>15.85</v>
+        <v>15.27</v>
       </c>
       <c r="AF8">
-        <v>-10.79</v>
+        <v>-61.17</v>
       </c>
       <c r="AG8">
-        <v>668.96</v>
+        <v>663.12</v>
       </c>
       <c r="AH8">
-        <v>574.95</v>
+        <v>573.0700000000001</v>
       </c>
       <c r="AI8">
-        <v>636.3</v>
+        <v>631.65</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>40.56</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1731,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>181.94</v>
+        <v>184.04</v>
       </c>
       <c r="D9">
-        <v>-0.66</v>
+        <v>1.15</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,49 +1743,49 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-34.46</v>
+        <v>-33.7</v>
       </c>
       <c r="H9">
-        <v>5.59</v>
+        <v>6.81</v>
       </c>
       <c r="I9">
-        <v>-2.98</v>
+        <v>-1.86</v>
       </c>
       <c r="J9">
-        <v>-5.32</v>
+        <v>-3.16</v>
       </c>
       <c r="K9">
-        <v>-6.02</v>
+        <v>-4.36</v>
       </c>
       <c r="L9">
-        <v>-29.7</v>
+        <v>-29.32</v>
       </c>
       <c r="M9">
-        <v>-8.09</v>
+        <v>-7.86</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P9">
-        <v>184.66</v>
+        <v>183.97</v>
       </c>
       <c r="Q9">
-        <v>190.66</v>
+        <v>190.43</v>
       </c>
       <c r="R9">
-        <v>190.5</v>
+        <v>190.55</v>
       </c>
       <c r="S9">
-        <v>200.36</v>
+        <v>199.99</v>
       </c>
       <c r="T9">
-        <v>-9.199999999999999</v>
+        <v>-7.98</v>
       </c>
       <c r="U9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="V9" t="s">
         <v>47</v>
@@ -1784,37 +1794,37 @@
         <v>47</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>33.87</v>
+        <v>39.27</v>
       </c>
       <c r="Z9">
-        <v>-2.2</v>
+        <v>-2.29</v>
       </c>
       <c r="AA9">
-        <v>-0.9399999999999999</v>
+        <v>-1.21</v>
       </c>
       <c r="AB9">
-        <v>-1.26</v>
+        <v>-1.08</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>8.34</v>
       </c>
       <c r="AD9">
-        <v>0.32</v>
+        <v>2.78</v>
       </c>
       <c r="AE9">
-        <v>4.53</v>
+        <v>4.62</v>
       </c>
       <c r="AF9">
-        <v>-73.7</v>
+        <v>-29.98</v>
       </c>
       <c r="AG9">
-        <v>201.98</v>
+        <v>202.1</v>
       </c>
       <c r="AH9">
-        <v>179.35</v>
+        <v>178.76</v>
       </c>
       <c r="AI9">
         <v>195.69</v>
@@ -1823,7 +1833,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>44.29</v>
+        <v>40.33</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,58 +1844,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>69.73999999999999</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="D10">
-        <v>-0.98</v>
+        <v>1.86</v>
       </c>
       <c r="E10">
-        <v>131.73</v>
+        <v>130.8</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-47.06</v>
+        <v>-45.69</v>
       </c>
       <c r="H10">
-        <v>17.65</v>
+        <v>19.84</v>
       </c>
       <c r="I10">
-        <v>-4.5</v>
+        <v>-3.65</v>
       </c>
       <c r="J10">
-        <v>-8.869999999999999</v>
+        <v>-6.16</v>
       </c>
       <c r="K10">
-        <v>-14.59</v>
+        <v>-14.56</v>
       </c>
       <c r="L10">
-        <v>-44.41</v>
+        <v>-46.07</v>
       </c>
       <c r="M10">
-        <v>-1.06</v>
+        <v>-0.43</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>71.64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="Q10">
-        <v>73</v>
+        <v>72.89</v>
       </c>
       <c r="R10">
-        <v>76.04000000000001</v>
+        <v>75.89</v>
       </c>
       <c r="S10">
-        <v>80.47</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="T10">
-        <v>-13.34</v>
+        <v>-11.64</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1910,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>33.25</v>
+        <v>39.95</v>
       </c>
       <c r="Z10">
-        <v>-1.41</v>
+        <v>-1.4</v>
       </c>
       <c r="AA10">
-        <v>-1.29</v>
+        <v>-1.31</v>
       </c>
       <c r="AB10">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="AC10">
-        <v>47.19</v>
+        <v>46.82</v>
       </c>
       <c r="AD10">
-        <v>61.28</v>
+        <v>51.18</v>
       </c>
       <c r="AE10">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AF10">
-        <v>-51.73</v>
+        <v>-36.16</v>
       </c>
       <c r="AG10">
-        <v>76.51000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="AH10">
-        <v>69.5</v>
+        <v>69.28</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1936,7 +1946,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>33.32</v>
+        <v>34.66</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2127,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1260 +2145,1314 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.28</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>-6.84</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>-5.47</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-3.51</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>-2.9</v>
       </c>
-      <c r="E8" s="7">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-2.64</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-6.9</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>-4.32</v>
       </c>
-      <c r="E9" s="7">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-2.58</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C11" s="7">
+        <v>1.4</v>
+      </c>
+      <c r="D11" s="7">
+        <v>3.32</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-0.6</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-8.24</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-7.07</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-9.34</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-9.32</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-5.32</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-3.16</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-6.16</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-2.87</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-1.12</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-5.85</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-4.73</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-1.69</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-3.1</v>
+      </c>
+      <c r="E19" s="9">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
         <v>0.8100000000000001</v>
       </c>
-      <c r="D10" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D20" s="7">
+        <v>-2.07</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-2.88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-0.6</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-2.91</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-4.18</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-8.24</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-4.33</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-3.46</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-11.3</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-9.34</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-3.76</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-4.13</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-5.32</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-2.98</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-1.86</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-7.97</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-4.5</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-3.65</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-3.43</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.87</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-33.11</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-33.01</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.73</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.12</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>21.78</v>
+      </c>
+      <c r="D27" s="7">
+        <v>22.26</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-2.56</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.69</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="D28" s="7">
+        <v>29.8</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.15</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>24.26</v>
+      </c>
+      <c r="D29" s="7">
+        <v>25.31</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-1.22</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.91</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>61.96</v>
+      </c>
+      <c r="D30" s="7">
+        <v>58.75</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-4.23</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.33</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-31.67</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-31.29</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-3.9</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-3.76</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-3.22</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-3.04</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-2.72</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-29.7</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-29.32</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-3.35</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-4.5</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-44.41</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-46.07</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-1.08</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-2.99</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-1.91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-13.34</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-15.44</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-5.73</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-5.63</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-8.19</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-10.69</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-10.65</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-10.87</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-16.53</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-18.96</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-6.02</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-4.36</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-14.59</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-14.56</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-35.53</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-35.22</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-9.09</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-8.99</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-20.84</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-20.59</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-7.69</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-18.71</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-17.27</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-35.27</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-34.9</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-27.44</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-27.38</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-34.46</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-33.7</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-47.06</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-45.69</v>
+      </c>
+      <c r="E52" s="8">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1226.6</v>
+      </c>
+      <c r="D53" s="7">
+        <v>1232.5</v>
+      </c>
+      <c r="E53" s="8">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>2920</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2923.2</v>
+      </c>
+      <c r="E54" s="8">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1270.2</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1274.2</v>
+      </c>
+      <c r="E55" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1723.8</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1738.3</v>
+      </c>
+      <c r="E56" s="8">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>202.34</v>
+      </c>
+      <c r="D57" s="7">
+        <v>205.92</v>
+      </c>
+      <c r="E57" s="8">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>381.05</v>
+      </c>
+      <c r="D58" s="7">
+        <v>383.25</v>
+      </c>
+      <c r="E58" s="8">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>586.5</v>
+      </c>
+      <c r="D59" s="7">
+        <v>587</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>181.94</v>
+      </c>
+      <c r="D60" s="7">
+        <v>184.04</v>
+      </c>
+      <c r="E60" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>69.73999999999999</v>
+      </c>
+      <c r="D61" s="7">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="E61" s="8">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="7">
+        <v>88</v>
+      </c>
+      <c r="D62" s="7">
+        <v>77</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>77</v>
+      </c>
+      <c r="D63" s="7">
+        <v>88</v>
+      </c>
+      <c r="E63" s="8">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-33.35</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-33.11</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>28.35</v>
+      </c>
+      <c r="D64" s="7">
+        <v>31.28</v>
+      </c>
+      <c r="E64" s="8">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>25.2</v>
-      </c>
-      <c r="D26" s="6">
-        <v>21.78</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-3.42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>43.04</v>
+      </c>
+      <c r="D65" s="7">
+        <v>43.35</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>30.27</v>
-      </c>
-      <c r="D27" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>42.52</v>
+      </c>
+      <c r="D66" s="7">
+        <v>43.32</v>
+      </c>
+      <c r="E66" s="8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>23.89</v>
-      </c>
-      <c r="D28" s="6">
-        <v>24.26</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>51.5</v>
+      </c>
+      <c r="D67" s="7">
+        <v>53.69</v>
+      </c>
+      <c r="E67" s="8">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>59.19</v>
-      </c>
-      <c r="D29" s="6">
-        <v>61.96</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>43.3</v>
+      </c>
+      <c r="D68" s="7">
+        <v>47.64</v>
+      </c>
+      <c r="E68" s="8">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-32.32</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-31.67</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>25.39</v>
+      </c>
+      <c r="D69" s="7">
+        <v>28.54</v>
+      </c>
+      <c r="E69" s="8">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-2.93</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-3.22</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>27.93</v>
+      </c>
+      <c r="D70" s="7">
+        <v>28.33</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-28.53</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-29.7</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>33.87</v>
+      </c>
+      <c r="D71" s="7">
+        <v>39.27</v>
+      </c>
+      <c r="E71" s="8">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-41.61</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-44.41</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>33.25</v>
+      </c>
+      <c r="D72" s="7">
+        <v>39.95</v>
+      </c>
+      <c r="E72" s="8">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-9.18</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-28.98</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-43.14</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-14.16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-0.51</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-1.08</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-63.51</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-71.84</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-8.33</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-15.35</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-13.34</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-57.17</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-50.68</v>
+      </c>
+      <c r="E75" s="8">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-5.94</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-5.73</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-55.82</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-66.67</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-10.85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-9.25</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-8.19</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-42.27</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-57.58</v>
+      </c>
+      <c r="E77" s="9">
+        <v>-15.31</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-10.4</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-10.65</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-46.55</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-32.02</v>
+      </c>
+      <c r="E78" s="8">
+        <v>14.53</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-18.71</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-16.53</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-10.79</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-61.17</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-50.38</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-7.16</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-6.02</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-73.7</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-29.98</v>
+      </c>
+      <c r="E80" s="8">
+        <v>43.72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-14.52</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-14.59</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-35.61</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-35.53</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-8.83</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-9.09</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-21.78</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-20.84</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-9</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-18.71</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-35.15</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-35.27</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-28.22</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-27.44</v>
-      </c>
-      <c r="E49" s="7">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-34.03</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-34.46</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-46.53</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-47.06</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1225.2</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1226.6</v>
-      </c>
-      <c r="E52" s="7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2928.6</v>
-      </c>
-      <c r="D53" s="6">
-        <v>2920</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-8.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1255</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1270.2</v>
-      </c>
-      <c r="E54" s="7">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1713.8</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1723.8</v>
-      </c>
-      <c r="E55" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>202</v>
-      </c>
-      <c r="D56" s="6">
-        <v>202.34</v>
-      </c>
-      <c r="E56" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>381.75</v>
-      </c>
-      <c r="D57" s="6">
-        <v>381.05</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>580.15</v>
-      </c>
-      <c r="D58" s="6">
-        <v>586.5</v>
-      </c>
-      <c r="E58" s="7">
-        <v>6.35</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>183.14</v>
-      </c>
-      <c r="D59" s="6">
-        <v>181.94</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>70.43000000000001</v>
-      </c>
-      <c r="D60" s="6">
-        <v>69.73999999999999</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>27.67</v>
-      </c>
-      <c r="D61" s="6">
-        <v>28.35</v>
-      </c>
-      <c r="E61" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>43.64</v>
-      </c>
-      <c r="D62" s="6">
-        <v>43.04</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>39.52</v>
-      </c>
-      <c r="D63" s="6">
-        <v>42.52</v>
-      </c>
-      <c r="E63" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>49.99</v>
-      </c>
-      <c r="D64" s="6">
-        <v>51.5</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>42.89</v>
-      </c>
-      <c r="D65" s="6">
-        <v>43.3</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>25.72</v>
-      </c>
-      <c r="D66" s="6">
-        <v>25.39</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>22.82</v>
-      </c>
-      <c r="D67" s="6">
-        <v>27.93</v>
-      </c>
-      <c r="E67" s="7">
-        <v>5.11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>35.55</v>
-      </c>
-      <c r="D68" s="6">
-        <v>33.87</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>35.19</v>
-      </c>
-      <c r="D69" s="6">
-        <v>33.25</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B70" s="5" t="s">
+      <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C70" s="6">
-        <v>77.73</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-28.98</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-106.71</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-14.69</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-63.51</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-48.82</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-33.12</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-57.17</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-24.05</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-33.47</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-55.82</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-22.35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-31.16</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-42.27</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-11.11</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-29.68</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-46.55</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-16.87</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-44.85</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-10.79</v>
-      </c>
-      <c r="E76" s="7">
-        <v>34.06</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-65.01000000000001</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-73.7</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-8.69</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-31.09</v>
-      </c>
-      <c r="D78" s="6">
+      <c r="C81" s="7">
         <v>-51.73</v>
       </c>
-      <c r="E78" s="8">
-        <v>-20.64</v>
+      <c r="D81" s="7">
+        <v>-36.16</v>
+      </c>
+      <c r="E81" s="8">
+        <v>15.57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3408,60 +3472,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="G1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>48.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>36.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>39.5</v>
+      </c>
+      <c r="E2" s="12">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-9.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-3.7</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-10.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3563,61 +3627,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.5932999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1814</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1425</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0166</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.0106</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0164</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.0809</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1199</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1635</v>
+      <c r="A2" s="15">
+        <v>0.5928</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1841</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1463</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0201</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.0043</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0105</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.0786</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.1165</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1603</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="85">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,28 +193,49 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>43.4 → 51.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>43.4</t>
+  </si>
+  <si>
+    <t>51.9</t>
+  </si>
+  <si>
+    <t>43.3 → 53.8</t>
+  </si>
+  <si>
+    <t>43.3</t>
+  </si>
+  <si>
+    <t>53.8</t>
+  </si>
+  <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>28.4 → 31.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.4</t>
-  </si>
-  <si>
-    <t>31.3</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
+    <t>28.5 → 35.3</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>35.3</t>
+  </si>
+  <si>
+    <t>28.3 → 62.0</t>
+  </si>
+  <si>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>62.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -416,7 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,7 +445,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -940,10 +960,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1232.5</v>
+        <v>1259.7</v>
       </c>
       <c r="D2">
-        <v>0.48</v>
+        <v>2.21</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -952,46 +972,46 @@
         <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-35.22</v>
+        <v>-33.79</v>
       </c>
       <c r="H2">
-        <v>0.6</v>
+        <v>2.82</v>
       </c>
       <c r="I2">
-        <v>-2</v>
+        <v>0.43</v>
       </c>
       <c r="J2">
-        <v>-5.47</v>
+        <v>-2.25</v>
       </c>
       <c r="K2">
-        <v>-9.300000000000001</v>
+        <v>-6.22</v>
       </c>
       <c r="L2">
-        <v>-33.01</v>
+        <v>-31.91</v>
       </c>
       <c r="M2">
-        <v>-11.65</v>
+        <v>-10.75</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="P2">
-        <v>1237.02</v>
+        <v>1238.1</v>
       </c>
       <c r="Q2">
-        <v>1275.47</v>
+        <v>1273.4</v>
       </c>
       <c r="R2">
-        <v>1324.44</v>
+        <v>1322.39</v>
       </c>
       <c r="S2">
-        <v>1467.78</v>
+        <v>1464.87</v>
       </c>
       <c r="T2">
-        <v>-16.03</v>
+        <v>-14.01</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1006,34 +1026,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.28</v>
+        <v>42.88</v>
       </c>
       <c r="Z2">
-        <v>-26.23</v>
+        <v>-23.9</v>
       </c>
       <c r="AA2">
-        <v>-22.95</v>
+        <v>-23.14</v>
       </c>
       <c r="AB2">
-        <v>-3.27</v>
+        <v>-0.76</v>
       </c>
       <c r="AC2">
-        <v>9.59</v>
+        <v>42.92</v>
       </c>
       <c r="AD2">
-        <v>3.67</v>
+        <v>17.98</v>
       </c>
       <c r="AE2">
-        <v>22.73</v>
+        <v>24.5</v>
       </c>
       <c r="AF2">
-        <v>-43.14</v>
+        <v>231.62</v>
       </c>
       <c r="AG2">
-        <v>1335.9</v>
+        <v>1332.97</v>
       </c>
       <c r="AH2">
-        <v>1215.05</v>
+        <v>1213.84</v>
       </c>
       <c r="AI2">
         <v>1296.94</v>
@@ -1042,7 +1062,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>24.04</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1053,10 +1073,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2923.2</v>
+        <v>3020</v>
       </c>
       <c r="D3">
-        <v>0.11</v>
+        <v>3.31</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1065,46 +1085,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-8.99</v>
+        <v>-5.98</v>
       </c>
       <c r="H3">
-        <v>66.28</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="I3">
-        <v>-5.85</v>
+        <v>-1.86</v>
       </c>
       <c r="J3">
-        <v>-2.64</v>
+        <v>0.99</v>
       </c>
       <c r="K3">
-        <v>-2.99</v>
+        <v>-0.61</v>
       </c>
       <c r="L3">
-        <v>22.26</v>
+        <v>26.77</v>
       </c>
       <c r="M3">
-        <v>14.63</v>
+        <v>16.38</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>2981.8</v>
+        <v>2970.36</v>
       </c>
       <c r="Q3">
-        <v>2996.03</v>
+        <v>2997.29</v>
       </c>
       <c r="R3">
-        <v>3037.36</v>
+        <v>3036.09</v>
       </c>
       <c r="S3">
-        <v>2537.02</v>
+        <v>2540.81</v>
       </c>
       <c r="T3">
-        <v>15.22</v>
+        <v>18.86</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1119,34 +1139,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.35</v>
+        <v>51.93</v>
       </c>
       <c r="Z3">
-        <v>-17.84</v>
+        <v>-13.06</v>
       </c>
       <c r="AA3">
-        <v>-13.64</v>
+        <v>-13.52</v>
       </c>
       <c r="AB3">
-        <v>-4.2</v>
+        <v>0.47</v>
       </c>
       <c r="AC3">
-        <v>25.78</v>
+        <v>40.5</v>
       </c>
       <c r="AD3">
-        <v>38.23</v>
+        <v>34.6</v>
       </c>
       <c r="AE3">
-        <v>82.97</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="AF3">
-        <v>-71.84</v>
+        <v>-21.74</v>
       </c>
       <c r="AG3">
-        <v>3194.8</v>
+        <v>3196.34</v>
       </c>
       <c r="AH3">
-        <v>2797.26</v>
+        <v>2798.23</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1155,7 +1175,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>23.81</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1166,10 +1186,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1274.2</v>
+        <v>1334.5</v>
       </c>
       <c r="D4">
-        <v>0.31</v>
+        <v>4.73</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1178,46 +1198,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-20.59</v>
+        <v>-16.83</v>
       </c>
       <c r="H4">
-        <v>64.88</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="I4">
-        <v>-3.1</v>
+        <v>2.72</v>
       </c>
       <c r="J4">
-        <v>-2.58</v>
+        <v>3.21</v>
       </c>
       <c r="K4">
-        <v>-15.44</v>
+        <v>-11.18</v>
       </c>
       <c r="L4">
-        <v>29.8</v>
+        <v>35.25</v>
       </c>
       <c r="M4">
-        <v>2.01</v>
+        <v>3.37</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P4">
-        <v>1275.96</v>
+        <v>1283.04</v>
       </c>
       <c r="Q4">
-        <v>1291.9</v>
+        <v>1293.53</v>
       </c>
       <c r="R4">
-        <v>1368.05</v>
+        <v>1365.01</v>
       </c>
       <c r="S4">
-        <v>1186.65</v>
+        <v>1188.12</v>
       </c>
       <c r="T4">
-        <v>7.38</v>
+        <v>12.32</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1232,34 +1252,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>43.32</v>
+        <v>53.75</v>
       </c>
       <c r="Z4">
-        <v>-23.25</v>
+        <v>-17.57</v>
       </c>
       <c r="AA4">
-        <v>-26.08</v>
+        <v>-24.38</v>
       </c>
       <c r="AB4">
-        <v>2.83</v>
+        <v>6.81</v>
       </c>
       <c r="AC4">
-        <v>66.06999999999999</v>
+        <v>81.37</v>
       </c>
       <c r="AD4">
-        <v>67.77</v>
+        <v>71.06</v>
       </c>
       <c r="AE4">
-        <v>37.52</v>
+        <v>39.39</v>
       </c>
       <c r="AF4">
-        <v>-50.68</v>
+        <v>79.88</v>
       </c>
       <c r="AG4">
-        <v>1346.42</v>
+        <v>1351.17</v>
       </c>
       <c r="AH4">
-        <v>1237.37</v>
+        <v>1235.89</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1268,7 +1288,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>18.53</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1279,10 +1299,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1738.3</v>
+        <v>1824</v>
       </c>
       <c r="D5">
-        <v>0.84</v>
+        <v>4.93</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1291,46 +1311,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.69</v>
+        <v>-3.14</v>
       </c>
       <c r="H5">
-        <v>33.91</v>
+        <v>40.51</v>
       </c>
       <c r="I5">
-        <v>-2.07</v>
+        <v>3.17</v>
       </c>
       <c r="J5">
-        <v>3.32</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K5">
-        <v>-5.63</v>
+        <v>-0.62</v>
       </c>
       <c r="L5">
-        <v>25.31</v>
+        <v>31.29</v>
       </c>
       <c r="M5">
-        <v>18.41</v>
+        <v>20.16</v>
       </c>
       <c r="N5">
         <v>88</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P5">
-        <v>1741.7</v>
+        <v>1752.9</v>
       </c>
       <c r="Q5">
-        <v>1704.94</v>
+        <v>1711.34</v>
       </c>
       <c r="R5">
-        <v>1729.34</v>
+        <v>1729.81</v>
       </c>
       <c r="S5">
-        <v>1611.85</v>
+        <v>1613.35</v>
       </c>
       <c r="T5">
-        <v>7.85</v>
+        <v>13.06</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1345,43 +1365,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>53.69</v>
+        <v>64.02</v>
       </c>
       <c r="Z5">
-        <v>7.05</v>
+        <v>14.57</v>
       </c>
       <c r="AA5">
-        <v>-0.19</v>
+        <v>2.76</v>
       </c>
       <c r="AB5">
-        <v>7.24</v>
+        <v>11.81</v>
       </c>
       <c r="AC5">
-        <v>70.34999999999999</v>
+        <v>82.19</v>
       </c>
       <c r="AD5">
-        <v>76.95999999999999</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="AE5">
-        <v>38.35</v>
+        <v>41.73</v>
       </c>
       <c r="AF5">
-        <v>-66.67</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AG5">
-        <v>1787.58</v>
+        <v>1809.44</v>
       </c>
       <c r="AH5">
-        <v>1622.29</v>
+        <v>1613.23</v>
       </c>
       <c r="AI5">
-        <v>1647.25</v>
+        <v>1658.8</v>
       </c>
       <c r="AJ5" t="s">
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>18.17</v>
+        <v>21.83</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1392,10 +1412,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>205.92</v>
+        <v>206.6</v>
       </c>
       <c r="D6">
-        <v>1.77</v>
+        <v>0.33</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1404,25 +1424,25 @@
         <v>126.1</v>
       </c>
       <c r="G6">
-        <v>-17.27</v>
+        <v>-17</v>
       </c>
       <c r="H6">
-        <v>63.3</v>
+        <v>63.84</v>
       </c>
       <c r="I6">
-        <v>-4.18</v>
+        <v>-3.23</v>
       </c>
       <c r="J6">
-        <v>0.17</v>
+        <v>1.26</v>
       </c>
       <c r="K6">
-        <v>-10.69</v>
+        <v>-10.86</v>
       </c>
       <c r="L6">
-        <v>58.75</v>
+        <v>60.37</v>
       </c>
       <c r="M6">
-        <v>59.28</v>
+        <v>61.11</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1431,19 +1451,19 @@
         <v>83</v>
       </c>
       <c r="P6">
-        <v>206.75</v>
+        <v>205.37</v>
       </c>
       <c r="Q6">
-        <v>207.07</v>
+        <v>207.2</v>
       </c>
       <c r="R6">
-        <v>210.08</v>
+        <v>209.88</v>
       </c>
       <c r="S6">
-        <v>185.17</v>
+        <v>185.47</v>
       </c>
       <c r="T6">
-        <v>11.21</v>
+        <v>11.4</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1458,34 +1478,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>47.64</v>
+        <v>48.44</v>
       </c>
       <c r="Z6">
-        <v>-0.95</v>
+        <v>-0.91</v>
       </c>
       <c r="AA6">
         <v>-0.9</v>
       </c>
       <c r="AB6">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>36.82</v>
+        <v>46.7</v>
       </c>
       <c r="AD6">
-        <v>45.27</v>
+        <v>41.33</v>
       </c>
       <c r="AE6">
-        <v>5.75</v>
+        <v>5.62</v>
       </c>
       <c r="AF6">
-        <v>-57.58</v>
+        <v>-10.14</v>
       </c>
       <c r="AG6">
-        <v>215.99</v>
+        <v>216.01</v>
       </c>
       <c r="AH6">
-        <v>198.15</v>
+        <v>198.39</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1494,7 +1514,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>21.27</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1505,10 +1525,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>383.25</v>
+        <v>388.3</v>
       </c>
       <c r="D7">
-        <v>0.58</v>
+        <v>1.32</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1517,25 +1537,25 @@
         <v>381.05</v>
       </c>
       <c r="G7">
-        <v>-34.9</v>
+        <v>-34.04</v>
       </c>
       <c r="H7">
-        <v>0.58</v>
+        <v>1.9</v>
       </c>
       <c r="I7">
-        <v>-3.46</v>
+        <v>-1.85</v>
       </c>
       <c r="J7">
-        <v>-7.07</v>
+        <v>-4.71</v>
       </c>
       <c r="K7">
-        <v>-10.87</v>
+        <v>-8.41</v>
       </c>
       <c r="L7">
-        <v>-31.29</v>
+        <v>-31.39</v>
       </c>
       <c r="M7">
-        <v>-1.05</v>
+        <v>-0.31</v>
       </c>
       <c r="N7">
         <v>23</v>
@@ -1544,19 +1564,19 @@
         <v>22</v>
       </c>
       <c r="P7">
-        <v>386.7</v>
+        <v>385.24</v>
       </c>
       <c r="Q7">
-        <v>401.66</v>
+        <v>400.52</v>
       </c>
       <c r="R7">
-        <v>418.54</v>
+        <v>417.75</v>
       </c>
       <c r="S7">
-        <v>462.25</v>
+        <v>461.49</v>
       </c>
       <c r="T7">
-        <v>-17.09</v>
+        <v>-15.86</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1571,34 +1591,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>28.54</v>
+        <v>35.31</v>
       </c>
       <c r="Z7">
-        <v>-9.68</v>
+        <v>-9.4</v>
       </c>
       <c r="AA7">
-        <v>-8</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AB7">
-        <v>-1.67</v>
+        <v>-1.11</v>
       </c>
       <c r="AC7">
-        <v>6.04</v>
+        <v>28.47</v>
       </c>
       <c r="AD7">
-        <v>2.01</v>
+        <v>11.5</v>
       </c>
       <c r="AE7">
-        <v>7.6</v>
+        <v>7.97</v>
       </c>
       <c r="AF7">
-        <v>-32.02</v>
+        <v>48.58</v>
       </c>
       <c r="AG7">
-        <v>423.64</v>
+        <v>422.82</v>
       </c>
       <c r="AH7">
-        <v>379.67</v>
+        <v>378.22</v>
       </c>
       <c r="AI7">
         <v>405.74</v>
@@ -1607,7 +1627,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>45.41</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1618,10 +1638,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>587</v>
+        <v>660.7</v>
       </c>
       <c r="D8">
-        <v>0.09</v>
+        <v>12.56</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1630,46 +1650,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-27.38</v>
+        <v>-18.26</v>
       </c>
       <c r="H8">
-        <v>25.5</v>
+        <v>41.25</v>
       </c>
       <c r="I8">
-        <v>-4.13</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="J8">
-        <v>-9.32</v>
+        <v>-0.53</v>
       </c>
       <c r="K8">
-        <v>-18.96</v>
+        <v>-9.16</v>
       </c>
       <c r="L8">
-        <v>-3.04</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="M8">
-        <v>-16.03</v>
+        <v>-13.85</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="P8">
-        <v>590.23</v>
+        <v>601.83</v>
       </c>
       <c r="Q8">
-        <v>618.1</v>
+        <v>618.25</v>
       </c>
       <c r="R8">
-        <v>651.99</v>
+        <v>651.1900000000001</v>
       </c>
       <c r="S8">
-        <v>613.52</v>
+        <v>613.79</v>
       </c>
       <c r="T8">
-        <v>-4.32</v>
+        <v>7.64</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1681,46 +1701,46 @@
         <v>47</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8">
-        <v>28.33</v>
+        <v>62.01</v>
       </c>
       <c r="Z8">
-        <v>-18.96</v>
+        <v>-12.95</v>
       </c>
       <c r="AA8">
-        <v>-17.01</v>
+        <v>-16.19</v>
       </c>
       <c r="AB8">
-        <v>-1.95</v>
+        <v>3.25</v>
       </c>
       <c r="AC8">
-        <v>22.78</v>
+        <v>56.11</v>
       </c>
       <c r="AD8">
-        <v>15.02</v>
+        <v>30.23</v>
       </c>
       <c r="AE8">
-        <v>15.27</v>
+        <v>20.45</v>
       </c>
       <c r="AF8">
-        <v>-61.17</v>
+        <v>3976.36</v>
       </c>
       <c r="AG8">
-        <v>663.12</v>
+        <v>663.85</v>
       </c>
       <c r="AH8">
-        <v>573.0700000000001</v>
+        <v>572.64</v>
       </c>
       <c r="AI8">
-        <v>631.65</v>
+        <v>570.71</v>
       </c>
       <c r="AJ8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK8">
-        <v>42.78</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1731,10 +1751,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>184.04</v>
+        <v>186.98</v>
       </c>
       <c r="D9">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1743,46 +1763,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.7</v>
+        <v>-32.64</v>
       </c>
       <c r="H9">
-        <v>6.81</v>
+        <v>8.52</v>
       </c>
       <c r="I9">
-        <v>-1.86</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J9">
-        <v>-3.16</v>
+        <v>-0.92</v>
       </c>
       <c r="K9">
-        <v>-4.36</v>
+        <v>1.45</v>
       </c>
       <c r="L9">
-        <v>-29.32</v>
+        <v>-27.6</v>
       </c>
       <c r="M9">
-        <v>-7.86</v>
+        <v>-7.53</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="P9">
-        <v>183.97</v>
+        <v>184.22</v>
       </c>
       <c r="Q9">
-        <v>190.43</v>
+        <v>190.35</v>
       </c>
       <c r="R9">
-        <v>190.55</v>
+        <v>190.58</v>
       </c>
       <c r="S9">
-        <v>199.99</v>
+        <v>199.65</v>
       </c>
       <c r="T9">
-        <v>-7.98</v>
+        <v>-6.35</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1797,34 +1817,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>39.27</v>
+        <v>45.93</v>
       </c>
       <c r="Z9">
-        <v>-2.29</v>
+        <v>-2.11</v>
       </c>
       <c r="AA9">
-        <v>-1.21</v>
+        <v>-1.39</v>
       </c>
       <c r="AB9">
-        <v>-1.08</v>
+        <v>-0.72</v>
       </c>
       <c r="AC9">
-        <v>8.34</v>
+        <v>30.48</v>
       </c>
       <c r="AD9">
-        <v>2.78</v>
+        <v>12.94</v>
       </c>
       <c r="AE9">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="AF9">
-        <v>-29.98</v>
+        <v>-20.46</v>
       </c>
       <c r="AG9">
         <v>202.1</v>
       </c>
       <c r="AH9">
-        <v>178.76</v>
+        <v>178.6</v>
       </c>
       <c r="AI9">
         <v>195.69</v>
@@ -1833,7 +1853,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>40.33</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1844,10 +1864,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>71.04000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="D10">
-        <v>1.86</v>
+        <v>0.96</v>
       </c>
       <c r="E10">
         <v>130.8</v>
@@ -1856,46 +1876,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-45.69</v>
+        <v>-45.17</v>
       </c>
       <c r="H10">
-        <v>19.84</v>
+        <v>20.99</v>
       </c>
       <c r="I10">
-        <v>-3.65</v>
+        <v>-0.79</v>
       </c>
       <c r="J10">
-        <v>-6.16</v>
+        <v>-2.21</v>
       </c>
       <c r="K10">
-        <v>-14.56</v>
+        <v>-11.49</v>
       </c>
       <c r="L10">
-        <v>-46.07</v>
+        <v>-44.09</v>
       </c>
       <c r="M10">
-        <v>-0.43</v>
+        <v>-2.13</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P10">
-        <v>71.09999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="Q10">
-        <v>72.89</v>
+        <v>72.7</v>
       </c>
       <c r="R10">
-        <v>75.89</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="S10">
-        <v>80.40000000000001</v>
+        <v>80.33</v>
       </c>
       <c r="T10">
-        <v>-11.64</v>
+        <v>-10.72</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1910,31 +1930,31 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>39.95</v>
+        <v>43.16</v>
       </c>
       <c r="Z10">
-        <v>-1.4</v>
+        <v>-1.31</v>
       </c>
       <c r="AA10">
         <v>-1.31</v>
       </c>
       <c r="AB10">
-        <v>-0.08</v>
+        <v>-0</v>
       </c>
       <c r="AC10">
-        <v>46.82</v>
+        <v>59.34</v>
       </c>
       <c r="AD10">
-        <v>51.18</v>
+        <v>51.12</v>
       </c>
       <c r="AE10">
         <v>2.45</v>
       </c>
       <c r="AF10">
-        <v>-36.16</v>
+        <v>-6.34</v>
       </c>
       <c r="AG10">
-        <v>76.48999999999999</v>
+        <v>76.12</v>
       </c>
       <c r="AH10">
         <v>69.28</v>
@@ -1946,7 +1966,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>34.66</v>
+        <v>31.37</v>
       </c>
     </row>
   </sheetData>
@@ -2087,7 +2107,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2127,7 +2147,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2146,1313 +2166,1339 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-5.47</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-2.25</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="E12" s="7">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-2.58</v>
+      </c>
+      <c r="D13" s="6">
+        <v>3.21</v>
+      </c>
+      <c r="E13" s="7">
+        <v>5.79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3.32</v>
+      </c>
+      <c r="D14" s="6">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="E14" s="7">
+        <v>5.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.17</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1.26</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-7.07</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-4.71</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-9.32</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-0.53</v>
+      </c>
+      <c r="E17" s="7">
+        <v>8.789999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-3.16</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.92</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-6.16</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.21</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-6.84</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-5.47</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-2.9</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-2.64</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-5.85</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-1.86</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-4.32</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-2.58</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-3.1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2.72</v>
+      </c>
+      <c r="E22" s="7">
+        <v>5.82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1.4</v>
-      </c>
-      <c r="D11" s="7">
-        <v>3.32</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-2.07</v>
+      </c>
+      <c r="D23" s="6">
+        <v>3.17</v>
+      </c>
+      <c r="E23" s="7">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-0.6</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.17</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-4.18</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.23</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-8.24</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-7.07</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-3.46</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-9.34</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-9.32</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-4.13</v>
+      </c>
+      <c r="D26" s="6">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="E26" s="7">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-5.32</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-3.16</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-1.86</v>
+      </c>
+      <c r="D27" s="6">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-6.16</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-3.65</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-0.79</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.87</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-2</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-33.01</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-31.91</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1.12</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-5.85</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-4.73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>22.26</v>
+      </c>
+      <c r="D30" s="6">
+        <v>26.77</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.69</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-3.1</v>
-      </c>
-      <c r="E19" s="9">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>29.8</v>
+      </c>
+      <c r="D31" s="6">
+        <v>35.25</v>
+      </c>
+      <c r="E31" s="7">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-2.07</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-2.88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>25.31</v>
+      </c>
+      <c r="D32" s="6">
+        <v>31.29</v>
+      </c>
+      <c r="E32" s="7">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-2.91</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-4.18</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>58.75</v>
+      </c>
+      <c r="D33" s="6">
+        <v>60.37</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-4.33</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-3.46</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-31.29</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-31.39</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-3.76</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-4.13</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-3.04</v>
+      </c>
+      <c r="D35" s="6">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="E35" s="7">
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-2.98</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-29.32</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-27.6</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-3.65</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-46.07</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-44.09</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-33.11</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-33.01</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-6.22</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>21.78</v>
-      </c>
-      <c r="D27" s="7">
-        <v>22.26</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-2.99</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-0.61</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>30.1</v>
-      </c>
-      <c r="D28" s="7">
-        <v>29.8</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-15.44</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-11.18</v>
+      </c>
+      <c r="E40" s="7">
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>24.26</v>
-      </c>
-      <c r="D29" s="7">
-        <v>25.31</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-5.63</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-0.62</v>
+      </c>
+      <c r="E41" s="7">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>61.96</v>
-      </c>
-      <c r="D30" s="7">
-        <v>58.75</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-3.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-10.69</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-10.86</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-31.67</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-31.29</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-10.87</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-8.41</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-3.22</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-3.04</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-18.96</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-9.16</v>
+      </c>
+      <c r="E44" s="7">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-29.7</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-29.32</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-4.36</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1.45</v>
+      </c>
+      <c r="E45" s="7">
+        <v>5.81</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-44.41</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-46.07</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-14.56</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-11.49</v>
+      </c>
+      <c r="E46" s="7">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-35.22</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-33.79</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-1.08</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-2.99</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-8.99</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-5.98</v>
+      </c>
+      <c r="E48" s="7">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-13.34</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-15.44</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-20.59</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-16.83</v>
+      </c>
+      <c r="E49" s="7">
+        <v>3.76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-5.73</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-5.63</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-7.69</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="E50" s="7">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-8.19</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-10.69</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-17.27</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-17</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-10.65</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-10.87</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-34.9</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-34.04</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-16.53</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-18.96</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-27.38</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-18.26</v>
+      </c>
+      <c r="E53" s="7">
+        <v>9.119999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-6.02</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-4.36</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="6">
+        <v>-33.7</v>
+      </c>
+      <c r="D54" s="6">
+        <v>-32.64</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-14.59</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-14.56</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="6">
+        <v>-45.69</v>
+      </c>
+      <c r="D55" s="6">
+        <v>-45.17</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-35.53</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-35.22</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1232.5</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1259.7</v>
+      </c>
+      <c r="E56" s="7">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-9.09</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-8.99</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>2923.2</v>
+      </c>
+      <c r="D57" s="6">
+        <v>3020</v>
+      </c>
+      <c r="E57" s="7">
+        <v>96.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-20.84</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-20.59</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>1274.2</v>
+      </c>
+      <c r="D58" s="6">
+        <v>1334.5</v>
+      </c>
+      <c r="E58" s="7">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-7.69</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>1738.3</v>
+      </c>
+      <c r="D59" s="6">
+        <v>1824</v>
+      </c>
+      <c r="E59" s="7">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-18.71</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-17.27</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>205.92</v>
+      </c>
+      <c r="D60" s="6">
+        <v>206.6</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-35.27</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-34.9</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>383.25</v>
+      </c>
+      <c r="D61" s="6">
+        <v>388.3</v>
+      </c>
+      <c r="E61" s="7">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-27.44</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-27.38</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="6">
+        <v>587</v>
+      </c>
+      <c r="D62" s="6">
+        <v>660.7</v>
+      </c>
+      <c r="E62" s="7">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-34.46</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-33.7</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
+      <c r="B63" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C63" s="6">
+        <v>184.04</v>
+      </c>
+      <c r="D63" s="6">
+        <v>186.98</v>
+      </c>
+      <c r="E63" s="7">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-47.06</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-45.69</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
+      <c r="B64" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C64" s="6">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="D64" s="6">
+        <v>71.72</v>
+      </c>
+      <c r="E64" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1226.6</v>
-      </c>
-      <c r="D53" s="7">
-        <v>1232.5</v>
-      </c>
-      <c r="E53" s="8">
-        <v>5.9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>31.28</v>
+      </c>
+      <c r="D65" s="6">
+        <v>42.88</v>
+      </c>
+      <c r="E65" s="7">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2920</v>
-      </c>
-      <c r="D54" s="7">
-        <v>2923.2</v>
-      </c>
-      <c r="E54" s="8">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>43.35</v>
+      </c>
+      <c r="D66" s="6">
+        <v>51.93</v>
+      </c>
+      <c r="E66" s="7">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1270.2</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1274.2</v>
-      </c>
-      <c r="E55" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>43.32</v>
+      </c>
+      <c r="D67" s="6">
+        <v>53.75</v>
+      </c>
+      <c r="E67" s="7">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>1723.8</v>
-      </c>
-      <c r="D56" s="7">
-        <v>1738.3</v>
-      </c>
-      <c r="E56" s="8">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>53.69</v>
+      </c>
+      <c r="D68" s="6">
+        <v>64.02</v>
+      </c>
+      <c r="E68" s="7">
+        <v>10.33</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>202.34</v>
-      </c>
-      <c r="D57" s="7">
-        <v>205.92</v>
-      </c>
-      <c r="E57" s="8">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>47.64</v>
+      </c>
+      <c r="D69" s="6">
+        <v>48.44</v>
+      </c>
+      <c r="E69" s="7">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>381.05</v>
-      </c>
-      <c r="D58" s="7">
-        <v>383.25</v>
-      </c>
-      <c r="E58" s="8">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>28.54</v>
+      </c>
+      <c r="D70" s="6">
+        <v>35.31</v>
+      </c>
+      <c r="E70" s="7">
+        <v>6.77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>586.5</v>
-      </c>
-      <c r="D59" s="7">
-        <v>587</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>28.33</v>
+      </c>
+      <c r="D71" s="6">
+        <v>62.01</v>
+      </c>
+      <c r="E71" s="7">
+        <v>33.68</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>181.94</v>
-      </c>
-      <c r="D60" s="7">
-        <v>184.04</v>
-      </c>
-      <c r="E60" s="8">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>39.27</v>
+      </c>
+      <c r="D72" s="6">
+        <v>45.93</v>
+      </c>
+      <c r="E72" s="7">
+        <v>6.66</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>69.73999999999999</v>
-      </c>
-      <c r="D61" s="7">
-        <v>71.04000000000001</v>
-      </c>
-      <c r="E61" s="8">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>39.95</v>
+      </c>
+      <c r="D73" s="6">
+        <v>43.16</v>
+      </c>
+      <c r="E73" s="7">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-43.14</v>
+      </c>
+      <c r="D74" s="6">
+        <v>231.62</v>
+      </c>
+      <c r="E74" s="7">
+        <v>274.76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>88</v>
-      </c>
-      <c r="D62" s="7">
-        <v>77</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-71.84</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-21.74</v>
+      </c>
+      <c r="E75" s="7">
+        <v>50.1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-50.68</v>
+      </c>
+      <c r="D76" s="6">
+        <v>79.88</v>
+      </c>
+      <c r="E76" s="7">
+        <v>130.56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>77</v>
-      </c>
-      <c r="D63" s="7">
-        <v>88</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>28.35</v>
-      </c>
-      <c r="D64" s="7">
-        <v>31.28</v>
-      </c>
-      <c r="E64" s="8">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>43.04</v>
-      </c>
-      <c r="D65" s="7">
-        <v>43.35</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>42.52</v>
-      </c>
-      <c r="D66" s="7">
-        <v>43.32</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>51.5</v>
-      </c>
-      <c r="D67" s="7">
-        <v>53.69</v>
-      </c>
-      <c r="E67" s="8">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-66.67</v>
+      </c>
+      <c r="D77" s="6">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="E77" s="7">
+        <v>143.07</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>43.3</v>
-      </c>
-      <c r="D68" s="7">
-        <v>47.64</v>
-      </c>
-      <c r="E68" s="8">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-57.58</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-10.14</v>
+      </c>
+      <c r="E78" s="7">
+        <v>47.44</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>25.39</v>
-      </c>
-      <c r="D69" s="7">
-        <v>28.54</v>
-      </c>
-      <c r="E69" s="8">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-32.02</v>
+      </c>
+      <c r="D79" s="6">
+        <v>48.58</v>
+      </c>
+      <c r="E79" s="7">
+        <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>27.93</v>
-      </c>
-      <c r="D70" s="7">
-        <v>28.33</v>
-      </c>
-      <c r="E70" s="8">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-61.17</v>
+      </c>
+      <c r="D80" s="6">
+        <v>3976.36</v>
+      </c>
+      <c r="E80" s="7">
+        <v>4037.53</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>33.87</v>
-      </c>
-      <c r="D71" s="7">
-        <v>39.27</v>
-      </c>
-      <c r="E71" s="8">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-29.98</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-20.46</v>
+      </c>
+      <c r="E81" s="7">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>33.25</v>
-      </c>
-      <c r="D72" s="7">
-        <v>39.95</v>
-      </c>
-      <c r="E72" s="8">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="7">
-        <v>-28.98</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-43.14</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-14.16</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-63.51</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-71.84</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-8.33</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-57.17</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-50.68</v>
-      </c>
-      <c r="E75" s="8">
-        <v>6.49</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-55.82</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-66.67</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-10.85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-42.27</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-57.58</v>
-      </c>
-      <c r="E77" s="9">
-        <v>-15.31</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-46.55</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-32.02</v>
-      </c>
-      <c r="E78" s="8">
-        <v>14.53</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-10.79</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-61.17</v>
-      </c>
-      <c r="E79" s="9">
-        <v>-50.38</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-73.7</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-29.98</v>
-      </c>
-      <c r="E80" s="8">
-        <v>43.72</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-51.73</v>
-      </c>
-      <c r="D81" s="7">
+      <c r="C82" s="6">
         <v>-36.16</v>
       </c>
-      <c r="E81" s="8">
-        <v>15.57</v>
+      <c r="D82" s="6">
+        <v>-6.34</v>
+      </c>
+      <c r="E82" s="7">
+        <v>29.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3472,60 +3518,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>77</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>56.16</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>39.5</v>
-      </c>
-      <c r="E2" s="12">
-        <v>40</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-3.7</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-10.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>49.7</v>
+      </c>
+      <c r="E2" s="11">
+        <v>60</v>
+      </c>
+      <c r="F2" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3627,61 +3673,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.5928</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1841</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1463</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0201</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.0043</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0105</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.0786</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.1165</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1603</v>
+      <c r="A2" s="14">
+        <v>0.6111</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2016</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1638</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0337</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.0031</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0213</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.07530000000000001</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.1075</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1385</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,46 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>43.4 → 51.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>43.4</t>
+    <t>51.9 → 48.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.9</t>
   </si>
   <si>
-    <t>43.3 → 53.8</t>
-  </si>
-  <si>
-    <t>43.3</t>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>53.8 → 48.8</t>
   </si>
   <si>
     <t>53.8</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.5 → 35.3</t>
-  </si>
-  <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>35.3</t>
-  </si>
-  <si>
-    <t>28.3 → 62.0</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>62.0</t>
+    <t>48.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -321,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -361,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -960,10 +939,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1259.7</v>
+        <v>1256.3</v>
       </c>
       <c r="D2">
-        <v>2.21</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -972,46 +951,46 @@
         <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-33.79</v>
+        <v>-33.97</v>
       </c>
       <c r="H2">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="I2">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
       <c r="J2">
-        <v>-2.25</v>
+        <v>-3.44</v>
       </c>
       <c r="K2">
-        <v>-6.22</v>
+        <v>-6.93</v>
       </c>
       <c r="L2">
-        <v>-31.91</v>
+        <v>-32.28</v>
       </c>
       <c r="M2">
-        <v>-10.75</v>
+        <v>-10.84</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2">
-        <v>1238.1</v>
+        <v>1240.06</v>
       </c>
       <c r="Q2">
-        <v>1273.4</v>
+        <v>1270.85</v>
       </c>
       <c r="R2">
-        <v>1322.39</v>
+        <v>1319.83</v>
       </c>
       <c r="S2">
-        <v>1464.87</v>
+        <v>1461.95</v>
       </c>
       <c r="T2">
-        <v>-14.01</v>
+        <v>-14.07</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1026,34 +1005,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.88</v>
+        <v>41.93</v>
       </c>
       <c r="Z2">
-        <v>-23.9</v>
+        <v>-22.08</v>
       </c>
       <c r="AA2">
-        <v>-23.14</v>
+        <v>-22.93</v>
       </c>
       <c r="AB2">
-        <v>-0.76</v>
+        <v>0.85</v>
       </c>
       <c r="AC2">
-        <v>42.92</v>
+        <v>72.73</v>
       </c>
       <c r="AD2">
-        <v>17.98</v>
+        <v>41.75</v>
       </c>
       <c r="AE2">
-        <v>24.5</v>
+        <v>24.25</v>
       </c>
       <c r="AF2">
-        <v>231.62</v>
+        <v>-48.1</v>
       </c>
       <c r="AG2">
-        <v>1332.97</v>
+        <v>1328.63</v>
       </c>
       <c r="AH2">
-        <v>1213.84</v>
+        <v>1213.07</v>
       </c>
       <c r="AI2">
         <v>1296.94</v>
@@ -1062,7 +1041,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>25.88</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1073,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>3020</v>
+        <v>2975</v>
       </c>
       <c r="D3">
-        <v>3.31</v>
+        <v>-1.49</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1085,46 +1064,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-5.98</v>
+        <v>-7.38</v>
       </c>
       <c r="H3">
-        <v>71.79000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="I3">
-        <v>-1.86</v>
+        <v>-2.78</v>
       </c>
       <c r="J3">
-        <v>0.99</v>
+        <v>-0.66</v>
       </c>
       <c r="K3">
-        <v>-0.61</v>
+        <v>-2.77</v>
       </c>
       <c r="L3">
-        <v>26.77</v>
+        <v>24.04</v>
       </c>
       <c r="M3">
-        <v>16.38</v>
+        <v>15.65</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P3">
-        <v>2970.36</v>
+        <v>2953.36</v>
       </c>
       <c r="Q3">
-        <v>2997.29</v>
+        <v>2996.19</v>
       </c>
       <c r="R3">
-        <v>3036.09</v>
+        <v>3032.44</v>
       </c>
       <c r="S3">
-        <v>2540.81</v>
+        <v>2544.49</v>
       </c>
       <c r="T3">
-        <v>18.86</v>
+        <v>16.92</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1139,34 +1118,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>51.93</v>
+        <v>48.27</v>
       </c>
       <c r="Z3">
-        <v>-13.06</v>
+        <v>-12.76</v>
       </c>
       <c r="AA3">
-        <v>-13.52</v>
+        <v>-13.37</v>
       </c>
       <c r="AB3">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="AC3">
-        <v>40.5</v>
+        <v>50.34</v>
       </c>
       <c r="AD3">
-        <v>34.6</v>
+        <v>38.87</v>
       </c>
       <c r="AE3">
-        <v>83.95999999999999</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="AF3">
-        <v>-21.74</v>
+        <v>-62.96</v>
       </c>
       <c r="AG3">
-        <v>3196.34</v>
+        <v>3195.49</v>
       </c>
       <c r="AH3">
-        <v>2798.23</v>
+        <v>2796.88</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1175,7 +1154,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>22.47</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1186,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1334.5</v>
+        <v>1303.6</v>
       </c>
       <c r="D4">
-        <v>4.73</v>
+        <v>-2.32</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1198,46 +1177,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-16.83</v>
+        <v>-18.75</v>
       </c>
       <c r="H4">
-        <v>72.68000000000001</v>
+        <v>68.69</v>
       </c>
       <c r="I4">
-        <v>2.72</v>
+        <v>1.74</v>
       </c>
       <c r="J4">
-        <v>3.21</v>
+        <v>0.14</v>
       </c>
       <c r="K4">
-        <v>-11.18</v>
+        <v>-15.89</v>
       </c>
       <c r="L4">
-        <v>35.25</v>
+        <v>31.96</v>
       </c>
       <c r="M4">
-        <v>3.37</v>
+        <v>3.07</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1283.04</v>
+        <v>1287.5</v>
       </c>
       <c r="Q4">
-        <v>1293.53</v>
+        <v>1292.71</v>
       </c>
       <c r="R4">
-        <v>1365.01</v>
+        <v>1360.35</v>
       </c>
       <c r="S4">
-        <v>1188.12</v>
+        <v>1189.53</v>
       </c>
       <c r="T4">
-        <v>12.32</v>
+        <v>9.59</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1252,34 +1231,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>53.75</v>
+        <v>48.79</v>
       </c>
       <c r="Z4">
-        <v>-17.57</v>
+        <v>-15.38</v>
       </c>
       <c r="AA4">
-        <v>-24.38</v>
+        <v>-22.58</v>
       </c>
       <c r="AB4">
-        <v>6.81</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>81.37</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="AD4">
-        <v>71.06</v>
+        <v>75.92</v>
       </c>
       <c r="AE4">
-        <v>39.39</v>
+        <v>39.03</v>
       </c>
       <c r="AF4">
-        <v>79.88</v>
+        <v>-57.15</v>
       </c>
       <c r="AG4">
-        <v>1351.17</v>
+        <v>1349.22</v>
       </c>
       <c r="AH4">
-        <v>1235.89</v>
+        <v>1236.2</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1288,7 +1267,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>19.71</v>
+        <v>20.74</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1299,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1824</v>
+        <v>1787.1</v>
       </c>
       <c r="D5">
-        <v>4.93</v>
+        <v>-2.02</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1311,46 +1290,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-3.14</v>
+        <v>-5.1</v>
       </c>
       <c r="H5">
-        <v>40.51</v>
+        <v>37.67</v>
       </c>
       <c r="I5">
-        <v>3.17</v>
+        <v>1.28</v>
       </c>
       <c r="J5">
-        <v>8.449999999999999</v>
+        <v>5.37</v>
       </c>
       <c r="K5">
-        <v>-0.62</v>
+        <v>-2.19</v>
       </c>
       <c r="L5">
-        <v>31.29</v>
+        <v>27.44</v>
       </c>
       <c r="M5">
-        <v>20.16</v>
+        <v>19.62</v>
       </c>
       <c r="N5">
         <v>88</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>1752.9</v>
+        <v>1757.4</v>
       </c>
       <c r="Q5">
-        <v>1711.34</v>
+        <v>1715.69</v>
       </c>
       <c r="R5">
-        <v>1729.81</v>
+        <v>1728.99</v>
       </c>
       <c r="S5">
-        <v>1613.35</v>
+        <v>1614.72</v>
       </c>
       <c r="T5">
-        <v>13.06</v>
+        <v>10.68</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1365,34 +1344,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>64.02</v>
+        <v>58.02</v>
       </c>
       <c r="Z5">
-        <v>14.57</v>
+        <v>17.36</v>
       </c>
       <c r="AA5">
-        <v>2.76</v>
+        <v>5.68</v>
       </c>
       <c r="AB5">
-        <v>11.81</v>
+        <v>11.68</v>
       </c>
       <c r="AC5">
-        <v>82.19</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="AD5">
-        <v>76.15000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="AE5">
-        <v>41.73</v>
+        <v>42.85</v>
       </c>
       <c r="AF5">
-        <v>76.40000000000001</v>
+        <v>-6.9</v>
       </c>
       <c r="AG5">
-        <v>1809.44</v>
+        <v>1819.26</v>
       </c>
       <c r="AH5">
-        <v>1613.23</v>
+        <v>1612.12</v>
       </c>
       <c r="AI5">
         <v>1658.8</v>
@@ -1401,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>21.83</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1412,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>206.6</v>
+        <v>206.55</v>
       </c>
       <c r="D6">
-        <v>0.33</v>
+        <v>-0.02</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1424,25 +1403,25 @@
         <v>126.1</v>
       </c>
       <c r="G6">
-        <v>-17</v>
+        <v>-17.02</v>
       </c>
       <c r="H6">
-        <v>63.84</v>
+        <v>63.8</v>
       </c>
       <c r="I6">
-        <v>-3.23</v>
+        <v>-1.63</v>
       </c>
       <c r="J6">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="K6">
-        <v>-10.86</v>
+        <v>-11.65</v>
       </c>
       <c r="L6">
-        <v>60.37</v>
+        <v>62.04</v>
       </c>
       <c r="M6">
-        <v>61.11</v>
+        <v>61.32</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1451,19 +1430,19 @@
         <v>83</v>
       </c>
       <c r="P6">
-        <v>205.37</v>
+        <v>204.68</v>
       </c>
       <c r="Q6">
-        <v>207.2</v>
+        <v>207.25</v>
       </c>
       <c r="R6">
-        <v>209.88</v>
+        <v>209.64</v>
       </c>
       <c r="S6">
-        <v>185.47</v>
+        <v>185.76</v>
       </c>
       <c r="T6">
-        <v>11.4</v>
+        <v>11.19</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1478,34 +1457,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>48.44</v>
+        <v>48.38</v>
       </c>
       <c r="Z6">
-        <v>-0.91</v>
+        <v>-0.87</v>
       </c>
       <c r="AA6">
-        <v>-0.9</v>
+        <v>-0.89</v>
       </c>
       <c r="AB6">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AC6">
-        <v>46.7</v>
+        <v>49.68</v>
       </c>
       <c r="AD6">
-        <v>41.33</v>
+        <v>44.4</v>
       </c>
       <c r="AE6">
-        <v>5.62</v>
+        <v>5.59</v>
       </c>
       <c r="AF6">
-        <v>-10.14</v>
+        <v>-44.17</v>
       </c>
       <c r="AG6">
-        <v>216.01</v>
+        <v>216.03</v>
       </c>
       <c r="AH6">
-        <v>198.39</v>
+        <v>198.48</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1514,7 +1493,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>18.76</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1525,10 +1504,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>388.3</v>
+        <v>390.75</v>
       </c>
       <c r="D7">
-        <v>1.32</v>
+        <v>0.63</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1537,46 +1516,46 @@
         <v>381.05</v>
       </c>
       <c r="G7">
-        <v>-34.04</v>
+        <v>-33.62</v>
       </c>
       <c r="H7">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="I7">
-        <v>-1.85</v>
+        <v>-0.28</v>
       </c>
       <c r="J7">
-        <v>-4.71</v>
+        <v>-4.93</v>
       </c>
       <c r="K7">
-        <v>-8.41</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="L7">
-        <v>-31.39</v>
+        <v>-31.55</v>
       </c>
       <c r="M7">
-        <v>-0.31</v>
+        <v>-0.35</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="P7">
-        <v>385.24</v>
+        <v>385.02</v>
       </c>
       <c r="Q7">
-        <v>400.52</v>
+        <v>399.33</v>
       </c>
       <c r="R7">
-        <v>417.75</v>
+        <v>416.83</v>
       </c>
       <c r="S7">
-        <v>461.49</v>
+        <v>460.74</v>
       </c>
       <c r="T7">
-        <v>-15.86</v>
+        <v>-15.19</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1591,34 +1570,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.31</v>
+        <v>38.36</v>
       </c>
       <c r="Z7">
-        <v>-9.4</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AA7">
-        <v>-8.279999999999999</v>
+        <v>-8.4</v>
       </c>
       <c r="AB7">
-        <v>-1.11</v>
+        <v>-0.47</v>
       </c>
       <c r="AC7">
-        <v>28.47</v>
+        <v>57.78</v>
       </c>
       <c r="AD7">
-        <v>11.5</v>
+        <v>30.76</v>
       </c>
       <c r="AE7">
-        <v>7.97</v>
+        <v>7.95</v>
       </c>
       <c r="AF7">
-        <v>48.58</v>
+        <v>-40.47</v>
       </c>
       <c r="AG7">
-        <v>422.82</v>
+        <v>421.02</v>
       </c>
       <c r="AH7">
-        <v>378.22</v>
+        <v>377.65</v>
       </c>
       <c r="AI7">
         <v>405.74</v>
@@ -1627,7 +1606,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>40.73</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1638,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>660.7</v>
+        <v>638.4</v>
       </c>
       <c r="D8">
-        <v>12.56</v>
+        <v>-3.38</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1650,46 +1629,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-18.26</v>
+        <v>-21.02</v>
       </c>
       <c r="H8">
-        <v>41.25</v>
+        <v>36.49</v>
       </c>
       <c r="I8">
-        <v>9.619999999999999</v>
+        <v>7.33</v>
       </c>
       <c r="J8">
-        <v>-0.53</v>
+        <v>-2.93</v>
       </c>
       <c r="K8">
-        <v>-9.16</v>
+        <v>-12.95</v>
       </c>
       <c r="L8">
-        <v>9.210000000000001</v>
+        <v>5.41</v>
       </c>
       <c r="M8">
-        <v>-13.85</v>
+        <v>-14.6</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P8">
-        <v>601.83</v>
+        <v>610.55</v>
       </c>
       <c r="Q8">
-        <v>618.25</v>
+        <v>617.86</v>
       </c>
       <c r="R8">
-        <v>651.1900000000001</v>
+        <v>649.48</v>
       </c>
       <c r="S8">
-        <v>613.79</v>
+        <v>613.98</v>
       </c>
       <c r="T8">
-        <v>7.64</v>
+        <v>3.98</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1704,43 +1683,43 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>62.01</v>
+        <v>53.78</v>
       </c>
       <c r="Z8">
-        <v>-12.95</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="AA8">
-        <v>-16.19</v>
+        <v>-14.93</v>
       </c>
       <c r="AB8">
-        <v>3.25</v>
+        <v>5.06</v>
       </c>
       <c r="AC8">
-        <v>56.11</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AD8">
-        <v>30.23</v>
+        <v>50.6</v>
       </c>
       <c r="AE8">
-        <v>20.45</v>
+        <v>21.24</v>
       </c>
       <c r="AF8">
-        <v>3976.36</v>
+        <v>57.46</v>
       </c>
       <c r="AG8">
-        <v>663.85</v>
+        <v>662.6</v>
       </c>
       <c r="AH8">
-        <v>572.64</v>
+        <v>573.13</v>
       </c>
       <c r="AI8">
-        <v>570.71</v>
+        <v>580.38</v>
       </c>
       <c r="AJ8" t="s">
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>43.84</v>
+        <v>44.77</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1751,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>186.98</v>
+        <v>183.56</v>
       </c>
       <c r="D9">
-        <v>1.6</v>
+        <v>-1.83</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1763,46 +1742,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.64</v>
+        <v>-33.88</v>
       </c>
       <c r="H9">
-        <v>8.52</v>
+        <v>6.54</v>
       </c>
       <c r="I9">
-        <v>0.6899999999999999</v>
+        <v>-0.79</v>
       </c>
       <c r="J9">
-        <v>-0.92</v>
+        <v>-2.69</v>
       </c>
       <c r="K9">
-        <v>1.45</v>
+        <v>-1.89</v>
       </c>
       <c r="L9">
-        <v>-27.6</v>
+        <v>-29.58</v>
       </c>
       <c r="M9">
-        <v>-7.53</v>
+        <v>-7.89</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="P9">
-        <v>184.22</v>
+        <v>183.93</v>
       </c>
       <c r="Q9">
-        <v>190.35</v>
+        <v>190.12</v>
       </c>
       <c r="R9">
-        <v>190.58</v>
+        <v>190.45</v>
       </c>
       <c r="S9">
-        <v>199.65</v>
+        <v>199.32</v>
       </c>
       <c r="T9">
-        <v>-6.35</v>
+        <v>-7.91</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1817,34 +1796,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>45.93</v>
+        <v>40.38</v>
       </c>
       <c r="Z9">
-        <v>-2.11</v>
+        <v>-2.21</v>
       </c>
       <c r="AA9">
-        <v>-1.39</v>
+        <v>-1.56</v>
       </c>
       <c r="AB9">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="AC9">
-        <v>30.48</v>
+        <v>42.44</v>
       </c>
       <c r="AD9">
-        <v>12.94</v>
+        <v>27.09</v>
       </c>
       <c r="AE9">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="AF9">
-        <v>-20.46</v>
+        <v>-52.7</v>
       </c>
       <c r="AG9">
-        <v>202.1</v>
+        <v>202.22</v>
       </c>
       <c r="AH9">
-        <v>178.6</v>
+        <v>178.02</v>
       </c>
       <c r="AI9">
         <v>195.69</v>
@@ -1853,7 +1832,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>36.89</v>
+        <v>34.76</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1864,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>71.72</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="D10">
-        <v>0.96</v>
+        <v>-0.21</v>
       </c>
       <c r="E10">
         <v>130.8</v>
@@ -1876,46 +1855,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-45.17</v>
+        <v>-45.28</v>
       </c>
       <c r="H10">
-        <v>20.99</v>
+        <v>20.73</v>
       </c>
       <c r="I10">
-        <v>-0.79</v>
+        <v>-0.62</v>
       </c>
       <c r="J10">
-        <v>-2.21</v>
+        <v>-5.21</v>
       </c>
       <c r="K10">
-        <v>-11.49</v>
+        <v>-13.6</v>
       </c>
       <c r="L10">
-        <v>-44.09</v>
+        <v>-43.39</v>
       </c>
       <c r="M10">
-        <v>-2.13</v>
+        <v>-4.01</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P10">
-        <v>70.98999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="Q10">
-        <v>72.7</v>
+        <v>72.5</v>
       </c>
       <c r="R10">
-        <v>75.68000000000001</v>
+        <v>75.45</v>
       </c>
       <c r="S10">
-        <v>80.33</v>
+        <v>80.27</v>
       </c>
       <c r="T10">
-        <v>-10.72</v>
+        <v>-10.84</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1930,34 +1909,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>43.16</v>
+        <v>42.62</v>
       </c>
       <c r="Z10">
-        <v>-1.31</v>
+        <v>-1.24</v>
       </c>
       <c r="AA10">
-        <v>-1.31</v>
+        <v>-1.3</v>
       </c>
       <c r="AB10">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="AC10">
-        <v>59.34</v>
+        <v>74.05</v>
       </c>
       <c r="AD10">
-        <v>51.12</v>
+        <v>60.07</v>
       </c>
       <c r="AE10">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="AF10">
-        <v>-6.34</v>
+        <v>-46.34</v>
       </c>
       <c r="AG10">
-        <v>76.12</v>
+        <v>75.69</v>
       </c>
       <c r="AH10">
-        <v>69.28</v>
+        <v>69.31</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1966,7 +1945,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>31.37</v>
+        <v>28.51</v>
       </c>
     </row>
   </sheetData>
@@ -2107,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2185,1320 +2164,1260 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>71</v>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-2.25</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-3.44</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.65</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>76</v>
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>3.21</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.14</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-3.07</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.47</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.25</v>
+        <v>5.37</v>
       </c>
       <c r="E11" s="7">
-        <v>3.22</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.64</v>
+        <v>1.26</v>
       </c>
       <c r="D12" s="6">
-        <v>0.99</v>
+        <v>1.25</v>
       </c>
       <c r="E12" s="7">
-        <v>3.63</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.58</v>
+        <v>-4.71</v>
       </c>
       <c r="D13" s="6">
-        <v>3.21</v>
+        <v>-4.93</v>
       </c>
       <c r="E13" s="7">
-        <v>5.79</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>3.32</v>
+        <v>-0.53</v>
       </c>
       <c r="D14" s="6">
-        <v>8.449999999999999</v>
+        <v>-2.93</v>
       </c>
       <c r="E14" s="7">
-        <v>5.13</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>0.17</v>
+        <v>-0.92</v>
       </c>
       <c r="D15" s="6">
-        <v>1.26</v>
+        <v>-2.69</v>
       </c>
       <c r="E15" s="7">
-        <v>1.09</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.07</v>
+        <v>-2.21</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.71</v>
+        <v>-5.21</v>
       </c>
       <c r="E16" s="7">
-        <v>2.36</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-9.32</v>
+        <v>0.43</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.53</v>
-      </c>
-      <c r="E17" s="7">
-        <v>8.789999999999999</v>
+        <v>0.79</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.16</v>
+        <v>-1.86</v>
       </c>
       <c r="D18" s="6">
+        <v>-2.78</v>
+      </c>
+      <c r="E18" s="7">
         <v>-0.92</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.24</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-6.16</v>
+        <v>2.72</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.21</v>
+        <v>1.74</v>
       </c>
       <c r="E19" s="7">
-        <v>3.95</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-2</v>
+        <v>3.17</v>
       </c>
       <c r="D20" s="6">
-        <v>0.43</v>
+        <v>1.28</v>
       </c>
       <c r="E20" s="7">
-        <v>2.43</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-5.85</v>
+        <v>-3.23</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="E21" s="7">
-        <v>3.99</v>
+        <v>-1.63</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.6</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.1</v>
+        <v>-1.85</v>
       </c>
       <c r="D22" s="6">
-        <v>2.72</v>
-      </c>
-      <c r="E22" s="7">
-        <v>5.82</v>
+        <v>-0.28</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.57</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-2.07</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="D23" s="6">
-        <v>3.17</v>
+        <v>7.33</v>
       </c>
       <c r="E23" s="7">
-        <v>5.24</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.23</v>
+        <v>-0.79</v>
       </c>
       <c r="E24" s="7">
-        <v>0.95</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-3.46</v>
+        <v>-0.79</v>
       </c>
       <c r="D25" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.61</v>
+        <v>-0.62</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.17</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-4.13</v>
+        <v>-31.91</v>
       </c>
       <c r="D26" s="6">
-        <v>9.619999999999999</v>
+        <v>-32.28</v>
       </c>
       <c r="E26" s="7">
-        <v>13.75</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-1.86</v>
+        <v>26.77</v>
       </c>
       <c r="D27" s="6">
-        <v>0.6899999999999999</v>
+        <v>24.04</v>
       </c>
       <c r="E27" s="7">
-        <v>2.55</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-3.65</v>
+        <v>35.25</v>
       </c>
       <c r="D28" s="6">
-        <v>-0.79</v>
+        <v>31.96</v>
       </c>
       <c r="E28" s="7">
-        <v>2.86</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-33.01</v>
+        <v>31.29</v>
       </c>
       <c r="D29" s="6">
-        <v>-31.91</v>
+        <v>27.44</v>
       </c>
       <c r="E29" s="7">
-        <v>1.1</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>22.26</v>
+        <v>60.37</v>
       </c>
       <c r="D30" s="6">
-        <v>26.77</v>
-      </c>
-      <c r="E30" s="7">
-        <v>4.51</v>
+        <v>62.04</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.67</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>29.8</v>
+        <v>-31.39</v>
       </c>
       <c r="D31" s="6">
-        <v>35.25</v>
+        <v>-31.55</v>
       </c>
       <c r="E31" s="7">
-        <v>5.45</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>25.31</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D32" s="6">
-        <v>31.29</v>
+        <v>5.41</v>
       </c>
       <c r="E32" s="7">
-        <v>5.98</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>58.75</v>
+        <v>-27.6</v>
       </c>
       <c r="D33" s="6">
-        <v>60.37</v>
+        <v>-29.58</v>
       </c>
       <c r="E33" s="7">
-        <v>1.62</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-31.29</v>
+        <v>-44.09</v>
       </c>
       <c r="D34" s="6">
-        <v>-31.39</v>
+        <v>-43.39</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-3.04</v>
+        <v>-6.22</v>
       </c>
       <c r="D35" s="6">
-        <v>9.210000000000001</v>
+        <v>-6.93</v>
       </c>
       <c r="E35" s="7">
-        <v>12.25</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-29.32</v>
+        <v>-0.61</v>
       </c>
       <c r="D36" s="6">
-        <v>-27.6</v>
+        <v>-2.77</v>
       </c>
       <c r="E36" s="7">
-        <v>1.72</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-46.07</v>
+        <v>-11.18</v>
       </c>
       <c r="D37" s="6">
-        <v>-44.09</v>
+        <v>-15.89</v>
       </c>
       <c r="E37" s="7">
-        <v>1.98</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-9.300000000000001</v>
+        <v>-0.62</v>
       </c>
       <c r="D38" s="6">
-        <v>-6.22</v>
+        <v>-2.19</v>
       </c>
       <c r="E38" s="7">
-        <v>3.08</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-2.99</v>
+        <v>-10.86</v>
       </c>
       <c r="D39" s="6">
-        <v>-0.61</v>
+        <v>-11.65</v>
       </c>
       <c r="E39" s="7">
-        <v>2.38</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-15.44</v>
+        <v>-8.41</v>
       </c>
       <c r="D40" s="6">
-        <v>-11.18</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="E40" s="7">
-        <v>4.26</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-5.63</v>
+        <v>-9.16</v>
       </c>
       <c r="D41" s="6">
-        <v>-0.62</v>
+        <v>-12.95</v>
       </c>
       <c r="E41" s="7">
-        <v>5.01</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-10.69</v>
+        <v>1.45</v>
       </c>
       <c r="D42" s="6">
-        <v>-10.86</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.17</v>
+        <v>-1.89</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-3.34</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-10.87</v>
+        <v>-11.49</v>
       </c>
       <c r="D43" s="6">
-        <v>-8.41</v>
+        <v>-13.6</v>
       </c>
       <c r="E43" s="7">
-        <v>2.46</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-18.96</v>
+        <v>-33.79</v>
       </c>
       <c r="D44" s="6">
-        <v>-9.16</v>
+        <v>-33.97</v>
       </c>
       <c r="E44" s="7">
-        <v>9.800000000000001</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-4.36</v>
+        <v>-5.98</v>
       </c>
       <c r="D45" s="6">
-        <v>1.45</v>
+        <v>-7.38</v>
       </c>
       <c r="E45" s="7">
-        <v>5.81</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-14.56</v>
+        <v>-16.83</v>
       </c>
       <c r="D46" s="6">
-        <v>-11.49</v>
+        <v>-18.75</v>
       </c>
       <c r="E46" s="7">
-        <v>3.07</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-35.22</v>
+        <v>-3.14</v>
       </c>
       <c r="D47" s="6">
-        <v>-33.79</v>
+        <v>-5.1</v>
       </c>
       <c r="E47" s="7">
-        <v>1.43</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-8.99</v>
+        <v>-17</v>
       </c>
       <c r="D48" s="6">
-        <v>-5.98</v>
+        <v>-17.02</v>
       </c>
       <c r="E48" s="7">
-        <v>3.01</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-20.59</v>
+        <v>-34.04</v>
       </c>
       <c r="D49" s="6">
-        <v>-16.83</v>
-      </c>
-      <c r="E49" s="7">
-        <v>3.76</v>
+        <v>-33.62</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-7.69</v>
+        <v>-18.26</v>
       </c>
       <c r="D50" s="6">
-        <v>-3.14</v>
+        <v>-21.02</v>
       </c>
       <c r="E50" s="7">
-        <v>4.55</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-17.27</v>
+        <v>-32.64</v>
       </c>
       <c r="D51" s="6">
-        <v>-17</v>
+        <v>-33.88</v>
       </c>
       <c r="E51" s="7">
-        <v>0.27</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>-34.9</v>
+        <v>-45.17</v>
       </c>
       <c r="D52" s="6">
-        <v>-34.04</v>
+        <v>-45.28</v>
       </c>
       <c r="E52" s="7">
-        <v>0.86</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>-27.38</v>
+        <v>1259.7</v>
       </c>
       <c r="D53" s="6">
-        <v>-18.26</v>
+        <v>1256.3</v>
       </c>
       <c r="E53" s="7">
-        <v>9.119999999999999</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>-33.7</v>
+        <v>3020</v>
       </c>
       <c r="D54" s="6">
-        <v>-32.64</v>
+        <v>2975</v>
       </c>
       <c r="E54" s="7">
-        <v>1.06</v>
+        <v>-45</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>-45.69</v>
+        <v>1334.5</v>
       </c>
       <c r="D55" s="6">
-        <v>-45.17</v>
+        <v>1303.6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.52</v>
+        <v>-30.9</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1232.5</v>
+        <v>1824</v>
       </c>
       <c r="D56" s="6">
-        <v>1259.7</v>
+        <v>1787.1</v>
       </c>
       <c r="E56" s="7">
-        <v>27.2</v>
+        <v>-36.9</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>2923.2</v>
+        <v>206.6</v>
       </c>
       <c r="D57" s="6">
-        <v>3020</v>
+        <v>206.55</v>
       </c>
       <c r="E57" s="7">
-        <v>96.8</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>1274.2</v>
+        <v>388.3</v>
       </c>
       <c r="D58" s="6">
-        <v>1334.5</v>
-      </c>
-      <c r="E58" s="7">
-        <v>60.3</v>
+        <v>390.75</v>
+      </c>
+      <c r="E58" s="8">
+        <v>2.45</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>1738.3</v>
+        <v>660.7</v>
       </c>
       <c r="D59" s="6">
-        <v>1824</v>
+        <v>638.4</v>
       </c>
       <c r="E59" s="7">
-        <v>85.7</v>
+        <v>-22.3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>205.92</v>
+        <v>186.98</v>
       </c>
       <c r="D60" s="6">
-        <v>206.6</v>
+        <v>183.56</v>
       </c>
       <c r="E60" s="7">
-        <v>0.68</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>383.25</v>
+        <v>71.72</v>
       </c>
       <c r="D61" s="6">
-        <v>388.3</v>
+        <v>71.56999999999999</v>
       </c>
       <c r="E61" s="7">
-        <v>5.05</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>587</v>
+        <v>42.88</v>
       </c>
       <c r="D62" s="6">
-        <v>660.7</v>
+        <v>41.93</v>
       </c>
       <c r="E62" s="7">
-        <v>73.7</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>184.04</v>
+        <v>51.93</v>
       </c>
       <c r="D63" s="6">
-        <v>186.98</v>
+        <v>48.27</v>
       </c>
       <c r="E63" s="7">
-        <v>2.94</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>71.04000000000001</v>
+        <v>53.75</v>
       </c>
       <c r="D64" s="6">
-        <v>71.72</v>
+        <v>48.79</v>
       </c>
       <c r="E64" s="7">
-        <v>0.68</v>
+        <v>-4.96</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>31.28</v>
+        <v>64.02</v>
       </c>
       <c r="D65" s="6">
-        <v>42.88</v>
+        <v>58.02</v>
       </c>
       <c r="E65" s="7">
-        <v>11.6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>43.35</v>
+        <v>48.44</v>
       </c>
       <c r="D66" s="6">
-        <v>51.93</v>
+        <v>48.38</v>
       </c>
       <c r="E66" s="7">
-        <v>8.58</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>43.32</v>
+        <v>35.31</v>
       </c>
       <c r="D67" s="6">
-        <v>53.75</v>
-      </c>
-      <c r="E67" s="7">
-        <v>10.43</v>
+        <v>38.36</v>
+      </c>
+      <c r="E67" s="8">
+        <v>3.05</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>53.69</v>
+        <v>62.01</v>
       </c>
       <c r="D68" s="6">
-        <v>64.02</v>
+        <v>53.78</v>
       </c>
       <c r="E68" s="7">
-        <v>10.33</v>
+        <v>-8.23</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>47.64</v>
+        <v>45.93</v>
       </c>
       <c r="D69" s="6">
-        <v>48.44</v>
+        <v>40.38</v>
       </c>
       <c r="E69" s="7">
-        <v>0.8</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>28.54</v>
+        <v>43.16</v>
       </c>
       <c r="D70" s="6">
-        <v>35.31</v>
+        <v>42.62</v>
       </c>
       <c r="E70" s="7">
-        <v>6.77</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>28.33</v>
+        <v>231.62</v>
       </c>
       <c r="D71" s="6">
-        <v>62.01</v>
+        <v>-48.1</v>
       </c>
       <c r="E71" s="7">
-        <v>33.68</v>
+        <v>-279.72</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>39.27</v>
+        <v>-21.74</v>
       </c>
       <c r="D72" s="6">
-        <v>45.93</v>
+        <v>-62.96</v>
       </c>
       <c r="E72" s="7">
-        <v>6.66</v>
+        <v>-41.22</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>39.95</v>
+        <v>79.88</v>
       </c>
       <c r="D73" s="6">
-        <v>43.16</v>
+        <v>-57.15</v>
       </c>
       <c r="E73" s="7">
-        <v>3.21</v>
+        <v>-137.03</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-43.14</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D74" s="6">
-        <v>231.62</v>
+        <v>-6.9</v>
       </c>
       <c r="E74" s="7">
-        <v>274.76</v>
+        <v>-83.3</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-71.84</v>
+        <v>-10.14</v>
       </c>
       <c r="D75" s="6">
-        <v>-21.74</v>
+        <v>-44.17</v>
       </c>
       <c r="E75" s="7">
-        <v>50.1</v>
+        <v>-34.03</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-50.68</v>
+        <v>48.58</v>
       </c>
       <c r="D76" s="6">
-        <v>79.88</v>
+        <v>-40.47</v>
       </c>
       <c r="E76" s="7">
-        <v>130.56</v>
+        <v>-89.05</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-66.67</v>
+        <v>3976.36</v>
       </c>
       <c r="D77" s="6">
-        <v>76.40000000000001</v>
+        <v>57.46</v>
       </c>
       <c r="E77" s="7">
-        <v>143.07</v>
+        <v>-3918.9</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-57.58</v>
+        <v>-20.46</v>
       </c>
       <c r="D78" s="6">
-        <v>-10.14</v>
+        <v>-52.7</v>
       </c>
       <c r="E78" s="7">
-        <v>47.44</v>
+        <v>-32.24</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-32.02</v>
+        <v>-6.34</v>
       </c>
       <c r="D79" s="6">
-        <v>48.58</v>
+        <v>-46.34</v>
       </c>
       <c r="E79" s="7">
-        <v>80.59999999999999</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-61.17</v>
-      </c>
-      <c r="D80" s="6">
-        <v>3976.36</v>
-      </c>
-      <c r="E80" s="7">
-        <v>4037.53</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-29.98</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-20.46</v>
-      </c>
-      <c r="E81" s="7">
-        <v>9.52</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-36.16</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-6.34</v>
-      </c>
-      <c r="E82" s="7">
-        <v>29.82</v>
+        <v>-40</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3522,28 +3441,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3557,16 +3476,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>49.7</v>
+        <v>46.7</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>0.4</v>
+        <v>-1.5</v>
       </c>
       <c r="G2" s="11">
-        <v>-6.3</v>
+        <v>-8.5</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3703,31 +3622,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.6111</v>
+        <v>0.6132</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2016</v>
+        <v>0.1962</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1638</v>
+        <v>0.1565</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0337</v>
+        <v>0.0307</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0031</v>
+        <v>-0.0035</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0213</v>
+        <v>-0.0401</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.07530000000000001</v>
+        <v>-0.0789</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1075</v>
+        <v>-0.1084</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1385</v>
+        <v>-0.146</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,25 +196,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.9 → 48.3</t>
+    <t>48.3 → 50.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>53.8 → 49.9</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>51.9</t>
-  </si>
-  <si>
-    <t>48.3</t>
-  </si>
-  <si>
-    <t>53.8 → 48.8</t>
-  </si>
-  <si>
     <t>53.8</t>
   </si>
   <si>
-    <t>48.8</t>
+    <t>49.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +303,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +343,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,10 +427,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -939,10 +943,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1256.3</v>
+        <v>1238.2</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>-1.44</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -951,46 +955,46 @@
         <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-33.97</v>
+        <v>-34.92</v>
       </c>
       <c r="H2">
-        <v>2.54</v>
+        <v>1.06</v>
       </c>
       <c r="I2">
-        <v>0.79</v>
+        <v>1.06</v>
       </c>
       <c r="J2">
-        <v>-3.44</v>
+        <v>-5.29</v>
       </c>
       <c r="K2">
-        <v>-6.93</v>
+        <v>-6.86</v>
       </c>
       <c r="L2">
-        <v>-32.28</v>
+        <v>-32.9</v>
       </c>
       <c r="M2">
-        <v>-10.84</v>
+        <v>-11.35</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P2">
-        <v>1240.06</v>
+        <v>1242.66</v>
       </c>
       <c r="Q2">
-        <v>1270.85</v>
+        <v>1267.71</v>
       </c>
       <c r="R2">
-        <v>1319.83</v>
+        <v>1317.01</v>
       </c>
       <c r="S2">
-        <v>1461.95</v>
+        <v>1458.99</v>
       </c>
       <c r="T2">
-        <v>-14.07</v>
+        <v>-15.13</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,34 +1009,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.93</v>
+        <v>37.19</v>
       </c>
       <c r="Z2">
-        <v>-22.08</v>
+        <v>-21.85</v>
       </c>
       <c r="AA2">
-        <v>-22.93</v>
+        <v>-22.71</v>
       </c>
       <c r="AB2">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AC2">
-        <v>72.73</v>
+        <v>85.44</v>
       </c>
       <c r="AD2">
-        <v>41.75</v>
+        <v>67.03</v>
       </c>
       <c r="AE2">
-        <v>24.25</v>
+        <v>24.31</v>
       </c>
       <c r="AF2">
-        <v>-48.1</v>
+        <v>-37.23</v>
       </c>
       <c r="AG2">
-        <v>1328.63</v>
+        <v>1325.43</v>
       </c>
       <c r="AH2">
-        <v>1213.07</v>
+        <v>1210</v>
       </c>
       <c r="AI2">
         <v>1296.94</v>
@@ -1041,7 +1045,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>27.48</v>
+        <v>25.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2975</v>
+        <v>2997</v>
       </c>
       <c r="D3">
-        <v>-1.49</v>
+        <v>0.74</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1064,46 +1068,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-7.38</v>
+        <v>-6.7</v>
       </c>
       <c r="H3">
-        <v>69.23</v>
+        <v>70.48</v>
       </c>
       <c r="I3">
-        <v>-2.78</v>
+        <v>2.34</v>
       </c>
       <c r="J3">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>-2.77</v>
+        <v>1.15</v>
       </c>
       <c r="L3">
-        <v>24.04</v>
+        <v>24.83</v>
       </c>
       <c r="M3">
-        <v>15.65</v>
+        <v>15.88</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>2953.36</v>
+        <v>2967.04</v>
       </c>
       <c r="Q3">
-        <v>2996.19</v>
+        <v>2996.11</v>
       </c>
       <c r="R3">
-        <v>3032.44</v>
+        <v>3028.83</v>
       </c>
       <c r="S3">
-        <v>2544.49</v>
+        <v>2548.53</v>
       </c>
       <c r="T3">
-        <v>16.92</v>
+        <v>17.6</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1118,34 +1122,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>48.27</v>
+        <v>50.12</v>
       </c>
       <c r="Z3">
-        <v>-12.76</v>
+        <v>-10.62</v>
       </c>
       <c r="AA3">
-        <v>-13.37</v>
+        <v>-12.82</v>
       </c>
       <c r="AB3">
-        <v>0.61</v>
+        <v>2.2</v>
       </c>
       <c r="AC3">
-        <v>50.34</v>
+        <v>60.64</v>
       </c>
       <c r="AD3">
-        <v>38.87</v>
+        <v>50.49</v>
       </c>
       <c r="AE3">
-        <v>81.31999999999999</v>
+        <v>79.16</v>
       </c>
       <c r="AF3">
-        <v>-62.96</v>
+        <v>-62.52</v>
       </c>
       <c r="AG3">
-        <v>3195.49</v>
+        <v>3195.41</v>
       </c>
       <c r="AH3">
-        <v>2796.88</v>
+        <v>2796.8</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1154,7 +1158,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>21.3</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1303.6</v>
+        <v>1304</v>
       </c>
       <c r="D4">
-        <v>-2.32</v>
+        <v>0.03</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1177,46 +1181,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.75</v>
+        <v>-18.73</v>
       </c>
       <c r="H4">
-        <v>68.69</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="I4">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="J4">
-        <v>0.14</v>
+        <v>-1.21</v>
       </c>
       <c r="K4">
-        <v>-15.89</v>
+        <v>-13.71</v>
       </c>
       <c r="L4">
-        <v>31.96</v>
+        <v>33.14</v>
       </c>
       <c r="M4">
-        <v>3.07</v>
+        <v>2.7</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1287.5</v>
+        <v>1297.3</v>
       </c>
       <c r="Q4">
-        <v>1292.71</v>
+        <v>1292.51</v>
       </c>
       <c r="R4">
-        <v>1360.35</v>
+        <v>1355.5</v>
       </c>
       <c r="S4">
-        <v>1189.53</v>
+        <v>1190.99</v>
       </c>
       <c r="T4">
-        <v>9.59</v>
+        <v>9.49</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1231,31 +1235,31 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>48.79</v>
+        <v>48.86</v>
       </c>
       <c r="Z4">
-        <v>-15.38</v>
+        <v>-13.46</v>
       </c>
       <c r="AA4">
-        <v>-22.58</v>
+        <v>-20.75</v>
       </c>
       <c r="AB4">
-        <v>7.2</v>
+        <v>7.29</v>
       </c>
       <c r="AC4">
-        <v>80.31999999999999</v>
+        <v>77.48</v>
       </c>
       <c r="AD4">
-        <v>75.92</v>
+        <v>79.72</v>
       </c>
       <c r="AE4">
-        <v>39.03</v>
+        <v>37.46</v>
       </c>
       <c r="AF4">
-        <v>-57.15</v>
+        <v>-70.52</v>
       </c>
       <c r="AG4">
-        <v>1349.22</v>
+        <v>1348.82</v>
       </c>
       <c r="AH4">
         <v>1236.2</v>
@@ -1267,7 +1271,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>20.74</v>
+        <v>21.61</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1787.1</v>
+        <v>1795</v>
       </c>
       <c r="D5">
-        <v>-2.02</v>
+        <v>0.44</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1290,46 +1294,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-5.1</v>
+        <v>-4.68</v>
       </c>
       <c r="H5">
-        <v>37.67</v>
+        <v>38.28</v>
       </c>
       <c r="I5">
-        <v>1.28</v>
+        <v>4.74</v>
       </c>
       <c r="J5">
-        <v>5.37</v>
+        <v>5.59</v>
       </c>
       <c r="K5">
-        <v>-2.19</v>
+        <v>0.62</v>
       </c>
       <c r="L5">
-        <v>27.44</v>
+        <v>28.2</v>
       </c>
       <c r="M5">
-        <v>19.62</v>
+        <v>19.87</v>
       </c>
       <c r="N5">
         <v>88</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>1757.4</v>
+        <v>1773.64</v>
       </c>
       <c r="Q5">
-        <v>1715.69</v>
+        <v>1721.84</v>
       </c>
       <c r="R5">
-        <v>1728.99</v>
+        <v>1728.69</v>
       </c>
       <c r="S5">
-        <v>1614.72</v>
+        <v>1616.24</v>
       </c>
       <c r="T5">
-        <v>10.68</v>
+        <v>11.06</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1344,43 +1348,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>58.02</v>
+        <v>58.91</v>
       </c>
       <c r="Z5">
-        <v>17.36</v>
+        <v>19.97</v>
       </c>
       <c r="AA5">
-        <v>5.68</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AB5">
-        <v>11.68</v>
+        <v>11.43</v>
       </c>
       <c r="AC5">
-        <v>83.34999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="AD5">
-        <v>78.63</v>
+        <v>82.37</v>
       </c>
       <c r="AE5">
-        <v>42.85</v>
+        <v>41.69</v>
       </c>
       <c r="AF5">
-        <v>-6.9</v>
+        <v>-65.42</v>
       </c>
       <c r="AG5">
-        <v>1819.26</v>
+        <v>1829.04</v>
       </c>
       <c r="AH5">
-        <v>1612.12</v>
+        <v>1614.63</v>
       </c>
       <c r="AI5">
-        <v>1658.8</v>
+        <v>1674.34</v>
       </c>
       <c r="AJ5" t="s">
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>25</v>
+        <v>28.49</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,37 +1395,37 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>206.55</v>
+        <v>206.96</v>
       </c>
       <c r="D6">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>126.1</v>
+        <v>126.27</v>
       </c>
       <c r="G6">
-        <v>-17.02</v>
+        <v>-16.85</v>
       </c>
       <c r="H6">
-        <v>63.8</v>
+        <v>63.9</v>
       </c>
       <c r="I6">
-        <v>-1.63</v>
+        <v>2.46</v>
       </c>
       <c r="J6">
-        <v>1.25</v>
+        <v>0.71</v>
       </c>
       <c r="K6">
-        <v>-11.65</v>
+        <v>-10.56</v>
       </c>
       <c r="L6">
-        <v>62.04</v>
+        <v>64.12</v>
       </c>
       <c r="M6">
-        <v>61.32</v>
+        <v>60.93</v>
       </c>
       <c r="N6">
         <v>99</v>
@@ -1430,19 +1434,19 @@
         <v>83</v>
       </c>
       <c r="P6">
-        <v>204.68</v>
+        <v>205.67</v>
       </c>
       <c r="Q6">
-        <v>207.25</v>
+        <v>207.42</v>
       </c>
       <c r="R6">
-        <v>209.64</v>
+        <v>209.48</v>
       </c>
       <c r="S6">
-        <v>185.76</v>
+        <v>186.07</v>
       </c>
       <c r="T6">
-        <v>11.19</v>
+        <v>11.22</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1457,34 +1461,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>48.38</v>
+        <v>48.93</v>
       </c>
       <c r="Z6">
+        <v>-0.79</v>
+      </c>
+      <c r="AA6">
         <v>-0.87</v>
       </c>
-      <c r="AA6">
-        <v>-0.89</v>
-      </c>
       <c r="AB6">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="AC6">
-        <v>49.68</v>
+        <v>46</v>
       </c>
       <c r="AD6">
-        <v>44.4</v>
+        <v>47.46</v>
       </c>
       <c r="AE6">
-        <v>5.59</v>
+        <v>5.43</v>
       </c>
       <c r="AF6">
-        <v>-44.17</v>
+        <v>-42.61</v>
       </c>
       <c r="AG6">
-        <v>216.03</v>
+        <v>216.04</v>
       </c>
       <c r="AH6">
-        <v>198.48</v>
+        <v>198.8</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1493,7 +1497,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>16.6</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,10 +1508,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>390.75</v>
+        <v>386.9</v>
       </c>
       <c r="D7">
-        <v>0.63</v>
+        <v>-0.99</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1516,46 +1520,46 @@
         <v>381.05</v>
       </c>
       <c r="G7">
-        <v>-33.62</v>
+        <v>-34.28</v>
       </c>
       <c r="H7">
-        <v>2.55</v>
+        <v>1.54</v>
       </c>
       <c r="I7">
-        <v>-0.28</v>
+        <v>1.35</v>
       </c>
       <c r="J7">
-        <v>-4.93</v>
+        <v>-6.66</v>
       </c>
       <c r="K7">
-        <v>-8.699999999999999</v>
+        <v>-6.74</v>
       </c>
       <c r="L7">
-        <v>-31.55</v>
+        <v>-33.2</v>
       </c>
       <c r="M7">
-        <v>-0.35</v>
+        <v>-0.85</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P7">
-        <v>385.02</v>
+        <v>386.05</v>
       </c>
       <c r="Q7">
-        <v>399.33</v>
+        <v>398.24</v>
       </c>
       <c r="R7">
-        <v>416.83</v>
+        <v>415.93</v>
       </c>
       <c r="S7">
-        <v>460.74</v>
+        <v>460.01</v>
       </c>
       <c r="T7">
-        <v>-15.19</v>
+        <v>-15.89</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1570,34 +1574,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>38.36</v>
+        <v>35.52</v>
       </c>
       <c r="Z7">
-        <v>-8.869999999999999</v>
+        <v>-8.67</v>
       </c>
       <c r="AA7">
-        <v>-8.4</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="AB7">
-        <v>-0.47</v>
+        <v>-0.22</v>
       </c>
       <c r="AC7">
-        <v>57.78</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AD7">
-        <v>30.76</v>
+        <v>53.64</v>
       </c>
       <c r="AE7">
-        <v>7.95</v>
+        <v>8.01</v>
       </c>
       <c r="AF7">
-        <v>-40.47</v>
+        <v>-29.66</v>
       </c>
       <c r="AG7">
-        <v>421.02</v>
+        <v>420.13</v>
       </c>
       <c r="AH7">
-        <v>377.65</v>
+        <v>376.35</v>
       </c>
       <c r="AI7">
         <v>405.74</v>
@@ -1606,7 +1610,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>36.68</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1621,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>638.4</v>
+        <v>626.25</v>
       </c>
       <c r="D8">
-        <v>-3.38</v>
+        <v>-1.9</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1629,46 +1633,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-21.02</v>
+        <v>-22.52</v>
       </c>
       <c r="H8">
-        <v>36.49</v>
+        <v>33.89</v>
       </c>
       <c r="I8">
-        <v>7.33</v>
+        <v>7.95</v>
       </c>
       <c r="J8">
-        <v>-2.93</v>
+        <v>-3.07</v>
       </c>
       <c r="K8">
-        <v>-12.95</v>
+        <v>-12.54</v>
       </c>
       <c r="L8">
-        <v>5.41</v>
+        <v>3.2</v>
       </c>
       <c r="M8">
-        <v>-14.6</v>
+        <v>-14.58</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="P8">
-        <v>610.55</v>
+        <v>619.77</v>
       </c>
       <c r="Q8">
-        <v>617.86</v>
+        <v>617.2</v>
       </c>
       <c r="R8">
-        <v>649.48</v>
+        <v>647.59</v>
       </c>
       <c r="S8">
-        <v>613.98</v>
+        <v>614.14</v>
       </c>
       <c r="T8">
-        <v>3.98</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,34 +1687,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>53.78</v>
+        <v>49.89</v>
       </c>
       <c r="Z8">
-        <v>-9.869999999999999</v>
+        <v>-8.31</v>
       </c>
       <c r="AA8">
-        <v>-14.93</v>
+        <v>-13.61</v>
       </c>
       <c r="AB8">
-        <v>5.06</v>
+        <v>5.29</v>
       </c>
       <c r="AC8">
-        <v>72.90000000000001</v>
+        <v>82.69</v>
       </c>
       <c r="AD8">
-        <v>50.6</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="AE8">
-        <v>21.24</v>
+        <v>21.21</v>
       </c>
       <c r="AF8">
-        <v>57.46</v>
+        <v>-52.98</v>
       </c>
       <c r="AG8">
-        <v>662.6</v>
+        <v>660.95</v>
       </c>
       <c r="AH8">
-        <v>573.13</v>
+        <v>573.4400000000001</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1719,7 +1723,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>44.77</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,10 +1734,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>183.56</v>
+        <v>183.1</v>
       </c>
       <c r="D9">
-        <v>-1.83</v>
+        <v>-0.25</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1742,46 +1746,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.88</v>
+        <v>-34.04</v>
       </c>
       <c r="H9">
-        <v>6.54</v>
+        <v>6.27</v>
       </c>
       <c r="I9">
-        <v>-0.79</v>
+        <v>-0.02</v>
       </c>
       <c r="J9">
-        <v>-2.69</v>
+        <v>-2.67</v>
       </c>
       <c r="K9">
-        <v>-1.89</v>
+        <v>-0.39</v>
       </c>
       <c r="L9">
-        <v>-29.58</v>
+        <v>-29.39</v>
       </c>
       <c r="M9">
-        <v>-7.89</v>
+        <v>-7.94</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P9">
-        <v>183.93</v>
+        <v>183.92</v>
       </c>
       <c r="Q9">
-        <v>190.12</v>
+        <v>189.58</v>
       </c>
       <c r="R9">
-        <v>190.45</v>
+        <v>190.32</v>
       </c>
       <c r="S9">
-        <v>199.32</v>
+        <v>199</v>
       </c>
       <c r="T9">
-        <v>-7.91</v>
+        <v>-7.99</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1796,34 +1800,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>40.38</v>
+        <v>39.69</v>
       </c>
       <c r="Z9">
-        <v>-2.21</v>
+        <v>-2.31</v>
       </c>
       <c r="AA9">
-        <v>-1.56</v>
+        <v>-1.71</v>
       </c>
       <c r="AB9">
-        <v>-0.66</v>
+        <v>-0.6</v>
       </c>
       <c r="AC9">
-        <v>42.44</v>
+        <v>48.76</v>
       </c>
       <c r="AD9">
-        <v>27.09</v>
+        <v>40.56</v>
       </c>
       <c r="AE9">
-        <v>4.56</v>
+        <v>4.42</v>
       </c>
       <c r="AF9">
-        <v>-52.7</v>
+        <v>-64.76000000000001</v>
       </c>
       <c r="AG9">
-        <v>202.22</v>
+        <v>201.93</v>
       </c>
       <c r="AH9">
-        <v>178.02</v>
+        <v>177.23</v>
       </c>
       <c r="AI9">
         <v>195.69</v>
@@ -1832,7 +1836,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>34.76</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,10 +1847,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>71.56999999999999</v>
+        <v>72.31</v>
       </c>
       <c r="D10">
-        <v>-0.21</v>
+        <v>1.03</v>
       </c>
       <c r="E10">
         <v>130.8</v>
@@ -1855,46 +1859,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-45.28</v>
+        <v>-44.72</v>
       </c>
       <c r="H10">
-        <v>20.73</v>
+        <v>21.98</v>
       </c>
       <c r="I10">
-        <v>-0.62</v>
+        <v>2.67</v>
       </c>
       <c r="J10">
-        <v>-5.21</v>
+        <v>-4.21</v>
       </c>
       <c r="K10">
-        <v>-13.6</v>
+        <v>-11.05</v>
       </c>
       <c r="L10">
-        <v>-43.39</v>
+        <v>-42.54</v>
       </c>
       <c r="M10">
-        <v>-4.01</v>
+        <v>-5.62</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P10">
-        <v>70.90000000000001</v>
+        <v>71.28</v>
       </c>
       <c r="Q10">
-        <v>72.5</v>
+        <v>72.36</v>
       </c>
       <c r="R10">
-        <v>75.45</v>
+        <v>75.25</v>
       </c>
       <c r="S10">
-        <v>80.27</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="T10">
-        <v>-10.84</v>
+        <v>-9.85</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1909,34 +1913,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>42.62</v>
+        <v>46.21</v>
       </c>
       <c r="Z10">
-        <v>-1.24</v>
+        <v>-1.12</v>
       </c>
       <c r="AA10">
-        <v>-1.3</v>
+        <v>-1.26</v>
       </c>
       <c r="AB10">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="AC10">
-        <v>74.05</v>
+        <v>83.88</v>
       </c>
       <c r="AD10">
-        <v>60.07</v>
+        <v>72.42</v>
       </c>
       <c r="AE10">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AF10">
-        <v>-46.34</v>
+        <v>-45.28</v>
       </c>
       <c r="AG10">
-        <v>75.69</v>
+        <v>75.3</v>
       </c>
       <c r="AH10">
-        <v>69.31</v>
+        <v>69.42</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1945,7 +1949,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>28.51</v>
+        <v>26.08</v>
       </c>
     </row>
   </sheetData>
@@ -2145,28 +2149,28 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2178,1240 +2182,1240 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-2.25</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="7">
         <v>-3.44</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.19</v>
+      <c r="D8" s="7">
+        <v>-5.29</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>0.99</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="7">
         <v>-0.66</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D9" s="7">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.14</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-1.21</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>5.37</v>
+      </c>
+      <c r="D11" s="7">
+        <v>5.59</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1.25</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.71</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-4.93</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-6.66</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-2.93</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-3.07</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-2.69</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-2.67</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-5.21</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-4.21</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.79</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1.06</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-2.78</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2.34</v>
+      </c>
+      <c r="E18" s="9">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1.74</v>
+      </c>
+      <c r="D19" s="7">
+        <v>3.9</v>
+      </c>
+      <c r="E19" s="9">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1.28</v>
+      </c>
+      <c r="D20" s="7">
+        <v>4.74</v>
+      </c>
+      <c r="E20" s="9">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1.63</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.46</v>
+      </c>
+      <c r="E21" s="9">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-0.28</v>
+      </c>
+      <c r="D22" s="7">
+        <v>1.35</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>7.33</v>
+      </c>
+      <c r="D23" s="7">
+        <v>7.95</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.79</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-0.02</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-0.62</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2.67</v>
+      </c>
+      <c r="E25" s="9">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-32.28</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-32.9</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>24.04</v>
+      </c>
+      <c r="D27" s="7">
+        <v>24.83</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>31.96</v>
+      </c>
+      <c r="D28" s="7">
+        <v>33.14</v>
+      </c>
+      <c r="E28" s="9">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>27.44</v>
+      </c>
+      <c r="D29" s="7">
+        <v>28.2</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>62.04</v>
+      </c>
+      <c r="D30" s="7">
+        <v>64.12</v>
+      </c>
+      <c r="E30" s="9">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-31.55</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-33.2</v>
+      </c>
+      <c r="E31" s="8">
         <v>-1.65</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>5.41</v>
+      </c>
+      <c r="D32" s="7">
+        <v>3.2</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-29.58</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-29.39</v>
+      </c>
+      <c r="E33" s="9">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-43.39</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-42.54</v>
+      </c>
+      <c r="E34" s="9">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-6.93</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-6.86</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-2.77</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1.15</v>
+      </c>
+      <c r="E36" s="9">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>3.21</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0.14</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-15.89</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-13.71</v>
+      </c>
+      <c r="E37" s="9">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="D11" s="6">
-        <v>5.37</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-2.19</v>
+      </c>
+      <c r="D38" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="E38" s="9">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.26</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1.25</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-11.65</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-10.56</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-4.71</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-4.93</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-6.74</v>
+      </c>
+      <c r="E40" s="9">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-0.53</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-2.93</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-12.95</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-12.54</v>
+      </c>
+      <c r="E41" s="9">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.92</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-1.89</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-0.39</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-5.21</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-13.6</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-11.05</v>
+      </c>
+      <c r="E43" s="9">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.43</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-33.97</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-34.92</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-7.38</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-6.7</v>
+      </c>
+      <c r="E45" s="9">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>2.72</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1.74</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-18.75</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-18.73</v>
+      </c>
+      <c r="E46" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>3.17</v>
-      </c>
-      <c r="D20" s="6">
-        <v>1.28</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-5.1</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-4.68</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-1.63</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-17.02</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-16.85</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-1.85</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-33.62</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-34.28</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>9.619999999999999</v>
-      </c>
-      <c r="D23" s="6">
-        <v>7.33</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-21.02</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-22.52</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-0.79</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-33.88</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-34.04</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-0.79</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-0.62</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-45.28</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-44.72</v>
+      </c>
+      <c r="E52" s="9">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-31.91</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-32.28</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1256.3</v>
+      </c>
+      <c r="D53" s="7">
+        <v>1238.2</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-18.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>26.77</v>
-      </c>
-      <c r="D27" s="6">
-        <v>24.04</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>2975</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2997</v>
+      </c>
+      <c r="E54" s="9">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>35.25</v>
-      </c>
-      <c r="D28" s="6">
-        <v>31.96</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1303.6</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1304</v>
+      </c>
+      <c r="E55" s="9">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>31.29</v>
-      </c>
-      <c r="D29" s="6">
-        <v>27.44</v>
-      </c>
-      <c r="E29" s="7">
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1787.1</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1795</v>
+      </c>
+      <c r="E56" s="9">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>206.55</v>
+      </c>
+      <c r="D57" s="7">
+        <v>206.96</v>
+      </c>
+      <c r="E57" s="9">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>390.75</v>
+      </c>
+      <c r="D58" s="7">
+        <v>386.9</v>
+      </c>
+      <c r="E58" s="8">
         <v>-3.85</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>638.4</v>
+      </c>
+      <c r="D59" s="7">
+        <v>626.25</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-12.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>183.56</v>
+      </c>
+      <c r="D60" s="7">
+        <v>183.1</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>71.56999999999999</v>
+      </c>
+      <c r="D61" s="7">
+        <v>72.31</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>41.93</v>
+      </c>
+      <c r="D62" s="7">
+        <v>37.19</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-4.74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>48.27</v>
+      </c>
+      <c r="D63" s="7">
+        <v>50.12</v>
+      </c>
+      <c r="E63" s="9">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>48.79</v>
+      </c>
+      <c r="D64" s="7">
+        <v>48.86</v>
+      </c>
+      <c r="E64" s="9">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>58.02</v>
+      </c>
+      <c r="D65" s="7">
+        <v>58.91</v>
+      </c>
+      <c r="E65" s="9">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>60.37</v>
-      </c>
-      <c r="D30" s="6">
-        <v>62.04</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>48.38</v>
+      </c>
+      <c r="D66" s="7">
+        <v>48.93</v>
+      </c>
+      <c r="E66" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-31.39</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-31.55</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>38.36</v>
+      </c>
+      <c r="D67" s="7">
+        <v>35.52</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2.84</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="D32" s="6">
-        <v>5.41</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>53.78</v>
+      </c>
+      <c r="D68" s="7">
+        <v>49.89</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-3.89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-27.6</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-29.58</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>40.38</v>
+      </c>
+      <c r="D69" s="7">
+        <v>39.69</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-44.09</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-43.39</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>42.62</v>
+      </c>
+      <c r="D70" s="7">
+        <v>46.21</v>
+      </c>
+      <c r="E70" s="9">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-6.22</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-6.93</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>-48.1</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-37.23</v>
+      </c>
+      <c r="E71" s="9">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>-62.96</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-62.52</v>
+      </c>
+      <c r="E72" s="9">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-11.18</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-15.89</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-4.71</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-57.15</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-70.52</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-13.37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-0.62</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-2.19</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-6.9</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-65.42</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-58.52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-10.86</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-11.65</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-44.17</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-42.61</v>
+      </c>
+      <c r="E75" s="9">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-8.41</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-40.47</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-29.66</v>
+      </c>
+      <c r="E76" s="9">
+        <v>10.81</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-9.16</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-12.95</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>57.46</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-52.98</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-110.44</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1.45</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-3.34</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-52.7</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-64.76000000000001</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-12.06</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-11.49</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-13.6</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-33.79</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-33.97</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-5.98</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-7.38</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-16.83</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-18.75</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-3.14</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-5.1</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-17</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-17.02</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-34.04</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-33.62</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-18.26</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-21.02</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-32.64</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-33.88</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-45.17</v>
-      </c>
-      <c r="D52" s="6">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-46.34</v>
+      </c>
+      <c r="D79" s="7">
         <v>-45.28</v>
       </c>
-      <c r="E52" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1259.7</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1256.3</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>3020</v>
-      </c>
-      <c r="D54" s="6">
-        <v>2975</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1334.5</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1303.6</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-30.9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1824</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1787.1</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-36.9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>206.6</v>
-      </c>
-      <c r="D57" s="6">
-        <v>206.55</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>388.3</v>
-      </c>
-      <c r="D58" s="6">
-        <v>390.75</v>
-      </c>
-      <c r="E58" s="8">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>660.7</v>
-      </c>
-      <c r="D59" s="6">
-        <v>638.4</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-22.3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>186.98</v>
-      </c>
-      <c r="D60" s="6">
-        <v>183.56</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-3.42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>71.72</v>
-      </c>
-      <c r="D61" s="6">
-        <v>71.56999999999999</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>42.88</v>
-      </c>
-      <c r="D62" s="6">
-        <v>41.93</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>51.93</v>
-      </c>
-      <c r="D63" s="6">
-        <v>48.27</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-3.66</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>53.75</v>
-      </c>
-      <c r="D64" s="6">
-        <v>48.79</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-4.96</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>64.02</v>
-      </c>
-      <c r="D65" s="6">
-        <v>58.02</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>48.44</v>
-      </c>
-      <c r="D66" s="6">
-        <v>48.38</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>35.31</v>
-      </c>
-      <c r="D67" s="6">
-        <v>38.36</v>
-      </c>
-      <c r="E67" s="8">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>62.01</v>
-      </c>
-      <c r="D68" s="6">
-        <v>53.78</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-8.23</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>45.93</v>
-      </c>
-      <c r="D69" s="6">
-        <v>40.38</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-5.55</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>43.16</v>
-      </c>
-      <c r="D70" s="6">
-        <v>42.62</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>231.62</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-48.1</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-279.72</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-21.74</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-62.96</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-41.22</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>79.88</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-57.15</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-137.03</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>76.40000000000001</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-6.9</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-83.3</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-10.14</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-44.17</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-34.03</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>48.58</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-40.47</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-89.05</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>3976.36</v>
-      </c>
-      <c r="D77" s="6">
-        <v>57.46</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-3918.9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-20.46</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-52.7</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-32.24</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-6.34</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-46.34</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-40</v>
+      <c r="E79" s="9">
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>
@@ -3437,60 +3441,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>77</v>
       </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>56.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.7</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>46.1</v>
+      </c>
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-1.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-6.7</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3592,61 +3596,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.6132</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1962</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1565</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0307</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.0035</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0401</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.0789</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1084</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.146</v>
+      <c r="A2" s="15">
+        <v>0.6093</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1987</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1588</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.027</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0562</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.0794</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.1135</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1458</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,28 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.3 → 50.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.3</t>
+    <t>50.1 → 49.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.1</t>
   </si>
   <si>
-    <t>53.8 → 49.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.8</t>
-  </si>
-  <si>
-    <t>49.9</t>
+    <t>49.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -303,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -427,7 +415,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -943,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1238.2</v>
+        <v>1251.4</v>
       </c>
       <c r="D2">
-        <v>-1.44</v>
+        <v>1.07</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -955,46 +942,46 @@
         <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-34.92</v>
+        <v>-34.23</v>
       </c>
       <c r="H2">
-        <v>1.06</v>
+        <v>2.14</v>
       </c>
       <c r="I2">
-        <v>1.06</v>
+        <v>2.02</v>
       </c>
       <c r="J2">
-        <v>-5.29</v>
+        <v>-3.81</v>
       </c>
       <c r="K2">
-        <v>-6.86</v>
+        <v>-7.1</v>
       </c>
       <c r="L2">
-        <v>-32.9</v>
+        <v>-32.26</v>
       </c>
       <c r="M2">
-        <v>-11.35</v>
+        <v>-11.05</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P2">
-        <v>1242.66</v>
+        <v>1247.62</v>
       </c>
       <c r="Q2">
-        <v>1267.71</v>
+        <v>1264.99</v>
       </c>
       <c r="R2">
-        <v>1317.01</v>
+        <v>1314.8</v>
       </c>
       <c r="S2">
-        <v>1458.99</v>
+        <v>1456.23</v>
       </c>
       <c r="T2">
-        <v>-15.13</v>
+        <v>-14.07</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>37.19</v>
+        <v>42.31</v>
       </c>
       <c r="Z2">
-        <v>-21.85</v>
+        <v>-20.36</v>
       </c>
       <c r="AA2">
-        <v>-22.71</v>
+        <v>-22.24</v>
       </c>
       <c r="AB2">
-        <v>0.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC2">
-        <v>85.44</v>
+        <v>84.19</v>
       </c>
       <c r="AD2">
-        <v>67.03</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="AE2">
-        <v>24.31</v>
+        <v>23.75</v>
       </c>
       <c r="AF2">
-        <v>-37.23</v>
+        <v>-57.63</v>
       </c>
       <c r="AG2">
-        <v>1325.43</v>
+        <v>1320.21</v>
       </c>
       <c r="AH2">
-        <v>1210</v>
+        <v>1209.77</v>
       </c>
       <c r="AI2">
         <v>1296.94</v>
@@ -1045,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>25.77</v>
+        <v>24.28</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2997</v>
+        <v>2993.2</v>
       </c>
       <c r="D3">
-        <v>0.74</v>
+        <v>-0.13</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1068,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.7</v>
+        <v>-6.81</v>
       </c>
       <c r="H3">
-        <v>70.48</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="I3">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="K3">
-        <v>1.15</v>
+        <v>-2.49</v>
       </c>
       <c r="L3">
-        <v>24.83</v>
+        <v>24.67</v>
       </c>
       <c r="M3">
-        <v>15.88</v>
+        <v>15.27</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>2967.04</v>
+        <v>2981.68</v>
       </c>
       <c r="Q3">
-        <v>2996.11</v>
+        <v>2990.27</v>
       </c>
       <c r="R3">
-        <v>3028.83</v>
+        <v>3024.92</v>
       </c>
       <c r="S3">
-        <v>2548.53</v>
+        <v>2552.42</v>
       </c>
       <c r="T3">
-        <v>17.6</v>
+        <v>17.27</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1122,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>50.12</v>
+        <v>49.79</v>
       </c>
       <c r="Z3">
-        <v>-10.62</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="AA3">
-        <v>-12.82</v>
+        <v>-12.08</v>
       </c>
       <c r="AB3">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="AC3">
-        <v>60.64</v>
+        <v>54.6</v>
       </c>
       <c r="AD3">
-        <v>50.49</v>
+        <v>55.2</v>
       </c>
       <c r="AE3">
-        <v>79.16</v>
+        <v>76.77</v>
       </c>
       <c r="AF3">
-        <v>-62.52</v>
+        <v>-59.58</v>
       </c>
       <c r="AG3">
-        <v>3195.41</v>
+        <v>3182.22</v>
       </c>
       <c r="AH3">
-        <v>2796.8</v>
+        <v>2798.31</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1158,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>20.76</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1304</v>
+        <v>1300.9</v>
       </c>
       <c r="D4">
-        <v>0.03</v>
+        <v>-0.24</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1181,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.73</v>
+        <v>-18.92</v>
       </c>
       <c r="H4">
-        <v>68.73999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="I4">
-        <v>3.9</v>
+        <v>2.42</v>
       </c>
       <c r="J4">
-        <v>-1.21</v>
+        <v>-0.54</v>
       </c>
       <c r="K4">
-        <v>-13.71</v>
+        <v>-14.72</v>
       </c>
       <c r="L4">
-        <v>33.14</v>
+        <v>32.89</v>
       </c>
       <c r="M4">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1297.3</v>
+        <v>1303.44</v>
       </c>
       <c r="Q4">
-        <v>1292.51</v>
+        <v>1291.05</v>
       </c>
       <c r="R4">
-        <v>1355.5</v>
+        <v>1349.42</v>
       </c>
       <c r="S4">
-        <v>1190.99</v>
+        <v>1192.42</v>
       </c>
       <c r="T4">
-        <v>9.49</v>
+        <v>9.1</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1235,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>48.86</v>
+        <v>48.34</v>
       </c>
       <c r="Z4">
-        <v>-13.46</v>
+        <v>-12.05</v>
       </c>
       <c r="AA4">
-        <v>-20.75</v>
+        <v>-19.01</v>
       </c>
       <c r="AB4">
-        <v>7.29</v>
+        <v>6.96</v>
       </c>
       <c r="AC4">
-        <v>77.48</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="AD4">
-        <v>79.72</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="AE4">
-        <v>37.46</v>
+        <v>36.74</v>
       </c>
       <c r="AF4">
-        <v>-70.52</v>
+        <v>-55.87</v>
       </c>
       <c r="AG4">
-        <v>1348.82</v>
+        <v>1344.73</v>
       </c>
       <c r="AH4">
-        <v>1236.2</v>
+        <v>1237.38</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1271,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>21.61</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1795</v>
+        <v>1807.3</v>
       </c>
       <c r="D5">
-        <v>0.44</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1294,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-4.68</v>
+        <v>-4.03</v>
       </c>
       <c r="H5">
-        <v>38.28</v>
+        <v>39.22</v>
       </c>
       <c r="I5">
-        <v>4.74</v>
+        <v>4.84</v>
       </c>
       <c r="J5">
-        <v>5.59</v>
+        <v>8.09</v>
       </c>
       <c r="K5">
-        <v>0.62</v>
+        <v>-0.33</v>
       </c>
       <c r="L5">
-        <v>28.2</v>
+        <v>28.46</v>
       </c>
       <c r="M5">
-        <v>19.87</v>
+        <v>19.74</v>
       </c>
       <c r="N5">
         <v>88</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>1773.64</v>
+        <v>1790.34</v>
       </c>
       <c r="Q5">
-        <v>1721.84</v>
+        <v>1727.07</v>
       </c>
       <c r="R5">
-        <v>1728.69</v>
+        <v>1728.4</v>
       </c>
       <c r="S5">
-        <v>1616.24</v>
+        <v>1617.78</v>
       </c>
       <c r="T5">
-        <v>11.06</v>
+        <v>11.71</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1348,43 +1335,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>58.91</v>
+        <v>60.31</v>
       </c>
       <c r="Z5">
-        <v>19.97</v>
+        <v>22.77</v>
       </c>
       <c r="AA5">
-        <v>8.539999999999999</v>
+        <v>11.38</v>
       </c>
       <c r="AB5">
-        <v>11.43</v>
+        <v>11.39</v>
       </c>
       <c r="AC5">
-        <v>81.58</v>
+        <v>73.28</v>
       </c>
       <c r="AD5">
-        <v>82.37</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AE5">
-        <v>41.69</v>
+        <v>40.11</v>
       </c>
       <c r="AF5">
-        <v>-65.42</v>
+        <v>-52.79</v>
       </c>
       <c r="AG5">
-        <v>1829.04</v>
+        <v>1840.37</v>
       </c>
       <c r="AH5">
-        <v>1614.63</v>
+        <v>1613.76</v>
       </c>
       <c r="AI5">
-        <v>1674.34</v>
+        <v>1679.97</v>
       </c>
       <c r="AJ5" t="s">
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.49</v>
+        <v>31.51</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,58 +1382,58 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>206.96</v>
+        <v>204.8</v>
       </c>
       <c r="D6">
-        <v>0.2</v>
+        <v>-1.04</v>
       </c>
       <c r="E6">
         <v>248.91</v>
       </c>
       <c r="F6">
-        <v>126.27</v>
+        <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-16.85</v>
+        <v>-17.72</v>
       </c>
       <c r="H6">
-        <v>63.9</v>
+        <v>54.03</v>
       </c>
       <c r="I6">
-        <v>2.46</v>
+        <v>1.22</v>
       </c>
       <c r="J6">
-        <v>0.71</v>
+        <v>0.54</v>
       </c>
       <c r="K6">
-        <v>-10.56</v>
+        <v>-10.86</v>
       </c>
       <c r="L6">
-        <v>64.12</v>
+        <v>62.19</v>
       </c>
       <c r="M6">
-        <v>60.93</v>
+        <v>60.21</v>
       </c>
       <c r="N6">
         <v>99</v>
       </c>
       <c r="O6">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P6">
-        <v>205.67</v>
+        <v>206.17</v>
       </c>
       <c r="Q6">
-        <v>207.42</v>
+        <v>207.34</v>
       </c>
       <c r="R6">
-        <v>209.48</v>
+        <v>209.05</v>
       </c>
       <c r="S6">
-        <v>186.07</v>
+        <v>186.38</v>
       </c>
       <c r="T6">
-        <v>11.22</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1461,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>48.93</v>
+        <v>46.15</v>
       </c>
       <c r="Z6">
-        <v>-0.79</v>
+        <v>-0.9</v>
       </c>
       <c r="AA6">
-        <v>-0.87</v>
+        <v>-0.88</v>
       </c>
       <c r="AB6">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="AC6">
-        <v>46</v>
+        <v>34.52</v>
       </c>
       <c r="AD6">
-        <v>47.46</v>
+        <v>43.4</v>
       </c>
       <c r="AE6">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="AF6">
-        <v>-42.61</v>
+        <v>-2.05</v>
       </c>
       <c r="AG6">
-        <v>216.04</v>
+        <v>216.03</v>
       </c>
       <c r="AH6">
-        <v>198.8</v>
+        <v>198.65</v>
       </c>
       <c r="AI6">
         <v>217.63</v>
@@ -1497,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>14.73</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>386.9</v>
+        <v>392.75</v>
       </c>
       <c r="D7">
-        <v>-0.99</v>
+        <v>1.51</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1520,46 +1507,46 @@
         <v>381.05</v>
       </c>
       <c r="G7">
-        <v>-34.28</v>
+        <v>-33.28</v>
       </c>
       <c r="H7">
-        <v>1.54</v>
+        <v>3.07</v>
       </c>
       <c r="I7">
-        <v>1.35</v>
+        <v>3.07</v>
       </c>
       <c r="J7">
-        <v>-6.66</v>
+        <v>-3.91</v>
       </c>
       <c r="K7">
-        <v>-6.74</v>
+        <v>-7.99</v>
       </c>
       <c r="L7">
-        <v>-33.2</v>
+        <v>-32.07</v>
       </c>
       <c r="M7">
-        <v>-0.85</v>
+        <v>-0.55</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P7">
-        <v>386.05</v>
+        <v>388.39</v>
       </c>
       <c r="Q7">
-        <v>398.24</v>
+        <v>397.22</v>
       </c>
       <c r="R7">
-        <v>415.93</v>
+        <v>415.19</v>
       </c>
       <c r="S7">
-        <v>460.01</v>
+        <v>459.3</v>
       </c>
       <c r="T7">
-        <v>-15.89</v>
+        <v>-14.49</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1574,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.52</v>
+        <v>42.48</v>
       </c>
       <c r="Z7">
-        <v>-8.67</v>
+        <v>-7.95</v>
       </c>
       <c r="AA7">
-        <v>-8.449999999999999</v>
+        <v>-8.35</v>
       </c>
       <c r="AB7">
-        <v>-0.22</v>
+        <v>0.41</v>
       </c>
       <c r="AC7">
-        <v>74.65000000000001</v>
+        <v>85.56</v>
       </c>
       <c r="AD7">
-        <v>53.64</v>
+        <v>72.67</v>
       </c>
       <c r="AE7">
-        <v>8.01</v>
+        <v>7.87</v>
       </c>
       <c r="AF7">
-        <v>-29.66</v>
+        <v>-51.4</v>
       </c>
       <c r="AG7">
-        <v>420.13</v>
+        <v>418.07</v>
       </c>
       <c r="AH7">
-        <v>376.35</v>
+        <v>376.38</v>
       </c>
       <c r="AI7">
         <v>405.74</v>
@@ -1610,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>34.93</v>
+        <v>33.42</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>626.25</v>
+        <v>625.25</v>
       </c>
       <c r="D8">
-        <v>-1.9</v>
+        <v>-0.16</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1633,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-22.52</v>
+        <v>-22.64</v>
       </c>
       <c r="H8">
-        <v>33.89</v>
+        <v>33.67</v>
       </c>
       <c r="I8">
-        <v>7.95</v>
+        <v>6.61</v>
       </c>
       <c r="J8">
-        <v>-3.07</v>
+        <v>-2.24</v>
       </c>
       <c r="K8">
-        <v>-12.54</v>
+        <v>-13.09</v>
       </c>
       <c r="L8">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="M8">
-        <v>-14.58</v>
+        <v>-14.9</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P8">
-        <v>619.77</v>
+        <v>627.52</v>
       </c>
       <c r="Q8">
-        <v>617.2</v>
+        <v>616.45</v>
       </c>
       <c r="R8">
-        <v>647.59</v>
+        <v>645.66</v>
       </c>
       <c r="S8">
-        <v>614.14</v>
+        <v>614.3</v>
       </c>
       <c r="T8">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1687,34 +1674,34 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>49.89</v>
+        <v>49.57</v>
       </c>
       <c r="Z8">
-        <v>-8.31</v>
+        <v>-7.08</v>
       </c>
       <c r="AA8">
-        <v>-13.61</v>
+        <v>-12.3</v>
       </c>
       <c r="AB8">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="AC8">
-        <v>82.69</v>
+        <v>72.11</v>
       </c>
       <c r="AD8">
-        <v>70.56999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="AE8">
-        <v>21.21</v>
+        <v>20.42</v>
       </c>
       <c r="AF8">
-        <v>-52.98</v>
+        <v>-63.71</v>
       </c>
       <c r="AG8">
-        <v>660.95</v>
+        <v>659.04</v>
       </c>
       <c r="AH8">
-        <v>573.4400000000001</v>
+        <v>573.85</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1723,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>44.17</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>183.1</v>
+        <v>186.18</v>
       </c>
       <c r="D9">
-        <v>-0.25</v>
+        <v>1.68</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1746,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-34.04</v>
+        <v>-32.93</v>
       </c>
       <c r="H9">
-        <v>6.27</v>
+        <v>8.06</v>
       </c>
       <c r="I9">
-        <v>-0.02</v>
+        <v>2.33</v>
       </c>
       <c r="J9">
-        <v>-2.67</v>
+        <v>-3.97</v>
       </c>
       <c r="K9">
-        <v>-0.39</v>
+        <v>1.69</v>
       </c>
       <c r="L9">
-        <v>-29.39</v>
+        <v>-28.28</v>
       </c>
       <c r="M9">
-        <v>-7.94</v>
+        <v>-7.6</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P9">
-        <v>183.92</v>
+        <v>184.77</v>
       </c>
       <c r="Q9">
-        <v>189.58</v>
+        <v>188.86</v>
       </c>
       <c r="R9">
-        <v>190.32</v>
+        <v>190.26</v>
       </c>
       <c r="S9">
-        <v>199</v>
+        <v>198.68</v>
       </c>
       <c r="T9">
-        <v>-7.99</v>
+        <v>-6.29</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1800,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>39.69</v>
+        <v>46.34</v>
       </c>
       <c r="Z9">
-        <v>-2.31</v>
+        <v>-2.11</v>
       </c>
       <c r="AA9">
-        <v>-1.71</v>
+        <v>-1.79</v>
       </c>
       <c r="AB9">
-        <v>-0.6</v>
+        <v>-0.32</v>
       </c>
       <c r="AC9">
-        <v>48.76</v>
+        <v>59.8</v>
       </c>
       <c r="AD9">
-        <v>40.56</v>
+        <v>50.33</v>
       </c>
       <c r="AE9">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="AF9">
-        <v>-64.76000000000001</v>
+        <v>-55.62</v>
       </c>
       <c r="AG9">
-        <v>201.93</v>
+        <v>200.13</v>
       </c>
       <c r="AH9">
-        <v>177.23</v>
+        <v>177.58</v>
       </c>
       <c r="AI9">
         <v>195.69</v>
@@ -1836,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>33.31</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>72.31</v>
+        <v>71.11</v>
       </c>
       <c r="D10">
-        <v>1.03</v>
+        <v>-1.66</v>
       </c>
       <c r="E10">
         <v>130.8</v>
@@ -1859,46 +1846,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-44.72</v>
+        <v>-45.63</v>
       </c>
       <c r="H10">
-        <v>21.98</v>
+        <v>19.96</v>
       </c>
       <c r="I10">
-        <v>2.67</v>
+        <v>1.96</v>
       </c>
       <c r="J10">
-        <v>-4.21</v>
+        <v>-5.36</v>
       </c>
       <c r="K10">
-        <v>-11.05</v>
+        <v>-12.34</v>
       </c>
       <c r="L10">
-        <v>-42.54</v>
+        <v>-42.44</v>
       </c>
       <c r="M10">
-        <v>-5.62</v>
+        <v>-6.84</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>71.28</v>
+        <v>71.55</v>
       </c>
       <c r="Q10">
-        <v>72.36</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="R10">
-        <v>75.25</v>
+        <v>75.03</v>
       </c>
       <c r="S10">
-        <v>80.20999999999999</v>
+        <v>80.16</v>
       </c>
       <c r="T10">
-        <v>-9.85</v>
+        <v>-11.29</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1913,31 +1900,31 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>46.21</v>
+        <v>41.66</v>
       </c>
       <c r="Z10">
-        <v>-1.12</v>
+        <v>-1.1</v>
       </c>
       <c r="AA10">
-        <v>-1.26</v>
+        <v>-1.23</v>
       </c>
       <c r="AB10">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AC10">
-        <v>83.88</v>
+        <v>81.52</v>
       </c>
       <c r="AD10">
-        <v>72.42</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="AE10">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AF10">
-        <v>-45.28</v>
+        <v>88.98</v>
       </c>
       <c r="AG10">
-        <v>75.3</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="AH10">
         <v>69.42</v>
@@ -1949,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>26.08</v>
+        <v>23.57</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2148,1280 +2135,1260 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.29</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-3.81</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-0.18</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-1.21</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-0.54</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>5.59</v>
+      </c>
+      <c r="D10" s="6">
+        <v>8.09</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.54</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-6.66</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-3.91</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-3.07</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.67</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-3.97</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.21</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-5.36</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-3.44</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-5.29</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2.02</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-0.66</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2.34</v>
+      </c>
+      <c r="D17" s="6">
+        <v>2.51</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0.14</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-1.21</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2.42</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5.37</v>
-      </c>
-      <c r="D11" s="7">
-        <v>5.59</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4.74</v>
+      </c>
+      <c r="D19" s="6">
+        <v>4.84</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1.25</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.71</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2.46</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-4.93</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-6.66</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>1.35</v>
+      </c>
+      <c r="D21" s="6">
+        <v>3.07</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-2.93</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-3.07</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>7.95</v>
+      </c>
+      <c r="D22" s="6">
+        <v>6.61</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-2.69</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-2.67</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.02</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-5.21</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-4.21</v>
-      </c>
-      <c r="E16" s="9">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.96</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-32.9</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-32.26</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>24.83</v>
+      </c>
+      <c r="D26" s="6">
+        <v>24.67</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>33.14</v>
+      </c>
+      <c r="D27" s="6">
+        <v>32.89</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>28.2</v>
+      </c>
+      <c r="D28" s="6">
+        <v>28.46</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>64.12</v>
+      </c>
+      <c r="D29" s="6">
+        <v>62.19</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-33.2</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-32.07</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="D31" s="6">
+        <v>3.05</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-29.39</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-28.28</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-42.54</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-42.44</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-6.86</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-7.1</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1.15</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-2.49</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-3.64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-13.71</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-14.72</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.62</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-10.56</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-10.86</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-6.74</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-7.99</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-12.54</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-13.09</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-0.39</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1.69</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-11.05</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-12.34</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-34.92</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-34.23</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-6.81</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-18.73</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-18.92</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-4.68</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-4.03</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-16.85</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-17.72</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-34.28</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-33.28</v>
+      </c>
+      <c r="E48" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-22.52</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-22.64</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-34.04</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-32.93</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-44.72</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-45.63</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0.79</v>
-      </c>
-      <c r="D17" s="7">
-        <v>1.06</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>1238.2</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1251.4</v>
+      </c>
+      <c r="E52" s="7">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>2997</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2993.2</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1304</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1300.9</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1795</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1807.3</v>
+      </c>
+      <c r="E55" s="7">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>206.96</v>
+      </c>
+      <c r="D56" s="6">
+        <v>204.8</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>386.9</v>
+      </c>
+      <c r="D57" s="6">
+        <v>392.75</v>
+      </c>
+      <c r="E57" s="7">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>626.25</v>
+      </c>
+      <c r="D58" s="6">
+        <v>625.25</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>183.1</v>
+      </c>
+      <c r="D59" s="6">
+        <v>186.18</v>
+      </c>
+      <c r="E59" s="7">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>72.31</v>
+      </c>
+      <c r="D60" s="6">
+        <v>71.11</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>37.19</v>
+      </c>
+      <c r="D61" s="6">
+        <v>42.31</v>
+      </c>
+      <c r="E61" s="7">
+        <v>5.12</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>50.12</v>
+      </c>
+      <c r="D62" s="6">
+        <v>49.79</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>48.86</v>
+      </c>
+      <c r="D63" s="6">
+        <v>48.34</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>58.91</v>
+      </c>
+      <c r="D64" s="6">
+        <v>60.31</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>48.93</v>
+      </c>
+      <c r="D65" s="6">
+        <v>46.15</v>
+      </c>
+      <c r="E65" s="8">
         <v>-2.78</v>
       </c>
-      <c r="D18" s="7">
-        <v>2.34</v>
-      </c>
-      <c r="E18" s="9">
-        <v>5.12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>35.52</v>
+      </c>
+      <c r="D66" s="6">
+        <v>42.48</v>
+      </c>
+      <c r="E66" s="7">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>49.89</v>
+      </c>
+      <c r="D67" s="6">
+        <v>49.57</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>39.69</v>
+      </c>
+      <c r="D68" s="6">
+        <v>46.34</v>
+      </c>
+      <c r="E68" s="7">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>46.21</v>
+      </c>
+      <c r="D69" s="6">
+        <v>41.66</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-37.23</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-57.63</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-20.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-62.52</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-59.58</v>
+      </c>
+      <c r="E71" s="7">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1.74</v>
-      </c>
-      <c r="D19" s="7">
-        <v>3.9</v>
-      </c>
-      <c r="E19" s="9">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-70.52</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-55.87</v>
+      </c>
+      <c r="E72" s="7">
+        <v>14.65</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1.28</v>
-      </c>
-      <c r="D20" s="7">
-        <v>4.74</v>
-      </c>
-      <c r="E20" s="9">
-        <v>3.46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-65.42</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-52.79</v>
+      </c>
+      <c r="E73" s="7">
+        <v>12.63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.63</v>
-      </c>
-      <c r="D21" s="7">
-        <v>2.46</v>
-      </c>
-      <c r="E21" s="9">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-42.61</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="E74" s="7">
+        <v>40.56</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-0.28</v>
-      </c>
-      <c r="D22" s="7">
-        <v>1.35</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-29.66</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-51.4</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-21.74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>7.33</v>
-      </c>
-      <c r="D23" s="7">
-        <v>7.95</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-52.98</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-63.71</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-10.73</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-0.79</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-0.02</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-64.76000000000001</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-55.62</v>
+      </c>
+      <c r="E77" s="7">
+        <v>9.140000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-0.62</v>
-      </c>
-      <c r="D25" s="7">
-        <v>2.67</v>
-      </c>
-      <c r="E25" s="9">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-32.28</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-32.9</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>24.04</v>
-      </c>
-      <c r="D27" s="7">
-        <v>24.83</v>
-      </c>
-      <c r="E27" s="9">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>31.96</v>
-      </c>
-      <c r="D28" s="7">
-        <v>33.14</v>
-      </c>
-      <c r="E28" s="9">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>27.44</v>
-      </c>
-      <c r="D29" s="7">
-        <v>28.2</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>62.04</v>
-      </c>
-      <c r="D30" s="7">
-        <v>64.12</v>
-      </c>
-      <c r="E30" s="9">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-31.55</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-33.2</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>5.41</v>
-      </c>
-      <c r="D32" s="7">
-        <v>3.2</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-29.58</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-29.39</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-43.39</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-42.54</v>
-      </c>
-      <c r="E34" s="9">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-6.93</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-6.86</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-2.77</v>
-      </c>
-      <c r="D36" s="7">
-        <v>1.15</v>
-      </c>
-      <c r="E36" s="9">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-15.89</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-13.71</v>
-      </c>
-      <c r="E37" s="9">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-2.19</v>
-      </c>
-      <c r="D38" s="7">
-        <v>0.62</v>
-      </c>
-      <c r="E38" s="9">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-11.65</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-10.56</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-6.74</v>
-      </c>
-      <c r="E40" s="9">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-12.95</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-12.54</v>
-      </c>
-      <c r="E41" s="9">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-1.89</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-0.39</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-13.6</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-11.05</v>
-      </c>
-      <c r="E43" s="9">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-33.97</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-34.92</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-7.38</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-6.7</v>
-      </c>
-      <c r="E45" s="9">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-18.75</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-18.73</v>
-      </c>
-      <c r="E46" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-5.1</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-4.68</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-17.02</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-16.85</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-33.62</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-34.28</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-21.02</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-22.52</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-33.88</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-34.04</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
         <v>-45.28</v>
       </c>
-      <c r="D52" s="7">
-        <v>-44.72</v>
-      </c>
-      <c r="E52" s="9">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1256.3</v>
-      </c>
-      <c r="D53" s="7">
-        <v>1238.2</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-18.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2975</v>
-      </c>
-      <c r="D54" s="7">
-        <v>2997</v>
-      </c>
-      <c r="E54" s="9">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1303.6</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1304</v>
-      </c>
-      <c r="E55" s="9">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>1787.1</v>
-      </c>
-      <c r="D56" s="7">
-        <v>1795</v>
-      </c>
-      <c r="E56" s="9">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>206.55</v>
-      </c>
-      <c r="D57" s="7">
-        <v>206.96</v>
-      </c>
-      <c r="E57" s="9">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>390.75</v>
-      </c>
-      <c r="D58" s="7">
-        <v>386.9</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>638.4</v>
-      </c>
-      <c r="D59" s="7">
-        <v>626.25</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-12.15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>183.56</v>
-      </c>
-      <c r="D60" s="7">
-        <v>183.1</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>71.56999999999999</v>
-      </c>
-      <c r="D61" s="7">
-        <v>72.31</v>
-      </c>
-      <c r="E61" s="9">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>41.93</v>
-      </c>
-      <c r="D62" s="7">
-        <v>37.19</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-4.74</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>48.27</v>
-      </c>
-      <c r="D63" s="7">
-        <v>50.12</v>
-      </c>
-      <c r="E63" s="9">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>48.79</v>
-      </c>
-      <c r="D64" s="7">
-        <v>48.86</v>
-      </c>
-      <c r="E64" s="9">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>58.02</v>
-      </c>
-      <c r="D65" s="7">
-        <v>58.91</v>
-      </c>
-      <c r="E65" s="9">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>48.38</v>
-      </c>
-      <c r="D66" s="7">
-        <v>48.93</v>
-      </c>
-      <c r="E66" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>38.36</v>
-      </c>
-      <c r="D67" s="7">
-        <v>35.52</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>53.78</v>
-      </c>
-      <c r="D68" s="7">
-        <v>49.89</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-3.89</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>40.38</v>
-      </c>
-      <c r="D69" s="7">
-        <v>39.69</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>42.62</v>
-      </c>
-      <c r="D70" s="7">
-        <v>46.21</v>
-      </c>
-      <c r="E70" s="9">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="7">
-        <v>-48.1</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-37.23</v>
-      </c>
-      <c r="E71" s="9">
-        <v>10.87</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>-62.96</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-62.52</v>
-      </c>
-      <c r="E72" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>-57.15</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-70.52</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-13.37</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-6.9</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-65.42</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-58.52</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-44.17</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-42.61</v>
-      </c>
-      <c r="E75" s="9">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-40.47</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-29.66</v>
-      </c>
-      <c r="E76" s="9">
-        <v>10.81</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>57.46</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-52.98</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-110.44</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-52.7</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-64.76000000000001</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-12.06</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-46.34</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-45.28</v>
-      </c>
-      <c r="E79" s="9">
-        <v>1.06</v>
+      <c r="D78" s="6">
+        <v>88.98</v>
+      </c>
+      <c r="E78" s="7">
+        <v>134.26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3441,60 +3408,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>56.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>46.1</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>47.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-1.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-6.7</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-1.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3596,61 +3563,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.6093</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1987</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1588</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.027</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.008500000000000001</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0562</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.0794</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.1135</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1458</v>
+      <c r="A2" s="14">
+        <v>0.6021</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1974</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1527</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0251</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0684</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.076</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.1105</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.149</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.1 → 49.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>49.8</t>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -930,10 +924,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1251.4</v>
+        <v>1236.1</v>
       </c>
       <c r="D2">
-        <v>1.07</v>
+        <v>-1.22</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +936,46 @@
         <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-34.23</v>
+        <v>-35.03</v>
       </c>
       <c r="H2">
-        <v>2.14</v>
+        <v>0.89</v>
       </c>
       <c r="I2">
-        <v>2.02</v>
+        <v>0.29</v>
       </c>
       <c r="J2">
-        <v>-3.81</v>
+        <v>-5.34</v>
       </c>
       <c r="K2">
-        <v>-7.1</v>
+        <v>-7.61</v>
       </c>
       <c r="L2">
-        <v>-32.26</v>
+        <v>-33.84</v>
       </c>
       <c r="M2">
-        <v>-11.05</v>
+        <v>-10.87</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P2">
-        <v>1247.62</v>
+        <v>1248.34</v>
       </c>
       <c r="Q2">
-        <v>1264.99</v>
+        <v>1260.21</v>
       </c>
       <c r="R2">
-        <v>1314.8</v>
+        <v>1311.86</v>
       </c>
       <c r="S2">
-        <v>1456.23</v>
+        <v>1453.47</v>
       </c>
       <c r="T2">
-        <v>-14.07</v>
+        <v>-14.96</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +990,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>42.31</v>
+        <v>38.4</v>
       </c>
       <c r="Z2">
-        <v>-20.36</v>
+        <v>-20.19</v>
       </c>
       <c r="AA2">
-        <v>-22.24</v>
+        <v>-21.83</v>
       </c>
       <c r="AB2">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AC2">
-        <v>84.19</v>
+        <v>76.47</v>
       </c>
       <c r="AD2">
-        <v>80.79000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="AE2">
-        <v>23.75</v>
+        <v>23.54</v>
       </c>
       <c r="AF2">
-        <v>-57.63</v>
+        <v>-27.56</v>
       </c>
       <c r="AG2">
-        <v>1320.21</v>
+        <v>1307.03</v>
       </c>
       <c r="AH2">
-        <v>1209.77</v>
+        <v>1213.39</v>
       </c>
       <c r="AI2">
         <v>1296.94</v>
@@ -1032,7 +1026,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>24.28</v>
+        <v>21.13</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1037,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2993.2</v>
+        <v>2900</v>
       </c>
       <c r="D3">
-        <v>-0.13</v>
+        <v>-3.11</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1049,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-6.81</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="H3">
-        <v>70.26000000000001</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="I3">
-        <v>2.51</v>
+        <v>-0.79</v>
       </c>
       <c r="J3">
-        <v>-0.18</v>
+        <v>-6.75</v>
       </c>
       <c r="K3">
-        <v>-2.49</v>
+        <v>-4.54</v>
       </c>
       <c r="L3">
-        <v>24.67</v>
+        <v>14.95</v>
       </c>
       <c r="M3">
-        <v>15.27</v>
+        <v>14.74</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="P3">
-        <v>2981.68</v>
+        <v>2977.04</v>
       </c>
       <c r="Q3">
-        <v>2990.27</v>
+        <v>2979.67</v>
       </c>
       <c r="R3">
-        <v>3024.92</v>
+        <v>3019.91</v>
       </c>
       <c r="S3">
-        <v>2552.42</v>
+        <v>2555.59</v>
       </c>
       <c r="T3">
-        <v>17.27</v>
+        <v>13.48</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>49.79</v>
+        <v>42.39</v>
       </c>
       <c r="Z3">
-        <v>-9.130000000000001</v>
+        <v>-15.29</v>
       </c>
       <c r="AA3">
-        <v>-12.08</v>
+        <v>-12.72</v>
       </c>
       <c r="AB3">
-        <v>2.96</v>
+        <v>-2.56</v>
       </c>
       <c r="AC3">
-        <v>54.6</v>
+        <v>36.5</v>
       </c>
       <c r="AD3">
-        <v>55.2</v>
+        <v>50.58</v>
       </c>
       <c r="AE3">
-        <v>76.77</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="AF3">
-        <v>-59.58</v>
+        <v>-48.91</v>
       </c>
       <c r="AG3">
-        <v>3182.22</v>
+        <v>3166.67</v>
       </c>
       <c r="AH3">
-        <v>2798.31</v>
+        <v>2792.66</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1145,7 +1139,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>20.18</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1150,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1300.9</v>
+        <v>1280.1</v>
       </c>
       <c r="D4">
-        <v>-0.24</v>
+        <v>-1.6</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1162,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.92</v>
+        <v>-20.22</v>
       </c>
       <c r="H4">
-        <v>68.34</v>
+        <v>65.64</v>
       </c>
       <c r="I4">
-        <v>2.42</v>
+        <v>0.46</v>
       </c>
       <c r="J4">
-        <v>-0.54</v>
+        <v>-3.75</v>
       </c>
       <c r="K4">
-        <v>-14.72</v>
+        <v>-16.12</v>
       </c>
       <c r="L4">
-        <v>32.89</v>
+        <v>24.2</v>
       </c>
       <c r="M4">
-        <v>2.51</v>
+        <v>2.14</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>1303.44</v>
+        <v>1304.62</v>
       </c>
       <c r="Q4">
-        <v>1291.05</v>
+        <v>1289.9</v>
       </c>
       <c r="R4">
-        <v>1349.42</v>
+        <v>1343.92</v>
       </c>
       <c r="S4">
-        <v>1192.42</v>
+        <v>1193.74</v>
       </c>
       <c r="T4">
-        <v>9.1</v>
+        <v>7.23</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1216,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>48.34</v>
+        <v>44.9</v>
       </c>
       <c r="Z4">
-        <v>-12.05</v>
+        <v>-12.47</v>
       </c>
       <c r="AA4">
-        <v>-19.01</v>
+        <v>-17.7</v>
       </c>
       <c r="AB4">
-        <v>6.96</v>
+        <v>5.24</v>
       </c>
       <c r="AC4">
-        <v>64.81999999999999</v>
+        <v>55.17</v>
       </c>
       <c r="AD4">
-        <v>74.20999999999999</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="AE4">
-        <v>36.74</v>
+        <v>36.4</v>
       </c>
       <c r="AF4">
-        <v>-55.87</v>
+        <v>64.47</v>
       </c>
       <c r="AG4">
-        <v>1344.73</v>
+        <v>1343.47</v>
       </c>
       <c r="AH4">
-        <v>1237.38</v>
+        <v>1236.33</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1258,7 +1252,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>20.65</v>
+        <v>18.04</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1263,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1807.3</v>
+        <v>1785.3</v>
       </c>
       <c r="D5">
-        <v>0.6899999999999999</v>
+        <v>-1.22</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,88 +1275,88 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-4.03</v>
+        <v>-5.2</v>
       </c>
       <c r="H5">
-        <v>39.22</v>
+        <v>37.53</v>
       </c>
       <c r="I5">
-        <v>4.84</v>
+        <v>2.7</v>
       </c>
       <c r="J5">
-        <v>8.09</v>
+        <v>4.85</v>
       </c>
       <c r="K5">
-        <v>-0.33</v>
+        <v>-0.6</v>
       </c>
       <c r="L5">
-        <v>28.46</v>
+        <v>25.57</v>
       </c>
       <c r="M5">
-        <v>19.74</v>
+        <v>19.75</v>
       </c>
       <c r="N5">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1790.34</v>
+        <v>1799.74</v>
       </c>
       <c r="Q5">
-        <v>1727.07</v>
+        <v>1731.76</v>
       </c>
       <c r="R5">
-        <v>1728.4</v>
+        <v>1727.52</v>
       </c>
       <c r="S5">
-        <v>1617.78</v>
+        <v>1619.19</v>
       </c>
       <c r="T5">
-        <v>11.71</v>
+        <v>10.26</v>
       </c>
       <c r="U5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="V5" t="s">
         <v>48</v>
       </c>
       <c r="W5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>60.31</v>
+        <v>56.58</v>
       </c>
       <c r="Z5">
-        <v>22.77</v>
+        <v>22.95</v>
       </c>
       <c r="AA5">
-        <v>11.38</v>
+        <v>13.7</v>
       </c>
       <c r="AB5">
-        <v>11.39</v>
+        <v>9.25</v>
       </c>
       <c r="AC5">
-        <v>73.28</v>
+        <v>65.59</v>
       </c>
       <c r="AD5">
-        <v>79.40000000000001</v>
+        <v>73.48</v>
       </c>
       <c r="AE5">
-        <v>40.11</v>
+        <v>39.55</v>
       </c>
       <c r="AF5">
-        <v>-52.79</v>
+        <v>-36.81</v>
       </c>
       <c r="AG5">
-        <v>1840.37</v>
+        <v>1846.61</v>
       </c>
       <c r="AH5">
-        <v>1613.76</v>
+        <v>1616.9</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1371,7 +1365,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>31.51</v>
+        <v>31.78</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1376,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>204.8</v>
+        <v>199.48</v>
       </c>
       <c r="D6">
-        <v>-1.04</v>
+        <v>-2.6</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1388,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-17.72</v>
+        <v>-19.86</v>
       </c>
       <c r="H6">
-        <v>54.03</v>
+        <v>50.03</v>
       </c>
       <c r="I6">
-        <v>1.22</v>
+        <v>-3.13</v>
       </c>
       <c r="J6">
-        <v>0.54</v>
+        <v>-3.32</v>
       </c>
       <c r="K6">
-        <v>-10.86</v>
+        <v>-12.99</v>
       </c>
       <c r="L6">
-        <v>62.19</v>
+        <v>40.6</v>
       </c>
       <c r="M6">
-        <v>60.21</v>
+        <v>59.77</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O6">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>206.17</v>
+        <v>204.88</v>
       </c>
       <c r="Q6">
-        <v>207.34</v>
+        <v>206.95</v>
       </c>
       <c r="R6">
-        <v>209.05</v>
+        <v>208.66</v>
       </c>
       <c r="S6">
-        <v>186.38</v>
+        <v>186.66</v>
       </c>
       <c r="T6">
-        <v>9.880000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,43 +1442,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>46.15</v>
+        <v>40.1</v>
       </c>
       <c r="Z6">
-        <v>-0.9</v>
+        <v>-1.39</v>
       </c>
       <c r="AA6">
-        <v>-0.88</v>
+        <v>-0.98</v>
       </c>
       <c r="AB6">
-        <v>-0.02</v>
+        <v>-0.41</v>
       </c>
       <c r="AC6">
-        <v>34.52</v>
+        <v>21.7</v>
       </c>
       <c r="AD6">
-        <v>43.4</v>
+        <v>34.07</v>
       </c>
       <c r="AE6">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="AF6">
-        <v>-2.05</v>
+        <v>-4.36</v>
       </c>
       <c r="AG6">
-        <v>216.03</v>
+        <v>216.33</v>
       </c>
       <c r="AH6">
-        <v>198.65</v>
+        <v>197.58</v>
       </c>
       <c r="AI6">
-        <v>217.63</v>
+        <v>217.62</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>14.8</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1489,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>392.75</v>
+        <v>384.1</v>
       </c>
       <c r="D7">
-        <v>1.51</v>
+        <v>-2.2</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1507,46 +1501,46 @@
         <v>381.05</v>
       </c>
       <c r="G7">
-        <v>-33.28</v>
+        <v>-34.75</v>
       </c>
       <c r="H7">
-        <v>3.07</v>
+        <v>0.8</v>
       </c>
       <c r="I7">
-        <v>3.07</v>
+        <v>0.22</v>
       </c>
       <c r="J7">
-        <v>-3.91</v>
+        <v>-7.02</v>
       </c>
       <c r="K7">
-        <v>-7.99</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="L7">
-        <v>-32.07</v>
+        <v>-33.73</v>
       </c>
       <c r="M7">
-        <v>-0.55</v>
+        <v>-0.57</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P7">
-        <v>388.39</v>
+        <v>388.56</v>
       </c>
       <c r="Q7">
-        <v>397.22</v>
+        <v>395.47</v>
       </c>
       <c r="R7">
-        <v>415.19</v>
+        <v>414.16</v>
       </c>
       <c r="S7">
-        <v>459.3</v>
+        <v>458.57</v>
       </c>
       <c r="T7">
-        <v>-14.49</v>
+        <v>-16.24</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1555,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.48</v>
+        <v>36.25</v>
       </c>
       <c r="Z7">
-        <v>-7.95</v>
+        <v>-7.98</v>
       </c>
       <c r="AA7">
-        <v>-8.35</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AB7">
-        <v>0.41</v>
+        <v>0.3</v>
       </c>
       <c r="AC7">
-        <v>85.56</v>
+        <v>77.44</v>
       </c>
       <c r="AD7">
-        <v>72.67</v>
+        <v>79.22</v>
       </c>
       <c r="AE7">
-        <v>7.87</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AF7">
-        <v>-51.4</v>
+        <v>-33.14</v>
       </c>
       <c r="AG7">
-        <v>418.07</v>
+        <v>414.34</v>
       </c>
       <c r="AH7">
-        <v>376.38</v>
+        <v>376.6</v>
       </c>
       <c r="AI7">
         <v>405.74</v>
@@ -1597,7 +1591,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>33.42</v>
+        <v>34.02</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1602,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>625.25</v>
+        <v>612.4</v>
       </c>
       <c r="D8">
-        <v>-0.16</v>
+        <v>-2.06</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1614,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-22.64</v>
+        <v>-24.23</v>
       </c>
       <c r="H8">
-        <v>33.67</v>
+        <v>30.93</v>
       </c>
       <c r="I8">
-        <v>6.61</v>
+        <v>4.33</v>
       </c>
       <c r="J8">
-        <v>-2.24</v>
+        <v>-4.35</v>
       </c>
       <c r="K8">
-        <v>-13.09</v>
+        <v>-14.92</v>
       </c>
       <c r="L8">
-        <v>3.05</v>
+        <v>-5.96</v>
       </c>
       <c r="M8">
-        <v>-14.9</v>
+        <v>-15.25</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="P8">
-        <v>627.52</v>
+        <v>632.6</v>
       </c>
       <c r="Q8">
-        <v>616.45</v>
+        <v>614.88</v>
       </c>
       <c r="R8">
-        <v>645.66</v>
+        <v>643.6</v>
       </c>
       <c r="S8">
-        <v>614.3</v>
+        <v>614.4</v>
       </c>
       <c r="T8">
-        <v>1.78</v>
+        <v>-0.33</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1671,37 +1665,37 @@
         <v>47</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>49.57</v>
+        <v>45.56</v>
       </c>
       <c r="Z8">
-        <v>-7.08</v>
+        <v>-7.06</v>
       </c>
       <c r="AA8">
-        <v>-12.3</v>
+        <v>-11.25</v>
       </c>
       <c r="AB8">
-        <v>5.22</v>
+        <v>4.2</v>
       </c>
       <c r="AC8">
-        <v>72.11</v>
+        <v>65.12</v>
       </c>
       <c r="AD8">
-        <v>75.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="AE8">
-        <v>20.42</v>
+        <v>19.97</v>
       </c>
       <c r="AF8">
-        <v>-63.71</v>
+        <v>-75.87</v>
       </c>
       <c r="AG8">
-        <v>659.04</v>
+        <v>655.51</v>
       </c>
       <c r="AH8">
-        <v>573.85</v>
+        <v>574.25</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1710,7 +1704,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>43.65</v>
+        <v>40.64</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1715,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>186.18</v>
+        <v>184.69</v>
       </c>
       <c r="D9">
-        <v>1.68</v>
+        <v>-0.8</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,25 +1727,25 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.93</v>
+        <v>-33.47</v>
       </c>
       <c r="H9">
-        <v>8.06</v>
+        <v>7.19</v>
       </c>
       <c r="I9">
-        <v>2.33</v>
+        <v>0.35</v>
       </c>
       <c r="J9">
-        <v>-3.97</v>
+        <v>-7.95</v>
       </c>
       <c r="K9">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="L9">
-        <v>-28.28</v>
+        <v>-28.12</v>
       </c>
       <c r="M9">
-        <v>-7.6</v>
+        <v>-7.75</v>
       </c>
       <c r="N9">
         <v>45</v>
@@ -1760,19 +1754,19 @@
         <v>35</v>
       </c>
       <c r="P9">
-        <v>184.77</v>
+        <v>184.9</v>
       </c>
       <c r="Q9">
-        <v>188.86</v>
+        <v>188</v>
       </c>
       <c r="R9">
-        <v>190.26</v>
+        <v>190.18</v>
       </c>
       <c r="S9">
-        <v>198.68</v>
+        <v>198.34</v>
       </c>
       <c r="T9">
-        <v>-6.29</v>
+        <v>-6.88</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1781,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.34</v>
+        <v>43.83</v>
       </c>
       <c r="Z9">
-        <v>-2.11</v>
+        <v>-2.04</v>
       </c>
       <c r="AA9">
-        <v>-1.79</v>
+        <v>-1.84</v>
       </c>
       <c r="AB9">
-        <v>-0.32</v>
+        <v>-0.21</v>
       </c>
       <c r="AC9">
-        <v>59.8</v>
+        <v>74.44</v>
       </c>
       <c r="AD9">
-        <v>50.33</v>
+        <v>61</v>
       </c>
       <c r="AE9">
-        <v>4.37</v>
+        <v>4.46</v>
       </c>
       <c r="AF9">
-        <v>-55.62</v>
+        <v>17.87</v>
       </c>
       <c r="AG9">
-        <v>200.13</v>
+        <v>197.58</v>
       </c>
       <c r="AH9">
-        <v>177.58</v>
+        <v>178.41</v>
       </c>
       <c r="AI9">
         <v>195.69</v>
@@ -1823,7 +1817,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>28.91</v>
+        <v>27.95</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,7 +1828,7 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>71.11</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="D10">
         <v>-1.66</v>
@@ -1846,46 +1840,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-45.63</v>
+        <v>-46.54</v>
       </c>
       <c r="H10">
-        <v>19.96</v>
+        <v>17.97</v>
       </c>
       <c r="I10">
-        <v>1.96</v>
+        <v>-1.56</v>
       </c>
       <c r="J10">
-        <v>-5.36</v>
+        <v>-6.47</v>
       </c>
       <c r="K10">
-        <v>-12.34</v>
+        <v>-13.75</v>
       </c>
       <c r="L10">
-        <v>-42.44</v>
+        <v>-46.08</v>
       </c>
       <c r="M10">
-        <v>-6.84</v>
+        <v>-6.2</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>71.55</v>
+        <v>71.33</v>
       </c>
       <c r="Q10">
-        <v>72.18000000000001</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="R10">
-        <v>75.03</v>
+        <v>74.8</v>
       </c>
       <c r="S10">
-        <v>80.16</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="T10">
-        <v>-11.29</v>
+        <v>-12.69</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1894,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>41.66</v>
+        <v>37.73</v>
       </c>
       <c r="Z10">
-        <v>-1.1</v>
+        <v>-1.17</v>
       </c>
       <c r="AA10">
-        <v>-1.23</v>
+        <v>-1.22</v>
       </c>
       <c r="AB10">
-        <v>0.13</v>
+        <v>0.05</v>
       </c>
       <c r="AC10">
-        <v>81.52</v>
+        <v>66.25</v>
       </c>
       <c r="AD10">
-        <v>79.81999999999999</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="AE10">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="AF10">
-        <v>88.98</v>
+        <v>-17.6</v>
       </c>
       <c r="AG10">
-        <v>74.93000000000001</v>
+        <v>74.69</v>
       </c>
       <c r="AH10">
-        <v>69.42</v>
+        <v>69.23</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1936,7 +1930,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>23.57</v>
+        <v>23.46</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2071,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,1278 +2111,1332 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-5.29</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-3.81</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1.48</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>0</v>
+        <v>-3.81</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.18</v>
+        <v>-5.34</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.21</v>
+        <v>-0.18</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.54</v>
+        <v>-6.75</v>
       </c>
       <c r="E9" s="7">
-        <v>0.67</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>5.59</v>
+        <v>-0.54</v>
       </c>
       <c r="D10" s="6">
-        <v>8.09</v>
+        <v>-3.75</v>
       </c>
       <c r="E10" s="7">
-        <v>2.5</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>0.71</v>
+        <v>8.09</v>
       </c>
       <c r="D11" s="6">
-        <v>0.54</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.17</v>
+        <v>4.85</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.66</v>
+        <v>0.54</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.91</v>
+        <v>-3.32</v>
       </c>
       <c r="E12" s="7">
-        <v>2.75</v>
+        <v>-3.86</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-3.07</v>
+        <v>-3.91</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.24</v>
+        <v>-7.02</v>
       </c>
       <c r="E13" s="7">
-        <v>0.83</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.67</v>
+        <v>-2.24</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.97</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.3</v>
+        <v>-4.35</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.21</v>
+        <v>-3.97</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.36</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.15</v>
+        <v>-7.95</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-3.98</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>1.06</v>
+        <v>-5.36</v>
       </c>
       <c r="D16" s="6">
-        <v>2.02</v>
+        <v>-6.47</v>
       </c>
       <c r="E16" s="7">
-        <v>0.96</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="D17" s="6">
-        <v>2.51</v>
+        <v>0.29</v>
       </c>
       <c r="E17" s="7">
-        <v>0.17</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>3.9</v>
+        <v>2.51</v>
       </c>
       <c r="D18" s="6">
-        <v>2.42</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.48</v>
+        <v>-0.79</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>4.74</v>
+        <v>2.42</v>
       </c>
       <c r="D19" s="6">
-        <v>4.84</v>
+        <v>0.46</v>
       </c>
       <c r="E19" s="7">
-        <v>0.1</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>2.46</v>
+        <v>4.84</v>
       </c>
       <c r="D20" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.24</v>
+        <v>2.7</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="D21" s="6">
-        <v>3.07</v>
+        <v>-3.13</v>
       </c>
       <c r="E21" s="7">
-        <v>1.72</v>
+        <v>-4.35</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>7.95</v>
+        <v>3.07</v>
       </c>
       <c r="D22" s="6">
-        <v>6.61</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.34</v>
+        <v>0.22</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-0.02</v>
+        <v>6.61</v>
       </c>
       <c r="D23" s="6">
-        <v>2.33</v>
+        <v>4.33</v>
       </c>
       <c r="E23" s="7">
-        <v>2.35</v>
+        <v>-2.28</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="D24" s="6">
-        <v>1.96</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.71</v>
+        <v>0.35</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-32.9</v>
+        <v>1.96</v>
       </c>
       <c r="D25" s="6">
-        <v>-32.26</v>
+        <v>-1.56</v>
       </c>
       <c r="E25" s="7">
-        <v>0.64</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>24.83</v>
+        <v>-32.26</v>
       </c>
       <c r="D26" s="6">
-        <v>24.67</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.16</v>
+        <v>-33.84</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>33.14</v>
+        <v>24.67</v>
       </c>
       <c r="D27" s="6">
-        <v>32.89</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.25</v>
+        <v>14.95</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-9.720000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>28.2</v>
+        <v>32.89</v>
       </c>
       <c r="D28" s="6">
-        <v>28.46</v>
+        <v>24.2</v>
       </c>
       <c r="E28" s="7">
-        <v>0.26</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>64.12</v>
+        <v>28.46</v>
       </c>
       <c r="D29" s="6">
-        <v>62.19</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.93</v>
+        <v>25.57</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.89</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-33.2</v>
+        <v>62.19</v>
       </c>
       <c r="D30" s="6">
-        <v>-32.07</v>
+        <v>40.6</v>
       </c>
       <c r="E30" s="7">
-        <v>1.13</v>
+        <v>-21.59</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>3.2</v>
+        <v>-32.07</v>
       </c>
       <c r="D31" s="6">
-        <v>3.05</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.15</v>
+        <v>-33.73</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-29.39</v>
+        <v>3.05</v>
       </c>
       <c r="D32" s="6">
-        <v>-28.28</v>
+        <v>-5.96</v>
       </c>
       <c r="E32" s="7">
-        <v>1.11</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-42.54</v>
+        <v>-28.28</v>
       </c>
       <c r="D33" s="6">
-        <v>-42.44</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.1</v>
+        <v>-28.12</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.16</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-6.86</v>
+        <v>-42.44</v>
       </c>
       <c r="D34" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.24</v>
+        <v>-46.08</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.64</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>1.15</v>
+        <v>-7.1</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.49</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-3.64</v>
+        <v>-7.61</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-13.71</v>
+        <v>-2.49</v>
       </c>
       <c r="D36" s="6">
-        <v>-14.72</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.01</v>
+        <v>-4.54</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>0.62</v>
+        <v>-14.72</v>
       </c>
       <c r="D37" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.95</v>
+        <v>-16.12</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-10.56</v>
+        <v>-0.33</v>
       </c>
       <c r="D38" s="6">
-        <v>-10.86</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.3</v>
+        <v>-0.6</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-6.74</v>
+        <v>-10.86</v>
       </c>
       <c r="D39" s="6">
-        <v>-7.99</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.25</v>
+        <v>-12.99</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-12.54</v>
+        <v>-7.99</v>
       </c>
       <c r="D40" s="6">
-        <v>-13.09</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.55</v>
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-0.39</v>
+        <v>-13.09</v>
       </c>
       <c r="D41" s="6">
-        <v>1.69</v>
+        <v>-14.92</v>
       </c>
       <c r="E41" s="7">
-        <v>2.08</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-11.05</v>
+        <v>1.69</v>
       </c>
       <c r="D42" s="6">
-        <v>-12.34</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.29</v>
+        <v>1.46</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-34.92</v>
+        <v>-12.34</v>
       </c>
       <c r="D43" s="6">
-        <v>-34.23</v>
+        <v>-13.75</v>
       </c>
       <c r="E43" s="7">
-        <v>0.6899999999999999</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-6.7</v>
+        <v>-34.23</v>
       </c>
       <c r="D44" s="6">
-        <v>-6.81</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.11</v>
+        <v>-35.03</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-18.73</v>
+        <v>-6.81</v>
       </c>
       <c r="D45" s="6">
-        <v>-18.92</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.19</v>
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-2.91</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-4.68</v>
+        <v>-18.92</v>
       </c>
       <c r="D46" s="6">
-        <v>-4.03</v>
+        <v>-20.22</v>
       </c>
       <c r="E46" s="7">
-        <v>0.65</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-16.85</v>
+        <v>-4.03</v>
       </c>
       <c r="D47" s="6">
-        <v>-17.72</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.87</v>
+        <v>-5.2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-34.28</v>
+        <v>-17.72</v>
       </c>
       <c r="D48" s="6">
-        <v>-33.28</v>
+        <v>-19.86</v>
       </c>
       <c r="E48" s="7">
-        <v>1</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-22.52</v>
+        <v>-33.28</v>
       </c>
       <c r="D49" s="6">
-        <v>-22.64</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.12</v>
+        <v>-34.75</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-34.04</v>
+        <v>-22.64</v>
       </c>
       <c r="D50" s="6">
-        <v>-32.93</v>
+        <v>-24.23</v>
       </c>
       <c r="E50" s="7">
-        <v>1.11</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-44.72</v>
+        <v>-32.93</v>
       </c>
       <c r="D51" s="6">
-        <v>-45.63</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.91</v>
+        <v>-33.47</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>1238.2</v>
+        <v>-45.63</v>
       </c>
       <c r="D52" s="6">
-        <v>1251.4</v>
+        <v>-46.54</v>
       </c>
       <c r="E52" s="7">
-        <v>13.2</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2997</v>
+        <v>1251.4</v>
       </c>
       <c r="D53" s="6">
-        <v>2993.2</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-3.8</v>
+        <v>1236.1</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-15.3</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1304</v>
+        <v>2993.2</v>
       </c>
       <c r="D54" s="6">
-        <v>1300.9</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-3.1</v>
+        <v>2900</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-93.2</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1795</v>
+        <v>1300.9</v>
       </c>
       <c r="D55" s="6">
-        <v>1807.3</v>
+        <v>1280.1</v>
       </c>
       <c r="E55" s="7">
-        <v>12.3</v>
+        <v>-20.8</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>206.96</v>
+        <v>1807.3</v>
       </c>
       <c r="D56" s="6">
-        <v>204.8</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-2.16</v>
+        <v>1785.3</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-22</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>386.9</v>
+        <v>204.8</v>
       </c>
       <c r="D57" s="6">
-        <v>392.75</v>
+        <v>199.48</v>
       </c>
       <c r="E57" s="7">
-        <v>5.85</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>626.25</v>
+        <v>392.75</v>
       </c>
       <c r="D58" s="6">
-        <v>625.25</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-1</v>
+        <v>384.1</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-8.65</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>183.1</v>
+        <v>625.25</v>
       </c>
       <c r="D59" s="6">
-        <v>186.18</v>
+        <v>612.4</v>
       </c>
       <c r="E59" s="7">
-        <v>3.08</v>
+        <v>-12.85</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>72.31</v>
+        <v>186.18</v>
       </c>
       <c r="D60" s="6">
-        <v>71.11</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.2</v>
+        <v>184.69</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>37.19</v>
+        <v>71.11</v>
       </c>
       <c r="D61" s="6">
-        <v>42.31</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="E61" s="7">
-        <v>5.12</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>50.12</v>
+        <v>88</v>
       </c>
       <c r="D62" s="6">
-        <v>49.79</v>
+        <v>99</v>
       </c>
       <c r="E62" s="8">
-        <v>-0.33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>48.86</v>
+        <v>99</v>
       </c>
       <c r="D63" s="6">
-        <v>48.34</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-0.52</v>
+        <v>88</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>58.91</v>
+        <v>42.31</v>
       </c>
       <c r="D64" s="6">
-        <v>60.31</v>
+        <v>38.4</v>
       </c>
       <c r="E64" s="7">
-        <v>1.4</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>48.93</v>
+        <v>49.79</v>
       </c>
       <c r="D65" s="6">
-        <v>46.15</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-2.78</v>
+        <v>42.39</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-7.4</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>35.52</v>
+        <v>48.34</v>
       </c>
       <c r="D66" s="6">
-        <v>42.48</v>
+        <v>44.9</v>
       </c>
       <c r="E66" s="7">
-        <v>6.96</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>49.89</v>
+        <v>60.31</v>
       </c>
       <c r="D67" s="6">
-        <v>49.57</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-0.32</v>
+        <v>56.58</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-3.73</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>39.69</v>
+        <v>46.15</v>
       </c>
       <c r="D68" s="6">
-        <v>46.34</v>
+        <v>40.1</v>
       </c>
       <c r="E68" s="7">
-        <v>6.65</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>46.21</v>
+        <v>42.48</v>
       </c>
       <c r="D69" s="6">
-        <v>41.66</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-4.55</v>
+        <v>36.25</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-6.23</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>-37.23</v>
+        <v>49.57</v>
       </c>
       <c r="D70" s="6">
-        <v>-57.63</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-20.4</v>
+        <v>45.56</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-4.01</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>-62.52</v>
+        <v>46.34</v>
       </c>
       <c r="D71" s="6">
-        <v>-59.58</v>
+        <v>43.83</v>
       </c>
       <c r="E71" s="7">
-        <v>2.94</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>-70.52</v>
+        <v>41.66</v>
       </c>
       <c r="D72" s="6">
-        <v>-55.87</v>
+        <v>37.73</v>
       </c>
       <c r="E72" s="7">
-        <v>14.65</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-65.42</v>
+        <v>-57.63</v>
       </c>
       <c r="D73" s="6">
-        <v>-52.79</v>
-      </c>
-      <c r="E73" s="7">
-        <v>12.63</v>
+        <v>-27.56</v>
+      </c>
+      <c r="E73" s="8">
+        <v>30.07</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-42.61</v>
+        <v>-59.58</v>
       </c>
       <c r="D74" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="E74" s="7">
-        <v>40.56</v>
+        <v>-48.91</v>
+      </c>
+      <c r="E74" s="8">
+        <v>10.67</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-29.66</v>
+        <v>-55.87</v>
       </c>
       <c r="D75" s="6">
-        <v>-51.4</v>
+        <v>64.47</v>
       </c>
       <c r="E75" s="8">
-        <v>-21.74</v>
+        <v>120.34</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-52.98</v>
+        <v>-52.79</v>
       </c>
       <c r="D76" s="6">
-        <v>-63.71</v>
+        <v>-36.81</v>
       </c>
       <c r="E76" s="8">
-        <v>-10.73</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-64.76000000000001</v>
+        <v>-2.05</v>
       </c>
       <c r="D77" s="6">
-        <v>-55.62</v>
+        <v>-4.36</v>
       </c>
       <c r="E77" s="7">
-        <v>9.140000000000001</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-45.28</v>
+        <v>-51.4</v>
       </c>
       <c r="D78" s="6">
+        <v>-33.14</v>
+      </c>
+      <c r="E78" s="8">
+        <v>18.26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-63.71</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-75.87</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-12.16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-55.62</v>
+      </c>
+      <c r="D80" s="6">
+        <v>17.87</v>
+      </c>
+      <c r="E80" s="8">
+        <v>73.48999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
         <v>88.98</v>
       </c>
-      <c r="E78" s="7">
-        <v>134.26</v>
+      <c r="D81" s="6">
+        <v>-17.6</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-106.58</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3412,28 +3460,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3441,28 +3489,28 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>56.16</v>
+        <v>48.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>47.4</v>
+        <v>42.9</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-1.3</v>
+        <v>-4.5</v>
       </c>
       <c r="G2" s="11">
-        <v>-7.5</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
       </c>
       <c r="I2" s="11">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3593,31 +3641,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.6021</v>
+        <v>0.5977</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1974</v>
+        <v>0.1975</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1527</v>
+        <v>0.1474</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0251</v>
+        <v>0.0214</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.005500000000000001</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0684</v>
+        <v>-0.062</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.076</v>
+        <v>-0.0775</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1105</v>
+        <v>-0.1087</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.149</v>
+        <v>-0.1525</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,28 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,18 +380,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -924,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1236.1</v>
+        <v>1236.4</v>
       </c>
       <c r="D2">
-        <v>-1.22</v>
+        <v>0.02</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -936,46 +914,46 @@
         <v>1225.2</v>
       </c>
       <c r="G2">
-        <v>-35.03</v>
+        <v>-35.02</v>
       </c>
       <c r="H2">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="I2">
-        <v>0.29</v>
+        <v>-1.85</v>
       </c>
       <c r="J2">
-        <v>-5.34</v>
+        <v>-7.16</v>
       </c>
       <c r="K2">
-        <v>-7.61</v>
+        <v>-7.27</v>
       </c>
       <c r="L2">
-        <v>-33.84</v>
+        <v>-33.93</v>
       </c>
       <c r="M2">
-        <v>-10.87</v>
+        <v>-11.13</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P2">
-        <v>1248.34</v>
+        <v>1243.68</v>
       </c>
       <c r="Q2">
-        <v>1260.21</v>
+        <v>1256.5</v>
       </c>
       <c r="R2">
-        <v>1311.86</v>
+        <v>1309.12</v>
       </c>
       <c r="S2">
-        <v>1453.47</v>
+        <v>1450.72</v>
       </c>
       <c r="T2">
-        <v>-14.96</v>
+        <v>-14.77</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -990,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.4</v>
+        <v>38.52</v>
       </c>
       <c r="Z2">
-        <v>-20.19</v>
+        <v>-19.8</v>
       </c>
       <c r="AA2">
-        <v>-21.83</v>
+        <v>-21.43</v>
       </c>
       <c r="AB2">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC2">
-        <v>76.47</v>
+        <v>79.39</v>
       </c>
       <c r="AD2">
-        <v>82.04000000000001</v>
+        <v>80.02</v>
       </c>
       <c r="AE2">
-        <v>23.54</v>
+        <v>22.53</v>
       </c>
       <c r="AF2">
-        <v>-27.56</v>
+        <v>-63.6</v>
       </c>
       <c r="AG2">
-        <v>1307.03</v>
+        <v>1297.96</v>
       </c>
       <c r="AH2">
-        <v>1213.39</v>
+        <v>1215.04</v>
       </c>
       <c r="AI2">
         <v>1296.94</v>
@@ -1026,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>21.13</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2900</v>
+        <v>2916.5</v>
       </c>
       <c r="D3">
-        <v>-3.11</v>
+        <v>0.57</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1049,46 +1027,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-9.720000000000001</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H3">
-        <v>64.95999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I3">
-        <v>-0.79</v>
+        <v>-3.43</v>
       </c>
       <c r="J3">
-        <v>-6.75</v>
+        <v>-6.28</v>
       </c>
       <c r="K3">
-        <v>-4.54</v>
+        <v>-1.55</v>
       </c>
       <c r="L3">
-        <v>14.95</v>
+        <v>10.96</v>
       </c>
       <c r="M3">
-        <v>14.74</v>
+        <v>13.82</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P3">
-        <v>2977.04</v>
+        <v>2956.34</v>
       </c>
       <c r="Q3">
-        <v>2979.67</v>
+        <v>2967.04</v>
       </c>
       <c r="R3">
-        <v>3019.91</v>
+        <v>3015.21</v>
       </c>
       <c r="S3">
-        <v>2555.59</v>
+        <v>2559.1</v>
       </c>
       <c r="T3">
-        <v>13.48</v>
+        <v>13.97</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1103,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>42.39</v>
+        <v>43.98</v>
       </c>
       <c r="Z3">
-        <v>-15.29</v>
+        <v>-18.62</v>
       </c>
       <c r="AA3">
-        <v>-12.72</v>
+        <v>-13.9</v>
       </c>
       <c r="AB3">
-        <v>-2.56</v>
+        <v>-4.72</v>
       </c>
       <c r="AC3">
-        <v>36.5</v>
+        <v>20.81</v>
       </c>
       <c r="AD3">
-        <v>50.58</v>
+        <v>37.3</v>
       </c>
       <c r="AE3">
-        <v>78.06999999999999</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="AF3">
-        <v>-48.91</v>
+        <v>-72.47</v>
       </c>
       <c r="AG3">
-        <v>3166.67</v>
+        <v>3133.15</v>
       </c>
       <c r="AH3">
-        <v>2792.66</v>
+        <v>2800.93</v>
       </c>
       <c r="AI3">
         <v>3113.12</v>
@@ -1139,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>19.87</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1280.1</v>
+        <v>1296.6</v>
       </c>
       <c r="D4">
-        <v>-1.6</v>
+        <v>1.29</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1162,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-20.22</v>
+        <v>-19.19</v>
       </c>
       <c r="H4">
-        <v>65.64</v>
+        <v>67.78</v>
       </c>
       <c r="I4">
-        <v>0.46</v>
+        <v>-2.84</v>
       </c>
       <c r="J4">
-        <v>-3.75</v>
+        <v>-0.51</v>
       </c>
       <c r="K4">
-        <v>-16.12</v>
+        <v>-13.7</v>
       </c>
       <c r="L4">
-        <v>24.2</v>
+        <v>12.54</v>
       </c>
       <c r="M4">
-        <v>2.14</v>
+        <v>2.37</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="P4">
-        <v>1304.62</v>
+        <v>1297.04</v>
       </c>
       <c r="Q4">
-        <v>1289.9</v>
+        <v>1288.3</v>
       </c>
       <c r="R4">
-        <v>1343.92</v>
+        <v>1338.98</v>
       </c>
       <c r="S4">
-        <v>1193.74</v>
+        <v>1195.25</v>
       </c>
       <c r="T4">
-        <v>7.23</v>
+        <v>8.48</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1216,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>44.9</v>
+        <v>48.06</v>
       </c>
       <c r="Z4">
-        <v>-12.47</v>
+        <v>-11.34</v>
       </c>
       <c r="AA4">
-        <v>-17.7</v>
+        <v>-16.43</v>
       </c>
       <c r="AB4">
-        <v>5.24</v>
+        <v>5.09</v>
       </c>
       <c r="AC4">
-        <v>55.17</v>
+        <v>53.3</v>
       </c>
       <c r="AD4">
-        <v>65.81999999999999</v>
+        <v>57.76</v>
       </c>
       <c r="AE4">
-        <v>36.4</v>
+        <v>35.9</v>
       </c>
       <c r="AF4">
-        <v>64.47</v>
+        <v>-32.71</v>
       </c>
       <c r="AG4">
-        <v>1343.47</v>
+        <v>1338.85</v>
       </c>
       <c r="AH4">
-        <v>1236.33</v>
+        <v>1237.76</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1252,7 +1230,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>18.04</v>
+        <v>16.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1785.3</v>
+        <v>1788</v>
       </c>
       <c r="D5">
-        <v>-1.22</v>
+        <v>0.15</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1275,25 +1253,25 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-5.2</v>
+        <v>-5.06</v>
       </c>
       <c r="H5">
-        <v>37.53</v>
+        <v>37.74</v>
       </c>
       <c r="I5">
-        <v>2.7</v>
+        <v>-1.97</v>
       </c>
       <c r="J5">
-        <v>4.85</v>
+        <v>5.7</v>
       </c>
       <c r="K5">
-        <v>-0.6</v>
+        <v>0.67</v>
       </c>
       <c r="L5">
-        <v>25.57</v>
+        <v>24.33</v>
       </c>
       <c r="M5">
-        <v>19.75</v>
+        <v>19.64</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1302,19 +1280,19 @@
         <v>74</v>
       </c>
       <c r="P5">
-        <v>1799.74</v>
+        <v>1792.54</v>
       </c>
       <c r="Q5">
-        <v>1731.76</v>
+        <v>1735.46</v>
       </c>
       <c r="R5">
-        <v>1727.52</v>
+        <v>1726.75</v>
       </c>
       <c r="S5">
-        <v>1619.19</v>
+        <v>1620.76</v>
       </c>
       <c r="T5">
-        <v>10.26</v>
+        <v>10.32</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1329,34 +1307,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>56.58</v>
+        <v>56.93</v>
       </c>
       <c r="Z5">
-        <v>22.95</v>
+        <v>23.05</v>
       </c>
       <c r="AA5">
-        <v>13.7</v>
+        <v>15.57</v>
       </c>
       <c r="AB5">
-        <v>9.25</v>
+        <v>7.48</v>
       </c>
       <c r="AC5">
-        <v>65.59</v>
+        <v>59.16</v>
       </c>
       <c r="AD5">
-        <v>73.48</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="AE5">
-        <v>39.55</v>
+        <v>38.55</v>
       </c>
       <c r="AF5">
-        <v>-36.81</v>
+        <v>-64.61</v>
       </c>
       <c r="AG5">
-        <v>1846.61</v>
+        <v>1852.65</v>
       </c>
       <c r="AH5">
-        <v>1616.9</v>
+        <v>1618.26</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1365,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>31.78</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>199.48</v>
+        <v>202.75</v>
       </c>
       <c r="D6">
-        <v>-2.6</v>
+        <v>1.64</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1388,46 +1366,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-19.86</v>
+        <v>-18.54</v>
       </c>
       <c r="H6">
-        <v>50.03</v>
+        <v>52.49</v>
       </c>
       <c r="I6">
-        <v>-3.13</v>
+        <v>-1.86</v>
       </c>
       <c r="J6">
-        <v>-3.32</v>
+        <v>-2.15</v>
       </c>
       <c r="K6">
-        <v>-12.99</v>
+        <v>-10.7</v>
       </c>
       <c r="L6">
-        <v>40.6</v>
+        <v>19.09</v>
       </c>
       <c r="M6">
-        <v>59.77</v>
+        <v>59.99</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="P6">
-        <v>204.88</v>
+        <v>204.11</v>
       </c>
       <c r="Q6">
-        <v>206.95</v>
+        <v>206.34</v>
       </c>
       <c r="R6">
-        <v>208.66</v>
+        <v>208.38</v>
       </c>
       <c r="S6">
-        <v>186.66</v>
+        <v>186.98</v>
       </c>
       <c r="T6">
-        <v>6.87</v>
+        <v>8.43</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1442,43 +1420,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>40.1</v>
+        <v>44.88</v>
       </c>
       <c r="Z6">
-        <v>-1.39</v>
+        <v>-1.51</v>
       </c>
       <c r="AA6">
-        <v>-0.98</v>
+        <v>-1.09</v>
       </c>
       <c r="AB6">
-        <v>-0.41</v>
+        <v>-0.42</v>
       </c>
       <c r="AC6">
-        <v>21.7</v>
+        <v>16.94</v>
       </c>
       <c r="AD6">
-        <v>34.07</v>
+        <v>24.38</v>
       </c>
       <c r="AE6">
-        <v>5.44</v>
+        <v>5.59</v>
       </c>
       <c r="AF6">
-        <v>-4.36</v>
+        <v>-24.76</v>
       </c>
       <c r="AG6">
-        <v>216.33</v>
+        <v>215.08</v>
       </c>
       <c r="AH6">
-        <v>197.58</v>
+        <v>197.6</v>
       </c>
       <c r="AI6">
-        <v>217.62</v>
+        <v>216.61</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>17.52</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>384.1</v>
+        <v>383.8</v>
       </c>
       <c r="D7">
-        <v>-2.2</v>
+        <v>-0.08</v>
       </c>
       <c r="E7">
         <v>588.6900000000001</v>
@@ -1501,25 +1479,25 @@
         <v>381.05</v>
       </c>
       <c r="G7">
-        <v>-34.75</v>
+        <v>-34.8</v>
       </c>
       <c r="H7">
-        <v>0.8</v>
+        <v>0.72</v>
       </c>
       <c r="I7">
-        <v>0.22</v>
+        <v>-1.16</v>
       </c>
       <c r="J7">
-        <v>-7.02</v>
+        <v>-8.44</v>
       </c>
       <c r="K7">
-        <v>-9.359999999999999</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L7">
-        <v>-33.73</v>
+        <v>-34.66</v>
       </c>
       <c r="M7">
-        <v>-0.57</v>
+        <v>-0.93</v>
       </c>
       <c r="N7">
         <v>23</v>
@@ -1528,19 +1506,19 @@
         <v>18</v>
       </c>
       <c r="P7">
-        <v>388.56</v>
+        <v>387.66</v>
       </c>
       <c r="Q7">
-        <v>395.47</v>
+        <v>394.1</v>
       </c>
       <c r="R7">
-        <v>414.16</v>
+        <v>413.17</v>
       </c>
       <c r="S7">
-        <v>458.57</v>
+        <v>457.85</v>
       </c>
       <c r="T7">
-        <v>-16.24</v>
+        <v>-16.17</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1555,34 +1533,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>36.25</v>
+        <v>36.05</v>
       </c>
       <c r="Z7">
-        <v>-7.98</v>
+        <v>-7.94</v>
       </c>
       <c r="AA7">
-        <v>-8.279999999999999</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="AB7">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AC7">
-        <v>77.44</v>
+        <v>75.33</v>
       </c>
       <c r="AD7">
-        <v>79.22</v>
+        <v>79.44</v>
       </c>
       <c r="AE7">
-        <v>8.029999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="AF7">
-        <v>-33.14</v>
+        <v>-11.77</v>
       </c>
       <c r="AG7">
-        <v>414.34</v>
+        <v>412.16</v>
       </c>
       <c r="AH7">
-        <v>376.6</v>
+        <v>376.05</v>
       </c>
       <c r="AI7">
         <v>405.74</v>
@@ -1591,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>34.02</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>612.4</v>
+        <v>611.65</v>
       </c>
       <c r="D8">
-        <v>-2.06</v>
+        <v>-0.12</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1614,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-24.23</v>
+        <v>-24.33</v>
       </c>
       <c r="H8">
-        <v>30.93</v>
+        <v>30.77</v>
       </c>
       <c r="I8">
-        <v>4.33</v>
+        <v>-7.42</v>
       </c>
       <c r="J8">
-        <v>-4.35</v>
+        <v>-4.98</v>
       </c>
       <c r="K8">
-        <v>-14.92</v>
+        <v>-16.4</v>
       </c>
       <c r="L8">
-        <v>-5.96</v>
+        <v>-21.63</v>
       </c>
       <c r="M8">
-        <v>-15.25</v>
+        <v>-15.48</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O8">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>632.6</v>
+        <v>622.79</v>
       </c>
       <c r="Q8">
-        <v>614.88</v>
+        <v>613.2</v>
       </c>
       <c r="R8">
-        <v>643.6</v>
+        <v>641.6799999999999</v>
       </c>
       <c r="S8">
-        <v>614.4</v>
+        <v>614.5700000000001</v>
       </c>
       <c r="T8">
-        <v>-0.33</v>
+        <v>-0.48</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1668,34 +1646,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>45.56</v>
+        <v>45.33</v>
       </c>
       <c r="Z8">
-        <v>-7.06</v>
+        <v>-7.02</v>
       </c>
       <c r="AA8">
-        <v>-11.25</v>
+        <v>-10.4</v>
       </c>
       <c r="AB8">
-        <v>4.2</v>
+        <v>3.39</v>
       </c>
       <c r="AC8">
-        <v>65.12</v>
+        <v>61.24</v>
       </c>
       <c r="AD8">
-        <v>73.3</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="AE8">
-        <v>19.97</v>
+        <v>19.25</v>
       </c>
       <c r="AF8">
-        <v>-75.87</v>
+        <v>-79.2</v>
       </c>
       <c r="AG8">
-        <v>655.51</v>
+        <v>651.22</v>
       </c>
       <c r="AH8">
-        <v>574.25</v>
+        <v>575.17</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1704,7 +1682,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>40.64</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1715,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>184.69</v>
+        <v>184.34</v>
       </c>
       <c r="D9">
-        <v>-0.8</v>
+        <v>-0.19</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1727,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.47</v>
+        <v>-33.6</v>
       </c>
       <c r="H9">
-        <v>7.19</v>
+        <v>6.99</v>
       </c>
       <c r="I9">
-        <v>0.35</v>
+        <v>-1.41</v>
       </c>
       <c r="J9">
-        <v>-7.95</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K9">
-        <v>1.46</v>
+        <v>0.91</v>
       </c>
       <c r="L9">
-        <v>-28.12</v>
+        <v>-32</v>
       </c>
       <c r="M9">
-        <v>-7.75</v>
+        <v>-7.79</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P9">
-        <v>184.9</v>
+        <v>184.37</v>
       </c>
       <c r="Q9">
-        <v>188</v>
+        <v>187.23</v>
       </c>
       <c r="R9">
-        <v>190.18</v>
+        <v>190.07</v>
       </c>
       <c r="S9">
-        <v>198.34</v>
+        <v>198.01</v>
       </c>
       <c r="T9">
-        <v>-6.88</v>
+        <v>-6.9</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1781,34 +1759,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>43.83</v>
+        <v>43.23</v>
       </c>
       <c r="Z9">
-        <v>-2.04</v>
+        <v>-2</v>
       </c>
       <c r="AA9">
-        <v>-1.84</v>
+        <v>-1.87</v>
       </c>
       <c r="AB9">
-        <v>-0.21</v>
+        <v>-0.13</v>
       </c>
       <c r="AC9">
-        <v>74.44</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="AD9">
-        <v>61</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="AE9">
-        <v>4.46</v>
+        <v>4.39</v>
       </c>
       <c r="AF9">
-        <v>17.87</v>
+        <v>-29.88</v>
       </c>
       <c r="AG9">
-        <v>197.58</v>
+        <v>195.17</v>
       </c>
       <c r="AH9">
-        <v>178.41</v>
+        <v>179.28</v>
       </c>
       <c r="AI9">
         <v>195.69</v>
@@ -1817,7 +1795,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>27.95</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1828,37 +1806,37 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>69.93000000000001</v>
+        <v>70.08</v>
       </c>
       <c r="D10">
-        <v>-1.66</v>
+        <v>0.21</v>
       </c>
       <c r="E10">
-        <v>130.8</v>
+        <v>126.36</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-46.54</v>
+        <v>-44.54</v>
       </c>
       <c r="H10">
-        <v>17.97</v>
+        <v>18.22</v>
       </c>
       <c r="I10">
-        <v>-1.56</v>
+        <v>-2.29</v>
       </c>
       <c r="J10">
-        <v>-6.47</v>
+        <v>-5.74</v>
       </c>
       <c r="K10">
-        <v>-13.75</v>
+        <v>-12.8</v>
       </c>
       <c r="L10">
-        <v>-46.08</v>
+        <v>-46.42</v>
       </c>
       <c r="M10">
-        <v>-6.2</v>
+        <v>-5.2</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1867,19 +1845,19 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>71.33</v>
+        <v>71</v>
       </c>
       <c r="Q10">
-        <v>71.95999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="R10">
-        <v>74.8</v>
+        <v>74.59</v>
       </c>
       <c r="S10">
-        <v>80.09999999999999</v>
+        <v>80.05</v>
       </c>
       <c r="T10">
-        <v>-12.69</v>
+        <v>-12.46</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1894,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>37.73</v>
+        <v>38.52</v>
       </c>
       <c r="Z10">
-        <v>-1.17</v>
+        <v>-1.2</v>
       </c>
       <c r="AA10">
-        <v>-1.22</v>
+        <v>-1.21</v>
       </c>
       <c r="AB10">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="AC10">
-        <v>66.25</v>
+        <v>48.2</v>
       </c>
       <c r="AD10">
-        <v>77.20999999999999</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="AE10">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AF10">
-        <v>-17.6</v>
+        <v>-64.05</v>
       </c>
       <c r="AG10">
-        <v>74.69</v>
+        <v>74.39</v>
       </c>
       <c r="AH10">
-        <v>69.23</v>
+        <v>69.11</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1930,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>23.46</v>
+        <v>23.36</v>
       </c>
     </row>
   </sheetData>
@@ -2071,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2091,1352 +2069,1297 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-5.34</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.16</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.82</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-6.75</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-6.28</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-3.75</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-0.51</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4.85</v>
+      </c>
+      <c r="D10" s="5">
+        <v>5.7</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.32</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-2.15</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7.02</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-8.44</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-4.35</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-4.98</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-7.95</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-6.47</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.74</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-3.81</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.29</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1.85</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-6.75</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-6.57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-0.79</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-3.43</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-0.54</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-3.21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.84</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>8.09</v>
-      </c>
-      <c r="D11" s="6">
-        <v>4.85</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-3.24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2.7</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-1.97</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-4.67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>0.54</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.32</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-3.13</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-3.91</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-7.02</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-1.16</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.24</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-4.35</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>4.33</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-7.42</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-11.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-3.97</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-7.95</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-1.41</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.36</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.47</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-1.56</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-2.29</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2.02</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.29</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-33.84</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-33.93</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2.51</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.79</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>14.95</v>
+      </c>
+      <c r="D26" s="5">
+        <v>10.96</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>24.2</v>
+      </c>
+      <c r="D27" s="5">
+        <v>12.54</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-11.66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>25.57</v>
+      </c>
+      <c r="D28" s="5">
+        <v>24.33</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>40.6</v>
+      </c>
+      <c r="D29" s="5">
+        <v>19.09</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-21.51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-33.73</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-34.66</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-5.96</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-21.63</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-15.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-28.12</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-32</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-3.88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-46.08</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-46.42</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-7.61</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-7.27</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-4.54</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-1.55</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-16.12</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-13.7</v>
+      </c>
+      <c r="E36" s="7">
         <v>2.42</v>
       </c>
-      <c r="D19" s="6">
-        <v>0.46</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>4.84</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-0.6</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0.67</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-12.99</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-10.7</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-14.92</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-16.4</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1.46</v>
+      </c>
+      <c r="D41" s="5">
+        <v>0.91</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-13.75</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-12.8</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-35.03</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-35.02</v>
+      </c>
+      <c r="E43" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-9.720000000000001</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-20.22</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-19.19</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-5.2</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-5.06</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-19.86</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-18.54</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-34.75</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-34.8</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-24.23</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-24.33</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-33.47</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-33.6</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-46.54</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-44.54</v>
+      </c>
+      <c r="E51" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1236.1</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1236.4</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>2900</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2916.5</v>
+      </c>
+      <c r="E53" s="7">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1280.1</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1296.6</v>
+      </c>
+      <c r="E54" s="7">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1785.3</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1788</v>
+      </c>
+      <c r="E55" s="7">
         <v>2.7</v>
       </c>
-      <c r="E20" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-3.13</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-4.35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>199.48</v>
+      </c>
+      <c r="D56" s="5">
+        <v>202.75</v>
+      </c>
+      <c r="E56" s="7">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>3.07</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>384.1</v>
+      </c>
+      <c r="D57" s="5">
+        <v>383.8</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>6.61</v>
-      </c>
-      <c r="D23" s="6">
-        <v>4.33</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>612.4</v>
+      </c>
+      <c r="D58" s="5">
+        <v>611.65</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>2.33</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>184.69</v>
+      </c>
+      <c r="D59" s="5">
+        <v>184.34</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>69.93000000000001</v>
+      </c>
+      <c r="D60" s="5">
+        <v>70.08</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
+        <v>55</v>
+      </c>
+      <c r="D61" s="5">
+        <v>45</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>45</v>
+      </c>
+      <c r="D62" s="5">
+        <v>55</v>
+      </c>
+      <c r="E62" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>38.4</v>
+      </c>
+      <c r="D63" s="5">
+        <v>38.52</v>
+      </c>
+      <c r="E63" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>42.39</v>
+      </c>
+      <c r="D64" s="5">
+        <v>43.98</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>44.9</v>
+      </c>
+      <c r="D65" s="5">
+        <v>48.06</v>
+      </c>
+      <c r="E65" s="7">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>56.58</v>
+      </c>
+      <c r="D66" s="5">
+        <v>56.93</v>
+      </c>
+      <c r="E66" s="7">
         <v>0.35</v>
       </c>
-      <c r="E24" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>40.1</v>
+      </c>
+      <c r="D67" s="5">
+        <v>44.88</v>
+      </c>
+      <c r="E67" s="7">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>36.25</v>
+      </c>
+      <c r="D68" s="5">
+        <v>36.05</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>45.56</v>
+      </c>
+      <c r="D69" s="5">
+        <v>45.33</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>43.83</v>
+      </c>
+      <c r="D70" s="5">
+        <v>43.23</v>
+      </c>
+      <c r="E70" s="6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>1.96</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="5">
+        <v>37.73</v>
+      </c>
+      <c r="D71" s="5">
+        <v>38.52</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-32.26</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-33.84</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-27.56</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-63.6</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-36.04</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>24.67</v>
-      </c>
-      <c r="D27" s="6">
-        <v>14.95</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-9.720000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-48.91</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-72.47</v>
+      </c>
+      <c r="E73" s="6">
+        <v>-23.56</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>32.89</v>
-      </c>
-      <c r="D28" s="6">
-        <v>24.2</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-8.69</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>64.47</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-32.71</v>
+      </c>
+      <c r="E74" s="6">
+        <v>-97.18000000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>28.46</v>
-      </c>
-      <c r="D29" s="6">
-        <v>25.57</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-36.81</v>
+      </c>
+      <c r="D75" s="5">
+        <v>-64.61</v>
+      </c>
+      <c r="E75" s="6">
+        <v>-27.8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>62.19</v>
-      </c>
-      <c r="D30" s="6">
-        <v>40.6</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-21.59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-4.36</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-24.76</v>
+      </c>
+      <c r="E76" s="6">
+        <v>-20.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-32.07</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-33.73</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-33.14</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-11.77</v>
+      </c>
+      <c r="E77" s="7">
+        <v>21.37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>3.05</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-5.96</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-9.01</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>-75.87</v>
+      </c>
+      <c r="D78" s="5">
+        <v>-79.2</v>
+      </c>
+      <c r="E78" s="6">
+        <v>-3.33</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-28.28</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-28.12</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>17.87</v>
+      </c>
+      <c r="D79" s="5">
+        <v>-29.88</v>
+      </c>
+      <c r="E79" s="6">
+        <v>-47.75</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-42.44</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-46.08</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-2.49</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-4.54</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-14.72</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-16.12</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-0.33</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-0.6</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-10.86</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-12.99</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-7.99</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-13.09</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-14.92</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1.69</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1.46</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-12.34</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-13.75</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-34.23</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-35.03</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-6.81</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-2.91</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-18.92</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-20.22</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-4.03</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-5.2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-17.72</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-19.86</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-33.28</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-34.75</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-22.64</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-24.23</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-32.93</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-33.47</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-45.63</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-46.54</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1251.4</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1236.1</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-15.3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>2993.2</v>
-      </c>
-      <c r="D54" s="6">
-        <v>2900</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-93.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1300.9</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1280.1</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-20.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1807.3</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1785.3</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>204.8</v>
-      </c>
-      <c r="D57" s="6">
-        <v>199.48</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-5.32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>392.75</v>
-      </c>
-      <c r="D58" s="6">
-        <v>384.1</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-8.65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>625.25</v>
-      </c>
-      <c r="D59" s="6">
-        <v>612.4</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-12.85</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>186.18</v>
-      </c>
-      <c r="D60" s="6">
-        <v>184.69</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>71.11</v>
-      </c>
-      <c r="D61" s="6">
-        <v>69.93000000000001</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>88</v>
-      </c>
-      <c r="D62" s="6">
-        <v>99</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>99</v>
-      </c>
-      <c r="D63" s="6">
-        <v>88</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>42.31</v>
-      </c>
-      <c r="D64" s="6">
-        <v>38.4</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-3.91</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>49.79</v>
-      </c>
-      <c r="D65" s="6">
-        <v>42.39</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-7.4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>48.34</v>
-      </c>
-      <c r="D66" s="6">
-        <v>44.9</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>60.31</v>
-      </c>
-      <c r="D67" s="6">
-        <v>56.58</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-3.73</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>46.15</v>
-      </c>
-      <c r="D68" s="6">
-        <v>40.1</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-6.05</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>42.48</v>
-      </c>
-      <c r="D69" s="6">
-        <v>36.25</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-6.23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>49.57</v>
-      </c>
-      <c r="D70" s="6">
-        <v>45.56</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-4.01</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>46.34</v>
-      </c>
-      <c r="D71" s="6">
-        <v>43.83</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>41.66</v>
-      </c>
-      <c r="D72" s="6">
-        <v>37.73</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-3.93</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="B80" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="6">
-        <v>-57.63</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-27.56</v>
-      </c>
-      <c r="E73" s="8">
-        <v>30.07</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-59.58</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-48.91</v>
-      </c>
-      <c r="E74" s="8">
-        <v>10.67</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-55.87</v>
-      </c>
-      <c r="D75" s="6">
-        <v>64.47</v>
-      </c>
-      <c r="E75" s="8">
-        <v>120.34</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-52.79</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-36.81</v>
-      </c>
-      <c r="E76" s="8">
-        <v>15.98</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-4.36</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-51.4</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-33.14</v>
-      </c>
-      <c r="E78" s="8">
-        <v>18.26</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-63.71</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-75.87</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-12.16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-55.62</v>
-      </c>
-      <c r="D80" s="6">
-        <v>17.87</v>
-      </c>
-      <c r="E80" s="8">
-        <v>73.48999999999999</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>88.98</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="C80" s="5">
         <v>-17.6</v>
       </c>
-      <c r="E81" s="7">
-        <v>-106.58</v>
+      <c r="D80" s="5">
+        <v>-64.05</v>
+      </c>
+      <c r="E80" s="6">
+        <v>-46.45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3456,60 +3379,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>42.9</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>43.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-4.5</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-4.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3611,61 +3534,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.5977</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1975</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1474</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0214</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.005699999999999999</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.062</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.0775</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1087</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1525</v>
+      <c r="A2" s="13">
+        <v>0.5999</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1964</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1382</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0237</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.052</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.0779</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.1113</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.1548</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>56.9 → 49.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>56.9</t>
+  </si>
+  <si>
+    <t>49.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,14 +407,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -902,58 +930,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1236.4</v>
+        <v>1213.5</v>
       </c>
       <c r="D2">
-        <v>0.02</v>
+        <v>-1.85</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1225.2</v>
+        <v>1213.5</v>
       </c>
       <c r="G2">
-        <v>-35.02</v>
+        <v>-36.22</v>
       </c>
       <c r="H2">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-1.85</v>
+        <v>-3.41</v>
       </c>
       <c r="J2">
-        <v>-7.16</v>
+        <v>-7.41</v>
       </c>
       <c r="K2">
-        <v>-7.27</v>
+        <v>-8.57</v>
       </c>
       <c r="L2">
-        <v>-33.93</v>
+        <v>-35.03</v>
       </c>
       <c r="M2">
-        <v>-11.13</v>
+        <v>-11.21</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P2">
-        <v>1243.68</v>
+        <v>1235.12</v>
       </c>
       <c r="Q2">
-        <v>1256.5</v>
+        <v>1251.85</v>
       </c>
       <c r="R2">
-        <v>1309.12</v>
+        <v>1305.84</v>
       </c>
       <c r="S2">
-        <v>1450.72</v>
+        <v>1447.91</v>
       </c>
       <c r="T2">
-        <v>-14.77</v>
+        <v>-16.19</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>38.52</v>
+        <v>33.21</v>
       </c>
       <c r="Z2">
-        <v>-19.8</v>
+        <v>-21.09</v>
       </c>
       <c r="AA2">
-        <v>-21.43</v>
+        <v>-21.36</v>
       </c>
       <c r="AB2">
-        <v>1.63</v>
+        <v>0.27</v>
       </c>
       <c r="AC2">
-        <v>79.39</v>
+        <v>59.45</v>
       </c>
       <c r="AD2">
-        <v>80.02</v>
+        <v>71.77</v>
       </c>
       <c r="AE2">
-        <v>22.53</v>
+        <v>22.75</v>
       </c>
       <c r="AF2">
-        <v>-63.6</v>
+        <v>28.43</v>
       </c>
       <c r="AG2">
-        <v>1297.96</v>
+        <v>1290.49</v>
       </c>
       <c r="AH2">
-        <v>1215.04</v>
+        <v>1213.22</v>
       </c>
       <c r="AI2">
-        <v>1296.94</v>
+        <v>1291.84</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>18.4</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2916.5</v>
+        <v>2831.1</v>
       </c>
       <c r="D3">
-        <v>0.57</v>
+        <v>-2.93</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-9.199999999999999</v>
+        <v>-11.86</v>
       </c>
       <c r="H3">
-        <v>65.90000000000001</v>
+        <v>61.04</v>
       </c>
       <c r="I3">
-        <v>-3.43</v>
+        <v>-4.84</v>
       </c>
       <c r="J3">
-        <v>-6.28</v>
+        <v>-10.66</v>
       </c>
       <c r="K3">
-        <v>-1.55</v>
+        <v>-6.75</v>
       </c>
       <c r="L3">
-        <v>10.96</v>
+        <v>5.83</v>
       </c>
       <c r="M3">
-        <v>13.82</v>
+        <v>13.79</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="P3">
-        <v>2956.34</v>
+        <v>2927.56</v>
       </c>
       <c r="Q3">
-        <v>2967.04</v>
+        <v>2950.17</v>
       </c>
       <c r="R3">
-        <v>3015.21</v>
+        <v>3008.62</v>
       </c>
       <c r="S3">
-        <v>2559.1</v>
+        <v>2562.04</v>
       </c>
       <c r="T3">
-        <v>13.97</v>
+        <v>10.5</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,43 +1109,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.98</v>
+        <v>38.12</v>
       </c>
       <c r="Z3">
-        <v>-18.62</v>
+        <v>-27.84</v>
       </c>
       <c r="AA3">
-        <v>-13.9</v>
+        <v>-16.69</v>
       </c>
       <c r="AB3">
-        <v>-4.72</v>
+        <v>-11.15</v>
       </c>
       <c r="AC3">
-        <v>20.81</v>
+        <v>3.23</v>
       </c>
       <c r="AD3">
-        <v>37.3</v>
+        <v>20.18</v>
       </c>
       <c r="AE3">
-        <v>75.34999999999999</v>
+        <v>78.03</v>
       </c>
       <c r="AF3">
-        <v>-72.47</v>
+        <v>-37.1</v>
       </c>
       <c r="AG3">
-        <v>3133.15</v>
+        <v>3097.61</v>
       </c>
       <c r="AH3">
-        <v>2800.93</v>
+        <v>2802.73</v>
       </c>
       <c r="AI3">
-        <v>3113.12</v>
+        <v>3101.6</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>19.6</v>
+        <v>22.75</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1296.6</v>
+        <v>1235</v>
       </c>
       <c r="D4">
-        <v>1.29</v>
+        <v>-4.75</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.19</v>
+        <v>-23.03</v>
       </c>
       <c r="H4">
-        <v>67.78</v>
+        <v>59.81</v>
       </c>
       <c r="I4">
-        <v>-2.84</v>
+        <v>-5.26</v>
       </c>
       <c r="J4">
-        <v>-0.51</v>
+        <v>-7.04</v>
       </c>
       <c r="K4">
-        <v>-13.7</v>
+        <v>-17.24</v>
       </c>
       <c r="L4">
-        <v>12.54</v>
+        <v>9.15</v>
       </c>
       <c r="M4">
-        <v>2.37</v>
+        <v>1.53</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="P4">
-        <v>1297.04</v>
+        <v>1283.32</v>
       </c>
       <c r="Q4">
-        <v>1288.3</v>
+        <v>1284.5</v>
       </c>
       <c r="R4">
-        <v>1338.98</v>
+        <v>1333.4</v>
       </c>
       <c r="S4">
-        <v>1195.25</v>
+        <v>1196.43</v>
       </c>
       <c r="T4">
-        <v>8.48</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>48.06</v>
+        <v>39.06</v>
       </c>
       <c r="Z4">
-        <v>-11.34</v>
+        <v>-15.23</v>
       </c>
       <c r="AA4">
-        <v>-16.43</v>
+        <v>-16.19</v>
       </c>
       <c r="AB4">
-        <v>5.09</v>
+        <v>0.96</v>
       </c>
       <c r="AC4">
-        <v>53.3</v>
+        <v>32.63</v>
       </c>
       <c r="AD4">
-        <v>57.76</v>
+        <v>47.03</v>
       </c>
       <c r="AE4">
-        <v>35.9</v>
+        <v>38.41</v>
       </c>
       <c r="AF4">
-        <v>-32.71</v>
+        <v>32.36</v>
       </c>
       <c r="AG4">
-        <v>1338.85</v>
+        <v>1339.13</v>
       </c>
       <c r="AH4">
-        <v>1237.76</v>
+        <v>1229.88</v>
       </c>
       <c r="AI4">
         <v>1367.12</v>
@@ -1230,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>16.57</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1788</v>
+        <v>1743.7</v>
       </c>
       <c r="D5">
-        <v>0.15</v>
+        <v>-2.48</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-5.06</v>
+        <v>-7.41</v>
       </c>
       <c r="H5">
-        <v>37.74</v>
+        <v>34.32</v>
       </c>
       <c r="I5">
-        <v>-1.97</v>
+        <v>-2.43</v>
       </c>
       <c r="J5">
-        <v>5.7</v>
+        <v>1.73</v>
       </c>
       <c r="K5">
-        <v>0.67</v>
+        <v>-3.67</v>
       </c>
       <c r="L5">
-        <v>24.33</v>
+        <v>21.47</v>
       </c>
       <c r="M5">
-        <v>19.64</v>
+        <v>19.39</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P5">
-        <v>1792.54</v>
+        <v>1783.86</v>
       </c>
       <c r="Q5">
-        <v>1735.46</v>
+        <v>1737.27</v>
       </c>
       <c r="R5">
-        <v>1726.75</v>
+        <v>1724.88</v>
       </c>
       <c r="S5">
-        <v>1620.76</v>
+        <v>1622.02</v>
       </c>
       <c r="T5">
-        <v>10.32</v>
+        <v>7.5</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>56.93</v>
+        <v>49.79</v>
       </c>
       <c r="Z5">
-        <v>23.05</v>
+        <v>19.32</v>
       </c>
       <c r="AA5">
-        <v>15.57</v>
+        <v>16.32</v>
       </c>
       <c r="AB5">
-        <v>7.48</v>
+        <v>3.01</v>
       </c>
       <c r="AC5">
-        <v>59.16</v>
+        <v>34.13</v>
       </c>
       <c r="AD5">
-        <v>66.01000000000001</v>
+        <v>52.96</v>
       </c>
       <c r="AE5">
-        <v>38.55</v>
+        <v>39.74</v>
       </c>
       <c r="AF5">
-        <v>-64.61</v>
+        <v>-49.1</v>
       </c>
       <c r="AG5">
-        <v>1852.65</v>
+        <v>1853.76</v>
       </c>
       <c r="AH5">
-        <v>1618.26</v>
+        <v>1620.77</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1343,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>32.02</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>202.75</v>
+        <v>196.14</v>
       </c>
       <c r="D6">
-        <v>1.64</v>
+        <v>-3.26</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,25 +1394,25 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-18.54</v>
+        <v>-21.2</v>
       </c>
       <c r="H6">
-        <v>52.49</v>
+        <v>47.52</v>
       </c>
       <c r="I6">
-        <v>-1.86</v>
+        <v>-5.04</v>
       </c>
       <c r="J6">
-        <v>-2.15</v>
+        <v>-8.77</v>
       </c>
       <c r="K6">
-        <v>-10.7</v>
+        <v>-12.35</v>
       </c>
       <c r="L6">
-        <v>19.09</v>
+        <v>20.81</v>
       </c>
       <c r="M6">
-        <v>59.99</v>
+        <v>59.18</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1393,19 +1421,19 @@
         <v>64</v>
       </c>
       <c r="P6">
-        <v>204.11</v>
+        <v>202.03</v>
       </c>
       <c r="Q6">
-        <v>206.34</v>
+        <v>205.52</v>
       </c>
       <c r="R6">
-        <v>208.38</v>
+        <v>208.02</v>
       </c>
       <c r="S6">
-        <v>186.98</v>
+        <v>187.25</v>
       </c>
       <c r="T6">
-        <v>8.43</v>
+        <v>4.75</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>44.88</v>
+        <v>38.23</v>
       </c>
       <c r="Z6">
-        <v>-1.51</v>
+        <v>-2.1</v>
       </c>
       <c r="AA6">
-        <v>-1.09</v>
+        <v>-1.29</v>
       </c>
       <c r="AB6">
-        <v>-0.42</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AC6">
-        <v>16.94</v>
+        <v>9.34</v>
       </c>
       <c r="AD6">
-        <v>24.38</v>
+        <v>15.99</v>
       </c>
       <c r="AE6">
-        <v>5.59</v>
+        <v>5.78</v>
       </c>
       <c r="AF6">
-        <v>-24.76</v>
+        <v>5.2</v>
       </c>
       <c r="AG6">
-        <v>215.08</v>
+        <v>214.85</v>
       </c>
       <c r="AH6">
-        <v>197.6</v>
+        <v>196.19</v>
       </c>
       <c r="AI6">
         <v>216.61</v>
@@ -1456,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>21.05</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,37 +1495,37 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>383.8</v>
+        <v>374.35</v>
       </c>
       <c r="D7">
-        <v>-0.08</v>
+        <v>-2.46</v>
       </c>
       <c r="E7">
-        <v>588.6900000000001</v>
+        <v>579.78</v>
       </c>
       <c r="F7">
-        <v>381.05</v>
+        <v>374.35</v>
       </c>
       <c r="G7">
-        <v>-34.8</v>
+        <v>-35.43</v>
       </c>
       <c r="H7">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-1.16</v>
+        <v>-4.2</v>
       </c>
       <c r="J7">
-        <v>-8.44</v>
+        <v>-8.93</v>
       </c>
       <c r="K7">
-        <v>-9.529999999999999</v>
+        <v>-11.26</v>
       </c>
       <c r="L7">
-        <v>-34.66</v>
+        <v>-36.41</v>
       </c>
       <c r="M7">
-        <v>-0.93</v>
+        <v>-1.19</v>
       </c>
       <c r="N7">
         <v>23</v>
@@ -1506,19 +1534,19 @@
         <v>18</v>
       </c>
       <c r="P7">
-        <v>387.66</v>
+        <v>384.38</v>
       </c>
       <c r="Q7">
-        <v>394.1</v>
+        <v>392.22</v>
       </c>
       <c r="R7">
-        <v>413.17</v>
+        <v>411.89</v>
       </c>
       <c r="S7">
-        <v>457.85</v>
+        <v>457.07</v>
       </c>
       <c r="T7">
-        <v>-16.17</v>
+        <v>-18.1</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,43 +1561,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>36.05</v>
+        <v>30.43</v>
       </c>
       <c r="Z7">
-        <v>-7.94</v>
+        <v>-8.57</v>
       </c>
       <c r="AA7">
-        <v>-8.210000000000001</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AB7">
-        <v>0.27</v>
+        <v>-0.29</v>
       </c>
       <c r="AC7">
-        <v>75.33</v>
+        <v>51.84</v>
       </c>
       <c r="AD7">
-        <v>79.44</v>
+        <v>68.2</v>
       </c>
       <c r="AE7">
-        <v>7.85</v>
+        <v>7.99</v>
       </c>
       <c r="AF7">
-        <v>-11.77</v>
+        <v>30.89</v>
       </c>
       <c r="AG7">
-        <v>412.16</v>
+        <v>410.26</v>
       </c>
       <c r="AH7">
-        <v>376.05</v>
+        <v>374.18</v>
       </c>
       <c r="AI7">
-        <v>405.74</v>
+        <v>402.86</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>34.9</v>
+        <v>37.91</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>611.65</v>
+        <v>594.45</v>
       </c>
       <c r="D8">
-        <v>-0.12</v>
+        <v>-2.81</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-24.33</v>
+        <v>-26.45</v>
       </c>
       <c r="H8">
-        <v>30.77</v>
+        <v>27.09</v>
       </c>
       <c r="I8">
-        <v>-7.42</v>
+        <v>-6.88</v>
       </c>
       <c r="J8">
-        <v>-4.98</v>
+        <v>-7.89</v>
       </c>
       <c r="K8">
-        <v>-16.4</v>
+        <v>-18.74</v>
       </c>
       <c r="L8">
-        <v>-21.63</v>
+        <v>-17.75</v>
       </c>
       <c r="M8">
-        <v>-15.48</v>
+        <v>-15.84</v>
       </c>
       <c r="N8">
         <v>45</v>
       </c>
       <c r="O8">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P8">
-        <v>622.79</v>
+        <v>614</v>
       </c>
       <c r="Q8">
-        <v>613.2</v>
+        <v>611.09</v>
       </c>
       <c r="R8">
-        <v>641.6799999999999</v>
+        <v>639.4400000000001</v>
       </c>
       <c r="S8">
-        <v>614.5700000000001</v>
+        <v>614.6</v>
       </c>
       <c r="T8">
-        <v>-0.48</v>
+        <v>-3.28</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1674,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>45.33</v>
+        <v>40.29</v>
       </c>
       <c r="Z8">
-        <v>-7.02</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="AA8">
-        <v>-10.4</v>
+        <v>-9.98</v>
       </c>
       <c r="AB8">
-        <v>3.39</v>
+        <v>1.7</v>
       </c>
       <c r="AC8">
-        <v>61.24</v>
+        <v>53.34</v>
       </c>
       <c r="AD8">
-        <v>66.15000000000001</v>
+        <v>59.9</v>
       </c>
       <c r="AE8">
-        <v>19.25</v>
+        <v>19.21</v>
       </c>
       <c r="AF8">
-        <v>-79.2</v>
+        <v>-76.64</v>
       </c>
       <c r="AG8">
-        <v>651.22</v>
+        <v>648.33</v>
       </c>
       <c r="AH8">
-        <v>575.17</v>
+        <v>573.85</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1682,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>36.83</v>
+        <v>32.49</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>184.34</v>
+        <v>180.66</v>
       </c>
       <c r="D9">
-        <v>-0.19</v>
+        <v>-2</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.6</v>
+        <v>-34.92</v>
       </c>
       <c r="H9">
-        <v>6.99</v>
+        <v>4.85</v>
       </c>
       <c r="I9">
-        <v>-1.41</v>
+        <v>-1.58</v>
       </c>
       <c r="J9">
-        <v>-8.699999999999999</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="K9">
-        <v>0.91</v>
+        <v>-1.61</v>
       </c>
       <c r="L9">
-        <v>-32</v>
+        <v>-30.54</v>
       </c>
       <c r="M9">
-        <v>-7.79</v>
+        <v>-8.17</v>
       </c>
       <c r="N9">
         <v>55</v>
       </c>
       <c r="O9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P9">
-        <v>184.37</v>
+        <v>183.79</v>
       </c>
       <c r="Q9">
-        <v>187.23</v>
+        <v>186.45</v>
       </c>
       <c r="R9">
-        <v>190.07</v>
+        <v>189.91</v>
       </c>
       <c r="S9">
-        <v>198.01</v>
+        <v>197.68</v>
       </c>
       <c r="T9">
-        <v>-6.9</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,43 +1787,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>43.23</v>
+        <v>37.47</v>
       </c>
       <c r="Z9">
-        <v>-2</v>
+        <v>-2.24</v>
       </c>
       <c r="AA9">
-        <v>-1.87</v>
+        <v>-1.94</v>
       </c>
       <c r="AB9">
-        <v>-0.13</v>
+        <v>-0.29</v>
       </c>
       <c r="AC9">
-        <v>84.79000000000001</v>
+        <v>61.25</v>
       </c>
       <c r="AD9">
-        <v>73.01000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="AE9">
-        <v>4.39</v>
+        <v>4.38</v>
       </c>
       <c r="AF9">
-        <v>-29.88</v>
+        <v>-64.02</v>
       </c>
       <c r="AG9">
-        <v>195.17</v>
+        <v>193.69</v>
       </c>
       <c r="AH9">
-        <v>179.28</v>
+        <v>179.21</v>
       </c>
       <c r="AI9">
-        <v>195.69</v>
+        <v>195.23</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>24.26</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,37 +1834,37 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>70.08</v>
+        <v>69.11</v>
       </c>
       <c r="D10">
-        <v>0.21</v>
+        <v>-1.38</v>
       </c>
       <c r="E10">
-        <v>126.36</v>
+        <v>122.23</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-44.54</v>
+        <v>-43.46</v>
       </c>
       <c r="H10">
-        <v>18.22</v>
+        <v>16.58</v>
       </c>
       <c r="I10">
-        <v>-2.29</v>
+        <v>-3.44</v>
       </c>
       <c r="J10">
-        <v>-5.74</v>
+        <v>-6.86</v>
       </c>
       <c r="K10">
-        <v>-12.8</v>
+        <v>-14.03</v>
       </c>
       <c r="L10">
-        <v>-46.42</v>
+        <v>-45.31</v>
       </c>
       <c r="M10">
-        <v>-5.2</v>
+        <v>-4.49</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1845,19 +1873,19 @@
         <v>9</v>
       </c>
       <c r="P10">
-        <v>71</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="Q10">
-        <v>71.75</v>
+        <v>71.52</v>
       </c>
       <c r="R10">
-        <v>74.59</v>
+        <v>74.37</v>
       </c>
       <c r="S10">
-        <v>80.05</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="T10">
-        <v>-12.46</v>
+        <v>-13.6</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>38.52</v>
+        <v>35.38</v>
       </c>
       <c r="Z10">
-        <v>-1.2</v>
+        <v>-1.29</v>
       </c>
       <c r="AA10">
-        <v>-1.21</v>
+        <v>-1.23</v>
       </c>
       <c r="AB10">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="AC10">
-        <v>48.2</v>
+        <v>29.32</v>
       </c>
       <c r="AD10">
-        <v>65.31999999999999</v>
+        <v>47.92</v>
       </c>
       <c r="AE10">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AF10">
-        <v>-64.05</v>
+        <v>-36.59</v>
       </c>
       <c r="AG10">
-        <v>74.39</v>
+        <v>74.23</v>
       </c>
       <c r="AH10">
-        <v>69.11</v>
+        <v>68.81</v>
       </c>
       <c r="AI10">
         <v>76.63</v>
@@ -1908,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>23.36</v>
+        <v>25.33</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,12 +2097,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2082,1278 +2145,1244 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-5.34</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-7.16</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.82</v>
+      <c r="D7" s="6">
+        <v>-7.41</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
+        <v>-6.28</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-10.66</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-0.51</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-6.53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.73</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-3.97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-2.15</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-8.77</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-6.62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-8.44</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-8.93</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-4.98</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-7.89</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-5.74</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-6.86</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.41</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.43</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-4.84</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.84</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-5.26</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.97</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.43</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-1.86</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-5.04</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-1.16</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-4.2</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-7.42</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-6.88</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-1.41</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-1.58</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-2.29</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-3.44</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-33.93</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-35.03</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>10.96</v>
+      </c>
+      <c r="D26" s="6">
+        <v>5.83</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-5.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>12.54</v>
+      </c>
+      <c r="D27" s="6">
+        <v>9.15</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>24.33</v>
+      </c>
+      <c r="D28" s="6">
+        <v>21.47</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>19.09</v>
+      </c>
+      <c r="D29" s="6">
+        <v>20.81</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-34.66</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-36.41</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-21.63</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-17.75</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-32</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-30.54</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-46.42</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-45.31</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-7.27</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-8.57</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-1.55</v>
+      </c>
+      <c r="D35" s="6">
         <v>-6.75</v>
       </c>
-      <c r="D8" s="5">
-        <v>-6.28</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="E35" s="7">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-3.75</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="E9" s="7">
-        <v>3.24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-13.7</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-17.24</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>4.85</v>
-      </c>
-      <c r="D10" s="5">
-        <v>5.7</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-4.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-3.32</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-2.15</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-10.7</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-12.35</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-7.02</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-8.44</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-11.26</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-4.35</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-4.98</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-16.4</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-18.74</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-1.61</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-12.8</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-14.03</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-35.02</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-36.22</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-11.86</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-19.19</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-23.03</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-3.84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-5.06</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-7.41</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-18.54</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-21.2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-34.8</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-35.43</v>
+      </c>
+      <c r="E48" s="7">
         <v>-0.63</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-24.33</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-26.45</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-7.95</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-33.6</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-34.92</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-6.47</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-5.74</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-44.54</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-43.46</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>0.29</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.85</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>1236.4</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1213.5</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-22.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.79</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-3.43</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>2916.5</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2831.1</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-85.40000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.46</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.84</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-3.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1296.6</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1235</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-61.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>2.7</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-1.97</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-4.67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1788</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1743.7</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-44.3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-3.13</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-1.86</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>202.75</v>
+      </c>
+      <c r="D56" s="6">
+        <v>196.14</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-6.61</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.22</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-1.16</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>383.8</v>
+      </c>
+      <c r="D57" s="6">
+        <v>374.35</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-9.449999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>4.33</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-7.42</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-11.75</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>611.65</v>
+      </c>
+      <c r="D58" s="6">
+        <v>594.45</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-17.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-1.41</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>184.34</v>
+      </c>
+      <c r="D59" s="6">
+        <v>180.66</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-3.68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-1.56</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-2.29</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>70.08</v>
+      </c>
+      <c r="D60" s="6">
+        <v>69.11</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-33.84</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-33.93</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>38.52</v>
+      </c>
+      <c r="D61" s="6">
+        <v>33.21</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-5.31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>14.95</v>
-      </c>
-      <c r="D26" s="5">
-        <v>10.96</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-3.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>43.98</v>
+      </c>
+      <c r="D62" s="6">
+        <v>38.12</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-5.86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="D27" s="5">
-        <v>12.54</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-11.66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>48.06</v>
+      </c>
+      <c r="D63" s="6">
+        <v>39.06</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>25.57</v>
-      </c>
-      <c r="D28" s="5">
-        <v>24.33</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>56.93</v>
+      </c>
+      <c r="D64" s="6">
+        <v>49.79</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-7.14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>40.6</v>
-      </c>
-      <c r="D29" s="5">
-        <v>19.09</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-21.51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>44.88</v>
+      </c>
+      <c r="D65" s="6">
+        <v>38.23</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-6.65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-33.73</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-34.66</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>36.05</v>
+      </c>
+      <c r="D66" s="6">
+        <v>30.43</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-5.62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-5.96</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-21.63</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-15.67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>45.33</v>
+      </c>
+      <c r="D67" s="6">
+        <v>40.29</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-5.04</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-28.12</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-32</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-3.88</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>43.23</v>
+      </c>
+      <c r="D68" s="6">
+        <v>37.47</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-5.76</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-46.08</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-46.42</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>38.52</v>
+      </c>
+      <c r="D69" s="6">
+        <v>35.38</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-7.61</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-7.27</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-63.6</v>
+      </c>
+      <c r="D70" s="6">
+        <v>28.43</v>
+      </c>
+      <c r="E70" s="8">
+        <v>92.03</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-4.54</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-1.55</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-72.47</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-37.1</v>
+      </c>
+      <c r="E71" s="8">
+        <v>35.37</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-16.12</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-13.7</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-32.71</v>
+      </c>
+      <c r="D72" s="6">
+        <v>32.36</v>
+      </c>
+      <c r="E72" s="8">
+        <v>65.06999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-0.6</v>
-      </c>
-      <c r="D37" s="5">
-        <v>0.67</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-64.61</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-49.1</v>
+      </c>
+      <c r="E73" s="8">
+        <v>15.51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-12.99</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-10.7</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-24.76</v>
+      </c>
+      <c r="D74" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="E74" s="8">
+        <v>29.96</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-11.77</v>
+      </c>
+      <c r="D75" s="6">
+        <v>30.89</v>
+      </c>
+      <c r="E75" s="8">
+        <v>42.66</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-14.92</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-16.4</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-79.2</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-76.64</v>
+      </c>
+      <c r="E76" s="8">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>1.46</v>
-      </c>
-      <c r="D41" s="5">
-        <v>0.91</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-29.88</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-64.02</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-34.14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-13.75</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-12.8</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-35.03</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-35.02</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-20.22</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-19.19</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-5.2</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-5.06</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-19.86</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-18.54</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-34.75</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-34.8</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-24.23</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-24.33</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-33.47</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-33.6</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-46.54</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-44.54</v>
-      </c>
-      <c r="E51" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1236.1</v>
-      </c>
-      <c r="D52" s="5">
-        <v>1236.4</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>2900</v>
-      </c>
-      <c r="D53" s="5">
-        <v>2916.5</v>
-      </c>
-      <c r="E53" s="7">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1280.1</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1296.6</v>
-      </c>
-      <c r="E54" s="7">
-        <v>16.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>1785.3</v>
-      </c>
-      <c r="D55" s="5">
-        <v>1788</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>199.48</v>
-      </c>
-      <c r="D56" s="5">
-        <v>202.75</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>384.1</v>
-      </c>
-      <c r="D57" s="5">
-        <v>383.8</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>612.4</v>
-      </c>
-      <c r="D58" s="5">
-        <v>611.65</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>184.69</v>
-      </c>
-      <c r="D59" s="5">
-        <v>184.34</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>69.93000000000001</v>
-      </c>
-      <c r="D60" s="5">
-        <v>70.08</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>55</v>
-      </c>
-      <c r="D61" s="5">
-        <v>45</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>45</v>
-      </c>
-      <c r="D62" s="5">
-        <v>55</v>
-      </c>
-      <c r="E62" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>38.4</v>
-      </c>
-      <c r="D63" s="5">
-        <v>38.52</v>
-      </c>
-      <c r="E63" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>42.39</v>
-      </c>
-      <c r="D64" s="5">
-        <v>43.98</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="5">
-        <v>44.9</v>
-      </c>
-      <c r="D65" s="5">
-        <v>48.06</v>
-      </c>
-      <c r="E65" s="7">
-        <v>3.16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="5">
-        <v>56.58</v>
-      </c>
-      <c r="D66" s="5">
-        <v>56.93</v>
-      </c>
-      <c r="E66" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>40.1</v>
-      </c>
-      <c r="D67" s="5">
-        <v>44.88</v>
-      </c>
-      <c r="E67" s="7">
-        <v>4.78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>36.25</v>
-      </c>
-      <c r="D68" s="5">
-        <v>36.05</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>45.56</v>
-      </c>
-      <c r="D69" s="5">
-        <v>45.33</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>43.83</v>
-      </c>
-      <c r="D70" s="5">
-        <v>43.23</v>
-      </c>
-      <c r="E70" s="6">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>37.73</v>
-      </c>
-      <c r="D71" s="5">
-        <v>38.52</v>
-      </c>
-      <c r="E71" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="5">
-        <v>-27.56</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-63.6</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-36.04</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="5">
-        <v>-48.91</v>
-      </c>
-      <c r="D73" s="5">
-        <v>-72.47</v>
-      </c>
-      <c r="E73" s="6">
-        <v>-23.56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="5">
-        <v>64.47</v>
-      </c>
-      <c r="D74" s="5">
-        <v>-32.71</v>
-      </c>
-      <c r="E74" s="6">
-        <v>-97.18000000000001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="5">
-        <v>-36.81</v>
-      </c>
-      <c r="D75" s="5">
-        <v>-64.61</v>
-      </c>
-      <c r="E75" s="6">
-        <v>-27.8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="5">
-        <v>-4.36</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-24.76</v>
-      </c>
-      <c r="E76" s="6">
-        <v>-20.4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-33.14</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-11.77</v>
-      </c>
-      <c r="E77" s="7">
-        <v>21.37</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-75.87</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-79.2</v>
-      </c>
-      <c r="E78" s="6">
-        <v>-3.33</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>17.87</v>
-      </c>
-      <c r="D79" s="5">
-        <v>-29.88</v>
-      </c>
-      <c r="E79" s="6">
-        <v>-47.75</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>-17.6</v>
-      </c>
-      <c r="D80" s="5">
+      <c r="C78" s="6">
         <v>-64.05</v>
       </c>
-      <c r="E80" s="6">
-        <v>-46.45</v>
+      <c r="D78" s="6">
+        <v>-36.59</v>
+      </c>
+      <c r="E78" s="8">
+        <v>27.46</v>
       </c>
     </row>
   </sheetData>
@@ -3379,60 +3408,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.16</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>43.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>38</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-4.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-7.8</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-7.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-10.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -3534,61 +3563,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.5999</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1964</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1382</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0237</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.009300000000000001</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.052</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.0779</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.1113</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.1548</v>
+      <c r="A2" s="14">
+        <v>0.5918</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1939</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1379</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0153</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.0119</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0449</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.08169999999999999</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.1121</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1584</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>56.9 → 49.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>56.9</t>
+    <t>38.1 → 50.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>38.1</t>
+  </si>
+  <si>
+    <t>50.0</t>
+  </si>
+  <si>
+    <t>49.8 → 59.5</t>
   </si>
   <si>
     <t>49.8</t>
+  </si>
+  <si>
+    <t>59.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +300,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +340,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,8 +426,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,37 +939,37 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1213.5</v>
+        <v>1202.6</v>
       </c>
       <c r="D2">
-        <v>-1.85</v>
+        <v>-0.9</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1213.5</v>
+        <v>1202.6</v>
       </c>
       <c r="G2">
-        <v>-36.22</v>
+        <v>-36.79</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-3.41</v>
+        <v>-2.88</v>
       </c>
       <c r="J2">
-        <v>-7.41</v>
+        <v>-7.95</v>
       </c>
       <c r="K2">
-        <v>-8.57</v>
+        <v>-9.73</v>
       </c>
       <c r="L2">
-        <v>-35.03</v>
+        <v>-35</v>
       </c>
       <c r="M2">
-        <v>-11.21</v>
+        <v>-11.14</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -969,19 +978,19 @@
         <v>20</v>
       </c>
       <c r="P2">
-        <v>1235.12</v>
+        <v>1228</v>
       </c>
       <c r="Q2">
-        <v>1251.85</v>
+        <v>1248.16</v>
       </c>
       <c r="R2">
-        <v>1305.84</v>
+        <v>1302.26</v>
       </c>
       <c r="S2">
-        <v>1447.91</v>
+        <v>1445.07</v>
       </c>
       <c r="T2">
-        <v>-16.19</v>
+        <v>-16.78</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1005,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>33.21</v>
+        <v>31.02</v>
       </c>
       <c r="Z2">
-        <v>-21.09</v>
+        <v>-22.74</v>
       </c>
       <c r="AA2">
-        <v>-21.36</v>
+        <v>-21.64</v>
       </c>
       <c r="AB2">
-        <v>0.27</v>
+        <v>-1.1</v>
       </c>
       <c r="AC2">
-        <v>59.45</v>
+        <v>43.27</v>
       </c>
       <c r="AD2">
-        <v>71.77</v>
+        <v>60.7</v>
       </c>
       <c r="AE2">
-        <v>22.75</v>
+        <v>23.72</v>
       </c>
       <c r="AF2">
-        <v>28.43</v>
+        <v>499.41</v>
       </c>
       <c r="AG2">
-        <v>1290.49</v>
+        <v>1290.8</v>
       </c>
       <c r="AH2">
-        <v>1213.22</v>
+        <v>1205.52</v>
       </c>
       <c r="AI2">
-        <v>1291.84</v>
+        <v>1277.47</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>19.11</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2831.1</v>
+        <v>2972.9</v>
       </c>
       <c r="D3">
-        <v>-2.93</v>
+        <v>5.01</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1064,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-11.86</v>
+        <v>-7.45</v>
       </c>
       <c r="H3">
-        <v>61.04</v>
+        <v>69.11</v>
       </c>
       <c r="I3">
-        <v>-4.84</v>
+        <v>-0.8</v>
       </c>
       <c r="J3">
-        <v>-10.66</v>
+        <v>-6.17</v>
       </c>
       <c r="K3">
-        <v>-6.75</v>
+        <v>-5.43</v>
       </c>
       <c r="L3">
-        <v>5.83</v>
+        <v>13.53</v>
       </c>
       <c r="M3">
-        <v>13.79</v>
+        <v>14.94</v>
       </c>
       <c r="N3">
         <v>77</v>
       </c>
       <c r="O3">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="P3">
-        <v>2927.56</v>
+        <v>2922.74</v>
       </c>
       <c r="Q3">
-        <v>2950.17</v>
+        <v>2955.86</v>
       </c>
       <c r="R3">
-        <v>3008.62</v>
+        <v>3004.41</v>
       </c>
       <c r="S3">
-        <v>2562.04</v>
+        <v>2565.85</v>
       </c>
       <c r="T3">
-        <v>10.5</v>
+        <v>15.86</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1118,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>38.12</v>
+        <v>50.02</v>
       </c>
       <c r="Z3">
-        <v>-27.84</v>
+        <v>-23.43</v>
       </c>
       <c r="AA3">
-        <v>-16.69</v>
+        <v>-18.04</v>
       </c>
       <c r="AB3">
-        <v>-11.15</v>
+        <v>-5.39</v>
       </c>
       <c r="AC3">
-        <v>3.23</v>
+        <v>22.43</v>
       </c>
       <c r="AD3">
-        <v>20.18</v>
+        <v>15.49</v>
       </c>
       <c r="AE3">
-        <v>78.03</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="AF3">
-        <v>-37.1</v>
+        <v>63.13</v>
       </c>
       <c r="AG3">
-        <v>3097.61</v>
+        <v>3097.16</v>
       </c>
       <c r="AH3">
-        <v>2802.73</v>
+        <v>2814.56</v>
       </c>
       <c r="AI3">
         <v>3101.6</v>
@@ -1145,7 +1154,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>22.75</v>
+        <v>22.42</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1235</v>
+        <v>1260</v>
       </c>
       <c r="D4">
-        <v>-4.75</v>
+        <v>2.02</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1177,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-23.03</v>
+        <v>-21.47</v>
       </c>
       <c r="H4">
-        <v>59.81</v>
+        <v>63.04</v>
       </c>
       <c r="I4">
-        <v>-5.26</v>
+        <v>-3.37</v>
       </c>
       <c r="J4">
-        <v>-7.04</v>
+        <v>-3.89</v>
       </c>
       <c r="K4">
-        <v>-17.24</v>
+        <v>-17.92</v>
       </c>
       <c r="L4">
-        <v>9.15</v>
+        <v>15.04</v>
       </c>
       <c r="M4">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="P4">
-        <v>1283.32</v>
+        <v>1274.52</v>
       </c>
       <c r="Q4">
-        <v>1284.5</v>
+        <v>1286.76</v>
       </c>
       <c r="R4">
-        <v>1333.4</v>
+        <v>1328</v>
       </c>
       <c r="S4">
-        <v>1196.43</v>
+        <v>1197.78</v>
       </c>
       <c r="T4">
-        <v>3.22</v>
+        <v>5.19</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,43 +1231,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>39.06</v>
+        <v>43.67</v>
       </c>
       <c r="Z4">
-        <v>-15.23</v>
+        <v>-16.12</v>
       </c>
       <c r="AA4">
-        <v>-16.19</v>
+        <v>-16.18</v>
       </c>
       <c r="AB4">
-        <v>0.96</v>
+        <v>0.06</v>
       </c>
       <c r="AC4">
-        <v>32.63</v>
+        <v>30.47</v>
       </c>
       <c r="AD4">
-        <v>47.03</v>
+        <v>38.8</v>
       </c>
       <c r="AE4">
-        <v>38.41</v>
+        <v>38.27</v>
       </c>
       <c r="AF4">
-        <v>32.36</v>
+        <v>13.51</v>
       </c>
       <c r="AG4">
-        <v>1339.13</v>
+        <v>1332.24</v>
       </c>
       <c r="AH4">
-        <v>1229.88</v>
+        <v>1241.28</v>
       </c>
       <c r="AI4">
-        <v>1367.12</v>
+        <v>1356.6</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>19.65</v>
+        <v>22.45</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1743.7</v>
+        <v>1822</v>
       </c>
       <c r="D5">
-        <v>-2.48</v>
+        <v>4.49</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1290,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.41</v>
+        <v>-3.25</v>
       </c>
       <c r="H5">
-        <v>34.32</v>
+        <v>40.36</v>
       </c>
       <c r="I5">
-        <v>-2.43</v>
+        <v>1.5</v>
       </c>
       <c r="J5">
-        <v>1.73</v>
+        <v>6.71</v>
       </c>
       <c r="K5">
-        <v>-3.67</v>
+        <v>-1.42</v>
       </c>
       <c r="L5">
-        <v>21.47</v>
+        <v>27.81</v>
       </c>
       <c r="M5">
-        <v>19.39</v>
+        <v>20.33</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1783.86</v>
+        <v>1789.26</v>
       </c>
       <c r="Q5">
-        <v>1737.27</v>
+        <v>1748.71</v>
       </c>
       <c r="R5">
-        <v>1724.88</v>
+        <v>1724.44</v>
       </c>
       <c r="S5">
-        <v>1622.02</v>
+        <v>1623.68</v>
       </c>
       <c r="T5">
-        <v>7.5</v>
+        <v>12.21</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1344,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.79</v>
+        <v>59.47</v>
       </c>
       <c r="Z5">
-        <v>19.32</v>
+        <v>22.43</v>
       </c>
       <c r="AA5">
-        <v>16.32</v>
+        <v>17.54</v>
       </c>
       <c r="AB5">
-        <v>3.01</v>
+        <v>4.89</v>
       </c>
       <c r="AC5">
-        <v>34.13</v>
+        <v>40.13</v>
       </c>
       <c r="AD5">
-        <v>52.96</v>
+        <v>44.47</v>
       </c>
       <c r="AE5">
-        <v>39.74</v>
+        <v>42.88</v>
       </c>
       <c r="AF5">
-        <v>-49.1</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="AG5">
-        <v>1853.76</v>
+        <v>1849.48</v>
       </c>
       <c r="AH5">
-        <v>1620.77</v>
+        <v>1647.94</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1371,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.22</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>196.14</v>
+        <v>196.3</v>
       </c>
       <c r="D6">
-        <v>-3.26</v>
+        <v>0.08</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1403,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-21.2</v>
+        <v>-21.14</v>
       </c>
       <c r="H6">
-        <v>47.52</v>
+        <v>47.64</v>
       </c>
       <c r="I6">
-        <v>-5.04</v>
+        <v>-5.15</v>
       </c>
       <c r="J6">
-        <v>-8.77</v>
+        <v>-7.68</v>
       </c>
       <c r="K6">
-        <v>-12.35</v>
+        <v>-13.47</v>
       </c>
       <c r="L6">
-        <v>20.81</v>
+        <v>35.85</v>
       </c>
       <c r="M6">
-        <v>59.18</v>
+        <v>58.45</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="P6">
-        <v>202.03</v>
+        <v>199.89</v>
       </c>
       <c r="Q6">
-        <v>205.52</v>
+        <v>205.43</v>
       </c>
       <c r="R6">
-        <v>208.02</v>
+        <v>207.54</v>
       </c>
       <c r="S6">
-        <v>187.25</v>
+        <v>187.53</v>
       </c>
       <c r="T6">
-        <v>4.75</v>
+        <v>4.68</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,43 +1457,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.23</v>
+        <v>38.47</v>
       </c>
       <c r="Z6">
-        <v>-2.1</v>
+        <v>-2.54</v>
       </c>
       <c r="AA6">
-        <v>-1.29</v>
+        <v>-1.54</v>
       </c>
       <c r="AB6">
-        <v>-0.8100000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AC6">
-        <v>9.34</v>
+        <v>9.75</v>
       </c>
       <c r="AD6">
-        <v>15.99</v>
+        <v>12.01</v>
       </c>
       <c r="AE6">
-        <v>5.78</v>
+        <v>5.89</v>
       </c>
       <c r="AF6">
-        <v>5.2</v>
+        <v>78.69</v>
       </c>
       <c r="AG6">
-        <v>214.85</v>
+        <v>215.08</v>
       </c>
       <c r="AH6">
-        <v>196.19</v>
+        <v>195.79</v>
       </c>
       <c r="AI6">
-        <v>216.61</v>
+        <v>213.83</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>24.41</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,58 +1504,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>374.35</v>
+        <v>365.75</v>
       </c>
       <c r="D7">
-        <v>-2.46</v>
+        <v>-2.3</v>
       </c>
       <c r="E7">
-        <v>579.78</v>
+        <v>576.55</v>
       </c>
       <c r="F7">
-        <v>374.35</v>
+        <v>365.75</v>
       </c>
       <c r="G7">
-        <v>-35.43</v>
+        <v>-36.56</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-4.2</v>
+        <v>-5.47</v>
       </c>
       <c r="J7">
-        <v>-8.93</v>
+        <v>-11.24</v>
       </c>
       <c r="K7">
-        <v>-11.26</v>
+        <v>-12.68</v>
       </c>
       <c r="L7">
-        <v>-36.41</v>
+        <v>-36.92</v>
       </c>
       <c r="M7">
-        <v>-1.19</v>
+        <v>-1.33</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="P7">
-        <v>384.38</v>
+        <v>380.15</v>
       </c>
       <c r="Q7">
-        <v>392.22</v>
+        <v>390.45</v>
       </c>
       <c r="R7">
-        <v>411.89</v>
+        <v>410.44</v>
       </c>
       <c r="S7">
-        <v>457.07</v>
+        <v>456.27</v>
       </c>
       <c r="T7">
-        <v>-18.1</v>
+        <v>-19.84</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,43 +1570,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>30.43</v>
+        <v>26.4</v>
       </c>
       <c r="Z7">
-        <v>-8.57</v>
+        <v>-9.65</v>
       </c>
       <c r="AA7">
-        <v>-8.279999999999999</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="AB7">
-        <v>-0.29</v>
+        <v>-1.09</v>
       </c>
       <c r="AC7">
-        <v>51.84</v>
+        <v>32.63</v>
       </c>
       <c r="AD7">
-        <v>68.2</v>
+        <v>53.27</v>
       </c>
       <c r="AE7">
-        <v>7.99</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AF7">
-        <v>30.89</v>
+        <v>35.91</v>
       </c>
       <c r="AG7">
-        <v>410.26</v>
+        <v>411.49</v>
       </c>
       <c r="AH7">
-        <v>374.18</v>
+        <v>369.41</v>
       </c>
       <c r="AI7">
-        <v>402.86</v>
+        <v>393.76</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>37.91</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>594.45</v>
+        <v>588.4</v>
       </c>
       <c r="D8">
-        <v>-2.81</v>
+        <v>-1.02</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1629,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-26.45</v>
+        <v>-27.2</v>
       </c>
       <c r="H8">
-        <v>27.09</v>
+        <v>25.8</v>
       </c>
       <c r="I8">
-        <v>-6.88</v>
+        <v>-6.04</v>
       </c>
       <c r="J8">
-        <v>-7.89</v>
+        <v>-7.56</v>
       </c>
       <c r="K8">
-        <v>-18.74</v>
+        <v>-19.84</v>
       </c>
       <c r="L8">
-        <v>-17.75</v>
+        <v>-11.79</v>
       </c>
       <c r="M8">
-        <v>-15.84</v>
+        <v>-16.11</v>
       </c>
       <c r="N8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O8">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P8">
-        <v>614</v>
+        <v>606.4299999999999</v>
       </c>
       <c r="Q8">
-        <v>611.09</v>
+        <v>609.45</v>
       </c>
       <c r="R8">
-        <v>639.4400000000001</v>
+        <v>636.95</v>
       </c>
       <c r="S8">
         <v>614.6</v>
       </c>
       <c r="T8">
-        <v>-3.28</v>
+        <v>-4.26</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1683,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>40.29</v>
+        <v>38.66</v>
       </c>
       <c r="Z8">
-        <v>-8.279999999999999</v>
+        <v>-9.66</v>
       </c>
       <c r="AA8">
-        <v>-9.98</v>
+        <v>-9.92</v>
       </c>
       <c r="AB8">
-        <v>1.7</v>
+        <v>0.26</v>
       </c>
       <c r="AC8">
-        <v>53.34</v>
+        <v>47.48</v>
       </c>
       <c r="AD8">
-        <v>59.9</v>
+        <v>54.02</v>
       </c>
       <c r="AE8">
-        <v>19.21</v>
+        <v>18.79</v>
       </c>
       <c r="AF8">
-        <v>-76.64</v>
+        <v>-76.98999999999999</v>
       </c>
       <c r="AG8">
-        <v>648.33</v>
+        <v>647.6900000000001</v>
       </c>
       <c r="AH8">
-        <v>573.85</v>
+        <v>571.21</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1710,7 +1719,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>32.49</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>180.66</v>
+        <v>178.75</v>
       </c>
       <c r="D9">
-        <v>-2</v>
+        <v>-1.06</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1742,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-34.92</v>
+        <v>-35.61</v>
       </c>
       <c r="H9">
-        <v>4.85</v>
+        <v>3.74</v>
       </c>
       <c r="I9">
-        <v>-1.58</v>
+        <v>-2.38</v>
       </c>
       <c r="J9">
-        <v>-9.550000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="K9">
-        <v>-1.61</v>
+        <v>-2.96</v>
       </c>
       <c r="L9">
-        <v>-30.54</v>
+        <v>-29.29</v>
       </c>
       <c r="M9">
-        <v>-8.17</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P9">
-        <v>183.79</v>
+        <v>182.92</v>
       </c>
       <c r="Q9">
-        <v>186.45</v>
+        <v>185.76</v>
       </c>
       <c r="R9">
-        <v>189.91</v>
+        <v>189.69</v>
       </c>
       <c r="S9">
-        <v>197.68</v>
+        <v>197.34</v>
       </c>
       <c r="T9">
-        <v>-8.609999999999999</v>
+        <v>-9.42</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,43 +1796,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>37.47</v>
+        <v>34.88</v>
       </c>
       <c r="Z9">
-        <v>-2.24</v>
+        <v>-2.55</v>
       </c>
       <c r="AA9">
-        <v>-1.94</v>
+        <v>-2.06</v>
       </c>
       <c r="AB9">
-        <v>-0.29</v>
+        <v>-0.49</v>
       </c>
       <c r="AC9">
-        <v>61.25</v>
+        <v>37.35</v>
       </c>
       <c r="AD9">
-        <v>73.5</v>
+        <v>61.13</v>
       </c>
       <c r="AE9">
-        <v>4.38</v>
+        <v>4.7</v>
       </c>
       <c r="AF9">
-        <v>-64.02</v>
+        <v>486.13</v>
       </c>
       <c r="AG9">
-        <v>193.69</v>
+        <v>193.17</v>
       </c>
       <c r="AH9">
-        <v>179.21</v>
+        <v>178.34</v>
       </c>
       <c r="AI9">
-        <v>195.23</v>
+        <v>191.11</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>22.59</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,55 +1843,55 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>69.11</v>
+        <v>69.06</v>
       </c>
       <c r="D10">
-        <v>-1.38</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E10">
-        <v>122.23</v>
+        <v>122.19</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-43.46</v>
+        <v>-43.48</v>
       </c>
       <c r="H10">
-        <v>16.58</v>
+        <v>16.5</v>
       </c>
       <c r="I10">
-        <v>-3.44</v>
+        <v>-4.49</v>
       </c>
       <c r="J10">
-        <v>-6.86</v>
+        <v>-6.38</v>
       </c>
       <c r="K10">
-        <v>-14.03</v>
+        <v>-14.59</v>
       </c>
       <c r="L10">
-        <v>-45.31</v>
+        <v>-43.5</v>
       </c>
       <c r="M10">
-        <v>-4.49</v>
+        <v>-4.32</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P10">
-        <v>70.51000000000001</v>
+        <v>69.86</v>
       </c>
       <c r="Q10">
-        <v>71.52</v>
+        <v>71.36</v>
       </c>
       <c r="R10">
-        <v>74.37</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="S10">
-        <v>79.98999999999999</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="T10">
         <v>-13.6</v>
@@ -1900,43 +1909,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>35.38</v>
+        <v>35.22</v>
       </c>
       <c r="Z10">
-        <v>-1.29</v>
+        <v>-1.34</v>
       </c>
       <c r="AA10">
-        <v>-1.23</v>
+        <v>-1.25</v>
       </c>
       <c r="AB10">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="AC10">
-        <v>29.32</v>
+        <v>23.78</v>
       </c>
       <c r="AD10">
-        <v>47.92</v>
+        <v>33.77</v>
       </c>
       <c r="AE10">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AF10">
-        <v>-36.59</v>
+        <v>-13.48</v>
       </c>
       <c r="AG10">
-        <v>74.23</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="AH10">
-        <v>68.81</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="AI10">
-        <v>76.63</v>
+        <v>76.48</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>25.33</v>
+        <v>27.03</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1260 +2144,1314 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-7.16</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-7.41</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.25</v>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-6.28</v>
+        <v>-7.41</v>
       </c>
       <c r="D8" s="6">
-        <v>-10.66</v>
+        <v>-7.95</v>
       </c>
       <c r="E8" s="7">
-        <v>-4.38</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.51</v>
+        <v>-10.66</v>
       </c>
       <c r="D9" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-6.53</v>
+        <v>-6.17</v>
+      </c>
+      <c r="E9" s="8">
+        <v>4.49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>5.7</v>
+        <v>-7.04</v>
       </c>
       <c r="D10" s="6">
-        <v>1.73</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-3.97</v>
+        <v>-3.89</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.15</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-2.15</v>
+        <v>1.73</v>
       </c>
       <c r="D11" s="6">
-        <v>-8.77</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-6.62</v>
+        <v>6.71</v>
+      </c>
+      <c r="E11" s="8">
+        <v>4.98</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-8.44</v>
+        <v>-8.77</v>
       </c>
       <c r="D12" s="6">
-        <v>-8.93</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.49</v>
+        <v>-7.68</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-4.98</v>
+        <v>-8.93</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.89</v>
+        <v>-11.24</v>
       </c>
       <c r="E13" s="7">
-        <v>-2.91</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-8.699999999999999</v>
+        <v>-7.89</v>
       </c>
       <c r="D14" s="6">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.85</v>
+        <v>-7.56</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.74</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="D15" s="6">
-        <v>-6.86</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.12</v>
+        <v>-8.93</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.62</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.85</v>
+        <v>-6.86</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.41</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.56</v>
+        <v>-6.38</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.43</v>
+        <v>-3.41</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.84</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.41</v>
+        <v>-2.88</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.53</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.84</v>
+        <v>-4.84</v>
       </c>
       <c r="D18" s="6">
-        <v>-5.26</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.42</v>
+        <v>-0.8</v>
+      </c>
+      <c r="E18" s="8">
+        <v>4.04</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.97</v>
+        <v>-5.26</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.43</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.46</v>
+        <v>-3.37</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.86</v>
+        <v>-2.43</v>
       </c>
       <c r="D20" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.18</v>
+        <v>1.5</v>
+      </c>
+      <c r="E20" s="8">
+        <v>3.93</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.16</v>
+        <v>-5.04</v>
       </c>
       <c r="D21" s="6">
-        <v>-4.2</v>
+        <v>-5.15</v>
       </c>
       <c r="E21" s="7">
-        <v>-3.04</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-7.42</v>
+        <v>-4.2</v>
       </c>
       <c r="D22" s="6">
-        <v>-6.88</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.54</v>
+        <v>-5.47</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.41</v>
+        <v>-6.88</v>
       </c>
       <c r="D23" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.17</v>
+        <v>-6.04</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.84</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.29</v>
+        <v>-1.58</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.44</v>
+        <v>-2.38</v>
       </c>
       <c r="E24" s="7">
-        <v>-1.15</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-33.93</v>
+        <v>-3.44</v>
       </c>
       <c r="D25" s="6">
-        <v>-35.03</v>
+        <v>-4.49</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.1</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>10.96</v>
+        <v>-35.03</v>
       </c>
       <c r="D26" s="6">
-        <v>5.83</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-5.13</v>
+        <v>-35</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.03</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>12.54</v>
+        <v>5.83</v>
       </c>
       <c r="D27" s="6">
-        <v>9.15</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.39</v>
+        <v>13.53</v>
+      </c>
+      <c r="E27" s="8">
+        <v>7.7</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>24.33</v>
+        <v>9.15</v>
       </c>
       <c r="D28" s="6">
-        <v>21.47</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.86</v>
+        <v>15.04</v>
+      </c>
+      <c r="E28" s="8">
+        <v>5.89</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>19.09</v>
+        <v>21.47</v>
       </c>
       <c r="D29" s="6">
-        <v>20.81</v>
+        <v>27.81</v>
       </c>
       <c r="E29" s="8">
-        <v>1.72</v>
+        <v>6.34</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-34.66</v>
+        <v>20.81</v>
       </c>
       <c r="D30" s="6">
-        <v>-36.41</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.75</v>
+        <v>35.85</v>
+      </c>
+      <c r="E30" s="8">
+        <v>15.04</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-21.63</v>
+        <v>-36.41</v>
       </c>
       <c r="D31" s="6">
-        <v>-17.75</v>
-      </c>
-      <c r="E31" s="8">
-        <v>3.88</v>
+        <v>-36.92</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-32</v>
+        <v>-17.75</v>
       </c>
       <c r="D32" s="6">
-        <v>-30.54</v>
+        <v>-11.79</v>
       </c>
       <c r="E32" s="8">
-        <v>1.46</v>
+        <v>5.96</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-46.42</v>
+        <v>-30.54</v>
       </c>
       <c r="D33" s="6">
-        <v>-45.31</v>
+        <v>-29.29</v>
       </c>
       <c r="E33" s="8">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-7.27</v>
+        <v>-45.31</v>
       </c>
       <c r="D34" s="6">
-        <v>-8.57</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.3</v>
+        <v>-43.5</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.81</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.55</v>
+        <v>-8.57</v>
       </c>
       <c r="D35" s="6">
-        <v>-6.75</v>
+        <v>-9.73</v>
       </c>
       <c r="E35" s="7">
-        <v>-5.2</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-13.7</v>
+        <v>-6.75</v>
       </c>
       <c r="D36" s="6">
-        <v>-17.24</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.54</v>
+        <v>-5.43</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.32</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>0.67</v>
+        <v>-17.24</v>
       </c>
       <c r="D37" s="6">
-        <v>-3.67</v>
+        <v>-17.92</v>
       </c>
       <c r="E37" s="7">
-        <v>-4.34</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-10.7</v>
+        <v>-3.67</v>
       </c>
       <c r="D38" s="6">
-        <v>-12.35</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.65</v>
+        <v>-1.42</v>
+      </c>
+      <c r="E38" s="8">
+        <v>2.25</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-9.529999999999999</v>
+        <v>-12.35</v>
       </c>
       <c r="D39" s="6">
-        <v>-11.26</v>
+        <v>-13.47</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.73</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-16.4</v>
+        <v>-11.26</v>
       </c>
       <c r="D40" s="6">
-        <v>-18.74</v>
+        <v>-12.68</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.34</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>0.91</v>
+        <v>-18.74</v>
       </c>
       <c r="D41" s="6">
-        <v>-1.61</v>
+        <v>-19.84</v>
       </c>
       <c r="E41" s="7">
-        <v>-2.52</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-12.8</v>
+        <v>-1.61</v>
       </c>
       <c r="D42" s="6">
-        <v>-14.03</v>
+        <v>-2.96</v>
       </c>
       <c r="E42" s="7">
-        <v>-1.23</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-35.02</v>
+        <v>-14.03</v>
       </c>
       <c r="D43" s="6">
-        <v>-36.22</v>
+        <v>-14.59</v>
       </c>
       <c r="E43" s="7">
-        <v>-1.2</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-9.199999999999999</v>
+        <v>-36.22</v>
       </c>
       <c r="D44" s="6">
-        <v>-11.86</v>
+        <v>-36.79</v>
       </c>
       <c r="E44" s="7">
-        <v>-2.66</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-19.19</v>
+        <v>-11.86</v>
       </c>
       <c r="D45" s="6">
-        <v>-23.03</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-3.84</v>
+        <v>-7.45</v>
+      </c>
+      <c r="E45" s="8">
+        <v>4.41</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-5.06</v>
+        <v>-23.03</v>
       </c>
       <c r="D46" s="6">
-        <v>-7.41</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.35</v>
+        <v>-21.47</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.56</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-18.54</v>
+        <v>-7.41</v>
       </c>
       <c r="D47" s="6">
-        <v>-21.2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.66</v>
+        <v>-3.25</v>
+      </c>
+      <c r="E47" s="8">
+        <v>4.16</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-34.8</v>
+        <v>-21.2</v>
       </c>
       <c r="D48" s="6">
-        <v>-35.43</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.63</v>
+        <v>-21.14</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.06</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-24.33</v>
+        <v>-35.43</v>
       </c>
       <c r="D49" s="6">
-        <v>-26.45</v>
+        <v>-36.56</v>
       </c>
       <c r="E49" s="7">
-        <v>-2.12</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-33.6</v>
+        <v>-26.45</v>
       </c>
       <c r="D50" s="6">
-        <v>-34.92</v>
+        <v>-27.2</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.32</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-44.54</v>
+        <v>-34.92</v>
       </c>
       <c r="D51" s="6">
-        <v>-43.46</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.08</v>
+        <v>-35.61</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>1236.4</v>
+        <v>-43.46</v>
       </c>
       <c r="D52" s="6">
-        <v>1213.5</v>
+        <v>-43.48</v>
       </c>
       <c r="E52" s="7">
-        <v>-22.9</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2916.5</v>
+        <v>1213.5</v>
       </c>
       <c r="D53" s="6">
-        <v>2831.1</v>
+        <v>1202.6</v>
       </c>
       <c r="E53" s="7">
-        <v>-85.40000000000001</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1296.6</v>
+        <v>2831.1</v>
       </c>
       <c r="D54" s="6">
-        <v>1235</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-61.6</v>
+        <v>2972.9</v>
+      </c>
+      <c r="E54" s="8">
+        <v>141.8</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1788</v>
+        <v>1235</v>
       </c>
       <c r="D55" s="6">
-        <v>1743.7</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-44.3</v>
+        <v>1260</v>
+      </c>
+      <c r="E55" s="8">
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>202.75</v>
+        <v>1743.7</v>
       </c>
       <c r="D56" s="6">
-        <v>196.14</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-6.61</v>
+        <v>1822</v>
+      </c>
+      <c r="E56" s="8">
+        <v>78.3</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>383.8</v>
+        <v>196.14</v>
       </c>
       <c r="D57" s="6">
-        <v>374.35</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-9.449999999999999</v>
+        <v>196.3</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.16</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>611.65</v>
+        <v>374.35</v>
       </c>
       <c r="D58" s="6">
-        <v>594.45</v>
+        <v>365.75</v>
       </c>
       <c r="E58" s="7">
-        <v>-17.2</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>184.34</v>
+        <v>594.45</v>
       </c>
       <c r="D59" s="6">
-        <v>180.66</v>
+        <v>588.4</v>
       </c>
       <c r="E59" s="7">
-        <v>-3.68</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>70.08</v>
+        <v>180.66</v>
       </c>
       <c r="D60" s="6">
-        <v>69.11</v>
+        <v>178.75</v>
       </c>
       <c r="E60" s="7">
-        <v>-0.97</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>38.52</v>
+        <v>69.11</v>
       </c>
       <c r="D61" s="6">
-        <v>33.21</v>
+        <v>69.06</v>
       </c>
       <c r="E61" s="7">
-        <v>-5.31</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>43.98</v>
+        <v>45</v>
       </c>
       <c r="D62" s="6">
-        <v>38.12</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-5.86</v>
+        <v>55</v>
+      </c>
+      <c r="E62" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>48.06</v>
+        <v>55</v>
       </c>
       <c r="D63" s="6">
-        <v>39.06</v>
+        <v>45</v>
       </c>
       <c r="E63" s="7">
-        <v>-9</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>56.93</v>
+        <v>33.21</v>
       </c>
       <c r="D64" s="6">
-        <v>49.79</v>
+        <v>31.02</v>
       </c>
       <c r="E64" s="7">
-        <v>-7.14</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>44.88</v>
+        <v>38.12</v>
       </c>
       <c r="D65" s="6">
-        <v>38.23</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-6.65</v>
+        <v>50.02</v>
+      </c>
+      <c r="E65" s="8">
+        <v>11.9</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>36.05</v>
+        <v>39.06</v>
       </c>
       <c r="D66" s="6">
-        <v>30.43</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-5.62</v>
+        <v>43.67</v>
+      </c>
+      <c r="E66" s="8">
+        <v>4.61</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>45.33</v>
+        <v>49.79</v>
       </c>
       <c r="D67" s="6">
-        <v>40.29</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-5.04</v>
+        <v>59.47</v>
+      </c>
+      <c r="E67" s="8">
+        <v>9.68</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>43.23</v>
+        <v>38.23</v>
       </c>
       <c r="D68" s="6">
-        <v>37.47</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-5.76</v>
+        <v>38.47</v>
+      </c>
+      <c r="E68" s="8">
+        <v>0.24</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>38.52</v>
+        <v>30.43</v>
       </c>
       <c r="D69" s="6">
-        <v>35.38</v>
+        <v>26.4</v>
       </c>
       <c r="E69" s="7">
-        <v>-3.14</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>-63.6</v>
+        <v>40.29</v>
       </c>
       <c r="D70" s="6">
-        <v>28.43</v>
-      </c>
-      <c r="E70" s="8">
-        <v>92.03</v>
+        <v>38.66</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>-72.47</v>
+        <v>37.47</v>
       </c>
       <c r="D71" s="6">
-        <v>-37.1</v>
-      </c>
-      <c r="E71" s="8">
-        <v>35.37</v>
+        <v>34.88</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>-32.71</v>
+        <v>35.38</v>
       </c>
       <c r="D72" s="6">
-        <v>32.36</v>
-      </c>
-      <c r="E72" s="8">
-        <v>65.06999999999999</v>
+        <v>35.22</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-64.61</v>
+        <v>28.43</v>
       </c>
       <c r="D73" s="6">
-        <v>-49.1</v>
+        <v>499.41</v>
       </c>
       <c r="E73" s="8">
-        <v>15.51</v>
+        <v>470.98</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-24.76</v>
+        <v>-37.1</v>
       </c>
       <c r="D74" s="6">
-        <v>5.2</v>
+        <v>63.13</v>
       </c>
       <c r="E74" s="8">
-        <v>29.96</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-11.77</v>
+        <v>32.36</v>
       </c>
       <c r="D75" s="6">
-        <v>30.89</v>
-      </c>
-      <c r="E75" s="8">
-        <v>42.66</v>
+        <v>13.51</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-18.85</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-79.2</v>
+        <v>-49.1</v>
       </c>
       <c r="D76" s="6">
-        <v>-76.64</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="E76" s="8">
-        <v>2.56</v>
+        <v>120.95</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-29.88</v>
+        <v>5.2</v>
       </c>
       <c r="D77" s="6">
-        <v>-64.02</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-34.14</v>
+        <v>78.69</v>
+      </c>
+      <c r="E77" s="8">
+        <v>73.48999999999999</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-64.05</v>
+        <v>30.89</v>
       </c>
       <c r="D78" s="6">
+        <v>35.91</v>
+      </c>
+      <c r="E78" s="8">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-76.64</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-76.98999999999999</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-64.02</v>
+      </c>
+      <c r="D80" s="6">
+        <v>486.13</v>
+      </c>
+      <c r="E80" s="8">
+        <v>550.15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
         <v>-36.59</v>
       </c>
-      <c r="E78" s="8">
-        <v>27.46</v>
+      <c r="D81" s="6">
+        <v>-13.48</v>
+      </c>
+      <c r="E81" s="8">
+        <v>23.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3412,28 +3475,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3447,16 +3510,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>38</v>
+        <v>39.8</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-7.3</v>
+        <v>-5.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-10.5</v>
+        <v>-10.9</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3593,31 +3656,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5918</v>
+        <v>0.5845</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1939</v>
+        <v>0.2033</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1379</v>
+        <v>0.1494</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0153</v>
+        <v>0.0205</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0119</v>
+        <v>-0.0133</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0449</v>
+        <v>-0.0432</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.08169999999999999</v>
+        <v>-0.08380000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1121</v>
+        <v>-0.1114</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1584</v>
+        <v>-0.1611</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,28 +193,34 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.4 → 35.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>26.4</t>
+  </si>
+  <si>
+    <t>35.3</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>38.1 → 50.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>38.1</t>
+    <t>50.0 → 45.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.0</t>
   </si>
   <si>
-    <t>49.8 → 59.5</t>
-  </si>
-  <si>
-    <t>49.8</t>
-  </si>
-  <si>
-    <t>59.5</t>
+    <t>45.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -416,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,10 +430,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -939,10 +946,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1202.6</v>
+        <v>1204.1</v>
       </c>
       <c r="D2">
-        <v>-0.9</v>
+        <v>0.12</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -951,25 +958,25 @@
         <v>1202.6</v>
       </c>
       <c r="G2">
-        <v>-36.79</v>
+        <v>-36.72</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="I2">
-        <v>-2.88</v>
+        <v>-3.78</v>
       </c>
       <c r="J2">
-        <v>-7.95</v>
+        <v>-5.67</v>
       </c>
       <c r="K2">
-        <v>-9.73</v>
+        <v>-10.85</v>
       </c>
       <c r="L2">
-        <v>-35</v>
+        <v>-34.59</v>
       </c>
       <c r="M2">
-        <v>-11.14</v>
+        <v>-10.99</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -978,19 +985,19 @@
         <v>20</v>
       </c>
       <c r="P2">
-        <v>1228</v>
+        <v>1218.54</v>
       </c>
       <c r="Q2">
-        <v>1248.16</v>
+        <v>1244.75</v>
       </c>
       <c r="R2">
-        <v>1302.26</v>
+        <v>1298.59</v>
       </c>
       <c r="S2">
-        <v>1445.07</v>
+        <v>1442.24</v>
       </c>
       <c r="T2">
-        <v>-16.78</v>
+        <v>-16.51</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,34 +1012,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.02</v>
+        <v>31.68</v>
       </c>
       <c r="Z2">
-        <v>-22.74</v>
+        <v>-23.65</v>
       </c>
       <c r="AA2">
-        <v>-21.64</v>
+        <v>-22.04</v>
       </c>
       <c r="AB2">
-        <v>-1.1</v>
+        <v>-1.61</v>
       </c>
       <c r="AC2">
-        <v>43.27</v>
+        <v>28.29</v>
       </c>
       <c r="AD2">
-        <v>60.7</v>
+        <v>43.67</v>
       </c>
       <c r="AE2">
-        <v>23.72</v>
+        <v>23.68</v>
       </c>
       <c r="AF2">
-        <v>499.41</v>
+        <v>-58.52</v>
       </c>
       <c r="AG2">
-        <v>1290.8</v>
+        <v>1290.08</v>
       </c>
       <c r="AH2">
-        <v>1205.52</v>
+        <v>1199.42</v>
       </c>
       <c r="AI2">
         <v>1277.47</v>
@@ -1041,7 +1048,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>22.2</v>
+        <v>24.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1059,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2972.9</v>
+        <v>2903.4</v>
       </c>
       <c r="D3">
-        <v>5.01</v>
+        <v>-2.34</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1064,25 +1071,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-7.45</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="H3">
-        <v>69.11</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="I3">
-        <v>-0.8</v>
+        <v>-3</v>
       </c>
       <c r="J3">
-        <v>-6.17</v>
+        <v>1.55</v>
       </c>
       <c r="K3">
-        <v>-5.43</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L3">
-        <v>13.53</v>
+        <v>12.74</v>
       </c>
       <c r="M3">
-        <v>14.94</v>
+        <v>14.67</v>
       </c>
       <c r="N3">
         <v>77</v>
@@ -1091,19 +1098,19 @@
         <v>65</v>
       </c>
       <c r="P3">
-        <v>2922.74</v>
+        <v>2904.78</v>
       </c>
       <c r="Q3">
-        <v>2955.86</v>
+        <v>2957.83</v>
       </c>
       <c r="R3">
-        <v>3004.41</v>
+        <v>2998.82</v>
       </c>
       <c r="S3">
-        <v>2565.85</v>
+        <v>2568.98</v>
       </c>
       <c r="T3">
-        <v>15.86</v>
+        <v>13.02</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1118,34 +1125,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>50.02</v>
+        <v>45.41</v>
       </c>
       <c r="Z3">
-        <v>-23.43</v>
+        <v>-25.25</v>
       </c>
       <c r="AA3">
-        <v>-18.04</v>
+        <v>-19.48</v>
       </c>
       <c r="AB3">
-        <v>-5.39</v>
+        <v>-5.77</v>
       </c>
       <c r="AC3">
-        <v>22.43</v>
+        <v>32.74</v>
       </c>
       <c r="AD3">
-        <v>15.49</v>
+        <v>19.47</v>
       </c>
       <c r="AE3">
-        <v>85.26000000000001</v>
+        <v>85.81</v>
       </c>
       <c r="AF3">
-        <v>63.13</v>
+        <v>-21</v>
       </c>
       <c r="AG3">
-        <v>3097.16</v>
+        <v>3094.76</v>
       </c>
       <c r="AH3">
-        <v>2814.56</v>
+        <v>2820.91</v>
       </c>
       <c r="AI3">
         <v>3101.6</v>
@@ -1154,7 +1161,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>22.42</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1172,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1260</v>
+        <v>1278</v>
       </c>
       <c r="D4">
-        <v>2.02</v>
+        <v>1.43</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1177,46 +1184,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-21.47</v>
+        <v>-20.35</v>
       </c>
       <c r="H4">
-        <v>63.04</v>
+        <v>65.37</v>
       </c>
       <c r="I4">
-        <v>-3.37</v>
+        <v>-1.76</v>
       </c>
       <c r="J4">
-        <v>-3.89</v>
+        <v>5.19</v>
       </c>
       <c r="K4">
-        <v>-17.92</v>
+        <v>-17.82</v>
       </c>
       <c r="L4">
-        <v>15.04</v>
+        <v>18.38</v>
       </c>
       <c r="M4">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="N4">
         <v>66</v>
       </c>
       <c r="O4">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>1274.52</v>
+        <v>1269.94</v>
       </c>
       <c r="Q4">
-        <v>1286.76</v>
+        <v>1287.41</v>
       </c>
       <c r="R4">
-        <v>1328</v>
+        <v>1322.72</v>
       </c>
       <c r="S4">
-        <v>1197.78</v>
+        <v>1199.08</v>
       </c>
       <c r="T4">
-        <v>5.19</v>
+        <v>6.58</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1231,34 +1238,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>43.67</v>
+        <v>46.79</v>
       </c>
       <c r="Z4">
-        <v>-16.12</v>
+        <v>-15.2</v>
       </c>
       <c r="AA4">
-        <v>-16.18</v>
+        <v>-15.98</v>
       </c>
       <c r="AB4">
-        <v>0.06</v>
+        <v>0.79</v>
       </c>
       <c r="AC4">
-        <v>30.47</v>
+        <v>28</v>
       </c>
       <c r="AD4">
-        <v>38.8</v>
+        <v>30.37</v>
       </c>
       <c r="AE4">
-        <v>38.27</v>
+        <v>37.99</v>
       </c>
       <c r="AF4">
-        <v>13.51</v>
+        <v>-0.67</v>
       </c>
       <c r="AG4">
-        <v>1332.24</v>
+        <v>1331.95</v>
       </c>
       <c r="AH4">
-        <v>1241.28</v>
+        <v>1242.87</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1267,7 +1274,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>22.45</v>
+        <v>21.08</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1285,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1822</v>
+        <v>1798.3</v>
       </c>
       <c r="D5">
-        <v>4.49</v>
+        <v>-1.3</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1290,25 +1297,25 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-3.25</v>
+        <v>-4.51</v>
       </c>
       <c r="H5">
-        <v>40.36</v>
+        <v>38.53</v>
       </c>
       <c r="I5">
-        <v>1.5</v>
+        <v>-0.5</v>
       </c>
       <c r="J5">
-        <v>6.71</v>
+        <v>12.88</v>
       </c>
       <c r="K5">
-        <v>-1.42</v>
+        <v>-4.51</v>
       </c>
       <c r="L5">
-        <v>27.81</v>
+        <v>28.33</v>
       </c>
       <c r="M5">
-        <v>20.33</v>
+        <v>20.15</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1317,19 +1324,19 @@
         <v>77</v>
       </c>
       <c r="P5">
-        <v>1789.26</v>
+        <v>1787.46</v>
       </c>
       <c r="Q5">
-        <v>1748.71</v>
+        <v>1756.25</v>
       </c>
       <c r="R5">
-        <v>1724.44</v>
+        <v>1723.47</v>
       </c>
       <c r="S5">
-        <v>1623.68</v>
+        <v>1625.18</v>
       </c>
       <c r="T5">
-        <v>12.21</v>
+        <v>10.65</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1344,34 +1351,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>59.47</v>
+        <v>55.95</v>
       </c>
       <c r="Z5">
-        <v>22.43</v>
+        <v>22.72</v>
       </c>
       <c r="AA5">
-        <v>17.54</v>
+        <v>18.58</v>
       </c>
       <c r="AB5">
-        <v>4.89</v>
+        <v>4.15</v>
       </c>
       <c r="AC5">
-        <v>40.13</v>
+        <v>37.1</v>
       </c>
       <c r="AD5">
-        <v>44.47</v>
+        <v>37.12</v>
       </c>
       <c r="AE5">
-        <v>42.88</v>
+        <v>43.14</v>
       </c>
       <c r="AF5">
-        <v>71.84999999999999</v>
+        <v>28.62</v>
       </c>
       <c r="AG5">
-        <v>1849.48</v>
+        <v>1847.23</v>
       </c>
       <c r="AH5">
-        <v>1647.94</v>
+        <v>1665.27</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1380,7 +1387,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>26.77</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1398,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>196.3</v>
+        <v>204</v>
       </c>
       <c r="D6">
-        <v>0.08</v>
+        <v>3.92</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1403,46 +1410,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-21.14</v>
+        <v>-18.04</v>
       </c>
       <c r="H6">
-        <v>47.64</v>
+        <v>53.43</v>
       </c>
       <c r="I6">
-        <v>-5.15</v>
+        <v>-0.39</v>
       </c>
       <c r="J6">
-        <v>-7.68</v>
+        <v>3.03</v>
       </c>
       <c r="K6">
-        <v>-13.47</v>
+        <v>-9.15</v>
       </c>
       <c r="L6">
-        <v>35.85</v>
+        <v>36.91</v>
       </c>
       <c r="M6">
-        <v>58.45</v>
+        <v>60.07</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>199.89</v>
+        <v>199.73</v>
       </c>
       <c r="Q6">
-        <v>205.43</v>
+        <v>205.41</v>
       </c>
       <c r="R6">
-        <v>207.54</v>
+        <v>207.21</v>
       </c>
       <c r="S6">
-        <v>187.53</v>
+        <v>187.85</v>
       </c>
       <c r="T6">
-        <v>4.68</v>
+        <v>8.6</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1457,34 +1464,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.47</v>
+        <v>48.7</v>
       </c>
       <c r="Z6">
-        <v>-2.54</v>
+        <v>-2.23</v>
       </c>
       <c r="AA6">
-        <v>-1.54</v>
+        <v>-1.68</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>-0.55</v>
       </c>
       <c r="AC6">
-        <v>9.75</v>
+        <v>20.75</v>
       </c>
       <c r="AD6">
-        <v>12.01</v>
+        <v>13.28</v>
       </c>
       <c r="AE6">
-        <v>5.89</v>
+        <v>6.06</v>
       </c>
       <c r="AF6">
-        <v>78.69</v>
+        <v>6.27</v>
       </c>
       <c r="AG6">
-        <v>215.08</v>
+        <v>215.07</v>
       </c>
       <c r="AH6">
-        <v>195.79</v>
+        <v>195.76</v>
       </c>
       <c r="AI6">
         <v>213.83</v>
@@ -1493,7 +1500,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>28.45</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,58 +1511,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>365.75</v>
+        <v>374</v>
       </c>
       <c r="D7">
-        <v>-2.3</v>
+        <v>2.26</v>
       </c>
       <c r="E7">
-        <v>576.55</v>
+        <v>574.36</v>
       </c>
       <c r="F7">
         <v>365.75</v>
       </c>
       <c r="G7">
-        <v>-36.56</v>
+        <v>-34.88</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="I7">
-        <v>-5.47</v>
+        <v>-4.77</v>
       </c>
       <c r="J7">
-        <v>-11.24</v>
+        <v>-6.77</v>
       </c>
       <c r="K7">
-        <v>-12.68</v>
+        <v>-12.81</v>
       </c>
       <c r="L7">
-        <v>-36.92</v>
+        <v>-35.13</v>
       </c>
       <c r="M7">
-        <v>-1.33</v>
+        <v>-0.58</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P7">
-        <v>380.15</v>
+        <v>376.4</v>
       </c>
       <c r="Q7">
-        <v>390.45</v>
+        <v>389.04</v>
       </c>
       <c r="R7">
-        <v>410.44</v>
+        <v>409.11</v>
       </c>
       <c r="S7">
-        <v>456.27</v>
+        <v>455.47</v>
       </c>
       <c r="T7">
-        <v>-19.84</v>
+        <v>-17.89</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1570,34 +1577,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>26.4</v>
+        <v>35.26</v>
       </c>
       <c r="Z7">
-        <v>-9.65</v>
+        <v>-9.73</v>
       </c>
       <c r="AA7">
-        <v>-8.550000000000001</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AB7">
-        <v>-1.09</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AC7">
-        <v>32.63</v>
+        <v>31.09</v>
       </c>
       <c r="AD7">
-        <v>53.27</v>
+        <v>38.52</v>
       </c>
       <c r="AE7">
-        <v>8.029999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="AF7">
-        <v>35.91</v>
+        <v>153.14</v>
       </c>
       <c r="AG7">
-        <v>411.49</v>
+        <v>410.54</v>
       </c>
       <c r="AH7">
-        <v>369.41</v>
+        <v>367.54</v>
       </c>
       <c r="AI7">
         <v>393.76</v>
@@ -1606,7 +1613,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>41.99</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1624,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>588.4</v>
+        <v>593.9</v>
       </c>
       <c r="D8">
-        <v>-1.02</v>
+        <v>0.93</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1629,46 +1636,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-27.2</v>
+        <v>-26.52</v>
       </c>
       <c r="H8">
-        <v>25.8</v>
+        <v>26.97</v>
       </c>
       <c r="I8">
-        <v>-6.04</v>
+        <v>-5.01</v>
       </c>
       <c r="J8">
-        <v>-7.56</v>
+        <v>-4.39</v>
       </c>
       <c r="K8">
-        <v>-19.84</v>
+        <v>-19.03</v>
       </c>
       <c r="L8">
-        <v>-11.79</v>
+        <v>-11.55</v>
       </c>
       <c r="M8">
-        <v>-16.11</v>
+        <v>-16.01</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="P8">
-        <v>606.4299999999999</v>
+        <v>600.16</v>
       </c>
       <c r="Q8">
-        <v>609.45</v>
+        <v>608.47</v>
       </c>
       <c r="R8">
-        <v>636.95</v>
+        <v>634.8200000000001</v>
       </c>
       <c r="S8">
-        <v>614.6</v>
+        <v>614.63</v>
       </c>
       <c r="T8">
-        <v>-4.26</v>
+        <v>-3.37</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,34 +1690,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>38.66</v>
+        <v>41</v>
       </c>
       <c r="Z8">
-        <v>-9.66</v>
+        <v>-10.19</v>
       </c>
       <c r="AA8">
-        <v>-9.92</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="AB8">
-        <v>0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="AC8">
-        <v>47.48</v>
+        <v>43.79</v>
       </c>
       <c r="AD8">
-        <v>54.02</v>
+        <v>48.2</v>
       </c>
       <c r="AE8">
-        <v>18.79</v>
+        <v>18.49</v>
       </c>
       <c r="AF8">
-        <v>-76.98999999999999</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="AG8">
-        <v>647.6900000000001</v>
+        <v>647.27</v>
       </c>
       <c r="AH8">
-        <v>571.21</v>
+        <v>569.66</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1719,7 +1726,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>29.87</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,10 +1737,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>178.75</v>
+        <v>177.68</v>
       </c>
       <c r="D9">
-        <v>-1.06</v>
+        <v>-0.6</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1742,46 +1749,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-35.61</v>
+        <v>-35.99</v>
       </c>
       <c r="H9">
-        <v>3.74</v>
+        <v>3.12</v>
       </c>
       <c r="I9">
-        <v>-2.38</v>
+        <v>-4.57</v>
       </c>
       <c r="J9">
-        <v>-8.93</v>
+        <v>-7.72</v>
       </c>
       <c r="K9">
-        <v>-2.96</v>
+        <v>-3.41</v>
       </c>
       <c r="L9">
-        <v>-29.29</v>
+        <v>-32.09</v>
       </c>
       <c r="M9">
-        <v>-8.380000000000001</v>
+        <v>-8.49</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="P9">
-        <v>182.92</v>
+        <v>181.22</v>
       </c>
       <c r="Q9">
-        <v>185.76</v>
+        <v>184.92</v>
       </c>
       <c r="R9">
-        <v>189.69</v>
+        <v>189.37</v>
       </c>
       <c r="S9">
-        <v>197.34</v>
+        <v>196.99</v>
       </c>
       <c r="T9">
-        <v>-9.42</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1796,34 +1803,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>34.88</v>
+        <v>33.48</v>
       </c>
       <c r="Z9">
-        <v>-2.55</v>
+        <v>-2.85</v>
       </c>
       <c r="AA9">
-        <v>-2.06</v>
+        <v>-2.22</v>
       </c>
       <c r="AB9">
-        <v>-0.49</v>
+        <v>-0.63</v>
       </c>
       <c r="AC9">
-        <v>37.35</v>
+        <v>12.34</v>
       </c>
       <c r="AD9">
-        <v>61.13</v>
+        <v>36.98</v>
       </c>
       <c r="AE9">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="AF9">
-        <v>486.13</v>
+        <v>-58.94</v>
       </c>
       <c r="AG9">
-        <v>193.17</v>
+        <v>192</v>
       </c>
       <c r="AH9">
-        <v>178.34</v>
+        <v>177.84</v>
       </c>
       <c r="AI9">
         <v>191.11</v>
@@ -1832,7 +1839,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>26.18</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,37 +1850,37 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>69.06</v>
+        <v>69.14</v>
       </c>
       <c r="D10">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="E10">
-        <v>122.19</v>
+        <v>119.02</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-43.48</v>
+        <v>-41.91</v>
       </c>
       <c r="H10">
-        <v>16.5</v>
+        <v>16.63</v>
       </c>
       <c r="I10">
-        <v>-4.49</v>
+        <v>-2.77</v>
       </c>
       <c r="J10">
-        <v>-6.38</v>
+        <v>-4.24</v>
       </c>
       <c r="K10">
-        <v>-14.59</v>
+        <v>-15.19</v>
       </c>
       <c r="L10">
-        <v>-43.5</v>
+        <v>-43.42</v>
       </c>
       <c r="M10">
-        <v>-4.32</v>
+        <v>-4.33</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1882,19 +1889,19 @@
         <v>11</v>
       </c>
       <c r="P10">
-        <v>69.86</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="Q10">
-        <v>71.36</v>
+        <v>71.25</v>
       </c>
       <c r="R10">
-        <v>74.15000000000001</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="S10">
-        <v>79.93000000000001</v>
+        <v>79.87</v>
       </c>
       <c r="T10">
-        <v>-13.6</v>
+        <v>-13.43</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1909,43 +1916,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>35.22</v>
+        <v>35.72</v>
       </c>
       <c r="Z10">
-        <v>-1.34</v>
+        <v>-1.36</v>
       </c>
       <c r="AA10">
-        <v>-1.25</v>
+        <v>-1.27</v>
       </c>
       <c r="AB10">
         <v>-0.09</v>
       </c>
       <c r="AC10">
-        <v>23.78</v>
+        <v>16.75</v>
       </c>
       <c r="AD10">
-        <v>33.77</v>
+        <v>23.28</v>
       </c>
       <c r="AE10">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AF10">
-        <v>-13.48</v>
+        <v>-46.92</v>
       </c>
       <c r="AG10">
-        <v>74.26000000000001</v>
+        <v>74.31</v>
       </c>
       <c r="AH10">
-        <v>68.45999999999999</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AI10">
-        <v>76.48</v>
+        <v>76.17</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>27.03</v>
+        <v>29.3</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2126,7 +2133,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2145,28 +2152,28 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>64</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2178,1274 +2185,1240 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-7.41</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="7">
         <v>-7.95</v>
       </c>
-      <c r="E8" s="7">
-        <v>-0.54</v>
+      <c r="D8" s="7">
+        <v>-5.67</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-10.66</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="7">
         <v>-6.17</v>
       </c>
+      <c r="D9" s="7">
+        <v>1.55</v>
+      </c>
       <c r="E9" s="8">
-        <v>4.49</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="7">
         <v>-3.89</v>
       </c>
+      <c r="D10" s="7">
+        <v>5.19</v>
+      </c>
       <c r="E10" s="8">
-        <v>3.15</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>1.73</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="7">
         <v>6.71</v>
       </c>
+      <c r="D11" s="7">
+        <v>12.88</v>
+      </c>
       <c r="E11" s="8">
-        <v>4.98</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-8.77</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="7">
         <v>-7.68</v>
       </c>
+      <c r="D12" s="7">
+        <v>3.03</v>
+      </c>
       <c r="E12" s="8">
-        <v>1.09</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
+        <v>-11.24</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-6.77</v>
+      </c>
+      <c r="E13" s="8">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-7.56</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-4.39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
         <v>-8.93</v>
       </c>
-      <c r="D13" s="6">
-        <v>-11.24</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-7.72</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-6.38</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-4.24</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-2.88</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-3.78</v>
+      </c>
+      <c r="E17" s="9">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-0.8</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-3</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-3.37</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.76</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-0.5</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-5.15</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-0.39</v>
+      </c>
+      <c r="E21" s="8">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-5.47</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-4.77</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-7.89</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-7.56</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-6.04</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-5.01</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-8.93</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-2.38</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-4.57</v>
+      </c>
+      <c r="E24" s="9">
+        <v>-2.19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-6.86</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-4.49</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-2.77</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-35</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-34.59</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>13.53</v>
+      </c>
+      <c r="D27" s="7">
+        <v>12.74</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>15.04</v>
+      </c>
+      <c r="D28" s="7">
+        <v>18.38</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>27.81</v>
+      </c>
+      <c r="D29" s="7">
+        <v>28.33</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>35.85</v>
+      </c>
+      <c r="D30" s="7">
+        <v>36.91</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-36.92</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-35.13</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-11.79</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-11.55</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-29.29</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-32.09</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-43.5</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-43.42</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-9.73</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-10.85</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-5.43</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-17.92</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-17.82</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-1.42</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-4.51</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-13.47</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-9.15</v>
+      </c>
+      <c r="E39" s="8">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-12.68</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-12.81</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-19.84</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-19.03</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-2.96</v>
+      </c>
+      <c r="D42" s="7">
         <v>-3.41</v>
       </c>
-      <c r="D17" s="6">
-        <v>-2.88</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="E42" s="9">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-14.59</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-15.19</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-36.79</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-36.72</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-4.84</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.8</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-7.45</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-5.26</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.37</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-21.47</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-20.35</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.43</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-3.25</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-4.51</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-21.14</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-18.04</v>
+      </c>
+      <c r="E48" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-36.56</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-34.88</v>
+      </c>
+      <c r="E49" s="8">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-27.2</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-26.52</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-35.61</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-35.99</v>
+      </c>
+      <c r="E51" s="9">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-43.48</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-41.91</v>
+      </c>
+      <c r="E52" s="8">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1202.6</v>
+      </c>
+      <c r="D53" s="7">
+        <v>1204.1</v>
+      </c>
+      <c r="E53" s="8">
         <v>1.5</v>
       </c>
-      <c r="E20" s="8">
-        <v>3.93</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>2972.9</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2903.4</v>
+      </c>
+      <c r="E54" s="9">
+        <v>-69.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1260</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1278</v>
+      </c>
+      <c r="E55" s="8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1822</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1798.3</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-23.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-5.04</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-5.15</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>196.3</v>
+      </c>
+      <c r="D57" s="7">
+        <v>204</v>
+      </c>
+      <c r="E57" s="8">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-4.2</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>365.75</v>
+      </c>
+      <c r="D58" s="7">
+        <v>374</v>
+      </c>
+      <c r="E58" s="8">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-6.88</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-6.04</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>588.4</v>
+      </c>
+      <c r="D59" s="7">
+        <v>593.9</v>
+      </c>
+      <c r="E59" s="8">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.38</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>178.75</v>
+      </c>
+      <c r="D60" s="7">
+        <v>177.68</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-3.44</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>69.06</v>
+      </c>
+      <c r="D61" s="7">
+        <v>69.14</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-35.03</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-35</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>31.02</v>
+      </c>
+      <c r="D62" s="7">
+        <v>31.68</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>5.83</v>
-      </c>
-      <c r="D27" s="6">
-        <v>13.53</v>
-      </c>
-      <c r="E27" s="8">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>50.02</v>
+      </c>
+      <c r="D63" s="7">
+        <v>45.41</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-4.61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>9.15</v>
-      </c>
-      <c r="D28" s="6">
-        <v>15.04</v>
-      </c>
-      <c r="E28" s="8">
-        <v>5.89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>43.67</v>
+      </c>
+      <c r="D64" s="7">
+        <v>46.79</v>
+      </c>
+      <c r="E64" s="8">
+        <v>3.12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>21.47</v>
-      </c>
-      <c r="D29" s="6">
-        <v>27.81</v>
-      </c>
-      <c r="E29" s="8">
-        <v>6.34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>59.47</v>
+      </c>
+      <c r="D65" s="7">
+        <v>55.95</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-3.52</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>20.81</v>
-      </c>
-      <c r="D30" s="6">
-        <v>35.85</v>
-      </c>
-      <c r="E30" s="8">
-        <v>15.04</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>38.47</v>
+      </c>
+      <c r="D66" s="7">
+        <v>48.7</v>
+      </c>
+      <c r="E66" s="8">
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-36.41</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-36.92</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>26.4</v>
+      </c>
+      <c r="D67" s="7">
+        <v>35.26</v>
+      </c>
+      <c r="E67" s="8">
+        <v>8.859999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-17.75</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-11.79</v>
-      </c>
-      <c r="E32" s="8">
-        <v>5.96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>38.66</v>
+      </c>
+      <c r="D68" s="7">
+        <v>41</v>
+      </c>
+      <c r="E68" s="8">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-30.54</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-29.29</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>34.88</v>
+      </c>
+      <c r="D69" s="7">
+        <v>33.48</v>
+      </c>
+      <c r="E69" s="9">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-45.31</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-43.5</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>35.22</v>
+      </c>
+      <c r="D70" s="7">
+        <v>35.72</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-8.57</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-9.73</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>499.41</v>
+      </c>
+      <c r="D71" s="7">
+        <v>-58.52</v>
+      </c>
+      <c r="E71" s="9">
+        <v>-557.9299999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-6.75</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-5.43</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>63.13</v>
+      </c>
+      <c r="D72" s="7">
+        <v>-21</v>
+      </c>
+      <c r="E72" s="9">
+        <v>-84.13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-17.24</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-17.92</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.68</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>13.51</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-0.67</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-14.18</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-1.42</v>
-      </c>
-      <c r="E38" s="8">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="D74" s="7">
+        <v>28.62</v>
+      </c>
+      <c r="E74" s="9">
+        <v>-43.23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-12.35</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-13.47</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>78.69</v>
+      </c>
+      <c r="D75" s="7">
+        <v>6.27</v>
+      </c>
+      <c r="E75" s="9">
+        <v>-72.42</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-11.26</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-12.68</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>35.91</v>
+      </c>
+      <c r="D76" s="7">
+        <v>153.14</v>
+      </c>
+      <c r="E76" s="8">
+        <v>117.23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-18.74</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-19.84</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-76.98999999999999</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-76.59999999999999</v>
+      </c>
+      <c r="E77" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-1.61</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-2.96</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>486.13</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-58.94</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-545.0700000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-14.03</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-14.59</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-36.22</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-36.79</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-11.86</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-7.45</v>
-      </c>
-      <c r="E45" s="8">
-        <v>4.41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-23.03</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-21.47</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-7.41</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-3.25</v>
-      </c>
-      <c r="E47" s="8">
-        <v>4.16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-21.2</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-21.14</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-35.43</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-36.56</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-26.45</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-27.2</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-34.92</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-35.61</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-43.46</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-43.48</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1213.5</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1202.6</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-10.9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>2831.1</v>
-      </c>
-      <c r="D54" s="6">
-        <v>2972.9</v>
-      </c>
-      <c r="E54" s="8">
-        <v>141.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1235</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1260</v>
-      </c>
-      <c r="E55" s="8">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1743.7</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1822</v>
-      </c>
-      <c r="E56" s="8">
-        <v>78.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>196.14</v>
-      </c>
-      <c r="D57" s="6">
-        <v>196.3</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>374.35</v>
-      </c>
-      <c r="D58" s="6">
-        <v>365.75</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-8.6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>594.45</v>
-      </c>
-      <c r="D59" s="6">
-        <v>588.4</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-6.05</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>180.66</v>
-      </c>
-      <c r="D60" s="6">
-        <v>178.75</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>69.11</v>
-      </c>
-      <c r="D61" s="6">
-        <v>69.06</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>45</v>
-      </c>
-      <c r="D62" s="6">
-        <v>55</v>
-      </c>
-      <c r="E62" s="8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>55</v>
-      </c>
-      <c r="D63" s="6">
-        <v>45</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>33.21</v>
-      </c>
-      <c r="D64" s="6">
-        <v>31.02</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>38.12</v>
-      </c>
-      <c r="D65" s="6">
-        <v>50.02</v>
-      </c>
-      <c r="E65" s="8">
-        <v>11.9</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>39.06</v>
-      </c>
-      <c r="D66" s="6">
-        <v>43.67</v>
-      </c>
-      <c r="E66" s="8">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>49.79</v>
-      </c>
-      <c r="D67" s="6">
-        <v>59.47</v>
-      </c>
-      <c r="E67" s="8">
-        <v>9.68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>38.23</v>
-      </c>
-      <c r="D68" s="6">
-        <v>38.47</v>
-      </c>
-      <c r="E68" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>30.43</v>
-      </c>
-      <c r="D69" s="6">
-        <v>26.4</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>40.29</v>
-      </c>
-      <c r="D70" s="6">
-        <v>38.66</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>37.47</v>
-      </c>
-      <c r="D71" s="6">
-        <v>34.88</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-2.59</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>35.38</v>
-      </c>
-      <c r="D72" s="6">
-        <v>35.22</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="B79" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="6">
-        <v>28.43</v>
-      </c>
-      <c r="D73" s="6">
-        <v>499.41</v>
-      </c>
-      <c r="E73" s="8">
-        <v>470.98</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-37.1</v>
-      </c>
-      <c r="D74" s="6">
-        <v>63.13</v>
-      </c>
-      <c r="E74" s="8">
-        <v>100.23</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>32.36</v>
-      </c>
-      <c r="D75" s="6">
-        <v>13.51</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-18.85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-49.1</v>
-      </c>
-      <c r="D76" s="6">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="E76" s="8">
-        <v>120.95</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="D77" s="6">
-        <v>78.69</v>
-      </c>
-      <c r="E77" s="8">
-        <v>73.48999999999999</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>30.89</v>
-      </c>
-      <c r="D78" s="6">
-        <v>35.91</v>
-      </c>
-      <c r="E78" s="8">
-        <v>5.02</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-76.64</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-76.98999999999999</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-64.02</v>
-      </c>
-      <c r="D80" s="6">
-        <v>486.13</v>
-      </c>
-      <c r="E80" s="8">
-        <v>550.15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-36.59</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="C79" s="7">
         <v>-13.48</v>
       </c>
-      <c r="E81" s="8">
-        <v>23.11</v>
+      <c r="D79" s="7">
+        <v>-46.92</v>
+      </c>
+      <c r="E79" s="9">
+        <v>-33.44</v>
       </c>
     </row>
   </sheetData>
@@ -3471,60 +3444,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>77</v>
       </c>
+      <c r="H1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>48.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>41.6</v>
+      </c>
+      <c r="E2" s="12">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-10.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-0.7</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-11.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>10</v>
       </c>
     </row>
@@ -3626,61 +3599,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.5845</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2033</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1494</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0205</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.0133</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0432</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.08380000000000001</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1114</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1611</v>
+      <c r="A2" s="15">
+        <v>0.6007</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2015</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1467</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0219</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.0058</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0433</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.0849</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.1099</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1601</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.4 → 35.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>26.4</t>
-  </si>
-  <si>
-    <t>35.3</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.0 → 45.4</t>
+    <t>56.0 → 48.1</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.0</t>
-  </si>
-  <si>
-    <t>45.4</t>
+    <t>56.0</t>
+  </si>
+  <si>
+    <t>48.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -306,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -346,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -430,7 +415,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -946,58 +930,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1204.1</v>
+        <v>1182.8</v>
       </c>
       <c r="D2">
-        <v>0.12</v>
+        <v>-1.77</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1202.6</v>
+        <v>1182.8</v>
       </c>
       <c r="G2">
-        <v>-36.72</v>
+        <v>-37.84</v>
       </c>
       <c r="H2">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-3.78</v>
+        <v>-4.31</v>
       </c>
       <c r="J2">
-        <v>-5.67</v>
+        <v>-7.03</v>
       </c>
       <c r="K2">
-        <v>-10.85</v>
+        <v>-15.14</v>
       </c>
       <c r="L2">
-        <v>-34.59</v>
+        <v>-34.79</v>
       </c>
       <c r="M2">
-        <v>-10.99</v>
+        <v>-11.17</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P2">
-        <v>1218.54</v>
+        <v>1207.88</v>
       </c>
       <c r="Q2">
-        <v>1244.75</v>
+        <v>1240.56</v>
       </c>
       <c r="R2">
-        <v>1298.59</v>
+        <v>1295.07</v>
       </c>
       <c r="S2">
-        <v>1442.24</v>
+        <v>1439.35</v>
       </c>
       <c r="T2">
-        <v>-16.51</v>
+        <v>-17.82</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1012,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>31.68</v>
+        <v>27.59</v>
       </c>
       <c r="Z2">
-        <v>-23.65</v>
+        <v>-25.79</v>
       </c>
       <c r="AA2">
-        <v>-22.04</v>
+        <v>-22.79</v>
       </c>
       <c r="AB2">
-        <v>-1.61</v>
+        <v>-3</v>
       </c>
       <c r="AC2">
-        <v>28.29</v>
+        <v>16.14</v>
       </c>
       <c r="AD2">
-        <v>43.67</v>
+        <v>29.23</v>
       </c>
       <c r="AE2">
-        <v>23.68</v>
+        <v>24.71</v>
       </c>
       <c r="AF2">
-        <v>-58.52</v>
+        <v>2.24</v>
       </c>
       <c r="AG2">
-        <v>1290.08</v>
+        <v>1292.41</v>
       </c>
       <c r="AH2">
-        <v>1199.42</v>
+        <v>1188.71</v>
       </c>
       <c r="AI2">
-        <v>1277.47</v>
+        <v>1259.12</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>24.87</v>
+        <v>29.74</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1059,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2903.4</v>
+        <v>2816.8</v>
       </c>
       <c r="D3">
-        <v>-2.34</v>
+        <v>-2.98</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1071,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-9.609999999999999</v>
+        <v>-12.31</v>
       </c>
       <c r="H3">
-        <v>65.15000000000001</v>
+        <v>60.23</v>
       </c>
       <c r="I3">
-        <v>-3</v>
+        <v>-2.87</v>
       </c>
       <c r="J3">
-        <v>1.55</v>
+        <v>-1.64</v>
       </c>
       <c r="K3">
-        <v>-8.630000000000001</v>
+        <v>-12.31</v>
       </c>
       <c r="L3">
-        <v>12.74</v>
+        <v>10.79</v>
       </c>
       <c r="M3">
-        <v>14.67</v>
+        <v>14.12</v>
       </c>
       <c r="N3">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="O3">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>2904.78</v>
+        <v>2888.14</v>
       </c>
       <c r="Q3">
-        <v>2957.83</v>
+        <v>2954.08</v>
       </c>
       <c r="R3">
-        <v>2998.82</v>
+        <v>2992.2</v>
       </c>
       <c r="S3">
-        <v>2568.98</v>
+        <v>2571.66</v>
       </c>
       <c r="T3">
-        <v>13.02</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1125,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.41</v>
+        <v>40.41</v>
       </c>
       <c r="Z3">
-        <v>-25.25</v>
+        <v>-33.3</v>
       </c>
       <c r="AA3">
-        <v>-19.48</v>
+        <v>-22.24</v>
       </c>
       <c r="AB3">
-        <v>-5.77</v>
+        <v>-11.06</v>
       </c>
       <c r="AC3">
-        <v>32.74</v>
+        <v>37.43</v>
       </c>
       <c r="AD3">
-        <v>19.47</v>
+        <v>30.87</v>
       </c>
       <c r="AE3">
-        <v>85.81</v>
+        <v>89.08</v>
       </c>
       <c r="AF3">
-        <v>-21</v>
+        <v>32.94</v>
       </c>
       <c r="AG3">
-        <v>3094.76</v>
+        <v>3102.27</v>
       </c>
       <c r="AH3">
-        <v>2820.91</v>
+        <v>2805.9</v>
       </c>
       <c r="AI3">
         <v>3101.6</v>
@@ -1161,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>22.14</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1172,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1278</v>
+        <v>1276.1</v>
       </c>
       <c r="D4">
-        <v>1.43</v>
+        <v>-0.15</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1184,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-20.35</v>
+        <v>-20.47</v>
       </c>
       <c r="H4">
-        <v>65.37</v>
+        <v>65.13</v>
       </c>
       <c r="I4">
-        <v>-1.76</v>
+        <v>-0.31</v>
       </c>
       <c r="J4">
-        <v>5.19</v>
+        <v>0.88</v>
       </c>
       <c r="K4">
-        <v>-17.82</v>
+        <v>-18</v>
       </c>
       <c r="L4">
-        <v>18.38</v>
+        <v>21.84</v>
       </c>
       <c r="M4">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="N4">
+        <v>77</v>
+      </c>
+      <c r="O4">
         <v>66</v>
       </c>
-      <c r="O4">
-        <v>64</v>
-      </c>
       <c r="P4">
-        <v>1269.94</v>
+        <v>1269.14</v>
       </c>
       <c r="Q4">
-        <v>1287.41</v>
+        <v>1286.41</v>
       </c>
       <c r="R4">
-        <v>1322.72</v>
+        <v>1318.8</v>
       </c>
       <c r="S4">
-        <v>1199.08</v>
+        <v>1200.26</v>
       </c>
       <c r="T4">
-        <v>6.58</v>
+        <v>6.32</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1238,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>46.79</v>
+        <v>46.5</v>
       </c>
       <c r="Z4">
-        <v>-15.2</v>
+        <v>-14.45</v>
       </c>
       <c r="AA4">
-        <v>-15.98</v>
+        <v>-15.67</v>
       </c>
       <c r="AB4">
-        <v>0.79</v>
+        <v>1.23</v>
       </c>
       <c r="AC4">
-        <v>28</v>
+        <v>44.88</v>
       </c>
       <c r="AD4">
-        <v>30.37</v>
+        <v>34.45</v>
       </c>
       <c r="AE4">
-        <v>37.99</v>
+        <v>37.97</v>
       </c>
       <c r="AF4">
-        <v>-0.67</v>
+        <v>348.82</v>
       </c>
       <c r="AG4">
-        <v>1331.95</v>
+        <v>1331.03</v>
       </c>
       <c r="AH4">
-        <v>1242.87</v>
+        <v>1241.8</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1274,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>21.08</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1285,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1798.3</v>
+        <v>1737.8</v>
       </c>
       <c r="D5">
-        <v>-1.3</v>
+        <v>-3.36</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1297,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-4.51</v>
+        <v>-7.72</v>
       </c>
       <c r="H5">
-        <v>38.53</v>
+        <v>33.87</v>
       </c>
       <c r="I5">
-        <v>-0.5</v>
+        <v>-2.66</v>
       </c>
       <c r="J5">
-        <v>12.88</v>
+        <v>5.48</v>
       </c>
       <c r="K5">
-        <v>-4.51</v>
+        <v>-7.28</v>
       </c>
       <c r="L5">
-        <v>28.33</v>
+        <v>25.37</v>
       </c>
       <c r="M5">
-        <v>20.15</v>
+        <v>19.43</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1787.46</v>
+        <v>1777.96</v>
       </c>
       <c r="Q5">
-        <v>1756.25</v>
+        <v>1759.51</v>
       </c>
       <c r="R5">
-        <v>1723.47</v>
+        <v>1721.84</v>
       </c>
       <c r="S5">
-        <v>1625.18</v>
+        <v>1626.29</v>
       </c>
       <c r="T5">
-        <v>10.65</v>
+        <v>6.86</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1351,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.95</v>
+        <v>48.13</v>
       </c>
       <c r="Z5">
-        <v>22.72</v>
+        <v>17.87</v>
       </c>
       <c r="AA5">
-        <v>18.58</v>
+        <v>18.44</v>
       </c>
       <c r="AB5">
-        <v>4.15</v>
+        <v>-0.57</v>
       </c>
       <c r="AC5">
         <v>37.1</v>
       </c>
       <c r="AD5">
-        <v>37.12</v>
+        <v>38.11</v>
       </c>
       <c r="AE5">
-        <v>43.14</v>
+        <v>45.94</v>
       </c>
       <c r="AF5">
-        <v>28.62</v>
+        <v>-2.06</v>
       </c>
       <c r="AG5">
-        <v>1847.23</v>
+        <v>1842.18</v>
       </c>
       <c r="AH5">
-        <v>1665.27</v>
+        <v>1676.83</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1387,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>25.5</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1398,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>204</v>
+        <v>196.21</v>
       </c>
       <c r="D6">
-        <v>3.92</v>
+        <v>-3.82</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1410,46 +1394,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-18.04</v>
+        <v>-21.17</v>
       </c>
       <c r="H6">
-        <v>53.43</v>
+        <v>47.57</v>
       </c>
       <c r="I6">
-        <v>-0.39</v>
+        <v>-1.64</v>
       </c>
       <c r="J6">
-        <v>3.03</v>
+        <v>-3.99</v>
       </c>
       <c r="K6">
-        <v>-9.15</v>
+        <v>-11.53</v>
       </c>
       <c r="L6">
-        <v>36.91</v>
+        <v>34.16</v>
       </c>
       <c r="M6">
-        <v>60.07</v>
+        <v>58.88</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>199.73</v>
+        <v>199.08</v>
       </c>
       <c r="Q6">
-        <v>205.41</v>
+        <v>204.84</v>
       </c>
       <c r="R6">
-        <v>207.21</v>
+        <v>206.8</v>
       </c>
       <c r="S6">
-        <v>187.85</v>
+        <v>188.1</v>
       </c>
       <c r="T6">
-        <v>8.6</v>
+        <v>4.31</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1464,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>48.7</v>
+        <v>41.23</v>
       </c>
       <c r="Z6">
-        <v>-2.23</v>
+        <v>-2.59</v>
       </c>
       <c r="AA6">
-        <v>-1.68</v>
+        <v>-1.86</v>
       </c>
       <c r="AB6">
-        <v>-0.55</v>
+        <v>-0.73</v>
       </c>
       <c r="AC6">
-        <v>20.75</v>
+        <v>28.54</v>
       </c>
       <c r="AD6">
-        <v>13.28</v>
+        <v>19.68</v>
       </c>
       <c r="AE6">
-        <v>6.06</v>
+        <v>6.4</v>
       </c>
       <c r="AF6">
-        <v>6.27</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="AG6">
-        <v>215.07</v>
+        <v>215.26</v>
       </c>
       <c r="AH6">
-        <v>195.76</v>
+        <v>194.42</v>
       </c>
       <c r="AI6">
         <v>213.83</v>
@@ -1500,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>27.32</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1511,58 +1495,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>374</v>
+        <v>362.25</v>
       </c>
       <c r="D7">
-        <v>2.26</v>
+        <v>-3.14</v>
       </c>
       <c r="E7">
         <v>574.36</v>
       </c>
       <c r="F7">
-        <v>365.75</v>
+        <v>362.25</v>
       </c>
       <c r="G7">
-        <v>-34.88</v>
+        <v>-36.93</v>
       </c>
       <c r="H7">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-4.77</v>
+        <v>-5.69</v>
       </c>
       <c r="J7">
-        <v>-6.77</v>
+        <v>-9.93</v>
       </c>
       <c r="K7">
-        <v>-12.81</v>
+        <v>-18.3</v>
       </c>
       <c r="L7">
-        <v>-35.13</v>
+        <v>-35.59</v>
       </c>
       <c r="M7">
-        <v>-0.58</v>
+        <v>-1.32</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P7">
-        <v>376.4</v>
+        <v>372.03</v>
       </c>
       <c r="Q7">
-        <v>389.04</v>
+        <v>387.02</v>
       </c>
       <c r="R7">
-        <v>409.11</v>
+        <v>407.74</v>
       </c>
       <c r="S7">
-        <v>455.47</v>
+        <v>454.55</v>
       </c>
       <c r="T7">
-        <v>-17.89</v>
+        <v>-20.31</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1577,43 +1561,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>35.26</v>
+        <v>29.77</v>
       </c>
       <c r="Z7">
-        <v>-9.73</v>
+        <v>-10.62</v>
       </c>
       <c r="AA7">
-        <v>-8.789999999999999</v>
+        <v>-9.15</v>
       </c>
       <c r="AB7">
-        <v>-0.9399999999999999</v>
+        <v>-1.46</v>
       </c>
       <c r="AC7">
-        <v>31.09</v>
+        <v>29.79</v>
       </c>
       <c r="AD7">
-        <v>38.52</v>
+        <v>31.17</v>
       </c>
       <c r="AE7">
-        <v>8.23</v>
+        <v>8.91</v>
       </c>
       <c r="AF7">
-        <v>153.14</v>
+        <v>194.86</v>
       </c>
       <c r="AG7">
-        <v>410.54</v>
+        <v>410.62</v>
       </c>
       <c r="AH7">
-        <v>367.54</v>
+        <v>363.42</v>
       </c>
       <c r="AI7">
-        <v>393.76</v>
+        <v>390.68</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>43.28</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1624,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>593.9</v>
+        <v>583.05</v>
       </c>
       <c r="D8">
-        <v>0.93</v>
+        <v>-1.83</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1636,25 +1620,25 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-26.52</v>
+        <v>-27.86</v>
       </c>
       <c r="H8">
-        <v>26.97</v>
+        <v>24.65</v>
       </c>
       <c r="I8">
-        <v>-5.01</v>
+        <v>-4.79</v>
       </c>
       <c r="J8">
-        <v>-4.39</v>
+        <v>-4.99</v>
       </c>
       <c r="K8">
-        <v>-19.03</v>
+        <v>-19.22</v>
       </c>
       <c r="L8">
-        <v>-11.55</v>
+        <v>-10.16</v>
       </c>
       <c r="M8">
-        <v>-16.01</v>
+        <v>-16.33</v>
       </c>
       <c r="N8">
         <v>55</v>
@@ -1663,19 +1647,19 @@
         <v>40</v>
       </c>
       <c r="P8">
-        <v>600.16</v>
+        <v>594.29</v>
       </c>
       <c r="Q8">
-        <v>608.47</v>
+        <v>606.87</v>
       </c>
       <c r="R8">
-        <v>634.8200000000001</v>
+        <v>632.84</v>
       </c>
       <c r="S8">
-        <v>614.63</v>
+        <v>614.58</v>
       </c>
       <c r="T8">
-        <v>-3.37</v>
+        <v>-5.13</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1690,34 +1674,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>41</v>
+        <v>37.93</v>
       </c>
       <c r="Z8">
-        <v>-10.19</v>
+        <v>-11.35</v>
       </c>
       <c r="AA8">
-        <v>-9.970000000000001</v>
+        <v>-10.25</v>
       </c>
       <c r="AB8">
-        <v>-0.22</v>
+        <v>-1.11</v>
       </c>
       <c r="AC8">
-        <v>43.79</v>
+        <v>41.79</v>
       </c>
       <c r="AD8">
-        <v>48.2</v>
+        <v>44.35</v>
       </c>
       <c r="AE8">
-        <v>18.49</v>
+        <v>18.75</v>
       </c>
       <c r="AF8">
-        <v>-76.59999999999999</v>
+        <v>-69.06999999999999</v>
       </c>
       <c r="AG8">
-        <v>647.27</v>
+        <v>647.14</v>
       </c>
       <c r="AH8">
-        <v>569.66</v>
+        <v>566.6</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1726,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.85</v>
+        <v>26.89</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1737,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>177.68</v>
+        <v>175.43</v>
       </c>
       <c r="D9">
-        <v>-0.6</v>
+        <v>-1.27</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1749,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-35.99</v>
+        <v>-36.8</v>
       </c>
       <c r="H9">
-        <v>3.12</v>
+        <v>1.82</v>
       </c>
       <c r="I9">
-        <v>-4.57</v>
+        <v>-5.01</v>
       </c>
       <c r="J9">
-        <v>-7.72</v>
+        <v>-9.75</v>
       </c>
       <c r="K9">
-        <v>-3.41</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L9">
-        <v>-32.09</v>
+        <v>-32.9</v>
       </c>
       <c r="M9">
-        <v>-8.49</v>
+        <v>-8.74</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="P9">
-        <v>181.22</v>
+        <v>179.37</v>
       </c>
       <c r="Q9">
-        <v>184.92</v>
+        <v>184.13</v>
       </c>
       <c r="R9">
-        <v>189.37</v>
+        <v>189.08</v>
       </c>
       <c r="S9">
-        <v>196.99</v>
+        <v>196.62</v>
       </c>
       <c r="T9">
-        <v>-9.800000000000001</v>
+        <v>-10.78</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1803,43 +1787,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>33.48</v>
+        <v>30.69</v>
       </c>
       <c r="Z9">
-        <v>-2.85</v>
+        <v>-3.23</v>
       </c>
       <c r="AA9">
-        <v>-2.22</v>
+        <v>-2.42</v>
       </c>
       <c r="AB9">
-        <v>-0.63</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AC9">
-        <v>12.34</v>
+        <v>2.7</v>
       </c>
       <c r="AD9">
-        <v>36.98</v>
+        <v>17.46</v>
       </c>
       <c r="AE9">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="AF9">
-        <v>-58.94</v>
+        <v>-4.84</v>
       </c>
       <c r="AG9">
-        <v>192</v>
+        <v>191.75</v>
       </c>
       <c r="AH9">
-        <v>177.84</v>
+        <v>176.51</v>
       </c>
       <c r="AI9">
-        <v>191.11</v>
+        <v>190.38</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>29.29</v>
+        <v>33.37</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1850,58 +1834,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>69.14</v>
+        <v>68.08</v>
       </c>
       <c r="D10">
-        <v>0.12</v>
+        <v>-1.53</v>
       </c>
       <c r="E10">
-        <v>119.02</v>
+        <v>117.09</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-41.91</v>
+        <v>-41.86</v>
       </c>
       <c r="H10">
-        <v>16.63</v>
+        <v>14.84</v>
       </c>
       <c r="I10">
-        <v>-2.77</v>
+        <v>-2.65</v>
       </c>
       <c r="J10">
-        <v>-4.24</v>
+        <v>-4.68</v>
       </c>
       <c r="K10">
-        <v>-15.19</v>
+        <v>-16.12</v>
       </c>
       <c r="L10">
-        <v>-43.42</v>
+        <v>-42.8</v>
       </c>
       <c r="M10">
-        <v>-4.33</v>
+        <v>-3.79</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P10">
-        <v>69.45999999999999</v>
+        <v>69.09</v>
       </c>
       <c r="Q10">
-        <v>71.25</v>
+        <v>71.11</v>
       </c>
       <c r="R10">
-        <v>73.93000000000001</v>
+        <v>73.78</v>
       </c>
       <c r="S10">
-        <v>79.87</v>
+        <v>79.8</v>
       </c>
       <c r="T10">
-        <v>-13.43</v>
+        <v>-14.68</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1916,43 +1900,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>35.72</v>
+        <v>32.18</v>
       </c>
       <c r="Z10">
-        <v>-1.36</v>
+        <v>-1.45</v>
       </c>
       <c r="AA10">
-        <v>-1.27</v>
+        <v>-1.31</v>
       </c>
       <c r="AB10">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="AC10">
-        <v>16.75</v>
+        <v>11.34</v>
       </c>
       <c r="AD10">
-        <v>23.28</v>
+        <v>17.29</v>
       </c>
       <c r="AE10">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="AF10">
-        <v>-46.92</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="AG10">
-        <v>74.31</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AH10">
-        <v>68.18000000000001</v>
+        <v>67.73</v>
       </c>
       <c r="AI10">
-        <v>76.17</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>29.3</v>
+        <v>31.81</v>
       </c>
     </row>
   </sheetData>
@@ -2093,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2133,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2151,1280 +2135,1294 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.67</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-7.03</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" s="5" t="s">
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-1.64</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-3.19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>5.19</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0.88</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-4.31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>12.88</v>
+      </c>
+      <c r="D10" s="6">
+        <v>5.48</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-7.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>3.03</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-3.99</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-7.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-6.77</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-9.93</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-4.39</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-4.99</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-7.72</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-9.75</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.24</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-4.68</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-3.78</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-4.31</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.87</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.76</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.31</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-0.5</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-2.66</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-0.39</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-1.64</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-4.77</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-5.69</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-5.01</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-4.79</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4.57</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-5.01</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.65</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-34.59</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-34.79</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>12.74</v>
+      </c>
+      <c r="D26" s="6">
+        <v>10.79</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>18.38</v>
+      </c>
+      <c r="D27" s="6">
+        <v>21.84</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>28.33</v>
+      </c>
+      <c r="D28" s="6">
+        <v>25.37</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>36.91</v>
+      </c>
+      <c r="D29" s="6">
+        <v>34.16</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-35.13</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-35.59</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-11.55</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-10.16</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-32.09</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-32.9</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-43.42</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-42.8</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-10.85</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-15.14</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-4.29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-12.31</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-3.68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-17.82</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-18</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-4.51</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-7.28</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-9.15</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-11.53</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-12.81</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-18.3</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-5.49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-19.03</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-19.22</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-3.41</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-4.79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-15.19</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-16.12</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-36.72</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-37.84</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-12.31</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-20.35</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-20.47</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-4.51</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-7.72</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-18.04</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-21.17</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3.13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-34.88</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-36.93</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-26.52</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-27.86</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-35.99</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-36.8</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-41.91</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-41.86</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>1204.1</v>
+      </c>
+      <c r="D52" s="6">
+        <v>1182.8</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-21.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>2903.4</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2816.8</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-86.59999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1278</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1276.1</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1798.3</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1737.8</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-60.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>204</v>
+      </c>
+      <c r="D56" s="6">
+        <v>196.21</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-7.79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>374</v>
+      </c>
+      <c r="D57" s="6">
+        <v>362.25</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-11.75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>593.9</v>
+      </c>
+      <c r="D58" s="6">
+        <v>583.05</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-10.85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>177.68</v>
+      </c>
+      <c r="D59" s="6">
+        <v>175.43</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>69.14</v>
+      </c>
+      <c r="D60" s="6">
+        <v>68.08</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>77</v>
+      </c>
+      <c r="D61" s="6">
         <v>66</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="E61" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>66</v>
+      </c>
+      <c r="D62" s="6">
+        <v>77</v>
+      </c>
+      <c r="E62" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-7.95</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-5.67</v>
-      </c>
-      <c r="E8" s="8">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>31.68</v>
+      </c>
+      <c r="D63" s="6">
+        <v>27.59</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-4.09</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-6.17</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.55</v>
-      </c>
-      <c r="E9" s="8">
-        <v>7.72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>45.41</v>
+      </c>
+      <c r="D64" s="6">
+        <v>40.41</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-3.89</v>
-      </c>
-      <c r="D10" s="7">
-        <v>5.19</v>
-      </c>
-      <c r="E10" s="8">
-        <v>9.08</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>46.79</v>
+      </c>
+      <c r="D65" s="6">
+        <v>46.5</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>6.71</v>
-      </c>
-      <c r="D11" s="7">
-        <v>12.88</v>
-      </c>
-      <c r="E11" s="8">
-        <v>6.17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>55.95</v>
+      </c>
+      <c r="D66" s="6">
+        <v>48.13</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-7.82</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-7.68</v>
-      </c>
-      <c r="D12" s="7">
-        <v>3.03</v>
-      </c>
-      <c r="E12" s="8">
-        <v>10.71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>48.7</v>
+      </c>
+      <c r="D67" s="6">
+        <v>41.23</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-7.47</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-11.24</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-6.77</v>
-      </c>
-      <c r="E13" s="8">
-        <v>4.47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>35.26</v>
+      </c>
+      <c r="D68" s="6">
+        <v>29.77</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-5.49</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-7.56</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-4.39</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>41</v>
+      </c>
+      <c r="D69" s="6">
+        <v>37.93</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-8.93</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-7.72</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>33.48</v>
+      </c>
+      <c r="D70" s="6">
+        <v>30.69</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-2.79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-6.38</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-4.24</v>
-      </c>
-      <c r="E16" s="8">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>35.72</v>
+      </c>
+      <c r="D71" s="6">
+        <v>32.18</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-3.54</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-2.88</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-3.78</v>
-      </c>
-      <c r="E17" s="9">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-58.52</v>
+      </c>
+      <c r="D72" s="6">
+        <v>2.24</v>
+      </c>
+      <c r="E72" s="8">
+        <v>60.76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-0.8</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-3</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-21</v>
+      </c>
+      <c r="D73" s="6">
+        <v>32.94</v>
+      </c>
+      <c r="E73" s="8">
+        <v>53.94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-3.37</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.76</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-0.67</v>
+      </c>
+      <c r="D74" s="6">
+        <v>348.82</v>
+      </c>
+      <c r="E74" s="8">
+        <v>349.49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>1.5</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-0.5</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>28.62</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-2.06</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-30.68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-5.15</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-0.39</v>
-      </c>
-      <c r="E21" s="8">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>6.27</v>
+      </c>
+      <c r="D76" s="6">
+        <v>83.65000000000001</v>
+      </c>
+      <c r="E76" s="8">
+        <v>77.38</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-5.47</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-4.77</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>153.14</v>
+      </c>
+      <c r="D77" s="6">
+        <v>194.86</v>
+      </c>
+      <c r="E77" s="8">
+        <v>41.72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-6.04</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-5.01</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-76.59999999999999</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-69.06999999999999</v>
+      </c>
+      <c r="E78" s="8">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-2.38</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-4.57</v>
-      </c>
-      <c r="E24" s="9">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-58.94</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-4.84</v>
+      </c>
+      <c r="E79" s="8">
+        <v>54.1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-4.49</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-2.77</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-35</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-34.59</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>13.53</v>
-      </c>
-      <c r="D27" s="7">
-        <v>12.74</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>15.04</v>
-      </c>
-      <c r="D28" s="7">
-        <v>18.38</v>
-      </c>
-      <c r="E28" s="8">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>27.81</v>
-      </c>
-      <c r="D29" s="7">
-        <v>28.33</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>35.85</v>
-      </c>
-      <c r="D30" s="7">
-        <v>36.91</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-36.92</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-35.13</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-11.79</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-11.55</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-29.29</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-32.09</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-43.5</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-43.42</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-9.73</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-10.85</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-5.43</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-8.630000000000001</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-3.2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-17.92</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-17.82</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-1.42</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-4.51</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-13.47</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-9.15</v>
-      </c>
-      <c r="E39" s="8">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-12.68</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-12.81</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-19.84</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-19.03</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-2.96</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-3.41</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-14.59</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-15.19</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-36.79</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-36.72</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-7.45</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-9.609999999999999</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-21.47</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-20.35</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-3.25</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-4.51</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-21.14</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-18.04</v>
-      </c>
-      <c r="E48" s="8">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-36.56</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-34.88</v>
-      </c>
-      <c r="E49" s="8">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-27.2</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-26.52</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-35.61</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-35.99</v>
-      </c>
-      <c r="E51" s="9">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-43.48</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-41.91</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1202.6</v>
-      </c>
-      <c r="D53" s="7">
-        <v>1204.1</v>
-      </c>
-      <c r="E53" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2972.9</v>
-      </c>
-      <c r="D54" s="7">
-        <v>2903.4</v>
-      </c>
-      <c r="E54" s="9">
-        <v>-69.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1260</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1278</v>
-      </c>
-      <c r="E55" s="8">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>1822</v>
-      </c>
-      <c r="D56" s="7">
-        <v>1798.3</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-23.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>196.3</v>
-      </c>
-      <c r="D57" s="7">
-        <v>204</v>
-      </c>
-      <c r="E57" s="8">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>365.75</v>
-      </c>
-      <c r="D58" s="7">
-        <v>374</v>
-      </c>
-      <c r="E58" s="8">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>588.4</v>
-      </c>
-      <c r="D59" s="7">
-        <v>593.9</v>
-      </c>
-      <c r="E59" s="8">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>178.75</v>
-      </c>
-      <c r="D60" s="7">
-        <v>177.68</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>69.06</v>
-      </c>
-      <c r="D61" s="7">
-        <v>69.14</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>31.02</v>
-      </c>
-      <c r="D62" s="7">
-        <v>31.68</v>
-      </c>
-      <c r="E62" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>50.02</v>
-      </c>
-      <c r="D63" s="7">
-        <v>45.41</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-4.61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>43.67</v>
-      </c>
-      <c r="D64" s="7">
-        <v>46.79</v>
-      </c>
-      <c r="E64" s="8">
-        <v>3.12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>59.47</v>
-      </c>
-      <c r="D65" s="7">
-        <v>55.95</v>
-      </c>
-      <c r="E65" s="9">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>38.47</v>
-      </c>
-      <c r="D66" s="7">
-        <v>48.7</v>
-      </c>
-      <c r="E66" s="8">
-        <v>10.23</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>26.4</v>
-      </c>
-      <c r="D67" s="7">
-        <v>35.26</v>
-      </c>
-      <c r="E67" s="8">
-        <v>8.859999999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>38.66</v>
-      </c>
-      <c r="D68" s="7">
-        <v>41</v>
-      </c>
-      <c r="E68" s="8">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>34.88</v>
-      </c>
-      <c r="D69" s="7">
-        <v>33.48</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>35.22</v>
-      </c>
-      <c r="D70" s="7">
-        <v>35.72</v>
-      </c>
-      <c r="E70" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="6" t="s">
+      <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C71" s="7">
-        <v>499.41</v>
-      </c>
-      <c r="D71" s="7">
-        <v>-58.52</v>
-      </c>
-      <c r="E71" s="9">
-        <v>-557.9299999999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>63.13</v>
-      </c>
-      <c r="D72" s="7">
-        <v>-21</v>
-      </c>
-      <c r="E72" s="9">
-        <v>-84.13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>13.51</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-0.67</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-14.18</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="D74" s="7">
-        <v>28.62</v>
-      </c>
-      <c r="E74" s="9">
-        <v>-43.23</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>78.69</v>
-      </c>
-      <c r="D75" s="7">
-        <v>6.27</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-72.42</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>35.91</v>
-      </c>
-      <c r="D76" s="7">
-        <v>153.14</v>
-      </c>
-      <c r="E76" s="8">
-        <v>117.23</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-76.98999999999999</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-76.59999999999999</v>
-      </c>
-      <c r="E77" s="8">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>486.13</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-58.94</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-545.0700000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-13.48</v>
-      </c>
-      <c r="D79" s="7">
+      <c r="C80" s="6">
         <v>-46.92</v>
       </c>
-      <c r="E79" s="9">
-        <v>-33.44</v>
+      <c r="D80" s="6">
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="E80" s="8">
+        <v>38.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3444,60 +3442,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>79</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>48.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>41.6</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>37.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="12">
-        <v>-0.7</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-11.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-14</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -3599,61 +3597,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.6007</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2015</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1467</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0219</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.0058</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0433</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.0849</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.1099</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1601</v>
+      <c r="A2" s="14">
+        <v>0.5888</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1943</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1412</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0208</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.0132</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0379</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.08740000000000001</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.1117</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1633</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>56.0 → 48.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>56.0</t>
+    <t>48.1 → 52.4</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>48.1</t>
+  </si>
+  <si>
+    <t>52.4</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.8 → 33.8</t>
+  </si>
+  <si>
+    <t>29.8</t>
+  </si>
+  <si>
+    <t>33.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +303,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +343,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -930,10 +942,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1182.8</v>
+        <v>1184.4</v>
       </c>
       <c r="D2">
-        <v>-1.77</v>
+        <v>0.14</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +954,46 @@
         <v>1182.8</v>
       </c>
       <c r="G2">
-        <v>-37.84</v>
+        <v>-37.75</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="I2">
-        <v>-4.31</v>
+        <v>-4.21</v>
       </c>
       <c r="J2">
-        <v>-7.03</v>
+        <v>-6.49</v>
       </c>
       <c r="K2">
-        <v>-15.14</v>
+        <v>-15.22</v>
       </c>
       <c r="L2">
-        <v>-34.79</v>
+        <v>-34.1</v>
       </c>
       <c r="M2">
-        <v>-11.17</v>
+        <v>-11.36</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P2">
-        <v>1207.88</v>
+        <v>1197.48</v>
       </c>
       <c r="Q2">
-        <v>1240.56</v>
+        <v>1236.18</v>
       </c>
       <c r="R2">
-        <v>1295.07</v>
+        <v>1292.08</v>
       </c>
       <c r="S2">
-        <v>1439.35</v>
+        <v>1436.44</v>
       </c>
       <c r="T2">
-        <v>-17.82</v>
+        <v>-17.55</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1008,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>27.59</v>
+        <v>28.34</v>
       </c>
       <c r="Z2">
-        <v>-25.79</v>
+        <v>-27.04</v>
       </c>
       <c r="AA2">
-        <v>-22.79</v>
+        <v>-23.64</v>
       </c>
       <c r="AB2">
-        <v>-3</v>
+        <v>-3.41</v>
       </c>
       <c r="AC2">
-        <v>16.14</v>
+        <v>10.44</v>
       </c>
       <c r="AD2">
-        <v>29.23</v>
+        <v>18.29</v>
       </c>
       <c r="AE2">
         <v>24.71</v>
       </c>
       <c r="AF2">
-        <v>2.24</v>
+        <v>-41.32</v>
       </c>
       <c r="AG2">
-        <v>1292.41</v>
+        <v>1291.53</v>
       </c>
       <c r="AH2">
-        <v>1188.71</v>
+        <v>1180.83</v>
       </c>
       <c r="AI2">
         <v>1259.12</v>
@@ -1032,7 +1044,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>29.74</v>
+        <v>33.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1055,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2816.8</v>
+        <v>2864</v>
       </c>
       <c r="D3">
-        <v>-2.98</v>
+        <v>1.68</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1067,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-12.31</v>
+        <v>-10.84</v>
       </c>
       <c r="H3">
-        <v>60.23</v>
+        <v>62.91</v>
       </c>
       <c r="I3">
-        <v>-2.87</v>
+        <v>-1.8</v>
       </c>
       <c r="J3">
-        <v>-1.64</v>
+        <v>-0.96</v>
       </c>
       <c r="K3">
-        <v>-12.31</v>
+        <v>-10.68</v>
       </c>
       <c r="L3">
-        <v>10.79</v>
+        <v>14.18</v>
       </c>
       <c r="M3">
-        <v>14.12</v>
+        <v>13.45</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P3">
-        <v>2888.14</v>
+        <v>2877.64</v>
       </c>
       <c r="Q3">
-        <v>2954.08</v>
+        <v>2952.23</v>
       </c>
       <c r="R3">
-        <v>2992.2</v>
+        <v>2989.28</v>
       </c>
       <c r="S3">
-        <v>2571.66</v>
+        <v>2574.59</v>
       </c>
       <c r="T3">
-        <v>9.529999999999999</v>
+        <v>11.24</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1121,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>40.41</v>
+        <v>44.03</v>
       </c>
       <c r="Z3">
-        <v>-33.3</v>
+        <v>-35.46</v>
       </c>
       <c r="AA3">
-        <v>-22.24</v>
+        <v>-24.89</v>
       </c>
       <c r="AB3">
-        <v>-11.06</v>
+        <v>-10.57</v>
       </c>
       <c r="AC3">
-        <v>37.43</v>
+        <v>32.49</v>
       </c>
       <c r="AD3">
-        <v>30.87</v>
+        <v>34.22</v>
       </c>
       <c r="AE3">
-        <v>89.08</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="AF3">
-        <v>32.94</v>
+        <v>19.11</v>
       </c>
       <c r="AG3">
-        <v>3102.27</v>
+        <v>3104.09</v>
       </c>
       <c r="AH3">
-        <v>2805.9</v>
+        <v>2800.38</v>
       </c>
       <c r="AI3">
         <v>3101.6</v>
@@ -1145,7 +1157,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>25.3</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1168,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1276.1</v>
+        <v>1284</v>
       </c>
       <c r="D4">
-        <v>-0.15</v>
+        <v>0.62</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1180,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-20.47</v>
+        <v>-19.98</v>
       </c>
       <c r="H4">
-        <v>65.13</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="I4">
-        <v>-0.31</v>
+        <v>-0.97</v>
       </c>
       <c r="J4">
-        <v>0.88</v>
+        <v>-0.93</v>
       </c>
       <c r="K4">
-        <v>-18</v>
+        <v>-17.12</v>
       </c>
       <c r="L4">
-        <v>21.84</v>
+        <v>24.02</v>
       </c>
       <c r="M4">
-        <v>2.08</v>
+        <v>0.99</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>1269.14</v>
+        <v>1266.62</v>
       </c>
       <c r="Q4">
-        <v>1286.41</v>
+        <v>1286.44</v>
       </c>
       <c r="R4">
-        <v>1318.8</v>
+        <v>1316.88</v>
       </c>
       <c r="S4">
-        <v>1200.26</v>
+        <v>1201.44</v>
       </c>
       <c r="T4">
-        <v>6.32</v>
+        <v>6.87</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1234,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>46.5</v>
+        <v>47.96</v>
       </c>
       <c r="Z4">
-        <v>-14.45</v>
+        <v>-13.07</v>
       </c>
       <c r="AA4">
-        <v>-15.67</v>
+        <v>-15.15</v>
       </c>
       <c r="AB4">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="AC4">
-        <v>44.88</v>
+        <v>54.61</v>
       </c>
       <c r="AD4">
-        <v>34.45</v>
+        <v>42.5</v>
       </c>
       <c r="AE4">
-        <v>37.97</v>
+        <v>37.89</v>
       </c>
       <c r="AF4">
-        <v>348.82</v>
+        <v>-33.05</v>
       </c>
       <c r="AG4">
-        <v>1331.03</v>
+        <v>1331.06</v>
       </c>
       <c r="AH4">
-        <v>1241.8</v>
+        <v>1241.83</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1258,7 +1270,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>18.31</v>
+        <v>16.59</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1281,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1737.8</v>
+        <v>1774</v>
       </c>
       <c r="D5">
-        <v>-3.36</v>
+        <v>2.08</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1293,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.72</v>
+        <v>-5.8</v>
       </c>
       <c r="H5">
-        <v>33.87</v>
+        <v>36.66</v>
       </c>
       <c r="I5">
-        <v>-2.66</v>
+        <v>-0.78</v>
       </c>
       <c r="J5">
-        <v>5.48</v>
+        <v>6.06</v>
       </c>
       <c r="K5">
-        <v>-7.28</v>
+        <v>-4.85</v>
       </c>
       <c r="L5">
-        <v>25.37</v>
+        <v>28.79</v>
       </c>
       <c r="M5">
-        <v>19.43</v>
+        <v>19.63</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1777.96</v>
+        <v>1775.16</v>
       </c>
       <c r="Q5">
-        <v>1759.51</v>
+        <v>1762.88</v>
       </c>
       <c r="R5">
-        <v>1721.84</v>
+        <v>1721.75</v>
       </c>
       <c r="S5">
-        <v>1626.29</v>
+        <v>1627.62</v>
       </c>
       <c r="T5">
-        <v>6.86</v>
+        <v>8.99</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1347,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>48.13</v>
+        <v>52.42</v>
       </c>
       <c r="Z5">
-        <v>17.87</v>
+        <v>16.74</v>
       </c>
       <c r="AA5">
-        <v>18.44</v>
+        <v>18.1</v>
       </c>
       <c r="AB5">
-        <v>-0.57</v>
+        <v>-1.35</v>
       </c>
       <c r="AC5">
-        <v>37.1</v>
+        <v>23.43</v>
       </c>
       <c r="AD5">
-        <v>38.11</v>
+        <v>32.55</v>
       </c>
       <c r="AE5">
-        <v>45.94</v>
+        <v>45.6</v>
       </c>
       <c r="AF5">
-        <v>-2.06</v>
+        <v>31.35</v>
       </c>
       <c r="AG5">
-        <v>1842.18</v>
+        <v>1841.87</v>
       </c>
       <c r="AH5">
-        <v>1676.83</v>
+        <v>1683.89</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1371,7 +1383,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>25.19</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1394,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>196.21</v>
+        <v>201</v>
       </c>
       <c r="D6">
-        <v>-3.82</v>
+        <v>2.44</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1406,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-21.17</v>
+        <v>-19.25</v>
       </c>
       <c r="H6">
-        <v>47.57</v>
+        <v>51.17</v>
       </c>
       <c r="I6">
-        <v>-1.64</v>
+        <v>-0.86</v>
       </c>
       <c r="J6">
-        <v>-3.99</v>
+        <v>-3.23</v>
       </c>
       <c r="K6">
-        <v>-11.53</v>
+        <v>-8.57</v>
       </c>
       <c r="L6">
-        <v>34.16</v>
+        <v>37.06</v>
       </c>
       <c r="M6">
-        <v>58.88</v>
+        <v>56.67</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>199.08</v>
+        <v>198.73</v>
       </c>
       <c r="Q6">
-        <v>204.84</v>
+        <v>204.48</v>
       </c>
       <c r="R6">
-        <v>206.8</v>
+        <v>206.58</v>
       </c>
       <c r="S6">
-        <v>188.1</v>
+        <v>188.39</v>
       </c>
       <c r="T6">
-        <v>4.31</v>
+        <v>6.7</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1460,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>41.23</v>
+        <v>46.65</v>
       </c>
       <c r="Z6">
-        <v>-2.59</v>
+        <v>-2.46</v>
       </c>
       <c r="AA6">
-        <v>-1.86</v>
+        <v>-1.98</v>
       </c>
       <c r="AB6">
-        <v>-0.73</v>
+        <v>-0.48</v>
       </c>
       <c r="AC6">
-        <v>28.54</v>
+        <v>54.34</v>
       </c>
       <c r="AD6">
-        <v>19.68</v>
+        <v>34.54</v>
       </c>
       <c r="AE6">
-        <v>6.4</v>
+        <v>6.34</v>
       </c>
       <c r="AF6">
-        <v>83.65000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="AG6">
-        <v>215.26</v>
+        <v>214.9</v>
       </c>
       <c r="AH6">
-        <v>194.42</v>
+        <v>194.05</v>
       </c>
       <c r="AI6">
         <v>213.83</v>
@@ -1484,7 +1496,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>28.86</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1507,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>362.25</v>
+        <v>366.5</v>
       </c>
       <c r="D7">
-        <v>-3.14</v>
+        <v>1.17</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1507,46 +1519,46 @@
         <v>362.25</v>
       </c>
       <c r="G7">
-        <v>-36.93</v>
+        <v>-36.19</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="I7">
-        <v>-5.69</v>
+        <v>-4.51</v>
       </c>
       <c r="J7">
-        <v>-9.93</v>
+        <v>-8.99</v>
       </c>
       <c r="K7">
-        <v>-18.3</v>
+        <v>-16.97</v>
       </c>
       <c r="L7">
-        <v>-35.59</v>
+        <v>-34.48</v>
       </c>
       <c r="M7">
-        <v>-1.32</v>
+        <v>-1.16</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="P7">
-        <v>372.03</v>
+        <v>368.57</v>
       </c>
       <c r="Q7">
-        <v>387.02</v>
+        <v>385.09</v>
       </c>
       <c r="R7">
-        <v>407.74</v>
+        <v>406.6</v>
       </c>
       <c r="S7">
-        <v>454.55</v>
+        <v>453.63</v>
       </c>
       <c r="T7">
-        <v>-20.31</v>
+        <v>-19.21</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1573,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>29.77</v>
+        <v>33.79</v>
       </c>
       <c r="Z7">
-        <v>-10.62</v>
+        <v>-10.85</v>
       </c>
       <c r="AA7">
-        <v>-9.15</v>
+        <v>-9.49</v>
       </c>
       <c r="AB7">
-        <v>-1.46</v>
+        <v>-1.36</v>
       </c>
       <c r="AC7">
-        <v>29.79</v>
+        <v>44.19</v>
       </c>
       <c r="AD7">
-        <v>31.17</v>
+        <v>35.02</v>
       </c>
       <c r="AE7">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="AF7">
-        <v>194.86</v>
+        <v>28.39</v>
       </c>
       <c r="AG7">
-        <v>410.62</v>
+        <v>408.8</v>
       </c>
       <c r="AH7">
-        <v>363.42</v>
+        <v>361.39</v>
       </c>
       <c r="AI7">
         <v>390.68</v>
@@ -1597,7 +1609,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>46.45</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1620,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>583.05</v>
+        <v>583.25</v>
       </c>
       <c r="D8">
-        <v>-1.83</v>
+        <v>0.03</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1632,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-27.86</v>
+        <v>-27.84</v>
       </c>
       <c r="H8">
-        <v>24.65</v>
+        <v>24.7</v>
       </c>
       <c r="I8">
-        <v>-4.79</v>
+        <v>-4.64</v>
       </c>
       <c r="J8">
-        <v>-4.99</v>
+        <v>-5.15</v>
       </c>
       <c r="K8">
-        <v>-19.22</v>
+        <v>-19.47</v>
       </c>
       <c r="L8">
-        <v>-10.16</v>
+        <v>-7.34</v>
       </c>
       <c r="M8">
-        <v>-16.33</v>
+        <v>-16.23</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P8">
-        <v>594.29</v>
+        <v>588.61</v>
       </c>
       <c r="Q8">
-        <v>606.87</v>
+        <v>605.33</v>
       </c>
       <c r="R8">
-        <v>632.84</v>
+        <v>631.26</v>
       </c>
       <c r="S8">
-        <v>614.58</v>
+        <v>614.53</v>
       </c>
       <c r="T8">
-        <v>-5.13</v>
+        <v>-5.09</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1686,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>37.93</v>
+        <v>38.02</v>
       </c>
       <c r="Z8">
-        <v>-11.35</v>
+        <v>-12.12</v>
       </c>
       <c r="AA8">
-        <v>-10.25</v>
+        <v>-10.62</v>
       </c>
       <c r="AB8">
-        <v>-1.11</v>
+        <v>-1.5</v>
       </c>
       <c r="AC8">
-        <v>41.79</v>
+        <v>41.24</v>
       </c>
       <c r="AD8">
-        <v>44.35</v>
+        <v>42.27</v>
       </c>
       <c r="AE8">
-        <v>18.75</v>
+        <v>18.43</v>
       </c>
       <c r="AF8">
-        <v>-69.06999999999999</v>
+        <v>-80.61</v>
       </c>
       <c r="AG8">
-        <v>647.14</v>
+        <v>646.78</v>
       </c>
       <c r="AH8">
-        <v>566.6</v>
+        <v>563.88</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1710,7 +1722,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.89</v>
+        <v>26.92</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1733,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>175.43</v>
+        <v>176.15</v>
       </c>
       <c r="D9">
-        <v>-1.27</v>
+        <v>0.41</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1745,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-36.8</v>
+        <v>-36.55</v>
       </c>
       <c r="H9">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="I9">
-        <v>-5.01</v>
+        <v>-4.44</v>
       </c>
       <c r="J9">
-        <v>-9.75</v>
+        <v>-7.9</v>
       </c>
       <c r="K9">
-        <v>-8.199999999999999</v>
+        <v>-7.66</v>
       </c>
       <c r="L9">
-        <v>-32.9</v>
+        <v>-32.55</v>
       </c>
       <c r="M9">
-        <v>-8.74</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P9">
-        <v>179.37</v>
+        <v>177.73</v>
       </c>
       <c r="Q9">
-        <v>184.13</v>
+        <v>183.4</v>
       </c>
       <c r="R9">
-        <v>189.08</v>
+        <v>188.86</v>
       </c>
       <c r="S9">
-        <v>196.62</v>
+        <v>196.27</v>
       </c>
       <c r="T9">
-        <v>-10.78</v>
+        <v>-10.25</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1799,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>30.69</v>
+        <v>32.63</v>
       </c>
       <c r="Z9">
-        <v>-3.23</v>
+        <v>-3.44</v>
       </c>
       <c r="AA9">
-        <v>-2.42</v>
+        <v>-2.63</v>
       </c>
       <c r="AB9">
         <v>-0.8100000000000001</v>
       </c>
       <c r="AC9">
-        <v>2.7</v>
+        <v>4.12</v>
       </c>
       <c r="AD9">
-        <v>17.46</v>
+        <v>6.39</v>
       </c>
       <c r="AE9">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="AF9">
-        <v>-4.84</v>
+        <v>-59.24</v>
       </c>
       <c r="AG9">
-        <v>191.75</v>
+        <v>191.14</v>
       </c>
       <c r="AH9">
-        <v>176.51</v>
+        <v>175.66</v>
       </c>
       <c r="AI9">
         <v>190.38</v>
@@ -1823,7 +1835,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>33.37</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,58 +1846,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>68.08</v>
+        <v>67.19</v>
       </c>
       <c r="D10">
-        <v>-1.53</v>
+        <v>-1.31</v>
       </c>
       <c r="E10">
-        <v>117.09</v>
+        <v>116.81</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-41.86</v>
+        <v>-42.48</v>
       </c>
       <c r="H10">
-        <v>14.84</v>
+        <v>13.34</v>
       </c>
       <c r="I10">
-        <v>-2.65</v>
+        <v>-4.12</v>
       </c>
       <c r="J10">
-        <v>-4.68</v>
+        <v>-5.15</v>
       </c>
       <c r="K10">
-        <v>-16.12</v>
+        <v>-16.81</v>
       </c>
       <c r="L10">
-        <v>-42.8</v>
+        <v>-42.62</v>
       </c>
       <c r="M10">
-        <v>-3.79</v>
+        <v>-4.82</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P10">
-        <v>69.09</v>
+        <v>68.52</v>
       </c>
       <c r="Q10">
-        <v>71.11</v>
+        <v>70.94</v>
       </c>
       <c r="R10">
-        <v>73.78</v>
+        <v>73.61</v>
       </c>
       <c r="S10">
-        <v>79.8</v>
+        <v>79.72</v>
       </c>
       <c r="T10">
-        <v>-14.68</v>
+        <v>-15.72</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,43 +1912,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>32.18</v>
+        <v>29.53</v>
       </c>
       <c r="Z10">
-        <v>-1.45</v>
+        <v>-1.57</v>
       </c>
       <c r="AA10">
-        <v>-1.31</v>
+        <v>-1.36</v>
       </c>
       <c r="AB10">
-        <v>-0.14</v>
+        <v>-0.21</v>
       </c>
       <c r="AC10">
-        <v>11.34</v>
+        <v>6.35</v>
       </c>
       <c r="AD10">
-        <v>17.29</v>
+        <v>11.48</v>
       </c>
       <c r="AE10">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AF10">
-        <v>-8.109999999999999</v>
+        <v>-7.5</v>
       </c>
       <c r="AG10">
-        <v>74.48999999999999</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="AH10">
-        <v>67.73</v>
+        <v>67.13</v>
       </c>
       <c r="AI10">
-        <v>75.20999999999999</v>
+        <v>74.78</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>31.81</v>
+        <v>35.33</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2135,1294 +2147,1280 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-5.67</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-7.03</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-1.36</v>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>1.55</v>
+        <v>-7.03</v>
       </c>
       <c r="D8" s="6">
-        <v>-1.64</v>
+        <v>-6.49</v>
       </c>
       <c r="E8" s="7">
-        <v>-3.19</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>5.19</v>
+        <v>-1.64</v>
       </c>
       <c r="D9" s="6">
-        <v>0.88</v>
+        <v>-0.96</v>
       </c>
       <c r="E9" s="7">
-        <v>-4.31</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>12.88</v>
+        <v>0.88</v>
       </c>
       <c r="D10" s="6">
-        <v>5.48</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-7.4</v>
+        <v>-0.93</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>3.03</v>
+        <v>5.48</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.99</v>
+        <v>6.06</v>
       </c>
       <c r="E11" s="7">
-        <v>-7.02</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.77</v>
+        <v>-3.99</v>
       </c>
       <c r="D12" s="6">
-        <v>-9.93</v>
+        <v>-3.23</v>
       </c>
       <c r="E12" s="7">
-        <v>-3.16</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-4.39</v>
+        <v>-9.93</v>
       </c>
       <c r="D13" s="6">
-        <v>-4.99</v>
+        <v>-8.99</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.6</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.72</v>
+        <v>-4.99</v>
       </c>
       <c r="D14" s="6">
-        <v>-9.75</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.03</v>
+        <v>-5.15</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.24</v>
+        <v>-9.75</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.68</v>
+        <v>-7.9</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.44</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.78</v>
+        <v>-4.68</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.31</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.53</v>
+        <v>-5.15</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3</v>
+        <v>-4.31</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.87</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.13</v>
+        <v>-4.21</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.76</v>
+        <v>-2.87</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.31</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.45</v>
+        <v>-1.8</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.07</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.5</v>
+        <v>-0.31</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.66</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.16</v>
+        <v>-0.97</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.39</v>
+        <v>-2.66</v>
       </c>
       <c r="D20" s="6">
-        <v>-1.64</v>
+        <v>-0.78</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.25</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.77</v>
+        <v>-1.64</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.69</v>
+        <v>-0.86</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.92</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.01</v>
+        <v>-5.69</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.22</v>
+        <v>-4.51</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.18</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.57</v>
+        <v>-4.79</v>
       </c>
       <c r="D23" s="6">
-        <v>-5.01</v>
+        <v>-4.64</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.44</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.77</v>
+        <v>-5.01</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.65</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.12</v>
+        <v>-4.44</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.57</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-34.59</v>
+        <v>-2.65</v>
       </c>
       <c r="D25" s="6">
-        <v>-34.79</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.2</v>
+        <v>-4.12</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>12.74</v>
+        <v>-34.79</v>
       </c>
       <c r="D26" s="6">
-        <v>10.79</v>
+        <v>-34.1</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.95</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>18.38</v>
+        <v>10.79</v>
       </c>
       <c r="D27" s="6">
-        <v>21.84</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.46</v>
+        <v>14.18</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3.39</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>28.33</v>
+        <v>21.84</v>
       </c>
       <c r="D28" s="6">
-        <v>25.37</v>
+        <v>24.02</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.96</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>36.91</v>
+        <v>25.37</v>
       </c>
       <c r="D29" s="6">
-        <v>34.16</v>
+        <v>28.79</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.75</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-35.13</v>
+        <v>34.16</v>
       </c>
       <c r="D30" s="6">
-        <v>-35.59</v>
+        <v>37.06</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.46</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-11.55</v>
+        <v>-35.59</v>
       </c>
       <c r="D31" s="6">
-        <v>-10.16</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.39</v>
+        <v>-34.48</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.11</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-32.09</v>
+        <v>-10.16</v>
       </c>
       <c r="D32" s="6">
-        <v>-32.9</v>
+        <v>-7.34</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.8100000000000001</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-43.42</v>
+        <v>-32.9</v>
       </c>
       <c r="D33" s="6">
-        <v>-42.8</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.62</v>
+        <v>-32.55</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-10.85</v>
+        <v>-42.8</v>
       </c>
       <c r="D34" s="6">
-        <v>-15.14</v>
+        <v>-42.62</v>
       </c>
       <c r="E34" s="7">
-        <v>-4.29</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-8.630000000000001</v>
+        <v>-15.14</v>
       </c>
       <c r="D35" s="6">
-        <v>-12.31</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3.68</v>
+        <v>-15.22</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-17.82</v>
+        <v>-12.31</v>
       </c>
       <c r="D36" s="6">
-        <v>-18</v>
+        <v>-10.68</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.18</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-4.51</v>
+        <v>-18</v>
       </c>
       <c r="D37" s="6">
-        <v>-7.28</v>
+        <v>-17.12</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.77</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-9.15</v>
+        <v>-7.28</v>
       </c>
       <c r="D38" s="6">
-        <v>-11.53</v>
+        <v>-4.85</v>
       </c>
       <c r="E38" s="7">
-        <v>-2.38</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-12.81</v>
+        <v>-11.53</v>
       </c>
       <c r="D39" s="6">
-        <v>-18.3</v>
+        <v>-8.57</v>
       </c>
       <c r="E39" s="7">
-        <v>-5.49</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-19.03</v>
+        <v>-18.3</v>
       </c>
       <c r="D40" s="6">
-        <v>-19.22</v>
+        <v>-16.97</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.19</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-3.41</v>
+        <v>-19.22</v>
       </c>
       <c r="D41" s="6">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-4.79</v>
+        <v>-19.47</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-15.19</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="D42" s="6">
-        <v>-16.12</v>
+        <v>-7.66</v>
       </c>
       <c r="E42" s="7">
-        <v>-0.93</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-36.72</v>
+        <v>-16.12</v>
       </c>
       <c r="D43" s="6">
-        <v>-37.84</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.12</v>
+        <v>-16.81</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-9.609999999999999</v>
+        <v>-37.84</v>
       </c>
       <c r="D44" s="6">
-        <v>-12.31</v>
+        <v>-37.75</v>
       </c>
       <c r="E44" s="7">
-        <v>-2.7</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-20.35</v>
+        <v>-12.31</v>
       </c>
       <c r="D45" s="6">
-        <v>-20.47</v>
+        <v>-10.84</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.12</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-4.51</v>
+        <v>-20.47</v>
       </c>
       <c r="D46" s="6">
-        <v>-7.72</v>
+        <v>-19.98</v>
       </c>
       <c r="E46" s="7">
-        <v>-3.21</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-18.04</v>
+        <v>-7.72</v>
       </c>
       <c r="D47" s="6">
-        <v>-21.17</v>
+        <v>-5.8</v>
       </c>
       <c r="E47" s="7">
-        <v>-3.13</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-34.88</v>
+        <v>-21.17</v>
       </c>
       <c r="D48" s="6">
-        <v>-36.93</v>
+        <v>-19.25</v>
       </c>
       <c r="E48" s="7">
-        <v>-2.05</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-26.52</v>
+        <v>-36.93</v>
       </c>
       <c r="D49" s="6">
-        <v>-27.86</v>
+        <v>-36.19</v>
       </c>
       <c r="E49" s="7">
-        <v>-1.34</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-35.99</v>
+        <v>-27.86</v>
       </c>
       <c r="D50" s="6">
-        <v>-36.8</v>
+        <v>-27.84</v>
       </c>
       <c r="E50" s="7">
-        <v>-0.8100000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-41.91</v>
+        <v>-36.8</v>
       </c>
       <c r="D51" s="6">
-        <v>-41.86</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.05</v>
+        <v>-36.55</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>1204.1</v>
+        <v>-41.86</v>
       </c>
       <c r="D52" s="6">
-        <v>1182.8</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-21.3</v>
+        <v>-42.48</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2903.4</v>
+        <v>1182.8</v>
       </c>
       <c r="D53" s="6">
-        <v>2816.8</v>
+        <v>1184.4</v>
       </c>
       <c r="E53" s="7">
-        <v>-86.59999999999999</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1278</v>
+        <v>2816.8</v>
       </c>
       <c r="D54" s="6">
-        <v>1276.1</v>
+        <v>2864</v>
       </c>
       <c r="E54" s="7">
-        <v>-1.9</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1798.3</v>
+        <v>1276.1</v>
       </c>
       <c r="D55" s="6">
-        <v>1737.8</v>
+        <v>1284</v>
       </c>
       <c r="E55" s="7">
-        <v>-60.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>204</v>
+        <v>1737.8</v>
       </c>
       <c r="D56" s="6">
-        <v>196.21</v>
+        <v>1774</v>
       </c>
       <c r="E56" s="7">
-        <v>-7.79</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>374</v>
+        <v>196.21</v>
       </c>
       <c r="D57" s="6">
-        <v>362.25</v>
+        <v>201</v>
       </c>
       <c r="E57" s="7">
-        <v>-11.75</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>593.9</v>
+        <v>362.25</v>
       </c>
       <c r="D58" s="6">
-        <v>583.05</v>
+        <v>366.5</v>
       </c>
       <c r="E58" s="7">
-        <v>-10.85</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>177.68</v>
+        <v>583.05</v>
       </c>
       <c r="D59" s="6">
-        <v>175.43</v>
+        <v>583.25</v>
       </c>
       <c r="E59" s="7">
-        <v>-2.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>69.14</v>
+        <v>175.43</v>
       </c>
       <c r="D60" s="6">
-        <v>68.08</v>
+        <v>176.15</v>
       </c>
       <c r="E60" s="7">
-        <v>-1.06</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>77</v>
+        <v>68.08</v>
       </c>
       <c r="D61" s="6">
-        <v>66</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
+        <v>67.19</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>66</v>
+        <v>27.59</v>
       </c>
       <c r="D62" s="6">
-        <v>77</v>
-      </c>
-      <c r="E62" s="8">
-        <v>11</v>
+        <v>28.34</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.75</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>31.68</v>
+        <v>40.41</v>
       </c>
       <c r="D63" s="6">
-        <v>27.59</v>
+        <v>44.03</v>
       </c>
       <c r="E63" s="7">
-        <v>-4.09</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>45.41</v>
+        <v>46.5</v>
       </c>
       <c r="D64" s="6">
-        <v>40.41</v>
+        <v>47.96</v>
       </c>
       <c r="E64" s="7">
-        <v>-5</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>46.79</v>
+        <v>48.13</v>
       </c>
       <c r="D65" s="6">
-        <v>46.5</v>
+        <v>52.42</v>
       </c>
       <c r="E65" s="7">
-        <v>-0.29</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>55.95</v>
+        <v>41.23</v>
       </c>
       <c r="D66" s="6">
-        <v>48.13</v>
+        <v>46.65</v>
       </c>
       <c r="E66" s="7">
-        <v>-7.82</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>48.7</v>
+        <v>29.77</v>
       </c>
       <c r="D67" s="6">
-        <v>41.23</v>
+        <v>33.79</v>
       </c>
       <c r="E67" s="7">
-        <v>-7.47</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>35.26</v>
+        <v>37.93</v>
       </c>
       <c r="D68" s="6">
-        <v>29.77</v>
+        <v>38.02</v>
       </c>
       <c r="E68" s="7">
-        <v>-5.49</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>41</v>
+        <v>30.69</v>
       </c>
       <c r="D69" s="6">
-        <v>37.93</v>
+        <v>32.63</v>
       </c>
       <c r="E69" s="7">
-        <v>-3.07</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>33.48</v>
+        <v>32.18</v>
       </c>
       <c r="D70" s="6">
-        <v>30.69</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-2.79</v>
+        <v>29.53</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>35.72</v>
+        <v>2.24</v>
       </c>
       <c r="D71" s="6">
-        <v>32.18</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-3.54</v>
+        <v>-41.32</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-43.56</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>-58.52</v>
+        <v>32.94</v>
       </c>
       <c r="D72" s="6">
-        <v>2.24</v>
+        <v>19.11</v>
       </c>
       <c r="E72" s="8">
-        <v>60.76</v>
+        <v>-13.83</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-21</v>
+        <v>348.82</v>
       </c>
       <c r="D73" s="6">
-        <v>32.94</v>
+        <v>-33.05</v>
       </c>
       <c r="E73" s="8">
-        <v>53.94</v>
+        <v>-381.87</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-0.67</v>
+        <v>-2.06</v>
       </c>
       <c r="D74" s="6">
-        <v>348.82</v>
-      </c>
-      <c r="E74" s="8">
-        <v>349.49</v>
+        <v>31.35</v>
+      </c>
+      <c r="E74" s="7">
+        <v>33.41</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>28.62</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="D75" s="6">
-        <v>-2.06</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-30.68</v>
+        <v>9.43</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-74.22</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>6.27</v>
+        <v>194.86</v>
       </c>
       <c r="D76" s="6">
-        <v>83.65000000000001</v>
+        <v>28.39</v>
       </c>
       <c r="E76" s="8">
-        <v>77.38</v>
+        <v>-166.47</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>153.14</v>
+        <v>-69.06999999999999</v>
       </c>
       <c r="D77" s="6">
-        <v>194.86</v>
+        <v>-80.61</v>
       </c>
       <c r="E77" s="8">
-        <v>41.72</v>
+        <v>-11.54</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-76.59999999999999</v>
+        <v>-4.84</v>
       </c>
       <c r="D78" s="6">
-        <v>-69.06999999999999</v>
+        <v>-59.24</v>
       </c>
       <c r="E78" s="8">
-        <v>7.53</v>
+        <v>-54.4</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-58.94</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="D79" s="6">
-        <v>-4.84</v>
-      </c>
-      <c r="E79" s="8">
-        <v>54.1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-46.92</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="E80" s="8">
-        <v>38.81</v>
+        <v>-7.5</v>
+      </c>
+      <c r="E79" s="7">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3446,28 +3444,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3481,16 +3479,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>37.2</v>
+        <v>39.3</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-4</v>
+        <v>-3.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3627,31 +3625,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5888</v>
+        <v>0.5667</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1943</v>
+        <v>0.1963</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1412</v>
+        <v>0.1345</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0208</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0132</v>
+        <v>-0.0116</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0379</v>
+        <v>-0.0482</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.08740000000000001</v>
+        <v>-0.0864</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1117</v>
+        <v>-0.1136</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1633</v>
+        <v>-0.1623</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,28 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.1 → 52.4</t>
+    <t>48.0 → 53.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.1</t>
-  </si>
-  <si>
-    <t>52.4</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.8 → 33.8</t>
-  </si>
-  <si>
-    <t>29.8</t>
-  </si>
-  <si>
-    <t>33.8</t>
+    <t>48.0</t>
+  </si>
+  <si>
+    <t>53.0</t>
+  </si>
+  <si>
+    <t>32.6 → 52.1</t>
+  </si>
+  <si>
+    <t>32.6</t>
+  </si>
+  <si>
+    <t>52.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -429,8 +426,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -942,58 +939,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1184.4</v>
+        <v>1177</v>
       </c>
       <c r="D2">
-        <v>0.14</v>
+        <v>-0.62</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1182.8</v>
+        <v>1177</v>
       </c>
       <c r="G2">
-        <v>-37.75</v>
+        <v>-38.14</v>
       </c>
       <c r="H2">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-4.21</v>
+        <v>-3.01</v>
       </c>
       <c r="J2">
-        <v>-6.49</v>
+        <v>-7.47</v>
       </c>
       <c r="K2">
-        <v>-15.22</v>
+        <v>-14.98</v>
       </c>
       <c r="L2">
-        <v>-34.1</v>
+        <v>-35.12</v>
       </c>
       <c r="M2">
-        <v>-11.36</v>
+        <v>-10.99</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P2">
-        <v>1197.48</v>
+        <v>1190.18</v>
       </c>
       <c r="Q2">
-        <v>1236.18</v>
+        <v>1230.84</v>
       </c>
       <c r="R2">
-        <v>1292.08</v>
+        <v>1288.8</v>
       </c>
       <c r="S2">
-        <v>1436.44</v>
+        <v>1433.52</v>
       </c>
       <c r="T2">
-        <v>-17.55</v>
+        <v>-17.89</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1008,43 +1005,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>28.34</v>
+        <v>26.96</v>
       </c>
       <c r="Z2">
-        <v>-27.04</v>
+        <v>-28.31</v>
       </c>
       <c r="AA2">
-        <v>-23.64</v>
+        <v>-24.57</v>
       </c>
       <c r="AB2">
-        <v>-3.41</v>
+        <v>-3.74</v>
       </c>
       <c r="AC2">
-        <v>10.44</v>
+        <v>1.63</v>
       </c>
       <c r="AD2">
-        <v>18.29</v>
+        <v>9.4</v>
       </c>
       <c r="AE2">
-        <v>24.71</v>
+        <v>24.22</v>
       </c>
       <c r="AF2">
-        <v>-41.32</v>
+        <v>-56.19</v>
       </c>
       <c r="AG2">
-        <v>1291.53</v>
+        <v>1287.44</v>
       </c>
       <c r="AH2">
-        <v>1180.83</v>
+        <v>1174.24</v>
       </c>
       <c r="AI2">
-        <v>1259.12</v>
+        <v>1255.56</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>33.97</v>
+        <v>37.66</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1055,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2864</v>
+        <v>2849.9</v>
       </c>
       <c r="D3">
-        <v>1.68</v>
+        <v>-0.49</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1067,46 +1064,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-10.84</v>
+        <v>-11.28</v>
       </c>
       <c r="H3">
-        <v>62.91</v>
+        <v>62.11</v>
       </c>
       <c r="I3">
-        <v>-1.8</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
-        <v>-0.96</v>
+        <v>-1.76</v>
       </c>
       <c r="K3">
-        <v>-10.68</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="L3">
-        <v>14.18</v>
+        <v>13.78</v>
       </c>
       <c r="M3">
-        <v>13.45</v>
+        <v>14.06</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P3">
-        <v>2877.64</v>
+        <v>2881.4</v>
       </c>
       <c r="Q3">
-        <v>2952.23</v>
+        <v>2947.83</v>
       </c>
       <c r="R3">
-        <v>2989.28</v>
+        <v>2985.75</v>
       </c>
       <c r="S3">
-        <v>2574.59</v>
+        <v>2577.6</v>
       </c>
       <c r="T3">
-        <v>11.24</v>
+        <v>10.56</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1121,34 +1118,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.03</v>
+        <v>43.19</v>
       </c>
       <c r="Z3">
-        <v>-35.46</v>
+        <v>-37.87</v>
       </c>
       <c r="AA3">
-        <v>-24.89</v>
+        <v>-27.48</v>
       </c>
       <c r="AB3">
-        <v>-10.57</v>
+        <v>-10.39</v>
       </c>
       <c r="AC3">
-        <v>32.49</v>
+        <v>31.19</v>
       </c>
       <c r="AD3">
-        <v>34.22</v>
+        <v>33.7</v>
       </c>
       <c r="AE3">
-        <v>88.01000000000001</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="AF3">
-        <v>19.11</v>
+        <v>-17.51</v>
       </c>
       <c r="AG3">
-        <v>3104.09</v>
+        <v>3106.39</v>
       </c>
       <c r="AH3">
-        <v>2800.38</v>
+        <v>2789.27</v>
       </c>
       <c r="AI3">
         <v>3101.6</v>
@@ -1157,7 +1154,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>28.03</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1168,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1284</v>
+        <v>1313</v>
       </c>
       <c r="D4">
-        <v>0.62</v>
+        <v>2.26</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1180,46 +1177,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.98</v>
+        <v>-18.17</v>
       </c>
       <c r="H4">
-        <v>66.15000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I4">
-        <v>-0.97</v>
+        <v>6.32</v>
       </c>
       <c r="J4">
-        <v>-0.93</v>
+        <v>2.31</v>
       </c>
       <c r="K4">
-        <v>-17.12</v>
+        <v>-13.56</v>
       </c>
       <c r="L4">
-        <v>24.02</v>
+        <v>27.87</v>
       </c>
       <c r="M4">
-        <v>0.99</v>
+        <v>1.57</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1266.62</v>
+        <v>1282.22</v>
       </c>
       <c r="Q4">
-        <v>1286.44</v>
+        <v>1287.03</v>
       </c>
       <c r="R4">
-        <v>1316.88</v>
+        <v>1315.24</v>
       </c>
       <c r="S4">
-        <v>1201.44</v>
+        <v>1202.86</v>
       </c>
       <c r="T4">
-        <v>6.87</v>
+        <v>9.16</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1234,34 +1231,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>47.96</v>
+        <v>53.02</v>
       </c>
       <c r="Z4">
-        <v>-13.07</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="AA4">
-        <v>-15.15</v>
+        <v>-14.03</v>
       </c>
       <c r="AB4">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="AC4">
-        <v>54.61</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="AD4">
-        <v>42.5</v>
+        <v>56.08</v>
       </c>
       <c r="AE4">
-        <v>37.89</v>
+        <v>38.68</v>
       </c>
       <c r="AF4">
-        <v>-33.05</v>
+        <v>78.94</v>
       </c>
       <c r="AG4">
-        <v>1331.06</v>
+        <v>1332.75</v>
       </c>
       <c r="AH4">
-        <v>1241.83</v>
+        <v>1241.31</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1270,7 +1267,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>16.59</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1281,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1774</v>
+        <v>1783.4</v>
       </c>
       <c r="D5">
-        <v>2.08</v>
+        <v>0.53</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1293,46 +1290,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-5.8</v>
+        <v>-5.3</v>
       </c>
       <c r="H5">
-        <v>36.66</v>
+        <v>37.38</v>
       </c>
       <c r="I5">
-        <v>-0.78</v>
+        <v>2.28</v>
       </c>
       <c r="J5">
-        <v>6.06</v>
+        <v>4.51</v>
       </c>
       <c r="K5">
-        <v>-4.85</v>
+        <v>-2.75</v>
       </c>
       <c r="L5">
-        <v>28.79</v>
+        <v>27.6</v>
       </c>
       <c r="M5">
-        <v>19.63</v>
+        <v>20.41</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>1775.16</v>
+        <v>1783.1</v>
       </c>
       <c r="Q5">
-        <v>1762.88</v>
+        <v>1766.69</v>
       </c>
       <c r="R5">
-        <v>1721.75</v>
+        <v>1722.05</v>
       </c>
       <c r="S5">
-        <v>1627.62</v>
+        <v>1629.08</v>
       </c>
       <c r="T5">
-        <v>8.99</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1347,34 +1344,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>52.42</v>
+        <v>53.49</v>
       </c>
       <c r="Z5">
-        <v>16.74</v>
+        <v>16.42</v>
       </c>
       <c r="AA5">
-        <v>18.1</v>
+        <v>17.76</v>
       </c>
       <c r="AB5">
-        <v>-1.35</v>
+        <v>-1.34</v>
       </c>
       <c r="AC5">
-        <v>23.43</v>
+        <v>20.24</v>
       </c>
       <c r="AD5">
-        <v>32.55</v>
+        <v>26.92</v>
       </c>
       <c r="AE5">
-        <v>45.6</v>
+        <v>44.34</v>
       </c>
       <c r="AF5">
-        <v>31.35</v>
+        <v>-21.57</v>
       </c>
       <c r="AG5">
-        <v>1841.87</v>
+        <v>1841.63</v>
       </c>
       <c r="AH5">
-        <v>1683.89</v>
+        <v>1691.74</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1383,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>24.93</v>
+        <v>23.51</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1394,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>201</v>
+        <v>202.4</v>
       </c>
       <c r="D6">
-        <v>2.44</v>
+        <v>0.7</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1406,46 +1403,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-19.25</v>
+        <v>-18.69</v>
       </c>
       <c r="H6">
-        <v>51.17</v>
+        <v>52.23</v>
       </c>
       <c r="I6">
-        <v>-0.86</v>
+        <v>3.19</v>
       </c>
       <c r="J6">
-        <v>-3.23</v>
+        <v>-2.83</v>
       </c>
       <c r="K6">
-        <v>-8.57</v>
+        <v>-7.19</v>
       </c>
       <c r="L6">
-        <v>37.06</v>
+        <v>39.92</v>
       </c>
       <c r="M6">
-        <v>56.67</v>
+        <v>58.39</v>
       </c>
       <c r="N6">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O6">
         <v>76</v>
       </c>
       <c r="P6">
-        <v>198.73</v>
+        <v>199.98</v>
       </c>
       <c r="Q6">
-        <v>204.48</v>
+        <v>204.24</v>
       </c>
       <c r="R6">
-        <v>206.58</v>
+        <v>206.35</v>
       </c>
       <c r="S6">
-        <v>188.39</v>
+        <v>188.67</v>
       </c>
       <c r="T6">
-        <v>6.7</v>
+        <v>7.28</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1460,34 +1457,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>46.65</v>
+        <v>48.15</v>
       </c>
       <c r="Z6">
-        <v>-2.46</v>
+        <v>-2.21</v>
       </c>
       <c r="AA6">
-        <v>-1.98</v>
+        <v>-2.03</v>
       </c>
       <c r="AB6">
-        <v>-0.48</v>
+        <v>-0.19</v>
       </c>
       <c r="AC6">
-        <v>54.34</v>
+        <v>64.92</v>
       </c>
       <c r="AD6">
-        <v>34.54</v>
+        <v>49.27</v>
       </c>
       <c r="AE6">
-        <v>6.34</v>
+        <v>6.2</v>
       </c>
       <c r="AF6">
-        <v>9.43</v>
+        <v>29.48</v>
       </c>
       <c r="AG6">
-        <v>214.9</v>
+        <v>214.61</v>
       </c>
       <c r="AH6">
-        <v>194.05</v>
+        <v>193.86</v>
       </c>
       <c r="AI6">
         <v>213.83</v>
@@ -1496,7 +1493,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>30.2</v>
+        <v>28.12</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1507,58 +1504,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>366.5</v>
+        <v>361.55</v>
       </c>
       <c r="D7">
-        <v>1.17</v>
+        <v>-1.35</v>
       </c>
       <c r="E7">
         <v>574.36</v>
       </c>
       <c r="F7">
-        <v>362.25</v>
+        <v>361.55</v>
       </c>
       <c r="G7">
-        <v>-36.19</v>
+        <v>-37.05</v>
       </c>
       <c r="H7">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>-4.51</v>
+        <v>-3.42</v>
       </c>
       <c r="J7">
-        <v>-8.99</v>
+        <v>-10.73</v>
       </c>
       <c r="K7">
-        <v>-16.97</v>
+        <v>-17.06</v>
       </c>
       <c r="L7">
-        <v>-34.48</v>
+        <v>-36.25</v>
       </c>
       <c r="M7">
-        <v>-1.16</v>
+        <v>-0.99</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="P7">
-        <v>368.57</v>
+        <v>366.01</v>
       </c>
       <c r="Q7">
-        <v>385.09</v>
+        <v>382.92</v>
       </c>
       <c r="R7">
-        <v>406.6</v>
+        <v>405.32</v>
       </c>
       <c r="S7">
-        <v>453.63</v>
+        <v>452.71</v>
       </c>
       <c r="T7">
-        <v>-19.21</v>
+        <v>-20.14</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1573,34 +1570,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>33.79</v>
+        <v>31.52</v>
       </c>
       <c r="Z7">
-        <v>-10.85</v>
+        <v>-11.31</v>
       </c>
       <c r="AA7">
-        <v>-9.49</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="AB7">
-        <v>-1.36</v>
+        <v>-1.45</v>
       </c>
       <c r="AC7">
-        <v>44.19</v>
+        <v>36.9</v>
       </c>
       <c r="AD7">
-        <v>35.02</v>
+        <v>36.96</v>
       </c>
       <c r="AE7">
-        <v>8.83</v>
+        <v>8.94</v>
       </c>
       <c r="AF7">
-        <v>28.39</v>
+        <v>60.76</v>
       </c>
       <c r="AG7">
-        <v>408.8</v>
+        <v>406.9</v>
       </c>
       <c r="AH7">
-        <v>361.39</v>
+        <v>358.94</v>
       </c>
       <c r="AI7">
         <v>390.68</v>
@@ -1609,7 +1606,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>49.2</v>
+        <v>51.76</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1620,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>583.25</v>
+        <v>588.45</v>
       </c>
       <c r="D8">
-        <v>0.03</v>
+        <v>0.89</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1632,25 +1629,25 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-27.84</v>
+        <v>-27.2</v>
       </c>
       <c r="H8">
-        <v>24.7</v>
+        <v>25.81</v>
       </c>
       <c r="I8">
-        <v>-4.64</v>
+        <v>-1.01</v>
       </c>
       <c r="J8">
-        <v>-5.15</v>
+        <v>-4.17</v>
       </c>
       <c r="K8">
-        <v>-19.47</v>
+        <v>-17.26</v>
       </c>
       <c r="L8">
-        <v>-7.34</v>
+        <v>-5.86</v>
       </c>
       <c r="M8">
-        <v>-16.23</v>
+        <v>-15.99</v>
       </c>
       <c r="N8">
         <v>55</v>
@@ -1659,19 +1656,19 @@
         <v>42</v>
       </c>
       <c r="P8">
-        <v>588.61</v>
+        <v>587.41</v>
       </c>
       <c r="Q8">
-        <v>605.33</v>
+        <v>604.14</v>
       </c>
       <c r="R8">
-        <v>631.26</v>
+        <v>629.97</v>
       </c>
       <c r="S8">
-        <v>614.53</v>
+        <v>614.54</v>
       </c>
       <c r="T8">
-        <v>-5.09</v>
+        <v>-4.25</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1686,34 +1683,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>38.02</v>
+        <v>40.49</v>
       </c>
       <c r="Z8">
-        <v>-12.12</v>
+        <v>-12.17</v>
       </c>
       <c r="AA8">
-        <v>-10.62</v>
+        <v>-10.93</v>
       </c>
       <c r="AB8">
-        <v>-1.5</v>
+        <v>-1.24</v>
       </c>
       <c r="AC8">
-        <v>41.24</v>
+        <v>38.07</v>
       </c>
       <c r="AD8">
-        <v>42.27</v>
+        <v>40.37</v>
       </c>
       <c r="AE8">
-        <v>18.43</v>
+        <v>17.81</v>
       </c>
       <c r="AF8">
-        <v>-80.61</v>
+        <v>-86.02</v>
       </c>
       <c r="AG8">
-        <v>646.78</v>
+        <v>646.11</v>
       </c>
       <c r="AH8">
-        <v>563.88</v>
+        <v>562.16</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1722,7 +1719,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.92</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1733,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>176.15</v>
+        <v>185.93</v>
       </c>
       <c r="D9">
-        <v>0.41</v>
+        <v>5.55</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1745,46 +1742,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-36.55</v>
+        <v>-33.02</v>
       </c>
       <c r="H9">
-        <v>2.23</v>
+        <v>7.91</v>
       </c>
       <c r="I9">
-        <v>-4.44</v>
+        <v>2.92</v>
       </c>
       <c r="J9">
-        <v>-7.9</v>
+        <v>-2.55</v>
       </c>
       <c r="K9">
-        <v>-7.66</v>
+        <v>0.3</v>
       </c>
       <c r="L9">
-        <v>-32.55</v>
+        <v>-28.91</v>
       </c>
       <c r="M9">
-        <v>-8.640000000000001</v>
+        <v>-7.57</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="P9">
-        <v>177.73</v>
+        <v>178.79</v>
       </c>
       <c r="Q9">
-        <v>183.4</v>
+        <v>183.33</v>
       </c>
       <c r="R9">
-        <v>188.86</v>
+        <v>188.81</v>
       </c>
       <c r="S9">
-        <v>196.27</v>
+        <v>195.99</v>
       </c>
       <c r="T9">
-        <v>-10.25</v>
+        <v>-5.13</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1799,34 +1796,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>32.63</v>
+        <v>52.15</v>
       </c>
       <c r="Z9">
-        <v>-3.44</v>
+        <v>-2.78</v>
       </c>
       <c r="AA9">
-        <v>-2.63</v>
+        <v>-2.66</v>
       </c>
       <c r="AB9">
-        <v>-0.8100000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="AC9">
-        <v>4.12</v>
+        <v>37.45</v>
       </c>
       <c r="AD9">
-        <v>6.39</v>
+        <v>14.76</v>
       </c>
       <c r="AE9">
-        <v>4.71</v>
+        <v>5.21</v>
       </c>
       <c r="AF9">
-        <v>-59.24</v>
+        <v>143.35</v>
       </c>
       <c r="AG9">
-        <v>191.14</v>
+        <v>190.95</v>
       </c>
       <c r="AH9">
-        <v>175.66</v>
+        <v>175.71</v>
       </c>
       <c r="AI9">
         <v>190.38</v>
@@ -1835,7 +1832,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>36.91</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1846,10 +1843,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>67.19</v>
+        <v>67.08</v>
       </c>
       <c r="D10">
-        <v>-1.31</v>
+        <v>-0.16</v>
       </c>
       <c r="E10">
         <v>116.81</v>
@@ -1858,43 +1855,43 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-42.48</v>
+        <v>-42.57</v>
       </c>
       <c r="H10">
-        <v>13.34</v>
+        <v>13.16</v>
       </c>
       <c r="I10">
-        <v>-4.12</v>
+        <v>-2.94</v>
       </c>
       <c r="J10">
-        <v>-5.15</v>
+        <v>-5.07</v>
       </c>
       <c r="K10">
-        <v>-16.81</v>
+        <v>-15.82</v>
       </c>
       <c r="L10">
-        <v>-42.62</v>
+        <v>-41.44</v>
       </c>
       <c r="M10">
-        <v>-4.82</v>
+        <v>-4.47</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P10">
-        <v>68.52</v>
+        <v>68.11</v>
       </c>
       <c r="Q10">
-        <v>70.94</v>
+        <v>70.58</v>
       </c>
       <c r="R10">
-        <v>73.61</v>
+        <v>73.41</v>
       </c>
       <c r="S10">
-        <v>79.72</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="T10">
         <v>-15.72</v>
@@ -1912,43 +1909,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>29.53</v>
+        <v>29.21</v>
       </c>
       <c r="Z10">
-        <v>-1.57</v>
+        <v>-1.66</v>
       </c>
       <c r="AA10">
-        <v>-1.36</v>
+        <v>-1.42</v>
       </c>
       <c r="AB10">
-        <v>-0.21</v>
+        <v>-0.24</v>
       </c>
       <c r="AC10">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>11.48</v>
+        <v>5.9</v>
       </c>
       <c r="AE10">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AF10">
-        <v>-7.5</v>
+        <v>7.57</v>
       </c>
       <c r="AG10">
-        <v>74.73999999999999</v>
+        <v>74.41</v>
       </c>
       <c r="AH10">
-        <v>67.13</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="AI10">
-        <v>74.78</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>35.33</v>
+        <v>38.55</v>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2129,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2149,27 +2146,27 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>59</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -2181,16 +2178,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2201,13 +2198,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-7.03</v>
+        <v>-6.49</v>
       </c>
       <c r="D8" s="6">
-        <v>-6.49</v>
+        <v>-7.47</v>
       </c>
       <c r="E8" s="7">
-        <v>0.54</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2218,13 +2215,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.64</v>
+        <v>-0.96</v>
       </c>
       <c r="D9" s="6">
-        <v>-0.96</v>
+        <v>-1.76</v>
       </c>
       <c r="E9" s="7">
-        <v>0.68</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2235,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>0.88</v>
+        <v>-0.93</v>
       </c>
       <c r="D10" s="6">
-        <v>-0.93</v>
+        <v>2.31</v>
       </c>
       <c r="E10" s="8">
-        <v>-1.81</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2252,13 +2249,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>5.48</v>
+        <v>6.06</v>
       </c>
       <c r="D11" s="6">
-        <v>6.06</v>
+        <v>4.51</v>
       </c>
       <c r="E11" s="7">
-        <v>0.58</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2269,13 +2266,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.99</v>
+        <v>-3.23</v>
       </c>
       <c r="D12" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.76</v>
+        <v>-2.83</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2286,13 +2283,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-9.93</v>
+        <v>-8.99</v>
       </c>
       <c r="D13" s="6">
-        <v>-8.99</v>
+        <v>-10.73</v>
       </c>
       <c r="E13" s="7">
-        <v>0.9399999999999999</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2303,13 +2300,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.99</v>
+        <v>-5.15</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.15</v>
+        <v>-4.17</v>
       </c>
       <c r="E14" s="8">
-        <v>-0.16</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2320,13 +2317,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-9.75</v>
+        <v>-7.9</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.9</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.85</v>
+        <v>-2.55</v>
+      </c>
+      <c r="E15" s="8">
+        <v>5.35</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2337,13 +2334,13 @@
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.68</v>
+        <v>-5.15</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.15</v>
+        <v>-5.07</v>
       </c>
       <c r="E16" s="8">
-        <v>-0.47</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2354,13 +2351,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.31</v>
+        <v>-4.21</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.21</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.1</v>
+        <v>-3.01</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2371,13 +2368,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.87</v>
+        <v>-1.8</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.8</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.07</v>
+        <v>0.66</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.46</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2388,13 +2385,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.31</v>
+        <v>-0.97</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.97</v>
+        <v>6.32</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.66</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2405,13 +2402,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-2.66</v>
+        <v>-0.78</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.88</v>
+        <v>2.28</v>
+      </c>
+      <c r="E20" s="8">
+        <v>3.06</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2422,13 +2419,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.64</v>
+        <v>-0.86</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.86</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.78</v>
+        <v>3.19</v>
+      </c>
+      <c r="E21" s="8">
+        <v>4.05</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2439,13 +2436,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.69</v>
+        <v>-4.51</v>
       </c>
       <c r="D22" s="6">
-        <v>-4.51</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.18</v>
+        <v>-3.42</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2456,13 +2453,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.79</v>
+        <v>-4.64</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.64</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.15</v>
+        <v>-1.01</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3.63</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2473,13 +2470,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-5.01</v>
+        <v>-4.44</v>
       </c>
       <c r="D24" s="6">
-        <v>-4.44</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.57</v>
+        <v>2.92</v>
+      </c>
+      <c r="E24" s="8">
+        <v>7.36</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2490,13 +2487,13 @@
         <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-2.65</v>
+        <v>-4.12</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.12</v>
+        <v>-2.94</v>
       </c>
       <c r="E25" s="8">
-        <v>-1.47</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2507,13 +2504,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-34.79</v>
+        <v>-34.1</v>
       </c>
       <c r="D26" s="6">
-        <v>-34.1</v>
+        <v>-35.12</v>
       </c>
       <c r="E26" s="7">
-        <v>0.6899999999999999</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2524,13 +2521,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>10.79</v>
+        <v>14.18</v>
       </c>
       <c r="D27" s="6">
-        <v>14.18</v>
+        <v>13.78</v>
       </c>
       <c r="E27" s="7">
-        <v>3.39</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2541,13 +2538,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>21.84</v>
+        <v>24.02</v>
       </c>
       <c r="D28" s="6">
-        <v>24.02</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.18</v>
+        <v>27.87</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3.85</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2558,13 +2555,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>25.37</v>
+        <v>28.79</v>
       </c>
       <c r="D29" s="6">
-        <v>28.79</v>
+        <v>27.6</v>
       </c>
       <c r="E29" s="7">
-        <v>3.42</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2575,13 +2572,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>34.16</v>
+        <v>37.06</v>
       </c>
       <c r="D30" s="6">
-        <v>37.06</v>
-      </c>
-      <c r="E30" s="7">
-        <v>2.9</v>
+        <v>39.92</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.86</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2592,13 +2589,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-35.59</v>
+        <v>-34.48</v>
       </c>
       <c r="D31" s="6">
-        <v>-34.48</v>
+        <v>-36.25</v>
       </c>
       <c r="E31" s="7">
-        <v>1.11</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2609,13 +2606,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-10.16</v>
+        <v>-7.34</v>
       </c>
       <c r="D32" s="6">
-        <v>-7.34</v>
-      </c>
-      <c r="E32" s="7">
-        <v>2.82</v>
+        <v>-5.86</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.48</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2626,13 +2623,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-32.9</v>
+        <v>-32.55</v>
       </c>
       <c r="D33" s="6">
-        <v>-32.55</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.35</v>
+        <v>-28.91</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3.64</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2643,13 +2640,13 @@
         <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-42.8</v>
+        <v>-42.62</v>
       </c>
       <c r="D34" s="6">
-        <v>-42.62</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.18</v>
+        <v>-41.44</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.18</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2660,13 +2657,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-15.14</v>
+        <v>-15.22</v>
       </c>
       <c r="D35" s="6">
-        <v>-15.22</v>
+        <v>-14.98</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.08</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2677,13 +2674,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-12.31</v>
+        <v>-10.68</v>
       </c>
       <c r="D36" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.63</v>
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.4</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2694,13 +2691,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-18</v>
+        <v>-17.12</v>
       </c>
       <c r="D37" s="6">
-        <v>-17.12</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.88</v>
+        <v>-13.56</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.56</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2711,13 +2708,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-7.28</v>
+        <v>-4.85</v>
       </c>
       <c r="D38" s="6">
-        <v>-4.85</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.43</v>
+        <v>-2.75</v>
+      </c>
+      <c r="E38" s="8">
+        <v>2.1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2728,13 +2725,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-11.53</v>
+        <v>-8.57</v>
       </c>
       <c r="D39" s="6">
-        <v>-8.57</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.96</v>
+        <v>-7.19</v>
+      </c>
+      <c r="E39" s="8">
+        <v>1.38</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2745,13 +2742,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-18.3</v>
+        <v>-16.97</v>
       </c>
       <c r="D40" s="6">
-        <v>-16.97</v>
+        <v>-17.06</v>
       </c>
       <c r="E40" s="7">
-        <v>1.33</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2762,13 +2759,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-19.22</v>
+        <v>-19.47</v>
       </c>
       <c r="D41" s="6">
-        <v>-19.47</v>
+        <v>-17.26</v>
       </c>
       <c r="E41" s="8">
-        <v>-0.25</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2779,13 +2776,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-8.199999999999999</v>
+        <v>-7.66</v>
       </c>
       <c r="D42" s="6">
-        <v>-7.66</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.54</v>
+        <v>0.3</v>
+      </c>
+      <c r="E42" s="8">
+        <v>7.96</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2796,13 +2793,13 @@
         <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-16.12</v>
+        <v>-16.81</v>
       </c>
       <c r="D43" s="6">
-        <v>-16.81</v>
+        <v>-15.82</v>
       </c>
       <c r="E43" s="8">
-        <v>-0.6899999999999999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2813,13 +2810,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-37.84</v>
+        <v>-37.75</v>
       </c>
       <c r="D44" s="6">
-        <v>-37.75</v>
+        <v>-38.14</v>
       </c>
       <c r="E44" s="7">
-        <v>0.09</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2830,13 +2827,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-12.31</v>
+        <v>-10.84</v>
       </c>
       <c r="D45" s="6">
-        <v>-10.84</v>
+        <v>-11.28</v>
       </c>
       <c r="E45" s="7">
-        <v>1.47</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2847,13 +2844,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-20.47</v>
+        <v>-19.98</v>
       </c>
       <c r="D46" s="6">
-        <v>-19.98</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.49</v>
+        <v>-18.17</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.81</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2864,13 +2861,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-7.72</v>
+        <v>-5.8</v>
       </c>
       <c r="D47" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.92</v>
+        <v>-5.3</v>
+      </c>
+      <c r="E47" s="8">
+        <v>0.5</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2881,13 +2878,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-21.17</v>
+        <v>-19.25</v>
       </c>
       <c r="D48" s="6">
-        <v>-19.25</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.92</v>
+        <v>-18.69</v>
+      </c>
+      <c r="E48" s="8">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2898,13 +2895,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-36.93</v>
+        <v>-36.19</v>
       </c>
       <c r="D49" s="6">
-        <v>-36.19</v>
+        <v>-37.05</v>
       </c>
       <c r="E49" s="7">
-        <v>0.74</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2915,13 +2912,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-27.86</v>
+        <v>-27.84</v>
       </c>
       <c r="D50" s="6">
-        <v>-27.84</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.02</v>
+        <v>-27.2</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.64</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2932,13 +2929,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-36.8</v>
+        <v>-36.55</v>
       </c>
       <c r="D51" s="6">
-        <v>-36.55</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.25</v>
+        <v>-33.02</v>
+      </c>
+      <c r="E51" s="8">
+        <v>3.53</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2949,13 +2946,13 @@
         <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>-41.86</v>
+        <v>-42.48</v>
       </c>
       <c r="D52" s="6">
-        <v>-42.48</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.62</v>
+        <v>-42.57</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2966,13 +2963,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>1182.8</v>
+        <v>1184.4</v>
       </c>
       <c r="D53" s="6">
-        <v>1184.4</v>
+        <v>1177</v>
       </c>
       <c r="E53" s="7">
-        <v>1.6</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2983,13 +2980,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>2816.8</v>
+        <v>2864</v>
       </c>
       <c r="D54" s="6">
-        <v>2864</v>
+        <v>2849.9</v>
       </c>
       <c r="E54" s="7">
-        <v>47.2</v>
+        <v>-14.1</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -3000,13 +2997,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1276.1</v>
+        <v>1284</v>
       </c>
       <c r="D55" s="6">
-        <v>1284</v>
-      </c>
-      <c r="E55" s="7">
-        <v>7.9</v>
+        <v>1313</v>
+      </c>
+      <c r="E55" s="8">
+        <v>29</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3017,13 +3014,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1737.8</v>
+        <v>1774</v>
       </c>
       <c r="D56" s="6">
-        <v>1774</v>
-      </c>
-      <c r="E56" s="7">
-        <v>36.2</v>
+        <v>1783.4</v>
+      </c>
+      <c r="E56" s="8">
+        <v>9.4</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3034,13 +3031,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>196.21</v>
+        <v>201</v>
       </c>
       <c r="D57" s="6">
-        <v>201</v>
-      </c>
-      <c r="E57" s="7">
-        <v>4.79</v>
+        <v>202.4</v>
+      </c>
+      <c r="E57" s="8">
+        <v>1.4</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3051,13 +3048,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>362.25</v>
+        <v>366.5</v>
       </c>
       <c r="D58" s="6">
-        <v>366.5</v>
+        <v>361.55</v>
       </c>
       <c r="E58" s="7">
-        <v>4.25</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3068,13 +3065,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>583.05</v>
+        <v>583.25</v>
       </c>
       <c r="D59" s="6">
-        <v>583.25</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0.2</v>
+        <v>588.45</v>
+      </c>
+      <c r="E59" s="8">
+        <v>5.2</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3085,13 +3082,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>175.43</v>
+        <v>176.15</v>
       </c>
       <c r="D60" s="6">
-        <v>176.15</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.72</v>
+        <v>185.93</v>
+      </c>
+      <c r="E60" s="8">
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3102,319 +3099,353 @@
         <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>68.08</v>
+        <v>67.19</v>
       </c>
       <c r="D61" s="6">
-        <v>67.19</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.89</v>
+        <v>67.08</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>27.59</v>
+        <v>99</v>
       </c>
       <c r="D62" s="6">
-        <v>28.34</v>
+        <v>88</v>
       </c>
       <c r="E62" s="7">
-        <v>0.75</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>40.41</v>
+        <v>88</v>
       </c>
       <c r="D63" s="6">
-        <v>44.03</v>
-      </c>
-      <c r="E63" s="7">
-        <v>3.62</v>
+        <v>99</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>46.5</v>
+        <v>28.34</v>
       </c>
       <c r="D64" s="6">
-        <v>47.96</v>
+        <v>26.96</v>
       </c>
       <c r="E64" s="7">
-        <v>1.46</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>48.13</v>
+        <v>44.03</v>
       </c>
       <c r="D65" s="6">
-        <v>52.42</v>
+        <v>43.19</v>
       </c>
       <c r="E65" s="7">
-        <v>4.29</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>41.23</v>
+        <v>47.96</v>
       </c>
       <c r="D66" s="6">
-        <v>46.65</v>
-      </c>
-      <c r="E66" s="7">
-        <v>5.42</v>
+        <v>53.02</v>
+      </c>
+      <c r="E66" s="8">
+        <v>5.06</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>29.77</v>
+        <v>52.42</v>
       </c>
       <c r="D67" s="6">
-        <v>33.79</v>
-      </c>
-      <c r="E67" s="7">
-        <v>4.02</v>
+        <v>53.49</v>
+      </c>
+      <c r="E67" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>37.93</v>
+        <v>46.65</v>
       </c>
       <c r="D68" s="6">
-        <v>38.02</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.09</v>
+        <v>48.15</v>
+      </c>
+      <c r="E68" s="8">
+        <v>1.5</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>30.69</v>
+        <v>33.79</v>
       </c>
       <c r="D69" s="6">
-        <v>32.63</v>
+        <v>31.52</v>
       </c>
       <c r="E69" s="7">
-        <v>1.94</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>32.18</v>
+        <v>38.02</v>
       </c>
       <c r="D70" s="6">
-        <v>29.53</v>
+        <v>40.49</v>
       </c>
       <c r="E70" s="8">
-        <v>-2.65</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>2.24</v>
+        <v>32.63</v>
       </c>
       <c r="D71" s="6">
-        <v>-41.32</v>
+        <v>52.15</v>
       </c>
       <c r="E71" s="8">
-        <v>-43.56</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>32.94</v>
+        <v>29.53</v>
       </c>
       <c r="D72" s="6">
-        <v>19.11</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-13.83</v>
+        <v>29.21</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>348.82</v>
+        <v>-41.32</v>
       </c>
       <c r="D73" s="6">
-        <v>-33.05</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-381.87</v>
+        <v>-56.19</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-14.87</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-2.06</v>
+        <v>19.11</v>
       </c>
       <c r="D74" s="6">
-        <v>31.35</v>
+        <v>-17.51</v>
       </c>
       <c r="E74" s="7">
-        <v>33.41</v>
+        <v>-36.62</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>83.65000000000001</v>
+        <v>-33.05</v>
       </c>
       <c r="D75" s="6">
-        <v>9.43</v>
+        <v>78.94</v>
       </c>
       <c r="E75" s="8">
-        <v>-74.22</v>
+        <v>111.99</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>194.86</v>
+        <v>31.35</v>
       </c>
       <c r="D76" s="6">
-        <v>28.39</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-166.47</v>
+        <v>-21.57</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-52.92</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-69.06999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="D77" s="6">
-        <v>-80.61</v>
+        <v>29.48</v>
       </c>
       <c r="E77" s="8">
-        <v>-11.54</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-4.84</v>
+        <v>28.39</v>
       </c>
       <c r="D78" s="6">
-        <v>-59.24</v>
+        <v>60.76</v>
       </c>
       <c r="E78" s="8">
-        <v>-54.4</v>
+        <v>32.37</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-8.109999999999999</v>
+        <v>-80.61</v>
       </c>
       <c r="D79" s="6">
+        <v>-86.02</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-5.41</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-59.24</v>
+      </c>
+      <c r="D80" s="6">
+        <v>143.35</v>
+      </c>
+      <c r="E80" s="8">
+        <v>202.59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
         <v>-7.5</v>
       </c>
-      <c r="E79" s="7">
-        <v>0.61</v>
+      <c r="D81" s="6">
+        <v>7.57</v>
+      </c>
+      <c r="E81" s="8">
+        <v>15.07</v>
       </c>
     </row>
   </sheetData>
@@ -3444,28 +3475,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3479,16 +3510,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>39.3</v>
+        <v>42</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.6</v>
+        <v>-3.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-13</v>
+        <v>-10.7</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3625,31 +3656,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5667</v>
+        <v>0.5839</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1963</v>
+        <v>0.2041</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1345</v>
+        <v>0.1406</v>
       </c>
       <c r="D2" s="14">
-        <v>0.009899999999999999</v>
+        <v>0.0157</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0116</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0482</v>
+        <v>-0.0447</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.0864</v>
+        <v>-0.0757</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1136</v>
+        <v>-0.1099</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1623</v>
+        <v>-0.1599</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,25 +196,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.0 → 53.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.0</t>
-  </si>
-  <si>
-    <t>53.0</t>
-  </si>
-  <si>
-    <t>32.6 → 52.1</t>
-  </si>
-  <si>
-    <t>32.6</t>
-  </si>
-  <si>
-    <t>52.1</t>
+    <t>53.5 → 49.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.5</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -300,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -340,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -939,58 +930,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1177</v>
+        <v>1165.5</v>
       </c>
       <c r="D2">
-        <v>-0.62</v>
+        <v>-0.98</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1177</v>
+        <v>1165.5</v>
       </c>
       <c r="G2">
-        <v>-38.14</v>
+        <v>-38.74</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-3.01</v>
+        <v>-3.08</v>
       </c>
       <c r="J2">
-        <v>-7.47</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="K2">
-        <v>-14.98</v>
+        <v>-12.7</v>
       </c>
       <c r="L2">
-        <v>-35.12</v>
+        <v>-35.87</v>
       </c>
       <c r="M2">
-        <v>-10.99</v>
+        <v>-11.66</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P2">
-        <v>1190.18</v>
+        <v>1182.76</v>
       </c>
       <c r="Q2">
-        <v>1230.84</v>
+        <v>1225.68</v>
       </c>
       <c r="R2">
-        <v>1288.8</v>
+        <v>1284.95</v>
       </c>
       <c r="S2">
-        <v>1433.52</v>
+        <v>1430.6</v>
       </c>
       <c r="T2">
-        <v>-17.89</v>
+        <v>-18.53</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1005,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>26.96</v>
+        <v>24.91</v>
       </c>
       <c r="Z2">
-        <v>-28.31</v>
+        <v>-29.9</v>
       </c>
       <c r="AA2">
-        <v>-24.57</v>
+        <v>-25.64</v>
       </c>
       <c r="AB2">
-        <v>-3.74</v>
+        <v>-4.26</v>
       </c>
       <c r="AC2">
         <v>1.63</v>
       </c>
       <c r="AD2">
-        <v>9.4</v>
+        <v>4.57</v>
       </c>
       <c r="AE2">
-        <v>24.22</v>
+        <v>24.1</v>
       </c>
       <c r="AF2">
-        <v>-56.19</v>
+        <v>-32.82</v>
       </c>
       <c r="AG2">
-        <v>1287.44</v>
+        <v>1286.41</v>
       </c>
       <c r="AH2">
-        <v>1174.24</v>
+        <v>1164.95</v>
       </c>
       <c r="AI2">
-        <v>1255.56</v>
+        <v>1243.71</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>37.66</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1052,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2849.9</v>
+        <v>2743</v>
       </c>
       <c r="D3">
-        <v>-0.49</v>
+        <v>-3.75</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1064,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-11.28</v>
+        <v>-14.6</v>
       </c>
       <c r="H3">
-        <v>62.11</v>
+        <v>56.03</v>
       </c>
       <c r="I3">
-        <v>0.66</v>
+        <v>-7.73</v>
       </c>
       <c r="J3">
-        <v>-1.76</v>
+        <v>-6.64</v>
       </c>
       <c r="K3">
-        <v>-8.279999999999999</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="L3">
-        <v>13.78</v>
+        <v>5.84</v>
       </c>
       <c r="M3">
-        <v>14.06</v>
+        <v>12.57</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>2881.4</v>
+        <v>2835.42</v>
       </c>
       <c r="Q3">
-        <v>2947.83</v>
+        <v>2937.48</v>
       </c>
       <c r="R3">
-        <v>2985.75</v>
+        <v>2979.88</v>
       </c>
       <c r="S3">
-        <v>2577.6</v>
+        <v>2580.16</v>
       </c>
       <c r="T3">
-        <v>10.56</v>
+        <v>6.31</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1118,43 +1109,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.19</v>
+        <v>37.35</v>
       </c>
       <c r="Z3">
-        <v>-37.87</v>
+        <v>-47.86</v>
       </c>
       <c r="AA3">
-        <v>-27.48</v>
+        <v>-31.56</v>
       </c>
       <c r="AB3">
-        <v>-10.39</v>
+        <v>-16.3</v>
       </c>
       <c r="AC3">
-        <v>31.19</v>
+        <v>26.49</v>
       </c>
       <c r="AD3">
-        <v>33.7</v>
+        <v>30.05</v>
       </c>
       <c r="AE3">
-        <v>85.54000000000001</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="AF3">
-        <v>-17.51</v>
+        <v>14.06</v>
       </c>
       <c r="AG3">
-        <v>3106.39</v>
+        <v>3120.57</v>
       </c>
       <c r="AH3">
-        <v>2789.27</v>
+        <v>2754.39</v>
       </c>
       <c r="AI3">
-        <v>3101.6</v>
+        <v>3053.71</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>30.41</v>
+        <v>34.76</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1165,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1313</v>
+        <v>1341.4</v>
       </c>
       <c r="D4">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1177,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.17</v>
+        <v>-16.4</v>
       </c>
       <c r="H4">
-        <v>69.90000000000001</v>
+        <v>73.58</v>
       </c>
       <c r="I4">
-        <v>6.32</v>
+        <v>6.46</v>
       </c>
       <c r="J4">
-        <v>2.31</v>
+        <v>3.08</v>
       </c>
       <c r="K4">
-        <v>-13.56</v>
+        <v>-10.85</v>
       </c>
       <c r="L4">
-        <v>27.87</v>
+        <v>25.99</v>
       </c>
       <c r="M4">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>1282.22</v>
+        <v>1298.5</v>
       </c>
       <c r="Q4">
-        <v>1287.03</v>
+        <v>1289.7</v>
       </c>
       <c r="R4">
-        <v>1315.24</v>
+        <v>1314.07</v>
       </c>
       <c r="S4">
-        <v>1202.86</v>
+        <v>1204.47</v>
       </c>
       <c r="T4">
-        <v>9.16</v>
+        <v>11.37</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1231,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>53.02</v>
+        <v>57.39</v>
       </c>
       <c r="Z4">
-        <v>-9.529999999999999</v>
+        <v>-4.38</v>
       </c>
       <c r="AA4">
-        <v>-14.03</v>
+        <v>-12.1</v>
       </c>
       <c r="AB4">
-        <v>4.5</v>
+        <v>7.72</v>
       </c>
       <c r="AC4">
-        <v>68.73999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="AD4">
-        <v>56.08</v>
+        <v>69.52</v>
       </c>
       <c r="AE4">
-        <v>38.68</v>
+        <v>40.71</v>
       </c>
       <c r="AF4">
-        <v>78.94</v>
+        <v>326.71</v>
       </c>
       <c r="AG4">
-        <v>1332.75</v>
+        <v>1341.5</v>
       </c>
       <c r="AH4">
-        <v>1241.31</v>
+        <v>1237.9</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1267,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>17.82</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1278,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1783.4</v>
+        <v>1750.1</v>
       </c>
       <c r="D5">
-        <v>0.53</v>
+        <v>-1.87</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1290,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-5.3</v>
+        <v>-7.07</v>
       </c>
       <c r="H5">
-        <v>37.38</v>
+        <v>34.82</v>
       </c>
       <c r="I5">
-        <v>2.28</v>
+        <v>-3.95</v>
       </c>
       <c r="J5">
-        <v>4.51</v>
+        <v>2.51</v>
       </c>
       <c r="K5">
-        <v>-2.75</v>
+        <v>-2.32</v>
       </c>
       <c r="L5">
-        <v>27.6</v>
+        <v>23.53</v>
       </c>
       <c r="M5">
-        <v>20.41</v>
+        <v>19.56</v>
       </c>
       <c r="N5">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1783.1</v>
+        <v>1768.72</v>
       </c>
       <c r="Q5">
-        <v>1766.69</v>
+        <v>1769.48</v>
       </c>
       <c r="R5">
-        <v>1722.05</v>
+        <v>1721.65</v>
       </c>
       <c r="S5">
-        <v>1629.08</v>
+        <v>1630.43</v>
       </c>
       <c r="T5">
-        <v>9.470000000000001</v>
+        <v>7.34</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1344,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.49</v>
+        <v>49.25</v>
       </c>
       <c r="Z5">
-        <v>16.42</v>
+        <v>13.33</v>
       </c>
       <c r="AA5">
-        <v>17.76</v>
+        <v>16.88</v>
       </c>
       <c r="AB5">
-        <v>-1.34</v>
+        <v>-3.55</v>
       </c>
       <c r="AC5">
-        <v>20.24</v>
+        <v>22.58</v>
       </c>
       <c r="AD5">
-        <v>26.92</v>
+        <v>22.08</v>
       </c>
       <c r="AE5">
-        <v>44.34</v>
+        <v>44.5</v>
       </c>
       <c r="AF5">
-        <v>-21.57</v>
+        <v>-42.54</v>
       </c>
       <c r="AG5">
-        <v>1841.63</v>
+        <v>1836.84</v>
       </c>
       <c r="AH5">
-        <v>1691.74</v>
+        <v>1702.11</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1380,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>23.51</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1391,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>202.4</v>
+        <v>196.94</v>
       </c>
       <c r="D6">
-        <v>0.7</v>
+        <v>-2.7</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1403,46 +1394,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-18.69</v>
+        <v>-20.88</v>
       </c>
       <c r="H6">
-        <v>52.23</v>
+        <v>48.12</v>
       </c>
       <c r="I6">
-        <v>3.19</v>
+        <v>0.33</v>
       </c>
       <c r="J6">
-        <v>-2.83</v>
+        <v>-4.95</v>
       </c>
       <c r="K6">
-        <v>-7.19</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L6">
-        <v>39.92</v>
+        <v>29.13</v>
       </c>
       <c r="M6">
-        <v>58.39</v>
+        <v>57.4</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="P6">
-        <v>199.98</v>
+        <v>200.11</v>
       </c>
       <c r="Q6">
-        <v>204.24</v>
+        <v>203.86</v>
       </c>
       <c r="R6">
-        <v>206.35</v>
+        <v>206.01</v>
       </c>
       <c r="S6">
-        <v>188.67</v>
+        <v>188.94</v>
       </c>
       <c r="T6">
-        <v>7.28</v>
+        <v>4.23</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1457,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>48.15</v>
+        <v>43.05</v>
       </c>
       <c r="Z6">
-        <v>-2.21</v>
+        <v>-2.43</v>
       </c>
       <c r="AA6">
-        <v>-2.03</v>
+        <v>-2.11</v>
       </c>
       <c r="AB6">
-        <v>-0.19</v>
+        <v>-0.33</v>
       </c>
       <c r="AC6">
-        <v>64.92</v>
+        <v>72.14</v>
       </c>
       <c r="AD6">
-        <v>49.27</v>
+        <v>63.8</v>
       </c>
       <c r="AE6">
-        <v>6.2</v>
+        <v>6.29</v>
       </c>
       <c r="AF6">
-        <v>29.48</v>
+        <v>2.36</v>
       </c>
       <c r="AG6">
-        <v>214.61</v>
+        <v>214.73</v>
       </c>
       <c r="AH6">
-        <v>193.86</v>
+        <v>192.98</v>
       </c>
       <c r="AI6">
         <v>213.83</v>
@@ -1493,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>28.12</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1504,58 +1495,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>361.55</v>
+        <v>356.9</v>
       </c>
       <c r="D7">
-        <v>-1.35</v>
+        <v>-1.29</v>
       </c>
       <c r="E7">
         <v>574.36</v>
       </c>
       <c r="F7">
-        <v>361.55</v>
+        <v>356.9</v>
       </c>
       <c r="G7">
-        <v>-37.05</v>
+        <v>-37.86</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-3.42</v>
+        <v>-2.42</v>
       </c>
       <c r="J7">
-        <v>-10.73</v>
+        <v>-11.88</v>
       </c>
       <c r="K7">
-        <v>-17.06</v>
+        <v>-15.25</v>
       </c>
       <c r="L7">
-        <v>-36.25</v>
+        <v>-37.2</v>
       </c>
       <c r="M7">
-        <v>-0.99</v>
+        <v>-1.64</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P7">
-        <v>366.01</v>
+        <v>364.24</v>
       </c>
       <c r="Q7">
-        <v>382.92</v>
+        <v>380.83</v>
       </c>
       <c r="R7">
-        <v>405.32</v>
+        <v>403.84</v>
       </c>
       <c r="S7">
-        <v>452.71</v>
+        <v>451.8</v>
       </c>
       <c r="T7">
-        <v>-20.14</v>
+        <v>-21</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1570,43 +1561,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>31.52</v>
+        <v>29.52</v>
       </c>
       <c r="Z7">
-        <v>-11.31</v>
+        <v>-11.91</v>
       </c>
       <c r="AA7">
-        <v>-9.859999999999999</v>
+        <v>-10.27</v>
       </c>
       <c r="AB7">
-        <v>-1.45</v>
+        <v>-1.64</v>
       </c>
       <c r="AC7">
-        <v>36.9</v>
+        <v>34.83</v>
       </c>
       <c r="AD7">
-        <v>36.96</v>
+        <v>38.64</v>
       </c>
       <c r="AE7">
-        <v>8.94</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AF7">
-        <v>60.76</v>
+        <v>126.14</v>
       </c>
       <c r="AG7">
-        <v>406.9</v>
+        <v>406.29</v>
       </c>
       <c r="AH7">
-        <v>358.94</v>
+        <v>355.38</v>
       </c>
       <c r="AI7">
-        <v>390.68</v>
+        <v>384.71</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>51.76</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1617,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>588.45</v>
+        <v>581.9</v>
       </c>
       <c r="D8">
-        <v>0.89</v>
+        <v>-1.11</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1629,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-27.2</v>
+        <v>-28.01</v>
       </c>
       <c r="H8">
-        <v>25.81</v>
+        <v>24.41</v>
       </c>
       <c r="I8">
-        <v>-1.01</v>
+        <v>-1.1</v>
       </c>
       <c r="J8">
-        <v>-4.17</v>
+        <v>-4.97</v>
       </c>
       <c r="K8">
-        <v>-17.26</v>
+        <v>-16.71</v>
       </c>
       <c r="L8">
-        <v>-5.86</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="M8">
-        <v>-15.99</v>
+        <v>-16.38</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O8">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P8">
-        <v>587.41</v>
+        <v>586.11</v>
       </c>
       <c r="Q8">
-        <v>604.14</v>
+        <v>603.05</v>
       </c>
       <c r="R8">
-        <v>629.97</v>
+        <v>628.4</v>
       </c>
       <c r="S8">
-        <v>614.54</v>
+        <v>614.53</v>
       </c>
       <c r="T8">
-        <v>-4.25</v>
+        <v>-5.31</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1683,34 +1674,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>40.49</v>
+        <v>38.41</v>
       </c>
       <c r="Z8">
-        <v>-12.17</v>
+        <v>-12.59</v>
       </c>
       <c r="AA8">
-        <v>-10.93</v>
+        <v>-11.26</v>
       </c>
       <c r="AB8">
-        <v>-1.24</v>
+        <v>-1.33</v>
       </c>
       <c r="AC8">
-        <v>38.07</v>
+        <v>35.19</v>
       </c>
       <c r="AD8">
-        <v>40.37</v>
+        <v>38.17</v>
       </c>
       <c r="AE8">
-        <v>17.81</v>
+        <v>17.62</v>
       </c>
       <c r="AF8">
-        <v>-86.02</v>
+        <v>-78.17</v>
       </c>
       <c r="AG8">
-        <v>646.11</v>
+        <v>646.1900000000001</v>
       </c>
       <c r="AH8">
-        <v>562.16</v>
+        <v>559.9</v>
       </c>
       <c r="AI8">
         <v>580.38</v>
@@ -1719,7 +1710,7 @@
         <v>50</v>
       </c>
       <c r="AK8">
-        <v>26.95</v>
+        <v>27.58</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1730,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>185.93</v>
+        <v>187.11</v>
       </c>
       <c r="D9">
-        <v>5.55</v>
+        <v>0.63</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1742,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.02</v>
+        <v>-32.6</v>
       </c>
       <c r="H9">
-        <v>7.91</v>
+        <v>8.6</v>
       </c>
       <c r="I9">
-        <v>2.92</v>
+        <v>4.68</v>
       </c>
       <c r="J9">
-        <v>-2.55</v>
+        <v>-0.1</v>
       </c>
       <c r="K9">
-        <v>0.3</v>
+        <v>3.12</v>
       </c>
       <c r="L9">
-        <v>-28.91</v>
+        <v>-28.87</v>
       </c>
       <c r="M9">
-        <v>-7.57</v>
+        <v>-7.44</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P9">
-        <v>178.79</v>
+        <v>180.46</v>
       </c>
       <c r="Q9">
-        <v>183.33</v>
+        <v>183.27</v>
       </c>
       <c r="R9">
-        <v>188.81</v>
+        <v>188.8</v>
       </c>
       <c r="S9">
-        <v>195.99</v>
+        <v>195.71</v>
       </c>
       <c r="T9">
-        <v>-5.13</v>
+        <v>-4.4</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1796,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>52.15</v>
+        <v>53.89</v>
       </c>
       <c r="Z9">
-        <v>-2.78</v>
+        <v>-2.14</v>
       </c>
       <c r="AA9">
-        <v>-2.66</v>
+        <v>-2.55</v>
       </c>
       <c r="AB9">
-        <v>-0.12</v>
+        <v>0.41</v>
       </c>
       <c r="AC9">
+        <v>70.78</v>
+      </c>
+      <c r="AD9">
         <v>37.45</v>
       </c>
-      <c r="AD9">
-        <v>14.76</v>
-      </c>
       <c r="AE9">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="AF9">
-        <v>143.35</v>
+        <v>32.9</v>
       </c>
       <c r="AG9">
-        <v>190.95</v>
+        <v>190.75</v>
       </c>
       <c r="AH9">
-        <v>175.71</v>
+        <v>175.8</v>
       </c>
       <c r="AI9">
         <v>190.38</v>
@@ -1832,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>32.86</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1843,58 +1834,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>67.08</v>
+        <v>66.48</v>
       </c>
       <c r="D10">
-        <v>-0.16</v>
+        <v>-0.89</v>
       </c>
       <c r="E10">
-        <v>116.81</v>
+        <v>115.58</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-42.57</v>
+        <v>-42.48</v>
       </c>
       <c r="H10">
-        <v>13.16</v>
+        <v>12.15</v>
       </c>
       <c r="I10">
-        <v>-2.94</v>
+        <v>-3.74</v>
       </c>
       <c r="J10">
-        <v>-5.07</v>
+        <v>-10.49</v>
       </c>
       <c r="K10">
-        <v>-15.82</v>
+        <v>-14.82</v>
       </c>
       <c r="L10">
-        <v>-41.44</v>
+        <v>-43.09</v>
       </c>
       <c r="M10">
-        <v>-4.47</v>
+        <v>-4.84</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>68.11</v>
+        <v>67.59</v>
       </c>
       <c r="Q10">
-        <v>70.58</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="R10">
-        <v>73.41</v>
+        <v>73.2</v>
       </c>
       <c r="S10">
-        <v>79.59999999999999</v>
+        <v>79.48</v>
       </c>
       <c r="T10">
-        <v>-15.72</v>
+        <v>-16.36</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1909,43 +1900,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>29.21</v>
+        <v>27.47</v>
       </c>
       <c r="Z10">
-        <v>-1.66</v>
+        <v>-1.76</v>
       </c>
       <c r="AA10">
-        <v>-1.42</v>
+        <v>-1.49</v>
       </c>
       <c r="AB10">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="AC10">
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>5.9</v>
+        <v>2.12</v>
       </c>
       <c r="AE10">
         <v>2.21</v>
       </c>
       <c r="AF10">
-        <v>7.57</v>
+        <v>12.32</v>
       </c>
       <c r="AG10">
-        <v>74.41</v>
+        <v>74.34</v>
       </c>
       <c r="AH10">
-        <v>66.73999999999999</v>
+        <v>66.17</v>
       </c>
       <c r="AI10">
-        <v>74.31999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>38.55</v>
+        <v>42.89</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2126,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2144,973 +2135,970 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-7.47</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-9.210000000000001</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-6.49</v>
+        <v>-1.76</v>
       </c>
       <c r="D8" s="6">
-        <v>-7.47</v>
+        <v>-6.64</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.98</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.96</v>
+        <v>2.31</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.76</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.8</v>
+        <v>3.08</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.77</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-0.93</v>
+        <v>4.51</v>
       </c>
       <c r="D10" s="6">
-        <v>2.31</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.24</v>
+        <v>2.51</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>6.06</v>
+        <v>-2.83</v>
       </c>
       <c r="D11" s="6">
-        <v>4.51</v>
+        <v>-4.95</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.55</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.23</v>
+        <v>-10.73</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.83</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.4</v>
+        <v>-11.88</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-8.99</v>
+        <v>-4.17</v>
       </c>
       <c r="D13" s="6">
-        <v>-10.73</v>
+        <v>-4.97</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.74</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.15</v>
+        <v>-2.55</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.17</v>
+        <v>-0.1</v>
       </c>
       <c r="E14" s="8">
-        <v>0.98</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-7.9</v>
+        <v>-5.07</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.55</v>
-      </c>
-      <c r="E15" s="8">
-        <v>5.35</v>
+        <v>-10.49</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-5.42</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.15</v>
+        <v>-3.01</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.07</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.08</v>
+        <v>-3.08</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.21</v>
+        <v>0.66</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.01</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.2</v>
+        <v>-7.73</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-8.390000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.8</v>
+        <v>6.32</v>
       </c>
       <c r="D18" s="6">
-        <v>0.66</v>
+        <v>6.46</v>
       </c>
       <c r="E18" s="8">
-        <v>2.46</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.97</v>
+        <v>2.28</v>
       </c>
       <c r="D19" s="6">
-        <v>6.32</v>
-      </c>
-      <c r="E19" s="8">
-        <v>7.29</v>
+        <v>-3.95</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-6.23</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.78</v>
+        <v>3.19</v>
       </c>
       <c r="D20" s="6">
-        <v>2.28</v>
-      </c>
-      <c r="E20" s="8">
-        <v>3.06</v>
+        <v>0.33</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.86</v>
+        <v>-3.42</v>
       </c>
       <c r="D21" s="6">
-        <v>3.19</v>
+        <v>-2.42</v>
       </c>
       <c r="E21" s="8">
-        <v>4.05</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-4.51</v>
+        <v>-1.01</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.09</v>
+        <v>-1.1</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.64</v>
+        <v>2.92</v>
       </c>
       <c r="D23" s="6">
-        <v>-1.01</v>
+        <v>4.68</v>
       </c>
       <c r="E23" s="8">
-        <v>3.63</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.44</v>
+        <v>-2.94</v>
       </c>
       <c r="D24" s="6">
-        <v>2.92</v>
-      </c>
-      <c r="E24" s="8">
-        <v>7.36</v>
+        <v>-3.74</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-4.12</v>
+        <v>-35.12</v>
       </c>
       <c r="D25" s="6">
-        <v>-2.94</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.18</v>
+        <v>-35.87</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-34.1</v>
+        <v>13.78</v>
       </c>
       <c r="D26" s="6">
-        <v>-35.12</v>
+        <v>5.84</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.02</v>
+        <v>-7.94</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>14.18</v>
+        <v>27.87</v>
       </c>
       <c r="D27" s="6">
-        <v>13.78</v>
+        <v>25.99</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.4</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>24.02</v>
+        <v>27.6</v>
       </c>
       <c r="D28" s="6">
-        <v>27.87</v>
-      </c>
-      <c r="E28" s="8">
-        <v>3.85</v>
+        <v>23.53</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-4.07</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>28.79</v>
+        <v>39.92</v>
       </c>
       <c r="D29" s="6">
-        <v>27.6</v>
+        <v>29.13</v>
       </c>
       <c r="E29" s="7">
-        <v>-1.19</v>
+        <v>-10.79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>37.06</v>
+        <v>-36.25</v>
       </c>
       <c r="D30" s="6">
-        <v>39.92</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.86</v>
+        <v>-37.2</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-34.48</v>
+        <v>-5.86</v>
       </c>
       <c r="D31" s="6">
-        <v>-36.25</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.77</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-7.34</v>
+        <v>-28.91</v>
       </c>
       <c r="D32" s="6">
-        <v>-5.86</v>
+        <v>-28.87</v>
       </c>
       <c r="E32" s="8">
-        <v>1.48</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-32.55</v>
+        <v>-41.44</v>
       </c>
       <c r="D33" s="6">
-        <v>-28.91</v>
-      </c>
-      <c r="E33" s="8">
-        <v>3.64</v>
+        <v>-43.09</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-42.62</v>
+        <v>-14.98</v>
       </c>
       <c r="D34" s="6">
-        <v>-41.44</v>
+        <v>-12.7</v>
       </c>
       <c r="E34" s="8">
-        <v>1.18</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-15.22</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D35" s="6">
-        <v>-14.98</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.24</v>
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-10.68</v>
+        <v>-13.56</v>
       </c>
       <c r="D36" s="6">
-        <v>-8.279999999999999</v>
+        <v>-10.85</v>
       </c>
       <c r="E36" s="8">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-17.12</v>
+        <v>-2.75</v>
       </c>
       <c r="D37" s="6">
-        <v>-13.56</v>
+        <v>-2.32</v>
       </c>
       <c r="E37" s="8">
-        <v>3.56</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-4.85</v>
+        <v>-7.19</v>
       </c>
       <c r="D38" s="6">
-        <v>-2.75</v>
-      </c>
-      <c r="E38" s="8">
-        <v>2.1</v>
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-8.57</v>
+        <v>-17.06</v>
       </c>
       <c r="D39" s="6">
-        <v>-7.19</v>
+        <v>-15.25</v>
       </c>
       <c r="E39" s="8">
-        <v>1.38</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-16.97</v>
+        <v>-17.26</v>
       </c>
       <c r="D40" s="6">
-        <v>-17.06</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.09</v>
+        <v>-16.71</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.55</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-19.47</v>
+        <v>0.3</v>
       </c>
       <c r="D41" s="6">
-        <v>-17.26</v>
+        <v>3.12</v>
       </c>
       <c r="E41" s="8">
-        <v>2.21</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-7.66</v>
+        <v>-15.82</v>
       </c>
       <c r="D42" s="6">
-        <v>0.3</v>
+        <v>-14.82</v>
       </c>
       <c r="E42" s="8">
-        <v>7.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-16.81</v>
+        <v>-38.14</v>
       </c>
       <c r="D43" s="6">
-        <v>-15.82</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.99</v>
+        <v>-38.74</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-37.75</v>
+        <v>-11.28</v>
       </c>
       <c r="D44" s="6">
-        <v>-38.14</v>
+        <v>-14.6</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.39</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-10.84</v>
+        <v>-18.17</v>
       </c>
       <c r="D45" s="6">
-        <v>-11.28</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.44</v>
+        <v>-16.4</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.77</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-19.98</v>
+        <v>-5.3</v>
       </c>
       <c r="D46" s="6">
-        <v>-18.17</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.81</v>
+        <v>-7.07</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-5.8</v>
+        <v>-18.69</v>
       </c>
       <c r="D47" s="6">
-        <v>-5.3</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.5</v>
+        <v>-20.88</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-19.25</v>
+        <v>-37.05</v>
       </c>
       <c r="D48" s="6">
-        <v>-18.69</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.5600000000000001</v>
+        <v>-37.86</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-36.19</v>
+        <v>-27.2</v>
       </c>
       <c r="D49" s="6">
-        <v>-37.05</v>
+        <v>-28.01</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.86</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-27.84</v>
+        <v>-33.02</v>
       </c>
       <c r="D50" s="6">
-        <v>-27.2</v>
+        <v>-32.6</v>
       </c>
       <c r="E50" s="8">
-        <v>0.64</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-36.55</v>
+        <v>-42.57</v>
       </c>
       <c r="D51" s="6">
-        <v>-33.02</v>
+        <v>-42.48</v>
       </c>
       <c r="E51" s="8">
-        <v>3.53</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>-42.48</v>
+        <v>1177</v>
       </c>
       <c r="D52" s="6">
-        <v>-42.57</v>
+        <v>1165.5</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.09</v>
+        <v>-11.5</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>1184.4</v>
+        <v>2849.9</v>
       </c>
       <c r="D53" s="6">
-        <v>1177</v>
+        <v>2743</v>
       </c>
       <c r="E53" s="7">
-        <v>-7.4</v>
+        <v>-106.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>2864</v>
+        <v>1313</v>
       </c>
       <c r="D54" s="6">
-        <v>2849.9</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-14.1</v>
+        <v>1341.4</v>
+      </c>
+      <c r="E54" s="8">
+        <v>28.4</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1284</v>
+        <v>1783.4</v>
       </c>
       <c r="D55" s="6">
-        <v>1313</v>
-      </c>
-      <c r="E55" s="8">
-        <v>29</v>
+        <v>1750.1</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-33.3</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1774</v>
+        <v>202.4</v>
       </c>
       <c r="D56" s="6">
-        <v>1783.4</v>
-      </c>
-      <c r="E56" s="8">
-        <v>9.4</v>
+        <v>196.94</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-5.46</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>201</v>
+        <v>361.55</v>
       </c>
       <c r="D57" s="6">
-        <v>202.4</v>
-      </c>
-      <c r="E57" s="8">
-        <v>1.4</v>
+        <v>356.9</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-4.65</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>366.5</v>
+        <v>588.45</v>
       </c>
       <c r="D58" s="6">
-        <v>361.55</v>
+        <v>581.9</v>
       </c>
       <c r="E58" s="7">
-        <v>-4.95</v>
+        <v>-6.55</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>583.25</v>
+        <v>185.93</v>
       </c>
       <c r="D59" s="6">
-        <v>588.45</v>
+        <v>187.11</v>
       </c>
       <c r="E59" s="8">
-        <v>5.2</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>176.15</v>
+        <v>67.08</v>
       </c>
       <c r="D60" s="6">
-        <v>185.93</v>
-      </c>
-      <c r="E60" s="8">
-        <v>9.779999999999999</v>
+        <v>66.48</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>67.19</v>
+        <v>88</v>
       </c>
       <c r="D61" s="6">
-        <v>67.08</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.11</v>
+        <v>99</v>
+      </c>
+      <c r="E61" s="8">
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>13</v>
@@ -3127,331 +3115,348 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="D63" s="6">
-        <v>99</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
+        <v>45</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-10</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>28.34</v>
+        <v>45</v>
       </c>
       <c r="D64" s="6">
-        <v>26.96</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-1.38</v>
+        <v>55</v>
+      </c>
+      <c r="E64" s="8">
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>44.03</v>
+        <v>26.96</v>
       </c>
       <c r="D65" s="6">
-        <v>43.19</v>
+        <v>24.91</v>
       </c>
       <c r="E65" s="7">
-        <v>-0.84</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>47.96</v>
+        <v>43.19</v>
       </c>
       <c r="D66" s="6">
-        <v>53.02</v>
-      </c>
-      <c r="E66" s="8">
-        <v>5.06</v>
+        <v>37.35</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-5.84</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>52.42</v>
+        <v>53.02</v>
       </c>
       <c r="D67" s="6">
-        <v>53.49</v>
+        <v>57.39</v>
       </c>
       <c r="E67" s="8">
-        <v>1.07</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>46.65</v>
+        <v>53.49</v>
       </c>
       <c r="D68" s="6">
-        <v>48.15</v>
-      </c>
-      <c r="E68" s="8">
-        <v>1.5</v>
+        <v>49.25</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-4.24</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>33.79</v>
+        <v>48.15</v>
       </c>
       <c r="D69" s="6">
-        <v>31.52</v>
+        <v>43.05</v>
       </c>
       <c r="E69" s="7">
-        <v>-2.27</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>38.02</v>
+        <v>31.52</v>
       </c>
       <c r="D70" s="6">
-        <v>40.49</v>
-      </c>
-      <c r="E70" s="8">
-        <v>2.47</v>
+        <v>29.52</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-2</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>32.63</v>
+        <v>40.49</v>
       </c>
       <c r="D71" s="6">
-        <v>52.15</v>
-      </c>
-      <c r="E71" s="8">
-        <v>19.52</v>
+        <v>38.41</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-2.08</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>29.53</v>
+        <v>52.15</v>
       </c>
       <c r="D72" s="6">
-        <v>29.21</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-0.32</v>
+        <v>53.89</v>
+      </c>
+      <c r="E72" s="8">
+        <v>1.74</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>-41.32</v>
+        <v>29.21</v>
       </c>
       <c r="D73" s="6">
-        <v>-56.19</v>
+        <v>27.47</v>
       </c>
       <c r="E73" s="7">
-        <v>-14.87</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>19.11</v>
+        <v>-56.19</v>
       </c>
       <c r="D74" s="6">
-        <v>-17.51</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-36.62</v>
+        <v>-32.82</v>
+      </c>
+      <c r="E74" s="8">
+        <v>23.37</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-33.05</v>
+        <v>-17.51</v>
       </c>
       <c r="D75" s="6">
-        <v>78.94</v>
+        <v>14.06</v>
       </c>
       <c r="E75" s="8">
-        <v>111.99</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>31.35</v>
+        <v>78.94</v>
       </c>
       <c r="D76" s="6">
-        <v>-21.57</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-52.92</v>
+        <v>326.71</v>
+      </c>
+      <c r="E76" s="8">
+        <v>247.77</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>9.43</v>
+        <v>-21.57</v>
       </c>
       <c r="D77" s="6">
-        <v>29.48</v>
-      </c>
-      <c r="E77" s="8">
-        <v>20.05</v>
+        <v>-42.54</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-20.97</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>28.39</v>
+        <v>29.48</v>
       </c>
       <c r="D78" s="6">
-        <v>60.76</v>
-      </c>
-      <c r="E78" s="8">
-        <v>32.37</v>
+        <v>2.36</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-27.12</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-80.61</v>
+        <v>60.76</v>
       </c>
       <c r="D79" s="6">
-        <v>-86.02</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-5.41</v>
+        <v>126.14</v>
+      </c>
+      <c r="E79" s="8">
+        <v>65.38</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-59.24</v>
+        <v>-86.02</v>
       </c>
       <c r="D80" s="6">
-        <v>143.35</v>
+        <v>-78.17</v>
       </c>
       <c r="E80" s="8">
-        <v>202.59</v>
+        <v>7.85</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C81" s="6">
-        <v>-7.5</v>
+        <v>143.35</v>
       </c>
       <c r="D81" s="6">
+        <v>32.9</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-110.45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
         <v>7.57</v>
       </c>
-      <c r="E81" s="8">
-        <v>15.07</v>
+      <c r="D82" s="6">
+        <v>12.32</v>
+      </c>
+      <c r="E82" s="8">
+        <v>4.75</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3475,28 +3480,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3510,16 +3515,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>42</v>
+        <v>40.1</v>
       </c>
       <c r="E2" s="11">
         <v>40</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.1</v>
+        <v>-4.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-10.7</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3656,31 +3661,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5839</v>
+        <v>0.574</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2041</v>
+        <v>0.1956</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1406</v>
+        <v>0.1257</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0157</v>
+        <v>0.0216</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.009899999999999999</v>
+        <v>-0.0164</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0447</v>
+        <v>-0.0484</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.0757</v>
+        <v>-0.07440000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1099</v>
+        <v>-0.1166</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1599</v>
+        <v>-0.1638</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.5 → 49.2</t>
+    <t>57.4 → 41.8</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>53.5</t>
-  </si>
-  <si>
-    <t>49.2</t>
+    <t>57.4</t>
+  </si>
+  <si>
+    <t>41.8</t>
+  </si>
+  <si>
+    <t>53.9 → 47.2</t>
+  </si>
+  <si>
+    <t>53.9</t>
+  </si>
+  <si>
+    <t>47.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -930,58 +939,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1165.5</v>
+        <v>1130.1</v>
       </c>
       <c r="D2">
-        <v>-0.98</v>
+        <v>-3.04</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1165.5</v>
+        <v>1130.1</v>
       </c>
       <c r="G2">
-        <v>-38.74</v>
+        <v>-40.61</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-3.08</v>
+        <v>-6.15</v>
       </c>
       <c r="J2">
-        <v>-9.210000000000001</v>
+        <v>-10.92</v>
       </c>
       <c r="K2">
-        <v>-12.7</v>
+        <v>-17.04</v>
       </c>
       <c r="L2">
-        <v>-35.87</v>
+        <v>-38.53</v>
       </c>
       <c r="M2">
-        <v>-11.66</v>
+        <v>-12.01</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P2">
-        <v>1182.76</v>
+        <v>1167.96</v>
       </c>
       <c r="Q2">
-        <v>1225.68</v>
+        <v>1219.04</v>
       </c>
       <c r="R2">
-        <v>1284.95</v>
+        <v>1280.71</v>
       </c>
       <c r="S2">
-        <v>1430.6</v>
+        <v>1427.53</v>
       </c>
       <c r="T2">
-        <v>-18.53</v>
+        <v>-20.84</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +1005,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>24.91</v>
+        <v>19.92</v>
       </c>
       <c r="Z2">
-        <v>-29.9</v>
+        <v>-33.62</v>
       </c>
       <c r="AA2">
-        <v>-25.64</v>
+        <v>-27.23</v>
       </c>
       <c r="AB2">
-        <v>-4.26</v>
+        <v>-6.39</v>
       </c>
       <c r="AC2">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>4.57</v>
+        <v>1.09</v>
       </c>
       <c r="AE2">
-        <v>24.1</v>
+        <v>25.27</v>
       </c>
       <c r="AF2">
-        <v>-32.82</v>
+        <v>-1.09</v>
       </c>
       <c r="AG2">
-        <v>1286.41</v>
+        <v>1290.71</v>
       </c>
       <c r="AH2">
-        <v>1164.95</v>
+        <v>1147.38</v>
       </c>
       <c r="AI2">
-        <v>1243.71</v>
+        <v>1220.85</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>41.73</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1052,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2743</v>
+        <v>2596</v>
       </c>
       <c r="D3">
-        <v>-3.75</v>
+        <v>-5.36</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1064,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-14.6</v>
+        <v>-19.18</v>
       </c>
       <c r="H3">
-        <v>56.03</v>
+        <v>47.67</v>
       </c>
       <c r="I3">
-        <v>-7.73</v>
+        <v>-10.59</v>
       </c>
       <c r="J3">
-        <v>-6.64</v>
+        <v>-12</v>
       </c>
       <c r="K3">
-        <v>-9.970000000000001</v>
+        <v>-15.81</v>
       </c>
       <c r="L3">
-        <v>5.84</v>
+        <v>0.28</v>
       </c>
       <c r="M3">
-        <v>12.57</v>
+        <v>10.95</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="P3">
-        <v>2835.42</v>
+        <v>2773.94</v>
       </c>
       <c r="Q3">
-        <v>2937.48</v>
+        <v>2919.62</v>
       </c>
       <c r="R3">
-        <v>2979.88</v>
+        <v>2971.76</v>
       </c>
       <c r="S3">
-        <v>2580.16</v>
+        <v>2582</v>
       </c>
       <c r="T3">
-        <v>6.31</v>
+        <v>0.54</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,43 +1118,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>37.35</v>
+        <v>31.12</v>
       </c>
       <c r="Z3">
-        <v>-47.86</v>
+        <v>-66.87</v>
       </c>
       <c r="AA3">
-        <v>-31.56</v>
+        <v>-38.62</v>
       </c>
       <c r="AB3">
-        <v>-16.3</v>
+        <v>-28.25</v>
       </c>
       <c r="AC3">
-        <v>26.49</v>
+        <v>12.23</v>
       </c>
       <c r="AD3">
-        <v>30.05</v>
+        <v>23.3</v>
       </c>
       <c r="AE3">
-        <v>87.84999999999999</v>
+        <v>95.58</v>
       </c>
       <c r="AF3">
-        <v>14.06</v>
+        <v>182.99</v>
       </c>
       <c r="AG3">
-        <v>3120.57</v>
+        <v>3157.69</v>
       </c>
       <c r="AH3">
-        <v>2754.39</v>
+        <v>2681.56</v>
       </c>
       <c r="AI3">
-        <v>3053.71</v>
+        <v>2931.73</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>34.76</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1165,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1341.4</v>
+        <v>1235.7</v>
       </c>
       <c r="D4">
-        <v>2.16</v>
+        <v>-7.88</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1177,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-16.4</v>
+        <v>-22.99</v>
       </c>
       <c r="H4">
-        <v>73.58</v>
+        <v>59.9</v>
       </c>
       <c r="I4">
-        <v>6.46</v>
+        <v>-3.31</v>
       </c>
       <c r="J4">
-        <v>3.08</v>
+        <v>-4.06</v>
       </c>
       <c r="K4">
-        <v>-10.85</v>
+        <v>-16.88</v>
       </c>
       <c r="L4">
-        <v>25.99</v>
+        <v>15.45</v>
       </c>
       <c r="M4">
-        <v>2.16</v>
+        <v>0.99</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="P4">
-        <v>1298.5</v>
+        <v>1290.04</v>
       </c>
       <c r="Q4">
-        <v>1289.7</v>
+        <v>1286.88</v>
       </c>
       <c r="R4">
-        <v>1314.07</v>
+        <v>1311.23</v>
       </c>
       <c r="S4">
-        <v>1204.47</v>
+        <v>1205.59</v>
       </c>
       <c r="T4">
-        <v>11.37</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1231,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>57.39</v>
+        <v>41.8</v>
       </c>
       <c r="Z4">
-        <v>-4.38</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="AA4">
-        <v>-12.1</v>
+        <v>-11.42</v>
       </c>
       <c r="AB4">
-        <v>7.72</v>
+        <v>2.7</v>
       </c>
       <c r="AC4">
-        <v>85.2</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="AD4">
-        <v>69.52</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AE4">
-        <v>40.71</v>
+        <v>47.57</v>
       </c>
       <c r="AF4">
-        <v>326.71</v>
+        <v>322.26</v>
       </c>
       <c r="AG4">
-        <v>1341.5</v>
+        <v>1344</v>
       </c>
       <c r="AH4">
-        <v>1237.9</v>
+        <v>1229.77</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1258,7 +1267,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>22.02</v>
+        <v>21.22</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1750.1</v>
+        <v>1708</v>
       </c>
       <c r="D5">
-        <v>-1.87</v>
+        <v>-2.41</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1290,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.07</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="H5">
-        <v>34.82</v>
+        <v>31.57</v>
       </c>
       <c r="I5">
-        <v>-3.95</v>
+        <v>-5.02</v>
       </c>
       <c r="J5">
-        <v>2.51</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K5">
-        <v>-2.32</v>
+        <v>-5.12</v>
       </c>
       <c r="L5">
-        <v>23.53</v>
+        <v>20.87</v>
       </c>
       <c r="M5">
-        <v>19.56</v>
+        <v>18.85</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>1768.72</v>
+        <v>1750.66</v>
       </c>
       <c r="Q5">
-        <v>1769.48</v>
+        <v>1769.38</v>
       </c>
       <c r="R5">
-        <v>1721.65</v>
+        <v>1720.31</v>
       </c>
       <c r="S5">
-        <v>1630.43</v>
+        <v>1631.52</v>
       </c>
       <c r="T5">
-        <v>7.34</v>
+        <v>4.69</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1344,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.25</v>
+        <v>44.45</v>
       </c>
       <c r="Z5">
-        <v>13.33</v>
+        <v>7.4</v>
       </c>
       <c r="AA5">
-        <v>16.88</v>
+        <v>14.98</v>
       </c>
       <c r="AB5">
-        <v>-3.55</v>
+        <v>-7.58</v>
       </c>
       <c r="AC5">
-        <v>22.58</v>
+        <v>13.59</v>
       </c>
       <c r="AD5">
-        <v>22.08</v>
+        <v>18.8</v>
       </c>
       <c r="AE5">
-        <v>44.5</v>
+        <v>46.75</v>
       </c>
       <c r="AF5">
-        <v>-42.54</v>
+        <v>62.14</v>
       </c>
       <c r="AG5">
-        <v>1836.84</v>
+        <v>1837.12</v>
       </c>
       <c r="AH5">
-        <v>1702.11</v>
+        <v>1701.63</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1371,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>24.01</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1391,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>196.94</v>
+        <v>188</v>
       </c>
       <c r="D6">
-        <v>-2.7</v>
+        <v>-4.54</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1403,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-20.88</v>
+        <v>-24.47</v>
       </c>
       <c r="H6">
-        <v>48.12</v>
+        <v>41.4</v>
       </c>
       <c r="I6">
-        <v>0.33</v>
+        <v>-7.84</v>
       </c>
       <c r="J6">
-        <v>-4.95</v>
+        <v>-8.06</v>
       </c>
       <c r="K6">
-        <v>-9.029999999999999</v>
+        <v>-13.09</v>
       </c>
       <c r="L6">
-        <v>29.13</v>
+        <v>27.56</v>
       </c>
       <c r="M6">
-        <v>57.4</v>
+        <v>56.05</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P6">
-        <v>200.11</v>
+        <v>196.91</v>
       </c>
       <c r="Q6">
-        <v>203.86</v>
+        <v>202.84</v>
       </c>
       <c r="R6">
-        <v>206.01</v>
+        <v>205.6</v>
       </c>
       <c r="S6">
-        <v>188.94</v>
+        <v>189.18</v>
       </c>
       <c r="T6">
-        <v>4.23</v>
+        <v>-0.62</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,46 +1454,46 @@
         <v>47</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>43.05</v>
+        <v>36.28</v>
       </c>
       <c r="Z6">
-        <v>-2.43</v>
+        <v>-3.29</v>
       </c>
       <c r="AA6">
-        <v>-2.11</v>
+        <v>-2.34</v>
       </c>
       <c r="AB6">
-        <v>-0.33</v>
+        <v>-0.95</v>
       </c>
       <c r="AC6">
-        <v>72.14</v>
+        <v>45.92</v>
       </c>
       <c r="AD6">
-        <v>63.8</v>
+        <v>61</v>
       </c>
       <c r="AE6">
-        <v>6.29</v>
+        <v>6.76</v>
       </c>
       <c r="AF6">
-        <v>2.36</v>
+        <v>146.26</v>
       </c>
       <c r="AG6">
-        <v>214.73</v>
+        <v>215.59</v>
       </c>
       <c r="AH6">
-        <v>192.98</v>
+        <v>190.09</v>
       </c>
       <c r="AI6">
-        <v>213.83</v>
+        <v>210.56</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>28.85</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,58 +1504,58 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>356.9</v>
+        <v>341</v>
       </c>
       <c r="D7">
-        <v>-1.29</v>
+        <v>-4.46</v>
       </c>
       <c r="E7">
         <v>574.36</v>
       </c>
       <c r="F7">
-        <v>356.9</v>
+        <v>341</v>
       </c>
       <c r="G7">
-        <v>-37.86</v>
+        <v>-40.63</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>-2.42</v>
+        <v>-8.82</v>
       </c>
       <c r="J7">
-        <v>-11.88</v>
+        <v>-14.45</v>
       </c>
       <c r="K7">
-        <v>-15.25</v>
+        <v>-20.36</v>
       </c>
       <c r="L7">
-        <v>-37.2</v>
+        <v>-40.52</v>
       </c>
       <c r="M7">
-        <v>-1.64</v>
+        <v>-2.54</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>364.24</v>
+        <v>357.64</v>
       </c>
       <c r="Q7">
-        <v>380.83</v>
+        <v>377.97</v>
       </c>
       <c r="R7">
-        <v>403.84</v>
+        <v>402.14</v>
       </c>
       <c r="S7">
-        <v>451.8</v>
+        <v>450.84</v>
       </c>
       <c r="T7">
-        <v>-21</v>
+        <v>-24.36</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,43 +1570,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>29.52</v>
+        <v>23.93</v>
       </c>
       <c r="Z7">
-        <v>-11.91</v>
+        <v>-13.51</v>
       </c>
       <c r="AA7">
-        <v>-10.27</v>
+        <v>-10.92</v>
       </c>
       <c r="AB7">
-        <v>-1.64</v>
+        <v>-2.6</v>
       </c>
       <c r="AC7">
-        <v>34.83</v>
+        <v>18.44</v>
       </c>
       <c r="AD7">
-        <v>38.64</v>
+        <v>30.06</v>
       </c>
       <c r="AE7">
-        <v>9.039999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AF7">
-        <v>126.14</v>
+        <v>49.84</v>
       </c>
       <c r="AG7">
-        <v>406.29</v>
+        <v>407.69</v>
       </c>
       <c r="AH7">
-        <v>355.38</v>
+        <v>348.25</v>
       </c>
       <c r="AI7">
-        <v>384.71</v>
+        <v>377.78</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>54.9</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1617,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>581.9</v>
+        <v>562.2</v>
       </c>
       <c r="D8">
-        <v>-1.11</v>
+        <v>-3.39</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1629,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-28.01</v>
+        <v>-30.44</v>
       </c>
       <c r="H8">
-        <v>24.41</v>
+        <v>20.19</v>
       </c>
       <c r="I8">
-        <v>-1.1</v>
+        <v>-5.34</v>
       </c>
       <c r="J8">
-        <v>-4.97</v>
+        <v>-6.87</v>
       </c>
       <c r="K8">
-        <v>-16.71</v>
+        <v>-19.76</v>
       </c>
       <c r="L8">
-        <v>-9.199999999999999</v>
+        <v>-11.75</v>
       </c>
       <c r="M8">
-        <v>-16.38</v>
+        <v>-16.59</v>
       </c>
       <c r="N8">
         <v>45</v>
       </c>
       <c r="O8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P8">
-        <v>586.11</v>
+        <v>579.77</v>
       </c>
       <c r="Q8">
-        <v>603.05</v>
+        <v>600.6900000000001</v>
       </c>
       <c r="R8">
-        <v>628.4</v>
+        <v>626.73</v>
       </c>
       <c r="S8">
-        <v>614.53</v>
+        <v>614.4299999999999</v>
       </c>
       <c r="T8">
-        <v>-5.31</v>
+        <v>-8.5</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1683,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>38.41</v>
+        <v>32.94</v>
       </c>
       <c r="Z8">
-        <v>-12.59</v>
+        <v>-14.35</v>
       </c>
       <c r="AA8">
-        <v>-11.26</v>
+        <v>-11.88</v>
       </c>
       <c r="AB8">
-        <v>-1.33</v>
+        <v>-2.47</v>
       </c>
       <c r="AC8">
-        <v>35.19</v>
+        <v>22.26</v>
       </c>
       <c r="AD8">
-        <v>38.17</v>
+        <v>31.84</v>
       </c>
       <c r="AE8">
-        <v>17.62</v>
+        <v>18.15</v>
       </c>
       <c r="AF8">
-        <v>-78.17</v>
+        <v>-71.84999999999999</v>
       </c>
       <c r="AG8">
-        <v>646.1900000000001</v>
+        <v>647.38</v>
       </c>
       <c r="AH8">
-        <v>559.9</v>
+        <v>553.99</v>
       </c>
       <c r="AI8">
-        <v>580.38</v>
+        <v>626.95</v>
       </c>
       <c r="AJ8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK8">
-        <v>27.58</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1730,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>187.11</v>
+        <v>182.81</v>
       </c>
       <c r="D9">
-        <v>0.63</v>
+        <v>-2.3</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1742,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.6</v>
+        <v>-34.15</v>
       </c>
       <c r="H9">
-        <v>8.6</v>
+        <v>6.1</v>
       </c>
       <c r="I9">
-        <v>4.68</v>
+        <v>2.89</v>
       </c>
       <c r="J9">
-        <v>-0.1</v>
+        <v>-2.9</v>
       </c>
       <c r="K9">
-        <v>3.12</v>
+        <v>-1.55</v>
       </c>
       <c r="L9">
-        <v>-28.87</v>
+        <v>-31.12</v>
       </c>
       <c r="M9">
-        <v>-7.44</v>
+        <v>-7.9</v>
       </c>
       <c r="N9">
         <v>55</v>
       </c>
       <c r="O9">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="P9">
-        <v>180.46</v>
+        <v>181.49</v>
       </c>
       <c r="Q9">
-        <v>183.27</v>
+        <v>183.04</v>
       </c>
       <c r="R9">
-        <v>188.8</v>
+        <v>188.73</v>
       </c>
       <c r="S9">
-        <v>195.71</v>
+        <v>195.43</v>
       </c>
       <c r="T9">
-        <v>-4.4</v>
+        <v>-6.46</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1796,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>53.89</v>
+        <v>47.17</v>
       </c>
       <c r="Z9">
-        <v>-2.14</v>
+        <v>-1.96</v>
       </c>
       <c r="AA9">
-        <v>-2.55</v>
+        <v>-2.43</v>
       </c>
       <c r="AB9">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="AC9">
-        <v>70.78</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="AD9">
-        <v>37.45</v>
+        <v>66.19</v>
       </c>
       <c r="AE9">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="AF9">
-        <v>32.9</v>
+        <v>-38.25</v>
       </c>
       <c r="AG9">
-        <v>190.75</v>
+        <v>190.24</v>
       </c>
       <c r="AH9">
-        <v>175.8</v>
+        <v>175.83</v>
       </c>
       <c r="AI9">
         <v>190.38</v>
@@ -1823,7 +1832,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>29.97</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,58 +1843,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>66.48</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="D10">
-        <v>-0.89</v>
+        <v>-3.2</v>
       </c>
       <c r="E10">
-        <v>115.58</v>
+        <v>115.19</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-42.48</v>
+        <v>-44.14</v>
       </c>
       <c r="H10">
-        <v>12.15</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I10">
-        <v>-3.74</v>
+        <v>-6.93</v>
       </c>
       <c r="J10">
-        <v>-10.49</v>
+        <v>-11.69</v>
       </c>
       <c r="K10">
-        <v>-14.82</v>
+        <v>-22.19</v>
       </c>
       <c r="L10">
-        <v>-43.09</v>
+        <v>-44.32</v>
       </c>
       <c r="M10">
-        <v>-4.84</v>
+        <v>-5.35</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P10">
-        <v>67.59</v>
+        <v>66.64</v>
       </c>
       <c r="Q10">
-        <v>70.26000000000001</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="R10">
-        <v>73.2</v>
+        <v>72.95</v>
       </c>
       <c r="S10">
-        <v>79.48</v>
+        <v>79.37</v>
       </c>
       <c r="T10">
-        <v>-16.36</v>
+        <v>-18.92</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,43 +1909,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>27.47</v>
+        <v>22.36</v>
       </c>
       <c r="Z10">
-        <v>-1.76</v>
+        <v>-1.98</v>
       </c>
       <c r="AA10">
-        <v>-1.49</v>
+        <v>-1.59</v>
       </c>
       <c r="AB10">
-        <v>-0.27</v>
+        <v>-0.4</v>
       </c>
       <c r="AC10">
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>2.21</v>
+        <v>2.29</v>
       </c>
       <c r="AF10">
-        <v>12.32</v>
+        <v>53.75</v>
       </c>
       <c r="AG10">
-        <v>74.34</v>
+        <v>74.47</v>
       </c>
       <c r="AH10">
-        <v>66.17</v>
+        <v>65.17</v>
       </c>
       <c r="AI10">
-        <v>73.11</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>42.89</v>
+        <v>47.78</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2126,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1328 +2144,1280 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-7.47</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-1.74</v>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-1.76</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="D8" s="6">
-        <v>-6.64</v>
+        <v>-10.92</v>
       </c>
       <c r="E8" s="7">
-        <v>-4.88</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>2.31</v>
+        <v>-6.64</v>
       </c>
       <c r="D9" s="6">
-        <v>3.08</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.77</v>
+        <v>-12</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-5.36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>4.51</v>
+        <v>3.08</v>
       </c>
       <c r="D10" s="6">
-        <v>2.51</v>
+        <v>-4.06</v>
       </c>
       <c r="E10" s="7">
-        <v>-2</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-2.83</v>
+        <v>2.51</v>
       </c>
       <c r="D11" s="6">
-        <v>-4.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.12</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-10.73</v>
+        <v>-4.95</v>
       </c>
       <c r="D12" s="6">
-        <v>-11.88</v>
+        <v>-8.06</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.15</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-4.17</v>
+        <v>-11.88</v>
       </c>
       <c r="D13" s="6">
-        <v>-4.97</v>
+        <v>-14.45</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.8</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.55</v>
+        <v>-4.97</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.45</v>
+        <v>-6.87</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.07</v>
+        <v>-0.1</v>
       </c>
       <c r="D15" s="6">
-        <v>-10.49</v>
+        <v>-2.9</v>
       </c>
       <c r="E15" s="7">
-        <v>-5.42</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.01</v>
+        <v>-10.49</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.08</v>
+        <v>-11.69</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.07000000000000001</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>0.66</v>
+        <v>-3.08</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.73</v>
+        <v>-6.15</v>
       </c>
       <c r="E17" s="7">
-        <v>-8.390000000000001</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>6.32</v>
+        <v>-7.73</v>
       </c>
       <c r="D18" s="6">
-        <v>6.46</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.14</v>
+        <v>-10.59</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>2.28</v>
+        <v>6.46</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.95</v>
+        <v>-3.31</v>
       </c>
       <c r="E19" s="7">
-        <v>-6.23</v>
+        <v>-9.77</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>3.19</v>
+        <v>-3.95</v>
       </c>
       <c r="D20" s="6">
-        <v>0.33</v>
+        <v>-5.02</v>
       </c>
       <c r="E20" s="7">
-        <v>-2.86</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.42</v>
+        <v>0.33</v>
       </c>
       <c r="D21" s="6">
-        <v>-2.42</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1</v>
+        <v>-7.84</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-8.17</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.01</v>
+        <v>-2.42</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.1</v>
+        <v>-8.82</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.09</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>2.92</v>
+        <v>-1.1</v>
       </c>
       <c r="D23" s="6">
-        <v>4.68</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.76</v>
+        <v>-5.34</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-4.24</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.94</v>
+        <v>4.68</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.74</v>
+        <v>2.89</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.8</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>-35.12</v>
+        <v>-3.74</v>
       </c>
       <c r="D25" s="6">
-        <v>-35.87</v>
+        <v>-6.93</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.75</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>13.78</v>
+        <v>-35.87</v>
       </c>
       <c r="D26" s="6">
-        <v>5.84</v>
+        <v>-38.53</v>
       </c>
       <c r="E26" s="7">
-        <v>-7.94</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>27.87</v>
+        <v>5.84</v>
       </c>
       <c r="D27" s="6">
-        <v>25.99</v>
+        <v>0.28</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.88</v>
+        <v>-5.56</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>27.6</v>
+        <v>25.99</v>
       </c>
       <c r="D28" s="6">
-        <v>23.53</v>
+        <v>15.45</v>
       </c>
       <c r="E28" s="7">
-        <v>-4.07</v>
+        <v>-10.54</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>39.92</v>
+        <v>23.53</v>
       </c>
       <c r="D29" s="6">
-        <v>29.13</v>
+        <v>20.87</v>
       </c>
       <c r="E29" s="7">
-        <v>-10.79</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-36.25</v>
+        <v>29.13</v>
       </c>
       <c r="D30" s="6">
-        <v>-37.2</v>
+        <v>27.56</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.95</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-5.86</v>
+        <v>-37.2</v>
       </c>
       <c r="D31" s="6">
-        <v>-9.199999999999999</v>
+        <v>-40.52</v>
       </c>
       <c r="E31" s="7">
-        <v>-3.34</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-28.91</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="D32" s="6">
-        <v>-28.87</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.04</v>
+        <v>-11.75</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.55</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-41.44</v>
+        <v>-28.87</v>
       </c>
       <c r="D33" s="6">
-        <v>-43.09</v>
+        <v>-31.12</v>
       </c>
       <c r="E33" s="7">
-        <v>-1.65</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-14.98</v>
+        <v>-43.09</v>
       </c>
       <c r="D34" s="6">
-        <v>-12.7</v>
-      </c>
-      <c r="E34" s="8">
-        <v>2.28</v>
+        <v>-44.32</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-8.279999999999999</v>
+        <v>-12.7</v>
       </c>
       <c r="D35" s="6">
-        <v>-9.970000000000001</v>
+        <v>-17.04</v>
       </c>
       <c r="E35" s="7">
-        <v>-1.69</v>
+        <v>-4.34</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-13.56</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="D36" s="6">
-        <v>-10.85</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.71</v>
+        <v>-15.81</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-5.84</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-2.75</v>
+        <v>-10.85</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.32</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.43</v>
+        <v>-16.88</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-6.03</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-7.19</v>
+        <v>-2.32</v>
       </c>
       <c r="D38" s="6">
-        <v>-9.029999999999999</v>
+        <v>-5.12</v>
       </c>
       <c r="E38" s="7">
-        <v>-1.84</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-17.06</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="D39" s="6">
-        <v>-15.25</v>
-      </c>
-      <c r="E39" s="8">
-        <v>1.81</v>
+        <v>-13.09</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-4.06</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-17.26</v>
+        <v>-15.25</v>
       </c>
       <c r="D40" s="6">
-        <v>-16.71</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.55</v>
+        <v>-20.36</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-5.11</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>0.3</v>
+        <v>-16.71</v>
       </c>
       <c r="D41" s="6">
-        <v>3.12</v>
-      </c>
-      <c r="E41" s="8">
-        <v>2.82</v>
+        <v>-19.76</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-3.05</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-15.82</v>
+        <v>3.12</v>
       </c>
       <c r="D42" s="6">
-        <v>-14.82</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1</v>
+        <v>-1.55</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-4.67</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6">
-        <v>-38.14</v>
+        <v>-14.82</v>
       </c>
       <c r="D43" s="6">
-        <v>-38.74</v>
+        <v>-22.19</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.6</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-11.28</v>
+        <v>-38.74</v>
       </c>
       <c r="D44" s="6">
-        <v>-14.6</v>
+        <v>-40.61</v>
       </c>
       <c r="E44" s="7">
-        <v>-3.32</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-18.17</v>
+        <v>-14.6</v>
       </c>
       <c r="D45" s="6">
-        <v>-16.4</v>
-      </c>
-      <c r="E45" s="8">
-        <v>1.77</v>
+        <v>-19.18</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-4.58</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-5.3</v>
+        <v>-16.4</v>
       </c>
       <c r="D46" s="6">
-        <v>-7.07</v>
+        <v>-22.99</v>
       </c>
       <c r="E46" s="7">
-        <v>-1.77</v>
+        <v>-6.59</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-18.69</v>
+        <v>-7.07</v>
       </c>
       <c r="D47" s="6">
-        <v>-20.88</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="E47" s="7">
-        <v>-2.19</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-37.05</v>
+        <v>-20.88</v>
       </c>
       <c r="D48" s="6">
-        <v>-37.86</v>
+        <v>-24.47</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-27.2</v>
+        <v>-37.86</v>
       </c>
       <c r="D49" s="6">
-        <v>-28.01</v>
+        <v>-40.63</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-33.02</v>
+        <v>-28.01</v>
       </c>
       <c r="D50" s="6">
-        <v>-32.6</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.42</v>
+        <v>-30.44</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-42.57</v>
+        <v>-32.6</v>
       </c>
       <c r="D51" s="6">
-        <v>-42.48</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.09</v>
+        <v>-34.15</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6">
-        <v>1177</v>
+        <v>-42.48</v>
       </c>
       <c r="D52" s="6">
-        <v>1165.5</v>
+        <v>-44.14</v>
       </c>
       <c r="E52" s="7">
-        <v>-11.5</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2849.9</v>
+        <v>1165.5</v>
       </c>
       <c r="D53" s="6">
-        <v>2743</v>
+        <v>1130.1</v>
       </c>
       <c r="E53" s="7">
-        <v>-106.9</v>
+        <v>-35.4</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1313</v>
+        <v>2743</v>
       </c>
       <c r="D54" s="6">
-        <v>1341.4</v>
-      </c>
-      <c r="E54" s="8">
-        <v>28.4</v>
+        <v>2596</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-147</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1783.4</v>
+        <v>1341.4</v>
       </c>
       <c r="D55" s="6">
-        <v>1750.1</v>
+        <v>1235.7</v>
       </c>
       <c r="E55" s="7">
-        <v>-33.3</v>
+        <v>-105.7</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>202.4</v>
+        <v>1750.1</v>
       </c>
       <c r="D56" s="6">
-        <v>196.94</v>
+        <v>1708</v>
       </c>
       <c r="E56" s="7">
-        <v>-5.46</v>
+        <v>-42.1</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>361.55</v>
+        <v>196.94</v>
       </c>
       <c r="D57" s="6">
-        <v>356.9</v>
+        <v>188</v>
       </c>
       <c r="E57" s="7">
-        <v>-4.65</v>
+        <v>-8.94</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>588.45</v>
+        <v>356.9</v>
       </c>
       <c r="D58" s="6">
-        <v>581.9</v>
+        <v>341</v>
       </c>
       <c r="E58" s="7">
-        <v>-6.55</v>
+        <v>-15.9</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>185.93</v>
+        <v>581.9</v>
       </c>
       <c r="D59" s="6">
-        <v>187.11</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1.18</v>
+        <v>562.2</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-19.7</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>67.08</v>
+        <v>187.11</v>
       </c>
       <c r="D60" s="6">
-        <v>66.48</v>
+        <v>182.81</v>
       </c>
       <c r="E60" s="7">
-        <v>-0.6</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C61" s="6">
-        <v>88</v>
+        <v>66.48</v>
       </c>
       <c r="D61" s="6">
-        <v>99</v>
-      </c>
-      <c r="E61" s="8">
-        <v>11</v>
+        <v>64.34999999999999</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>99</v>
+        <v>24.91</v>
       </c>
       <c r="D62" s="6">
-        <v>88</v>
+        <v>19.92</v>
       </c>
       <c r="E62" s="7">
-        <v>-11</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>55</v>
+        <v>37.35</v>
       </c>
       <c r="D63" s="6">
-        <v>45</v>
+        <v>31.12</v>
       </c>
       <c r="E63" s="7">
-        <v>-10</v>
+        <v>-6.23</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>45</v>
+        <v>57.39</v>
       </c>
       <c r="D64" s="6">
-        <v>55</v>
-      </c>
-      <c r="E64" s="8">
-        <v>10</v>
+        <v>41.8</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-15.59</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>26.96</v>
+        <v>49.25</v>
       </c>
       <c r="D65" s="6">
-        <v>24.91</v>
+        <v>44.45</v>
       </c>
       <c r="E65" s="7">
-        <v>-2.05</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>43.19</v>
+        <v>43.05</v>
       </c>
       <c r="D66" s="6">
-        <v>37.35</v>
+        <v>36.28</v>
       </c>
       <c r="E66" s="7">
-        <v>-5.84</v>
+        <v>-6.77</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>53.02</v>
+        <v>29.52</v>
       </c>
       <c r="D67" s="6">
-        <v>57.39</v>
-      </c>
-      <c r="E67" s="8">
-        <v>4.37</v>
+        <v>23.93</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-5.59</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>53.49</v>
+        <v>38.41</v>
       </c>
       <c r="D68" s="6">
-        <v>49.25</v>
+        <v>32.94</v>
       </c>
       <c r="E68" s="7">
-        <v>-4.24</v>
+        <v>-5.47</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>48.15</v>
+        <v>53.89</v>
       </c>
       <c r="D69" s="6">
-        <v>43.05</v>
+        <v>47.17</v>
       </c>
       <c r="E69" s="7">
-        <v>-5.1</v>
+        <v>-6.72</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>31.52</v>
+        <v>27.47</v>
       </c>
       <c r="D70" s="6">
-        <v>29.52</v>
+        <v>22.36</v>
       </c>
       <c r="E70" s="7">
-        <v>-2</v>
+        <v>-5.11</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>40.49</v>
+        <v>-32.82</v>
       </c>
       <c r="D71" s="6">
-        <v>38.41</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-2.08</v>
+        <v>-1.09</v>
+      </c>
+      <c r="E71" s="8">
+        <v>31.73</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>52.15</v>
+        <v>14.06</v>
       </c>
       <c r="D72" s="6">
-        <v>53.89</v>
+        <v>182.99</v>
       </c>
       <c r="E72" s="8">
-        <v>1.74</v>
+        <v>168.93</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>29.21</v>
+        <v>326.71</v>
       </c>
       <c r="D73" s="6">
-        <v>27.47</v>
+        <v>322.26</v>
       </c>
       <c r="E73" s="7">
-        <v>-1.74</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>-56.19</v>
+        <v>-42.54</v>
       </c>
       <c r="D74" s="6">
-        <v>-32.82</v>
+        <v>62.14</v>
       </c>
       <c r="E74" s="8">
-        <v>23.37</v>
+        <v>104.68</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>-17.51</v>
+        <v>2.36</v>
       </c>
       <c r="D75" s="6">
-        <v>14.06</v>
+        <v>146.26</v>
       </c>
       <c r="E75" s="8">
-        <v>31.57</v>
+        <v>143.9</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>78.94</v>
+        <v>126.14</v>
       </c>
       <c r="D76" s="6">
-        <v>326.71</v>
-      </c>
-      <c r="E76" s="8">
-        <v>247.77</v>
+        <v>49.84</v>
+      </c>
+      <c r="E76" s="7">
+        <v>-76.3</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>-21.57</v>
+        <v>-78.17</v>
       </c>
       <c r="D77" s="6">
-        <v>-42.54</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-20.97</v>
+        <v>-71.84999999999999</v>
+      </c>
+      <c r="E77" s="8">
+        <v>6.32</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>29.48</v>
+        <v>32.9</v>
       </c>
       <c r="D78" s="6">
-        <v>2.36</v>
+        <v>-38.25</v>
       </c>
       <c r="E78" s="7">
-        <v>-27.12</v>
+        <v>-71.15000000000001</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>60.76</v>
+        <v>12.32</v>
       </c>
       <c r="D79" s="6">
-        <v>126.14</v>
+        <v>53.75</v>
       </c>
       <c r="E79" s="8">
-        <v>65.38</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-86.02</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-78.17</v>
-      </c>
-      <c r="E80" s="8">
-        <v>7.85</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>143.35</v>
-      </c>
-      <c r="D81" s="6">
-        <v>32.9</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-110.45</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>7.57</v>
-      </c>
-      <c r="D82" s="6">
-        <v>12.32</v>
-      </c>
-      <c r="E82" s="8">
-        <v>4.75</v>
+        <v>41.43</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3480,28 +3441,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3509,22 +3470,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="11">
-        <v>48.16</v>
+        <v>44.16</v>
       </c>
       <c r="C2" s="12">
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>40.1</v>
+        <v>33.3</v>
       </c>
       <c r="E2" s="11">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.7</v>
+        <v>-7.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-9.800000000000001</v>
+        <v>-14.6</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3661,31 +3622,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.574</v>
+        <v>0.5605</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1956</v>
+        <v>0.1885</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1257</v>
+        <v>0.1095</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0216</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0164</v>
+        <v>-0.0254</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.0484</v>
+        <v>-0.0535</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.07440000000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1166</v>
+        <v>-0.1201</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1638</v>
+        <v>-0.1659</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,58 +178,13 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>57.4 → 41.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>57.4</t>
-  </si>
-  <si>
-    <t>41.8</t>
-  </si>
-  <si>
-    <t>53.9 → 47.2</t>
-  </si>
-  <si>
-    <t>53.9</t>
-  </si>
-  <si>
-    <t>47.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -260,13 +215,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,22 +251,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -329,24 +268,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,34 +337,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2086,7 +2000,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2106,1318 +2020,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-9.210000000000001</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-10.92</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-6.64</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-12</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-5.36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>3.08</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-4.06</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-7.14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>2.51</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-8.06</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-3.11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-11.88</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-14.45</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-4.97</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-6.87</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.9</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-10.49</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-11.69</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.08</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.15</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-7.73</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-10.59</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>6.46</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-9.77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-3.95</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.33</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-7.84</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-8.17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.42</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-8.82</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-1.1</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-5.34</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-4.24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>4.68</v>
-      </c>
-      <c r="D24" s="6">
-        <v>2.89</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-6.93</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-3.19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-35.87</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-38.53</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>5.84</v>
-      </c>
-      <c r="D27" s="6">
-        <v>0.28</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-5.56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>25.99</v>
-      </c>
-      <c r="D28" s="6">
-        <v>15.45</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-10.54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>23.53</v>
-      </c>
-      <c r="D29" s="6">
-        <v>20.87</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>29.13</v>
-      </c>
-      <c r="D30" s="6">
-        <v>27.56</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-37.2</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-40.52</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-3.32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-11.75</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-28.87</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-31.12</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-43.09</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-44.32</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-12.7</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-17.04</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-4.34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-15.81</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-5.84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-10.85</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-16.88</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-6.03</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-2.32</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-5.12</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-13.09</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-4.06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-15.25</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-20.36</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-16.71</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-19.76</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-3.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>3.12</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-1.55</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-4.67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-14.82</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-22.19</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-7.37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-38.74</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-40.61</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-14.6</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-19.18</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-4.58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-16.4</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-22.99</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-6.59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-7.07</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-20.88</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-24.47</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-3.59</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-37.86</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-40.63</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-28.01</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-30.44</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-32.6</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-34.15</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-42.48</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-44.14</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1165.5</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1130.1</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-35.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>2743</v>
-      </c>
-      <c r="D54" s="6">
-        <v>2596</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-147</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1341.4</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1235.7</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-105.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1750.1</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1708</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-42.1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>196.94</v>
-      </c>
-      <c r="D57" s="6">
-        <v>188</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-8.94</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>356.9</v>
-      </c>
-      <c r="D58" s="6">
-        <v>341</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-15.9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>581.9</v>
-      </c>
-      <c r="D59" s="6">
-        <v>562.2</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-19.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>187.11</v>
-      </c>
-      <c r="D60" s="6">
-        <v>182.81</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>66.48</v>
-      </c>
-      <c r="D61" s="6">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>24.91</v>
-      </c>
-      <c r="D62" s="6">
-        <v>19.92</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-4.99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>37.35</v>
-      </c>
-      <c r="D63" s="6">
-        <v>31.12</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-6.23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>57.39</v>
-      </c>
-      <c r="D64" s="6">
-        <v>41.8</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-15.59</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>49.25</v>
-      </c>
-      <c r="D65" s="6">
-        <v>44.45</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>43.05</v>
-      </c>
-      <c r="D66" s="6">
-        <v>36.28</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-6.77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>29.52</v>
-      </c>
-      <c r="D67" s="6">
-        <v>23.93</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-5.59</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>38.41</v>
-      </c>
-      <c r="D68" s="6">
-        <v>32.94</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-5.47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>53.89</v>
-      </c>
-      <c r="D69" s="6">
-        <v>47.17</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-6.72</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>27.47</v>
-      </c>
-      <c r="D70" s="6">
-        <v>22.36</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-32.82</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="E71" s="8">
-        <v>31.73</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>14.06</v>
-      </c>
-      <c r="D72" s="6">
-        <v>182.99</v>
-      </c>
-      <c r="E72" s="8">
-        <v>168.93</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>326.71</v>
-      </c>
-      <c r="D73" s="6">
-        <v>322.26</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-42.54</v>
-      </c>
-      <c r="D74" s="6">
-        <v>62.14</v>
-      </c>
-      <c r="E74" s="8">
-        <v>104.68</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>2.36</v>
-      </c>
-      <c r="D75" s="6">
-        <v>146.26</v>
-      </c>
-      <c r="E75" s="8">
-        <v>143.9</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>126.14</v>
-      </c>
-      <c r="D76" s="6">
-        <v>49.84</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-76.3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-78.17</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-71.84999999999999</v>
-      </c>
-      <c r="E77" s="8">
-        <v>6.32</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>32.9</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-38.25</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-71.15000000000001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>12.32</v>
-      </c>
-      <c r="D79" s="6">
-        <v>53.75</v>
-      </c>
-      <c r="E79" s="8">
-        <v>41.43</v>
+      <c r="A6" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3437,60 +2060,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>77</v>
+      <c r="B1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>44.16</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>33.3</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>30</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>-7.8</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>-14.6</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="6">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>10</v>
       </c>
     </row>
@@ -3592,60 +2215,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>0.5605</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>0.1885</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="9">
         <v>0.1095</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>0.009899999999999999</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>-0.0254</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="9">
         <v>-0.0535</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>-0.079</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="9">
         <v>-0.1201</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="9">
         <v>-0.1659</v>
       </c>
     </row>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,13 +178,61 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>44.5 → 50.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>50.9</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>23.9 → 33.0</t>
+  </si>
+  <si>
+    <t>23.9</t>
+  </si>
+  <si>
+    <t>33.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -215,11 +263,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,8 +301,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -268,6 +332,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,27 +419,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -853,10 +942,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1130.1</v>
+        <v>1133</v>
       </c>
       <c r="D2">
-        <v>-3.04</v>
+        <v>0.26</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -865,25 +954,25 @@
         <v>1130.1</v>
       </c>
       <c r="G2">
-        <v>-40.61</v>
+        <v>-40.45</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="I2">
-        <v>-6.15</v>
+        <v>-4.21</v>
       </c>
       <c r="J2">
-        <v>-10.92</v>
+        <v>-10.28</v>
       </c>
       <c r="K2">
-        <v>-17.04</v>
+        <v>-18.17</v>
       </c>
       <c r="L2">
-        <v>-38.53</v>
+        <v>-37.84</v>
       </c>
       <c r="M2">
-        <v>-12.01</v>
+        <v>-12.04</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -892,19 +981,19 @@
         <v>15</v>
       </c>
       <c r="P2">
-        <v>1167.96</v>
+        <v>1158</v>
       </c>
       <c r="Q2">
-        <v>1219.04</v>
+        <v>1212.81</v>
       </c>
       <c r="R2">
-        <v>1280.71</v>
+        <v>1275.96</v>
       </c>
       <c r="S2">
-        <v>1427.53</v>
+        <v>1424.48</v>
       </c>
       <c r="T2">
-        <v>-20.84</v>
+        <v>-20.46</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -919,43 +1008,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>19.92</v>
+        <v>21.31</v>
       </c>
       <c r="Z2">
-        <v>-33.62</v>
+        <v>-35.93</v>
       </c>
       <c r="AA2">
-        <v>-27.23</v>
+        <v>-28.97</v>
       </c>
       <c r="AB2">
-        <v>-6.39</v>
+        <v>-6.96</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AD2">
-        <v>1.09</v>
+        <v>1.24</v>
       </c>
       <c r="AE2">
-        <v>25.27</v>
+        <v>24.73</v>
       </c>
       <c r="AF2">
-        <v>-1.09</v>
+        <v>-17.8</v>
       </c>
       <c r="AG2">
-        <v>1290.71</v>
+        <v>1291.66</v>
       </c>
       <c r="AH2">
-        <v>1147.38</v>
+        <v>1133.96</v>
       </c>
       <c r="AI2">
-        <v>1220.85</v>
+        <v>1207.7</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>46.64</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -966,10 +1055,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2596</v>
+        <v>2634.4</v>
       </c>
       <c r="D3">
-        <v>-5.36</v>
+        <v>1.48</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -978,25 +1067,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-19.18</v>
+        <v>-17.99</v>
       </c>
       <c r="H3">
-        <v>47.67</v>
+        <v>49.85</v>
       </c>
       <c r="I3">
-        <v>-10.59</v>
+        <v>-6.48</v>
       </c>
       <c r="J3">
-        <v>-12</v>
+        <v>-10.79</v>
       </c>
       <c r="K3">
-        <v>-15.81</v>
+        <v>-16.56</v>
       </c>
       <c r="L3">
-        <v>0.28</v>
+        <v>2.41</v>
       </c>
       <c r="M3">
-        <v>10.95</v>
+        <v>11.4</v>
       </c>
       <c r="N3">
         <v>66</v>
@@ -1005,19 +1094,19 @@
         <v>50</v>
       </c>
       <c r="P3">
-        <v>2773.94</v>
+        <v>2737.46</v>
       </c>
       <c r="Q3">
-        <v>2919.62</v>
+        <v>2896.11</v>
       </c>
       <c r="R3">
-        <v>2971.76</v>
+        <v>2963.95</v>
       </c>
       <c r="S3">
-        <v>2582</v>
+        <v>2583.98</v>
       </c>
       <c r="T3">
-        <v>0.54</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1032,43 +1121,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>31.12</v>
+        <v>34.2</v>
       </c>
       <c r="Z3">
-        <v>-66.87</v>
+        <v>-77.93000000000001</v>
       </c>
       <c r="AA3">
-        <v>-38.62</v>
+        <v>-46.48</v>
       </c>
       <c r="AB3">
-        <v>-28.25</v>
+        <v>-31.45</v>
       </c>
       <c r="AC3">
-        <v>12.23</v>
+        <v>5.42</v>
       </c>
       <c r="AD3">
-        <v>23.3</v>
+        <v>14.71</v>
       </c>
       <c r="AE3">
-        <v>95.58</v>
+        <v>93.8</v>
       </c>
       <c r="AF3">
-        <v>182.99</v>
+        <v>-6.17</v>
       </c>
       <c r="AG3">
-        <v>3157.69</v>
+        <v>3149.61</v>
       </c>
       <c r="AH3">
-        <v>2681.56</v>
+        <v>2642.61</v>
       </c>
       <c r="AI3">
-        <v>2931.73</v>
+        <v>2899.05</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>40.5</v>
+        <v>45.47</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1079,10 +1168,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1235.7</v>
+        <v>1255.8</v>
       </c>
       <c r="D4">
-        <v>-7.88</v>
+        <v>1.63</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1091,25 +1180,25 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-22.99</v>
+        <v>-21.73</v>
       </c>
       <c r="H4">
-        <v>59.9</v>
+        <v>62.5</v>
       </c>
       <c r="I4">
-        <v>-3.31</v>
+        <v>-1.59</v>
       </c>
       <c r="J4">
-        <v>-4.06</v>
+        <v>-2.8</v>
       </c>
       <c r="K4">
-        <v>-16.88</v>
+        <v>-18.27</v>
       </c>
       <c r="L4">
-        <v>15.45</v>
+        <v>18.54</v>
       </c>
       <c r="M4">
-        <v>0.99</v>
+        <v>1.56</v>
       </c>
       <c r="N4">
         <v>77</v>
@@ -1118,19 +1207,19 @@
         <v>65</v>
       </c>
       <c r="P4">
-        <v>1290.04</v>
+        <v>1285.98</v>
       </c>
       <c r="Q4">
-        <v>1286.88</v>
+        <v>1283.92</v>
       </c>
       <c r="R4">
-        <v>1311.23</v>
+        <v>1308.88</v>
       </c>
       <c r="S4">
-        <v>1205.59</v>
+        <v>1206.76</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>4.06</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1145,34 +1234,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>41.8</v>
+        <v>44.87</v>
       </c>
       <c r="Z4">
-        <v>-8.720000000000001</v>
+        <v>-10.43</v>
       </c>
       <c r="AA4">
-        <v>-11.42</v>
+        <v>-11.22</v>
       </c>
       <c r="AB4">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="AC4">
-        <v>69.98999999999999</v>
+        <v>48.87</v>
       </c>
       <c r="AD4">
-        <v>74.65000000000001</v>
+        <v>68.02</v>
       </c>
       <c r="AE4">
-        <v>47.57</v>
+        <v>46.98</v>
       </c>
       <c r="AF4">
-        <v>322.26</v>
+        <v>30.37</v>
       </c>
       <c r="AG4">
-        <v>1344</v>
+        <v>1341.04</v>
       </c>
       <c r="AH4">
-        <v>1229.77</v>
+        <v>1226.81</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1181,7 +1270,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>21.22</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1192,10 +1281,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1708</v>
+        <v>1761</v>
       </c>
       <c r="D5">
-        <v>-2.41</v>
+        <v>3.1</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1204,25 +1293,25 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9.300000000000001</v>
+        <v>-6.49</v>
       </c>
       <c r="H5">
-        <v>31.57</v>
+        <v>35.66</v>
       </c>
       <c r="I5">
-        <v>-5.02</v>
+        <v>1.34</v>
       </c>
       <c r="J5">
-        <v>0.8100000000000001</v>
+        <v>2.98</v>
       </c>
       <c r="K5">
-        <v>-5.12</v>
+        <v>-3.67</v>
       </c>
       <c r="L5">
-        <v>20.87</v>
+        <v>26.27</v>
       </c>
       <c r="M5">
-        <v>18.85</v>
+        <v>19.69</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1231,19 +1320,19 @@
         <v>75</v>
       </c>
       <c r="P5">
-        <v>1750.66</v>
+        <v>1755.3</v>
       </c>
       <c r="Q5">
-        <v>1769.38</v>
+        <v>1768.68</v>
       </c>
       <c r="R5">
-        <v>1720.31</v>
+        <v>1721.14</v>
       </c>
       <c r="S5">
-        <v>1631.52</v>
+        <v>1632.88</v>
       </c>
       <c r="T5">
-        <v>4.69</v>
+        <v>7.85</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1258,34 +1347,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>44.45</v>
+        <v>50.93</v>
       </c>
       <c r="Z5">
-        <v>7.4</v>
+        <v>6.89</v>
       </c>
       <c r="AA5">
-        <v>14.98</v>
+        <v>13.36</v>
       </c>
       <c r="AB5">
-        <v>-7.58</v>
+        <v>-6.47</v>
       </c>
       <c r="AC5">
-        <v>13.59</v>
+        <v>15.97</v>
       </c>
       <c r="AD5">
-        <v>18.8</v>
+        <v>17.38</v>
       </c>
       <c r="AE5">
-        <v>46.75</v>
+        <v>48.47</v>
       </c>
       <c r="AF5">
-        <v>62.14</v>
+        <v>356.67</v>
       </c>
       <c r="AG5">
-        <v>1837.12</v>
+        <v>1836.47</v>
       </c>
       <c r="AH5">
-        <v>1701.63</v>
+        <v>1700.88</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1294,7 +1383,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>27.8</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1305,10 +1394,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D6">
-        <v>-4.54</v>
+        <v>0.53</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1317,25 +1406,25 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-24.47</v>
+        <v>-24.07</v>
       </c>
       <c r="H6">
-        <v>41.4</v>
+        <v>42.15</v>
       </c>
       <c r="I6">
-        <v>-7.84</v>
+        <v>-3.67</v>
       </c>
       <c r="J6">
-        <v>-8.06</v>
+        <v>-9.31</v>
       </c>
       <c r="K6">
-        <v>-13.09</v>
+        <v>-13.48</v>
       </c>
       <c r="L6">
-        <v>27.56</v>
+        <v>24.35</v>
       </c>
       <c r="M6">
-        <v>56.05</v>
+        <v>56.22</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1344,19 +1433,19 @@
         <v>72</v>
       </c>
       <c r="P6">
-        <v>196.91</v>
+        <v>195.47</v>
       </c>
       <c r="Q6">
-        <v>202.84</v>
+        <v>201.54</v>
       </c>
       <c r="R6">
-        <v>205.6</v>
+        <v>205.19</v>
       </c>
       <c r="S6">
-        <v>189.18</v>
+        <v>189.41</v>
       </c>
       <c r="T6">
-        <v>-0.62</v>
+        <v>-0.22</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1371,43 +1460,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>36.28</v>
+        <v>37.47</v>
       </c>
       <c r="Z6">
-        <v>-3.29</v>
+        <v>-3.85</v>
       </c>
       <c r="AA6">
-        <v>-2.34</v>
+        <v>-2.64</v>
       </c>
       <c r="AB6">
-        <v>-0.95</v>
+        <v>-1.2</v>
       </c>
       <c r="AC6">
-        <v>45.92</v>
+        <v>18.14</v>
       </c>
       <c r="AD6">
-        <v>61</v>
+        <v>45.4</v>
       </c>
       <c r="AE6">
-        <v>6.76</v>
+        <v>6.59</v>
       </c>
       <c r="AF6">
-        <v>146.26</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="AG6">
-        <v>215.59</v>
+        <v>214.39</v>
       </c>
       <c r="AH6">
-        <v>190.09</v>
+        <v>188.69</v>
       </c>
       <c r="AI6">
-        <v>210.56</v>
+        <v>209.19</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>32.72</v>
+        <v>36.08</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1418,10 +1507,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>341</v>
+        <v>351.5</v>
       </c>
       <c r="D7">
-        <v>-4.46</v>
+        <v>3.08</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1430,25 +1519,25 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-40.63</v>
+        <v>-38.8</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="I7">
-        <v>-8.82</v>
+        <v>-2.97</v>
       </c>
       <c r="J7">
-        <v>-14.45</v>
+        <v>-11.75</v>
       </c>
       <c r="K7">
-        <v>-20.36</v>
+        <v>-19.46</v>
       </c>
       <c r="L7">
-        <v>-40.52</v>
+        <v>-38.44</v>
       </c>
       <c r="M7">
-        <v>-2.54</v>
+        <v>-1.95</v>
       </c>
       <c r="N7">
         <v>23</v>
@@ -1457,19 +1546,19 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>357.64</v>
+        <v>355.49</v>
       </c>
       <c r="Q7">
-        <v>377.97</v>
+        <v>375.69</v>
       </c>
       <c r="R7">
-        <v>402.14</v>
+        <v>400.47</v>
       </c>
       <c r="S7">
-        <v>450.84</v>
+        <v>449.91</v>
       </c>
       <c r="T7">
-        <v>-24.36</v>
+        <v>-21.87</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1484,43 +1573,43 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>23.93</v>
+        <v>32.96</v>
       </c>
       <c r="Z7">
-        <v>-13.51</v>
+        <v>-13.78</v>
       </c>
       <c r="AA7">
-        <v>-10.92</v>
+        <v>-11.49</v>
       </c>
       <c r="AB7">
-        <v>-2.6</v>
+        <v>-2.29</v>
       </c>
       <c r="AC7">
-        <v>18.44</v>
+        <v>22.71</v>
       </c>
       <c r="AD7">
-        <v>30.06</v>
+        <v>25.33</v>
       </c>
       <c r="AE7">
-        <v>9.550000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AF7">
-        <v>49.84</v>
+        <v>50.49</v>
       </c>
       <c r="AG7">
-        <v>407.69</v>
+        <v>406.23</v>
       </c>
       <c r="AH7">
-        <v>348.25</v>
+        <v>345.16</v>
       </c>
       <c r="AI7">
-        <v>377.78</v>
+        <v>375.26</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>58.55</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1531,10 +1620,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>562.2</v>
+        <v>563.45</v>
       </c>
       <c r="D8">
-        <v>-3.39</v>
+        <v>0.22</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1543,46 +1632,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-30.44</v>
+        <v>-30.29</v>
       </c>
       <c r="H8">
-        <v>20.19</v>
+        <v>20.46</v>
       </c>
       <c r="I8">
-        <v>-5.34</v>
+        <v>-3.36</v>
       </c>
       <c r="J8">
-        <v>-6.87</v>
+        <v>-7.54</v>
       </c>
       <c r="K8">
-        <v>-19.76</v>
+        <v>-22.16</v>
       </c>
       <c r="L8">
-        <v>-11.75</v>
+        <v>-11.02</v>
       </c>
       <c r="M8">
-        <v>-16.59</v>
+        <v>-16.82</v>
       </c>
       <c r="N8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O8">
         <v>36</v>
       </c>
       <c r="P8">
-        <v>579.77</v>
+        <v>575.85</v>
       </c>
       <c r="Q8">
-        <v>600.6900000000001</v>
+        <v>598.24</v>
       </c>
       <c r="R8">
-        <v>626.73</v>
+        <v>624.88</v>
       </c>
       <c r="S8">
-        <v>614.4299999999999</v>
+        <v>614.41</v>
       </c>
       <c r="T8">
-        <v>-8.5</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1597,43 +1686,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>32.94</v>
+        <v>33.59</v>
       </c>
       <c r="Z8">
-        <v>-14.35</v>
+        <v>-15.46</v>
       </c>
       <c r="AA8">
-        <v>-11.88</v>
+        <v>-12.6</v>
       </c>
       <c r="AB8">
-        <v>-2.47</v>
+        <v>-2.87</v>
       </c>
       <c r="AC8">
-        <v>22.26</v>
+        <v>11.01</v>
       </c>
       <c r="AD8">
-        <v>31.84</v>
+        <v>22.82</v>
       </c>
       <c r="AE8">
-        <v>18.15</v>
+        <v>17.66</v>
       </c>
       <c r="AF8">
-        <v>-71.84999999999999</v>
+        <v>-82.97</v>
       </c>
       <c r="AG8">
-        <v>647.38</v>
+        <v>647.42</v>
       </c>
       <c r="AH8">
-        <v>553.99</v>
+        <v>549.0599999999999</v>
       </c>
       <c r="AI8">
-        <v>626.95</v>
+        <v>620.12</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.83</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1644,10 +1733,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>182.81</v>
+        <v>182.18</v>
       </c>
       <c r="D9">
-        <v>-2.3</v>
+        <v>-0.34</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1656,46 +1745,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-34.15</v>
+        <v>-34.37</v>
       </c>
       <c r="H9">
-        <v>6.1</v>
+        <v>5.73</v>
       </c>
       <c r="I9">
-        <v>2.89</v>
+        <v>3.85</v>
       </c>
       <c r="J9">
-        <v>-2.9</v>
+        <v>-2.85</v>
       </c>
       <c r="K9">
-        <v>-1.55</v>
+        <v>-4.12</v>
       </c>
       <c r="L9">
-        <v>-31.12</v>
+        <v>-31.52</v>
       </c>
       <c r="M9">
-        <v>-7.9</v>
+        <v>-7.96</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
         <v>39</v>
       </c>
       <c r="P9">
-        <v>181.49</v>
+        <v>182.84</v>
       </c>
       <c r="Q9">
-        <v>183.04</v>
+        <v>182.77</v>
       </c>
       <c r="R9">
-        <v>188.73</v>
+        <v>188.58</v>
       </c>
       <c r="S9">
-        <v>195.43</v>
+        <v>195.12</v>
       </c>
       <c r="T9">
-        <v>-6.46</v>
+        <v>-6.63</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1710,34 +1799,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>47.17</v>
+        <v>46.26</v>
       </c>
       <c r="Z9">
-        <v>-1.96</v>
+        <v>-1.84</v>
       </c>
       <c r="AA9">
-        <v>-2.43</v>
+        <v>-2.32</v>
       </c>
       <c r="AB9">
         <v>0.48</v>
       </c>
       <c r="AC9">
-        <v>90.34999999999999</v>
+        <v>79.38</v>
       </c>
       <c r="AD9">
-        <v>66.19</v>
+        <v>80.17</v>
       </c>
       <c r="AE9">
-        <v>5.3</v>
+        <v>5.15</v>
       </c>
       <c r="AF9">
-        <v>-38.25</v>
+        <v>-30.08</v>
       </c>
       <c r="AG9">
-        <v>190.24</v>
+        <v>189.66</v>
       </c>
       <c r="AH9">
-        <v>175.83</v>
+        <v>175.88</v>
       </c>
       <c r="AI9">
         <v>190.38</v>
@@ -1746,7 +1835,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>25.99</v>
+        <v>23.12</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1757,37 +1846,37 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>64.34999999999999</v>
+        <v>63.79</v>
       </c>
       <c r="D10">
-        <v>-3.2</v>
+        <v>-0.87</v>
       </c>
       <c r="E10">
-        <v>115.19</v>
+        <v>113.79</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-44.14</v>
+        <v>-43.94</v>
       </c>
       <c r="H10">
-        <v>8.550000000000001</v>
+        <v>7.61</v>
       </c>
       <c r="I10">
-        <v>-6.93</v>
+        <v>-6.3</v>
       </c>
       <c r="J10">
-        <v>-11.69</v>
+        <v>-12.65</v>
       </c>
       <c r="K10">
-        <v>-22.19</v>
+        <v>-23.11</v>
       </c>
       <c r="L10">
-        <v>-44.32</v>
+        <v>-44.62</v>
       </c>
       <c r="M10">
-        <v>-5.35</v>
+        <v>-5.31</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1796,19 +1885,19 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>66.64</v>
+        <v>65.78</v>
       </c>
       <c r="Q10">
-        <v>69.81999999999999</v>
+        <v>69.33</v>
       </c>
       <c r="R10">
-        <v>72.95</v>
+        <v>72.7</v>
       </c>
       <c r="S10">
-        <v>79.37</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="T10">
-        <v>-18.92</v>
+        <v>-19.5</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1823,16 +1912,16 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>22.36</v>
+        <v>21.24</v>
       </c>
       <c r="Z10">
-        <v>-1.98</v>
+        <v>-2.18</v>
       </c>
       <c r="AA10">
-        <v>-1.59</v>
+        <v>-1.71</v>
       </c>
       <c r="AB10">
-        <v>-0.4</v>
+        <v>-0.48</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -1841,25 +1930,25 @@
         <v>0</v>
       </c>
       <c r="AE10">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AF10">
-        <v>53.75</v>
+        <v>5.47</v>
       </c>
       <c r="AG10">
-        <v>74.47</v>
+        <v>74.33</v>
       </c>
       <c r="AH10">
-        <v>65.17</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="AI10">
-        <v>72.18000000000001</v>
+        <v>70.83</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>47.78</v>
+        <v>52.25</v>
       </c>
     </row>
   </sheetData>
@@ -2000,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2020,27 +2109,1352 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>54</v>
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-10.92</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-10.28</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-10.79</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-4.06</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-2.8</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2.98</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-8.06</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-9.31</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-14.45</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-11.75</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-6.87</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-7.54</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.9</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.85</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-11.69</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-12.65</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-6.15</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-4.21</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-10.59</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-6.48</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4.11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.31</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.59</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-5.02</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.34</v>
+      </c>
+      <c r="E20" s="7">
+        <v>6.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-7.84</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="E21" s="7">
+        <v>4.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-8.82</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-2.97</v>
+      </c>
+      <c r="E22" s="7">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-5.34</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-3.36</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>2.89</v>
+      </c>
+      <c r="D24" s="6">
+        <v>3.85</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-6.93</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-6.3</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-38.53</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-37.84</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>0.28</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2.41</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>15.45</v>
+      </c>
+      <c r="D28" s="6">
+        <v>18.54</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>20.87</v>
+      </c>
+      <c r="D29" s="6">
+        <v>26.27</v>
+      </c>
+      <c r="E29" s="7">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>27.56</v>
+      </c>
+      <c r="D30" s="6">
+        <v>24.35</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-40.52</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-38.44</v>
+      </c>
+      <c r="E31" s="7">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-11.75</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-11.02</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-31.12</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-31.52</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-44.32</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-44.62</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-17.04</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-18.17</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-15.81</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-16.56</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-16.88</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-18.27</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-5.12</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-13.09</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-13.48</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-20.36</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-19.46</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-19.76</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-22.16</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-1.55</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-4.12</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-22.19</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-23.11</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-40.61</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-40.45</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-19.18</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-17.99</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-22.99</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-21.73</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-6.49</v>
+      </c>
+      <c r="E47" s="7">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-24.47</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-24.07</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-40.63</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-38.8</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-30.44</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-30.29</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-34.15</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-34.37</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-44.14</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-43.94</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1130.1</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1133</v>
+      </c>
+      <c r="E53" s="7">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>2596</v>
+      </c>
+      <c r="D54" s="6">
+        <v>2634.4</v>
+      </c>
+      <c r="E54" s="7">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>1235.7</v>
+      </c>
+      <c r="D55" s="6">
+        <v>1255.8</v>
+      </c>
+      <c r="E55" s="7">
+        <v>20.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1708</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1761</v>
+      </c>
+      <c r="E56" s="7">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>188</v>
+      </c>
+      <c r="D57" s="6">
+        <v>189</v>
+      </c>
+      <c r="E57" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>341</v>
+      </c>
+      <c r="D58" s="6">
+        <v>351.5</v>
+      </c>
+      <c r="E58" s="7">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>562.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>563.45</v>
+      </c>
+      <c r="E59" s="7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>182.81</v>
+      </c>
+      <c r="D60" s="6">
+        <v>182.18</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="D61" s="6">
+        <v>63.79</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>45</v>
+      </c>
+      <c r="D62" s="6">
+        <v>55</v>
+      </c>
+      <c r="E62" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>55</v>
+      </c>
+      <c r="D63" s="6">
+        <v>45</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>19.92</v>
+      </c>
+      <c r="D64" s="6">
+        <v>21.31</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>31.12</v>
+      </c>
+      <c r="D65" s="6">
+        <v>34.2</v>
+      </c>
+      <c r="E65" s="7">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>41.8</v>
+      </c>
+      <c r="D66" s="6">
+        <v>44.87</v>
+      </c>
+      <c r="E66" s="7">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>44.45</v>
+      </c>
+      <c r="D67" s="6">
+        <v>50.93</v>
+      </c>
+      <c r="E67" s="7">
+        <v>6.48</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>36.28</v>
+      </c>
+      <c r="D68" s="6">
+        <v>37.47</v>
+      </c>
+      <c r="E68" s="7">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>23.93</v>
+      </c>
+      <c r="D69" s="6">
+        <v>32.96</v>
+      </c>
+      <c r="E69" s="7">
+        <v>9.029999999999999</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>32.94</v>
+      </c>
+      <c r="D70" s="6">
+        <v>33.59</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>47.17</v>
+      </c>
+      <c r="D71" s="6">
+        <v>46.26</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>22.36</v>
+      </c>
+      <c r="D72" s="6">
+        <v>21.24</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-1.09</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-17.8</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-16.71</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>182.99</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-6.17</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-189.16</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>322.26</v>
+      </c>
+      <c r="D75" s="6">
+        <v>30.37</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-291.89</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>62.14</v>
+      </c>
+      <c r="D76" s="6">
+        <v>356.67</v>
+      </c>
+      <c r="E76" s="7">
+        <v>294.53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>146.26</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-154.8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>49.84</v>
+      </c>
+      <c r="D78" s="6">
+        <v>50.49</v>
+      </c>
+      <c r="E78" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-71.84999999999999</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-82.97</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-11.12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-38.25</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-30.08</v>
+      </c>
+      <c r="E80" s="7">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>53.75</v>
+      </c>
+      <c r="D81" s="6">
+        <v>5.47</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-48.28</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2060,60 +3474,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>62</v>
+      <c r="B1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>44.16</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="6">
-        <v>33.3</v>
-      </c>
-      <c r="E2" s="6">
+      <c r="D2" s="11">
+        <v>35.9</v>
+      </c>
+      <c r="E2" s="11">
         <v>30</v>
       </c>
-      <c r="F2" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-14.6</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="F2" s="11">
+        <v>-7.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-15.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -2215,61 +3629,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9">
-        <v>0.5605</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.1885</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.1095</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.009899999999999999</v>
-      </c>
-      <c r="E2" s="9">
-        <v>-0.0254</v>
-      </c>
-      <c r="F2" s="9">
-        <v>-0.0535</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-0.079</v>
-      </c>
-      <c r="H2" s="9">
-        <v>-0.1201</v>
-      </c>
-      <c r="I2" s="9">
-        <v>-0.1659</v>
+      <c r="A2" s="14">
+        <v>0.5622</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1969</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.114</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0156</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.0195</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.05309999999999999</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.0796</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.1204</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1682</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -1091,7 +1091,7 @@
         <v>66</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P3">
         <v>2737.46</v>
@@ -1204,7 +1204,7 @@
         <v>77</v>
       </c>
       <c r="O4">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P4">
         <v>1285.98</v>
@@ -1317,7 +1317,7 @@
         <v>99</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P5">
         <v>1755.3</v>
@@ -1430,7 +1430,7 @@
         <v>88</v>
       </c>
       <c r="O6">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P6">
         <v>195.47</v>
@@ -1543,7 +1543,7 @@
         <v>23</v>
       </c>
       <c r="O7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P7">
         <v>355.49</v>
@@ -1656,7 +1656,7 @@
         <v>55</v>
       </c>
       <c r="O8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P8">
         <v>575.85</v>
@@ -1769,7 +1769,7 @@
         <v>45</v>
       </c>
       <c r="O9">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="P9">
         <v>182.84</v>
@@ -1882,7 +1882,7 @@
         <v>12</v>
       </c>
       <c r="O10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>65.78</v>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,31 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>44.5 → 50.9</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>21.2 → 30.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>44.5</t>
-  </si>
-  <si>
-    <t>50.9</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>23.9 → 33.0</t>
-  </si>
-  <si>
-    <t>23.9</t>
-  </si>
-  <si>
-    <t>33.0</t>
+    <t>21.2</t>
+  </si>
+  <si>
+    <t>30.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -429,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -942,58 +930,58 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1133</v>
+        <v>1124.9</v>
       </c>
       <c r="D2">
-        <v>0.26</v>
+        <v>-0.71</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
       </c>
       <c r="F2">
-        <v>1130.1</v>
+        <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-40.45</v>
+        <v>-40.88</v>
       </c>
       <c r="H2">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>-4.21</v>
+        <v>-5.02</v>
       </c>
       <c r="J2">
-        <v>-10.28</v>
+        <v>-10.56</v>
       </c>
       <c r="K2">
-        <v>-18.17</v>
+        <v>-18.41</v>
       </c>
       <c r="L2">
-        <v>-37.84</v>
+        <v>-39.09</v>
       </c>
       <c r="M2">
-        <v>-12.04</v>
+        <v>-12.13</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P2">
-        <v>1158</v>
+        <v>1146.1</v>
       </c>
       <c r="Q2">
-        <v>1212.81</v>
+        <v>1206.34</v>
       </c>
       <c r="R2">
-        <v>1275.96</v>
+        <v>1271.32</v>
       </c>
       <c r="S2">
-        <v>1424.48</v>
+        <v>1421.25</v>
       </c>
       <c r="T2">
-        <v>-20.46</v>
+        <v>-20.85</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1008,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>21.31</v>
+        <v>20.25</v>
       </c>
       <c r="Z2">
-        <v>-35.93</v>
+        <v>-37.97</v>
       </c>
       <c r="AA2">
-        <v>-28.97</v>
+        <v>-30.77</v>
       </c>
       <c r="AB2">
-        <v>-6.96</v>
+        <v>-7.2</v>
       </c>
       <c r="AC2">
-        <v>2.07</v>
+        <v>2.57</v>
       </c>
       <c r="AD2">
-        <v>1.24</v>
+        <v>1.55</v>
       </c>
       <c r="AE2">
-        <v>24.73</v>
+        <v>24.79</v>
       </c>
       <c r="AF2">
-        <v>-17.8</v>
+        <v>-30.9</v>
       </c>
       <c r="AG2">
-        <v>1291.66</v>
+        <v>1291.81</v>
       </c>
       <c r="AH2">
-        <v>1133.96</v>
+        <v>1120.87</v>
       </c>
       <c r="AI2">
         <v>1207.7</v>
@@ -1044,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>50.92</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1055,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2634.4</v>
+        <v>2630</v>
       </c>
       <c r="D3">
-        <v>1.48</v>
+        <v>-0.17</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1067,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-17.99</v>
+        <v>-18.12</v>
       </c>
       <c r="H3">
-        <v>49.85</v>
+        <v>49.6</v>
       </c>
       <c r="I3">
-        <v>-6.48</v>
+        <v>-8.17</v>
       </c>
       <c r="J3">
-        <v>-10.79</v>
+        <v>-15.29</v>
       </c>
       <c r="K3">
-        <v>-16.56</v>
+        <v>-17.23</v>
       </c>
       <c r="L3">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="M3">
-        <v>11.4</v>
+        <v>11.14</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P3">
-        <v>2737.46</v>
+        <v>2690.66</v>
       </c>
       <c r="Q3">
-        <v>2896.11</v>
+        <v>2873.75</v>
       </c>
       <c r="R3">
-        <v>2963.95</v>
+        <v>2955.57</v>
       </c>
       <c r="S3">
-        <v>2583.98</v>
+        <v>2585.82</v>
       </c>
       <c r="T3">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1121,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>34.2</v>
+        <v>34.02</v>
       </c>
       <c r="Z3">
-        <v>-77.93000000000001</v>
+        <v>-86.06</v>
       </c>
       <c r="AA3">
-        <v>-46.48</v>
+        <v>-54.4</v>
       </c>
       <c r="AB3">
-        <v>-31.45</v>
+        <v>-31.66</v>
       </c>
       <c r="AC3">
-        <v>5.42</v>
+        <v>10.5</v>
       </c>
       <c r="AD3">
-        <v>14.71</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AE3">
-        <v>93.8</v>
+        <v>89.89</v>
       </c>
       <c r="AF3">
-        <v>-6.17</v>
+        <v>-36.36</v>
       </c>
       <c r="AG3">
-        <v>3149.61</v>
+        <v>3138.63</v>
       </c>
       <c r="AH3">
-        <v>2642.61</v>
+        <v>2608.87</v>
       </c>
       <c r="AI3">
         <v>2899.05</v>
@@ -1157,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>45.47</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1168,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1255.8</v>
+        <v>1274</v>
       </c>
       <c r="D4">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1180,25 +1168,25 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-21.73</v>
+        <v>-20.6</v>
       </c>
       <c r="H4">
-        <v>62.5</v>
+        <v>64.86</v>
       </c>
       <c r="I4">
-        <v>-1.59</v>
+        <v>-0.78</v>
       </c>
       <c r="J4">
-        <v>-2.8</v>
+        <v>-3.12</v>
       </c>
       <c r="K4">
-        <v>-18.27</v>
+        <v>-17.62</v>
       </c>
       <c r="L4">
-        <v>18.54</v>
+        <v>20.11</v>
       </c>
       <c r="M4">
-        <v>1.56</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
         <v>77</v>
@@ -1207,19 +1195,19 @@
         <v>66</v>
       </c>
       <c r="P4">
-        <v>1285.98</v>
+        <v>1283.98</v>
       </c>
       <c r="Q4">
-        <v>1283.92</v>
+        <v>1282.67</v>
       </c>
       <c r="R4">
-        <v>1308.88</v>
+        <v>1307.19</v>
       </c>
       <c r="S4">
-        <v>1206.76</v>
+        <v>1208.03</v>
       </c>
       <c r="T4">
-        <v>4.06</v>
+        <v>5.46</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1234,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>44.87</v>
+        <v>47.56</v>
       </c>
       <c r="Z4">
-        <v>-10.43</v>
+        <v>-10.19</v>
       </c>
       <c r="AA4">
-        <v>-11.22</v>
+        <v>-11.02</v>
       </c>
       <c r="AB4">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AC4">
-        <v>48.87</v>
+        <v>31</v>
       </c>
       <c r="AD4">
-        <v>68.02</v>
+        <v>49.95</v>
       </c>
       <c r="AE4">
-        <v>46.98</v>
+        <v>45.31</v>
       </c>
       <c r="AF4">
-        <v>30.37</v>
+        <v>-30.36</v>
       </c>
       <c r="AG4">
-        <v>1341.04</v>
+        <v>1339.48</v>
       </c>
       <c r="AH4">
-        <v>1226.81</v>
+        <v>1225.86</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1270,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>20.52</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1281,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1761</v>
+        <v>1754</v>
       </c>
       <c r="D5">
-        <v>3.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1293,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-6.49</v>
+        <v>-6.86</v>
       </c>
       <c r="H5">
-        <v>35.66</v>
+        <v>35.12</v>
       </c>
       <c r="I5">
-        <v>1.34</v>
+        <v>-1.13</v>
       </c>
       <c r="J5">
-        <v>2.98</v>
+        <v>-1.18</v>
       </c>
       <c r="K5">
-        <v>-3.67</v>
+        <v>-3.11</v>
       </c>
       <c r="L5">
-        <v>26.27</v>
+        <v>25.86</v>
       </c>
       <c r="M5">
-        <v>19.69</v>
+        <v>19.58</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>1755.3</v>
+        <v>1751.3</v>
       </c>
       <c r="Q5">
-        <v>1768.68</v>
+        <v>1767.98</v>
       </c>
       <c r="R5">
-        <v>1721.14</v>
+        <v>1722.94</v>
       </c>
       <c r="S5">
-        <v>1632.88</v>
+        <v>1634.13</v>
       </c>
       <c r="T5">
-        <v>7.85</v>
+        <v>7.34</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1347,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>50.93</v>
+        <v>50.1</v>
       </c>
       <c r="Z5">
-        <v>6.89</v>
+        <v>5.86</v>
       </c>
       <c r="AA5">
-        <v>13.36</v>
+        <v>11.86</v>
       </c>
       <c r="AB5">
-        <v>-6.47</v>
+        <v>-6</v>
       </c>
       <c r="AC5">
-        <v>15.97</v>
+        <v>25.5</v>
       </c>
       <c r="AD5">
-        <v>17.38</v>
+        <v>18.35</v>
       </c>
       <c r="AE5">
-        <v>48.47</v>
+        <v>47.27</v>
       </c>
       <c r="AF5">
-        <v>356.67</v>
+        <v>322.05</v>
       </c>
       <c r="AG5">
-        <v>1836.47</v>
+        <v>1836.08</v>
       </c>
       <c r="AH5">
-        <v>1700.88</v>
+        <v>1699.87</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1383,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.86</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1394,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>189</v>
+        <v>185.9</v>
       </c>
       <c r="D6">
-        <v>0.53</v>
+        <v>-1.64</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1406,46 +1394,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-24.07</v>
+        <v>-25.31</v>
       </c>
       <c r="H6">
-        <v>42.15</v>
+        <v>39.82</v>
       </c>
       <c r="I6">
-        <v>-3.67</v>
+        <v>-7.51</v>
       </c>
       <c r="J6">
-        <v>-9.31</v>
+        <v>-13.49</v>
       </c>
       <c r="K6">
-        <v>-13.48</v>
+        <v>-13.72</v>
       </c>
       <c r="L6">
-        <v>24.35</v>
+        <v>22.72</v>
       </c>
       <c r="M6">
-        <v>56.22</v>
+        <v>55.69</v>
       </c>
       <c r="N6">
         <v>88</v>
       </c>
       <c r="O6">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="P6">
-        <v>195.47</v>
+        <v>192.45</v>
       </c>
       <c r="Q6">
-        <v>201.54</v>
+        <v>200.16</v>
       </c>
       <c r="R6">
-        <v>205.19</v>
+        <v>204.73</v>
       </c>
       <c r="S6">
-        <v>189.41</v>
+        <v>189.63</v>
       </c>
       <c r="T6">
-        <v>-0.22</v>
+        <v>-1.96</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1460,43 +1448,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>37.47</v>
+        <v>35.28</v>
       </c>
       <c r="Z6">
-        <v>-3.85</v>
+        <v>-4.48</v>
       </c>
       <c r="AA6">
-        <v>-2.64</v>
+        <v>-3.01</v>
       </c>
       <c r="AB6">
-        <v>-1.2</v>
+        <v>-1.47</v>
       </c>
       <c r="AC6">
-        <v>18.14</v>
+        <v>3.12</v>
       </c>
       <c r="AD6">
-        <v>45.4</v>
+        <v>22.4</v>
       </c>
       <c r="AE6">
-        <v>6.59</v>
+        <v>6.52</v>
       </c>
       <c r="AF6">
-        <v>-8.539999999999999</v>
+        <v>-35.46</v>
       </c>
       <c r="AG6">
-        <v>214.39</v>
+        <v>213.52</v>
       </c>
       <c r="AH6">
-        <v>188.69</v>
+        <v>186.8</v>
       </c>
       <c r="AI6">
-        <v>209.19</v>
+        <v>207.72</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>36.08</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1507,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>351.5</v>
+        <v>348</v>
       </c>
       <c r="D7">
-        <v>3.08</v>
+        <v>-1</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1519,46 +1507,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-38.8</v>
+        <v>-39.41</v>
       </c>
       <c r="H7">
-        <v>3.08</v>
+        <v>2.05</v>
       </c>
       <c r="I7">
-        <v>-2.97</v>
+        <v>-5.05</v>
       </c>
       <c r="J7">
-        <v>-11.75</v>
+        <v>-12.34</v>
       </c>
       <c r="K7">
-        <v>-19.46</v>
+        <v>-19.47</v>
       </c>
       <c r="L7">
-        <v>-38.44</v>
+        <v>-38.64</v>
       </c>
       <c r="M7">
-        <v>-1.95</v>
+        <v>-2.17</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P7">
-        <v>355.49</v>
+        <v>351.79</v>
       </c>
       <c r="Q7">
-        <v>375.69</v>
+        <v>373.31</v>
       </c>
       <c r="R7">
-        <v>400.47</v>
+        <v>398.74</v>
       </c>
       <c r="S7">
-        <v>449.91</v>
+        <v>448.97</v>
       </c>
       <c r="T7">
-        <v>-21.87</v>
+        <v>-22.49</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1573,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>32.96</v>
+        <v>31.61</v>
       </c>
       <c r="Z7">
-        <v>-13.78</v>
+        <v>-14.11</v>
       </c>
       <c r="AA7">
-        <v>-11.49</v>
+        <v>-12.01</v>
       </c>
       <c r="AB7">
-        <v>-2.29</v>
+        <v>-2.09</v>
       </c>
       <c r="AC7">
-        <v>22.71</v>
+        <v>30.05</v>
       </c>
       <c r="AD7">
-        <v>25.33</v>
+        <v>23.73</v>
       </c>
       <c r="AE7">
-        <v>9.619999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="AF7">
-        <v>50.49</v>
+        <v>21.81</v>
       </c>
       <c r="AG7">
-        <v>406.23</v>
+        <v>404.73</v>
       </c>
       <c r="AH7">
-        <v>345.16</v>
+        <v>341.9</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1609,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>61.71</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1620,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>563.45</v>
+        <v>563.2</v>
       </c>
       <c r="D8">
-        <v>0.22</v>
+        <v>-0.04</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1632,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-30.29</v>
+        <v>-30.32</v>
       </c>
       <c r="H8">
-        <v>20.46</v>
+        <v>20.41</v>
       </c>
       <c r="I8">
-        <v>-3.36</v>
+        <v>-3.44</v>
       </c>
       <c r="J8">
-        <v>-7.54</v>
+        <v>-8.02</v>
       </c>
       <c r="K8">
-        <v>-22.16</v>
+        <v>-21.88</v>
       </c>
       <c r="L8">
-        <v>-11.02</v>
+        <v>-11.43</v>
       </c>
       <c r="M8">
-        <v>-16.82</v>
+        <v>-16.7</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P8">
-        <v>575.85</v>
+        <v>571.84</v>
       </c>
       <c r="Q8">
-        <v>598.24</v>
+        <v>596.27</v>
       </c>
       <c r="R8">
-        <v>624.88</v>
+        <v>623.14</v>
       </c>
       <c r="S8">
-        <v>614.41</v>
+        <v>614.38</v>
       </c>
       <c r="T8">
-        <v>-8.289999999999999</v>
+        <v>-8.33</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1686,43 +1674,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>33.59</v>
+        <v>33.52</v>
       </c>
       <c r="Z8">
-        <v>-15.46</v>
+        <v>-16.18</v>
       </c>
       <c r="AA8">
-        <v>-12.6</v>
+        <v>-13.31</v>
       </c>
       <c r="AB8">
         <v>-2.87</v>
       </c>
       <c r="AC8">
-        <v>11.01</v>
+        <v>2.17</v>
       </c>
       <c r="AD8">
-        <v>22.82</v>
+        <v>11.82</v>
       </c>
       <c r="AE8">
-        <v>17.66</v>
+        <v>17.22</v>
       </c>
       <c r="AF8">
-        <v>-82.97</v>
+        <v>-85.23</v>
       </c>
       <c r="AG8">
-        <v>647.42</v>
+        <v>647.8099999999999</v>
       </c>
       <c r="AH8">
-        <v>549.0599999999999</v>
+        <v>544.72</v>
       </c>
       <c r="AI8">
-        <v>620.12</v>
+        <v>619.4299999999999</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>33.66</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1733,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>182.18</v>
+        <v>183.37</v>
       </c>
       <c r="D9">
-        <v>-0.34</v>
+        <v>0.65</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1745,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-34.37</v>
+        <v>-33.94</v>
       </c>
       <c r="H9">
-        <v>5.73</v>
+        <v>6.42</v>
       </c>
       <c r="I9">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J9">
-        <v>-2.85</v>
+        <v>-2.21</v>
       </c>
       <c r="K9">
-        <v>-4.12</v>
+        <v>-3.17</v>
       </c>
       <c r="L9">
-        <v>-31.52</v>
+        <v>-30.83</v>
       </c>
       <c r="M9">
-        <v>-7.96</v>
+        <v>-7.82</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P9">
-        <v>182.84</v>
+        <v>184.28</v>
       </c>
       <c r="Q9">
-        <v>182.77</v>
+        <v>182.65</v>
       </c>
       <c r="R9">
-        <v>188.58</v>
+        <v>188.49</v>
       </c>
       <c r="S9">
-        <v>195.12</v>
+        <v>194.83</v>
       </c>
       <c r="T9">
-        <v>-6.63</v>
+        <v>-5.88</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1799,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.26</v>
+        <v>48.29</v>
       </c>
       <c r="Z9">
-        <v>-1.84</v>
+        <v>-1.63</v>
       </c>
       <c r="AA9">
-        <v>-2.32</v>
+        <v>-2.18</v>
       </c>
       <c r="AB9">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="AC9">
-        <v>79.38</v>
+        <v>71.34</v>
       </c>
       <c r="AD9">
-        <v>80.17</v>
+        <v>80.36</v>
       </c>
       <c r="AE9">
-        <v>5.15</v>
+        <v>5.08</v>
       </c>
       <c r="AF9">
-        <v>-30.08</v>
+        <v>-14.77</v>
       </c>
       <c r="AG9">
-        <v>189.66</v>
+        <v>189.42</v>
       </c>
       <c r="AH9">
-        <v>175.88</v>
+        <v>175.89</v>
       </c>
       <c r="AI9">
         <v>190.38</v>
@@ -1835,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>23.12</v>
+        <v>20.41</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1846,58 +1834,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>63.79</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="D10">
-        <v>-0.87</v>
+        <v>2.18</v>
       </c>
       <c r="E10">
-        <v>113.79</v>
+        <v>113.29</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-43.94</v>
+        <v>-42.47</v>
       </c>
       <c r="H10">
-        <v>7.61</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I10">
-        <v>-6.3</v>
+        <v>-2.99</v>
       </c>
       <c r="J10">
-        <v>-12.65</v>
+        <v>-11.6</v>
       </c>
       <c r="K10">
-        <v>-23.11</v>
+        <v>-20.79</v>
       </c>
       <c r="L10">
-        <v>-44.62</v>
+        <v>-42.72</v>
       </c>
       <c r="M10">
-        <v>-5.31</v>
+        <v>-4.65</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>65.78</v>
+        <v>65.38</v>
       </c>
       <c r="Q10">
-        <v>69.33</v>
+        <v>68.97</v>
       </c>
       <c r="R10">
-        <v>72.7</v>
+        <v>72.48</v>
       </c>
       <c r="S10">
-        <v>79.23999999999999</v>
+        <v>79.13</v>
       </c>
       <c r="T10">
-        <v>-19.5</v>
+        <v>-17.62</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1912,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>21.24</v>
+        <v>30.53</v>
       </c>
       <c r="Z10">
-        <v>-2.18</v>
+        <v>-2.2</v>
       </c>
       <c r="AA10">
-        <v>-1.71</v>
+        <v>-1.81</v>
       </c>
       <c r="AB10">
-        <v>-0.48</v>
+        <v>-0.4</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>12.41</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AE10">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AF10">
-        <v>5.47</v>
+        <v>-11.35</v>
       </c>
       <c r="AG10">
-        <v>74.33</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="AH10">
-        <v>64.31999999999999</v>
+        <v>63.84</v>
       </c>
       <c r="AI10">
         <v>70.83</v>
@@ -1948,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>52.25</v>
+        <v>53.06</v>
       </c>
     </row>
   </sheetData>
@@ -2089,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2129,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2147,973 +2135,970 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-10.28</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-10.56</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-10.92</v>
+        <v>-10.79</v>
       </c>
       <c r="D8" s="6">
-        <v>-10.28</v>
+        <v>-15.29</v>
       </c>
       <c r="E8" s="7">
-        <v>0.64</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-12</v>
+        <v>-2.8</v>
       </c>
       <c r="D9" s="6">
-        <v>-10.79</v>
+        <v>-3.12</v>
       </c>
       <c r="E9" s="7">
-        <v>1.21</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.06</v>
+        <v>2.98</v>
       </c>
       <c r="D10" s="6">
-        <v>-2.8</v>
+        <v>-1.18</v>
       </c>
       <c r="E10" s="7">
-        <v>1.26</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>0.8100000000000001</v>
+        <v>-9.31</v>
       </c>
       <c r="D11" s="6">
-        <v>2.98</v>
+        <v>-13.49</v>
       </c>
       <c r="E11" s="7">
-        <v>2.17</v>
+        <v>-4.18</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-8.06</v>
+        <v>-11.75</v>
       </c>
       <c r="D12" s="6">
-        <v>-9.31</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.25</v>
+        <v>-12.34</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-14.45</v>
+        <v>-7.54</v>
       </c>
       <c r="D13" s="6">
-        <v>-11.75</v>
+        <v>-8.02</v>
       </c>
       <c r="E13" s="7">
-        <v>2.7</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.87</v>
+        <v>-2.85</v>
       </c>
       <c r="D14" s="6">
-        <v>-7.54</v>
+        <v>-2.21</v>
       </c>
       <c r="E14" s="8">
-        <v>-0.67</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.9</v>
+        <v>-12.65</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.85</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.05</v>
+        <v>-11.6</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.05</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-11.69</v>
+        <v>-4.21</v>
       </c>
       <c r="D16" s="6">
-        <v>-12.65</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.96</v>
+        <v>-5.02</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.15</v>
+        <v>-6.48</v>
       </c>
       <c r="D17" s="6">
-        <v>-4.21</v>
+        <v>-8.17</v>
       </c>
       <c r="E17" s="7">
-        <v>1.94</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-10.59</v>
+        <v>-1.59</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.48</v>
-      </c>
-      <c r="E18" s="7">
-        <v>4.11</v>
+        <v>-0.78</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.31</v>
+        <v>1.34</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.59</v>
+        <v>-1.13</v>
       </c>
       <c r="E19" s="7">
-        <v>1.72</v>
+        <v>-2.47</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-5.02</v>
+        <v>-3.67</v>
       </c>
       <c r="D20" s="6">
-        <v>1.34</v>
+        <v>-7.51</v>
       </c>
       <c r="E20" s="7">
-        <v>6.36</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-7.84</v>
+        <v>-2.97</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.67</v>
+        <v>-5.05</v>
       </c>
       <c r="E21" s="7">
-        <v>4.17</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-8.82</v>
+        <v>-3.36</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.97</v>
+        <v>-3.44</v>
       </c>
       <c r="E22" s="7">
-        <v>5.85</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-5.34</v>
+        <v>3.85</v>
       </c>
       <c r="D23" s="6">
-        <v>-3.36</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.98</v>
+        <v>4.1</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>2.89</v>
+        <v>-6.3</v>
       </c>
       <c r="D24" s="6">
-        <v>3.85</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.96</v>
+        <v>-2.99</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3.31</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-6.93</v>
+        <v>-37.84</v>
       </c>
       <c r="D25" s="6">
-        <v>-6.3</v>
+        <v>-39.09</v>
       </c>
       <c r="E25" s="7">
-        <v>0.63</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-38.53</v>
+        <v>2.41</v>
       </c>
       <c r="D26" s="6">
-        <v>-37.84</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.6899999999999999</v>
+        <v>3.5</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.09</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>0.28</v>
+        <v>18.54</v>
       </c>
       <c r="D27" s="6">
-        <v>2.41</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.13</v>
+        <v>20.11</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.57</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>15.45</v>
+        <v>26.27</v>
       </c>
       <c r="D28" s="6">
-        <v>18.54</v>
+        <v>25.86</v>
       </c>
       <c r="E28" s="7">
-        <v>3.09</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>20.87</v>
+        <v>24.35</v>
       </c>
       <c r="D29" s="6">
-        <v>26.27</v>
+        <v>22.72</v>
       </c>
       <c r="E29" s="7">
-        <v>5.4</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>27.56</v>
+        <v>-38.44</v>
       </c>
       <c r="D30" s="6">
-        <v>24.35</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-3.21</v>
+        <v>-38.64</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-40.52</v>
+        <v>-11.02</v>
       </c>
       <c r="D31" s="6">
-        <v>-38.44</v>
+        <v>-11.43</v>
       </c>
       <c r="E31" s="7">
-        <v>2.08</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-11.75</v>
+        <v>-31.52</v>
       </c>
       <c r="D32" s="6">
-        <v>-11.02</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.73</v>
+        <v>-30.83</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-31.12</v>
+        <v>-44.62</v>
       </c>
       <c r="D33" s="6">
-        <v>-31.52</v>
+        <v>-42.72</v>
       </c>
       <c r="E33" s="8">
-        <v>-0.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-44.32</v>
+        <v>-18.17</v>
       </c>
       <c r="D34" s="6">
-        <v>-44.62</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.3</v>
+        <v>-18.41</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-17.04</v>
+        <v>-16.56</v>
       </c>
       <c r="D35" s="6">
-        <v>-18.17</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.13</v>
+        <v>-17.23</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-15.81</v>
+        <v>-18.27</v>
       </c>
       <c r="D36" s="6">
-        <v>-16.56</v>
+        <v>-17.62</v>
       </c>
       <c r="E36" s="8">
-        <v>-0.75</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-16.88</v>
+        <v>-3.67</v>
       </c>
       <c r="D37" s="6">
-        <v>-18.27</v>
+        <v>-3.11</v>
       </c>
       <c r="E37" s="8">
-        <v>-1.39</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-5.12</v>
+        <v>-13.48</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.67</v>
+        <v>-13.72</v>
       </c>
       <c r="E38" s="7">
-        <v>1.45</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-13.09</v>
+        <v>-19.46</v>
       </c>
       <c r="D39" s="6">
-        <v>-13.48</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.39</v>
+        <v>-19.47</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-20.36</v>
+        <v>-22.16</v>
       </c>
       <c r="D40" s="6">
-        <v>-19.46</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.9</v>
+        <v>-21.88</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.28</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-19.76</v>
+        <v>-4.12</v>
       </c>
       <c r="D41" s="6">
-        <v>-22.16</v>
+        <v>-3.17</v>
       </c>
       <c r="E41" s="8">
-        <v>-2.4</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-1.55</v>
+        <v>-23.11</v>
       </c>
       <c r="D42" s="6">
-        <v>-4.12</v>
+        <v>-20.79</v>
       </c>
       <c r="E42" s="8">
-        <v>-2.57</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-22.19</v>
+        <v>-40.45</v>
       </c>
       <c r="D43" s="6">
-        <v>-23.11</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.92</v>
+        <v>-40.88</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-40.61</v>
+        <v>-17.99</v>
       </c>
       <c r="D44" s="6">
-        <v>-40.45</v>
+        <v>-18.12</v>
       </c>
       <c r="E44" s="7">
-        <v>0.16</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-19.18</v>
+        <v>-21.73</v>
       </c>
       <c r="D45" s="6">
-        <v>-17.99</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.19</v>
+        <v>-20.6</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.13</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-22.99</v>
+        <v>-6.49</v>
       </c>
       <c r="D46" s="6">
-        <v>-21.73</v>
+        <v>-6.86</v>
       </c>
       <c r="E46" s="7">
-        <v>1.26</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-9.300000000000001</v>
+        <v>-24.07</v>
       </c>
       <c r="D47" s="6">
-        <v>-6.49</v>
+        <v>-25.31</v>
       </c>
       <c r="E47" s="7">
-        <v>2.81</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-24.47</v>
+        <v>-38.8</v>
       </c>
       <c r="D48" s="6">
-        <v>-24.07</v>
+        <v>-39.41</v>
       </c>
       <c r="E48" s="7">
-        <v>0.4</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-40.63</v>
+        <v>-30.29</v>
       </c>
       <c r="D49" s="6">
-        <v>-38.8</v>
+        <v>-30.32</v>
       </c>
       <c r="E49" s="7">
-        <v>1.83</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-30.44</v>
+        <v>-34.37</v>
       </c>
       <c r="D50" s="6">
-        <v>-30.29</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.15</v>
+        <v>-33.94</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-34.15</v>
+        <v>-43.94</v>
       </c>
       <c r="D51" s="6">
-        <v>-34.37</v>
+        <v>-42.47</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.22</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>-44.14</v>
+        <v>1133</v>
       </c>
       <c r="D52" s="6">
-        <v>-43.94</v>
+        <v>1124.9</v>
       </c>
       <c r="E52" s="7">
-        <v>0.2</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>1130.1</v>
+        <v>2634.4</v>
       </c>
       <c r="D53" s="6">
-        <v>1133</v>
+        <v>2630</v>
       </c>
       <c r="E53" s="7">
-        <v>2.9</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>2596</v>
+        <v>1255.8</v>
       </c>
       <c r="D54" s="6">
-        <v>2634.4</v>
-      </c>
-      <c r="E54" s="7">
-        <v>38.4</v>
+        <v>1274</v>
+      </c>
+      <c r="E54" s="8">
+        <v>18.2</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1235.7</v>
+        <v>1761</v>
       </c>
       <c r="D55" s="6">
-        <v>1255.8</v>
+        <v>1754</v>
       </c>
       <c r="E55" s="7">
-        <v>20.1</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>1708</v>
+        <v>189</v>
       </c>
       <c r="D56" s="6">
-        <v>1761</v>
+        <v>185.9</v>
       </c>
       <c r="E56" s="7">
-        <v>53</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>188</v>
+        <v>351.5</v>
       </c>
       <c r="D57" s="6">
-        <v>189</v>
+        <v>348</v>
       </c>
       <c r="E57" s="7">
-        <v>1</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>341</v>
+        <v>563.45</v>
       </c>
       <c r="D58" s="6">
-        <v>351.5</v>
+        <v>563.2</v>
       </c>
       <c r="E58" s="7">
-        <v>10.5</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>562.2</v>
+        <v>182.18</v>
       </c>
       <c r="D59" s="6">
-        <v>563.45</v>
-      </c>
-      <c r="E59" s="7">
-        <v>1.25</v>
+        <v>183.37</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1.19</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>182.81</v>
+        <v>63.79</v>
       </c>
       <c r="D60" s="6">
-        <v>182.18</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="E60" s="8">
-        <v>-0.63</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>55</v>
+      </c>
+      <c r="D61" s="6">
         <v>45</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>64.34999999999999</v>
-      </c>
-      <c r="D61" s="6">
-        <v>63.79</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.5600000000000001</v>
+      <c r="E61" s="7">
+        <v>-10</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>13</v>
@@ -3124,337 +3109,320 @@
       <c r="D62" s="6">
         <v>55</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="8">
         <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>55</v>
+        <v>21.31</v>
       </c>
       <c r="D63" s="6">
-        <v>45</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-10</v>
+        <v>20.25</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>19.92</v>
+        <v>34.2</v>
       </c>
       <c r="D64" s="6">
-        <v>21.31</v>
+        <v>34.02</v>
       </c>
       <c r="E64" s="7">
-        <v>1.39</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>31.12</v>
+        <v>44.87</v>
       </c>
       <c r="D65" s="6">
-        <v>34.2</v>
-      </c>
-      <c r="E65" s="7">
-        <v>3.08</v>
+        <v>47.56</v>
+      </c>
+      <c r="E65" s="8">
+        <v>2.69</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>41.8</v>
+        <v>50.93</v>
       </c>
       <c r="D66" s="6">
-        <v>44.87</v>
+        <v>50.1</v>
       </c>
       <c r="E66" s="7">
-        <v>3.07</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>44.45</v>
+        <v>37.47</v>
       </c>
       <c r="D67" s="6">
-        <v>50.93</v>
+        <v>35.28</v>
       </c>
       <c r="E67" s="7">
-        <v>6.48</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>36.28</v>
+        <v>32.96</v>
       </c>
       <c r="D68" s="6">
-        <v>37.47</v>
+        <v>31.61</v>
       </c>
       <c r="E68" s="7">
-        <v>1.19</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>23.93</v>
+        <v>33.59</v>
       </c>
       <c r="D69" s="6">
-        <v>32.96</v>
+        <v>33.52</v>
       </c>
       <c r="E69" s="7">
-        <v>9.029999999999999</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>32.94</v>
+        <v>46.26</v>
       </c>
       <c r="D70" s="6">
-        <v>33.59</v>
-      </c>
-      <c r="E70" s="7">
-        <v>0.65</v>
+        <v>48.29</v>
+      </c>
+      <c r="E70" s="8">
+        <v>2.03</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>47.17</v>
+        <v>21.24</v>
       </c>
       <c r="D71" s="6">
-        <v>46.26</v>
+        <v>30.53</v>
       </c>
       <c r="E71" s="8">
-        <v>-0.91</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>22.36</v>
+        <v>-17.8</v>
       </c>
       <c r="D72" s="6">
-        <v>21.24</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-1.12</v>
+        <v>-30.9</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-13.1</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C73" s="6">
-        <v>-1.09</v>
+        <v>-6.17</v>
       </c>
       <c r="D73" s="6">
-        <v>-17.8</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-16.71</v>
+        <v>-36.36</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-30.19</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>182.99</v>
+        <v>30.37</v>
       </c>
       <c r="D74" s="6">
-        <v>-6.17</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-189.16</v>
+        <v>-30.36</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-60.73</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>322.26</v>
+        <v>356.67</v>
       </c>
       <c r="D75" s="6">
-        <v>30.37</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-291.89</v>
+        <v>322.05</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-34.62</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>62.14</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="D76" s="6">
-        <v>356.67</v>
+        <v>-35.46</v>
       </c>
       <c r="E76" s="7">
-        <v>294.53</v>
+        <v>-26.92</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>146.26</v>
+        <v>50.49</v>
       </c>
       <c r="D77" s="6">
-        <v>-8.539999999999999</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-154.8</v>
+        <v>21.81</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-28.68</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>49.84</v>
+        <v>-82.97</v>
       </c>
       <c r="D78" s="6">
-        <v>50.49</v>
+        <v>-85.23</v>
       </c>
       <c r="E78" s="7">
-        <v>0.65</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-71.84999999999999</v>
+        <v>-30.08</v>
       </c>
       <c r="D79" s="6">
-        <v>-82.97</v>
+        <v>-14.77</v>
       </c>
       <c r="E79" s="8">
-        <v>-11.12</v>
+        <v>15.31</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>-38.25</v>
+        <v>5.47</v>
       </c>
       <c r="D80" s="6">
-        <v>-30.08</v>
+        <v>-11.35</v>
       </c>
       <c r="E80" s="7">
-        <v>8.17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>53.75</v>
-      </c>
-      <c r="D81" s="6">
-        <v>5.47</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-48.28</v>
+        <v>-16.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3478,28 +3446,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3513,16 +3481,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>35.9</v>
+        <v>36.8</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-7.2</v>
+        <v>-8.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-15.4</v>
+        <v>-15</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3659,31 +3627,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5622</v>
+        <v>0.5569</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1969</v>
+        <v>0.1958</v>
       </c>
       <c r="C2" s="14">
-        <v>0.114</v>
+        <v>0.1114</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0156</v>
+        <v>0.0106</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0195</v>
+        <v>-0.0217</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.05309999999999999</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.0796</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1204</v>
+        <v>-0.1213</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.1682</v>
+        <v>-0.167</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>21.2 → 30.5</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.3 → 50.9</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>21.2</t>
-  </si>
-  <si>
-    <t>30.5</t>
+    <t>48.3</t>
+  </si>
+  <si>
+    <t>50.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -417,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1124.9</v>
+        <v>1137</v>
       </c>
       <c r="D2">
-        <v>-0.71</v>
+        <v>1.08</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,25 +942,25 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-40.88</v>
+        <v>-40.24</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="I2">
-        <v>-5.02</v>
+        <v>-3.4</v>
       </c>
       <c r="J2">
-        <v>-10.56</v>
+        <v>-9.35</v>
       </c>
       <c r="K2">
-        <v>-18.41</v>
+        <v>-16.51</v>
       </c>
       <c r="L2">
-        <v>-39.09</v>
+        <v>-38.7</v>
       </c>
       <c r="M2">
-        <v>-12.13</v>
+        <v>-12.05</v>
       </c>
       <c r="N2">
         <v>34</v>
@@ -969,19 +969,19 @@
         <v>13</v>
       </c>
       <c r="P2">
-        <v>1146.1</v>
+        <v>1138.1</v>
       </c>
       <c r="Q2">
-        <v>1206.34</v>
+        <v>1200.86</v>
       </c>
       <c r="R2">
-        <v>1271.32</v>
+        <v>1266.92</v>
       </c>
       <c r="S2">
-        <v>1421.25</v>
+        <v>1418.21</v>
       </c>
       <c r="T2">
-        <v>-20.85</v>
+        <v>-19.83</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,43 +996,43 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>20.25</v>
+        <v>26.16</v>
       </c>
       <c r="Z2">
-        <v>-37.97</v>
+        <v>-38.17</v>
       </c>
       <c r="AA2">
-        <v>-30.77</v>
+        <v>-32.25</v>
       </c>
       <c r="AB2">
-        <v>-7.2</v>
+        <v>-5.92</v>
       </c>
       <c r="AC2">
-        <v>2.57</v>
+        <v>11.86</v>
       </c>
       <c r="AD2">
-        <v>1.55</v>
+        <v>5.5</v>
       </c>
       <c r="AE2">
-        <v>24.79</v>
+        <v>24.11</v>
       </c>
       <c r="AF2">
-        <v>-30.9</v>
+        <v>-42.14</v>
       </c>
       <c r="AG2">
-        <v>1291.81</v>
+        <v>1289.47</v>
       </c>
       <c r="AH2">
-        <v>1120.87</v>
+        <v>1112.26</v>
       </c>
       <c r="AI2">
-        <v>1207.7</v>
+        <v>1203.99</v>
       </c>
       <c r="AJ2" t="s">
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>52.95</v>
+        <v>54.71</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2630</v>
+        <v>2695</v>
       </c>
       <c r="D3">
-        <v>-0.17</v>
+        <v>2.47</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-18.12</v>
+        <v>-16.1</v>
       </c>
       <c r="H3">
-        <v>49.6</v>
+        <v>53.3</v>
       </c>
       <c r="I3">
-        <v>-8.17</v>
+        <v>-5.44</v>
       </c>
       <c r="J3">
-        <v>-15.29</v>
+        <v>-12.42</v>
       </c>
       <c r="K3">
-        <v>-17.23</v>
+        <v>-15.49</v>
       </c>
       <c r="L3">
-        <v>3.5</v>
+        <v>6.82</v>
       </c>
       <c r="M3">
-        <v>11.14</v>
+        <v>11.47</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P3">
-        <v>2690.66</v>
+        <v>2659.68</v>
       </c>
       <c r="Q3">
-        <v>2873.75</v>
+        <v>2855.5</v>
       </c>
       <c r="R3">
-        <v>2955.57</v>
+        <v>2949.28</v>
       </c>
       <c r="S3">
-        <v>2585.82</v>
+        <v>2588.05</v>
       </c>
       <c r="T3">
-        <v>1.71</v>
+        <v>4.13</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>34.02</v>
+        <v>39.33</v>
       </c>
       <c r="Z3">
-        <v>-86.06</v>
+        <v>-86.27</v>
       </c>
       <c r="AA3">
-        <v>-54.4</v>
+        <v>-60.77</v>
       </c>
       <c r="AB3">
-        <v>-31.66</v>
+        <v>-25.5</v>
       </c>
       <c r="AC3">
-        <v>10.5</v>
+        <v>24.98</v>
       </c>
       <c r="AD3">
-        <v>9.380000000000001</v>
+        <v>13.63</v>
       </c>
       <c r="AE3">
-        <v>89.89</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="AF3">
-        <v>-36.36</v>
+        <v>-21.59</v>
       </c>
       <c r="AG3">
-        <v>3138.63</v>
+        <v>3116.62</v>
       </c>
       <c r="AH3">
-        <v>2608.87</v>
+        <v>2594.38</v>
       </c>
       <c r="AI3">
         <v>2899.05</v>
@@ -1145,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>49.04</v>
+        <v>50.08</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1274</v>
+        <v>1287</v>
       </c>
       <c r="D4">
-        <v>1.45</v>
+        <v>1.02</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1168,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-20.6</v>
+        <v>-19.79</v>
       </c>
       <c r="H4">
-        <v>64.86</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="I4">
-        <v>-0.78</v>
+        <v>-1.98</v>
       </c>
       <c r="J4">
-        <v>-3.12</v>
+        <v>-0.93</v>
       </c>
       <c r="K4">
-        <v>-17.62</v>
+        <v>-19.79</v>
       </c>
       <c r="L4">
-        <v>20.11</v>
+        <v>23.15</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.52</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O4">
         <v>66</v>
       </c>
       <c r="P4">
-        <v>1283.98</v>
+        <v>1278.78</v>
       </c>
       <c r="Q4">
-        <v>1282.67</v>
+        <v>1282.95</v>
       </c>
       <c r="R4">
-        <v>1307.19</v>
+        <v>1305.27</v>
       </c>
       <c r="S4">
-        <v>1208.03</v>
+        <v>1209.38</v>
       </c>
       <c r="T4">
-        <v>5.46</v>
+        <v>6.42</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>47.56</v>
+        <v>49.46</v>
       </c>
       <c r="Z4">
-        <v>-10.19</v>
+        <v>-8.85</v>
       </c>
       <c r="AA4">
-        <v>-11.02</v>
+        <v>-10.58</v>
       </c>
       <c r="AB4">
-        <v>0.83</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
-        <v>31</v>
+        <v>44.93</v>
       </c>
       <c r="AD4">
-        <v>49.95</v>
+        <v>41.6</v>
       </c>
       <c r="AE4">
-        <v>45.31</v>
+        <v>44.35</v>
       </c>
       <c r="AF4">
-        <v>-30.36</v>
+        <v>-30.42</v>
       </c>
       <c r="AG4">
-        <v>1339.48</v>
+        <v>1339.8</v>
       </c>
       <c r="AH4">
-        <v>1225.86</v>
+        <v>1226.11</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1258,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>19.57</v>
+        <v>17.94</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1754</v>
+        <v>1763</v>
       </c>
       <c r="D5">
-        <v>-0.4</v>
+        <v>0.51</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,25 +1281,25 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-6.86</v>
+        <v>-6.38</v>
       </c>
       <c r="H5">
-        <v>35.12</v>
+        <v>35.81</v>
       </c>
       <c r="I5">
-        <v>-1.13</v>
+        <v>-1.14</v>
       </c>
       <c r="J5">
-        <v>-1.18</v>
+        <v>-0.28</v>
       </c>
       <c r="K5">
-        <v>-3.11</v>
+        <v>-3.23</v>
       </c>
       <c r="L5">
-        <v>25.86</v>
+        <v>26.98</v>
       </c>
       <c r="M5">
-        <v>19.58</v>
+        <v>19</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1308,19 +1308,19 @@
         <v>76</v>
       </c>
       <c r="P5">
-        <v>1751.3</v>
+        <v>1747.22</v>
       </c>
       <c r="Q5">
-        <v>1767.98</v>
+        <v>1767.9</v>
       </c>
       <c r="R5">
-        <v>1722.94</v>
+        <v>1724.27</v>
       </c>
       <c r="S5">
-        <v>1634.13</v>
+        <v>1635.51</v>
       </c>
       <c r="T5">
-        <v>7.34</v>
+        <v>7.8</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>50.1</v>
+        <v>51.2</v>
       </c>
       <c r="Z5">
-        <v>5.86</v>
+        <v>5.7</v>
       </c>
       <c r="AA5">
-        <v>11.86</v>
+        <v>10.63</v>
       </c>
       <c r="AB5">
-        <v>-6</v>
+        <v>-4.93</v>
       </c>
       <c r="AC5">
-        <v>25.5</v>
+        <v>39.69</v>
       </c>
       <c r="AD5">
-        <v>18.35</v>
+        <v>27.05</v>
       </c>
       <c r="AE5">
-        <v>47.27</v>
+        <v>46.61</v>
       </c>
       <c r="AF5">
-        <v>322.05</v>
+        <v>21.72</v>
       </c>
       <c r="AG5">
-        <v>1836.08</v>
+        <v>1836.02</v>
       </c>
       <c r="AH5">
-        <v>1699.87</v>
+        <v>1699.77</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1371,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.91</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>185.9</v>
+        <v>185.96</v>
       </c>
       <c r="D6">
-        <v>-1.64</v>
+        <v>0.03</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1394,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-25.31</v>
+        <v>-25.29</v>
       </c>
       <c r="H6">
-        <v>39.82</v>
+        <v>39.86</v>
       </c>
       <c r="I6">
-        <v>-7.51</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="J6">
-        <v>-13.49</v>
+        <v>-12.9</v>
       </c>
       <c r="K6">
-        <v>-13.72</v>
+        <v>-17.78</v>
       </c>
       <c r="L6">
-        <v>22.72</v>
+        <v>24.99</v>
       </c>
       <c r="M6">
-        <v>55.69</v>
+        <v>54.2</v>
       </c>
       <c r="N6">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O6">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P6">
-        <v>192.45</v>
+        <v>189.16</v>
       </c>
       <c r="Q6">
-        <v>200.16</v>
+        <v>198.96</v>
       </c>
       <c r="R6">
-        <v>204.73</v>
+        <v>204.23</v>
       </c>
       <c r="S6">
-        <v>189.63</v>
+        <v>189.83</v>
       </c>
       <c r="T6">
-        <v>-1.96</v>
+        <v>-2.04</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,43 +1448,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>35.28</v>
+        <v>35.36</v>
       </c>
       <c r="Z6">
-        <v>-4.48</v>
+        <v>-4.93</v>
       </c>
       <c r="AA6">
-        <v>-3.01</v>
+        <v>-3.4</v>
       </c>
       <c r="AB6">
-        <v>-1.47</v>
+        <v>-1.53</v>
       </c>
       <c r="AC6">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="AD6">
-        <v>22.4</v>
+        <v>8.19</v>
       </c>
       <c r="AE6">
-        <v>6.52</v>
+        <v>6.37</v>
       </c>
       <c r="AF6">
-        <v>-35.46</v>
+        <v>-24.29</v>
       </c>
       <c r="AG6">
-        <v>213.52</v>
+        <v>212.92</v>
       </c>
       <c r="AH6">
-        <v>186.8</v>
+        <v>185.01</v>
       </c>
       <c r="AI6">
-        <v>207.72</v>
+        <v>204.13</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>39.4</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>0.57</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1507,46 +1507,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-39.41</v>
+        <v>-39.06</v>
       </c>
       <c r="H7">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="I7">
-        <v>-5.05</v>
+        <v>-3.19</v>
       </c>
       <c r="J7">
-        <v>-12.34</v>
+        <v>-11.53</v>
       </c>
       <c r="K7">
-        <v>-19.47</v>
+        <v>-18.57</v>
       </c>
       <c r="L7">
-        <v>-38.64</v>
+        <v>-37.89</v>
       </c>
       <c r="M7">
-        <v>-2.17</v>
+        <v>-2.08</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P7">
-        <v>351.79</v>
+        <v>349.48</v>
       </c>
       <c r="Q7">
-        <v>373.31</v>
+        <v>371.22</v>
       </c>
       <c r="R7">
-        <v>398.74</v>
+        <v>397.1</v>
       </c>
       <c r="S7">
-        <v>448.97</v>
+        <v>447.99</v>
       </c>
       <c r="T7">
-        <v>-22.49</v>
+        <v>-21.87</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>31.61</v>
+        <v>33.29</v>
       </c>
       <c r="Z7">
-        <v>-14.11</v>
+        <v>-14.04</v>
       </c>
       <c r="AA7">
-        <v>-12.01</v>
+        <v>-12.42</v>
       </c>
       <c r="AB7">
-        <v>-2.09</v>
+        <v>-1.62</v>
       </c>
       <c r="AC7">
-        <v>30.05</v>
+        <v>46.87</v>
       </c>
       <c r="AD7">
-        <v>23.73</v>
+        <v>33.21</v>
       </c>
       <c r="AE7">
-        <v>10.05</v>
+        <v>9.94</v>
       </c>
       <c r="AF7">
-        <v>21.81</v>
+        <v>31.38</v>
       </c>
       <c r="AG7">
-        <v>404.73</v>
+        <v>403.01</v>
       </c>
       <c r="AH7">
-        <v>341.9</v>
+        <v>339.44</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1597,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>60.8</v>
+        <v>60.01</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>563.2</v>
+        <v>572.2</v>
       </c>
       <c r="D8">
-        <v>-0.04</v>
+        <v>1.6</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-30.32</v>
+        <v>-29.21</v>
       </c>
       <c r="H8">
-        <v>20.41</v>
+        <v>22.33</v>
       </c>
       <c r="I8">
-        <v>-3.44</v>
+        <v>-2.76</v>
       </c>
       <c r="J8">
-        <v>-8.02</v>
+        <v>-5.06</v>
       </c>
       <c r="K8">
-        <v>-21.88</v>
+        <v>-20.7</v>
       </c>
       <c r="L8">
-        <v>-11.43</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="M8">
-        <v>-16.7</v>
+        <v>-16.92</v>
       </c>
       <c r="N8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O8">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P8">
-        <v>571.84</v>
+        <v>568.59</v>
       </c>
       <c r="Q8">
-        <v>596.27</v>
+        <v>595.14</v>
       </c>
       <c r="R8">
-        <v>623.14</v>
+        <v>621.5599999999999</v>
       </c>
       <c r="S8">
-        <v>614.38</v>
+        <v>614.42</v>
       </c>
       <c r="T8">
-        <v>-8.33</v>
+        <v>-6.87</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,43 +1674,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>33.52</v>
+        <v>38.46</v>
       </c>
       <c r="Z8">
-        <v>-16.18</v>
+        <v>-15.84</v>
       </c>
       <c r="AA8">
-        <v>-13.31</v>
+        <v>-13.82</v>
       </c>
       <c r="AB8">
-        <v>-2.87</v>
+        <v>-2.02</v>
       </c>
       <c r="AC8">
-        <v>2.17</v>
+        <v>13.24</v>
       </c>
       <c r="AD8">
-        <v>11.82</v>
+        <v>8.81</v>
       </c>
       <c r="AE8">
-        <v>17.22</v>
+        <v>16.99</v>
       </c>
       <c r="AF8">
-        <v>-85.23</v>
+        <v>-81.78</v>
       </c>
       <c r="AG8">
-        <v>647.8099999999999</v>
+        <v>647.79</v>
       </c>
       <c r="AH8">
-        <v>544.72</v>
+        <v>542.48</v>
       </c>
       <c r="AI8">
-        <v>619.4299999999999</v>
+        <v>617.98</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>35.79</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>183.37</v>
+        <v>184.91</v>
       </c>
       <c r="D9">
-        <v>0.65</v>
+        <v>0.84</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.94</v>
+        <v>-33.39</v>
       </c>
       <c r="H9">
-        <v>6.42</v>
+        <v>7.32</v>
       </c>
       <c r="I9">
-        <v>4.1</v>
+        <v>-0.55</v>
       </c>
       <c r="J9">
-        <v>-2.21</v>
+        <v>-0.43</v>
       </c>
       <c r="K9">
-        <v>-3.17</v>
+        <v>-2.3</v>
       </c>
       <c r="L9">
-        <v>-30.83</v>
+        <v>-30.47</v>
       </c>
       <c r="M9">
-        <v>-7.82</v>
+        <v>-7.65</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
         <v>37</v>
       </c>
       <c r="P9">
-        <v>184.28</v>
+        <v>184.08</v>
       </c>
       <c r="Q9">
         <v>182.65</v>
       </c>
       <c r="R9">
-        <v>188.49</v>
+        <v>188.4</v>
       </c>
       <c r="S9">
-        <v>194.83</v>
+        <v>194.56</v>
       </c>
       <c r="T9">
-        <v>-5.88</v>
+        <v>-4.96</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,31 +1787,31 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>48.29</v>
+        <v>50.87</v>
       </c>
       <c r="Z9">
-        <v>-1.63</v>
+        <v>-1.33</v>
       </c>
       <c r="AA9">
-        <v>-2.18</v>
+        <v>-2.01</v>
       </c>
       <c r="AB9">
-        <v>0.55</v>
+        <v>0.68</v>
       </c>
       <c r="AC9">
-        <v>71.34</v>
+        <v>76.66</v>
       </c>
       <c r="AD9">
-        <v>80.36</v>
+        <v>75.8</v>
       </c>
       <c r="AE9">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="AF9">
-        <v>-14.77</v>
+        <v>-47.18</v>
       </c>
       <c r="AG9">
-        <v>189.42</v>
+        <v>189.4</v>
       </c>
       <c r="AH9">
         <v>175.89</v>
@@ -1823,7 +1823,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>20.41</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,58 +1834,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>65.18000000000001</v>
+        <v>65.91</v>
       </c>
       <c r="D10">
-        <v>2.18</v>
+        <v>1.12</v>
       </c>
       <c r="E10">
-        <v>113.29</v>
+        <v>111.16</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-42.47</v>
+        <v>-40.71</v>
       </c>
       <c r="H10">
-        <v>9.949999999999999</v>
+        <v>11.18</v>
       </c>
       <c r="I10">
-        <v>-2.99</v>
+        <v>-1.74</v>
       </c>
       <c r="J10">
-        <v>-11.6</v>
+        <v>-8.83</v>
       </c>
       <c r="K10">
-        <v>-20.79</v>
+        <v>-19.66</v>
       </c>
       <c r="L10">
-        <v>-42.72</v>
+        <v>-41.82</v>
       </c>
       <c r="M10">
-        <v>-4.65</v>
+        <v>-4.46</v>
       </c>
       <c r="N10">
         <v>12</v>
       </c>
       <c r="O10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>65.38</v>
+        <v>65.14</v>
       </c>
       <c r="Q10">
-        <v>68.97</v>
+        <v>68.67</v>
       </c>
       <c r="R10">
-        <v>72.48</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="S10">
-        <v>79.13</v>
+        <v>79</v>
       </c>
       <c r="T10">
-        <v>-17.62</v>
+        <v>-16.56</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>30.53</v>
+        <v>34.88</v>
       </c>
       <c r="Z10">
-        <v>-2.2</v>
+        <v>-2.14</v>
       </c>
       <c r="AA10">
-        <v>-1.81</v>
+        <v>-1.87</v>
       </c>
       <c r="AB10">
-        <v>-0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="AC10">
-        <v>12.41</v>
+        <v>34.67</v>
       </c>
       <c r="AD10">
-        <v>4.14</v>
+        <v>15.69</v>
       </c>
       <c r="AE10">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AF10">
-        <v>-11.35</v>
+        <v>-41.1</v>
       </c>
       <c r="AG10">
-        <v>74.09999999999999</v>
+        <v>73.75</v>
       </c>
       <c r="AH10">
-        <v>63.84</v>
+        <v>63.58</v>
       </c>
       <c r="AI10">
         <v>70.83</v>
@@ -1936,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>53.06</v>
+        <v>48.41</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2169,13 +2169,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-10.28</v>
+        <v>-10.56</v>
       </c>
       <c r="D7" s="6">
-        <v>-10.56</v>
+        <v>-9.35</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.28</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2186,13 +2186,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-10.79</v>
+        <v>-15.29</v>
       </c>
       <c r="D8" s="6">
-        <v>-15.29</v>
+        <v>-12.42</v>
       </c>
       <c r="E8" s="7">
-        <v>-4.5</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2203,13 +2203,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.8</v>
+        <v>-3.12</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.12</v>
+        <v>-0.93</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.32</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2220,13 +2220,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>2.98</v>
+        <v>-1.18</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.18</v>
+        <v>-0.28</v>
       </c>
       <c r="E10" s="7">
-        <v>-4.16</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2237,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-9.31</v>
+        <v>-13.49</v>
       </c>
       <c r="D11" s="6">
-        <v>-13.49</v>
+        <v>-12.9</v>
       </c>
       <c r="E11" s="7">
-        <v>-4.18</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2254,13 +2254,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-11.75</v>
+        <v>-12.34</v>
       </c>
       <c r="D12" s="6">
-        <v>-12.34</v>
+        <v>-11.53</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.59</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2271,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.54</v>
+        <v>-8.02</v>
       </c>
       <c r="D13" s="6">
-        <v>-8.02</v>
+        <v>-5.06</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.48</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2288,13 +2288,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.85</v>
+        <v>-2.21</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.64</v>
+        <v>-0.43</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.78</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2305,13 +2305,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-12.65</v>
+        <v>-11.6</v>
       </c>
       <c r="D15" s="6">
-        <v>-11.6</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.05</v>
+        <v>-8.83</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.77</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2322,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.21</v>
+        <v>-5.02</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.02</v>
+        <v>-3.4</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.8100000000000001</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2339,13 +2339,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.48</v>
+        <v>-8.17</v>
       </c>
       <c r="D17" s="6">
-        <v>-8.17</v>
+        <v>-5.44</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.69</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2356,13 +2356,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.59</v>
+        <v>-0.78</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.78</v>
+        <v>-1.98</v>
       </c>
       <c r="E18" s="8">
-        <v>0.8100000000000001</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2373,13 +2373,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>1.34</v>
+        <v>-1.13</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.13</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.47</v>
+        <v>-1.14</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2390,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.67</v>
+        <v>-7.51</v>
       </c>
       <c r="D20" s="6">
-        <v>-7.51</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-3.84</v>
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2407,13 +2407,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.97</v>
+        <v>-5.05</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.05</v>
+        <v>-3.19</v>
       </c>
       <c r="E21" s="7">
-        <v>-2.08</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2424,13 +2424,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.36</v>
+        <v>-3.44</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.44</v>
+        <v>-2.76</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.08</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2441,13 +2441,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="D23" s="6">
-        <v>4.1</v>
+        <v>-0.55</v>
       </c>
       <c r="E23" s="8">
-        <v>0.25</v>
+        <v>-4.65</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2458,13 +2458,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-6.3</v>
+        <v>-2.99</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="E24" s="8">
-        <v>3.31</v>
+        <v>-1.74</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2475,13 +2475,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-37.84</v>
+        <v>-39.09</v>
       </c>
       <c r="D25" s="6">
-        <v>-39.09</v>
+        <v>-38.7</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.25</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2492,13 +2492,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="D26" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.09</v>
+        <v>6.82</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.32</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2509,13 +2509,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>18.54</v>
+        <v>20.11</v>
       </c>
       <c r="D27" s="6">
-        <v>20.11</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.57</v>
+        <v>23.15</v>
+      </c>
+      <c r="E27" s="7">
+        <v>3.04</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2526,13 +2526,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>26.27</v>
+        <v>25.86</v>
       </c>
       <c r="D28" s="6">
-        <v>25.86</v>
+        <v>26.98</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.41</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2543,13 +2543,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>24.35</v>
+        <v>22.72</v>
       </c>
       <c r="D29" s="6">
-        <v>22.72</v>
+        <v>24.99</v>
       </c>
       <c r="E29" s="7">
-        <v>-1.63</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2560,13 +2560,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-38.44</v>
+        <v>-38.64</v>
       </c>
       <c r="D30" s="6">
-        <v>-38.64</v>
+        <v>-37.89</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.2</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2577,13 +2577,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-11.02</v>
+        <v>-11.43</v>
       </c>
       <c r="D31" s="6">
-        <v>-11.43</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.41</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2594,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-31.52</v>
+        <v>-30.83</v>
       </c>
       <c r="D32" s="6">
-        <v>-30.83</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.6899999999999999</v>
+        <v>-30.47</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2611,13 +2611,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>-44.62</v>
+        <v>-42.72</v>
       </c>
       <c r="D33" s="6">
-        <v>-42.72</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.9</v>
+        <v>-41.82</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2628,13 +2628,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-18.17</v>
+        <v>-18.41</v>
       </c>
       <c r="D34" s="6">
-        <v>-18.41</v>
+        <v>-16.51</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.24</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2645,13 +2645,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-16.56</v>
+        <v>-17.23</v>
       </c>
       <c r="D35" s="6">
-        <v>-17.23</v>
+        <v>-15.49</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.67</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2662,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-18.27</v>
+        <v>-17.62</v>
       </c>
       <c r="D36" s="6">
-        <v>-17.62</v>
+        <v>-19.79</v>
       </c>
       <c r="E36" s="8">
-        <v>0.65</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2679,13 +2679,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-3.67</v>
+        <v>-3.11</v>
       </c>
       <c r="D37" s="6">
-        <v>-3.11</v>
+        <v>-3.23</v>
       </c>
       <c r="E37" s="8">
-        <v>0.5600000000000001</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2696,13 +2696,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-13.48</v>
+        <v>-13.72</v>
       </c>
       <c r="D38" s="6">
-        <v>-13.72</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.24</v>
+        <v>-17.78</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-4.06</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2713,13 +2713,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-19.46</v>
+        <v>-19.47</v>
       </c>
       <c r="D39" s="6">
-        <v>-19.47</v>
+        <v>-18.57</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.01</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2730,13 +2730,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-22.16</v>
+        <v>-21.88</v>
       </c>
       <c r="D40" s="6">
-        <v>-21.88</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.28</v>
+        <v>-20.7</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.18</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2747,13 +2747,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-4.12</v>
+        <v>-3.17</v>
       </c>
       <c r="D41" s="6">
-        <v>-3.17</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.95</v>
+        <v>-2.3</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.87</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2764,13 +2764,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-23.11</v>
+        <v>-20.79</v>
       </c>
       <c r="D42" s="6">
-        <v>-20.79</v>
-      </c>
-      <c r="E42" s="8">
-        <v>2.32</v>
+        <v>-19.66</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2781,13 +2781,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-40.45</v>
+        <v>-40.88</v>
       </c>
       <c r="D43" s="6">
-        <v>-40.88</v>
+        <v>-40.24</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.43</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2798,13 +2798,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-17.99</v>
+        <v>-18.12</v>
       </c>
       <c r="D44" s="6">
-        <v>-18.12</v>
+        <v>-16.1</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.13</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2815,13 +2815,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-21.73</v>
+        <v>-20.6</v>
       </c>
       <c r="D45" s="6">
-        <v>-20.6</v>
-      </c>
-      <c r="E45" s="8">
-        <v>1.13</v>
+        <v>-19.79</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2832,13 +2832,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-6.49</v>
+        <v>-6.86</v>
       </c>
       <c r="D46" s="6">
-        <v>-6.86</v>
+        <v>-6.38</v>
       </c>
       <c r="E46" s="7">
-        <v>-0.37</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2849,13 +2849,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-24.07</v>
+        <v>-25.31</v>
       </c>
       <c r="D47" s="6">
-        <v>-25.31</v>
+        <v>-25.29</v>
       </c>
       <c r="E47" s="7">
-        <v>-1.24</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2866,13 +2866,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-38.8</v>
+        <v>-39.41</v>
       </c>
       <c r="D48" s="6">
-        <v>-39.41</v>
+        <v>-39.06</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.61</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2883,13 +2883,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>-30.29</v>
+        <v>-30.32</v>
       </c>
       <c r="D49" s="6">
-        <v>-30.32</v>
+        <v>-29.21</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.03</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2900,13 +2900,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>-34.37</v>
+        <v>-33.94</v>
       </c>
       <c r="D50" s="6">
-        <v>-33.94</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.43</v>
+        <v>-33.39</v>
+      </c>
+      <c r="E50" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2917,13 +2917,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="6">
-        <v>-43.94</v>
+        <v>-42.47</v>
       </c>
       <c r="D51" s="6">
-        <v>-42.47</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.47</v>
+        <v>-40.71</v>
+      </c>
+      <c r="E51" s="7">
+        <v>1.76</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2934,13 +2934,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>1133</v>
+        <v>1124.9</v>
       </c>
       <c r="D52" s="6">
-        <v>1124.9</v>
+        <v>1137</v>
       </c>
       <c r="E52" s="7">
-        <v>-8.1</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2951,13 +2951,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>2634.4</v>
+        <v>2630</v>
       </c>
       <c r="D53" s="6">
-        <v>2630</v>
+        <v>2695</v>
       </c>
       <c r="E53" s="7">
-        <v>-4.4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2968,13 +2968,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1255.8</v>
+        <v>1274</v>
       </c>
       <c r="D54" s="6">
-        <v>1274</v>
-      </c>
-      <c r="E54" s="8">
-        <v>18.2</v>
+        <v>1287</v>
+      </c>
+      <c r="E54" s="7">
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>1761</v>
+        <v>1754</v>
       </c>
       <c r="D55" s="6">
-        <v>1754</v>
+        <v>1763</v>
       </c>
       <c r="E55" s="7">
-        <v>-7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -3002,13 +3002,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>189</v>
+        <v>185.9</v>
       </c>
       <c r="D56" s="6">
-        <v>185.9</v>
+        <v>185.96</v>
       </c>
       <c r="E56" s="7">
-        <v>-3.1</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -3019,13 +3019,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>351.5</v>
+        <v>348</v>
       </c>
       <c r="D57" s="6">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E57" s="7">
-        <v>-3.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -3036,13 +3036,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>563.45</v>
+        <v>563.2</v>
       </c>
       <c r="D58" s="6">
-        <v>563.2</v>
+        <v>572.2</v>
       </c>
       <c r="E58" s="7">
-        <v>-0.25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -3053,13 +3053,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="6">
-        <v>182.18</v>
+        <v>183.37</v>
       </c>
       <c r="D59" s="6">
-        <v>183.37</v>
-      </c>
-      <c r="E59" s="8">
-        <v>1.19</v>
+        <v>184.91</v>
+      </c>
+      <c r="E59" s="7">
+        <v>1.54</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3070,353 +3070,387 @@
         <v>2</v>
       </c>
       <c r="C60" s="6">
-        <v>63.79</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="D60" s="6">
-        <v>65.18000000000001</v>
-      </c>
-      <c r="E60" s="8">
-        <v>1.39</v>
+        <v>65.91</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.73</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C61" s="6">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="D61" s="6">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="E61" s="7">
-        <v>-10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C62" s="6">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="D62" s="6">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="E62" s="8">
-        <v>10</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C63" s="6">
-        <v>21.31</v>
+        <v>45</v>
       </c>
       <c r="D63" s="6">
-        <v>20.25</v>
+        <v>55</v>
       </c>
       <c r="E63" s="7">
-        <v>-1.06</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C64" s="6">
-        <v>34.2</v>
+        <v>55</v>
       </c>
       <c r="D64" s="6">
-        <v>34.02</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.18</v>
+        <v>45</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>44.87</v>
+        <v>20.25</v>
       </c>
       <c r="D65" s="6">
-        <v>47.56</v>
-      </c>
-      <c r="E65" s="8">
-        <v>2.69</v>
+        <v>26.16</v>
+      </c>
+      <c r="E65" s="7">
+        <v>5.91</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>50.93</v>
+        <v>34.02</v>
       </c>
       <c r="D66" s="6">
-        <v>50.1</v>
+        <v>39.33</v>
       </c>
       <c r="E66" s="7">
-        <v>-0.83</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6">
-        <v>37.47</v>
+        <v>47.56</v>
       </c>
       <c r="D67" s="6">
-        <v>35.28</v>
+        <v>49.46</v>
       </c>
       <c r="E67" s="7">
-        <v>-2.19</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6">
-        <v>32.96</v>
+        <v>50.1</v>
       </c>
       <c r="D68" s="6">
-        <v>31.61</v>
+        <v>51.2</v>
       </c>
       <c r="E68" s="7">
-        <v>-1.35</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6">
-        <v>33.59</v>
+        <v>35.28</v>
       </c>
       <c r="D69" s="6">
-        <v>33.52</v>
+        <v>35.36</v>
       </c>
       <c r="E69" s="7">
-        <v>-0.07000000000000001</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C70" s="6">
-        <v>46.26</v>
+        <v>31.61</v>
       </c>
       <c r="D70" s="6">
-        <v>48.29</v>
-      </c>
-      <c r="E70" s="8">
-        <v>2.03</v>
+        <v>33.29</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.68</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C71" s="6">
-        <v>21.24</v>
+        <v>33.52</v>
       </c>
       <c r="D71" s="6">
-        <v>30.53</v>
-      </c>
-      <c r="E71" s="8">
-        <v>9.289999999999999</v>
+        <v>38.46</v>
+      </c>
+      <c r="E71" s="7">
+        <v>4.94</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C72" s="6">
-        <v>-17.8</v>
+        <v>48.29</v>
       </c>
       <c r="D72" s="6">
-        <v>-30.9</v>
+        <v>50.87</v>
       </c>
       <c r="E72" s="7">
-        <v>-13.1</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C73" s="6">
-        <v>-6.17</v>
+        <v>30.53</v>
       </c>
       <c r="D73" s="6">
-        <v>-36.36</v>
+        <v>34.88</v>
       </c>
       <c r="E73" s="7">
-        <v>-30.19</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C74" s="6">
-        <v>30.37</v>
+        <v>-30.9</v>
       </c>
       <c r="D74" s="6">
-        <v>-30.36</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-60.73</v>
+        <v>-42.14</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-11.24</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C75" s="6">
-        <v>356.67</v>
+        <v>-36.36</v>
       </c>
       <c r="D75" s="6">
-        <v>322.05</v>
+        <v>-21.59</v>
       </c>
       <c r="E75" s="7">
-        <v>-34.62</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C76" s="6">
-        <v>-8.539999999999999</v>
+        <v>-30.36</v>
       </c>
       <c r="D76" s="6">
-        <v>-35.46</v>
-      </c>
-      <c r="E76" s="7">
-        <v>-26.92</v>
+        <v>-30.42</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C77" s="6">
-        <v>50.49</v>
+        <v>322.05</v>
       </c>
       <c r="D77" s="6">
-        <v>21.81</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-28.68</v>
+        <v>21.72</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-300.33</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C78" s="6">
-        <v>-82.97</v>
+        <v>-35.46</v>
       </c>
       <c r="D78" s="6">
-        <v>-85.23</v>
+        <v>-24.29</v>
       </c>
       <c r="E78" s="7">
-        <v>-2.26</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C79" s="6">
-        <v>-30.08</v>
+        <v>21.81</v>
       </c>
       <c r="D79" s="6">
-        <v>-14.77</v>
-      </c>
-      <c r="E79" s="8">
-        <v>15.31</v>
+        <v>31.38</v>
+      </c>
+      <c r="E79" s="7">
+        <v>9.57</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C80" s="6">
-        <v>5.47</v>
+        <v>-85.23</v>
       </c>
       <c r="D80" s="6">
+        <v>-81.78</v>
+      </c>
+      <c r="E80" s="7">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>-14.77</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-47.18</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-32.41</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="6">
         <v>-11.35</v>
       </c>
-      <c r="E80" s="7">
-        <v>-16.82</v>
+      <c r="D82" s="6">
+        <v>-41.1</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-29.75</v>
       </c>
     </row>
   </sheetData>
@@ -3481,16 +3515,16 @@
         <v>9</v>
       </c>
       <c r="D2" s="11">
-        <v>36.8</v>
+        <v>39.9</v>
       </c>
       <c r="E2" s="11">
         <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-8.6</v>
+        <v>-6.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-15</v>
+        <v>-14.9</v>
       </c>
       <c r="H2" s="11">
         <v>55.4</v>
@@ -3627,31 +3661,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="14">
-        <v>0.5569</v>
+        <v>0.542</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1958</v>
+        <v>0.19</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1114</v>
+        <v>0.1147</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0106</v>
+        <v>0.0152</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.0217</v>
+        <v>-0.0208</v>
       </c>
       <c r="F2" s="14">
-        <v>-0.04650000000000001</v>
+        <v>-0.0446</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.07820000000000001</v>
+        <v>-0.0765</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.1213</v>
+        <v>-0.1205</v>
       </c>
       <c r="I2" s="14">
-        <v>-0.167</v>
+        <v>-0.1692</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,16 +196,28 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.3 → 50.9</t>
+    <t>49.5 → 53.8</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>48.3</t>
-  </si>
-  <si>
-    <t>50.9</t>
+    <t>49.5</t>
+  </si>
+  <si>
+    <t>53.8</t>
+  </si>
+  <si>
+    <t>51.2 → 49.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>49.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,6 +427,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -930,10 +943,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1137</v>
+        <v>1135.9</v>
       </c>
       <c r="D2">
-        <v>1.08</v>
+        <v>-0.1</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +955,46 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-40.24</v>
+        <v>-40.3</v>
       </c>
       <c r="H2">
-        <v>1.08</v>
+        <v>0.98</v>
       </c>
       <c r="I2">
-        <v>-3.4</v>
+        <v>-2.54</v>
       </c>
       <c r="J2">
-        <v>-9.35</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="K2">
-        <v>-16.51</v>
+        <v>-17.88</v>
       </c>
       <c r="L2">
-        <v>-38.7</v>
+        <v>-39.06</v>
       </c>
       <c r="M2">
-        <v>-12.05</v>
+        <v>-12.45</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P2">
-        <v>1138.1</v>
+        <v>1132.18</v>
       </c>
       <c r="Q2">
-        <v>1200.86</v>
+        <v>1196.4</v>
       </c>
       <c r="R2">
-        <v>1266.92</v>
+        <v>1261.67</v>
       </c>
       <c r="S2">
-        <v>1418.21</v>
+        <v>1415.24</v>
       </c>
       <c r="T2">
-        <v>-19.83</v>
+        <v>-19.74</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1009,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>26.16</v>
+        <v>25.97</v>
       </c>
       <c r="Z2">
-        <v>-38.17</v>
+        <v>-37.99</v>
       </c>
       <c r="AA2">
-        <v>-32.25</v>
+        <v>-33.4</v>
       </c>
       <c r="AB2">
-        <v>-5.92</v>
+        <v>-4.59</v>
       </c>
       <c r="AC2">
-        <v>11.86</v>
+        <v>20.63</v>
       </c>
       <c r="AD2">
-        <v>5.5</v>
+        <v>11.69</v>
       </c>
       <c r="AE2">
-        <v>24.11</v>
+        <v>23.55</v>
       </c>
       <c r="AF2">
-        <v>-42.14</v>
+        <v>-51.5</v>
       </c>
       <c r="AG2">
-        <v>1289.47</v>
+        <v>1288.77</v>
       </c>
       <c r="AH2">
-        <v>1112.26</v>
+        <v>1104.03</v>
       </c>
       <c r="AI2">
         <v>1203.99</v>
@@ -1032,7 +1045,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>54.71</v>
+        <v>53.83</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2695</v>
+        <v>2722.6</v>
       </c>
       <c r="D3">
-        <v>2.47</v>
+        <v>1.02</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1068,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-16.1</v>
+        <v>-15.24</v>
       </c>
       <c r="H3">
-        <v>53.3</v>
+        <v>54.87</v>
       </c>
       <c r="I3">
-        <v>-5.44</v>
+        <v>-0.74</v>
       </c>
       <c r="J3">
-        <v>-12.42</v>
+        <v>-11.03</v>
       </c>
       <c r="K3">
-        <v>-15.49</v>
+        <v>-13.58</v>
       </c>
       <c r="L3">
-        <v>6.82</v>
+        <v>7.14</v>
       </c>
       <c r="M3">
-        <v>11.47</v>
+        <v>10.63</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P3">
-        <v>2659.68</v>
+        <v>2655.6</v>
       </c>
       <c r="Q3">
-        <v>2855.5</v>
+        <v>2845.2</v>
       </c>
       <c r="R3">
-        <v>2949.28</v>
+        <v>2942.37</v>
       </c>
       <c r="S3">
-        <v>2588.05</v>
+        <v>2590.56</v>
       </c>
       <c r="T3">
-        <v>4.13</v>
+        <v>5.1</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1122,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.33</v>
+        <v>41.48</v>
       </c>
       <c r="Z3">
-        <v>-86.27</v>
+        <v>-83.25</v>
       </c>
       <c r="AA3">
-        <v>-60.77</v>
+        <v>-65.27</v>
       </c>
       <c r="AB3">
-        <v>-25.5</v>
+        <v>-17.98</v>
       </c>
       <c r="AC3">
-        <v>24.98</v>
+        <v>37.83</v>
       </c>
       <c r="AD3">
-        <v>13.63</v>
+        <v>24.44</v>
       </c>
       <c r="AE3">
-        <v>89.54000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="AF3">
-        <v>-21.59</v>
+        <v>-5.08</v>
       </c>
       <c r="AG3">
-        <v>3116.62</v>
+        <v>3110.4</v>
       </c>
       <c r="AH3">
-        <v>2594.38</v>
+        <v>2580</v>
       </c>
       <c r="AI3">
         <v>2899.05</v>
@@ -1145,7 +1158,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>50.08</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1287</v>
+        <v>1318.4</v>
       </c>
       <c r="D4">
-        <v>1.02</v>
+        <v>2.44</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1181,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.79</v>
+        <v>-17.83</v>
       </c>
       <c r="H4">
-        <v>66.54000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I4">
-        <v>-1.98</v>
+        <v>-1.71</v>
       </c>
       <c r="J4">
-        <v>-0.93</v>
+        <v>2.9</v>
       </c>
       <c r="K4">
-        <v>-19.79</v>
+        <v>-15.24</v>
       </c>
       <c r="L4">
-        <v>23.15</v>
+        <v>25.38</v>
       </c>
       <c r="M4">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="N4">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>1278.78</v>
+        <v>1274.18</v>
       </c>
       <c r="Q4">
-        <v>1282.95</v>
+        <v>1286.12</v>
       </c>
       <c r="R4">
-        <v>1305.27</v>
+        <v>1303.74</v>
       </c>
       <c r="S4">
-        <v>1209.38</v>
+        <v>1210.9</v>
       </c>
       <c r="T4">
-        <v>6.42</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1235,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>49.46</v>
+        <v>53.82</v>
       </c>
       <c r="Z4">
-        <v>-8.85</v>
+        <v>-5.2</v>
       </c>
       <c r="AA4">
-        <v>-10.58</v>
+        <v>-9.51</v>
       </c>
       <c r="AB4">
-        <v>1.73</v>
+        <v>4.31</v>
       </c>
       <c r="AC4">
-        <v>44.93</v>
+        <v>61.21</v>
       </c>
       <c r="AD4">
-        <v>41.6</v>
+        <v>45.71</v>
       </c>
       <c r="AE4">
-        <v>44.35</v>
+        <v>44.79</v>
       </c>
       <c r="AF4">
-        <v>-30.42</v>
+        <v>-18.03</v>
       </c>
       <c r="AG4">
-        <v>1339.8</v>
+        <v>1343.47</v>
       </c>
       <c r="AH4">
-        <v>1226.11</v>
+        <v>1228.78</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1258,7 +1271,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>17.94</v>
+        <v>17.51</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1763</v>
+        <v>1748.7</v>
       </c>
       <c r="D5">
-        <v>0.51</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1294,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-6.38</v>
+        <v>-7.14</v>
       </c>
       <c r="H5">
-        <v>35.81</v>
+        <v>34.71</v>
       </c>
       <c r="I5">
-        <v>-1.14</v>
+        <v>-0.08</v>
       </c>
       <c r="J5">
-        <v>-0.28</v>
+        <v>-0.9</v>
       </c>
       <c r="K5">
-        <v>-3.23</v>
+        <v>-4.4</v>
       </c>
       <c r="L5">
-        <v>26.98</v>
+        <v>25.83</v>
       </c>
       <c r="M5">
-        <v>19</v>
+        <v>17.19</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1747.22</v>
+        <v>1746.94</v>
       </c>
       <c r="Q5">
-        <v>1767.9</v>
+        <v>1769.64</v>
       </c>
       <c r="R5">
-        <v>1724.27</v>
+        <v>1725.22</v>
       </c>
       <c r="S5">
-        <v>1635.51</v>
+        <v>1636.81</v>
       </c>
       <c r="T5">
-        <v>7.8</v>
+        <v>6.84</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1348,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>51.2</v>
+        <v>49.34</v>
       </c>
       <c r="Z5">
-        <v>5.7</v>
+        <v>4.37</v>
       </c>
       <c r="AA5">
-        <v>10.63</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB5">
-        <v>-4.93</v>
+        <v>-5.01</v>
       </c>
       <c r="AC5">
-        <v>39.69</v>
+        <v>36.92</v>
       </c>
       <c r="AD5">
-        <v>27.05</v>
+        <v>34.04</v>
       </c>
       <c r="AE5">
-        <v>46.61</v>
+        <v>46.77</v>
       </c>
       <c r="AF5">
-        <v>21.72</v>
+        <v>-37.7</v>
       </c>
       <c r="AG5">
-        <v>1836.02</v>
+        <v>1833.59</v>
       </c>
       <c r="AH5">
-        <v>1699.77</v>
+        <v>1705.69</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1371,7 +1384,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>29.46</v>
+        <v>30.74</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>185.96</v>
+        <v>195.15</v>
       </c>
       <c r="D6">
-        <v>0.03</v>
+        <v>4.94</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,46 +1407,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-25.29</v>
+        <v>-21.6</v>
       </c>
       <c r="H6">
-        <v>39.86</v>
+        <v>46.77</v>
       </c>
       <c r="I6">
-        <v>-8.119999999999999</v>
+        <v>-0.91</v>
       </c>
       <c r="J6">
-        <v>-12.9</v>
+        <v>-7.06</v>
       </c>
       <c r="K6">
-        <v>-17.78</v>
+        <v>-10.88</v>
       </c>
       <c r="L6">
-        <v>24.99</v>
+        <v>31.05</v>
       </c>
       <c r="M6">
-        <v>54.2</v>
+        <v>54.19</v>
       </c>
       <c r="N6">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O6">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="P6">
-        <v>189.16</v>
+        <v>188.8</v>
       </c>
       <c r="Q6">
-        <v>198.96</v>
+        <v>198.62</v>
       </c>
       <c r="R6">
-        <v>204.23</v>
+        <v>203.86</v>
       </c>
       <c r="S6">
-        <v>189.83</v>
+        <v>190.09</v>
       </c>
       <c r="T6">
-        <v>-2.04</v>
+        <v>2.66</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,37 +1458,37 @@
         <v>47</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>35.36</v>
+        <v>46.16</v>
       </c>
       <c r="Z6">
-        <v>-4.93</v>
+        <v>-4.49</v>
       </c>
       <c r="AA6">
-        <v>-3.4</v>
+        <v>-3.61</v>
       </c>
       <c r="AB6">
-        <v>-1.53</v>
+        <v>-0.87</v>
       </c>
       <c r="AC6">
-        <v>3.32</v>
+        <v>27.23</v>
       </c>
       <c r="AD6">
-        <v>8.19</v>
+        <v>11.22</v>
       </c>
       <c r="AE6">
-        <v>6.37</v>
+        <v>6.83</v>
       </c>
       <c r="AF6">
-        <v>-24.29</v>
+        <v>87.25</v>
       </c>
       <c r="AG6">
-        <v>212.92</v>
+        <v>212.6</v>
       </c>
       <c r="AH6">
-        <v>185.01</v>
+        <v>184.64</v>
       </c>
       <c r="AI6">
         <v>204.13</v>
@@ -1484,7 +1497,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>42.78</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1508,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D7">
-        <v>0.57</v>
+        <v>-0.29</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1507,46 +1520,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-39.06</v>
+        <v>-39.24</v>
       </c>
       <c r="H7">
-        <v>2.64</v>
+        <v>2.35</v>
       </c>
       <c r="I7">
-        <v>-3.19</v>
+        <v>-2.21</v>
       </c>
       <c r="J7">
-        <v>-11.53</v>
+        <v>-10.94</v>
       </c>
       <c r="K7">
-        <v>-18.57</v>
+        <v>-19.82</v>
       </c>
       <c r="L7">
-        <v>-37.89</v>
+        <v>-38.02</v>
       </c>
       <c r="M7">
-        <v>-2.08</v>
+        <v>-2.36</v>
       </c>
       <c r="N7">
         <v>23</v>
       </c>
       <c r="O7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>349.48</v>
+        <v>347.9</v>
       </c>
       <c r="Q7">
-        <v>371.22</v>
+        <v>369.58</v>
       </c>
       <c r="R7">
-        <v>397.1</v>
+        <v>395.2</v>
       </c>
       <c r="S7">
-        <v>447.99</v>
+        <v>447.01</v>
       </c>
       <c r="T7">
-        <v>-21.87</v>
+        <v>-21.93</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1574,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>33.29</v>
+        <v>32.86</v>
       </c>
       <c r="Z7">
-        <v>-14.04</v>
+        <v>-13.91</v>
       </c>
       <c r="AA7">
-        <v>-12.42</v>
+        <v>-12.72</v>
       </c>
       <c r="AB7">
-        <v>-1.62</v>
+        <v>-1.2</v>
       </c>
       <c r="AC7">
-        <v>46.87</v>
+        <v>54.79</v>
       </c>
       <c r="AD7">
-        <v>33.21</v>
+        <v>43.9</v>
       </c>
       <c r="AE7">
-        <v>9.94</v>
+        <v>9.58</v>
       </c>
       <c r="AF7">
-        <v>31.38</v>
+        <v>-24.76</v>
       </c>
       <c r="AG7">
-        <v>403.01</v>
+        <v>402.44</v>
       </c>
       <c r="AH7">
-        <v>339.44</v>
+        <v>336.73</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1597,7 +1610,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>60.01</v>
+        <v>58.84</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1621,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>572.2</v>
+        <v>581.6</v>
       </c>
       <c r="D8">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1633,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-29.21</v>
+        <v>-28.04</v>
       </c>
       <c r="H8">
-        <v>22.33</v>
+        <v>24.34</v>
       </c>
       <c r="I8">
-        <v>-2.76</v>
+        <v>-0.05</v>
       </c>
       <c r="J8">
-        <v>-5.06</v>
+        <v>-2.22</v>
       </c>
       <c r="K8">
-        <v>-20.7</v>
+        <v>-18.7</v>
       </c>
       <c r="L8">
-        <v>-9.029999999999999</v>
+        <v>-7.31</v>
       </c>
       <c r="M8">
-        <v>-16.92</v>
+        <v>-16.7</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P8">
-        <v>568.59</v>
+        <v>568.53</v>
       </c>
       <c r="Q8">
-        <v>595.14</v>
+        <v>595.21</v>
       </c>
       <c r="R8">
-        <v>621.5599999999999</v>
+        <v>619.84</v>
       </c>
       <c r="S8">
-        <v>614.42</v>
+        <v>614.51</v>
       </c>
       <c r="T8">
-        <v>-6.87</v>
+        <v>-5.36</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1687,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>38.46</v>
+        <v>43.21</v>
       </c>
       <c r="Z8">
-        <v>-15.84</v>
+        <v>-14.64</v>
       </c>
       <c r="AA8">
-        <v>-13.82</v>
+        <v>-13.98</v>
       </c>
       <c r="AB8">
-        <v>-2.02</v>
+        <v>-0.66</v>
       </c>
       <c r="AC8">
-        <v>13.24</v>
+        <v>39.34</v>
       </c>
       <c r="AD8">
-        <v>8.81</v>
+        <v>18.25</v>
       </c>
       <c r="AE8">
-        <v>16.99</v>
+        <v>17.02</v>
       </c>
       <c r="AF8">
-        <v>-81.78</v>
+        <v>-75.33</v>
       </c>
       <c r="AG8">
-        <v>647.79</v>
+        <v>647.78</v>
       </c>
       <c r="AH8">
-        <v>542.48</v>
+        <v>542.64</v>
       </c>
       <c r="AI8">
         <v>617.98</v>
@@ -1710,7 +1723,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>37.92</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1734,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>184.91</v>
+        <v>188.21</v>
       </c>
       <c r="D9">
-        <v>0.84</v>
+        <v>1.78</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1746,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-33.39</v>
+        <v>-32.2</v>
       </c>
       <c r="H9">
-        <v>7.32</v>
+        <v>9.23</v>
       </c>
       <c r="I9">
-        <v>-0.55</v>
+        <v>0.59</v>
       </c>
       <c r="J9">
-        <v>-0.43</v>
+        <v>1.72</v>
       </c>
       <c r="K9">
-        <v>-2.3</v>
+        <v>-0.39</v>
       </c>
       <c r="L9">
-        <v>-30.47</v>
+        <v>-29.81</v>
       </c>
       <c r="M9">
-        <v>-7.65</v>
+        <v>-7.29</v>
       </c>
       <c r="N9">
         <v>45</v>
       </c>
       <c r="O9">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P9">
-        <v>184.08</v>
+        <v>184.3</v>
       </c>
       <c r="Q9">
-        <v>182.65</v>
+        <v>182.9</v>
       </c>
       <c r="R9">
-        <v>188.4</v>
+        <v>188.36</v>
       </c>
       <c r="S9">
-        <v>194.56</v>
+        <v>194.31</v>
       </c>
       <c r="T9">
-        <v>-4.96</v>
+        <v>-3.14</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1800,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>50.87</v>
+        <v>55.96</v>
       </c>
       <c r="Z9">
-        <v>-1.33</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AA9">
-        <v>-2.01</v>
+        <v>-1.77</v>
       </c>
       <c r="AB9">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AC9">
-        <v>76.66</v>
+        <v>87.62</v>
       </c>
       <c r="AD9">
-        <v>75.8</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="AE9">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="AF9">
-        <v>-47.18</v>
+        <v>-14.84</v>
       </c>
       <c r="AG9">
-        <v>189.4</v>
+        <v>190.1</v>
       </c>
       <c r="AH9">
-        <v>175.89</v>
+        <v>175.7</v>
       </c>
       <c r="AI9">
         <v>190.38</v>
@@ -1823,7 +1836,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>18.64</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,37 +1847,37 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>65.91</v>
+        <v>65.98</v>
       </c>
       <c r="D10">
-        <v>1.12</v>
+        <v>0.11</v>
       </c>
       <c r="E10">
-        <v>111.16</v>
+        <v>105.03</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-40.71</v>
+        <v>-37.18</v>
       </c>
       <c r="H10">
-        <v>11.18</v>
+        <v>11.3</v>
       </c>
       <c r="I10">
-        <v>-1.74</v>
+        <v>-0.75</v>
       </c>
       <c r="J10">
-        <v>-8.83</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="K10">
-        <v>-19.66</v>
+        <v>-18.94</v>
       </c>
       <c r="L10">
-        <v>-41.82</v>
+        <v>-40.64</v>
       </c>
       <c r="M10">
-        <v>-4.46</v>
+        <v>-4.38</v>
       </c>
       <c r="N10">
         <v>12</v>
@@ -1873,19 +1886,19 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>65.14</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="Q10">
-        <v>68.67</v>
+        <v>68.44</v>
       </c>
       <c r="R10">
-        <v>72.26000000000001</v>
+        <v>72.03</v>
       </c>
       <c r="S10">
-        <v>79</v>
+        <v>78.86</v>
       </c>
       <c r="T10">
-        <v>-16.56</v>
+        <v>-16.33</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1913,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>34.88</v>
+        <v>35.29</v>
       </c>
       <c r="Z10">
-        <v>-2.14</v>
+        <v>-2.05</v>
       </c>
       <c r="AA10">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="AB10">
-        <v>-0.26</v>
+        <v>-0.14</v>
       </c>
       <c r="AC10">
-        <v>34.67</v>
+        <v>61.78</v>
       </c>
       <c r="AD10">
-        <v>15.69</v>
+        <v>36.28</v>
       </c>
       <c r="AE10">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AF10">
-        <v>-41.1</v>
+        <v>53.83</v>
       </c>
       <c r="AG10">
-        <v>73.75</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AH10">
-        <v>63.58</v>
+        <v>63.29</v>
       </c>
       <c r="AI10">
         <v>70.83</v>
@@ -1936,7 +1949,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>48.41</v>
+        <v>43.48</v>
       </c>
     </row>
   </sheetData>
@@ -2077,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2130,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1328 +2148,1314 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.56</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>-9.35</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-15.29</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>-12.42</v>
       </c>
-      <c r="E8" s="7">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-11.03</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-3.12</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>-0.93</v>
       </c>
-      <c r="E9" s="7">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>2.9</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="7">
         <v>-0.28</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-0.9</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-13.49</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="7">
         <v>-12.9</v>
       </c>
-      <c r="E11" s="7">
+      <c r="D12" s="7">
+        <v>-7.06</v>
+      </c>
+      <c r="E12" s="8">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-11.53</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-10.94</v>
+      </c>
+      <c r="E13" s="8">
         <v>0.59</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-5.06</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-2.22</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-0.43</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1.72</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-8.83</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-3.4</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2.54</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-5.44</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-0.74</v>
+      </c>
+      <c r="E18" s="8">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-1.98</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.71</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.14</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-0.08</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-8.119999999999999</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-0.91</v>
+      </c>
+      <c r="E21" s="8">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-12.34</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-11.53</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-3.19</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-2.21</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-8.02</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-5.06</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2.96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-2.76</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-0.05</v>
+      </c>
+      <c r="E23" s="8">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.55</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0.59</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-1.74</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-0.75</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-38.7</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-39.06</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>6.82</v>
+      </c>
+      <c r="D27" s="7">
+        <v>7.14</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>23.15</v>
+      </c>
+      <c r="D28" s="7">
+        <v>25.38</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>26.98</v>
+      </c>
+      <c r="D29" s="7">
+        <v>25.83</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>24.99</v>
+      </c>
+      <c r="D30" s="7">
+        <v>31.05</v>
+      </c>
+      <c r="E30" s="8">
+        <v>6.06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-37.89</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-38.02</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-7.31</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-30.47</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-29.81</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-41.82</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-40.64</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-16.51</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-17.88</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-15.49</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-13.58</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-19.79</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-15.24</v>
+      </c>
+      <c r="E37" s="8">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-3.23</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-4.4</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-17.78</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-10.88</v>
+      </c>
+      <c r="E39" s="8">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-18.57</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-19.82</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-20.7</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-18.7</v>
+      </c>
+      <c r="E41" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-2.3</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-0.39</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-19.66</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-18.94</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-40.24</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-40.3</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-16.1</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-15.24</v>
+      </c>
+      <c r="E45" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-19.79</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-17.83</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-6.38</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-7.14</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-25.29</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-21.6</v>
+      </c>
+      <c r="E48" s="8">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-39.06</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-39.24</v>
+      </c>
+      <c r="E49" s="9">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-29.21</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-28.04</v>
+      </c>
+      <c r="E50" s="8">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-33.39</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-32.2</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-40.71</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-37.18</v>
+      </c>
+      <c r="E52" s="8">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1137</v>
+      </c>
+      <c r="D53" s="7">
+        <v>1135.9</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>2695</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2722.6</v>
+      </c>
+      <c r="E54" s="8">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1287</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1318.4</v>
+      </c>
+      <c r="E55" s="8">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1763</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1748.7</v>
+      </c>
+      <c r="E56" s="9">
+        <v>-14.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>185.96</v>
+      </c>
+      <c r="D57" s="7">
+        <v>195.15</v>
+      </c>
+      <c r="E57" s="8">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>350</v>
+      </c>
+      <c r="D58" s="7">
+        <v>349</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>572.2</v>
+      </c>
+      <c r="D59" s="7">
+        <v>581.6</v>
+      </c>
+      <c r="E59" s="8">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>184.91</v>
+      </c>
+      <c r="D60" s="7">
+        <v>188.21</v>
+      </c>
+      <c r="E60" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>65.91</v>
+      </c>
+      <c r="D61" s="7">
+        <v>65.98</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="7">
+        <v>88</v>
+      </c>
+      <c r="D62" s="7">
+        <v>77</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>77</v>
+      </c>
+      <c r="D63" s="7">
+        <v>88</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>26.16</v>
+      </c>
+      <c r="D64" s="7">
+        <v>25.97</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>39.33</v>
+      </c>
+      <c r="D65" s="7">
+        <v>41.48</v>
+      </c>
+      <c r="E65" s="8">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>49.46</v>
+      </c>
+      <c r="D66" s="7">
+        <v>53.82</v>
+      </c>
+      <c r="E66" s="8">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>51.2</v>
+      </c>
+      <c r="D67" s="7">
+        <v>49.34</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>35.36</v>
+      </c>
+      <c r="D68" s="7">
+        <v>46.16</v>
+      </c>
+      <c r="E68" s="8">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>33.29</v>
+      </c>
+      <c r="D69" s="7">
+        <v>32.86</v>
+      </c>
+      <c r="E69" s="9">
         <v>-0.43</v>
       </c>
-      <c r="E14" s="7">
-        <v>1.78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>38.46</v>
+      </c>
+      <c r="D70" s="7">
+        <v>43.21</v>
+      </c>
+      <c r="E70" s="8">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>50.87</v>
+      </c>
+      <c r="D71" s="7">
+        <v>55.96</v>
+      </c>
+      <c r="E71" s="8">
+        <v>5.09</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-11.6</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-8.83</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>34.88</v>
+      </c>
+      <c r="D72" s="7">
+        <v>35.29</v>
+      </c>
+      <c r="E72" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>-42.14</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-51.5</v>
+      </c>
+      <c r="E73" s="9">
+        <v>-9.359999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-8.17</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-5.44</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="7">
+        <v>-21.59</v>
+      </c>
+      <c r="D74" s="7">
+        <v>-5.08</v>
+      </c>
+      <c r="E74" s="8">
+        <v>16.51</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.98</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>-30.42</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-18.03</v>
+      </c>
+      <c r="E75" s="8">
+        <v>12.39</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.13</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>21.72</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-37.7</v>
+      </c>
+      <c r="E76" s="9">
+        <v>-59.42</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-7.51</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-24.29</v>
+      </c>
+      <c r="D77" s="7">
+        <v>87.25</v>
+      </c>
+      <c r="E77" s="8">
+        <v>111.54</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-5.05</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-3.19</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>31.38</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-24.76</v>
+      </c>
+      <c r="E78" s="9">
+        <v>-56.14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-3.44</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-2.76</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-81.78</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-75.33</v>
+      </c>
+      <c r="E79" s="8">
+        <v>6.45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>4.1</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-4.65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>-47.18</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-14.84</v>
+      </c>
+      <c r="E80" s="8">
+        <v>32.34</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-1.74</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-39.09</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-38.7</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="D26" s="6">
-        <v>6.82</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>20.11</v>
-      </c>
-      <c r="D27" s="6">
-        <v>23.15</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>25.86</v>
-      </c>
-      <c r="D28" s="6">
-        <v>26.98</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>22.72</v>
-      </c>
-      <c r="D29" s="6">
-        <v>24.99</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-38.64</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-37.89</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-11.43</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-30.83</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-30.47</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-42.72</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-41.82</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-18.41</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-16.51</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-17.23</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-15.49</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-17.62</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-19.79</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-3.11</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-13.72</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-17.78</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-4.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-19.47</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-18.57</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-21.88</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-20.7</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-3.17</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-20.79</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-19.66</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-40.88</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-40.24</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-18.12</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-16.1</v>
-      </c>
-      <c r="E44" s="7">
-        <v>2.02</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-20.6</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-19.79</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-6.86</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-25.31</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-25.29</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-39.41</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-39.06</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-30.32</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-29.21</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-33.94</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-33.39</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-42.47</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-40.71</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>1124.9</v>
-      </c>
-      <c r="D52" s="6">
-        <v>1137</v>
-      </c>
-      <c r="E52" s="7">
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>2630</v>
-      </c>
-      <c r="D53" s="6">
-        <v>2695</v>
-      </c>
-      <c r="E53" s="7">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1274</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1287</v>
-      </c>
-      <c r="E54" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>1754</v>
-      </c>
-      <c r="D55" s="6">
-        <v>1763</v>
-      </c>
-      <c r="E55" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>185.9</v>
-      </c>
-      <c r="D56" s="6">
-        <v>185.96</v>
-      </c>
-      <c r="E56" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>348</v>
-      </c>
-      <c r="D57" s="6">
-        <v>350</v>
-      </c>
-      <c r="E57" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>563.2</v>
-      </c>
-      <c r="D58" s="6">
-        <v>572.2</v>
-      </c>
-      <c r="E58" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>183.37</v>
-      </c>
-      <c r="D59" s="6">
-        <v>184.91</v>
-      </c>
-      <c r="E59" s="7">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>65.18000000000001</v>
-      </c>
-      <c r="D60" s="6">
-        <v>65.91</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>77</v>
-      </c>
-      <c r="D61" s="6">
-        <v>88</v>
-      </c>
-      <c r="E61" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>88</v>
-      </c>
-      <c r="D62" s="6">
-        <v>77</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>45</v>
-      </c>
-      <c r="D63" s="6">
-        <v>55</v>
-      </c>
-      <c r="E63" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>55</v>
-      </c>
-      <c r="D64" s="6">
-        <v>45</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>20.25</v>
-      </c>
-      <c r="D65" s="6">
-        <v>26.16</v>
-      </c>
-      <c r="E65" s="7">
-        <v>5.91</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>34.02</v>
-      </c>
-      <c r="D66" s="6">
-        <v>39.33</v>
-      </c>
-      <c r="E66" s="7">
-        <v>5.31</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>47.56</v>
-      </c>
-      <c r="D67" s="6">
-        <v>49.46</v>
-      </c>
-      <c r="E67" s="7">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>50.1</v>
-      </c>
-      <c r="D68" s="6">
-        <v>51.2</v>
-      </c>
-      <c r="E68" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>35.28</v>
-      </c>
-      <c r="D69" s="6">
-        <v>35.36</v>
-      </c>
-      <c r="E69" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>31.61</v>
-      </c>
-      <c r="D70" s="6">
-        <v>33.29</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>33.52</v>
-      </c>
-      <c r="D71" s="6">
-        <v>38.46</v>
-      </c>
-      <c r="E71" s="7">
-        <v>4.94</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>48.29</v>
-      </c>
-      <c r="D72" s="6">
-        <v>50.87</v>
-      </c>
-      <c r="E72" s="7">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>30.53</v>
-      </c>
-      <c r="D73" s="6">
-        <v>34.88</v>
-      </c>
-      <c r="E73" s="7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="5" t="s">
+      <c r="B81" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="6">
-        <v>-30.9</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-42.14</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-11.24</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-36.36</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-21.59</v>
-      </c>
-      <c r="E75" s="7">
-        <v>14.77</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-30.36</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-30.42</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>322.05</v>
-      </c>
-      <c r="D77" s="6">
-        <v>21.72</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-300.33</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-35.46</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-24.29</v>
-      </c>
-      <c r="E78" s="7">
-        <v>11.17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>21.81</v>
-      </c>
-      <c r="D79" s="6">
-        <v>31.38</v>
-      </c>
-      <c r="E79" s="7">
-        <v>9.57</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-85.23</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-81.78</v>
-      </c>
-      <c r="E80" s="7">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>-14.77</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-47.18</v>
+      <c r="C81" s="7">
+        <v>-41.1</v>
+      </c>
+      <c r="D81" s="7">
+        <v>53.83</v>
       </c>
       <c r="E81" s="8">
-        <v>-32.41</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-11.35</v>
-      </c>
-      <c r="D82" s="6">
-        <v>-41.1</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-29.75</v>
+        <v>94.93000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3476,60 +3475,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="F1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>44.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>48.16</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.9</v>
-      </c>
-      <c r="E2" s="11">
-        <v>30</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-6.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-14.9</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>42.7</v>
+      </c>
+      <c r="E2" s="12">
+        <v>40</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-5</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-13.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>55.4</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>10</v>
       </c>
     </row>
@@ -3631,61 +3630,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.542</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.19</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1147</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0152</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.0208</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0446</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.0765</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1205</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1692</v>
+      <c r="A2" s="15">
+        <v>0.5418999999999999</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1719</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1063</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0179</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.0236</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0438</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.07290000000000001</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.1245</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.167</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,46 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.5 → 53.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.5</t>
-  </si>
-  <si>
-    <t>53.8</t>
-  </si>
-  <si>
-    <t>51.2 → 49.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.2</t>
-  </si>
-  <si>
-    <t>49.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -419,16 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -943,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1135.9</v>
+        <v>1137.4</v>
       </c>
       <c r="D2">
-        <v>-0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -955,46 +914,46 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-40.3</v>
+        <v>-40.22</v>
       </c>
       <c r="H2">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="I2">
-        <v>-2.54</v>
+        <v>0.65</v>
       </c>
       <c r="J2">
-        <v>-8.869999999999999</v>
+        <v>-7.17</v>
       </c>
       <c r="K2">
-        <v>-17.88</v>
+        <v>-17.18</v>
       </c>
       <c r="L2">
-        <v>-39.06</v>
+        <v>-39.33</v>
       </c>
       <c r="M2">
-        <v>-12.45</v>
+        <v>-12.4</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P2">
-        <v>1132.18</v>
+        <v>1133.64</v>
       </c>
       <c r="Q2">
-        <v>1196.4</v>
+        <v>1191.94</v>
       </c>
       <c r="R2">
-        <v>1261.67</v>
+        <v>1256.73</v>
       </c>
       <c r="S2">
-        <v>1415.24</v>
+        <v>1412.3</v>
       </c>
       <c r="T2">
-        <v>-19.74</v>
+        <v>-19.46</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>25.97</v>
+        <v>26.74</v>
       </c>
       <c r="Z2">
-        <v>-37.99</v>
+        <v>-37.29</v>
       </c>
       <c r="AA2">
-        <v>-33.4</v>
+        <v>-34.18</v>
       </c>
       <c r="AB2">
-        <v>-4.59</v>
+        <v>-3.11</v>
       </c>
       <c r="AC2">
-        <v>20.63</v>
+        <v>32.36</v>
       </c>
       <c r="AD2">
-        <v>11.69</v>
+        <v>21.62</v>
       </c>
       <c r="AE2">
-        <v>23.55</v>
+        <v>23.21</v>
       </c>
       <c r="AF2">
-        <v>-51.5</v>
+        <v>-20.78</v>
       </c>
       <c r="AG2">
-        <v>1288.77</v>
+        <v>1286.75</v>
       </c>
       <c r="AH2">
-        <v>1104.03</v>
+        <v>1097.13</v>
       </c>
       <c r="AI2">
         <v>1203.99</v>
@@ -1045,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>53.83</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2722.6</v>
+        <v>2700</v>
       </c>
       <c r="D3">
-        <v>1.02</v>
+        <v>-0.83</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1068,25 +1027,25 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-15.24</v>
+        <v>-15.94</v>
       </c>
       <c r="H3">
-        <v>54.87</v>
+        <v>53.58</v>
       </c>
       <c r="I3">
-        <v>-0.74</v>
+        <v>4.01</v>
       </c>
       <c r="J3">
-        <v>-11.03</v>
+        <v>-7.81</v>
       </c>
       <c r="K3">
-        <v>-13.58</v>
+        <v>-14.32</v>
       </c>
       <c r="L3">
-        <v>7.14</v>
+        <v>5.89</v>
       </c>
       <c r="M3">
-        <v>10.63</v>
+        <v>10.89</v>
       </c>
       <c r="N3">
         <v>66</v>
@@ -1095,19 +1054,19 @@
         <v>55</v>
       </c>
       <c r="P3">
-        <v>2655.6</v>
+        <v>2676.4</v>
       </c>
       <c r="Q3">
-        <v>2845.2</v>
+        <v>2834.2</v>
       </c>
       <c r="R3">
-        <v>2942.37</v>
+        <v>2935.37</v>
       </c>
       <c r="S3">
-        <v>2590.56</v>
+        <v>2592.91</v>
       </c>
       <c r="T3">
-        <v>5.1</v>
+        <v>4.13</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1122,34 +1081,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>41.48</v>
+        <v>40.22</v>
       </c>
       <c r="Z3">
-        <v>-83.25</v>
+        <v>-81.73</v>
       </c>
       <c r="AA3">
-        <v>-65.27</v>
+        <v>-68.56</v>
       </c>
       <c r="AB3">
-        <v>-17.98</v>
+        <v>-13.17</v>
       </c>
       <c r="AC3">
-        <v>37.83</v>
+        <v>48.8</v>
       </c>
       <c r="AD3">
-        <v>24.44</v>
+        <v>37.2</v>
       </c>
       <c r="AE3">
-        <v>86.84</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="AF3">
-        <v>-5.08</v>
+        <v>-44.58</v>
       </c>
       <c r="AG3">
-        <v>3110.4</v>
+        <v>3104.54</v>
       </c>
       <c r="AH3">
-        <v>2580</v>
+        <v>2563.86</v>
       </c>
       <c r="AI3">
         <v>2899.05</v>
@@ -1158,7 +1117,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>48.5</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1318.4</v>
+        <v>1307.1</v>
       </c>
       <c r="D4">
-        <v>2.44</v>
+        <v>-0.86</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1181,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-17.83</v>
+        <v>-18.54</v>
       </c>
       <c r="H4">
-        <v>70.59999999999999</v>
+        <v>69.14</v>
       </c>
       <c r="I4">
-        <v>-1.71</v>
+        <v>5.78</v>
       </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>4.15</v>
       </c>
       <c r="K4">
-        <v>-15.24</v>
+        <v>-15.33</v>
       </c>
       <c r="L4">
-        <v>25.38</v>
+        <v>22.81</v>
       </c>
       <c r="M4">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1274.18</v>
+        <v>1288.46</v>
       </c>
       <c r="Q4">
-        <v>1286.12</v>
+        <v>1287.97</v>
       </c>
       <c r="R4">
-        <v>1303.74</v>
+        <v>1302.2</v>
       </c>
       <c r="S4">
-        <v>1210.9</v>
+        <v>1212.34</v>
       </c>
       <c r="T4">
-        <v>8.880000000000001</v>
+        <v>7.82</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1235,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>53.82</v>
+        <v>52.08</v>
       </c>
       <c r="Z4">
-        <v>-5.2</v>
+        <v>-3.18</v>
       </c>
       <c r="AA4">
-        <v>-9.51</v>
+        <v>-8.24</v>
       </c>
       <c r="AB4">
-        <v>4.31</v>
+        <v>5.06</v>
       </c>
       <c r="AC4">
-        <v>61.21</v>
+        <v>69.42</v>
       </c>
       <c r="AD4">
-        <v>45.71</v>
+        <v>58.52</v>
       </c>
       <c r="AE4">
-        <v>44.79</v>
+        <v>42.99</v>
       </c>
       <c r="AF4">
-        <v>-18.03</v>
+        <v>-56.33</v>
       </c>
       <c r="AG4">
-        <v>1343.47</v>
+        <v>1345.53</v>
       </c>
       <c r="AH4">
-        <v>1228.78</v>
+        <v>1230.41</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1271,7 +1230,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>17.51</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1748.7</v>
+        <v>1743.2</v>
       </c>
       <c r="D5">
-        <v>-0.8100000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1294,46 +1253,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.14</v>
+        <v>-7.43</v>
       </c>
       <c r="H5">
-        <v>34.71</v>
+        <v>34.29</v>
       </c>
       <c r="I5">
-        <v>-0.08</v>
+        <v>2.06</v>
       </c>
       <c r="J5">
-        <v>-0.9</v>
+        <v>1.72</v>
       </c>
       <c r="K5">
-        <v>-4.4</v>
+        <v>-4.56</v>
       </c>
       <c r="L5">
-        <v>25.83</v>
+        <v>24.2</v>
       </c>
       <c r="M5">
-        <v>17.19</v>
+        <v>17.21</v>
       </c>
       <c r="N5">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>1746.94</v>
+        <v>1753.98</v>
       </c>
       <c r="Q5">
-        <v>1769.64</v>
+        <v>1770.61</v>
       </c>
       <c r="R5">
-        <v>1725.22</v>
+        <v>1725.95</v>
       </c>
       <c r="S5">
-        <v>1636.81</v>
+        <v>1638.13</v>
       </c>
       <c r="T5">
-        <v>6.84</v>
+        <v>6.41</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1348,34 +1307,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.34</v>
+        <v>48.6</v>
       </c>
       <c r="Z5">
-        <v>4.37</v>
+        <v>2.84</v>
       </c>
       <c r="AA5">
-        <v>9.380000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="AB5">
-        <v>-5.01</v>
+        <v>-5.23</v>
       </c>
       <c r="AC5">
-        <v>36.92</v>
+        <v>34.27</v>
       </c>
       <c r="AD5">
-        <v>34.04</v>
+        <v>36.96</v>
       </c>
       <c r="AE5">
-        <v>46.77</v>
+        <v>46.03</v>
       </c>
       <c r="AF5">
-        <v>-37.7</v>
+        <v>-21.7</v>
       </c>
       <c r="AG5">
-        <v>1833.59</v>
+        <v>1832.18</v>
       </c>
       <c r="AH5">
-        <v>1705.69</v>
+        <v>1709.04</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1384,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>30.74</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>195.15</v>
+        <v>196.5</v>
       </c>
       <c r="D6">
-        <v>4.94</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1407,46 +1366,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-21.6</v>
+        <v>-21.06</v>
       </c>
       <c r="H6">
-        <v>46.77</v>
+        <v>47.79</v>
       </c>
       <c r="I6">
-        <v>-0.91</v>
+        <v>4.52</v>
       </c>
       <c r="J6">
-        <v>-7.06</v>
+        <v>-2.72</v>
       </c>
       <c r="K6">
-        <v>-10.88</v>
+        <v>-9.27</v>
       </c>
       <c r="L6">
-        <v>31.05</v>
+        <v>31.26</v>
       </c>
       <c r="M6">
-        <v>54.19</v>
+        <v>51.59</v>
       </c>
       <c r="N6">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O6">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>188.8</v>
+        <v>190.5</v>
       </c>
       <c r="Q6">
-        <v>198.62</v>
+        <v>198.33</v>
       </c>
       <c r="R6">
-        <v>203.86</v>
+        <v>203.59</v>
       </c>
       <c r="S6">
-        <v>190.09</v>
+        <v>190.37</v>
       </c>
       <c r="T6">
-        <v>2.66</v>
+        <v>3.22</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1461,34 +1420,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>46.16</v>
+        <v>47.55</v>
       </c>
       <c r="Z6">
-        <v>-4.49</v>
+        <v>-3.98</v>
       </c>
       <c r="AA6">
-        <v>-3.61</v>
+        <v>-3.69</v>
       </c>
       <c r="AB6">
-        <v>-0.87</v>
+        <v>-0.29</v>
       </c>
       <c r="AC6">
-        <v>27.23</v>
+        <v>57.72</v>
       </c>
       <c r="AD6">
-        <v>11.22</v>
+        <v>29.42</v>
       </c>
       <c r="AE6">
-        <v>6.83</v>
+        <v>6.69</v>
       </c>
       <c r="AF6">
-        <v>87.25</v>
+        <v>-29.94</v>
       </c>
       <c r="AG6">
-        <v>212.6</v>
+        <v>212.22</v>
       </c>
       <c r="AH6">
-        <v>184.64</v>
+        <v>184.44</v>
       </c>
       <c r="AI6">
         <v>204.13</v>
@@ -1497,7 +1456,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>38.95</v>
+        <v>35.28</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>349</v>
+        <v>350.9</v>
       </c>
       <c r="D7">
-        <v>-0.29</v>
+        <v>0.54</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1520,46 +1479,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-39.24</v>
+        <v>-38.91</v>
       </c>
       <c r="H7">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="I7">
-        <v>-2.21</v>
+        <v>2.9</v>
       </c>
       <c r="J7">
-        <v>-10.94</v>
+        <v>-8.08</v>
       </c>
       <c r="K7">
-        <v>-19.82</v>
+        <v>-19.07</v>
       </c>
       <c r="L7">
-        <v>-38.02</v>
+        <v>-38.05</v>
       </c>
       <c r="M7">
-        <v>-2.36</v>
+        <v>-2.35</v>
       </c>
       <c r="N7">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="O7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P7">
-        <v>347.9</v>
+        <v>349.88</v>
       </c>
       <c r="Q7">
-        <v>369.58</v>
+        <v>368.08</v>
       </c>
       <c r="R7">
-        <v>395.2</v>
+        <v>393.5</v>
       </c>
       <c r="S7">
-        <v>447.01</v>
+        <v>446.01</v>
       </c>
       <c r="T7">
-        <v>-21.93</v>
+        <v>-21.32</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1574,34 +1533,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>32.86</v>
+        <v>34.6</v>
       </c>
       <c r="Z7">
-        <v>-13.91</v>
+        <v>-13.5</v>
       </c>
       <c r="AA7">
-        <v>-12.72</v>
+        <v>-12.87</v>
       </c>
       <c r="AB7">
-        <v>-1.2</v>
+        <v>-0.63</v>
       </c>
       <c r="AC7">
-        <v>54.79</v>
+        <v>70.33</v>
       </c>
       <c r="AD7">
-        <v>43.9</v>
+        <v>57.33</v>
       </c>
       <c r="AE7">
-        <v>9.58</v>
+        <v>9.49</v>
       </c>
       <c r="AF7">
-        <v>-24.76</v>
+        <v>52.85</v>
       </c>
       <c r="AG7">
-        <v>402.44</v>
+        <v>401.48</v>
       </c>
       <c r="AH7">
-        <v>336.73</v>
+        <v>334.67</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1610,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>58.84</v>
+        <v>54.58</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>581.6</v>
+        <v>576.8</v>
       </c>
       <c r="D8">
-        <v>1.64</v>
+        <v>-0.83</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1633,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-28.04</v>
+        <v>-28.64</v>
       </c>
       <c r="H8">
-        <v>24.34</v>
+        <v>23.32</v>
       </c>
       <c r="I8">
-        <v>-0.05</v>
+        <v>2.6</v>
       </c>
       <c r="J8">
-        <v>-2.22</v>
+        <v>-0.58</v>
       </c>
       <c r="K8">
-        <v>-18.7</v>
+        <v>-18.5</v>
       </c>
       <c r="L8">
-        <v>-7.31</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="M8">
-        <v>-16.7</v>
+        <v>-16.78</v>
       </c>
       <c r="N8">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O8">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="P8">
-        <v>568.53</v>
+        <v>571.45</v>
       </c>
       <c r="Q8">
-        <v>595.21</v>
+        <v>594.73</v>
       </c>
       <c r="R8">
-        <v>619.84</v>
+        <v>618.03</v>
       </c>
       <c r="S8">
-        <v>614.51</v>
+        <v>614.54</v>
       </c>
       <c r="T8">
-        <v>-5.36</v>
+        <v>-6.14</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1687,34 +1646,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>43.21</v>
+        <v>41.45</v>
       </c>
       <c r="Z8">
-        <v>-14.64</v>
+        <v>-13.92</v>
       </c>
       <c r="AA8">
-        <v>-13.98</v>
+        <v>-13.97</v>
       </c>
       <c r="AB8">
-        <v>-0.66</v>
+        <v>0.05</v>
       </c>
       <c r="AC8">
-        <v>39.34</v>
+        <v>61.11</v>
       </c>
       <c r="AD8">
-        <v>18.25</v>
+        <v>37.89</v>
       </c>
       <c r="AE8">
-        <v>17.02</v>
+        <v>16.4</v>
       </c>
       <c r="AF8">
-        <v>-75.33</v>
+        <v>-85.95999999999999</v>
       </c>
       <c r="AG8">
-        <v>647.78</v>
+        <v>647.8099999999999</v>
       </c>
       <c r="AH8">
-        <v>542.64</v>
+        <v>541.64</v>
       </c>
       <c r="AI8">
         <v>617.98</v>
@@ -1723,7 +1682,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>35.45</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>188.21</v>
+        <v>190.54</v>
       </c>
       <c r="D9">
-        <v>1.78</v>
+        <v>1.24</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1746,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.2</v>
+        <v>-31.36</v>
       </c>
       <c r="H9">
-        <v>9.23</v>
+        <v>10.59</v>
       </c>
       <c r="I9">
-        <v>0.59</v>
+        <v>4.23</v>
       </c>
       <c r="J9">
-        <v>1.72</v>
+        <v>4.04</v>
       </c>
       <c r="K9">
-        <v>-0.39</v>
+        <v>0.37</v>
       </c>
       <c r="L9">
-        <v>-29.81</v>
+        <v>-29.15</v>
       </c>
       <c r="M9">
-        <v>-7.29</v>
+        <v>-7.05</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O9">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P9">
-        <v>184.3</v>
+        <v>185.84</v>
       </c>
       <c r="Q9">
-        <v>182.9</v>
+        <v>183.33</v>
       </c>
       <c r="R9">
         <v>188.36</v>
       </c>
       <c r="S9">
-        <v>194.31</v>
+        <v>194.08</v>
       </c>
       <c r="T9">
-        <v>-3.14</v>
+        <v>-1.82</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1800,43 +1759,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>55.96</v>
+        <v>59.17</v>
       </c>
       <c r="Z9">
-        <v>-0.8100000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="AA9">
-        <v>-1.77</v>
+        <v>-1.46</v>
       </c>
       <c r="AB9">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AC9">
-        <v>87.62</v>
+        <v>95.67</v>
       </c>
       <c r="AD9">
-        <v>78.54000000000001</v>
+        <v>86.65000000000001</v>
       </c>
       <c r="AE9">
-        <v>5.11</v>
+        <v>5.53</v>
       </c>
       <c r="AF9">
-        <v>-14.84</v>
+        <v>97.11</v>
       </c>
       <c r="AG9">
-        <v>190.1</v>
+        <v>191.28</v>
       </c>
       <c r="AH9">
-        <v>175.7</v>
+        <v>175.39</v>
       </c>
       <c r="AI9">
-        <v>190.38</v>
+        <v>176.41</v>
       </c>
       <c r="AJ9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AK9">
-        <v>20.33</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,58 +1806,58 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>65.98</v>
+        <v>65.34</v>
       </c>
       <c r="D10">
-        <v>0.11</v>
+        <v>-0.97</v>
       </c>
       <c r="E10">
-        <v>105.03</v>
+        <v>101.33</v>
       </c>
       <c r="F10">
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-37.18</v>
+        <v>-35.52</v>
       </c>
       <c r="H10">
-        <v>11.3</v>
+        <v>10.22</v>
       </c>
       <c r="I10">
-        <v>-0.75</v>
+        <v>1.54</v>
       </c>
       <c r="J10">
-        <v>-8.390000000000001</v>
+        <v>-7.23</v>
       </c>
       <c r="K10">
-        <v>-18.94</v>
+        <v>-18.9</v>
       </c>
       <c r="L10">
-        <v>-40.64</v>
+        <v>-37.79</v>
       </c>
       <c r="M10">
-        <v>-4.38</v>
+        <v>-4.58</v>
       </c>
       <c r="N10">
+        <v>23</v>
+      </c>
+      <c r="O10">
         <v>12</v>
       </c>
-      <c r="O10">
-        <v>10</v>
-      </c>
       <c r="P10">
-        <v>65.04000000000001</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="Q10">
-        <v>68.44</v>
+        <v>68.22</v>
       </c>
       <c r="R10">
-        <v>72.03</v>
+        <v>71.81</v>
       </c>
       <c r="S10">
-        <v>78.86</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="T10">
-        <v>-16.33</v>
+        <v>-16.95</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1913,34 +1872,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>35.29</v>
+        <v>33.2</v>
       </c>
       <c r="Z10">
-        <v>-2.05</v>
+        <v>-2.02</v>
       </c>
       <c r="AA10">
-        <v>-1.91</v>
+        <v>-1.93</v>
       </c>
       <c r="AB10">
-        <v>-0.14</v>
+        <v>-0.09</v>
       </c>
       <c r="AC10">
-        <v>61.78</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="AD10">
-        <v>36.28</v>
+        <v>56.29</v>
       </c>
       <c r="AE10">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AF10">
-        <v>53.83</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AG10">
-        <v>73.59999999999999</v>
+        <v>73.52</v>
       </c>
       <c r="AH10">
-        <v>63.29</v>
+        <v>62.93</v>
       </c>
       <c r="AI10">
         <v>70.83</v>
@@ -1949,7 +1908,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>43.48</v>
+        <v>39.21</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2110,1352 +2069,1365 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-8.869999999999999</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.17</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1.7</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-11.03</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-7.81</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2.9</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4.15</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-0.9</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.72</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-7.06</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-2.72</v>
+      </c>
+      <c r="E11" s="6">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-10.94</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-8.08</v>
+      </c>
+      <c r="E12" s="6">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.22</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.58</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1.72</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4.04</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-7.23</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-9.35</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.54</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="E16" s="6">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-12.42</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-11.03</v>
-      </c>
-      <c r="E9" s="8">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-0.74</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4.01</v>
+      </c>
+      <c r="E17" s="6">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-1.71</v>
+      </c>
+      <c r="D18" s="5">
+        <v>5.78</v>
+      </c>
+      <c r="E18" s="6">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-0.08</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2.06</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-0.91</v>
+      </c>
+      <c r="D20" s="5">
+        <v>4.52</v>
+      </c>
+      <c r="E20" s="6">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-2.21</v>
+      </c>
+      <c r="D21" s="5">
+        <v>2.9</v>
+      </c>
+      <c r="E21" s="6">
+        <v>5.11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-0.05</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2.6</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.59</v>
+      </c>
+      <c r="D23" s="5">
+        <v>4.23</v>
+      </c>
+      <c r="E23" s="6">
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-0.75</v>
+      </c>
+      <c r="D24" s="5">
+        <v>1.54</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-39.06</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-39.33</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>7.14</v>
+      </c>
+      <c r="D26" s="5">
+        <v>5.89</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>25.38</v>
+      </c>
+      <c r="D27" s="5">
+        <v>22.81</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>25.83</v>
+      </c>
+      <c r="D28" s="5">
+        <v>24.2</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>31.05</v>
+      </c>
+      <c r="D29" s="5">
+        <v>31.26</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-38.02</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-38.05</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-7.31</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-29.81</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-29.15</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-40.64</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-37.79</v>
+      </c>
+      <c r="E33" s="6">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-17.88</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-17.18</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-13.58</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-14.32</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-15.24</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-15.33</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-4.4</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-4.56</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-10.88</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-9.27</v>
+      </c>
+      <c r="E38" s="6">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-19.82</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-19.07</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-18.7</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-18.5</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-0.39</v>
+      </c>
+      <c r="D41" s="5">
+        <v>0.37</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-18.94</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-18.9</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-40.3</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-40.22</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-15.24</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-15.94</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-17.83</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-18.54</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-7.14</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-7.43</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-21.6</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-21.06</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-39.24</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-38.91</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-28.04</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-28.64</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-32.2</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-31.36</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-37.18</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-35.52</v>
+      </c>
+      <c r="E51" s="6">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1135.9</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1137.4</v>
+      </c>
+      <c r="E52" s="6">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>2722.6</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2700</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-22.6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1318.4</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1307.1</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-11.3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1748.7</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1743.2</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>195.15</v>
+      </c>
+      <c r="D56" s="5">
+        <v>196.5</v>
+      </c>
+      <c r="E56" s="6">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>349</v>
+      </c>
+      <c r="D57" s="5">
+        <v>350.9</v>
+      </c>
+      <c r="E57" s="6">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>581.6</v>
+      </c>
+      <c r="D58" s="5">
+        <v>576.8</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-4.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>188.21</v>
+      </c>
+      <c r="D59" s="5">
+        <v>190.54</v>
+      </c>
+      <c r="E59" s="6">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>65.98</v>
+      </c>
+      <c r="D60" s="5">
+        <v>65.34</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="5">
+        <v>99</v>
+      </c>
+      <c r="D61" s="5">
+        <v>88</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="5">
+        <v>88</v>
+      </c>
+      <c r="D62" s="5">
+        <v>99</v>
+      </c>
+      <c r="E62" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="5">
+        <v>23</v>
+      </c>
+      <c r="D63" s="5">
+        <v>12</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="5">
+        <v>55</v>
+      </c>
+      <c r="D64" s="5">
+        <v>45</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="5">
+        <v>45</v>
+      </c>
+      <c r="D65" s="5">
+        <v>55</v>
+      </c>
+      <c r="E65" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="5">
+        <v>12</v>
+      </c>
+      <c r="D66" s="5">
+        <v>23</v>
+      </c>
+      <c r="E66" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>25.97</v>
+      </c>
+      <c r="D67" s="5">
+        <v>26.74</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>41.48</v>
+      </c>
+      <c r="D68" s="5">
+        <v>40.22</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>53.82</v>
+      </c>
+      <c r="D69" s="5">
+        <v>52.08</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="5">
+        <v>49.34</v>
+      </c>
+      <c r="D70" s="5">
+        <v>48.6</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="5">
+        <v>46.16</v>
+      </c>
+      <c r="D71" s="5">
+        <v>47.55</v>
+      </c>
+      <c r="E71" s="6">
         <v>1.39</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="5">
+        <v>32.86</v>
+      </c>
+      <c r="D72" s="5">
+        <v>34.6</v>
+      </c>
+      <c r="E72" s="6">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="5">
+        <v>43.21</v>
+      </c>
+      <c r="D73" s="5">
+        <v>41.45</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="5">
+        <v>55.96</v>
+      </c>
+      <c r="D74" s="5">
+        <v>59.17</v>
+      </c>
+      <c r="E74" s="6">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="5">
+        <v>35.29</v>
+      </c>
+      <c r="D75" s="5">
+        <v>33.2</v>
+      </c>
+      <c r="E75" s="7">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-51.5</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-20.78</v>
+      </c>
+      <c r="E76" s="6">
+        <v>30.72</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-5.08</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-44.58</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-39.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-0.93</v>
-      </c>
-      <c r="D10" s="7">
-        <v>2.9</v>
-      </c>
-      <c r="E10" s="8">
-        <v>3.83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B78" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="5">
+        <v>-18.03</v>
+      </c>
+      <c r="D78" s="5">
+        <v>-56.33</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-38.3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-0.28</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-0.9</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="5">
+        <v>-37.7</v>
+      </c>
+      <c r="D79" s="5">
+        <v>-21.7</v>
+      </c>
+      <c r="E79" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-12.9</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-7.06</v>
-      </c>
-      <c r="E12" s="8">
-        <v>5.84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B80" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="5">
+        <v>87.25</v>
+      </c>
+      <c r="D80" s="5">
+        <v>-29.94</v>
+      </c>
+      <c r="E80" s="7">
+        <v>-117.19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-11.53</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-10.94</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B81" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="5">
+        <v>-24.76</v>
+      </c>
+      <c r="D81" s="5">
+        <v>52.85</v>
+      </c>
+      <c r="E81" s="6">
+        <v>77.61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-5.06</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-2.22</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B82" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="5">
+        <v>-75.33</v>
+      </c>
+      <c r="D82" s="5">
+        <v>-85.95999999999999</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-10.63</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-0.43</v>
-      </c>
-      <c r="D15" s="7">
-        <v>1.72</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B83" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="5">
+        <v>-14.84</v>
+      </c>
+      <c r="D83" s="5">
+        <v>97.11</v>
+      </c>
+      <c r="E83" s="6">
+        <v>111.95</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-8.83</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-3.4</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-2.54</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-5.44</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-0.74</v>
-      </c>
-      <c r="E18" s="8">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.98</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-1.71</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.14</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-0.08</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.06</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-0.91</v>
-      </c>
-      <c r="E21" s="8">
-        <v>7.21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-3.19</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-2.21</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-2.76</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-0.05</v>
-      </c>
-      <c r="E23" s="8">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-0.55</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0.59</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-1.74</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-0.75</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-38.7</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-39.06</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>6.82</v>
-      </c>
-      <c r="D27" s="7">
-        <v>7.14</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>23.15</v>
-      </c>
-      <c r="D28" s="7">
-        <v>25.38</v>
-      </c>
-      <c r="E28" s="8">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>26.98</v>
-      </c>
-      <c r="D29" s="7">
-        <v>25.83</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>24.99</v>
-      </c>
-      <c r="D30" s="7">
-        <v>31.05</v>
-      </c>
-      <c r="E30" s="8">
-        <v>6.06</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-37.89</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-38.02</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-7.31</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-30.47</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-29.81</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-41.82</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-40.64</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-16.51</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-17.88</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-15.49</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-13.58</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-19.79</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-15.24</v>
-      </c>
-      <c r="E37" s="8">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-3.23</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-4.4</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-17.78</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-10.88</v>
-      </c>
-      <c r="E39" s="8">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-18.57</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-19.82</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-20.7</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-18.7</v>
-      </c>
-      <c r="E41" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-2.3</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-0.39</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-19.66</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-18.94</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-40.24</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-40.3</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-16.1</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-15.24</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-19.79</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-17.83</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-6.38</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-7.14</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-25.29</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-21.6</v>
-      </c>
-      <c r="E48" s="8">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-39.06</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-39.24</v>
-      </c>
-      <c r="E49" s="9">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-29.21</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-28.04</v>
-      </c>
-      <c r="E50" s="8">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-33.39</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-32.2</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-40.71</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-37.18</v>
-      </c>
-      <c r="E52" s="8">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1137</v>
-      </c>
-      <c r="D53" s="7">
-        <v>1135.9</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2695</v>
-      </c>
-      <c r="D54" s="7">
-        <v>2722.6</v>
-      </c>
-      <c r="E54" s="8">
-        <v>27.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1287</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1318.4</v>
-      </c>
-      <c r="E55" s="8">
-        <v>31.4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>1763</v>
-      </c>
-      <c r="D56" s="7">
-        <v>1748.7</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-14.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>185.96</v>
-      </c>
-      <c r="D57" s="7">
-        <v>195.15</v>
-      </c>
-      <c r="E57" s="8">
-        <v>9.19</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>350</v>
-      </c>
-      <c r="D58" s="7">
-        <v>349</v>
-      </c>
-      <c r="E58" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>572.2</v>
-      </c>
-      <c r="D59" s="7">
-        <v>581.6</v>
-      </c>
-      <c r="E59" s="8">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>184.91</v>
-      </c>
-      <c r="D60" s="7">
-        <v>188.21</v>
-      </c>
-      <c r="E60" s="8">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>65.91</v>
-      </c>
-      <c r="D61" s="7">
-        <v>65.98</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>88</v>
-      </c>
-      <c r="D62" s="7">
-        <v>77</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>77</v>
-      </c>
-      <c r="D63" s="7">
-        <v>88</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>26.16</v>
-      </c>
-      <c r="D64" s="7">
-        <v>25.97</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>39.33</v>
-      </c>
-      <c r="D65" s="7">
-        <v>41.48</v>
-      </c>
-      <c r="E65" s="8">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>49.46</v>
-      </c>
-      <c r="D66" s="7">
-        <v>53.82</v>
-      </c>
-      <c r="E66" s="8">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>51.2</v>
-      </c>
-      <c r="D67" s="7">
-        <v>49.34</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>35.36</v>
-      </c>
-      <c r="D68" s="7">
-        <v>46.16</v>
-      </c>
-      <c r="E68" s="8">
-        <v>10.8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>33.29</v>
-      </c>
-      <c r="D69" s="7">
-        <v>32.86</v>
-      </c>
-      <c r="E69" s="9">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>38.46</v>
-      </c>
-      <c r="D70" s="7">
-        <v>43.21</v>
-      </c>
-      <c r="E70" s="8">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>50.87</v>
-      </c>
-      <c r="D71" s="7">
-        <v>55.96</v>
-      </c>
-      <c r="E71" s="8">
-        <v>5.09</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>34.88</v>
-      </c>
-      <c r="D72" s="7">
-        <v>35.29</v>
-      </c>
-      <c r="E72" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="B84" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="7">
-        <v>-42.14</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-51.5</v>
-      </c>
-      <c r="E73" s="9">
-        <v>-9.359999999999999</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>-21.59</v>
-      </c>
-      <c r="D74" s="7">
-        <v>-5.08</v>
-      </c>
-      <c r="E74" s="8">
-        <v>16.51</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="7">
-        <v>-30.42</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-18.03</v>
-      </c>
-      <c r="E75" s="8">
-        <v>12.39</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>21.72</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-37.7</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-59.42</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-24.29</v>
-      </c>
-      <c r="D77" s="7">
-        <v>87.25</v>
-      </c>
-      <c r="E77" s="8">
-        <v>111.54</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>31.38</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-24.76</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-56.14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-81.78</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-75.33</v>
-      </c>
-      <c r="E79" s="8">
-        <v>6.45</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>-47.18</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-14.84</v>
-      </c>
-      <c r="E80" s="8">
-        <v>32.34</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-41.1</v>
-      </c>
-      <c r="D81" s="7">
+      <c r="C84" s="5">
         <v>53.83</v>
       </c>
-      <c r="E81" s="8">
-        <v>94.93000000000001</v>
+      <c r="D84" s="5">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="E84" s="7">
+        <v>-44.61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3475,60 +3447,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>78</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>48.16</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>42.7</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>42.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="12">
-        <v>-5</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-13.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-2.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-13</v>
+      </c>
+      <c r="H2" s="10">
         <v>55.4</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3630,61 +3602,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.5418999999999999</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1719</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1063</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0179</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.0236</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0438</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.07290000000000001</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.1245</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.167</v>
+      <c r="A2" s="13">
+        <v>0.5159</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1721</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1089</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0167</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.0235</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0458</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.07049999999999999</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.124</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.1678</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.7 → 46.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>26.7</t>
+  </si>
+  <si>
+    <t>46.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,14 +407,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -902,10 +930,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1137.4</v>
+        <v>1187.2</v>
       </c>
       <c r="D2">
-        <v>0.13</v>
+        <v>4.38</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,46 +942,46 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-40.22</v>
+        <v>-37.6</v>
       </c>
       <c r="H2">
-        <v>1.11</v>
+        <v>5.54</v>
       </c>
       <c r="I2">
-        <v>0.65</v>
+        <v>4.78</v>
       </c>
       <c r="J2">
-        <v>-7.17</v>
+        <v>-3.21</v>
       </c>
       <c r="K2">
-        <v>-17.18</v>
+        <v>-13.83</v>
       </c>
       <c r="L2">
-        <v>-39.33</v>
+        <v>-36.15</v>
       </c>
       <c r="M2">
-        <v>-12.4</v>
+        <v>-11.64</v>
       </c>
       <c r="N2">
         <v>34</v>
       </c>
       <c r="O2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="P2">
-        <v>1133.64</v>
+        <v>1144.48</v>
       </c>
       <c r="Q2">
-        <v>1191.94</v>
+        <v>1189.68</v>
       </c>
       <c r="R2">
-        <v>1256.73</v>
+        <v>1252.59</v>
       </c>
       <c r="S2">
-        <v>1412.3</v>
+        <v>1409.66</v>
       </c>
       <c r="T2">
-        <v>-19.46</v>
+        <v>-15.78</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +996,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>26.74</v>
+        <v>46.68</v>
       </c>
       <c r="Z2">
-        <v>-37.29</v>
+        <v>-32.34</v>
       </c>
       <c r="AA2">
-        <v>-34.18</v>
+        <v>-33.81</v>
       </c>
       <c r="AB2">
-        <v>-3.11</v>
+        <v>1.47</v>
       </c>
       <c r="AC2">
-        <v>32.36</v>
+        <v>56.4</v>
       </c>
       <c r="AD2">
-        <v>21.62</v>
+        <v>36.46</v>
       </c>
       <c r="AE2">
-        <v>23.21</v>
+        <v>26.09</v>
       </c>
       <c r="AF2">
-        <v>-20.78</v>
+        <v>188.74</v>
       </c>
       <c r="AG2">
-        <v>1286.75</v>
+        <v>1282.55</v>
       </c>
       <c r="AH2">
-        <v>1097.13</v>
+        <v>1096.8</v>
       </c>
       <c r="AI2">
         <v>1203.99</v>
@@ -1004,7 +1032,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>51.38</v>
+        <v>47.24</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1043,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2700</v>
+        <v>2692</v>
       </c>
       <c r="D3">
-        <v>-0.83</v>
+        <v>-0.3</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1055,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-15.94</v>
+        <v>-16.19</v>
       </c>
       <c r="H3">
-        <v>53.58</v>
+        <v>53.13</v>
       </c>
       <c r="I3">
-        <v>4.01</v>
+        <v>2.19</v>
       </c>
       <c r="J3">
         <v>-7.81</v>
       </c>
       <c r="K3">
-        <v>-14.32</v>
+        <v>-14.83</v>
       </c>
       <c r="L3">
-        <v>5.89</v>
+        <v>6.56</v>
       </c>
       <c r="M3">
-        <v>10.89</v>
+        <v>10.82</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="P3">
-        <v>2676.4</v>
+        <v>2687.92</v>
       </c>
       <c r="Q3">
-        <v>2834.2</v>
+        <v>2822.64</v>
       </c>
       <c r="R3">
-        <v>2935.37</v>
+        <v>2928.21</v>
       </c>
       <c r="S3">
-        <v>2592.91</v>
+        <v>2595.36</v>
       </c>
       <c r="T3">
-        <v>4.13</v>
+        <v>3.72</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,34 +1109,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>40.22</v>
+        <v>39.76</v>
       </c>
       <c r="Z3">
-        <v>-81.73</v>
+        <v>-80.25</v>
       </c>
       <c r="AA3">
-        <v>-68.56</v>
+        <v>-70.90000000000001</v>
       </c>
       <c r="AB3">
-        <v>-13.17</v>
+        <v>-9.35</v>
       </c>
       <c r="AC3">
-        <v>48.8</v>
+        <v>49.57</v>
       </c>
       <c r="AD3">
-        <v>37.2</v>
+        <v>45.4</v>
       </c>
       <c r="AE3">
-        <v>84.40000000000001</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="AF3">
-        <v>-44.58</v>
+        <v>-41.94</v>
       </c>
       <c r="AG3">
-        <v>3104.54</v>
+        <v>3096.7</v>
       </c>
       <c r="AH3">
-        <v>2563.86</v>
+        <v>2548.58</v>
       </c>
       <c r="AI3">
         <v>2899.05</v>
@@ -1117,7 +1145,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>47.48</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1156,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1307.1</v>
+        <v>1302</v>
       </c>
       <c r="D4">
-        <v>-0.86</v>
+        <v>-0.39</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,25 +1168,25 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.54</v>
+        <v>-18.85</v>
       </c>
       <c r="H4">
-        <v>69.14</v>
+        <v>68.48</v>
       </c>
       <c r="I4">
-        <v>5.78</v>
+        <v>3.68</v>
       </c>
       <c r="J4">
-        <v>4.15</v>
+        <v>2.5</v>
       </c>
       <c r="K4">
-        <v>-15.33</v>
+        <v>-14</v>
       </c>
       <c r="L4">
-        <v>22.81</v>
+        <v>23.85</v>
       </c>
       <c r="M4">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="N4">
         <v>77</v>
@@ -1167,19 +1195,19 @@
         <v>69</v>
       </c>
       <c r="P4">
-        <v>1288.46</v>
+        <v>1297.7</v>
       </c>
       <c r="Q4">
-        <v>1287.97</v>
+        <v>1289.36</v>
       </c>
       <c r="R4">
-        <v>1302.2</v>
+        <v>1300.64</v>
       </c>
       <c r="S4">
-        <v>1212.34</v>
+        <v>1213.84</v>
       </c>
       <c r="T4">
-        <v>7.82</v>
+        <v>7.26</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1194,34 +1222,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>52.08</v>
+        <v>51.27</v>
       </c>
       <c r="Z4">
-        <v>-3.18</v>
+        <v>-1.96</v>
       </c>
       <c r="AA4">
-        <v>-8.24</v>
+        <v>-6.98</v>
       </c>
       <c r="AB4">
-        <v>5.06</v>
+        <v>5.02</v>
       </c>
       <c r="AC4">
-        <v>69.42</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="AD4">
-        <v>58.52</v>
+        <v>67.78</v>
       </c>
       <c r="AE4">
-        <v>42.99</v>
+        <v>41.3</v>
       </c>
       <c r="AF4">
-        <v>-56.33</v>
+        <v>-56.58</v>
       </c>
       <c r="AG4">
-        <v>1345.53</v>
+        <v>1346.87</v>
       </c>
       <c r="AH4">
-        <v>1230.41</v>
+        <v>1231.85</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1230,7 +1258,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>17.15</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1269,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1743.2</v>
+        <v>1750.8</v>
       </c>
       <c r="D5">
-        <v>-0.31</v>
+        <v>0.44</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,46 +1281,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.43</v>
+        <v>-7.03</v>
       </c>
       <c r="H5">
-        <v>34.29</v>
+        <v>34.87</v>
       </c>
       <c r="I5">
-        <v>2.06</v>
+        <v>-0.58</v>
       </c>
       <c r="J5">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="K5">
-        <v>-4.56</v>
+        <v>-4.71</v>
       </c>
       <c r="L5">
-        <v>24.2</v>
+        <v>22.28</v>
       </c>
       <c r="M5">
-        <v>17.21</v>
+        <v>17.31</v>
       </c>
       <c r="N5">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>1753.98</v>
+        <v>1751.94</v>
       </c>
       <c r="Q5">
-        <v>1770.61</v>
+        <v>1771.24</v>
       </c>
       <c r="R5">
-        <v>1725.95</v>
+        <v>1726.97</v>
       </c>
       <c r="S5">
-        <v>1638.13</v>
+        <v>1639.64</v>
       </c>
       <c r="T5">
-        <v>6.41</v>
+        <v>6.78</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1335,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>48.6</v>
+        <v>49.72</v>
       </c>
       <c r="Z5">
-        <v>2.84</v>
+        <v>2.21</v>
       </c>
       <c r="AA5">
-        <v>8.07</v>
+        <v>6.9</v>
       </c>
       <c r="AB5">
-        <v>-5.23</v>
+        <v>-4.68</v>
       </c>
       <c r="AC5">
-        <v>34.27</v>
+        <v>31.76</v>
       </c>
       <c r="AD5">
-        <v>36.96</v>
+        <v>34.32</v>
       </c>
       <c r="AE5">
-        <v>46.03</v>
+        <v>44.6</v>
       </c>
       <c r="AF5">
-        <v>-21.7</v>
+        <v>-56.58</v>
       </c>
       <c r="AG5">
-        <v>1832.18</v>
+        <v>1831.67</v>
       </c>
       <c r="AH5">
-        <v>1709.04</v>
+        <v>1710.8</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1343,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>31.85</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1382,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>196.5</v>
+        <v>195.85</v>
       </c>
       <c r="D6">
-        <v>0.6899999999999999</v>
+        <v>-0.33</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,46 +1394,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-21.06</v>
+        <v>-21.32</v>
       </c>
       <c r="H6">
-        <v>47.79</v>
+        <v>47.3</v>
       </c>
       <c r="I6">
-        <v>4.52</v>
+        <v>3.62</v>
       </c>
       <c r="J6">
-        <v>-2.72</v>
+        <v>-3.21</v>
       </c>
       <c r="K6">
-        <v>-9.27</v>
+        <v>-8.67</v>
       </c>
       <c r="L6">
-        <v>31.26</v>
+        <v>26.82</v>
       </c>
       <c r="M6">
-        <v>51.59</v>
+        <v>51.45</v>
       </c>
       <c r="N6">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P6">
-        <v>190.5</v>
+        <v>191.87</v>
       </c>
       <c r="Q6">
-        <v>198.33</v>
+        <v>197.82</v>
       </c>
       <c r="R6">
-        <v>203.59</v>
+        <v>203.32</v>
       </c>
       <c r="S6">
-        <v>190.37</v>
+        <v>190.64</v>
       </c>
       <c r="T6">
-        <v>3.22</v>
+        <v>2.73</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1448,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>47.55</v>
+        <v>46.92</v>
       </c>
       <c r="Z6">
-        <v>-3.98</v>
+        <v>-3.59</v>
       </c>
       <c r="AA6">
-        <v>-3.69</v>
+        <v>-3.67</v>
       </c>
       <c r="AB6">
-        <v>-0.29</v>
+        <v>0.08</v>
       </c>
       <c r="AC6">
-        <v>57.72</v>
+        <v>86.45</v>
       </c>
       <c r="AD6">
-        <v>29.42</v>
+        <v>57.13</v>
       </c>
       <c r="AE6">
-        <v>6.69</v>
+        <v>6.55</v>
       </c>
       <c r="AF6">
-        <v>-29.94</v>
+        <v>-25.18</v>
       </c>
       <c r="AG6">
-        <v>212.22</v>
+        <v>211.28</v>
       </c>
       <c r="AH6">
-        <v>184.44</v>
+        <v>184.37</v>
       </c>
       <c r="AI6">
         <v>204.13</v>
@@ -1456,7 +1484,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>35.28</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1495,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>350.9</v>
+        <v>360</v>
       </c>
       <c r="D7">
-        <v>0.54</v>
+        <v>2.59</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1479,46 +1507,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-38.91</v>
+        <v>-37.32</v>
       </c>
       <c r="H7">
-        <v>2.9</v>
+        <v>5.57</v>
       </c>
       <c r="I7">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="J7">
-        <v>-8.08</v>
+        <v>-5.52</v>
       </c>
       <c r="K7">
-        <v>-19.07</v>
+        <v>-17.9</v>
       </c>
       <c r="L7">
-        <v>-38.05</v>
+        <v>-36.17</v>
       </c>
       <c r="M7">
-        <v>-2.35</v>
+        <v>-1.85</v>
       </c>
       <c r="N7">
         <v>12</v>
       </c>
       <c r="O7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P7">
-        <v>349.88</v>
+        <v>351.58</v>
       </c>
       <c r="Q7">
-        <v>368.08</v>
+        <v>366.91</v>
       </c>
       <c r="R7">
-        <v>393.5</v>
+        <v>391.8</v>
       </c>
       <c r="S7">
-        <v>446.01</v>
+        <v>445.06</v>
       </c>
       <c r="T7">
-        <v>-21.32</v>
+        <v>-19.11</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1561,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>34.6</v>
+        <v>42.33</v>
       </c>
       <c r="Z7">
-        <v>-13.5</v>
+        <v>-12.3</v>
       </c>
       <c r="AA7">
-        <v>-12.87</v>
+        <v>-12.76</v>
       </c>
       <c r="AB7">
-        <v>-0.63</v>
+        <v>0.46</v>
       </c>
       <c r="AC7">
-        <v>70.33</v>
+        <v>86.83</v>
       </c>
       <c r="AD7">
-        <v>57.33</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="AE7">
-        <v>9.49</v>
+        <v>10.07</v>
       </c>
       <c r="AF7">
-        <v>52.85</v>
+        <v>70.44</v>
       </c>
       <c r="AG7">
-        <v>401.48</v>
+        <v>399.71</v>
       </c>
       <c r="AH7">
-        <v>334.67</v>
+        <v>334.12</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1569,7 +1597,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>54.58</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1608,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>576.8</v>
+        <v>579.35</v>
       </c>
       <c r="D8">
-        <v>-0.83</v>
+        <v>0.44</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1620,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-28.64</v>
+        <v>-28.32</v>
       </c>
       <c r="H8">
-        <v>23.32</v>
+        <v>23.86</v>
       </c>
       <c r="I8">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="J8">
-        <v>-0.58</v>
+        <v>-1.22</v>
       </c>
       <c r="K8">
-        <v>-18.5</v>
+        <v>-18.01</v>
       </c>
       <c r="L8">
-        <v>-8.130000000000001</v>
+        <v>-7.32</v>
       </c>
       <c r="M8">
-        <v>-16.78</v>
+        <v>-16.7</v>
       </c>
       <c r="N8">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O8">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P8">
-        <v>571.45</v>
+        <v>574.63</v>
       </c>
       <c r="Q8">
-        <v>594.73</v>
+        <v>594.34</v>
       </c>
       <c r="R8">
-        <v>618.03</v>
+        <v>616.41</v>
       </c>
       <c r="S8">
-        <v>614.54</v>
+        <v>614.62</v>
       </c>
       <c r="T8">
-        <v>-6.14</v>
+        <v>-5.74</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,34 +1674,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>41.45</v>
+        <v>42.79</v>
       </c>
       <c r="Z8">
-        <v>-13.92</v>
+        <v>-12.99</v>
       </c>
       <c r="AA8">
-        <v>-13.97</v>
+        <v>-13.77</v>
       </c>
       <c r="AB8">
-        <v>0.05</v>
+        <v>0.78</v>
       </c>
       <c r="AC8">
-        <v>61.11</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="AD8">
-        <v>37.89</v>
+        <v>60.81</v>
       </c>
       <c r="AE8">
-        <v>16.4</v>
+        <v>16.07</v>
       </c>
       <c r="AF8">
-        <v>-85.95999999999999</v>
+        <v>-86.2</v>
       </c>
       <c r="AG8">
-        <v>647.8099999999999</v>
+        <v>647.78</v>
       </c>
       <c r="AH8">
-        <v>541.64</v>
+        <v>540.91</v>
       </c>
       <c r="AI8">
         <v>617.98</v>
@@ -1682,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>33.3</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1721,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>190.54</v>
+        <v>187.3</v>
       </c>
       <c r="D9">
-        <v>1.24</v>
+        <v>-1.7</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1733,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-31.36</v>
+        <v>-32.53</v>
       </c>
       <c r="H9">
-        <v>10.59</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I9">
-        <v>4.23</v>
+        <v>2.81</v>
       </c>
       <c r="J9">
-        <v>4.04</v>
+        <v>2.95</v>
       </c>
       <c r="K9">
-        <v>0.37</v>
+        <v>-0.72</v>
       </c>
       <c r="L9">
-        <v>-29.15</v>
+        <v>-30.29</v>
       </c>
       <c r="M9">
-        <v>-7.05</v>
+        <v>-7.38</v>
       </c>
       <c r="N9">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O9">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P9">
-        <v>185.84</v>
+        <v>186.87</v>
       </c>
       <c r="Q9">
-        <v>183.33</v>
+        <v>183.49</v>
       </c>
       <c r="R9">
-        <v>188.36</v>
+        <v>188.24</v>
       </c>
       <c r="S9">
-        <v>194.08</v>
+        <v>193.83</v>
       </c>
       <c r="T9">
-        <v>-1.82</v>
+        <v>-3.37</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,34 +1787,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>59.17</v>
+        <v>53.34</v>
       </c>
       <c r="Z9">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>-1.46</v>
+        <v>-1.17</v>
       </c>
       <c r="AB9">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC9">
-        <v>95.67</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="AD9">
-        <v>86.65000000000001</v>
+        <v>92.16</v>
       </c>
       <c r="AE9">
         <v>5.53</v>
       </c>
       <c r="AF9">
-        <v>97.11</v>
+        <v>1.78</v>
       </c>
       <c r="AG9">
-        <v>191.28</v>
+        <v>191.63</v>
       </c>
       <c r="AH9">
-        <v>175.39</v>
+        <v>175.36</v>
       </c>
       <c r="AI9">
         <v>176.41</v>
@@ -1795,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>25.11</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1834,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>65.34</v>
+        <v>65.16</v>
       </c>
       <c r="D10">
-        <v>-0.97</v>
+        <v>-0.28</v>
       </c>
       <c r="E10">
         <v>101.33</v>
@@ -1818,46 +1846,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-35.52</v>
+        <v>-35.7</v>
       </c>
       <c r="H10">
-        <v>10.22</v>
+        <v>9.92</v>
       </c>
       <c r="I10">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="J10">
-        <v>-7.23</v>
+        <v>-6.57</v>
       </c>
       <c r="K10">
-        <v>-18.9</v>
+        <v>-18.78</v>
       </c>
       <c r="L10">
-        <v>-37.79</v>
+        <v>-31.47</v>
       </c>
       <c r="M10">
-        <v>-4.58</v>
+        <v>-4.63</v>
       </c>
       <c r="N10">
         <v>23</v>
       </c>
       <c r="O10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P10">
-        <v>65.23999999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="Q10">
-        <v>68.22</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="R10">
-        <v>71.81</v>
+        <v>71.56</v>
       </c>
       <c r="S10">
-        <v>78.68000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="T10">
-        <v>-16.95</v>
+        <v>-17.01</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,34 +1900,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>33.2</v>
+        <v>32.61</v>
       </c>
       <c r="Z10">
-        <v>-2.02</v>
+        <v>-1.98</v>
       </c>
       <c r="AA10">
-        <v>-1.93</v>
+        <v>-1.94</v>
       </c>
       <c r="AB10">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AC10">
-        <v>72.43000000000001</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="AD10">
-        <v>56.29</v>
+        <v>70.19</v>
       </c>
       <c r="AE10">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AF10">
-        <v>9.220000000000001</v>
+        <v>18.77</v>
       </c>
       <c r="AG10">
-        <v>73.52</v>
+        <v>73.22</v>
       </c>
       <c r="AH10">
-        <v>62.93</v>
+        <v>62.64</v>
       </c>
       <c r="AI10">
         <v>70.83</v>
@@ -1908,7 +1936,7 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>39.21</v>
+        <v>36.4</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2077,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,12 +2097,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2082,1346 +2145,1295 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-7.17</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-3.21</v>
+      </c>
+      <c r="E7" s="7">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>4.15</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-2.72</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-3.21</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-8.08</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.52</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-1.22</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>4.04</v>
+      </c>
+      <c r="D13" s="6">
+        <v>2.95</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-7.23</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-6.57</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.65</v>
+      </c>
+      <c r="D15" s="6">
+        <v>4.78</v>
+      </c>
+      <c r="E15" s="7">
+        <v>4.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>4.01</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2.19</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>5.78</v>
+      </c>
+      <c r="D17" s="6">
+        <v>3.68</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.06</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4.52</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3.62</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2.42</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2.82</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>4.23</v>
+      </c>
+      <c r="D22" s="6">
+        <v>2.81</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>1.54</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2.15</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-39.33</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-36.15</v>
+      </c>
+      <c r="E24" s="7">
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>5.89</v>
+      </c>
+      <c r="D25" s="6">
+        <v>6.56</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>22.81</v>
+      </c>
+      <c r="D26" s="6">
+        <v>23.85</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>24.2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>22.28</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>31.26</v>
+      </c>
+      <c r="D28" s="6">
+        <v>26.82</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-38.05</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-36.17</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-7.32</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-29.15</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-30.29</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-37.79</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-31.47</v>
+      </c>
+      <c r="E32" s="7">
+        <v>6.32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-17.18</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-13.83</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-14.32</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-14.83</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-15.33</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-14</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-4.56</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-4.71</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-9.27</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-8.67</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-19.07</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-17.9</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-18.5</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-18.01</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-0.72</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-18.9</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-18.78</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-40.22</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-37.6</v>
+      </c>
+      <c r="E42" s="7">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-15.94</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-16.19</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-18.54</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-18.85</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-7.43</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-7.03</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-21.06</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-21.32</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-38.91</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-37.32</v>
+      </c>
+      <c r="E47" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-28.64</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-28.32</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-31.36</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-32.53</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-35.52</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-35.7</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>1137.4</v>
+      </c>
+      <c r="D51" s="6">
+        <v>1187.2</v>
+      </c>
+      <c r="E51" s="7">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>2700</v>
+      </c>
+      <c r="D52" s="6">
+        <v>2692</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>1307.1</v>
+      </c>
+      <c r="D53" s="6">
+        <v>1302</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1743.2</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1750.8</v>
+      </c>
+      <c r="E54" s="7">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>196.5</v>
+      </c>
+      <c r="D55" s="6">
+        <v>195.85</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>350.9</v>
+      </c>
+      <c r="D56" s="6">
+        <v>360</v>
+      </c>
+      <c r="E56" s="7">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>576.8</v>
+      </c>
+      <c r="D57" s="6">
+        <v>579.35</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>190.54</v>
+      </c>
+      <c r="D58" s="6">
+        <v>187.3</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-3.24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>65.34</v>
+      </c>
+      <c r="D59" s="6">
+        <v>65.16</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="6">
+        <v>88</v>
+      </c>
+      <c r="D60" s="6">
+        <v>99</v>
+      </c>
+      <c r="E60" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C61" s="6">
+        <v>99</v>
+      </c>
+      <c r="D61" s="6">
+        <v>88</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="6">
+        <v>45</v>
+      </c>
+      <c r="D62" s="6">
         <v>55</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="E62" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>55</v>
+      </c>
+      <c r="D63" s="6">
+        <v>45</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-8.869999999999999</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-7.17</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>26.74</v>
+      </c>
+      <c r="D64" s="6">
+        <v>46.68</v>
+      </c>
+      <c r="E64" s="7">
+        <v>19.94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-11.03</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-7.81</v>
-      </c>
-      <c r="E8" s="6">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>40.22</v>
+      </c>
+      <c r="D65" s="6">
+        <v>39.76</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>2.9</v>
-      </c>
-      <c r="D9" s="5">
-        <v>4.15</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>52.08</v>
+      </c>
+      <c r="D66" s="6">
+        <v>51.27</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-0.9</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1.72</v>
-      </c>
-      <c r="E10" s="6">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>48.6</v>
+      </c>
+      <c r="D67" s="6">
+        <v>49.72</v>
+      </c>
+      <c r="E67" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-7.06</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-2.72</v>
-      </c>
-      <c r="E11" s="6">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>47.55</v>
+      </c>
+      <c r="D68" s="6">
+        <v>46.92</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-10.94</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-8.08</v>
-      </c>
-      <c r="E12" s="6">
-        <v>2.86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>34.6</v>
+      </c>
+      <c r="D69" s="6">
+        <v>42.33</v>
+      </c>
+      <c r="E69" s="7">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-2.22</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-0.58</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>41.45</v>
+      </c>
+      <c r="D70" s="6">
+        <v>42.79</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.72</v>
-      </c>
-      <c r="D14" s="5">
-        <v>4.04</v>
-      </c>
-      <c r="E14" s="6">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>59.17</v>
+      </c>
+      <c r="D71" s="6">
+        <v>53.34</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-5.83</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-7.23</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>33.2</v>
+      </c>
+      <c r="D72" s="6">
+        <v>32.61</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.54</v>
-      </c>
-      <c r="D16" s="5">
-        <v>0.65</v>
-      </c>
-      <c r="E16" s="6">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-20.78</v>
+      </c>
+      <c r="D73" s="6">
+        <v>188.74</v>
+      </c>
+      <c r="E73" s="7">
+        <v>209.52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.74</v>
-      </c>
-      <c r="D17" s="5">
-        <v>4.01</v>
-      </c>
-      <c r="E17" s="6">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-44.58</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-41.94</v>
+      </c>
+      <c r="E74" s="7">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.71</v>
-      </c>
-      <c r="D18" s="5">
-        <v>5.78</v>
-      </c>
-      <c r="E18" s="6">
-        <v>7.49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-56.33</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-56.58</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-0.08</v>
-      </c>
-      <c r="D19" s="5">
-        <v>2.06</v>
-      </c>
-      <c r="E19" s="6">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-21.7</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-56.58</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-34.88</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-0.91</v>
-      </c>
-      <c r="D20" s="5">
-        <v>4.52</v>
-      </c>
-      <c r="E20" s="6">
-        <v>5.43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-29.94</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-25.18</v>
+      </c>
+      <c r="E77" s="7">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-2.21</v>
-      </c>
-      <c r="D21" s="5">
-        <v>2.9</v>
-      </c>
-      <c r="E21" s="6">
-        <v>5.11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>52.85</v>
+      </c>
+      <c r="D78" s="6">
+        <v>70.44</v>
+      </c>
+      <c r="E78" s="7">
+        <v>17.59</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-0.05</v>
-      </c>
-      <c r="D22" s="5">
-        <v>2.6</v>
-      </c>
-      <c r="E22" s="6">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-85.95999999999999</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-86.2</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0.59</v>
-      </c>
-      <c r="D23" s="5">
-        <v>4.23</v>
-      </c>
-      <c r="E23" s="6">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>97.11</v>
+      </c>
+      <c r="D80" s="6">
+        <v>1.78</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-95.33</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-0.75</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1.54</v>
-      </c>
-      <c r="E24" s="6">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-39.06</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-39.33</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>7.14</v>
-      </c>
-      <c r="D26" s="5">
-        <v>5.89</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>25.38</v>
-      </c>
-      <c r="D27" s="5">
-        <v>22.81</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>25.83</v>
-      </c>
-      <c r="D28" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>31.05</v>
-      </c>
-      <c r="D29" s="5">
-        <v>31.26</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-38.02</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-38.05</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-7.31</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-29.81</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-29.15</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-40.64</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-37.79</v>
-      </c>
-      <c r="E33" s="6">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-17.88</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-17.18</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-13.58</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-14.32</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-15.24</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-15.33</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-4.4</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-4.56</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-10.88</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-9.27</v>
-      </c>
-      <c r="E38" s="6">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-19.82</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-19.07</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-18.7</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-18.5</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-0.39</v>
-      </c>
-      <c r="D41" s="5">
-        <v>0.37</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-18.94</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-18.9</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-40.3</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-40.22</v>
-      </c>
-      <c r="E43" s="6">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-15.24</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-15.94</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-17.83</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-18.54</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-7.14</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-7.43</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-21.6</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-21.06</v>
-      </c>
-      <c r="E47" s="6">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-39.24</v>
-      </c>
-      <c r="D48" s="5">
-        <v>-38.91</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="5">
-        <v>-28.04</v>
-      </c>
-      <c r="D49" s="5">
-        <v>-28.64</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="5">
-        <v>-32.2</v>
-      </c>
-      <c r="D50" s="5">
-        <v>-31.36</v>
-      </c>
-      <c r="E50" s="6">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5">
-        <v>-37.18</v>
-      </c>
-      <c r="D51" s="5">
-        <v>-35.52</v>
-      </c>
-      <c r="E51" s="6">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>1135.9</v>
-      </c>
-      <c r="D52" s="5">
-        <v>1137.4</v>
-      </c>
-      <c r="E52" s="6">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>2722.6</v>
-      </c>
-      <c r="D53" s="5">
-        <v>2700</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-22.6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>1318.4</v>
-      </c>
-      <c r="D54" s="5">
-        <v>1307.1</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-11.3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="5">
-        <v>1748.7</v>
-      </c>
-      <c r="D55" s="5">
-        <v>1743.2</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="5">
-        <v>195.15</v>
-      </c>
-      <c r="D56" s="5">
-        <v>196.5</v>
-      </c>
-      <c r="E56" s="6">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="5">
-        <v>349</v>
-      </c>
-      <c r="D57" s="5">
-        <v>350.9</v>
-      </c>
-      <c r="E57" s="6">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="5">
-        <v>581.6</v>
-      </c>
-      <c r="D58" s="5">
-        <v>576.8</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="5">
-        <v>188.21</v>
-      </c>
-      <c r="D59" s="5">
-        <v>190.54</v>
-      </c>
-      <c r="E59" s="6">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="5">
-        <v>65.98</v>
-      </c>
-      <c r="D60" s="5">
-        <v>65.34</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="5">
-        <v>99</v>
-      </c>
-      <c r="D61" s="5">
-        <v>88</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="5">
-        <v>88</v>
-      </c>
-      <c r="D62" s="5">
-        <v>99</v>
-      </c>
-      <c r="E62" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="5">
-        <v>23</v>
-      </c>
-      <c r="D63" s="5">
-        <v>12</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="5">
-        <v>55</v>
-      </c>
-      <c r="D64" s="5">
-        <v>45</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="5">
-        <v>45</v>
-      </c>
-      <c r="D65" s="5">
-        <v>55</v>
-      </c>
-      <c r="E65" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C66" s="5">
-        <v>12</v>
-      </c>
-      <c r="D66" s="5">
-        <v>23</v>
-      </c>
-      <c r="E66" s="6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="5">
-        <v>25.97</v>
-      </c>
-      <c r="D67" s="5">
-        <v>26.74</v>
-      </c>
-      <c r="E67" s="6">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="5">
-        <v>41.48</v>
-      </c>
-      <c r="D68" s="5">
-        <v>40.22</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="5">
-        <v>53.82</v>
-      </c>
-      <c r="D69" s="5">
-        <v>52.08</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="5">
-        <v>49.34</v>
-      </c>
-      <c r="D70" s="5">
-        <v>48.6</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="5">
-        <v>46.16</v>
-      </c>
-      <c r="D71" s="5">
-        <v>47.55</v>
-      </c>
-      <c r="E71" s="6">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="5">
-        <v>32.86</v>
-      </c>
-      <c r="D72" s="5">
-        <v>34.6</v>
-      </c>
-      <c r="E72" s="6">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="5">
-        <v>43.21</v>
-      </c>
-      <c r="D73" s="5">
-        <v>41.45</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="5">
-        <v>55.96</v>
-      </c>
-      <c r="D74" s="5">
-        <v>59.17</v>
-      </c>
-      <c r="E74" s="6">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" s="5">
-        <v>35.29</v>
-      </c>
-      <c r="D75" s="5">
-        <v>33.2</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B76" s="3" t="s">
+      <c r="B81" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="5">
-        <v>-51.5</v>
-      </c>
-      <c r="D76" s="5">
-        <v>-20.78</v>
-      </c>
-      <c r="E76" s="6">
-        <v>30.72</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="5">
-        <v>-5.08</v>
-      </c>
-      <c r="D77" s="5">
-        <v>-44.58</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-39.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="5">
-        <v>-18.03</v>
-      </c>
-      <c r="D78" s="5">
-        <v>-56.33</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-38.3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="5">
-        <v>-37.7</v>
-      </c>
-      <c r="D79" s="5">
-        <v>-21.7</v>
-      </c>
-      <c r="E79" s="6">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="5">
-        <v>87.25</v>
-      </c>
-      <c r="D80" s="5">
-        <v>-29.94</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-117.19</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="5">
-        <v>-24.76</v>
-      </c>
-      <c r="D81" s="5">
-        <v>52.85</v>
-      </c>
-      <c r="E81" s="6">
-        <v>77.61</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="5">
-        <v>-75.33</v>
-      </c>
-      <c r="D82" s="5">
-        <v>-85.95999999999999</v>
-      </c>
-      <c r="E82" s="7">
-        <v>-10.63</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="5">
-        <v>-14.84</v>
-      </c>
-      <c r="D83" s="5">
-        <v>97.11</v>
-      </c>
-      <c r="E83" s="6">
-        <v>111.95</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="5">
-        <v>53.83</v>
-      </c>
-      <c r="D84" s="5">
+      <c r="C81" s="6">
         <v>9.220000000000001</v>
       </c>
-      <c r="E84" s="7">
-        <v>-44.61</v>
+      <c r="D81" s="6">
+        <v>18.77</v>
+      </c>
+      <c r="E81" s="7">
+        <v>9.550000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3447,60 +3459,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>65</v>
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.16</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="10">
-        <v>42.6</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>45</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-2.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-13</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-2.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-12.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>55.4</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -3602,61 +3614,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="13">
-        <v>0.5159</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1721</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1089</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0167</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.0235</v>
-      </c>
-      <c r="F2" s="13">
-        <v>-0.0458</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.07049999999999999</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.124</v>
-      </c>
-      <c r="I2" s="13">
-        <v>-0.1678</v>
+      <c r="A2" s="14">
+        <v>0.5145000000000001</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1731</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1082</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0159</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.0185</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.0463</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.0738</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.1164</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.167</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,19 +193,31 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.7 → 46.7</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>49.7 → 52.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>26.7</t>
-  </si>
-  <si>
-    <t>46.7</t>
+    <t>49.7</t>
+  </si>
+  <si>
+    <t>52.0</t>
+  </si>
+  <si>
+    <t>53.3 → 43.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.3</t>
+  </si>
+  <si>
+    <t>43.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,10 +427,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +943,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1187.2</v>
+        <v>1167.8</v>
       </c>
       <c r="D2">
-        <v>4.38</v>
+        <v>-1.63</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -942,46 +955,46 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-37.6</v>
+        <v>-38.62</v>
       </c>
       <c r="H2">
-        <v>5.54</v>
+        <v>3.81</v>
       </c>
       <c r="I2">
-        <v>4.78</v>
+        <v>3.81</v>
       </c>
       <c r="J2">
-        <v>-3.21</v>
+        <v>-5.25</v>
       </c>
       <c r="K2">
-        <v>-13.83</v>
+        <v>-15.46</v>
       </c>
       <c r="L2">
-        <v>-36.15</v>
+        <v>-36.94</v>
       </c>
       <c r="M2">
-        <v>-11.64</v>
+        <v>-11.44</v>
       </c>
       <c r="N2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P2">
-        <v>1144.48</v>
+        <v>1153.06</v>
       </c>
       <c r="Q2">
-        <v>1189.68</v>
+        <v>1185.08</v>
       </c>
       <c r="R2">
-        <v>1252.59</v>
+        <v>1248.38</v>
       </c>
       <c r="S2">
-        <v>1409.66</v>
+        <v>1406.89</v>
       </c>
       <c r="T2">
-        <v>-15.78</v>
+        <v>-16.99</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -996,34 +1009,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>46.68</v>
+        <v>41.9</v>
       </c>
       <c r="Z2">
-        <v>-32.34</v>
+        <v>-29.64</v>
       </c>
       <c r="AA2">
-        <v>-33.81</v>
+        <v>-32.98</v>
       </c>
       <c r="AB2">
-        <v>1.47</v>
+        <v>3.33</v>
       </c>
       <c r="AC2">
-        <v>56.4</v>
+        <v>72.94</v>
       </c>
       <c r="AD2">
-        <v>36.46</v>
+        <v>53.9</v>
       </c>
       <c r="AE2">
-        <v>26.09</v>
+        <v>27.99</v>
       </c>
       <c r="AF2">
-        <v>188.74</v>
+        <v>-7.07</v>
       </c>
       <c r="AG2">
-        <v>1282.55</v>
+        <v>1272.29</v>
       </c>
       <c r="AH2">
-        <v>1096.8</v>
+        <v>1097.87</v>
       </c>
       <c r="AI2">
         <v>1203.99</v>
@@ -1032,7 +1045,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>47.24</v>
+        <v>45.08</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2692</v>
+        <v>2657.5</v>
       </c>
       <c r="D3">
-        <v>-0.3</v>
+        <v>-1.28</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1055,46 +1068,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-16.19</v>
+        <v>-17.27</v>
       </c>
       <c r="H3">
-        <v>53.13</v>
+        <v>51.17</v>
       </c>
       <c r="I3">
-        <v>2.19</v>
+        <v>1.05</v>
       </c>
       <c r="J3">
-        <v>-7.81</v>
+        <v>-9.09</v>
       </c>
       <c r="K3">
-        <v>-14.83</v>
+        <v>-16.52</v>
       </c>
       <c r="L3">
-        <v>6.56</v>
+        <v>5.63</v>
       </c>
       <c r="M3">
-        <v>10.82</v>
+        <v>11.16</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P3">
-        <v>2687.92</v>
+        <v>2693.42</v>
       </c>
       <c r="Q3">
-        <v>2822.64</v>
+        <v>2804.51</v>
       </c>
       <c r="R3">
-        <v>2928.21</v>
+        <v>2920.84</v>
       </c>
       <c r="S3">
-        <v>2595.36</v>
+        <v>2597.58</v>
       </c>
       <c r="T3">
-        <v>3.72</v>
+        <v>2.31</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1109,34 +1122,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.76</v>
+        <v>37.76</v>
       </c>
       <c r="Z3">
-        <v>-80.25</v>
+        <v>-80.93000000000001</v>
       </c>
       <c r="AA3">
-        <v>-70.90000000000001</v>
+        <v>-72.90000000000001</v>
       </c>
       <c r="AB3">
-        <v>-9.35</v>
+        <v>-8.02</v>
       </c>
       <c r="AC3">
-        <v>49.57</v>
+        <v>43</v>
       </c>
       <c r="AD3">
-        <v>45.4</v>
+        <v>47.12</v>
       </c>
       <c r="AE3">
-        <v>81.54000000000001</v>
+        <v>79.41</v>
       </c>
       <c r="AF3">
-        <v>-41.94</v>
+        <v>-41.71</v>
       </c>
       <c r="AG3">
-        <v>3096.7</v>
+        <v>3071.47</v>
       </c>
       <c r="AH3">
-        <v>2548.58</v>
+        <v>2537.56</v>
       </c>
       <c r="AI3">
         <v>2899.05</v>
@@ -1145,7 +1158,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>46.6</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1169,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1302</v>
+        <v>1295.2</v>
       </c>
       <c r="D4">
-        <v>-0.39</v>
+        <v>-0.52</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1168,46 +1181,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-18.85</v>
+        <v>-19.28</v>
       </c>
       <c r="H4">
-        <v>68.48</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I4">
-        <v>3.68</v>
+        <v>1.66</v>
       </c>
       <c r="J4">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="K4">
-        <v>-14</v>
+        <v>-15.35</v>
       </c>
       <c r="L4">
-        <v>23.85</v>
+        <v>25</v>
       </c>
       <c r="M4">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="N4">
         <v>77</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="P4">
-        <v>1297.7</v>
+        <v>1301.94</v>
       </c>
       <c r="Q4">
-        <v>1289.36</v>
+        <v>1287.39</v>
       </c>
       <c r="R4">
-        <v>1300.64</v>
+        <v>1299.11</v>
       </c>
       <c r="S4">
-        <v>1213.84</v>
+        <v>1215.28</v>
       </c>
       <c r="T4">
-        <v>7.26</v>
+        <v>6.58</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1222,34 +1235,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>51.27</v>
+        <v>50.16</v>
       </c>
       <c r="Z4">
-        <v>-1.96</v>
+        <v>-1.53</v>
       </c>
       <c r="AA4">
-        <v>-6.98</v>
+        <v>-5.89</v>
       </c>
       <c r="AB4">
-        <v>5.02</v>
+        <v>4.36</v>
       </c>
       <c r="AC4">
-        <v>72.70999999999999</v>
+        <v>63.75</v>
       </c>
       <c r="AD4">
-        <v>67.78</v>
+        <v>68.62</v>
       </c>
       <c r="AE4">
-        <v>41.3</v>
+        <v>40.37</v>
       </c>
       <c r="AF4">
-        <v>-56.58</v>
+        <v>-56.5</v>
       </c>
       <c r="AG4">
-        <v>1346.87</v>
+        <v>1340.96</v>
       </c>
       <c r="AH4">
-        <v>1231.85</v>
+        <v>1233.83</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1258,7 +1271,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>16.56</v>
+        <v>15.21</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1282,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1750.8</v>
+        <v>1766</v>
       </c>
       <c r="D5">
-        <v>0.44</v>
+        <v>0.87</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1281,46 +1294,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.03</v>
+        <v>-6.22</v>
       </c>
       <c r="H5">
-        <v>34.87</v>
+        <v>36.04</v>
       </c>
       <c r="I5">
-        <v>-0.58</v>
+        <v>0.68</v>
       </c>
       <c r="J5">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="K5">
-        <v>-4.71</v>
+        <v>-4.23</v>
       </c>
       <c r="L5">
-        <v>22.28</v>
+        <v>24.1</v>
       </c>
       <c r="M5">
-        <v>17.31</v>
+        <v>18.03</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1751.94</v>
+        <v>1754.34</v>
       </c>
       <c r="Q5">
-        <v>1771.24</v>
+        <v>1768.34</v>
       </c>
       <c r="R5">
-        <v>1726.97</v>
+        <v>1728.39</v>
       </c>
       <c r="S5">
-        <v>1639.64</v>
+        <v>1641.19</v>
       </c>
       <c r="T5">
-        <v>6.78</v>
+        <v>7.6</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1335,34 +1348,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.72</v>
+        <v>51.96</v>
       </c>
       <c r="Z5">
-        <v>2.21</v>
+        <v>2.91</v>
       </c>
       <c r="AA5">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="AB5">
-        <v>-4.68</v>
+        <v>-3.19</v>
       </c>
       <c r="AC5">
-        <v>31.76</v>
+        <v>37.58</v>
       </c>
       <c r="AD5">
-        <v>34.32</v>
+        <v>34.54</v>
       </c>
       <c r="AE5">
-        <v>44.6</v>
+        <v>44.19</v>
       </c>
       <c r="AF5">
-        <v>-56.58</v>
+        <v>-13.23</v>
       </c>
       <c r="AG5">
-        <v>1831.67</v>
+        <v>1823.44</v>
       </c>
       <c r="AH5">
-        <v>1710.8</v>
+        <v>1713.23</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1371,7 +1384,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>32.81</v>
+        <v>29.57</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,10 +1395,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>195.85</v>
+        <v>194.08</v>
       </c>
       <c r="D6">
-        <v>-0.33</v>
+        <v>-0.9</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1394,25 +1407,25 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-21.32</v>
+        <v>-22.03</v>
       </c>
       <c r="H6">
-        <v>47.3</v>
+        <v>45.97</v>
       </c>
       <c r="I6">
-        <v>3.62</v>
+        <v>4.4</v>
       </c>
       <c r="J6">
-        <v>-3.21</v>
+        <v>-5.75</v>
       </c>
       <c r="K6">
-        <v>-8.67</v>
+        <v>-11.77</v>
       </c>
       <c r="L6">
-        <v>26.82</v>
+        <v>25.29</v>
       </c>
       <c r="M6">
-        <v>51.45</v>
+        <v>50.71</v>
       </c>
       <c r="N6">
         <v>88</v>
@@ -1421,19 +1434,19 @@
         <v>72</v>
       </c>
       <c r="P6">
-        <v>191.87</v>
+        <v>193.51</v>
       </c>
       <c r="Q6">
-        <v>197.82</v>
+        <v>197.2</v>
       </c>
       <c r="R6">
-        <v>203.32</v>
+        <v>203.04</v>
       </c>
       <c r="S6">
-        <v>190.64</v>
+        <v>190.89</v>
       </c>
       <c r="T6">
-        <v>2.73</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1448,34 +1461,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>46.92</v>
+        <v>45.18</v>
       </c>
       <c r="Z6">
-        <v>-3.59</v>
+        <v>-3.39</v>
       </c>
       <c r="AA6">
-        <v>-3.67</v>
+        <v>-3.61</v>
       </c>
       <c r="AB6">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="AC6">
-        <v>86.45</v>
+        <v>84</v>
       </c>
       <c r="AD6">
-        <v>57.13</v>
+        <v>76.06</v>
       </c>
       <c r="AE6">
-        <v>6.55</v>
+        <v>6.41</v>
       </c>
       <c r="AF6">
-        <v>-25.18</v>
+        <v>-59.25</v>
       </c>
       <c r="AG6">
-        <v>211.28</v>
+        <v>210.09</v>
       </c>
       <c r="AH6">
-        <v>184.37</v>
+        <v>184.31</v>
       </c>
       <c r="AI6">
         <v>204.13</v>
@@ -1484,7 +1497,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>31.74</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1508,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>360</v>
+        <v>361.85</v>
       </c>
       <c r="D7">
-        <v>2.59</v>
+        <v>0.51</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1507,46 +1520,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-37.32</v>
+        <v>-37</v>
       </c>
       <c r="H7">
-        <v>5.57</v>
+        <v>6.11</v>
       </c>
       <c r="I7">
-        <v>2.42</v>
+        <v>3.98</v>
       </c>
       <c r="J7">
-        <v>-5.52</v>
+        <v>-5.58</v>
       </c>
       <c r="K7">
-        <v>-17.9</v>
+        <v>-17.35</v>
       </c>
       <c r="L7">
-        <v>-36.17</v>
+        <v>-35.48</v>
       </c>
       <c r="M7">
-        <v>-1.85</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N7">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P7">
-        <v>351.58</v>
+        <v>354.35</v>
       </c>
       <c r="Q7">
-        <v>366.91</v>
+        <v>365.59</v>
       </c>
       <c r="R7">
-        <v>391.8</v>
+        <v>390.3</v>
       </c>
       <c r="S7">
-        <v>445.06</v>
+        <v>444.13</v>
       </c>
       <c r="T7">
-        <v>-19.11</v>
+        <v>-18.53</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1561,34 +1574,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.33</v>
+        <v>43.79</v>
       </c>
       <c r="Z7">
-        <v>-12.3</v>
+        <v>-11.07</v>
       </c>
       <c r="AA7">
-        <v>-12.76</v>
+        <v>-12.42</v>
       </c>
       <c r="AB7">
-        <v>0.46</v>
+        <v>1.35</v>
       </c>
       <c r="AC7">
-        <v>86.83</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="AD7">
-        <v>70.65000000000001</v>
+        <v>84.39</v>
       </c>
       <c r="AE7">
-        <v>10.07</v>
+        <v>9.94</v>
       </c>
       <c r="AF7">
-        <v>70.44</v>
+        <v>-26</v>
       </c>
       <c r="AG7">
-        <v>399.71</v>
+        <v>396.85</v>
       </c>
       <c r="AH7">
-        <v>334.12</v>
+        <v>334.33</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1597,7 +1610,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>49.02</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1621,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>579.35</v>
+        <v>573.65</v>
       </c>
       <c r="D8">
-        <v>0.44</v>
+        <v>-0.98</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1620,46 +1633,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-28.32</v>
+        <v>-29.03</v>
       </c>
       <c r="H8">
-        <v>23.86</v>
+        <v>22.64</v>
       </c>
       <c r="I8">
-        <v>2.82</v>
+        <v>1.86</v>
       </c>
       <c r="J8">
-        <v>-1.22</v>
+        <v>-2.27</v>
       </c>
       <c r="K8">
-        <v>-18.01</v>
+        <v>-19.53</v>
       </c>
       <c r="L8">
-        <v>-7.32</v>
+        <v>-6.96</v>
       </c>
       <c r="M8">
-        <v>-16.7</v>
+        <v>-16.57</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="P8">
-        <v>574.63</v>
+        <v>576.72</v>
       </c>
       <c r="Q8">
-        <v>594.34</v>
+        <v>589.99</v>
       </c>
       <c r="R8">
-        <v>616.41</v>
+        <v>614.6799999999999</v>
       </c>
       <c r="S8">
-        <v>614.62</v>
+        <v>614.67</v>
       </c>
       <c r="T8">
-        <v>-5.74</v>
+        <v>-6.67</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1674,34 +1687,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>42.79</v>
+        <v>40.56</v>
       </c>
       <c r="Z8">
-        <v>-12.99</v>
+        <v>-12.57</v>
       </c>
       <c r="AA8">
-        <v>-13.77</v>
+        <v>-13.53</v>
       </c>
       <c r="AB8">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="AC8">
-        <v>81.98999999999999</v>
+        <v>79.59</v>
       </c>
       <c r="AD8">
-        <v>60.81</v>
+        <v>74.23</v>
       </c>
       <c r="AE8">
-        <v>16.07</v>
+        <v>15.64</v>
       </c>
       <c r="AF8">
-        <v>-86.2</v>
+        <v>-87.41</v>
       </c>
       <c r="AG8">
-        <v>647.78</v>
+        <v>634.02</v>
       </c>
       <c r="AH8">
-        <v>540.91</v>
+        <v>545.96</v>
       </c>
       <c r="AI8">
         <v>617.98</v>
@@ -1710,7 +1723,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.66</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1721,10 +1734,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>187.3</v>
+        <v>180.62</v>
       </c>
       <c r="D9">
-        <v>-1.7</v>
+        <v>-3.57</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1733,46 +1746,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-32.53</v>
+        <v>-34.94</v>
       </c>
       <c r="H9">
-        <v>8.710000000000001</v>
+        <v>4.83</v>
       </c>
       <c r="I9">
-        <v>2.81</v>
+        <v>-1.5</v>
       </c>
       <c r="J9">
-        <v>2.95</v>
+        <v>-1.86</v>
       </c>
       <c r="K9">
-        <v>-0.72</v>
+        <v>-4.62</v>
       </c>
       <c r="L9">
-        <v>-30.29</v>
+        <v>-32.77</v>
       </c>
       <c r="M9">
-        <v>-7.38</v>
+        <v>-8.08</v>
       </c>
       <c r="N9">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O9">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="P9">
-        <v>186.87</v>
+        <v>186.32</v>
       </c>
       <c r="Q9">
-        <v>183.49</v>
+        <v>183.18</v>
       </c>
       <c r="R9">
-        <v>188.24</v>
+        <v>187.9</v>
       </c>
       <c r="S9">
-        <v>193.83</v>
+        <v>193.53</v>
       </c>
       <c r="T9">
-        <v>-3.37</v>
+        <v>-6.67</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1787,34 +1800,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>53.34</v>
+        <v>43.77</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="AA9">
-        <v>-1.17</v>
+        <v>-1.01</v>
       </c>
       <c r="AB9">
-        <v>1.17</v>
+        <v>0.64</v>
       </c>
       <c r="AC9">
-        <v>93.18000000000001</v>
+        <v>75.16</v>
       </c>
       <c r="AD9">
-        <v>92.16</v>
+        <v>88</v>
       </c>
       <c r="AE9">
-        <v>5.53</v>
+        <v>5.75</v>
       </c>
       <c r="AF9">
-        <v>1.78</v>
+        <v>112.51</v>
       </c>
       <c r="AG9">
-        <v>191.63</v>
+        <v>191.24</v>
       </c>
       <c r="AH9">
-        <v>175.36</v>
+        <v>175.11</v>
       </c>
       <c r="AI9">
         <v>176.41</v>
@@ -1823,7 +1836,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>28.5</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1834,10 +1847,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>65.16</v>
+        <v>63.02</v>
       </c>
       <c r="D10">
-        <v>-0.28</v>
+        <v>-3.28</v>
       </c>
       <c r="E10">
         <v>101.33</v>
@@ -1846,46 +1859,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-35.7</v>
+        <v>-37.81</v>
       </c>
       <c r="H10">
-        <v>9.92</v>
+        <v>6.31</v>
       </c>
       <c r="I10">
-        <v>2.15</v>
+        <v>-3.31</v>
       </c>
       <c r="J10">
-        <v>-6.57</v>
+        <v>-11.29</v>
       </c>
       <c r="K10">
-        <v>-18.78</v>
+        <v>-21.26</v>
       </c>
       <c r="L10">
-        <v>-31.47</v>
+        <v>-33.57</v>
       </c>
       <c r="M10">
-        <v>-4.63</v>
+        <v>-5.01</v>
       </c>
       <c r="N10">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="O10">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="P10">
-        <v>65.51000000000001</v>
+        <v>65.08</v>
       </c>
       <c r="Q10">
-        <v>67.93000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="R10">
-        <v>71.56</v>
+        <v>71.28</v>
       </c>
       <c r="S10">
-        <v>78.52</v>
+        <v>78.34</v>
       </c>
       <c r="T10">
-        <v>-17.01</v>
+        <v>-19.56</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1900,34 +1913,34 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>32.61</v>
+        <v>26.59</v>
       </c>
       <c r="Z10">
-        <v>-1.98</v>
+        <v>-2.1</v>
       </c>
       <c r="AA10">
-        <v>-1.94</v>
+        <v>-1.97</v>
       </c>
       <c r="AB10">
-        <v>-0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="AC10">
-        <v>76.34999999999999</v>
+        <v>61.56</v>
       </c>
       <c r="AD10">
-        <v>70.19</v>
+        <v>70.11</v>
       </c>
       <c r="AE10">
-        <v>2.19</v>
+        <v>2.26</v>
       </c>
       <c r="AF10">
-        <v>18.77</v>
+        <v>-23.82</v>
       </c>
       <c r="AG10">
-        <v>73.22</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="AH10">
-        <v>62.64</v>
+        <v>62.09</v>
       </c>
       <c r="AI10">
         <v>70.83</v>
@@ -1936,12 +1949,72 @@
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>36.4</v>
+        <v>37.06</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK10"/>
   <conditionalFormatting sqref="AF2:AF10">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D10">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I10">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J10">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K10">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L10">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1953,8 +2026,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D10">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N10">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1963,72 +2042,6 @@
         <color rgb="FFFFFFFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I10">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J10">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K10">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L10">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N10">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T10">
@@ -2040,26 +2053,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U10">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V10">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W10">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2077,7 +2090,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2117,7 +2130,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2135,1311 +2148,1348 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-7.17</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>-3.21</v>
       </c>
-      <c r="E7" s="7">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>-5.25</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-7.81</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-9.09</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>4.15</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C10" s="7">
         <v>2.5</v>
       </c>
-      <c r="E8" s="8">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D10" s="7">
+        <v>1.65</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>1.72</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C11" s="7">
         <v>1.57</v>
       </c>
-      <c r="E9" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D11" s="7">
+        <v>1.59</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-2.72</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C12" s="7">
         <v>-3.21</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-5.75</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-8.08</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C13" s="7">
         <v>-5.52</v>
       </c>
-      <c r="E11" s="7">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-5.58</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C14" s="7">
+        <v>-1.22</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-2.27</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2.95</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-1.86</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-4.81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-6.57</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-11.29</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-4.72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>4.78</v>
+      </c>
+      <c r="D17" s="7">
+        <v>3.81</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>2.19</v>
+      </c>
+      <c r="D18" s="7">
+        <v>1.05</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>3.68</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1.66</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
         <v>-0.58</v>
       </c>
-      <c r="D12" s="6">
-        <v>-1.22</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D20" s="7">
+        <v>0.68</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>3.62</v>
+      </c>
+      <c r="D21" s="7">
+        <v>4.4</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2.42</v>
+      </c>
+      <c r="D22" s="7">
+        <v>3.98</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>2.82</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.86</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>4.04</v>
-      </c>
-      <c r="D13" s="6">
-        <v>2.95</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>2.81</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-1.5</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-4.31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-7.23</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="7">
+        <v>2.15</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-3.31</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-5.46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="D15" s="6">
-        <v>4.78</v>
-      </c>
-      <c r="E15" s="7">
-        <v>4.13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-36.15</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-36.94</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>4.01</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2.19</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>6.56</v>
+      </c>
+      <c r="D27" s="7">
+        <v>5.63</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>5.78</v>
-      </c>
-      <c r="D17" s="6">
-        <v>3.68</v>
-      </c>
-      <c r="E17" s="8">
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>23.85</v>
+      </c>
+      <c r="D28" s="7">
+        <v>25</v>
+      </c>
+      <c r="E28" s="9">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>22.28</v>
+      </c>
+      <c r="D29" s="7">
+        <v>24.1</v>
+      </c>
+      <c r="E29" s="9">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>26.82</v>
+      </c>
+      <c r="D30" s="7">
+        <v>25.29</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-36.17</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-35.48</v>
+      </c>
+      <c r="E31" s="9">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-7.32</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-6.96</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-30.29</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-32.77</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-31.47</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-33.57</v>
+      </c>
+      <c r="E34" s="8">
         <v>-2.1</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-13.83</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-15.46</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.63</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-14.83</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-16.52</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-14</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-15.35</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2.06</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-4.71</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-4.23</v>
+      </c>
+      <c r="E38" s="9">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>4.52</v>
-      </c>
-      <c r="D19" s="6">
-        <v>3.62</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-8.67</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-11.77</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="D20" s="6">
-        <v>2.42</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-17.9</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-17.35</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="D21" s="6">
-        <v>2.82</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-18.01</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-19.53</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>4.23</v>
-      </c>
-      <c r="D22" s="6">
-        <v>2.81</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-0.72</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-4.62</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>1.54</v>
-      </c>
-      <c r="D23" s="6">
-        <v>2.15</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-18.78</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-21.26</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-37.6</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-38.62</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-16.19</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-17.27</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-18.85</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-19.28</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-7.03</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-6.22</v>
+      </c>
+      <c r="E47" s="9">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-21.32</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-22.03</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="7">
+        <v>-37.32</v>
+      </c>
+      <c r="D49" s="7">
+        <v>-37</v>
+      </c>
+      <c r="E49" s="9">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="7">
+        <v>-28.32</v>
+      </c>
+      <c r="D50" s="7">
+        <v>-29.03</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="7">
+        <v>-32.53</v>
+      </c>
+      <c r="D51" s="7">
+        <v>-34.94</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="7">
+        <v>-35.7</v>
+      </c>
+      <c r="D52" s="7">
+        <v>-37.81</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>1187.2</v>
+      </c>
+      <c r="D53" s="7">
+        <v>1167.8</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-19.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>2692</v>
+      </c>
+      <c r="D54" s="7">
+        <v>2657.5</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-34.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>1302</v>
+      </c>
+      <c r="D55" s="7">
+        <v>1295.2</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>1750.8</v>
+      </c>
+      <c r="D56" s="7">
+        <v>1766</v>
+      </c>
+      <c r="E56" s="9">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="7">
+        <v>195.85</v>
+      </c>
+      <c r="D57" s="7">
+        <v>194.08</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="7">
+        <v>360</v>
+      </c>
+      <c r="D58" s="7">
+        <v>361.85</v>
+      </c>
+      <c r="E58" s="9">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="7">
+        <v>579.35</v>
+      </c>
+      <c r="D59" s="7">
+        <v>573.65</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="7">
+        <v>187.3</v>
+      </c>
+      <c r="D60" s="7">
+        <v>180.62</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-6.68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="7">
+        <v>65.16</v>
+      </c>
+      <c r="D61" s="7">
+        <v>63.02</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="7">
+        <v>34</v>
+      </c>
+      <c r="D62" s="7">
+        <v>33</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="7">
+        <v>12</v>
+      </c>
+      <c r="D63" s="7">
+        <v>22</v>
+      </c>
+      <c r="E63" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="7">
+        <v>45</v>
+      </c>
+      <c r="D64" s="7">
+        <v>44</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="7">
+        <v>23</v>
+      </c>
+      <c r="D65" s="7">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-39.33</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-36.15</v>
-      </c>
-      <c r="E24" s="7">
-        <v>3.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="E65" s="8">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>46.68</v>
+      </c>
+      <c r="D66" s="7">
+        <v>41.9</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-4.78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>5.89</v>
-      </c>
-      <c r="D25" s="6">
-        <v>6.56</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="7">
+        <v>39.76</v>
+      </c>
+      <c r="D67" s="7">
+        <v>37.76</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>22.81</v>
-      </c>
-      <c r="D26" s="6">
-        <v>23.85</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="7">
+        <v>51.27</v>
+      </c>
+      <c r="D68" s="7">
+        <v>50.16</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>24.2</v>
-      </c>
-      <c r="D27" s="6">
-        <v>22.28</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="7">
+        <v>49.72</v>
+      </c>
+      <c r="D69" s="7">
+        <v>51.96</v>
+      </c>
+      <c r="E69" s="9">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>31.26</v>
-      </c>
-      <c r="D28" s="6">
-        <v>26.82</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-4.44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="7">
+        <v>46.92</v>
+      </c>
+      <c r="D70" s="7">
+        <v>45.18</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-1.74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-38.05</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-36.17</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="7">
+        <v>42.33</v>
+      </c>
+      <c r="D71" s="7">
+        <v>43.79</v>
+      </c>
+      <c r="E71" s="9">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-8.130000000000001</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-7.32</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="7">
+        <v>42.79</v>
+      </c>
+      <c r="D72" s="7">
+        <v>40.56</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-29.15</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-30.29</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="7">
+        <v>53.34</v>
+      </c>
+      <c r="D73" s="7">
+        <v>43.77</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-9.57</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-37.79</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-31.47</v>
-      </c>
-      <c r="E32" s="7">
-        <v>6.32</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="7">
+        <v>32.61</v>
+      </c>
+      <c r="D74" s="7">
+        <v>26.59</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-6.02</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-17.18</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-13.83</v>
-      </c>
-      <c r="E33" s="7">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B75" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="7">
+        <v>188.74</v>
+      </c>
+      <c r="D75" s="7">
+        <v>-7.07</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-195.81</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-14.32</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-14.83</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="7">
+        <v>-41.94</v>
+      </c>
+      <c r="D76" s="7">
+        <v>-41.71</v>
+      </c>
+      <c r="E76" s="9">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-15.33</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-14</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B77" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="7">
+        <v>-56.58</v>
+      </c>
+      <c r="D77" s="7">
+        <v>-56.5</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-4.56</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-4.71</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="7">
+        <v>-56.58</v>
+      </c>
+      <c r="D78" s="7">
+        <v>-13.23</v>
+      </c>
+      <c r="E78" s="9">
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-9.27</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-8.67</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="7">
+        <v>-25.18</v>
+      </c>
+      <c r="D79" s="7">
+        <v>-59.25</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-34.07</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-19.07</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-17.9</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="7">
+        <v>70.44</v>
+      </c>
+      <c r="D80" s="7">
+        <v>-26</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-96.44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-18.5</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-18.01</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="7">
+        <v>-86.2</v>
+      </c>
+      <c r="D81" s="7">
+        <v>-87.41</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>0.37</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-0.72</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C82" s="7">
+        <v>1.78</v>
+      </c>
+      <c r="D82" s="7">
+        <v>112.51</v>
+      </c>
+      <c r="E82" s="9">
+        <v>110.73</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-18.9</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-18.78</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-40.22</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-37.6</v>
-      </c>
-      <c r="E42" s="7">
-        <v>2.62</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-15.94</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-16.19</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-18.54</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-7.43</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-7.03</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-21.06</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-21.32</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-38.91</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-37.32</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-28.64</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-28.32</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-31.36</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-32.53</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-35.52</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-35.7</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>1137.4</v>
-      </c>
-      <c r="D51" s="6">
-        <v>1187.2</v>
-      </c>
-      <c r="E51" s="7">
-        <v>49.8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>2700</v>
-      </c>
-      <c r="D52" s="6">
-        <v>2692</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>1307.1</v>
-      </c>
-      <c r="D53" s="6">
-        <v>1302</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-5.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1743.2</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1750.8</v>
-      </c>
-      <c r="E54" s="7">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>196.5</v>
-      </c>
-      <c r="D55" s="6">
-        <v>195.85</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>350.9</v>
-      </c>
-      <c r="D56" s="6">
-        <v>360</v>
-      </c>
-      <c r="E56" s="7">
-        <v>9.1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>576.8</v>
-      </c>
-      <c r="D57" s="6">
-        <v>579.35</v>
-      </c>
-      <c r="E57" s="7">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>190.54</v>
-      </c>
-      <c r="D58" s="6">
-        <v>187.3</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-3.24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>65.34</v>
-      </c>
-      <c r="D59" s="6">
-        <v>65.16</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C60" s="6">
-        <v>88</v>
-      </c>
-      <c r="D60" s="6">
-        <v>99</v>
-      </c>
-      <c r="E60" s="7">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C61" s="6">
-        <v>99</v>
-      </c>
-      <c r="D61" s="6">
-        <v>88</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="6">
-        <v>45</v>
-      </c>
-      <c r="D62" s="6">
-        <v>55</v>
-      </c>
-      <c r="E62" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>55</v>
-      </c>
-      <c r="D63" s="6">
-        <v>45</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>26.74</v>
-      </c>
-      <c r="D64" s="6">
-        <v>46.68</v>
-      </c>
-      <c r="E64" s="7">
-        <v>19.94</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>40.22</v>
-      </c>
-      <c r="D65" s="6">
-        <v>39.76</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>52.08</v>
-      </c>
-      <c r="D66" s="6">
-        <v>51.27</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>48.6</v>
-      </c>
-      <c r="D67" s="6">
-        <v>49.72</v>
-      </c>
-      <c r="E67" s="7">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>47.55</v>
-      </c>
-      <c r="D68" s="6">
-        <v>46.92</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>34.6</v>
-      </c>
-      <c r="D69" s="6">
-        <v>42.33</v>
-      </c>
-      <c r="E69" s="7">
-        <v>7.73</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>41.45</v>
-      </c>
-      <c r="D70" s="6">
-        <v>42.79</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>59.17</v>
-      </c>
-      <c r="D71" s="6">
-        <v>53.34</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-5.83</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>33.2</v>
-      </c>
-      <c r="D72" s="6">
-        <v>32.61</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="B83" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="6">
-        <v>-20.78</v>
-      </c>
-      <c r="D73" s="6">
-        <v>188.74</v>
-      </c>
-      <c r="E73" s="7">
-        <v>209.52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-44.58</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-41.94</v>
-      </c>
-      <c r="E74" s="7">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-56.33</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-56.58</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-21.7</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-56.58</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-34.88</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-29.94</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-25.18</v>
-      </c>
-      <c r="E77" s="7">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>52.85</v>
-      </c>
-      <c r="D78" s="6">
-        <v>70.44</v>
-      </c>
-      <c r="E78" s="7">
-        <v>17.59</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-85.95999999999999</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-86.2</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>97.11</v>
-      </c>
-      <c r="D80" s="6">
-        <v>1.78</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-95.33</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="C83" s="7">
         <v>18.77</v>
       </c>
-      <c r="E81" s="7">
-        <v>9.550000000000001</v>
+      <c r="D83" s="7">
+        <v>-23.82</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-42.59</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3459,61 +3509,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>74</v>
       </c>
+      <c r="F1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
-        <v>48.16</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>49.76000000000001</v>
+      </c>
+      <c r="C2" s="13">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>45</v>
-      </c>
-      <c r="E2" s="11">
-        <v>40</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-2.3</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-12.4</v>
-      </c>
-      <c r="H2" s="11">
-        <v>55.4</v>
-      </c>
-      <c r="I2" s="11">
-        <v>10</v>
+      <c r="D2" s="12">
+        <v>42.4</v>
+      </c>
+      <c r="E2" s="12">
+        <v>44.4</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-4.2</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-14</v>
+      </c>
+      <c r="H2" s="12">
+        <v>55</v>
+      </c>
+      <c r="I2" s="12">
+        <v>11.1</v>
       </c>
     </row>
   </sheetData>
@@ -3614,61 +3664,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.5145000000000001</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1731</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1082</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0159</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.0185</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.0463</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.0738</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1164</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.167</v>
+      <c r="A2" s="15">
+        <v>0.5071</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1803</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1116</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0186</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.0069</v>
+      </c>
+      <c r="F2" s="15">
+        <v>-0.0501</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.0808</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.1144</v>
+      </c>
+      <c r="I2" s="15">
+        <v>-0.1657</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -196,28 +196,34 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.7 → 52.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.7</t>
+    <t>50.2 → 44.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.2</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>52.0 → 49.3</t>
   </si>
   <si>
     <t>52.0</t>
   </si>
   <si>
-    <t>53.3 → 43.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.3</t>
-  </si>
-  <si>
-    <t>43.8</t>
+    <t>49.3</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -303,14 +309,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,13 +349,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -427,11 +433,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -943,10 +948,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1167.8</v>
+        <v>1163.6</v>
       </c>
       <c r="D2">
-        <v>-1.63</v>
+        <v>-0.36</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -955,46 +960,46 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-38.62</v>
+        <v>-38.84</v>
       </c>
       <c r="H2">
-        <v>3.81</v>
+        <v>3.44</v>
       </c>
       <c r="I2">
-        <v>3.81</v>
+        <v>2.34</v>
       </c>
       <c r="J2">
-        <v>-5.25</v>
+        <v>-7.63</v>
       </c>
       <c r="K2">
-        <v>-15.46</v>
+        <v>-16.16</v>
       </c>
       <c r="L2">
-        <v>-36.94</v>
+        <v>-36.99</v>
       </c>
       <c r="M2">
-        <v>-11.44</v>
+        <v>-11.46</v>
       </c>
       <c r="N2">
         <v>33</v>
       </c>
       <c r="O2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P2">
-        <v>1153.06</v>
+        <v>1158.38</v>
       </c>
       <c r="Q2">
-        <v>1185.08</v>
+        <v>1180.45</v>
       </c>
       <c r="R2">
-        <v>1248.38</v>
+        <v>1244.4</v>
       </c>
       <c r="S2">
-        <v>1406.89</v>
+        <v>1404.07</v>
       </c>
       <c r="T2">
-        <v>-16.99</v>
+        <v>-17.13</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1009,34 +1014,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.9</v>
+        <v>40.92</v>
       </c>
       <c r="Z2">
-        <v>-29.64</v>
+        <v>-27.53</v>
       </c>
       <c r="AA2">
-        <v>-32.98</v>
+        <v>-31.89</v>
       </c>
       <c r="AB2">
-        <v>3.33</v>
+        <v>4.36</v>
       </c>
       <c r="AC2">
-        <v>72.94</v>
+        <v>86.87</v>
       </c>
       <c r="AD2">
-        <v>53.9</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="AE2">
-        <v>27.99</v>
+        <v>28.11</v>
       </c>
       <c r="AF2">
-        <v>-7.07</v>
+        <v>-32.39</v>
       </c>
       <c r="AG2">
-        <v>1272.29</v>
+        <v>1261.34</v>
       </c>
       <c r="AH2">
-        <v>1097.87</v>
+        <v>1099.55</v>
       </c>
       <c r="AI2">
         <v>1203.99</v>
@@ -1045,7 +1050,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>45.08</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1061,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2657.5</v>
+        <v>2594.5</v>
       </c>
       <c r="D3">
-        <v>-1.28</v>
+        <v>-2.37</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1068,46 +1073,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-17.27</v>
+        <v>-19.23</v>
       </c>
       <c r="H3">
-        <v>51.17</v>
+        <v>47.58</v>
       </c>
       <c r="I3">
-        <v>1.05</v>
+        <v>-3.73</v>
       </c>
       <c r="J3">
-        <v>-9.09</v>
+        <v>-14.09</v>
       </c>
       <c r="K3">
-        <v>-16.52</v>
+        <v>-18.48</v>
       </c>
       <c r="L3">
-        <v>5.63</v>
+        <v>2.48</v>
       </c>
       <c r="M3">
-        <v>11.16</v>
+        <v>10.27</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="P3">
-        <v>2693.42</v>
+        <v>2673.32</v>
       </c>
       <c r="Q3">
-        <v>2804.51</v>
+        <v>2785.49</v>
       </c>
       <c r="R3">
-        <v>2920.84</v>
+        <v>2912.33</v>
       </c>
       <c r="S3">
-        <v>2597.58</v>
+        <v>2599.36</v>
       </c>
       <c r="T3">
-        <v>2.31</v>
+        <v>-0.19</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1119,46 +1124,46 @@
         <v>47</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>37.76</v>
+        <v>34.35</v>
       </c>
       <c r="Z3">
-        <v>-80.93000000000001</v>
+        <v>-85.56</v>
       </c>
       <c r="AA3">
-        <v>-72.90000000000001</v>
+        <v>-75.44</v>
       </c>
       <c r="AB3">
-        <v>-8.02</v>
+        <v>-10.13</v>
       </c>
       <c r="AC3">
-        <v>43</v>
+        <v>34.48</v>
       </c>
       <c r="AD3">
-        <v>47.12</v>
+        <v>42.35</v>
       </c>
       <c r="AE3">
-        <v>79.41</v>
+        <v>82.12</v>
       </c>
       <c r="AF3">
-        <v>-41.71</v>
+        <v>-36.97</v>
       </c>
       <c r="AG3">
-        <v>3071.47</v>
+        <v>3055.51</v>
       </c>
       <c r="AH3">
-        <v>2537.56</v>
+        <v>2515.47</v>
       </c>
       <c r="AI3">
-        <v>2899.05</v>
+        <v>2872.66</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>46.51</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1174,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1295.2</v>
+        <v>1258.5</v>
       </c>
       <c r="D4">
-        <v>-0.52</v>
+        <v>-2.83</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1181,46 +1186,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-19.28</v>
+        <v>-21.56</v>
       </c>
       <c r="H4">
-        <v>67.59999999999999</v>
+        <v>62.85</v>
       </c>
       <c r="I4">
-        <v>1.66</v>
+        <v>-2.21</v>
       </c>
       <c r="J4">
-        <v>1.65</v>
+        <v>-5.7</v>
       </c>
       <c r="K4">
-        <v>-15.35</v>
+        <v>-18.38</v>
       </c>
       <c r="L4">
-        <v>25</v>
+        <v>20.57</v>
       </c>
       <c r="M4">
-        <v>1.86</v>
+        <v>0.97</v>
       </c>
       <c r="N4">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O4">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1301.94</v>
+        <v>1296.24</v>
       </c>
       <c r="Q4">
-        <v>1287.39</v>
+        <v>1285.14</v>
       </c>
       <c r="R4">
-        <v>1299.11</v>
+        <v>1296.83</v>
       </c>
       <c r="S4">
-        <v>1215.28</v>
+        <v>1216.5</v>
       </c>
       <c r="T4">
-        <v>6.58</v>
+        <v>3.45</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1235,34 +1240,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>50.16</v>
+        <v>44.54</v>
       </c>
       <c r="Z4">
-        <v>-1.53</v>
+        <v>-4.11</v>
       </c>
       <c r="AA4">
-        <v>-5.89</v>
+        <v>-5.54</v>
       </c>
       <c r="AB4">
-        <v>4.36</v>
+        <v>1.43</v>
       </c>
       <c r="AC4">
-        <v>63.75</v>
+        <v>45.93</v>
       </c>
       <c r="AD4">
-        <v>68.62</v>
+        <v>60.79</v>
       </c>
       <c r="AE4">
-        <v>40.37</v>
+        <v>41.57</v>
       </c>
       <c r="AF4">
-        <v>-56.5</v>
+        <v>-23.14</v>
       </c>
       <c r="AG4">
-        <v>1340.96</v>
+        <v>1339.62</v>
       </c>
       <c r="AH4">
-        <v>1233.83</v>
+        <v>1230.66</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1271,7 +1276,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>15.21</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1287,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1766</v>
+        <v>1748.8</v>
       </c>
       <c r="D5">
-        <v>0.87</v>
+        <v>-0.97</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1294,46 +1299,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-6.22</v>
+        <v>-7.14</v>
       </c>
       <c r="H5">
-        <v>36.04</v>
+        <v>34.72</v>
       </c>
       <c r="I5">
-        <v>0.68</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J5">
-        <v>1.59</v>
+        <v>-4.12</v>
       </c>
       <c r="K5">
-        <v>-4.23</v>
+        <v>-5.29</v>
       </c>
       <c r="L5">
-        <v>24.1</v>
+        <v>21.06</v>
       </c>
       <c r="M5">
-        <v>18.03</v>
+        <v>18.18</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P5">
-        <v>1754.34</v>
+        <v>1751.5</v>
       </c>
       <c r="Q5">
-        <v>1768.34</v>
+        <v>1766.42</v>
       </c>
       <c r="R5">
-        <v>1728.39</v>
+        <v>1729.49</v>
       </c>
       <c r="S5">
-        <v>1641.19</v>
+        <v>1642.62</v>
       </c>
       <c r="T5">
-        <v>7.6</v>
+        <v>6.46</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1348,34 +1353,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>51.96</v>
+        <v>49.28</v>
       </c>
       <c r="Z5">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="AA5">
-        <v>6.1</v>
+        <v>5.29</v>
       </c>
       <c r="AB5">
-        <v>-3.19</v>
+        <v>-3.24</v>
       </c>
       <c r="AC5">
-        <v>37.58</v>
+        <v>42.36</v>
       </c>
       <c r="AD5">
-        <v>34.54</v>
+        <v>37.23</v>
       </c>
       <c r="AE5">
-        <v>44.19</v>
+        <v>45.27</v>
       </c>
       <c r="AF5">
-        <v>-13.23</v>
+        <v>-23.22</v>
       </c>
       <c r="AG5">
-        <v>1823.44</v>
+        <v>1821.44</v>
       </c>
       <c r="AH5">
-        <v>1713.23</v>
+        <v>1711.4</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1384,7 +1389,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>29.57</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1400,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>194.08</v>
+        <v>187.09</v>
       </c>
       <c r="D6">
-        <v>-0.9</v>
+        <v>-3.6</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1407,46 +1412,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-22.03</v>
+        <v>-24.84</v>
       </c>
       <c r="H6">
-        <v>45.97</v>
+        <v>40.71</v>
       </c>
       <c r="I6">
-        <v>4.4</v>
+        <v>0.61</v>
       </c>
       <c r="J6">
-        <v>-5.75</v>
+        <v>-9.44</v>
       </c>
       <c r="K6">
-        <v>-11.77</v>
+        <v>-15.1</v>
       </c>
       <c r="L6">
-        <v>25.29</v>
+        <v>18.78</v>
       </c>
       <c r="M6">
-        <v>50.71</v>
+        <v>50.01</v>
       </c>
       <c r="N6">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="O6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="P6">
-        <v>193.51</v>
+        <v>193.73</v>
       </c>
       <c r="Q6">
-        <v>197.2</v>
+        <v>196.23</v>
       </c>
       <c r="R6">
-        <v>203.04</v>
+        <v>202.6</v>
       </c>
       <c r="S6">
-        <v>190.89</v>
+        <v>191.11</v>
       </c>
       <c r="T6">
-        <v>1.67</v>
+        <v>-2.1</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1458,37 +1463,37 @@
         <v>47</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>45.18</v>
+        <v>39</v>
       </c>
       <c r="Z6">
-        <v>-3.39</v>
+        <v>-3.75</v>
       </c>
       <c r="AA6">
-        <v>-3.61</v>
+        <v>-3.64</v>
       </c>
       <c r="AB6">
-        <v>0.22</v>
+        <v>-0.11</v>
       </c>
       <c r="AC6">
-        <v>84</v>
+        <v>62.77</v>
       </c>
       <c r="AD6">
-        <v>76.06</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="AE6">
-        <v>6.41</v>
+        <v>6.58</v>
       </c>
       <c r="AF6">
-        <v>-59.25</v>
+        <v>-10.02</v>
       </c>
       <c r="AG6">
-        <v>210.09</v>
+        <v>209.08</v>
       </c>
       <c r="AH6">
-        <v>184.31</v>
+        <v>183.37</v>
       </c>
       <c r="AI6">
         <v>204.13</v>
@@ -1497,7 +1502,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>29.15</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1513,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>361.85</v>
+        <v>359.9</v>
       </c>
       <c r="D7">
-        <v>0.51</v>
+        <v>-0.54</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1520,46 +1525,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-37</v>
+        <v>-37.34</v>
       </c>
       <c r="H7">
-        <v>6.11</v>
+        <v>5.54</v>
       </c>
       <c r="I7">
-        <v>3.98</v>
+        <v>2.83</v>
       </c>
       <c r="J7">
-        <v>-5.58</v>
+        <v>-7.31</v>
       </c>
       <c r="K7">
-        <v>-17.35</v>
+        <v>-18.36</v>
       </c>
       <c r="L7">
-        <v>-35.48</v>
+        <v>-36.21</v>
       </c>
       <c r="M7">
-        <v>-0.6899999999999999</v>
+        <v>-0.31</v>
       </c>
       <c r="N7">
         <v>22</v>
       </c>
       <c r="O7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="P7">
-        <v>354.35</v>
+        <v>356.33</v>
       </c>
       <c r="Q7">
-        <v>365.59</v>
+        <v>364.05</v>
       </c>
       <c r="R7">
-        <v>390.3</v>
+        <v>388.82</v>
       </c>
       <c r="S7">
-        <v>444.13</v>
+        <v>443.17</v>
       </c>
       <c r="T7">
-        <v>-18.53</v>
+        <v>-18.79</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1574,34 +1579,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>43.79</v>
+        <v>42.57</v>
       </c>
       <c r="Z7">
-        <v>-11.07</v>
+        <v>-10.14</v>
       </c>
       <c r="AA7">
-        <v>-12.42</v>
+        <v>-11.96</v>
       </c>
       <c r="AB7">
-        <v>1.35</v>
+        <v>1.83</v>
       </c>
       <c r="AC7">
-        <v>96.01000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="AD7">
-        <v>84.39</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AE7">
-        <v>9.94</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AF7">
-        <v>-26</v>
+        <v>-43.86</v>
       </c>
       <c r="AG7">
-        <v>396.85</v>
+        <v>393.05</v>
       </c>
       <c r="AH7">
-        <v>334.33</v>
+        <v>335.05</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1610,7 +1615,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>44.2</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,10 +1626,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>573.65</v>
+        <v>559.4</v>
       </c>
       <c r="D8">
-        <v>-0.98</v>
+        <v>-2.48</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1633,97 +1638,97 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-29.03</v>
+        <v>-30.79</v>
       </c>
       <c r="H8">
-        <v>22.64</v>
+        <v>19.6</v>
       </c>
       <c r="I8">
-        <v>1.86</v>
+        <v>-2.24</v>
       </c>
       <c r="J8">
-        <v>-2.27</v>
+        <v>-15.33</v>
       </c>
       <c r="K8">
-        <v>-19.53</v>
+        <v>-20.13</v>
       </c>
       <c r="L8">
-        <v>-6.96</v>
+        <v>-9.6</v>
       </c>
       <c r="M8">
-        <v>-16.57</v>
+        <v>-17.51</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="P8">
-        <v>576.72</v>
+        <v>574.16</v>
       </c>
       <c r="Q8">
-        <v>589.99</v>
+        <v>586.04</v>
       </c>
       <c r="R8">
-        <v>614.6799999999999</v>
+        <v>612.72</v>
       </c>
       <c r="S8">
-        <v>614.67</v>
+        <v>614.63</v>
       </c>
       <c r="T8">
-        <v>-6.67</v>
+        <v>-8.99</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
       </c>
       <c r="V8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="W8" t="s">
         <v>47</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>40.56</v>
+        <v>35.59</v>
       </c>
       <c r="Z8">
-        <v>-12.57</v>
+        <v>-13.24</v>
       </c>
       <c r="AA8">
-        <v>-13.53</v>
+        <v>-13.47</v>
       </c>
       <c r="AB8">
-        <v>0.96</v>
+        <v>0.24</v>
       </c>
       <c r="AC8">
-        <v>79.59</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="AD8">
-        <v>74.23</v>
+        <v>75.61</v>
       </c>
       <c r="AE8">
-        <v>15.64</v>
+        <v>15.86</v>
       </c>
       <c r="AF8">
-        <v>-87.41</v>
+        <v>-84.45999999999999</v>
       </c>
       <c r="AG8">
-        <v>634.02</v>
+        <v>625.74</v>
       </c>
       <c r="AH8">
-        <v>545.96</v>
+        <v>546.34</v>
       </c>
       <c r="AI8">
-        <v>617.98</v>
+        <v>612.1900000000001</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>28.71</v>
+        <v>30.93</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1734,10 +1739,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>180.62</v>
+        <v>179.66</v>
       </c>
       <c r="D9">
-        <v>-3.57</v>
+        <v>-0.53</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1746,46 +1751,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-34.94</v>
+        <v>-35.28</v>
       </c>
       <c r="H9">
-        <v>4.83</v>
+        <v>4.27</v>
       </c>
       <c r="I9">
-        <v>-1.5</v>
+        <v>-2.84</v>
       </c>
       <c r="J9">
-        <v>-1.86</v>
+        <v>-3.91</v>
       </c>
       <c r="K9">
-        <v>-4.62</v>
+        <v>-7.36</v>
       </c>
       <c r="L9">
-        <v>-32.77</v>
+        <v>-32.94</v>
       </c>
       <c r="M9">
-        <v>-8.08</v>
+        <v>-8.18</v>
       </c>
       <c r="N9">
         <v>44</v>
       </c>
       <c r="O9">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P9">
-        <v>186.32</v>
+        <v>185.27</v>
       </c>
       <c r="Q9">
-        <v>183.18</v>
+        <v>182.98</v>
       </c>
       <c r="R9">
-        <v>187.9</v>
+        <v>187.54</v>
       </c>
       <c r="S9">
-        <v>193.53</v>
+        <v>193.24</v>
       </c>
       <c r="T9">
-        <v>-6.67</v>
+        <v>-7.03</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1800,34 +1805,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>43.77</v>
+        <v>42.59</v>
       </c>
       <c r="Z9">
-        <v>-0.36</v>
+        <v>-0.72</v>
       </c>
       <c r="AA9">
-        <v>-1.01</v>
+        <v>-0.95</v>
       </c>
       <c r="AB9">
-        <v>0.64</v>
+        <v>0.23</v>
       </c>
       <c r="AC9">
-        <v>75.16</v>
+        <v>55.76</v>
       </c>
       <c r="AD9">
-        <v>88</v>
+        <v>74.7</v>
       </c>
       <c r="AE9">
-        <v>5.75</v>
+        <v>5.63</v>
       </c>
       <c r="AF9">
-        <v>112.51</v>
+        <v>-50.49</v>
       </c>
       <c r="AG9">
-        <v>191.24</v>
+        <v>191.19</v>
       </c>
       <c r="AH9">
-        <v>175.11</v>
+        <v>174.77</v>
       </c>
       <c r="AI9">
         <v>176.41</v>
@@ -1836,7 +1841,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>25.51</v>
+        <v>22.58</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1847,10 +1852,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>63.02</v>
+        <v>63.2</v>
       </c>
       <c r="D10">
-        <v>-3.28</v>
+        <v>0.29</v>
       </c>
       <c r="E10">
         <v>101.33</v>
@@ -1859,46 +1864,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-37.81</v>
+        <v>-37.63</v>
       </c>
       <c r="H10">
-        <v>6.31</v>
+        <v>6.61</v>
       </c>
       <c r="I10">
-        <v>-3.31</v>
+        <v>-4.11</v>
       </c>
       <c r="J10">
-        <v>-11.29</v>
+        <v>-11.88</v>
       </c>
       <c r="K10">
-        <v>-21.26</v>
+        <v>-20.81</v>
       </c>
       <c r="L10">
-        <v>-33.57</v>
+        <v>-33.46</v>
       </c>
       <c r="M10">
-        <v>-5.01</v>
+        <v>-5.4</v>
       </c>
       <c r="N10">
         <v>11</v>
       </c>
       <c r="O10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P10">
-        <v>65.08</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="Q10">
-        <v>67.48999999999999</v>
+        <v>67.08</v>
       </c>
       <c r="R10">
-        <v>71.28</v>
+        <v>71</v>
       </c>
       <c r="S10">
-        <v>78.34</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="T10">
-        <v>-19.56</v>
+        <v>-19.16</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1913,43 +1918,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>26.59</v>
+        <v>27.8</v>
       </c>
       <c r="Z10">
-        <v>-2.1</v>
+        <v>-2.15</v>
       </c>
       <c r="AA10">
-        <v>-1.97</v>
+        <v>-2.01</v>
       </c>
       <c r="AB10">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="AC10">
-        <v>61.56</v>
+        <v>53.59</v>
       </c>
       <c r="AD10">
-        <v>70.11</v>
+        <v>63.83</v>
       </c>
       <c r="AE10">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="AF10">
-        <v>-23.82</v>
+        <v>106.05</v>
       </c>
       <c r="AG10">
-        <v>72.90000000000001</v>
+        <v>72.45</v>
       </c>
       <c r="AH10">
-        <v>62.09</v>
+        <v>61.7</v>
       </c>
       <c r="AI10">
-        <v>70.83</v>
+        <v>69.84</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>37.06</v>
+        <v>39.94</v>
       </c>
     </row>
   </sheetData>
@@ -2090,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2130,7 +2135,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>57</v>
@@ -2149,1347 +2154,1333 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-5.25</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-7.63</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-2.38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-9.09</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-14.09</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1.65</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.7</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-7.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>1.59</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-4.12</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-5.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-5.75</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-9.44</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-5.58</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-7.31</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.27</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-15.33</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-13.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-1.86</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.91</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-11.29</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-11.88</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-5.25</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3.81</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2.34</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-7.81</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-9.09</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1.05</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-3.73</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-4.78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>2.5</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.65</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>1.66</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.21</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-3.87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1.57</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.59</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>0.68</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-5.75</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-2.54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>4.4</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-5.52</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-5.58</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>3.98</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2.83</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1.86</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-4.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-2.84</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-3.31</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-4.11</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-36.94</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-36.99</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>5.63</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2.48</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>25</v>
+      </c>
+      <c r="D29" s="6">
+        <v>20.57</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-4.43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>24.1</v>
+      </c>
+      <c r="D30" s="6">
+        <v>21.06</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>25.29</v>
+      </c>
+      <c r="D31" s="6">
+        <v>18.78</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-6.51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-35.48</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-36.21</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-6.96</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-9.6</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-32.77</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-32.94</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-33.57</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-33.46</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-15.46</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-16.16</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-16.52</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-18.48</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-15.35</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-18.38</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-4.23</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-5.29</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-11.77</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-15.1</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.33</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-17.35</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-18.36</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-19.53</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-20.13</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-4.62</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-7.36</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-21.26</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-20.81</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-38.62</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-38.84</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-17.27</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-19.23</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-19.28</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-21.56</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-6.22</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-7.14</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-22.03</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-24.84</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6">
+        <v>-37</v>
+      </c>
+      <c r="D50" s="6">
+        <v>-37.34</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-29.03</v>
+      </c>
+      <c r="D51" s="6">
+        <v>-30.79</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6">
+        <v>-34.94</v>
+      </c>
+      <c r="D52" s="6">
+        <v>-35.28</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.34</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6">
+        <v>-37.81</v>
+      </c>
+      <c r="D53" s="6">
+        <v>-37.63</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>1167.8</v>
+      </c>
+      <c r="D54" s="6">
+        <v>1163.6</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>2657.5</v>
+      </c>
+      <c r="D55" s="6">
+        <v>2594.5</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>1295.2</v>
+      </c>
+      <c r="D56" s="6">
+        <v>1258.5</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-36.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>1766</v>
+      </c>
+      <c r="D57" s="6">
+        <v>1748.8</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-17.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="6">
+        <v>194.08</v>
+      </c>
+      <c r="D58" s="6">
+        <v>187.09</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-6.99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="6">
+        <v>361.85</v>
+      </c>
+      <c r="D59" s="6">
+        <v>359.9</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="6">
+        <v>573.65</v>
+      </c>
+      <c r="D60" s="6">
+        <v>559.4</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-14.25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="6">
+        <v>180.62</v>
+      </c>
+      <c r="D61" s="6">
+        <v>179.66</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C62" s="6">
+        <v>63.02</v>
+      </c>
+      <c r="D62" s="6">
+        <v>63.2</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="6">
+        <v>77</v>
+      </c>
+      <c r="D63" s="6">
+        <v>88</v>
+      </c>
+      <c r="E63" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="6">
+        <v>88</v>
+      </c>
+      <c r="D64" s="6">
+        <v>77</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>41.9</v>
+      </c>
+      <c r="D65" s="6">
+        <v>40.92</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>37.76</v>
+      </c>
+      <c r="D66" s="6">
+        <v>34.35</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-3.41</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="6">
+        <v>50.16</v>
+      </c>
+      <c r="D67" s="6">
+        <v>44.54</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-5.62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="6">
+        <v>51.96</v>
+      </c>
+      <c r="D68" s="6">
+        <v>49.28</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="6">
+        <v>45.18</v>
+      </c>
+      <c r="D69" s="6">
+        <v>39</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-6.18</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="6">
+        <v>43.79</v>
+      </c>
+      <c r="D70" s="6">
+        <v>42.57</v>
+      </c>
+      <c r="E70" s="7">
         <v>-1.22</v>
       </c>
-      <c r="D14" s="7">
-        <v>-2.27</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="6">
+        <v>40.56</v>
+      </c>
+      <c r="D71" s="6">
+        <v>35.59</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-4.97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
+      <c r="B72" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="6">
+        <v>43.77</v>
+      </c>
+      <c r="D72" s="6">
+        <v>42.59</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="6">
+        <v>26.59</v>
+      </c>
+      <c r="D73" s="6">
+        <v>27.8</v>
+      </c>
+      <c r="E73" s="8">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
+        <v>-7.07</v>
+      </c>
+      <c r="D74" s="6">
+        <v>-32.39</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-25.32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="6">
+        <v>-41.71</v>
+      </c>
+      <c r="D75" s="6">
+        <v>-36.97</v>
+      </c>
+      <c r="E75" s="8">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6">
+        <v>-56.5</v>
+      </c>
+      <c r="D76" s="6">
+        <v>-23.14</v>
+      </c>
+      <c r="E76" s="8">
+        <v>33.36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="6">
+        <v>-13.23</v>
+      </c>
+      <c r="D77" s="6">
+        <v>-23.22</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-9.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" s="6">
+        <v>-59.25</v>
+      </c>
+      <c r="D78" s="6">
+        <v>-10.02</v>
+      </c>
+      <c r="E78" s="8">
+        <v>49.23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="6">
+        <v>-26</v>
+      </c>
+      <c r="D79" s="6">
+        <v>-43.86</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-17.86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6">
+        <v>-87.41</v>
+      </c>
+      <c r="D80" s="6">
+        <v>-84.45999999999999</v>
+      </c>
+      <c r="E80" s="8">
         <v>2.95</v>
       </c>
-      <c r="D15" s="7">
-        <v>-1.86</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-4.81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6">
+        <v>112.51</v>
+      </c>
+      <c r="D81" s="6">
+        <v>-50.49</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-163</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-6.57</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-11.29</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-4.72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>4.78</v>
-      </c>
-      <c r="D17" s="7">
-        <v>3.81</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>2.19</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1.05</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>3.68</v>
-      </c>
-      <c r="D19" s="7">
-        <v>1.66</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-0.58</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0.68</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>3.62</v>
-      </c>
-      <c r="D21" s="7">
-        <v>4.4</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2.42</v>
-      </c>
-      <c r="D22" s="7">
-        <v>3.98</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>2.82</v>
-      </c>
-      <c r="D23" s="7">
-        <v>1.86</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.81</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-1.5</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-4.31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="7">
-        <v>2.15</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-3.31</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-5.46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-36.15</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-36.94</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>6.56</v>
-      </c>
-      <c r="D27" s="7">
-        <v>5.63</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>23.85</v>
-      </c>
-      <c r="D28" s="7">
-        <v>25</v>
-      </c>
-      <c r="E28" s="9">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>22.28</v>
-      </c>
-      <c r="D29" s="7">
-        <v>24.1</v>
-      </c>
-      <c r="E29" s="9">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>26.82</v>
-      </c>
-      <c r="D30" s="7">
-        <v>25.29</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-36.17</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-35.48</v>
-      </c>
-      <c r="E31" s="9">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-7.32</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-6.96</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-30.29</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-32.77</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-31.47</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-33.57</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-13.83</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-15.46</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-14.83</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-16.52</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-14</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-15.35</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-4.71</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-4.23</v>
-      </c>
-      <c r="E38" s="9">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-8.67</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-11.77</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-17.9</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-17.35</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-18.01</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-19.53</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-0.72</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-4.62</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-18.78</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-21.26</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-2.48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-37.6</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-38.62</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-16.19</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-17.27</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-18.85</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-19.28</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-7.03</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-6.22</v>
-      </c>
-      <c r="E47" s="9">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-21.32</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-22.03</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7">
-        <v>-37.32</v>
-      </c>
-      <c r="D49" s="7">
-        <v>-37</v>
-      </c>
-      <c r="E49" s="9">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7">
-        <v>-28.32</v>
-      </c>
-      <c r="D50" s="7">
-        <v>-29.03</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7">
-        <v>-32.53</v>
-      </c>
-      <c r="D51" s="7">
-        <v>-34.94</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="7">
-        <v>-35.7</v>
-      </c>
-      <c r="D52" s="7">
-        <v>-37.81</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>1187.2</v>
-      </c>
-      <c r="D53" s="7">
-        <v>1167.8</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-19.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>2692</v>
-      </c>
-      <c r="D54" s="7">
-        <v>2657.5</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-34.5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1302</v>
-      </c>
-      <c r="D55" s="7">
-        <v>1295.2</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>1750.8</v>
-      </c>
-      <c r="D56" s="7">
-        <v>1766</v>
-      </c>
-      <c r="E56" s="9">
-        <v>15.2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="7">
-        <v>195.85</v>
-      </c>
-      <c r="D57" s="7">
-        <v>194.08</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="7">
-        <v>360</v>
-      </c>
-      <c r="D58" s="7">
-        <v>361.85</v>
-      </c>
-      <c r="E58" s="9">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="7">
-        <v>579.35</v>
-      </c>
-      <c r="D59" s="7">
-        <v>573.65</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-5.7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="7">
-        <v>187.3</v>
-      </c>
-      <c r="D60" s="7">
-        <v>180.62</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-6.68</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="7">
-        <v>65.16</v>
-      </c>
-      <c r="D61" s="7">
-        <v>63.02</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="7">
-        <v>34</v>
-      </c>
-      <c r="D62" s="7">
-        <v>33</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="7">
-        <v>12</v>
-      </c>
-      <c r="D63" s="7">
-        <v>22</v>
-      </c>
-      <c r="E63" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="7">
-        <v>45</v>
-      </c>
-      <c r="D64" s="7">
-        <v>44</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C65" s="7">
-        <v>23</v>
-      </c>
-      <c r="D65" s="7">
-        <v>11</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>46.68</v>
-      </c>
-      <c r="D66" s="7">
-        <v>41.9</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-4.78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="7">
-        <v>39.76</v>
-      </c>
-      <c r="D67" s="7">
-        <v>37.76</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="7">
-        <v>51.27</v>
-      </c>
-      <c r="D68" s="7">
-        <v>50.16</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="7">
-        <v>49.72</v>
-      </c>
-      <c r="D69" s="7">
-        <v>51.96</v>
-      </c>
-      <c r="E69" s="9">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="7">
-        <v>46.92</v>
-      </c>
-      <c r="D70" s="7">
-        <v>45.18</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="7">
-        <v>42.33</v>
-      </c>
-      <c r="D71" s="7">
-        <v>43.79</v>
-      </c>
-      <c r="E71" s="9">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="7">
-        <v>42.79</v>
-      </c>
-      <c r="D72" s="7">
-        <v>40.56</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="7">
-        <v>53.34</v>
-      </c>
-      <c r="D73" s="7">
-        <v>43.77</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-9.57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" s="7">
-        <v>32.61</v>
-      </c>
-      <c r="D74" s="7">
-        <v>26.59</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-6.02</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B75" s="6" t="s">
+      <c r="B82" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C75" s="7">
-        <v>188.74</v>
-      </c>
-      <c r="D75" s="7">
-        <v>-7.07</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-195.81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="7">
-        <v>-41.94</v>
-      </c>
-      <c r="D76" s="7">
-        <v>-41.71</v>
-      </c>
-      <c r="E76" s="9">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="7">
-        <v>-56.58</v>
-      </c>
-      <c r="D77" s="7">
-        <v>-56.5</v>
-      </c>
-      <c r="E77" s="9">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="7">
-        <v>-56.58</v>
-      </c>
-      <c r="D78" s="7">
-        <v>-13.23</v>
-      </c>
-      <c r="E78" s="9">
-        <v>43.35</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="7">
-        <v>-25.18</v>
-      </c>
-      <c r="D79" s="7">
-        <v>-59.25</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-34.07</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="7">
-        <v>70.44</v>
-      </c>
-      <c r="D80" s="7">
-        <v>-26</v>
-      </c>
-      <c r="E80" s="8">
-        <v>-96.44</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="7">
-        <v>-86.2</v>
-      </c>
-      <c r="D81" s="7">
-        <v>-87.41</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="7">
-        <v>1.78</v>
-      </c>
-      <c r="D82" s="7">
-        <v>112.51</v>
-      </c>
-      <c r="E82" s="9">
-        <v>110.73</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="7">
-        <v>18.77</v>
-      </c>
-      <c r="D83" s="7">
+      <c r="C82" s="6">
         <v>-23.82</v>
       </c>
-      <c r="E83" s="8">
-        <v>-42.59</v>
+      <c r="D82" s="6">
+        <v>106.05</v>
+      </c>
+      <c r="E82" s="8">
+        <v>129.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3509,60 +3500,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>78</v>
       </c>
+      <c r="H1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="12">
-        <v>49.76000000000001</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>40.88</v>
+      </c>
+      <c r="C2" s="12">
         <v>9</v>
       </c>
-      <c r="D2" s="12">
-        <v>42.4</v>
-      </c>
-      <c r="E2" s="12">
-        <v>44.4</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-4.2</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-14</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>39.6</v>
+      </c>
+      <c r="E2" s="11">
+        <v>22.2</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-15.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>55</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>11.1</v>
       </c>
     </row>
@@ -3664,61 +3655,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="15">
-        <v>0.5071</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1803</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1116</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0186</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.0069</v>
-      </c>
-      <c r="F2" s="15">
-        <v>-0.0501</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.0808</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.1144</v>
-      </c>
-      <c r="I2" s="15">
-        <v>-0.1657</v>
+      <c r="A2" s="14">
+        <v>0.5001</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1818</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1027</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0097</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.0031</v>
+      </c>
+      <c r="F2" s="14">
+        <v>-0.05400000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.0818</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.1146</v>
+      </c>
+      <c r="I2" s="14">
+        <v>-0.1751</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,52 +178,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.2 → 44.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.2</t>
-  </si>
-  <si>
-    <t>44.5</t>
-  </si>
-  <si>
-    <t>52.0 → 49.3</t>
-  </si>
-  <si>
-    <t>52.0</t>
-  </si>
-  <si>
-    <t>49.3</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -309,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -349,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,15 +380,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -948,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1163.6</v>
+        <v>1186.9</v>
       </c>
       <c r="D2">
-        <v>-0.36</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -960,46 +914,46 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-38.84</v>
+        <v>-37.62</v>
       </c>
       <c r="H2">
-        <v>3.44</v>
+        <v>5.51</v>
       </c>
       <c r="I2">
-        <v>2.34</v>
+        <v>4.49</v>
       </c>
       <c r="J2">
-        <v>-7.63</v>
+        <v>-5.52</v>
       </c>
       <c r="K2">
-        <v>-16.16</v>
+        <v>-12.66</v>
       </c>
       <c r="L2">
-        <v>-36.99</v>
+        <v>-35.82</v>
       </c>
       <c r="M2">
-        <v>-11.46</v>
+        <v>-10.91</v>
       </c>
       <c r="N2">
         <v>33</v>
       </c>
       <c r="O2">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P2">
-        <v>1158.38</v>
+        <v>1168.58</v>
       </c>
       <c r="Q2">
-        <v>1180.45</v>
+        <v>1177.88</v>
       </c>
       <c r="R2">
-        <v>1244.4</v>
+        <v>1240.98</v>
       </c>
       <c r="S2">
-        <v>1404.07</v>
+        <v>1401.35</v>
       </c>
       <c r="T2">
-        <v>-17.13</v>
+        <v>-15.3</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -1014,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>40.92</v>
+        <v>48.15</v>
       </c>
       <c r="Z2">
-        <v>-27.53</v>
+        <v>-23.7</v>
       </c>
       <c r="AA2">
-        <v>-31.89</v>
+        <v>-30.25</v>
       </c>
       <c r="AB2">
-        <v>4.36</v>
+        <v>6.55</v>
       </c>
       <c r="AC2">
         <v>86.87</v>
       </c>
       <c r="AD2">
-        <v>72.06999999999999</v>
+        <v>82.22</v>
       </c>
       <c r="AE2">
-        <v>28.11</v>
+        <v>30.51</v>
       </c>
       <c r="AF2">
-        <v>-32.39</v>
+        <v>40.42</v>
       </c>
       <c r="AG2">
-        <v>1261.34</v>
+        <v>1254.19</v>
       </c>
       <c r="AH2">
-        <v>1099.55</v>
+        <v>1101.57</v>
       </c>
       <c r="AI2">
         <v>1203.99</v>
@@ -1050,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>42.01</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1061,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2594.5</v>
+        <v>2550</v>
       </c>
       <c r="D3">
-        <v>-2.37</v>
+        <v>-1.72</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1073,46 +1027,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-19.23</v>
+        <v>-20.61</v>
       </c>
       <c r="H3">
-        <v>47.58</v>
+        <v>45.05</v>
       </c>
       <c r="I3">
-        <v>-3.73</v>
+        <v>-6.34</v>
       </c>
       <c r="J3">
-        <v>-14.09</v>
+        <v>-14.29</v>
       </c>
       <c r="K3">
-        <v>-18.48</v>
+        <v>-18.99</v>
       </c>
       <c r="L3">
-        <v>2.48</v>
+        <v>-0.25</v>
       </c>
       <c r="M3">
-        <v>10.27</v>
+        <v>10.62</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P3">
-        <v>2673.32</v>
+        <v>2638.8</v>
       </c>
       <c r="Q3">
-        <v>2785.49</v>
+        <v>2763.14</v>
       </c>
       <c r="R3">
-        <v>2912.33</v>
+        <v>2903.13</v>
       </c>
       <c r="S3">
-        <v>2599.36</v>
+        <v>2600.82</v>
       </c>
       <c r="T3">
-        <v>-0.19</v>
+        <v>-1.95</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1127,43 +1081,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>34.35</v>
+        <v>32.14</v>
       </c>
       <c r="Z3">
-        <v>-85.56</v>
+        <v>-91.77</v>
       </c>
       <c r="AA3">
-        <v>-75.44</v>
+        <v>-78.7</v>
       </c>
       <c r="AB3">
-        <v>-10.13</v>
+        <v>-13.07</v>
       </c>
       <c r="AC3">
-        <v>34.48</v>
+        <v>21.89</v>
       </c>
       <c r="AD3">
-        <v>42.35</v>
+        <v>33.12</v>
       </c>
       <c r="AE3">
-        <v>82.12</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="AF3">
-        <v>-36.97</v>
+        <v>-29.98</v>
       </c>
       <c r="AG3">
-        <v>3055.51</v>
+        <v>3033.44</v>
       </c>
       <c r="AH3">
-        <v>2515.47</v>
+        <v>2492.84</v>
       </c>
       <c r="AI3">
-        <v>2872.66</v>
+        <v>2804.12</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>48.41</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1174,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1258.5</v>
+        <v>1250</v>
       </c>
       <c r="D4">
-        <v>-2.83</v>
+        <v>-0.68</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1186,46 +1140,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-21.56</v>
+        <v>-22.09</v>
       </c>
       <c r="H4">
-        <v>62.85</v>
+        <v>61.75</v>
       </c>
       <c r="I4">
-        <v>-2.21</v>
+        <v>-5.19</v>
       </c>
       <c r="J4">
-        <v>-5.7</v>
+        <v>-4.11</v>
       </c>
       <c r="K4">
-        <v>-18.38</v>
+        <v>-15.1</v>
       </c>
       <c r="L4">
-        <v>20.57</v>
+        <v>17.89</v>
       </c>
       <c r="M4">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="N4">
         <v>88</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>1296.24</v>
+        <v>1282.56</v>
       </c>
       <c r="Q4">
-        <v>1285.14</v>
+        <v>1282.44</v>
       </c>
       <c r="R4">
-        <v>1296.83</v>
+        <v>1294.45</v>
       </c>
       <c r="S4">
-        <v>1216.5</v>
+        <v>1217.62</v>
       </c>
       <c r="T4">
-        <v>3.45</v>
+        <v>2.66</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1240,34 +1194,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>44.54</v>
+        <v>43.33</v>
       </c>
       <c r="Z4">
-        <v>-4.11</v>
+        <v>-6.75</v>
       </c>
       <c r="AA4">
-        <v>-5.54</v>
+        <v>-5.78</v>
       </c>
       <c r="AB4">
-        <v>1.43</v>
+        <v>-0.97</v>
       </c>
       <c r="AC4">
-        <v>45.93</v>
+        <v>26.98</v>
       </c>
       <c r="AD4">
-        <v>60.79</v>
+        <v>45.55</v>
       </c>
       <c r="AE4">
-        <v>41.57</v>
+        <v>42.36</v>
       </c>
       <c r="AF4">
-        <v>-23.14</v>
+        <v>-22.77</v>
       </c>
       <c r="AG4">
-        <v>1339.62</v>
+        <v>1338.32</v>
       </c>
       <c r="AH4">
-        <v>1230.66</v>
+        <v>1226.56</v>
       </c>
       <c r="AI4">
         <v>1356.6</v>
@@ -1276,7 +1230,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>16.53</v>
+        <v>19.69</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1287,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1748.8</v>
+        <v>1750</v>
       </c>
       <c r="D5">
-        <v>-0.97</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1299,46 +1253,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.14</v>
+        <v>-7.07</v>
       </c>
       <c r="H5">
-        <v>34.72</v>
+        <v>34.81</v>
       </c>
       <c r="I5">
-        <v>-0.8100000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J5">
-        <v>-4.12</v>
+        <v>-2.08</v>
       </c>
       <c r="K5">
-        <v>-5.29</v>
+        <v>-3.81</v>
       </c>
       <c r="L5">
-        <v>21.06</v>
+        <v>18.78</v>
       </c>
       <c r="M5">
-        <v>18.18</v>
+        <v>18.74</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P5">
-        <v>1751.5</v>
+        <v>1751.76</v>
       </c>
       <c r="Q5">
-        <v>1766.42</v>
+        <v>1764.17</v>
       </c>
       <c r="R5">
-        <v>1729.49</v>
+        <v>1730.87</v>
       </c>
       <c r="S5">
-        <v>1642.62</v>
+        <v>1644</v>
       </c>
       <c r="T5">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1353,34 +1307,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.28</v>
+        <v>49.48</v>
       </c>
       <c r="Z5">
-        <v>2.05</v>
+        <v>1.45</v>
       </c>
       <c r="AA5">
-        <v>5.29</v>
+        <v>4.52</v>
       </c>
       <c r="AB5">
-        <v>-3.24</v>
+        <v>-3.07</v>
       </c>
       <c r="AC5">
-        <v>42.36</v>
+        <v>49.2</v>
       </c>
       <c r="AD5">
-        <v>37.23</v>
+        <v>43.05</v>
       </c>
       <c r="AE5">
-        <v>45.27</v>
+        <v>44.52</v>
       </c>
       <c r="AF5">
-        <v>-23.22</v>
+        <v>-43.77</v>
       </c>
       <c r="AG5">
-        <v>1821.44</v>
+        <v>1817.93</v>
       </c>
       <c r="AH5">
-        <v>1711.4</v>
+        <v>1710.41</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1389,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.85</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1400,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>187.09</v>
+        <v>185.27</v>
       </c>
       <c r="D6">
-        <v>-3.6</v>
+        <v>-0.97</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1412,25 +1366,25 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-24.84</v>
+        <v>-25.57</v>
       </c>
       <c r="H6">
-        <v>40.71</v>
+        <v>39.34</v>
       </c>
       <c r="I6">
-        <v>0.61</v>
+        <v>-5.06</v>
       </c>
       <c r="J6">
-        <v>-9.44</v>
+        <v>-10.3</v>
       </c>
       <c r="K6">
-        <v>-15.1</v>
+        <v>-14.6</v>
       </c>
       <c r="L6">
-        <v>18.78</v>
+        <v>17.73</v>
       </c>
       <c r="M6">
-        <v>50.01</v>
+        <v>51.25</v>
       </c>
       <c r="N6">
         <v>77</v>
@@ -1439,19 +1393,19 @@
         <v>69</v>
       </c>
       <c r="P6">
-        <v>193.73</v>
+        <v>191.76</v>
       </c>
       <c r="Q6">
-        <v>196.23</v>
+        <v>195.14</v>
       </c>
       <c r="R6">
-        <v>202.6</v>
+        <v>202.1</v>
       </c>
       <c r="S6">
-        <v>191.11</v>
+        <v>191.29</v>
       </c>
       <c r="T6">
-        <v>-2.1</v>
+        <v>-3.15</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1466,34 +1420,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>39</v>
+        <v>37.56</v>
       </c>
       <c r="Z6">
-        <v>-3.75</v>
+        <v>-4.13</v>
       </c>
       <c r="AA6">
-        <v>-3.64</v>
+        <v>-3.74</v>
       </c>
       <c r="AB6">
-        <v>-0.11</v>
+        <v>-0.39</v>
       </c>
       <c r="AC6">
-        <v>62.77</v>
+        <v>39.76</v>
       </c>
       <c r="AD6">
-        <v>77.73999999999999</v>
+        <v>62.18</v>
       </c>
       <c r="AE6">
-        <v>6.58</v>
+        <v>6.47</v>
       </c>
       <c r="AF6">
-        <v>-10.02</v>
+        <v>-36.23</v>
       </c>
       <c r="AG6">
-        <v>209.08</v>
+        <v>207.84</v>
       </c>
       <c r="AH6">
-        <v>183.37</v>
+        <v>182.44</v>
       </c>
       <c r="AI6">
         <v>204.13</v>
@@ -1502,7 +1456,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>29.9</v>
+        <v>31.53</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1513,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>359.9</v>
+        <v>363</v>
       </c>
       <c r="D7">
-        <v>-0.54</v>
+        <v>0.86</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1525,46 +1479,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-37.34</v>
+        <v>-36.8</v>
       </c>
       <c r="H7">
-        <v>5.54</v>
+        <v>6.45</v>
       </c>
       <c r="I7">
-        <v>2.83</v>
+        <v>4.01</v>
       </c>
       <c r="J7">
-        <v>-7.31</v>
+        <v>-7.1</v>
       </c>
       <c r="K7">
-        <v>-18.36</v>
+        <v>-15.74</v>
       </c>
       <c r="L7">
-        <v>-36.21</v>
+        <v>-35.97</v>
       </c>
       <c r="M7">
-        <v>-0.31</v>
+        <v>0.06</v>
       </c>
       <c r="N7">
         <v>22</v>
       </c>
       <c r="O7">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P7">
-        <v>356.33</v>
+        <v>359.13</v>
       </c>
       <c r="Q7">
-        <v>364.05</v>
+        <v>362.85</v>
       </c>
       <c r="R7">
-        <v>388.82</v>
+        <v>387.46</v>
       </c>
       <c r="S7">
-        <v>443.17</v>
+        <v>442.2</v>
       </c>
       <c r="T7">
-        <v>-18.79</v>
+        <v>-17.91</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1579,34 +1533,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.57</v>
+        <v>45.18</v>
       </c>
       <c r="Z7">
-        <v>-10.14</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="AA7">
-        <v>-11.96</v>
+        <v>-11.38</v>
       </c>
       <c r="AB7">
-        <v>1.83</v>
+        <v>2.34</v>
       </c>
       <c r="AC7">
         <v>97.95</v>
       </c>
       <c r="AD7">
-        <v>93.59999999999999</v>
+        <v>97.31</v>
       </c>
       <c r="AE7">
-        <v>9.880000000000001</v>
+        <v>10.97</v>
       </c>
       <c r="AF7">
-        <v>-43.86</v>
+        <v>166.33</v>
       </c>
       <c r="AG7">
-        <v>393.05</v>
+        <v>389.78</v>
       </c>
       <c r="AH7">
-        <v>335.05</v>
+        <v>335.93</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1615,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>38.4</v>
+        <v>36.73</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1626,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>559.4</v>
+        <v>552.85</v>
       </c>
       <c r="D8">
-        <v>-2.48</v>
+        <v>-1.17</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1638,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-30.79</v>
+        <v>-31.6</v>
       </c>
       <c r="H8">
-        <v>19.6</v>
+        <v>18.2</v>
       </c>
       <c r="I8">
-        <v>-2.24</v>
+        <v>-4.94</v>
       </c>
       <c r="J8">
-        <v>-15.33</v>
+        <v>-13.4</v>
       </c>
       <c r="K8">
-        <v>-20.13</v>
+        <v>-18.89</v>
       </c>
       <c r="L8">
-        <v>-9.6</v>
+        <v>-11.04</v>
       </c>
       <c r="M8">
-        <v>-17.51</v>
+        <v>-17.29</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P8">
-        <v>574.16</v>
+        <v>568.41</v>
       </c>
       <c r="Q8">
-        <v>586.04</v>
+        <v>582.37</v>
       </c>
       <c r="R8">
-        <v>612.72</v>
+        <v>610.5700000000001</v>
       </c>
       <c r="S8">
-        <v>614.63</v>
+        <v>614.4299999999999</v>
       </c>
       <c r="T8">
-        <v>-8.99</v>
+        <v>-10.02</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1692,43 +1646,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>35.59</v>
+        <v>33.55</v>
       </c>
       <c r="Z8">
-        <v>-13.24</v>
+        <v>-14.13</v>
       </c>
       <c r="AA8">
-        <v>-13.47</v>
+        <v>-13.6</v>
       </c>
       <c r="AB8">
-        <v>0.24</v>
+        <v>-0.52</v>
       </c>
       <c r="AC8">
-        <v>65.26000000000001</v>
+        <v>35.28</v>
       </c>
       <c r="AD8">
-        <v>75.61</v>
+        <v>60.04</v>
       </c>
       <c r="AE8">
-        <v>15.86</v>
+        <v>15.57</v>
       </c>
       <c r="AF8">
-        <v>-84.45999999999999</v>
+        <v>-38.17</v>
       </c>
       <c r="AG8">
-        <v>625.74</v>
+        <v>619.9400000000001</v>
       </c>
       <c r="AH8">
-        <v>546.34</v>
+        <v>544.8</v>
       </c>
       <c r="AI8">
-        <v>612.1900000000001</v>
+        <v>599.86</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>30.93</v>
+        <v>33.97</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1739,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>179.66</v>
+        <v>178.51</v>
       </c>
       <c r="D9">
-        <v>-0.53</v>
+        <v>-0.64</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1751,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-35.28</v>
+        <v>-35.7</v>
       </c>
       <c r="H9">
-        <v>4.27</v>
+        <v>3.6</v>
       </c>
       <c r="I9">
-        <v>-2.84</v>
+        <v>-5.15</v>
       </c>
       <c r="J9">
-        <v>-3.91</v>
+        <v>-2.75</v>
       </c>
       <c r="K9">
-        <v>-7.36</v>
+        <v>-6</v>
       </c>
       <c r="L9">
-        <v>-32.94</v>
+        <v>-32.93</v>
       </c>
       <c r="M9">
-        <v>-8.18</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="N9">
         <v>44</v>
       </c>
       <c r="O9">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="P9">
-        <v>185.27</v>
+        <v>183.33</v>
       </c>
       <c r="Q9">
-        <v>182.98</v>
+        <v>182.75</v>
       </c>
       <c r="R9">
-        <v>187.54</v>
+        <v>187.19</v>
       </c>
       <c r="S9">
-        <v>193.24</v>
+        <v>192.94</v>
       </c>
       <c r="T9">
-        <v>-7.03</v>
+        <v>-7.48</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1805,34 +1759,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>42.59</v>
+        <v>41.16</v>
       </c>
       <c r="Z9">
-        <v>-0.72</v>
+        <v>-1.09</v>
       </c>
       <c r="AA9">
-        <v>-0.95</v>
+        <v>-0.98</v>
       </c>
       <c r="AB9">
-        <v>0.23</v>
+        <v>-0.11</v>
       </c>
       <c r="AC9">
-        <v>55.76</v>
+        <v>41.5</v>
       </c>
       <c r="AD9">
-        <v>74.7</v>
+        <v>57.47</v>
       </c>
       <c r="AE9">
-        <v>5.63</v>
+        <v>5.49</v>
       </c>
       <c r="AF9">
-        <v>-50.49</v>
+        <v>-66.89</v>
       </c>
       <c r="AG9">
-        <v>191.19</v>
+        <v>191.2</v>
       </c>
       <c r="AH9">
-        <v>174.77</v>
+        <v>174.3</v>
       </c>
       <c r="AI9">
         <v>176.41</v>
@@ -1841,7 +1795,7 @@
         <v>50</v>
       </c>
       <c r="AK9">
-        <v>22.58</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1852,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>63.2</v>
+        <v>61.4</v>
       </c>
       <c r="D10">
-        <v>0.29</v>
+        <v>-2.85</v>
       </c>
       <c r="E10">
         <v>101.33</v>
@@ -1864,25 +1818,25 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-37.63</v>
+        <v>-39.41</v>
       </c>
       <c r="H10">
-        <v>6.61</v>
+        <v>3.58</v>
       </c>
       <c r="I10">
-        <v>-4.11</v>
+        <v>-6.94</v>
       </c>
       <c r="J10">
-        <v>-11.88</v>
+        <v>-14.21</v>
       </c>
       <c r="K10">
-        <v>-20.81</v>
+        <v>-19.23</v>
       </c>
       <c r="L10">
-        <v>-33.46</v>
+        <v>-35.12</v>
       </c>
       <c r="M10">
-        <v>-5.4</v>
+        <v>-5.33</v>
       </c>
       <c r="N10">
         <v>11</v>
@@ -1891,19 +1845,19 @@
         <v>15</v>
       </c>
       <c r="P10">
-        <v>64.54000000000001</v>
+        <v>63.62</v>
       </c>
       <c r="Q10">
-        <v>67.08</v>
+        <v>66.53</v>
       </c>
       <c r="R10">
-        <v>71</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="S10">
-        <v>78.18000000000001</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="T10">
-        <v>-19.16</v>
+        <v>-21.27</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1918,43 +1872,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>27.8</v>
+        <v>23.61</v>
       </c>
       <c r="Z10">
-        <v>-2.15</v>
+        <v>-2.31</v>
       </c>
       <c r="AA10">
-        <v>-2.01</v>
+        <v>-2.07</v>
       </c>
       <c r="AB10">
-        <v>-0.14</v>
+        <v>-0.24</v>
       </c>
       <c r="AC10">
-        <v>53.59</v>
+        <v>33.05</v>
       </c>
       <c r="AD10">
-        <v>63.83</v>
+        <v>49.4</v>
       </c>
       <c r="AE10">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="AF10">
-        <v>106.05</v>
+        <v>-35.93</v>
       </c>
       <c r="AG10">
-        <v>72.45</v>
+        <v>71.88</v>
       </c>
       <c r="AH10">
-        <v>61.7</v>
+        <v>61.18</v>
       </c>
       <c r="AI10">
-        <v>69.84</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>39.94</v>
+        <v>42.83</v>
       </c>
     </row>
   </sheetData>
@@ -2095,7 +2049,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2115,1372 +2069,1263 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-7.63</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-5.52</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2.11</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-14.09</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-14.29</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-5.7</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-4.11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-4.12</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-2.08</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-9.44</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-10.3</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-7.31</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-7.1</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-15.33</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-13.4</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-3.91</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.75</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-11.88</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-14.21</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-5.25</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2.34</v>
+      </c>
+      <c r="D16" s="5">
+        <v>4.49</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-9.09</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-14.09</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-3.73</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-6.34</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1.65</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-5.7</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-7.35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.21</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-5.19</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1.59</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-4.12</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-5.71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="D19" s="5">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-5.75</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-9.44</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-5.06</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-5.67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-5.58</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-7.31</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>2.83</v>
+      </c>
+      <c r="D21" s="5">
+        <v>4.01</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.27</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-15.33</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-13.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-2.24</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-4.94</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.86</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.91</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-2.84</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-5.15</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-11.29</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-11.88</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-4.11</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-6.94</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>3.81</v>
-      </c>
-      <c r="D18" s="6">
-        <v>2.34</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-36.99</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-35.82</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.05</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.73</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-4.78</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-0.25</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>1.66</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>20.57</v>
+      </c>
+      <c r="D27" s="5">
+        <v>17.89</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>21.06</v>
+      </c>
+      <c r="D28" s="5">
+        <v>18.78</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>18.78</v>
+      </c>
+      <c r="D29" s="5">
+        <v>17.73</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-36.21</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-35.97</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-9.6</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-11.04</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-32.94</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-32.93</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-33.46</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-35.12</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-16.16</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-12.66</v>
+      </c>
+      <c r="E34" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-18.48</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-18.99</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-18.38</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-15.1</v>
+      </c>
+      <c r="E36" s="6">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-5.29</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-3.81</v>
+      </c>
+      <c r="E37" s="6">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-15.1</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-14.6</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-18.36</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-15.74</v>
+      </c>
+      <c r="E39" s="6">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-20.13</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-18.89</v>
+      </c>
+      <c r="E40" s="6">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-7.36</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-6</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-20.81</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-19.23</v>
+      </c>
+      <c r="E42" s="6">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-38.84</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-37.62</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-19.23</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-20.61</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-21.56</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-22.09</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-7.14</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-7.07</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-24.84</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-25.57</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="5">
+        <v>-37.34</v>
+      </c>
+      <c r="D48" s="5">
+        <v>-36.8</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="5">
+        <v>-30.79</v>
+      </c>
+      <c r="D49" s="5">
+        <v>-31.6</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="5">
+        <v>-35.28</v>
+      </c>
+      <c r="D50" s="5">
+        <v>-35.7</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="5">
+        <v>-37.63</v>
+      </c>
+      <c r="D51" s="5">
+        <v>-39.41</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1163.6</v>
+      </c>
+      <c r="D52" s="5">
+        <v>1186.9</v>
+      </c>
+      <c r="E52" s="6">
+        <v>23.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>2594.5</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2550</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-44.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>1258.5</v>
+      </c>
+      <c r="D54" s="5">
+        <v>1250</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-8.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="5">
+        <v>1748.8</v>
+      </c>
+      <c r="D55" s="5">
+        <v>1750</v>
+      </c>
+      <c r="E55" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="5">
+        <v>187.09</v>
+      </c>
+      <c r="D56" s="5">
+        <v>185.27</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="5">
+        <v>359.9</v>
+      </c>
+      <c r="D57" s="5">
+        <v>363</v>
+      </c>
+      <c r="E57" s="6">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="5">
+        <v>559.4</v>
+      </c>
+      <c r="D58" s="5">
+        <v>552.85</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-6.55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="5">
+        <v>179.66</v>
+      </c>
+      <c r="D59" s="5">
+        <v>178.51</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C60" s="5">
+        <v>63.2</v>
+      </c>
+      <c r="D60" s="5">
+        <v>61.4</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>40.92</v>
+      </c>
+      <c r="D61" s="5">
+        <v>48.15</v>
+      </c>
+      <c r="E61" s="6">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>34.35</v>
+      </c>
+      <c r="D62" s="5">
+        <v>32.14</v>
+      </c>
+      <c r="E62" s="7">
         <v>-2.21</v>
       </c>
-      <c r="E20" s="7">
-        <v>-3.87</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>44.54</v>
+      </c>
+      <c r="D63" s="5">
+        <v>43.33</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>49.28</v>
+      </c>
+      <c r="D64" s="5">
+        <v>49.48</v>
+      </c>
+      <c r="E64" s="6">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>4.4</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.61</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="5">
+        <v>39</v>
+      </c>
+      <c r="D65" s="5">
+        <v>37.56</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="D23" s="6">
-        <v>2.83</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="5">
+        <v>42.57</v>
+      </c>
+      <c r="D66" s="5">
+        <v>45.18</v>
+      </c>
+      <c r="E66" s="6">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1.86</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.24</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="5">
+        <v>35.59</v>
+      </c>
+      <c r="D67" s="5">
+        <v>33.55</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-1.5</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-2.84</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="5">
+        <v>42.59</v>
+      </c>
+      <c r="D68" s="5">
+        <v>41.16</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-4.11</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="5">
+        <v>27.8</v>
+      </c>
+      <c r="D69" s="5">
+        <v>23.61</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-4.19</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-36.94</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-36.99</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>-32.39</v>
+      </c>
+      <c r="D70" s="5">
+        <v>40.42</v>
+      </c>
+      <c r="E70" s="6">
+        <v>72.81</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>5.63</v>
-      </c>
-      <c r="D28" s="6">
-        <v>2.48</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-36.97</v>
+      </c>
+      <c r="D71" s="5">
+        <v>-29.98</v>
+      </c>
+      <c r="E71" s="6">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>25</v>
-      </c>
-      <c r="D29" s="6">
-        <v>20.57</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-4.43</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
+        <v>-23.14</v>
+      </c>
+      <c r="D72" s="5">
+        <v>-22.77</v>
+      </c>
+      <c r="E72" s="6">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>24.1</v>
-      </c>
-      <c r="D30" s="6">
-        <v>21.06</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B73" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="5">
+        <v>-23.22</v>
+      </c>
+      <c r="D73" s="5">
+        <v>-43.77</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-20.55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>25.29</v>
-      </c>
-      <c r="D31" s="6">
-        <v>18.78</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-6.51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="5">
+        <v>-10.02</v>
+      </c>
+      <c r="D74" s="5">
+        <v>-36.23</v>
+      </c>
+      <c r="E74" s="7">
+        <v>-26.21</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-35.48</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-36.21</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B75" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="5">
+        <v>-43.86</v>
+      </c>
+      <c r="D75" s="5">
+        <v>166.33</v>
+      </c>
+      <c r="E75" s="6">
+        <v>210.19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-6.96</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-9.6</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B76" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="5">
+        <v>-84.45999999999999</v>
+      </c>
+      <c r="D76" s="5">
+        <v>-38.17</v>
+      </c>
+      <c r="E76" s="6">
+        <v>46.29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-32.77</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-32.94</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B77" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" s="5">
+        <v>-50.49</v>
+      </c>
+      <c r="D77" s="5">
+        <v>-66.89</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-16.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-33.57</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-33.46</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-15.46</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-16.16</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-16.52</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-18.48</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-15.35</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-18.38</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-4.23</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-5.29</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-11.77</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-15.1</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.33</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-17.35</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-18.36</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-19.53</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-20.13</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-4.62</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-7.36</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-21.26</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-20.81</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-38.62</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-38.84</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-17.27</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-19.23</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-19.28</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-21.56</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-6.22</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-7.14</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-22.03</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-24.84</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6">
-        <v>-37</v>
-      </c>
-      <c r="D50" s="6">
-        <v>-37.34</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6">
-        <v>-29.03</v>
-      </c>
-      <c r="D51" s="6">
-        <v>-30.79</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6">
-        <v>-34.94</v>
-      </c>
-      <c r="D52" s="6">
-        <v>-35.28</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="6">
-        <v>-37.81</v>
-      </c>
-      <c r="D53" s="6">
-        <v>-37.63</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>1167.8</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1163.6</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-4.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>2657.5</v>
-      </c>
-      <c r="D55" s="6">
-        <v>2594.5</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>1295.2</v>
-      </c>
-      <c r="D56" s="6">
-        <v>1258.5</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-36.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>1766</v>
-      </c>
-      <c r="D57" s="6">
-        <v>1748.8</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-17.2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C58" s="6">
-        <v>194.08</v>
-      </c>
-      <c r="D58" s="6">
-        <v>187.09</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-6.99</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C59" s="6">
-        <v>361.85</v>
-      </c>
-      <c r="D59" s="6">
-        <v>359.9</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6">
-        <v>573.65</v>
-      </c>
-      <c r="D60" s="6">
-        <v>559.4</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-14.25</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C61" s="6">
-        <v>180.62</v>
-      </c>
-      <c r="D61" s="6">
-        <v>179.66</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="6">
-        <v>63.02</v>
-      </c>
-      <c r="D62" s="6">
-        <v>63.2</v>
-      </c>
-      <c r="E62" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C63" s="6">
-        <v>77</v>
-      </c>
-      <c r="D63" s="6">
-        <v>88</v>
-      </c>
-      <c r="E63" s="8">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C64" s="6">
-        <v>88</v>
-      </c>
-      <c r="D64" s="6">
-        <v>77</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>41.9</v>
-      </c>
-      <c r="D65" s="6">
-        <v>40.92</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>37.76</v>
-      </c>
-      <c r="D66" s="6">
-        <v>34.35</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" s="6">
-        <v>50.16</v>
-      </c>
-      <c r="D67" s="6">
-        <v>44.54</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-5.62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" s="6">
-        <v>51.96</v>
-      </c>
-      <c r="D68" s="6">
-        <v>49.28</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-2.68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" s="6">
-        <v>45.18</v>
-      </c>
-      <c r="D69" s="6">
-        <v>39</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-6.18</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" s="6">
-        <v>43.79</v>
-      </c>
-      <c r="D70" s="6">
-        <v>42.57</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" s="6">
-        <v>40.56</v>
-      </c>
-      <c r="D71" s="6">
-        <v>35.59</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-4.97</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" s="6">
-        <v>43.77</v>
-      </c>
-      <c r="D72" s="6">
-        <v>42.59</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="6">
-        <v>26.59</v>
-      </c>
-      <c r="D73" s="6">
-        <v>27.8</v>
-      </c>
-      <c r="E73" s="8">
-        <v>1.21</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B74" s="5" t="s">
+      <c r="B78" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C74" s="6">
-        <v>-7.07</v>
-      </c>
-      <c r="D74" s="6">
-        <v>-32.39</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-25.32</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C75" s="6">
-        <v>-41.71</v>
-      </c>
-      <c r="D75" s="6">
-        <v>-36.97</v>
-      </c>
-      <c r="E75" s="8">
-        <v>4.74</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="6">
-        <v>-56.5</v>
-      </c>
-      <c r="D76" s="6">
-        <v>-23.14</v>
-      </c>
-      <c r="E76" s="8">
-        <v>33.36</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C77" s="6">
-        <v>-13.23</v>
-      </c>
-      <c r="D77" s="6">
-        <v>-23.22</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-9.99</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C78" s="6">
-        <v>-59.25</v>
-      </c>
-      <c r="D78" s="6">
-        <v>-10.02</v>
-      </c>
-      <c r="E78" s="8">
-        <v>49.23</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C79" s="6">
-        <v>-26</v>
-      </c>
-      <c r="D79" s="6">
-        <v>-43.86</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-17.86</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6">
-        <v>-87.41</v>
-      </c>
-      <c r="D80" s="6">
-        <v>-84.45999999999999</v>
-      </c>
-      <c r="E80" s="8">
-        <v>2.95</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6">
-        <v>112.51</v>
-      </c>
-      <c r="D81" s="6">
-        <v>-50.49</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-163</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C82" s="6">
-        <v>-23.82</v>
-      </c>
-      <c r="D82" s="6">
+      <c r="C78" s="5">
         <v>106.05</v>
       </c>
-      <c r="E82" s="8">
-        <v>129.87</v>
+      <c r="D78" s="5">
+        <v>-35.93</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-141.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3500,60 +3345,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>80</v>
+      <c r="B1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>40.88</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>39.4</v>
+      </c>
+      <c r="E2" s="10">
         <v>22.2</v>
       </c>
-      <c r="F2" s="11">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-15.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-13.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>55</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>11.1</v>
       </c>
     </row>
@@ -3655,61 +3500,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="14">
-        <v>0.5001</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1818</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1027</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0097</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.0031</v>
-      </c>
-      <c r="F2" s="14">
-        <v>-0.05400000000000001</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.0818</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.1146</v>
-      </c>
-      <c r="I2" s="14">
-        <v>-0.1751</v>
+      <c r="A2" s="13">
+        <v>0.5125</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1874</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1062</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="F2" s="13">
+        <v>-0.0533</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.083</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.1091</v>
+      </c>
+      <c r="I2" s="13">
+        <v>-0.1729</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -264,14 +264,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +304,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -769,7 +769,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -902,10 +902,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1186.9</v>
+        <v>1159.4</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>-2.32</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,46 +914,46 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-37.62</v>
+        <v>-39.07</v>
       </c>
       <c r="H2">
-        <v>5.51</v>
+        <v>3.07</v>
       </c>
       <c r="I2">
-        <v>4.49</v>
+        <v>1.93</v>
       </c>
       <c r="J2">
-        <v>-5.52</v>
+        <v>-6.36</v>
       </c>
       <c r="K2">
-        <v>-12.66</v>
+        <v>-13.08</v>
       </c>
       <c r="L2">
-        <v>-35.82</v>
+        <v>-36.37</v>
       </c>
       <c r="M2">
-        <v>-10.91</v>
+        <v>-11.31</v>
       </c>
       <c r="N2">
         <v>33</v>
       </c>
       <c r="O2">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P2">
-        <v>1168.58</v>
+        <v>1172.98</v>
       </c>
       <c r="Q2">
-        <v>1177.88</v>
+        <v>1173.28</v>
       </c>
       <c r="R2">
-        <v>1240.98</v>
+        <v>1237.37</v>
       </c>
       <c r="S2">
-        <v>1401.35</v>
+        <v>1398.46</v>
       </c>
       <c r="T2">
-        <v>-15.3</v>
+        <v>-17.09</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +968,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>48.15</v>
+        <v>41.67</v>
       </c>
       <c r="Z2">
-        <v>-23.7</v>
+        <v>-22.62</v>
       </c>
       <c r="AA2">
-        <v>-30.25</v>
+        <v>-28.72</v>
       </c>
       <c r="AB2">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="AC2">
-        <v>86.87</v>
+        <v>85.17</v>
       </c>
       <c r="AD2">
-        <v>82.22</v>
+        <v>86.3</v>
       </c>
       <c r="AE2">
-        <v>30.51</v>
+        <v>31.19</v>
       </c>
       <c r="AF2">
-        <v>40.42</v>
+        <v>-29.03</v>
       </c>
       <c r="AG2">
-        <v>1254.19</v>
+        <v>1241.6</v>
       </c>
       <c r="AH2">
-        <v>1101.57</v>
+        <v>1104.96</v>
       </c>
       <c r="AI2">
         <v>1203.99</v>
@@ -1004,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>41.16</v>
+        <v>40.42</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1015,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2550</v>
+        <v>2477</v>
       </c>
       <c r="D3">
-        <v>-1.72</v>
+        <v>-2.86</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1027,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-20.61</v>
+        <v>-22.89</v>
       </c>
       <c r="H3">
-        <v>45.05</v>
+        <v>40.9</v>
       </c>
       <c r="I3">
-        <v>-6.34</v>
+        <v>-8.26</v>
       </c>
       <c r="J3">
-        <v>-14.29</v>
+        <v>-17.35</v>
       </c>
       <c r="K3">
-        <v>-18.99</v>
+        <v>-17.71</v>
       </c>
       <c r="L3">
-        <v>-0.25</v>
+        <v>-2.8</v>
       </c>
       <c r="M3">
-        <v>10.62</v>
+        <v>10.15</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P3">
-        <v>2638.8</v>
+        <v>2594.2</v>
       </c>
       <c r="Q3">
-        <v>2763.14</v>
+        <v>2737.33</v>
       </c>
       <c r="R3">
-        <v>2903.13</v>
+        <v>2892.76</v>
       </c>
       <c r="S3">
-        <v>2600.82</v>
+        <v>2601.81</v>
       </c>
       <c r="T3">
-        <v>-1.95</v>
+        <v>-4.8</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,43 +1081,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>32.14</v>
+        <v>28.87</v>
       </c>
       <c r="Z3">
-        <v>-91.77</v>
+        <v>-101.41</v>
       </c>
       <c r="AA3">
-        <v>-78.7</v>
+        <v>-83.23999999999999</v>
       </c>
       <c r="AB3">
-        <v>-13.07</v>
+        <v>-18.16</v>
       </c>
       <c r="AC3">
-        <v>21.89</v>
+        <v>10.19</v>
       </c>
       <c r="AD3">
-        <v>33.12</v>
+        <v>22.19</v>
       </c>
       <c r="AE3">
-        <v>80.76000000000001</v>
+        <v>81.34</v>
       </c>
       <c r="AF3">
-        <v>-29.98</v>
+        <v>22.79</v>
       </c>
       <c r="AG3">
-        <v>3033.44</v>
+        <v>3013.65</v>
       </c>
       <c r="AH3">
-        <v>2492.84</v>
+        <v>2461.01</v>
       </c>
       <c r="AI3">
-        <v>2804.12</v>
+        <v>2750.63</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>50.7</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1128,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1250</v>
+        <v>1185.1</v>
       </c>
       <c r="D4">
-        <v>-0.68</v>
+        <v>-5.19</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,25 +1140,25 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-22.09</v>
+        <v>-26.14</v>
       </c>
       <c r="H4">
-        <v>61.75</v>
+        <v>53.35</v>
       </c>
       <c r="I4">
-        <v>-5.19</v>
+        <v>-9.33</v>
       </c>
       <c r="J4">
-        <v>-4.11</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="K4">
-        <v>-15.1</v>
+        <v>-14.12</v>
       </c>
       <c r="L4">
-        <v>17.89</v>
+        <v>14.31</v>
       </c>
       <c r="M4">
-        <v>0.78</v>
+        <v>-0.29</v>
       </c>
       <c r="N4">
         <v>88</v>
@@ -1167,19 +1167,19 @@
         <v>71</v>
       </c>
       <c r="P4">
-        <v>1282.56</v>
+        <v>1258.16</v>
       </c>
       <c r="Q4">
-        <v>1282.44</v>
+        <v>1276.65</v>
       </c>
       <c r="R4">
-        <v>1294.45</v>
+        <v>1290.84</v>
       </c>
       <c r="S4">
-        <v>1217.62</v>
+        <v>1218.35</v>
       </c>
       <c r="T4">
-        <v>2.66</v>
+        <v>-2.73</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1191,46 +1191,46 @@
         <v>47</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>43.33</v>
+        <v>35.41</v>
       </c>
       <c r="Z4">
-        <v>-6.75</v>
+        <v>-13.93</v>
       </c>
       <c r="AA4">
-        <v>-5.78</v>
+        <v>-7.41</v>
       </c>
       <c r="AB4">
-        <v>-0.97</v>
+        <v>-6.52</v>
       </c>
       <c r="AC4">
-        <v>26.98</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AD4">
-        <v>45.55</v>
+        <v>27.34</v>
       </c>
       <c r="AE4">
-        <v>42.36</v>
+        <v>44.98</v>
       </c>
       <c r="AF4">
-        <v>-22.77</v>
+        <v>33.01</v>
       </c>
       <c r="AG4">
-        <v>1338.32</v>
+        <v>1346.68</v>
       </c>
       <c r="AH4">
-        <v>1226.56</v>
+        <v>1206.62</v>
       </c>
       <c r="AI4">
-        <v>1356.6</v>
+        <v>1344.34</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>19.69</v>
+        <v>24.13</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1241,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1750</v>
+        <v>1702.7</v>
       </c>
       <c r="D5">
-        <v>0.07000000000000001</v>
+        <v>-2.7</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,25 +1253,25 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-7.07</v>
+        <v>-9.58</v>
       </c>
       <c r="H5">
-        <v>34.81</v>
+        <v>31.17</v>
       </c>
       <c r="I5">
-        <v>0.07000000000000001</v>
+        <v>-2.32</v>
       </c>
       <c r="J5">
-        <v>-2.08</v>
+        <v>-5.14</v>
       </c>
       <c r="K5">
-        <v>-3.81</v>
+        <v>-4.26</v>
       </c>
       <c r="L5">
-        <v>18.78</v>
+        <v>15.58</v>
       </c>
       <c r="M5">
-        <v>18.74</v>
+        <v>18.42</v>
       </c>
       <c r="N5">
         <v>99</v>
@@ -1280,19 +1280,19 @@
         <v>79</v>
       </c>
       <c r="P5">
-        <v>1751.76</v>
+        <v>1743.66</v>
       </c>
       <c r="Q5">
-        <v>1764.17</v>
+        <v>1758.94</v>
       </c>
       <c r="R5">
-        <v>1730.87</v>
+        <v>1731.56</v>
       </c>
       <c r="S5">
-        <v>1644</v>
+        <v>1645.09</v>
       </c>
       <c r="T5">
-        <v>6.45</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1307,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.48</v>
+        <v>42.52</v>
       </c>
       <c r="Z5">
-        <v>1.45</v>
+        <v>-2.81</v>
       </c>
       <c r="AA5">
-        <v>4.52</v>
+        <v>3.06</v>
       </c>
       <c r="AB5">
-        <v>-3.07</v>
+        <v>-5.87</v>
       </c>
       <c r="AC5">
-        <v>49.2</v>
+        <v>32.53</v>
       </c>
       <c r="AD5">
-        <v>43.05</v>
+        <v>41.36</v>
       </c>
       <c r="AE5">
-        <v>44.52</v>
+        <v>45.77</v>
       </c>
       <c r="AF5">
-        <v>-43.77</v>
+        <v>-43.35</v>
       </c>
       <c r="AG5">
-        <v>1817.93</v>
+        <v>1815.33</v>
       </c>
       <c r="AH5">
-        <v>1710.41</v>
+        <v>1702.55</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1343,7 +1343,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>28.99</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1354,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>185.27</v>
+        <v>182.04</v>
       </c>
       <c r="D6">
-        <v>-0.97</v>
+        <v>-1.74</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,46 +1366,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-25.57</v>
+        <v>-26.87</v>
       </c>
       <c r="H6">
-        <v>39.34</v>
+        <v>36.91</v>
       </c>
       <c r="I6">
-        <v>-5.06</v>
+        <v>-7.36</v>
       </c>
       <c r="J6">
-        <v>-10.3</v>
+        <v>-12.04</v>
       </c>
       <c r="K6">
-        <v>-14.6</v>
+        <v>-14.23</v>
       </c>
       <c r="L6">
-        <v>17.73</v>
+        <v>9.68</v>
       </c>
       <c r="M6">
-        <v>51.25</v>
+        <v>52.35</v>
       </c>
       <c r="N6">
         <v>77</v>
       </c>
       <c r="O6">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P6">
-        <v>191.76</v>
+        <v>188.87</v>
       </c>
       <c r="Q6">
-        <v>195.14</v>
+        <v>194</v>
       </c>
       <c r="R6">
-        <v>202.1</v>
+        <v>201.56</v>
       </c>
       <c r="S6">
-        <v>191.29</v>
+        <v>191.46</v>
       </c>
       <c r="T6">
-        <v>-3.15</v>
+        <v>-4.92</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,43 +1420,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>37.56</v>
+        <v>35.09</v>
       </c>
       <c r="Z6">
-        <v>-4.13</v>
+        <v>-4.64</v>
       </c>
       <c r="AA6">
-        <v>-3.74</v>
+        <v>-3.92</v>
       </c>
       <c r="AB6">
-        <v>-0.39</v>
+        <v>-0.72</v>
       </c>
       <c r="AC6">
-        <v>39.76</v>
+        <v>15.17</v>
       </c>
       <c r="AD6">
-        <v>62.18</v>
+        <v>39.23</v>
       </c>
       <c r="AE6">
-        <v>6.47</v>
+        <v>6.77</v>
       </c>
       <c r="AF6">
-        <v>-36.23</v>
+        <v>119.08</v>
       </c>
       <c r="AG6">
-        <v>207.84</v>
+        <v>207.13</v>
       </c>
       <c r="AH6">
-        <v>182.44</v>
+        <v>180.87</v>
       </c>
       <c r="AI6">
-        <v>204.13</v>
+        <v>200.91</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>31.53</v>
+        <v>34.92</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1467,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>363</v>
+        <v>358.9</v>
       </c>
       <c r="D7">
-        <v>0.86</v>
+        <v>-1.13</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1479,46 +1479,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-36.8</v>
+        <v>-37.51</v>
       </c>
       <c r="H7">
-        <v>6.45</v>
+        <v>5.25</v>
       </c>
       <c r="I7">
-        <v>4.01</v>
+        <v>2.28</v>
       </c>
       <c r="J7">
-        <v>-7.1</v>
+        <v>-7.24</v>
       </c>
       <c r="K7">
-        <v>-15.74</v>
+        <v>-15.26</v>
       </c>
       <c r="L7">
-        <v>-35.97</v>
+        <v>-36</v>
       </c>
       <c r="M7">
-        <v>0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="N7">
         <v>22</v>
       </c>
       <c r="O7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P7">
-        <v>359.13</v>
+        <v>360.73</v>
       </c>
       <c r="Q7">
-        <v>362.85</v>
+        <v>361.16</v>
       </c>
       <c r="R7">
-        <v>387.46</v>
+        <v>386.16</v>
       </c>
       <c r="S7">
-        <v>442.2</v>
+        <v>441.18</v>
       </c>
       <c r="T7">
-        <v>-17.91</v>
+        <v>-18.65</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1533,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>45.18</v>
+        <v>42.43</v>
       </c>
       <c r="Z7">
-        <v>-9.039999999999999</v>
+        <v>-8.41</v>
       </c>
       <c r="AA7">
-        <v>-11.38</v>
+        <v>-10.79</v>
       </c>
       <c r="AB7">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="AC7">
-        <v>97.95</v>
+        <v>93.64</v>
       </c>
       <c r="AD7">
-        <v>97.31</v>
+        <v>96.52</v>
       </c>
       <c r="AE7">
-        <v>10.97</v>
+        <v>11</v>
       </c>
       <c r="AF7">
-        <v>166.33</v>
+        <v>12.46</v>
       </c>
       <c r="AG7">
-        <v>389.78</v>
+        <v>384.15</v>
       </c>
       <c r="AH7">
-        <v>335.93</v>
+        <v>338.18</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1569,7 +1569,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>36.73</v>
+        <v>35.28</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1580,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>552.85</v>
+        <v>529.5</v>
       </c>
       <c r="D8">
-        <v>-1.17</v>
+        <v>-4.22</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1592,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-31.6</v>
+        <v>-34.49</v>
       </c>
       <c r="H8">
-        <v>18.2</v>
+        <v>13.2</v>
       </c>
       <c r="I8">
-        <v>-4.94</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>-13.4</v>
+        <v>-15.45</v>
       </c>
       <c r="K8">
-        <v>-18.89</v>
+        <v>-20.09</v>
       </c>
       <c r="L8">
-        <v>-11.04</v>
+        <v>-14.54</v>
       </c>
       <c r="M8">
-        <v>-17.29</v>
+        <v>-18.3</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="P8">
-        <v>568.41</v>
+        <v>558.95</v>
       </c>
       <c r="Q8">
-        <v>582.37</v>
+        <v>577.58</v>
       </c>
       <c r="R8">
-        <v>610.5700000000001</v>
+        <v>607.84</v>
       </c>
       <c r="S8">
-        <v>614.4299999999999</v>
+        <v>614.14</v>
       </c>
       <c r="T8">
-        <v>-10.02</v>
+        <v>-13.78</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,43 +1646,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>33.55</v>
+        <v>27.5</v>
       </c>
       <c r="Z8">
-        <v>-14.13</v>
+        <v>-16.53</v>
       </c>
       <c r="AA8">
-        <v>-13.6</v>
+        <v>-14.19</v>
       </c>
       <c r="AB8">
-        <v>-0.52</v>
+        <v>-2.34</v>
       </c>
       <c r="AC8">
-        <v>35.28</v>
+        <v>10.55</v>
       </c>
       <c r="AD8">
-        <v>60.04</v>
+        <v>37.03</v>
       </c>
       <c r="AE8">
-        <v>15.57</v>
+        <v>17.26</v>
       </c>
       <c r="AF8">
-        <v>-38.17</v>
+        <v>112.13</v>
       </c>
       <c r="AG8">
-        <v>619.9400000000001</v>
+        <v>616.52</v>
       </c>
       <c r="AH8">
-        <v>544.8</v>
+        <v>538.65</v>
       </c>
       <c r="AI8">
-        <v>599.86</v>
+        <v>591.96</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>33.97</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1693,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>178.51</v>
+        <v>173.1</v>
       </c>
       <c r="D9">
-        <v>-0.64</v>
+        <v>-3.03</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1705,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-35.7</v>
+        <v>-37.64</v>
       </c>
       <c r="H9">
-        <v>3.6</v>
+        <v>0.46</v>
       </c>
       <c r="I9">
-        <v>-5.15</v>
+        <v>-9.15</v>
       </c>
       <c r="J9">
-        <v>-2.75</v>
+        <v>-5.46</v>
       </c>
       <c r="K9">
-        <v>-6</v>
+        <v>-7.64</v>
       </c>
       <c r="L9">
-        <v>-32.93</v>
+        <v>-33.8</v>
       </c>
       <c r="M9">
-        <v>-8.300000000000001</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="N9">
         <v>44</v>
       </c>
       <c r="O9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P9">
-        <v>183.33</v>
+        <v>179.84</v>
       </c>
       <c r="Q9">
-        <v>182.75</v>
+        <v>182.1</v>
       </c>
       <c r="R9">
-        <v>187.19</v>
+        <v>186.8</v>
       </c>
       <c r="S9">
-        <v>192.94</v>
+        <v>192.62</v>
       </c>
       <c r="T9">
-        <v>-7.48</v>
+        <v>-10.14</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,43 +1759,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>41.16</v>
+        <v>35.16</v>
       </c>
       <c r="Z9">
-        <v>-1.09</v>
+        <v>-1.79</v>
       </c>
       <c r="AA9">
-        <v>-0.98</v>
+        <v>-1.14</v>
       </c>
       <c r="AB9">
-        <v>-0.11</v>
+        <v>-0.65</v>
       </c>
       <c r="AC9">
-        <v>41.5</v>
+        <v>29.37</v>
       </c>
       <c r="AD9">
-        <v>57.47</v>
+        <v>42.21</v>
       </c>
       <c r="AE9">
-        <v>5.49</v>
+        <v>5.58</v>
       </c>
       <c r="AF9">
-        <v>-66.89</v>
+        <v>-47.39</v>
       </c>
       <c r="AG9">
-        <v>191.2</v>
+        <v>191.41</v>
       </c>
       <c r="AH9">
-        <v>174.3</v>
+        <v>172.79</v>
       </c>
       <c r="AI9">
-        <v>176.41</v>
+        <v>192.28</v>
       </c>
       <c r="AJ9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AK9">
-        <v>20.62</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1806,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>61.4</v>
+        <v>60.22</v>
       </c>
       <c r="D10">
-        <v>-2.85</v>
+        <v>-1.92</v>
       </c>
       <c r="E10">
         <v>101.33</v>
@@ -1818,46 +1818,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-39.41</v>
+        <v>-40.57</v>
       </c>
       <c r="H10">
-        <v>3.58</v>
+        <v>1.59</v>
       </c>
       <c r="I10">
-        <v>-6.94</v>
+        <v>-7.84</v>
       </c>
       <c r="J10">
-        <v>-14.21</v>
+        <v>-16.72</v>
       </c>
       <c r="K10">
-        <v>-19.23</v>
+        <v>-20.43</v>
       </c>
       <c r="L10">
-        <v>-35.12</v>
+        <v>-36.48</v>
       </c>
       <c r="M10">
-        <v>-5.33</v>
+        <v>-5.3</v>
       </c>
       <c r="N10">
         <v>11</v>
       </c>
       <c r="O10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P10">
-        <v>63.62</v>
+        <v>62.6</v>
       </c>
       <c r="Q10">
-        <v>66.53</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="R10">
-        <v>70.70999999999999</v>
+        <v>70.37</v>
       </c>
       <c r="S10">
-        <v>77.98999999999999</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="T10">
-        <v>-21.27</v>
+        <v>-22.58</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,43 +1872,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>23.61</v>
+        <v>21.34</v>
       </c>
       <c r="Z10">
-        <v>-2.31</v>
+        <v>-2.51</v>
       </c>
       <c r="AA10">
-        <v>-2.07</v>
+        <v>-2.16</v>
       </c>
       <c r="AB10">
-        <v>-0.24</v>
+        <v>-0.35</v>
       </c>
       <c r="AC10">
-        <v>33.05</v>
+        <v>20.99</v>
       </c>
       <c r="AD10">
-        <v>49.4</v>
+        <v>35.88</v>
       </c>
       <c r="AE10">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AF10">
-        <v>-35.93</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="AG10">
-        <v>71.88</v>
+        <v>71.58</v>
       </c>
       <c r="AH10">
-        <v>61.18</v>
+        <v>60.39</v>
       </c>
       <c r="AI10">
-        <v>69.54000000000001</v>
+        <v>67.87</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>42.83</v>
+        <v>46.18</v>
       </c>
     </row>
   </sheetData>
@@ -2106,13 +2106,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-7.63</v>
+        <v>-5.52</v>
       </c>
       <c r="D7" s="5">
-        <v>-5.52</v>
+        <v>-6.36</v>
       </c>
       <c r="E7" s="6">
-        <v>2.11</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2123,13 +2123,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-14.09</v>
+        <v>-14.29</v>
       </c>
       <c r="D8" s="5">
-        <v>-14.29</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.2</v>
+        <v>-17.35</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2140,13 +2140,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.7</v>
+        <v>-4.11</v>
       </c>
       <c r="D9" s="5">
-        <v>-4.11</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="E9" s="6">
-        <v>1.59</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2157,13 +2157,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-4.12</v>
+        <v>-2.08</v>
       </c>
       <c r="D10" s="5">
-        <v>-2.08</v>
+        <v>-5.14</v>
       </c>
       <c r="E10" s="6">
-        <v>2.04</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2174,13 +2174,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-9.44</v>
+        <v>-10.3</v>
       </c>
       <c r="D11" s="5">
-        <v>-10.3</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.86</v>
+        <v>-12.04</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2191,13 +2191,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-7.31</v>
+        <v>-7.1</v>
       </c>
       <c r="D12" s="5">
-        <v>-7.1</v>
+        <v>-7.24</v>
       </c>
       <c r="E12" s="6">
-        <v>0.21</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2208,13 +2208,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-15.33</v>
+        <v>-13.4</v>
       </c>
       <c r="D13" s="5">
-        <v>-13.4</v>
+        <v>-15.45</v>
       </c>
       <c r="E13" s="6">
-        <v>1.93</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2225,13 +2225,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-3.91</v>
+        <v>-2.75</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.75</v>
+        <v>-5.46</v>
       </c>
       <c r="E14" s="6">
-        <v>1.16</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2242,13 +2242,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="5">
-        <v>-11.88</v>
+        <v>-14.21</v>
       </c>
       <c r="D15" s="5">
-        <v>-14.21</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.33</v>
+        <v>-16.72</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-2.51</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2259,13 +2259,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>2.34</v>
+        <v>4.49</v>
       </c>
       <c r="D16" s="5">
-        <v>4.49</v>
+        <v>1.93</v>
       </c>
       <c r="E16" s="6">
-        <v>2.15</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2276,13 +2276,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-3.73</v>
+        <v>-6.34</v>
       </c>
       <c r="D17" s="5">
-        <v>-6.34</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.61</v>
+        <v>-8.26</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.92</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2293,13 +2293,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-2.21</v>
+        <v>-5.19</v>
       </c>
       <c r="D18" s="5">
-        <v>-5.19</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.98</v>
+        <v>-9.33</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-4.14</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2310,13 +2310,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-0.8100000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D19" s="5">
-        <v>0.07000000000000001</v>
+        <v>-2.32</v>
       </c>
       <c r="E19" s="6">
-        <v>0.88</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2327,13 +2327,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>0.61</v>
+        <v>-5.06</v>
       </c>
       <c r="D20" s="5">
-        <v>-5.06</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-5.67</v>
+        <v>-7.36</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.3</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2344,13 +2344,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>2.83</v>
+        <v>4.01</v>
       </c>
       <c r="D21" s="5">
-        <v>4.01</v>
+        <v>2.28</v>
       </c>
       <c r="E21" s="6">
-        <v>1.18</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2361,13 +2361,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>-2.24</v>
+        <v>-4.94</v>
       </c>
       <c r="D22" s="5">
-        <v>-4.94</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.7</v>
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-3.26</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2378,13 +2378,13 @@
         <v>8</v>
       </c>
       <c r="C23" s="5">
-        <v>-2.84</v>
+        <v>-5.15</v>
       </c>
       <c r="D23" s="5">
-        <v>-5.15</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.31</v>
+        <v>-9.15</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2395,13 +2395,13 @@
         <v>8</v>
       </c>
       <c r="C24" s="5">
-        <v>-4.11</v>
+        <v>-6.94</v>
       </c>
       <c r="D24" s="5">
-        <v>-6.94</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.83</v>
+        <v>-7.84</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2412,13 +2412,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-36.99</v>
+        <v>-35.82</v>
       </c>
       <c r="D25" s="5">
-        <v>-35.82</v>
+        <v>-36.37</v>
       </c>
       <c r="E25" s="6">
-        <v>1.17</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2429,13 +2429,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>2.48</v>
+        <v>-0.25</v>
       </c>
       <c r="D26" s="5">
-        <v>-0.25</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.73</v>
+        <v>-2.8</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.55</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2446,13 +2446,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>20.57</v>
+        <v>17.89</v>
       </c>
       <c r="D27" s="5">
-        <v>17.89</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.68</v>
+        <v>14.31</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2463,13 +2463,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>21.06</v>
+        <v>18.78</v>
       </c>
       <c r="D28" s="5">
-        <v>18.78</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.28</v>
+        <v>15.58</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-3.2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2480,13 +2480,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>18.78</v>
+        <v>17.73</v>
       </c>
       <c r="D29" s="5">
-        <v>17.73</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.05</v>
+        <v>9.68</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-8.050000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2497,13 +2497,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-36.21</v>
+        <v>-35.97</v>
       </c>
       <c r="D30" s="5">
-        <v>-35.97</v>
+        <v>-36</v>
       </c>
       <c r="E30" s="6">
-        <v>0.24</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2514,13 +2514,13 @@
         <v>11</v>
       </c>
       <c r="C31" s="5">
-        <v>-9.6</v>
+        <v>-11.04</v>
       </c>
       <c r="D31" s="5">
-        <v>-11.04</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.44</v>
+        <v>-14.54</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2531,13 +2531,13 @@
         <v>11</v>
       </c>
       <c r="C32" s="5">
-        <v>-32.94</v>
+        <v>-32.93</v>
       </c>
       <c r="D32" s="5">
-        <v>-32.93</v>
+        <v>-33.8</v>
       </c>
       <c r="E32" s="6">
-        <v>0.01</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2548,13 +2548,13 @@
         <v>11</v>
       </c>
       <c r="C33" s="5">
-        <v>-33.46</v>
+        <v>-35.12</v>
       </c>
       <c r="D33" s="5">
-        <v>-35.12</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.66</v>
+        <v>-36.48</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2565,13 +2565,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-16.16</v>
+        <v>-12.66</v>
       </c>
       <c r="D34" s="5">
-        <v>-12.66</v>
+        <v>-13.08</v>
       </c>
       <c r="E34" s="6">
-        <v>3.5</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2582,13 +2582,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>-18.48</v>
+        <v>-18.99</v>
       </c>
       <c r="D35" s="5">
-        <v>-18.99</v>
+        <v>-17.71</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.51</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2599,13 +2599,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>-18.38</v>
+        <v>-15.1</v>
       </c>
       <c r="D36" s="5">
-        <v>-15.1</v>
-      </c>
-      <c r="E36" s="6">
-        <v>3.28</v>
+        <v>-14.12</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.98</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2616,13 +2616,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-5.29</v>
+        <v>-3.81</v>
       </c>
       <c r="D37" s="5">
-        <v>-3.81</v>
+        <v>-4.26</v>
       </c>
       <c r="E37" s="6">
-        <v>1.48</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2633,13 +2633,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>-15.1</v>
+        <v>-14.6</v>
       </c>
       <c r="D38" s="5">
-        <v>-14.6</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.5</v>
+        <v>-14.23</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.37</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2650,13 +2650,13 @@
         <v>10</v>
       </c>
       <c r="C39" s="5">
-        <v>-18.36</v>
+        <v>-15.74</v>
       </c>
       <c r="D39" s="5">
-        <v>-15.74</v>
-      </c>
-      <c r="E39" s="6">
-        <v>2.62</v>
+        <v>-15.26</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2667,13 +2667,13 @@
         <v>10</v>
       </c>
       <c r="C40" s="5">
-        <v>-20.13</v>
+        <v>-18.89</v>
       </c>
       <c r="D40" s="5">
-        <v>-18.89</v>
+        <v>-20.09</v>
       </c>
       <c r="E40" s="6">
-        <v>1.24</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2684,13 +2684,13 @@
         <v>10</v>
       </c>
       <c r="C41" s="5">
-        <v>-7.36</v>
+        <v>-6</v>
       </c>
       <c r="D41" s="5">
-        <v>-6</v>
+        <v>-7.64</v>
       </c>
       <c r="E41" s="6">
-        <v>1.36</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2701,13 +2701,13 @@
         <v>10</v>
       </c>
       <c r="C42" s="5">
-        <v>-20.81</v>
+        <v>-19.23</v>
       </c>
       <c r="D42" s="5">
-        <v>-19.23</v>
+        <v>-20.43</v>
       </c>
       <c r="E42" s="6">
-        <v>1.58</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2718,13 +2718,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-38.84</v>
+        <v>-37.62</v>
       </c>
       <c r="D43" s="5">
-        <v>-37.62</v>
+        <v>-39.07</v>
       </c>
       <c r="E43" s="6">
-        <v>1.22</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2735,13 +2735,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-19.23</v>
+        <v>-20.61</v>
       </c>
       <c r="D44" s="5">
-        <v>-20.61</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.38</v>
+        <v>-22.89</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2752,13 +2752,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-21.56</v>
+        <v>-22.09</v>
       </c>
       <c r="D45" s="5">
-        <v>-22.09</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.53</v>
+        <v>-26.14</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-4.05</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2769,13 +2769,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-7.14</v>
+        <v>-7.07</v>
       </c>
       <c r="D46" s="5">
-        <v>-7.07</v>
+        <v>-9.58</v>
       </c>
       <c r="E46" s="6">
-        <v>0.07000000000000001</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2786,13 +2786,13 @@
         <v>6</v>
       </c>
       <c r="C47" s="5">
-        <v>-24.84</v>
+        <v>-25.57</v>
       </c>
       <c r="D47" s="5">
-        <v>-25.57</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-0.73</v>
+        <v>-26.87</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2803,13 +2803,13 @@
         <v>6</v>
       </c>
       <c r="C48" s="5">
-        <v>-37.34</v>
+        <v>-36.8</v>
       </c>
       <c r="D48" s="5">
-        <v>-36.8</v>
+        <v>-37.51</v>
       </c>
       <c r="E48" s="6">
-        <v>0.54</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2820,13 +2820,13 @@
         <v>6</v>
       </c>
       <c r="C49" s="5">
-        <v>-30.79</v>
+        <v>-31.6</v>
       </c>
       <c r="D49" s="5">
-        <v>-31.6</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-34.49</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-2.89</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2837,13 +2837,13 @@
         <v>6</v>
       </c>
       <c r="C50" s="5">
-        <v>-35.28</v>
+        <v>-35.7</v>
       </c>
       <c r="D50" s="5">
-        <v>-35.7</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.42</v>
+        <v>-37.64</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2854,13 +2854,13 @@
         <v>6</v>
       </c>
       <c r="C51" s="5">
-        <v>-37.63</v>
+        <v>-39.41</v>
       </c>
       <c r="D51" s="5">
-        <v>-39.41</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-1.78</v>
+        <v>-40.57</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2871,13 +2871,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>1163.6</v>
+        <v>1186.9</v>
       </c>
       <c r="D52" s="5">
-        <v>1186.9</v>
+        <v>1159.4</v>
       </c>
       <c r="E52" s="6">
-        <v>23.3</v>
+        <v>-27.5</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2888,13 +2888,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>2594.5</v>
+        <v>2550</v>
       </c>
       <c r="D53" s="5">
-        <v>2550</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-44.5</v>
+        <v>2477</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-73</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2905,13 +2905,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>1258.5</v>
+        <v>1250</v>
       </c>
       <c r="D54" s="5">
-        <v>1250</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-8.5</v>
+        <v>1185.1</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-64.90000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2922,13 +2922,13 @@
         <v>2</v>
       </c>
       <c r="C55" s="5">
-        <v>1748.8</v>
+        <v>1750</v>
       </c>
       <c r="D55" s="5">
-        <v>1750</v>
+        <v>1702.7</v>
       </c>
       <c r="E55" s="6">
-        <v>1.2</v>
+        <v>-47.3</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2939,13 +2939,13 @@
         <v>2</v>
       </c>
       <c r="C56" s="5">
-        <v>187.09</v>
+        <v>185.27</v>
       </c>
       <c r="D56" s="5">
-        <v>185.27</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.82</v>
+        <v>182.04</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-3.23</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2956,13 +2956,13 @@
         <v>2</v>
       </c>
       <c r="C57" s="5">
-        <v>359.9</v>
+        <v>363</v>
       </c>
       <c r="D57" s="5">
-        <v>363</v>
+        <v>358.9</v>
       </c>
       <c r="E57" s="6">
-        <v>3.1</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2973,13 +2973,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="5">
-        <v>559.4</v>
+        <v>552.85</v>
       </c>
       <c r="D58" s="5">
-        <v>552.85</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-6.55</v>
+        <v>529.5</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-23.35</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2990,13 +2990,13 @@
         <v>2</v>
       </c>
       <c r="C59" s="5">
-        <v>179.66</v>
+        <v>178.51</v>
       </c>
       <c r="D59" s="5">
-        <v>178.51</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-1.15</v>
+        <v>173.1</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-5.41</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -3007,13 +3007,13 @@
         <v>2</v>
       </c>
       <c r="C60" s="5">
-        <v>63.2</v>
+        <v>61.4</v>
       </c>
       <c r="D60" s="5">
-        <v>61.4</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.8</v>
+        <v>60.22</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -3024,13 +3024,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>40.92</v>
+        <v>48.15</v>
       </c>
       <c r="D61" s="5">
-        <v>48.15</v>
+        <v>41.67</v>
       </c>
       <c r="E61" s="6">
-        <v>7.23</v>
+        <v>-6.48</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -3041,13 +3041,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="5">
-        <v>34.35</v>
+        <v>32.14</v>
       </c>
       <c r="D62" s="5">
-        <v>32.14</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-2.21</v>
+        <v>28.87</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3058,13 +3058,13 @@
         <v>24</v>
       </c>
       <c r="C63" s="5">
-        <v>44.54</v>
+        <v>43.33</v>
       </c>
       <c r="D63" s="5">
-        <v>43.33</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-1.21</v>
+        <v>35.41</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-7.92</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3075,13 +3075,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="5">
-        <v>49.28</v>
+        <v>49.48</v>
       </c>
       <c r="D64" s="5">
-        <v>49.48</v>
+        <v>42.52</v>
       </c>
       <c r="E64" s="6">
-        <v>0.2</v>
+        <v>-6.96</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3092,13 +3092,13 @@
         <v>24</v>
       </c>
       <c r="C65" s="5">
-        <v>39</v>
+        <v>37.56</v>
       </c>
       <c r="D65" s="5">
-        <v>37.56</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-1.44</v>
+        <v>35.09</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-2.47</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3109,13 +3109,13 @@
         <v>24</v>
       </c>
       <c r="C66" s="5">
-        <v>42.57</v>
+        <v>45.18</v>
       </c>
       <c r="D66" s="5">
-        <v>45.18</v>
+        <v>42.43</v>
       </c>
       <c r="E66" s="6">
-        <v>2.61</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3126,13 +3126,13 @@
         <v>24</v>
       </c>
       <c r="C67" s="5">
-        <v>35.59</v>
+        <v>33.55</v>
       </c>
       <c r="D67" s="5">
-        <v>33.55</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-2.04</v>
+        <v>27.5</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-6.05</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3143,13 +3143,13 @@
         <v>24</v>
       </c>
       <c r="C68" s="5">
-        <v>42.59</v>
+        <v>41.16</v>
       </c>
       <c r="D68" s="5">
-        <v>41.16</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-1.43</v>
+        <v>35.16</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-6</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="C69" s="5">
-        <v>27.8</v>
+        <v>23.61</v>
       </c>
       <c r="D69" s="5">
-        <v>23.61</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-4.19</v>
+        <v>21.34</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3177,13 +3177,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="5">
-        <v>-32.39</v>
+        <v>40.42</v>
       </c>
       <c r="D70" s="5">
-        <v>40.42</v>
+        <v>-29.03</v>
       </c>
       <c r="E70" s="6">
-        <v>72.81</v>
+        <v>-69.45</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3194,13 +3194,13 @@
         <v>31</v>
       </c>
       <c r="C71" s="5">
-        <v>-36.97</v>
+        <v>-29.98</v>
       </c>
       <c r="D71" s="5">
-        <v>-29.98</v>
-      </c>
-      <c r="E71" s="6">
-        <v>6.99</v>
+        <v>22.79</v>
+      </c>
+      <c r="E71" s="7">
+        <v>52.77</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3211,13 +3211,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="5">
-        <v>-23.14</v>
+        <v>-22.77</v>
       </c>
       <c r="D72" s="5">
-        <v>-22.77</v>
-      </c>
-      <c r="E72" s="6">
-        <v>0.37</v>
+        <v>33.01</v>
+      </c>
+      <c r="E72" s="7">
+        <v>55.78</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -3228,13 +3228,13 @@
         <v>31</v>
       </c>
       <c r="C73" s="5">
-        <v>-23.22</v>
+        <v>-43.77</v>
       </c>
       <c r="D73" s="5">
-        <v>-43.77</v>
+        <v>-43.35</v>
       </c>
       <c r="E73" s="7">
-        <v>-20.55</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -3245,13 +3245,13 @@
         <v>31</v>
       </c>
       <c r="C74" s="5">
-        <v>-10.02</v>
+        <v>-36.23</v>
       </c>
       <c r="D74" s="5">
-        <v>-36.23</v>
+        <v>119.08</v>
       </c>
       <c r="E74" s="7">
-        <v>-26.21</v>
+        <v>155.31</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -3262,13 +3262,13 @@
         <v>31</v>
       </c>
       <c r="C75" s="5">
-        <v>-43.86</v>
+        <v>166.33</v>
       </c>
       <c r="D75" s="5">
-        <v>166.33</v>
+        <v>12.46</v>
       </c>
       <c r="E75" s="6">
-        <v>210.19</v>
+        <v>-153.87</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -3279,13 +3279,13 @@
         <v>31</v>
       </c>
       <c r="C76" s="5">
-        <v>-84.45999999999999</v>
+        <v>-38.17</v>
       </c>
       <c r="D76" s="5">
-        <v>-38.17</v>
-      </c>
-      <c r="E76" s="6">
-        <v>46.29</v>
+        <v>112.13</v>
+      </c>
+      <c r="E76" s="7">
+        <v>150.3</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -3296,13 +3296,13 @@
         <v>31</v>
       </c>
       <c r="C77" s="5">
-        <v>-50.49</v>
+        <v>-66.89</v>
       </c>
       <c r="D77" s="5">
-        <v>-66.89</v>
+        <v>-47.39</v>
       </c>
       <c r="E77" s="7">
-        <v>-16.4</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -3313,13 +3313,13 @@
         <v>31</v>
       </c>
       <c r="C78" s="5">
-        <v>106.05</v>
+        <v>-35.93</v>
       </c>
       <c r="D78" s="5">
-        <v>-35.93</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E78" s="7">
-        <v>-141.98</v>
+        <v>99.97</v>
       </c>
     </row>
   </sheetData>
@@ -3378,22 +3378,22 @@
         <v>46</v>
       </c>
       <c r="B2" s="10">
-        <v>40.88</v>
+        <v>36.44</v>
       </c>
       <c r="C2" s="11">
         <v>9</v>
       </c>
       <c r="D2" s="10">
-        <v>39.4</v>
+        <v>34.4</v>
       </c>
       <c r="E2" s="10">
-        <v>22.2</v>
+        <v>11.1</v>
       </c>
       <c r="F2" s="10">
-        <v>-8.199999999999999</v>
+        <v>-10.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-13.9</v>
+        <v>-14.1</v>
       </c>
       <c r="H2" s="10">
         <v>55</v>
@@ -3510,10 +3510,10 @@
         <v>38</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>42</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>45</v>
@@ -3530,31 +3530,31 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="13">
-        <v>0.5125</v>
+        <v>0.5235</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1874</v>
+        <v>0.1842</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1062</v>
+        <v>0.1015</v>
       </c>
       <c r="D2" s="13">
-        <v>0.007800000000000001</v>
+        <v>-0.0016</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0005999999999999999</v>
+        <v>-0.0029</v>
       </c>
       <c r="F2" s="13">
-        <v>-0.0533</v>
+        <v>-0.053</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.083</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.1091</v>
+        <v>-0.1131</v>
       </c>
       <c r="I2" s="13">
-        <v>-0.1729</v>
+        <v>-0.183</v>
       </c>
     </row>
   </sheetData>

--- a/ADANI_GROUP_Technical_Metrics.xlsx
+++ b/ADANI_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -178,7 +178,46 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.9 → 32.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>42.5 → 50.4</t>
+  </si>
+  <si>
+    <t>42.5</t>
+  </si>
+  <si>
+    <t>50.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -264,14 +303,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -304,13 +343,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,17 +419,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -902,10 +942,10 @@
         <v>46</v>
       </c>
       <c r="C2">
-        <v>1159.4</v>
+        <v>1166.7</v>
       </c>
       <c r="D2">
-        <v>-2.32</v>
+        <v>0.63</v>
       </c>
       <c r="E2">
         <v>1902.69</v>
@@ -914,46 +954,46 @@
         <v>1124.9</v>
       </c>
       <c r="G2">
-        <v>-39.07</v>
+        <v>-38.68</v>
       </c>
       <c r="H2">
-        <v>3.07</v>
+        <v>3.72</v>
       </c>
       <c r="I2">
-        <v>1.93</v>
+        <v>-1.73</v>
       </c>
       <c r="J2">
-        <v>-6.36</v>
+        <v>-6.77</v>
       </c>
       <c r="K2">
-        <v>-13.08</v>
+        <v>-12.99</v>
       </c>
       <c r="L2">
-        <v>-36.37</v>
+        <v>-35.91</v>
       </c>
       <c r="M2">
-        <v>-11.31</v>
+        <v>-11.41</v>
       </c>
       <c r="N2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="O2">
         <v>27</v>
       </c>
       <c r="P2">
-        <v>1172.98</v>
+        <v>1168.88</v>
       </c>
       <c r="Q2">
-        <v>1173.28</v>
+        <v>1169.81</v>
       </c>
       <c r="R2">
-        <v>1237.37</v>
+        <v>1234.05</v>
       </c>
       <c r="S2">
-        <v>1398.46</v>
+        <v>1395.48</v>
       </c>
       <c r="T2">
-        <v>-17.09</v>
+        <v>-16.39</v>
       </c>
       <c r="U2" t="s">
         <v>47</v>
@@ -968,34 +1008,34 @@
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>41.67</v>
+        <v>43.83</v>
       </c>
       <c r="Z2">
-        <v>-22.62</v>
+        <v>-20.94</v>
       </c>
       <c r="AA2">
-        <v>-28.72</v>
+        <v>-27.17</v>
       </c>
       <c r="AB2">
-        <v>6.1</v>
+        <v>6.23</v>
       </c>
       <c r="AC2">
-        <v>85.17</v>
+        <v>87.25</v>
       </c>
       <c r="AD2">
-        <v>86.3</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="AE2">
-        <v>31.19</v>
+        <v>31.31</v>
       </c>
       <c r="AF2">
-        <v>-29.03</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="AG2">
-        <v>1241.6</v>
+        <v>1231.41</v>
       </c>
       <c r="AH2">
-        <v>1104.96</v>
+        <v>1108.21</v>
       </c>
       <c r="AI2">
         <v>1203.99</v>
@@ -1004,7 +1044,7 @@
         <v>49</v>
       </c>
       <c r="AK2">
-        <v>40.42</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1015,10 +1055,10 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>2477</v>
+        <v>2508</v>
       </c>
       <c r="D3">
-        <v>-2.86</v>
+        <v>1.25</v>
       </c>
       <c r="E3">
         <v>3212.1</v>
@@ -1027,46 +1067,46 @@
         <v>1758.01</v>
       </c>
       <c r="G3">
-        <v>-22.89</v>
+        <v>-21.92</v>
       </c>
       <c r="H3">
-        <v>40.9</v>
+        <v>42.66</v>
       </c>
       <c r="I3">
-        <v>-8.26</v>
+        <v>-6.84</v>
       </c>
       <c r="J3">
-        <v>-17.35</v>
+        <v>-16.21</v>
       </c>
       <c r="K3">
-        <v>-17.71</v>
+        <v>-17.13</v>
       </c>
       <c r="L3">
-        <v>-2.8</v>
+        <v>-1.53</v>
       </c>
       <c r="M3">
-        <v>10.15</v>
+        <v>10.24</v>
       </c>
       <c r="N3">
         <v>66</v>
       </c>
       <c r="O3">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P3">
-        <v>2594.2</v>
+        <v>2557.4</v>
       </c>
       <c r="Q3">
-        <v>2737.33</v>
+        <v>2717.73</v>
       </c>
       <c r="R3">
-        <v>2892.76</v>
+        <v>2883.21</v>
       </c>
       <c r="S3">
-        <v>2601.81</v>
+        <v>2602.96</v>
       </c>
       <c r="T3">
-        <v>-4.8</v>
+        <v>-3.65</v>
       </c>
       <c r="U3" t="s">
         <v>47</v>
@@ -1081,43 +1121,43 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>28.87</v>
+        <v>32.03</v>
       </c>
       <c r="Z3">
-        <v>-101.41</v>
+        <v>-105.33</v>
       </c>
       <c r="AA3">
-        <v>-83.23999999999999</v>
+        <v>-87.66</v>
       </c>
       <c r="AB3">
-        <v>-18.16</v>
+        <v>-17.67</v>
       </c>
       <c r="AC3">
-        <v>10.19</v>
+        <v>10.02</v>
       </c>
       <c r="AD3">
-        <v>22.19</v>
+        <v>14.03</v>
       </c>
       <c r="AE3">
-        <v>81.34</v>
+        <v>80.25</v>
       </c>
       <c r="AF3">
-        <v>22.79</v>
+        <v>-4.29</v>
       </c>
       <c r="AG3">
-        <v>3013.65</v>
+        <v>3000.99</v>
       </c>
       <c r="AH3">
-        <v>2461.01</v>
+        <v>2434.47</v>
       </c>
       <c r="AI3">
-        <v>2750.63</v>
+        <v>2720.65</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>53.66</v>
+        <v>56.42</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1128,10 +1168,10 @@
         <v>46</v>
       </c>
       <c r="C4">
-        <v>1185.1</v>
+        <v>1250</v>
       </c>
       <c r="D4">
-        <v>-5.19</v>
+        <v>5.48</v>
       </c>
       <c r="E4">
         <v>1604.5</v>
@@ -1140,46 +1180,46 @@
         <v>772.8</v>
       </c>
       <c r="G4">
-        <v>-26.14</v>
+        <v>-22.09</v>
       </c>
       <c r="H4">
-        <v>53.35</v>
+        <v>61.75</v>
       </c>
       <c r="I4">
-        <v>-9.33</v>
+        <v>-3.99</v>
       </c>
       <c r="J4">
-        <v>-9.119999999999999</v>
+        <v>-3.91</v>
       </c>
       <c r="K4">
-        <v>-14.12</v>
+        <v>-10.4</v>
       </c>
       <c r="L4">
-        <v>14.31</v>
+        <v>20.88</v>
       </c>
       <c r="M4">
-        <v>-0.29</v>
+        <v>1.16</v>
       </c>
       <c r="N4">
         <v>88</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="P4">
-        <v>1258.16</v>
+        <v>1247.76</v>
       </c>
       <c r="Q4">
-        <v>1276.65</v>
+        <v>1275.14</v>
       </c>
       <c r="R4">
-        <v>1290.84</v>
+        <v>1289.19</v>
       </c>
       <c r="S4">
-        <v>1218.35</v>
+        <v>1219.45</v>
       </c>
       <c r="T4">
-        <v>-2.73</v>
+        <v>2.51</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1191,37 +1231,37 @@
         <v>47</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>35.41</v>
+        <v>46.03</v>
       </c>
       <c r="Z4">
-        <v>-13.93</v>
+        <v>-14.21</v>
       </c>
       <c r="AA4">
-        <v>-7.41</v>
+        <v>-8.77</v>
       </c>
       <c r="AB4">
-        <v>-6.52</v>
+        <v>-5.44</v>
       </c>
       <c r="AC4">
-        <v>9.109999999999999</v>
+        <v>19.37</v>
       </c>
       <c r="AD4">
-        <v>27.34</v>
+        <v>18.49</v>
       </c>
       <c r="AE4">
-        <v>44.98</v>
+        <v>47.12</v>
       </c>
       <c r="AF4">
-        <v>33.01</v>
+        <v>-12.26</v>
       </c>
       <c r="AG4">
-        <v>1346.68</v>
+        <v>1346.15</v>
       </c>
       <c r="AH4">
-        <v>1206.62</v>
+        <v>1204.14</v>
       </c>
       <c r="AI4">
         <v>1344.34</v>
@@ -1230,7 +1270,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>24.13</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1241,10 +1281,10 @@
         <v>46</v>
       </c>
       <c r="C5">
-        <v>1702.7</v>
+        <v>1752.5</v>
       </c>
       <c r="D5">
-        <v>-2.7</v>
+        <v>2.92</v>
       </c>
       <c r="E5">
         <v>1883.2</v>
@@ -1253,46 +1293,46 @@
         <v>1298.13</v>
       </c>
       <c r="G5">
-        <v>-9.58</v>
+        <v>-6.94</v>
       </c>
       <c r="H5">
-        <v>31.17</v>
+        <v>35</v>
       </c>
       <c r="I5">
-        <v>-2.32</v>
+        <v>0.1</v>
       </c>
       <c r="J5">
-        <v>-5.14</v>
+        <v>-3.03</v>
       </c>
       <c r="K5">
-        <v>-4.26</v>
+        <v>-0.89</v>
       </c>
       <c r="L5">
-        <v>15.58</v>
+        <v>19.97</v>
       </c>
       <c r="M5">
-        <v>18.42</v>
+        <v>19.15</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P5">
-        <v>1743.66</v>
+        <v>1744</v>
       </c>
       <c r="Q5">
-        <v>1758.94</v>
+        <v>1757.3</v>
       </c>
       <c r="R5">
-        <v>1731.56</v>
+        <v>1733.31</v>
       </c>
       <c r="S5">
-        <v>1645.09</v>
+        <v>1646.42</v>
       </c>
       <c r="T5">
-        <v>3.5</v>
+        <v>6.44</v>
       </c>
       <c r="U5" t="s">
         <v>48</v>
@@ -1307,34 +1347,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>42.52</v>
+        <v>50.42</v>
       </c>
       <c r="Z5">
-        <v>-2.81</v>
+        <v>-2.14</v>
       </c>
       <c r="AA5">
-        <v>3.06</v>
+        <v>2.02</v>
       </c>
       <c r="AB5">
-        <v>-5.87</v>
+        <v>-4.16</v>
       </c>
       <c r="AC5">
-        <v>32.53</v>
+        <v>42.55</v>
       </c>
       <c r="AD5">
-        <v>41.36</v>
+        <v>41.43</v>
       </c>
       <c r="AE5">
-        <v>45.77</v>
+        <v>47.11</v>
       </c>
       <c r="AF5">
-        <v>-43.35</v>
+        <v>-34.75</v>
       </c>
       <c r="AG5">
-        <v>1815.33</v>
+        <v>1812.35</v>
       </c>
       <c r="AH5">
-        <v>1702.55</v>
+        <v>1702.25</v>
       </c>
       <c r="AI5">
         <v>1679.97</v>
@@ -1343,7 +1383,7 @@
         <v>50</v>
       </c>
       <c r="AK5">
-        <v>31.07</v>
+        <v>32.45</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1354,10 +1394,10 @@
         <v>46</v>
       </c>
       <c r="C6">
-        <v>182.04</v>
+        <v>186.55</v>
       </c>
       <c r="D6">
-        <v>-1.74</v>
+        <v>2.48</v>
       </c>
       <c r="E6">
         <v>248.91</v>
@@ -1366,46 +1406,46 @@
         <v>132.96</v>
       </c>
       <c r="G6">
-        <v>-26.87</v>
+        <v>-25.05</v>
       </c>
       <c r="H6">
-        <v>36.91</v>
+        <v>40.31</v>
       </c>
       <c r="I6">
-        <v>-7.36</v>
+        <v>-4.75</v>
       </c>
       <c r="J6">
-        <v>-12.04</v>
+        <v>-8.91</v>
       </c>
       <c r="K6">
-        <v>-14.23</v>
+        <v>-12.69</v>
       </c>
       <c r="L6">
-        <v>9.68</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M6">
-        <v>52.35</v>
+        <v>52.75</v>
       </c>
       <c r="N6">
         <v>77</v>
       </c>
       <c r="O6">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P6">
-        <v>188.87</v>
+        <v>187.01</v>
       </c>
       <c r="Q6">
-        <v>194</v>
+        <v>193.36</v>
       </c>
       <c r="R6">
-        <v>201.56</v>
+        <v>201.15</v>
       </c>
       <c r="S6">
-        <v>191.46</v>
+        <v>191.66</v>
       </c>
       <c r="T6">
-        <v>-4.92</v>
+        <v>-2.67</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1420,34 +1460,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>35.09</v>
+        <v>40.94</v>
       </c>
       <c r="Z6">
-        <v>-4.64</v>
+        <v>-4.63</v>
       </c>
       <c r="AA6">
-        <v>-3.92</v>
+        <v>-4.06</v>
       </c>
       <c r="AB6">
-        <v>-0.72</v>
+        <v>-0.57</v>
       </c>
       <c r="AC6">
-        <v>15.17</v>
+        <v>20.85</v>
       </c>
       <c r="AD6">
-        <v>39.23</v>
+        <v>25.26</v>
       </c>
       <c r="AE6">
-        <v>6.77</v>
+        <v>6.92</v>
       </c>
       <c r="AF6">
-        <v>119.08</v>
+        <v>1.76</v>
       </c>
       <c r="AG6">
-        <v>207.13</v>
+        <v>206.62</v>
       </c>
       <c r="AH6">
-        <v>180.87</v>
+        <v>180.09</v>
       </c>
       <c r="AI6">
         <v>200.91</v>
@@ -1456,7 +1496,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>34.92</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1467,10 +1507,10 @@
         <v>46</v>
       </c>
       <c r="C7">
-        <v>358.9</v>
+        <v>368</v>
       </c>
       <c r="D7">
-        <v>-1.13</v>
+        <v>2.54</v>
       </c>
       <c r="E7">
         <v>574.36</v>
@@ -1479,46 +1519,46 @@
         <v>341</v>
       </c>
       <c r="G7">
-        <v>-37.51</v>
+        <v>-35.93</v>
       </c>
       <c r="H7">
-        <v>5.25</v>
+        <v>7.92</v>
       </c>
       <c r="I7">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="J7">
-        <v>-7.24</v>
+        <v>-6.3</v>
       </c>
       <c r="K7">
-        <v>-15.26</v>
+        <v>-13.44</v>
       </c>
       <c r="L7">
-        <v>-36</v>
+        <v>-34.6</v>
       </c>
       <c r="M7">
-        <v>-0.16</v>
+        <v>0.11</v>
       </c>
       <c r="N7">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="O7">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="P7">
-        <v>360.73</v>
+        <v>362.33</v>
       </c>
       <c r="Q7">
-        <v>361.16</v>
+        <v>360.36</v>
       </c>
       <c r="R7">
-        <v>386.16</v>
+        <v>385.1</v>
       </c>
       <c r="S7">
-        <v>441.18</v>
+        <v>440.17</v>
       </c>
       <c r="T7">
-        <v>-18.65</v>
+        <v>-16.4</v>
       </c>
       <c r="U7" t="s">
         <v>47</v>
@@ -1533,34 +1573,34 @@
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>42.43</v>
+        <v>49.74</v>
       </c>
       <c r="Z7">
-        <v>-8.41</v>
+        <v>-7.09</v>
       </c>
       <c r="AA7">
-        <v>-10.79</v>
+        <v>-10.05</v>
       </c>
       <c r="AB7">
-        <v>2.38</v>
+        <v>2.96</v>
       </c>
       <c r="AC7">
-        <v>93.64</v>
+        <v>95.69</v>
       </c>
       <c r="AD7">
-        <v>96.52</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="AE7">
-        <v>11</v>
+        <v>11.96</v>
       </c>
       <c r="AF7">
-        <v>12.46</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="AG7">
-        <v>384.15</v>
+        <v>380.96</v>
       </c>
       <c r="AH7">
-        <v>338.18</v>
+        <v>339.75</v>
       </c>
       <c r="AI7">
         <v>375.26</v>
@@ -1569,7 +1609,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>35.28</v>
+        <v>36.68</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1580,10 +1620,10 @@
         <v>46</v>
       </c>
       <c r="C8">
-        <v>529.5</v>
+        <v>532</v>
       </c>
       <c r="D8">
-        <v>-4.22</v>
+        <v>0.47</v>
       </c>
       <c r="E8">
         <v>808.27</v>
@@ -1592,46 +1632,46 @@
         <v>467.74</v>
       </c>
       <c r="G8">
-        <v>-34.49</v>
+        <v>-34.18</v>
       </c>
       <c r="H8">
-        <v>13.2</v>
+        <v>13.74</v>
       </c>
       <c r="I8">
-        <v>-8.199999999999999</v>
+        <v>-8.17</v>
       </c>
       <c r="J8">
-        <v>-15.45</v>
+        <v>-14.91</v>
       </c>
       <c r="K8">
-        <v>-20.09</v>
+        <v>-18.51</v>
       </c>
       <c r="L8">
-        <v>-14.54</v>
+        <v>-14.26</v>
       </c>
       <c r="M8">
-        <v>-18.3</v>
+        <v>-17.97</v>
       </c>
       <c r="N8">
         <v>55</v>
       </c>
       <c r="O8">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="P8">
-        <v>558.95</v>
+        <v>549.48</v>
       </c>
       <c r="Q8">
-        <v>577.58</v>
+        <v>573.5599999999999</v>
       </c>
       <c r="R8">
-        <v>607.84</v>
+        <v>605.27</v>
       </c>
       <c r="S8">
-        <v>614.14</v>
+        <v>613.91</v>
       </c>
       <c r="T8">
-        <v>-13.78</v>
+        <v>-13.34</v>
       </c>
       <c r="U8" t="s">
         <v>47</v>
@@ -1646,43 +1686,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>27.5</v>
+        <v>28.98</v>
       </c>
       <c r="Z8">
-        <v>-16.53</v>
+        <v>-18.02</v>
       </c>
       <c r="AA8">
-        <v>-14.19</v>
+        <v>-14.96</v>
       </c>
       <c r="AB8">
-        <v>-2.34</v>
+        <v>-3.07</v>
       </c>
       <c r="AC8">
-        <v>10.55</v>
+        <v>5.1</v>
       </c>
       <c r="AD8">
-        <v>37.03</v>
+        <v>16.97</v>
       </c>
       <c r="AE8">
-        <v>17.26</v>
+        <v>17.42</v>
       </c>
       <c r="AF8">
-        <v>112.13</v>
+        <v>25.95</v>
       </c>
       <c r="AG8">
-        <v>616.52</v>
+        <v>613.9400000000001</v>
       </c>
       <c r="AH8">
-        <v>538.65</v>
+        <v>533.1900000000001</v>
       </c>
       <c r="AI8">
-        <v>591.96</v>
+        <v>581.1</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>38.99</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1693,10 +1733,10 @@
         <v>46</v>
       </c>
       <c r="C9">
-        <v>173.1</v>
+        <v>172.77</v>
       </c>
       <c r="D9">
-        <v>-3.03</v>
+        <v>-0.19</v>
       </c>
       <c r="E9">
         <v>277.6</v>
@@ -1705,46 +1745,46 @@
         <v>172.3</v>
       </c>
       <c r="G9">
-        <v>-37.64</v>
+        <v>-37.76</v>
       </c>
       <c r="H9">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="I9">
-        <v>-9.15</v>
+        <v>-7.76</v>
       </c>
       <c r="J9">
-        <v>-5.46</v>
+        <v>-7.2</v>
       </c>
       <c r="K9">
-        <v>-7.64</v>
+        <v>-8.18</v>
       </c>
       <c r="L9">
-        <v>-33.8</v>
+        <v>-33.18</v>
       </c>
       <c r="M9">
-        <v>-8.890000000000001</v>
+        <v>-8.91</v>
       </c>
       <c r="N9">
         <v>44</v>
       </c>
       <c r="O9">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P9">
-        <v>179.84</v>
+        <v>176.93</v>
       </c>
       <c r="Q9">
-        <v>182.1</v>
+        <v>181.5</v>
       </c>
       <c r="R9">
-        <v>186.8</v>
+        <v>186.37</v>
       </c>
       <c r="S9">
-        <v>192.62</v>
+        <v>192.32</v>
       </c>
       <c r="T9">
-        <v>-10.14</v>
+        <v>-10.16</v>
       </c>
       <c r="U9" t="s">
         <v>47</v>
@@ -1759,43 +1799,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>35.16</v>
+        <v>34.83</v>
       </c>
       <c r="Z9">
-        <v>-1.79</v>
+        <v>-2.35</v>
       </c>
       <c r="AA9">
-        <v>-1.14</v>
+        <v>-1.38</v>
       </c>
       <c r="AB9">
-        <v>-0.65</v>
+        <v>-0.97</v>
       </c>
       <c r="AC9">
-        <v>29.37</v>
+        <v>15.44</v>
       </c>
       <c r="AD9">
-        <v>42.21</v>
+        <v>28.77</v>
       </c>
       <c r="AE9">
-        <v>5.58</v>
+        <v>5.44</v>
       </c>
       <c r="AF9">
-        <v>-47.39</v>
+        <v>-57.1</v>
       </c>
       <c r="AG9">
-        <v>191.41</v>
+        <v>191.61</v>
       </c>
       <c r="AH9">
-        <v>172.79</v>
+        <v>171.4</v>
       </c>
       <c r="AI9">
-        <v>192.28</v>
+        <v>189.15</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>20.95</v>
+        <v>21.81</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1806,10 +1846,10 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>60.22</v>
+        <v>61.03</v>
       </c>
       <c r="D10">
-        <v>-1.92</v>
+        <v>1.35</v>
       </c>
       <c r="E10">
         <v>101.33</v>
@@ -1818,46 +1858,46 @@
         <v>59.28</v>
       </c>
       <c r="G10">
-        <v>-40.57</v>
+        <v>-39.77</v>
       </c>
       <c r="H10">
-        <v>1.59</v>
+        <v>2.95</v>
       </c>
       <c r="I10">
-        <v>-7.84</v>
+        <v>-6.34</v>
       </c>
       <c r="J10">
-        <v>-16.72</v>
+        <v>-14.18</v>
       </c>
       <c r="K10">
-        <v>-20.43</v>
+        <v>-20.39</v>
       </c>
       <c r="L10">
-        <v>-36.48</v>
+        <v>-35.71</v>
       </c>
       <c r="M10">
-        <v>-5.3</v>
+        <v>-5.21</v>
       </c>
       <c r="N10">
         <v>11</v>
       </c>
       <c r="O10">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P10">
-        <v>62.6</v>
+        <v>61.77</v>
       </c>
       <c r="Q10">
-        <v>65.98999999999999</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="R10">
-        <v>70.37</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="S10">
-        <v>77.79000000000001</v>
+        <v>77.59</v>
       </c>
       <c r="T10">
-        <v>-22.58</v>
+        <v>-21.35</v>
       </c>
       <c r="U10" t="s">
         <v>47</v>
@@ -1872,43 +1912,43 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>21.34</v>
+        <v>26.56</v>
       </c>
       <c r="Z10">
-        <v>-2.51</v>
+        <v>-2.57</v>
       </c>
       <c r="AA10">
-        <v>-2.16</v>
+        <v>-2.24</v>
       </c>
       <c r="AB10">
-        <v>-0.35</v>
+        <v>-0.33</v>
       </c>
       <c r="AC10">
-        <v>20.99</v>
+        <v>18.51</v>
       </c>
       <c r="AD10">
-        <v>35.88</v>
+        <v>24.18</v>
       </c>
       <c r="AE10">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AF10">
-        <v>64.04000000000001</v>
+        <v>-4.66</v>
       </c>
       <c r="AG10">
-        <v>71.58</v>
+        <v>71.23</v>
       </c>
       <c r="AH10">
-        <v>60.39</v>
+        <v>59.85</v>
       </c>
       <c r="AI10">
-        <v>67.87</v>
+        <v>67.53</v>
       </c>
       <c r="AJ10" t="s">
         <v>49</v>
       </c>
       <c r="AK10">
-        <v>46.18</v>
+        <v>49.68</v>
       </c>
     </row>
   </sheetData>
@@ -2049,7 +2089,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2069,1263 +2109,1352 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-5.52</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-6.36</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-6.77</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-14.29</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-17.35</v>
       </c>
-      <c r="E8" s="6">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-16.21</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-4.11</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-9.119999999999999</v>
       </c>
-      <c r="E9" s="6">
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-3.91</v>
+      </c>
+      <c r="E10" s="8">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
 